--- a/LoanOfficer-A/LoanBook.xlsx
+++ b/LoanOfficer-A/LoanBook.xlsx
@@ -38,6 +38,7 @@
     <externalReference r:id="rId27"/>
     <externalReference r:id="rId28"/>
     <externalReference r:id="rId29"/>
+    <externalReference r:id="rId30"/>
   </externalReferences>
   <calcPr calcId="124519" iterateDelta="1E-4"/>
   <extLst>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="56">
   <si>
     <t>Code</t>
   </si>
@@ -214,6 +215,9 @@
   </si>
   <si>
     <t>RK Smitha</t>
+  </si>
+  <si>
+    <t>Sheenarani</t>
   </si>
 </sst>
 </file>
@@ -554,18 +558,18 @@
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>34</v>
+            <v>33</v>
           </cell>
           <cell r="O1">
-            <v>24500</v>
+            <v>26250</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>14</v>
+            <v>15</v>
           </cell>
           <cell r="O2">
-            <v>59500</v>
+            <v>57750</v>
           </cell>
         </row>
         <row r="3">
@@ -635,18 +639,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>32</v>
+            <v>28</v>
           </cell>
           <cell r="O1">
-            <v>17600</v>
+            <v>18400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>88</v>
+            <v>92</v>
           </cell>
           <cell r="O2">
-            <v>6400</v>
+            <v>5600</v>
           </cell>
         </row>
         <row r="3">
@@ -676,18 +680,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>37</v>
+            <v>36</v>
           </cell>
           <cell r="O1">
-            <v>3850</v>
+            <v>4200</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>11</v>
+            <v>12</v>
           </cell>
           <cell r="O2">
-            <v>12950</v>
+            <v>12600</v>
           </cell>
         </row>
         <row r="3">
@@ -758,18 +762,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>38</v>
+            <v>37</v>
           </cell>
           <cell r="O1">
-            <v>3500</v>
+            <v>3850</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>10</v>
+            <v>11</v>
           </cell>
           <cell r="O2">
-            <v>13300</v>
+            <v>12950</v>
           </cell>
         </row>
         <row r="3">
@@ -800,18 +804,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>38</v>
+            <v>37</v>
           </cell>
           <cell r="O1">
-            <v>3500</v>
+            <v>3850</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>10</v>
+            <v>11</v>
           </cell>
           <cell r="O2">
-            <v>13300</v>
+            <v>12950</v>
           </cell>
         </row>
         <row r="3">
@@ -841,18 +845,18 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>8</v>
+            <v>7</v>
           </cell>
           <cell r="O1">
-            <v>3200</v>
+            <v>3550</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>9</v>
+            <v>10</v>
           </cell>
           <cell r="O2">
-            <v>2800</v>
+            <v>2450</v>
           </cell>
         </row>
         <row r="3">
@@ -881,18 +885,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>40</v>
+            <v>39</v>
           </cell>
           <cell r="O1">
-            <v>2800</v>
+            <v>3150</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>8</v>
+            <v>9</v>
           </cell>
           <cell r="O2">
-            <v>14000</v>
+            <v>13650</v>
           </cell>
         </row>
         <row r="3">
@@ -922,18 +926,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>41</v>
+            <v>40</v>
           </cell>
           <cell r="O1">
-            <v>2450</v>
+            <v>2800</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>7</v>
+            <v>8</v>
           </cell>
           <cell r="O2">
-            <v>14350</v>
+            <v>14000</v>
           </cell>
         </row>
         <row r="3">
@@ -1045,18 +1049,18 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>11</v>
+            <v>10</v>
           </cell>
           <cell r="O1">
-            <v>2150</v>
+            <v>2500</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>6</v>
+            <v>7</v>
           </cell>
           <cell r="O2">
-            <v>3850</v>
+            <v>3500</v>
           </cell>
         </row>
         <row r="3">
@@ -1085,18 +1089,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>85</v>
+            <v>80</v>
           </cell>
           <cell r="O1">
-            <v>3500</v>
+            <v>4000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>35</v>
+            <v>40</v>
           </cell>
           <cell r="O2">
-            <v>8500</v>
+            <v>8000</v>
           </cell>
         </row>
         <row r="3">
@@ -1125,18 +1129,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>80</v>
+            <v>73</v>
           </cell>
           <cell r="O1">
-            <v>4000</v>
+            <v>4700</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>40</v>
+            <v>47</v>
           </cell>
           <cell r="O2">
-            <v>8000</v>
+            <v>7300</v>
           </cell>
         </row>
         <row r="3">
@@ -1166,18 +1170,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>11</v>
+            <v>10</v>
           </cell>
           <cell r="O1">
-            <v>8600</v>
+            <v>10000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>6</v>
+            <v>7</v>
           </cell>
           <cell r="O2">
-            <v>15400</v>
+            <v>14000</v>
           </cell>
         </row>
         <row r="3">
@@ -1208,18 +1212,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>12</v>
+            <v>11</v>
           </cell>
           <cell r="O1">
-            <v>7000</v>
+            <v>8400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>5</v>
+            <v>6</v>
           </cell>
           <cell r="O2">
-            <v>17000</v>
+            <v>15600</v>
           </cell>
         </row>
         <row r="3">
@@ -1249,18 +1253,18 @@
             <v>30000</v>
           </cell>
           <cell r="K1">
-            <v>102</v>
+            <v>98</v>
           </cell>
           <cell r="O1">
-            <v>5400</v>
+            <v>6600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>18</v>
+            <v>22</v>
           </cell>
           <cell r="O2">
-            <v>30600</v>
+            <v>29400</v>
           </cell>
         </row>
         <row r="3">
@@ -1290,18 +1294,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>46</v>
+            <v>45</v>
           </cell>
           <cell r="O1">
-            <v>700</v>
+            <v>1050</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="O2">
-            <v>16100</v>
+            <v>15750</v>
           </cell>
         </row>
         <row r="3">
@@ -1325,14 +1329,56 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>17</v>
+            <v>16</v>
+          </cell>
+          <cell r="O1">
+            <v>1600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>1</v>
+          </cell>
+          <cell r="O2">
+            <v>22400</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45380</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.10-JAN"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>48</v>
           </cell>
           <cell r="O1">
             <v>0</v>
@@ -1343,11 +1389,11 @@
             <v>0</v>
           </cell>
           <cell r="O2">
-            <v>24000</v>
+            <v>16800</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1573,18 +1619,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>4</v>
+            <v>3</v>
           </cell>
           <cell r="O1">
-            <v>18400</v>
+            <v>19800</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>13</v>
+            <v>14</v>
           </cell>
           <cell r="O2">
-            <v>5600</v>
+            <v>4200</v>
           </cell>
         </row>
         <row r="3">
@@ -1615,18 +1661,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="O1">
-            <v>19800</v>
+            <v>21200</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>14</v>
+            <v>15</v>
           </cell>
           <cell r="O2">
-            <v>4200</v>
+            <v>2800</v>
           </cell>
         </row>
         <row r="3">
@@ -1896,7 +1942,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1904,7 +1950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:Q33"/>
+  <dimension ref="B2:Q34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="1" customWidth="1"/>
@@ -1938,12 +1984,12 @@
       <c r="K2" s="22"/>
       <c r="L2" s="18">
         <f>SUM(L5:L48)</f>
-        <v>276050</v>
+        <v>277900</v>
       </c>
       <c r="M2" s="19"/>
       <c r="N2" s="1">
         <f>SUM(N9:N35)</f>
-        <v>17850</v>
+        <v>18200</v>
       </c>
       <c r="Q2" s="1">
         <f>14900+260750</f>
@@ -2336,11 +2382,11 @@
       <c r="G13" s="9"/>
       <c r="H13" s="9">
         <f>'[8]MD20000.15-DEC'!$K$1</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I13" s="9">
         <f>'[8]MD20000.15-DEC'!$K$2</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J13" s="10" t="s">
         <v>12</v>
@@ -2351,11 +2397,11 @@
       </c>
       <c r="L13" s="8">
         <f>'[8]MD20000.15-DEC'!$O$2</f>
-        <v>5600</v>
+        <v>4200</v>
       </c>
       <c r="M13" s="8">
         <f>'[8]MD20000.15-DEC'!$O$1</f>
-        <v>18400</v>
+        <v>19800</v>
       </c>
       <c r="N13" s="1">
         <v>1400</v>
@@ -2379,11 +2425,11 @@
       <c r="G14" s="14"/>
       <c r="H14" s="14">
         <f>'[9]MD20000.15-DEc'!$K$1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I14" s="14">
         <f>'[9]MD20000.15-DEc'!$K$2</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J14" s="17" t="s">
         <v>12</v>
@@ -2394,11 +2440,11 @@
       </c>
       <c r="L14" s="16">
         <f>'[9]MD20000.15-DEc'!$O$2</f>
-        <v>4200</v>
+        <v>2800</v>
       </c>
       <c r="M14" s="16">
         <f>'[9]MD20000.15-DEc'!$O$1</f>
-        <v>19800</v>
+        <v>21200</v>
       </c>
       <c r="N14" s="1">
         <v>1400</v>
@@ -2422,11 +2468,11 @@
       <c r="G15" s="9"/>
       <c r="H15" s="9">
         <f>'[10]MD50000.15-DEC'!$K$1</f>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I15" s="9">
         <f>'[10]MD50000.15-DEC'!$K$2</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J15" s="10" t="s">
         <v>12</v>
@@ -2437,11 +2483,11 @@
       </c>
       <c r="L15" s="8">
         <f>'[10]MD50000.15-DEC'!$O$2</f>
-        <v>59500</v>
+        <v>57750</v>
       </c>
       <c r="M15" s="8">
         <f>'[10]MD50000.15-DEC'!$O$1</f>
-        <v>24500</v>
+        <v>26250</v>
       </c>
       <c r="N15" s="1">
         <v>1750</v>
@@ -2503,11 +2549,11 @@
       </c>
       <c r="F17" s="9">
         <f>'[12]MD20000.22-DEC'!$K$1</f>
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G17" s="9">
         <f>'[12]MD20000.22-DEC'!$K$2</f>
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
@@ -2520,11 +2566,11 @@
       </c>
       <c r="L17" s="8">
         <f>'[12]MD20000.22-DEC'!$O$2</f>
-        <v>6400</v>
+        <v>5600</v>
       </c>
       <c r="M17" s="8">
         <f>'[12]MD20000.22-DEC'!$O$1</f>
-        <v>17600</v>
+        <v>18400</v>
       </c>
       <c r="N17" s="1">
         <v>1400</v>
@@ -2548,11 +2594,11 @@
       <c r="G18" s="14"/>
       <c r="H18" s="14">
         <f>'[13]MD50000.15-DEC'!$K$1</f>
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I18" s="14">
         <f>'[13]MD50000.15-DEC'!$K$2</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J18" s="17" t="s">
         <v>12</v>
@@ -2563,11 +2609,11 @@
       </c>
       <c r="L18" s="16">
         <f>'[13]MD50000.15-DEC'!$O$2</f>
-        <v>12950</v>
+        <v>12600</v>
       </c>
       <c r="M18" s="16">
         <f>'[13]MD50000.15-DEC'!$O$1</f>
-        <v>3850</v>
+        <v>4200</v>
       </c>
       <c r="N18" s="1">
         <v>350</v>
@@ -2634,11 +2680,11 @@
       <c r="G20" s="14"/>
       <c r="H20" s="14">
         <f>'[15]MD10000.10-JAN'!$K$1</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I20" s="14">
         <f>'[15]MD10000.10-JAN'!$K$2</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J20" s="17" t="s">
         <v>12</v>
@@ -2649,11 +2695,11 @@
       </c>
       <c r="L20" s="16">
         <f>'[15]MD10000.10-JAN'!$O$2</f>
-        <v>13300</v>
+        <v>12950</v>
       </c>
       <c r="M20" s="16">
         <f>'[15]MD10000.10-JAN'!$O$1</f>
-        <v>3500</v>
+        <v>3850</v>
       </c>
       <c r="N20" s="1">
         <v>350</v>
@@ -2677,11 +2723,11 @@
       <c r="G21" s="9"/>
       <c r="H21" s="9">
         <f>'[16]MD10000.10-JAN'!$K$1</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I21" s="9">
         <f>'[16]MD10000.10-JAN'!$K$2</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J21" s="10" t="s">
         <v>12</v>
@@ -2692,11 +2738,11 @@
       </c>
       <c r="L21" s="8">
         <f>'[16]MD10000.10-JAN'!$O$2</f>
-        <v>13300</v>
+        <v>12950</v>
       </c>
       <c r="M21" s="8">
         <f>'[16]MD10000.10-JAN'!$O$1</f>
-        <v>3500</v>
+        <v>3850</v>
       </c>
       <c r="N21" s="1">
         <v>350</v>
@@ -2720,11 +2766,11 @@
       <c r="G22" s="14"/>
       <c r="H22" s="14">
         <f>'[17]MD10000.20-OCT'!$K$1</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I22" s="14">
         <f>'[17]MD10000.20-OCT'!$K$2</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J22" s="17" t="s">
         <v>12</v>
@@ -2735,11 +2781,11 @@
       </c>
       <c r="L22" s="16">
         <f>'[17]MD10000.20-OCT'!$O$2</f>
-        <v>2800</v>
+        <v>2450</v>
       </c>
       <c r="M22" s="16">
         <f>'[17]MD10000.20-OCT'!$O$1</f>
-        <v>3200</v>
+        <v>3550</v>
       </c>
       <c r="N22" s="1">
         <v>350</v>
@@ -2763,11 +2809,11 @@
       <c r="G23" s="9"/>
       <c r="H23" s="9">
         <f>'[18]MD10000.20-OCT'!$K$1</f>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I23" s="9">
         <f>'[18]MD10000.20-OCT'!$K$2</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J23" s="10" t="s">
         <v>12</v>
@@ -2778,11 +2824,11 @@
       </c>
       <c r="L23" s="8">
         <f>'[18]MD10000.20-OCT'!$O$2</f>
-        <v>14000</v>
+        <v>13650</v>
       </c>
       <c r="M23" s="8">
         <f>'[18]MD10000.20-OCT'!$O$1</f>
-        <v>2800</v>
+        <v>3150</v>
       </c>
       <c r="N23" s="1">
         <v>350</v>
@@ -2806,11 +2852,11 @@
       <c r="G24" s="9"/>
       <c r="H24" s="9">
         <f>'[19]MD10000.20-OCT'!$K$1</f>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I24" s="9">
         <f>'[19]MD10000.20-OCT'!$K$2</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J24" s="10" t="s">
         <v>12</v>
@@ -2821,11 +2867,11 @@
       </c>
       <c r="L24" s="8">
         <f>'[19]MD10000.20-OCT'!$O$2</f>
-        <v>14350</v>
+        <v>14000</v>
       </c>
       <c r="M24" s="8">
         <f>'[19]MD10000.20-OCT'!$O$1</f>
-        <v>2450</v>
+        <v>2800</v>
       </c>
       <c r="N24" s="1">
         <v>350</v>
@@ -2892,11 +2938,11 @@
       <c r="G26" s="9"/>
       <c r="H26" s="9">
         <f>'[21]MD10000.20-OCT'!$K$1</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I26" s="9">
         <f>'[21]MD10000.20-OCT'!$K$2</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J26" s="10" t="s">
         <v>12</v>
@@ -2907,11 +2953,11 @@
       </c>
       <c r="L26" s="8">
         <f>'[21]MD10000.20-OCT'!$O$2</f>
-        <v>3850</v>
+        <v>3500</v>
       </c>
       <c r="M26" s="8">
         <f>'[21]MD10000.20-OCT'!$O$1</f>
-        <v>2150</v>
+        <v>2500</v>
       </c>
       <c r="N26" s="1">
         <v>350</v>
@@ -2933,11 +2979,11 @@
       </c>
       <c r="F27" s="14">
         <f>'[22]MD10000.1-OCT'!$K$1</f>
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G27" s="14">
         <f>'[22]MD10000.1-OCT'!$K$2</f>
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H27" s="14"/>
       <c r="I27" s="14"/>
@@ -2950,11 +2996,11 @@
       </c>
       <c r="L27" s="16">
         <f>'[22]MD10000.1-OCT'!$O$2</f>
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="M27" s="16">
         <f>'[22]MD10000.1-OCT'!$O$1</f>
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="N27" s="1">
         <v>700</v>
@@ -2976,11 +3022,11 @@
       </c>
       <c r="F28" s="9">
         <f>'[23]MD10000.1-OCT'!$K$1</f>
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G28" s="9">
         <f>'[23]MD10000.1-OCT'!$K$2</f>
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="H28" s="9"/>
       <c r="I28" s="9"/>
@@ -2993,11 +3039,11 @@
       </c>
       <c r="L28" s="8">
         <f>'[23]MD10000.1-OCT'!$O$2</f>
-        <v>8000</v>
+        <v>7300</v>
       </c>
       <c r="M28" s="8">
         <f>'[23]MD10000.1-OCT'!$O$1</f>
-        <v>4000</v>
+        <v>4700</v>
       </c>
       <c r="N28" s="1">
         <v>700</v>
@@ -3021,11 +3067,11 @@
       <c r="G29" s="9"/>
       <c r="H29" s="9">
         <f>'[24]MD20000.15-DEC'!$K$1</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I29" s="9">
         <f>'[24]MD20000.15-DEC'!$K$2</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J29" s="10" t="s">
         <v>12</v>
@@ -3036,11 +3082,11 @@
       </c>
       <c r="L29" s="8">
         <f>'[24]MD20000.15-DEC'!$O$2</f>
-        <v>15400</v>
+        <v>14000</v>
       </c>
       <c r="M29" s="8">
         <f>'[24]MD20000.15-DEC'!$O$1</f>
-        <v>8600</v>
+        <v>10000</v>
       </c>
       <c r="N29" s="1">
         <v>1400</v>
@@ -3064,11 +3110,11 @@
       <c r="G30" s="9"/>
       <c r="H30" s="9">
         <f>'[25]MD20000.15-DEC'!$K$1</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I30" s="9">
         <f>'[25]MD20000.15-DEC'!$K$2</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J30" s="10" t="s">
         <v>12</v>
@@ -3079,11 +3125,11 @@
       </c>
       <c r="L30" s="8">
         <f>'[25]MD20000.15-DEC'!$O$2</f>
-        <v>17000</v>
+        <v>15600</v>
       </c>
       <c r="M30" s="8">
         <f>'[25]MD20000.15-DEC'!$O$1</f>
-        <v>7000</v>
+        <v>8400</v>
       </c>
       <c r="N30" s="1">
         <v>1400</v>
@@ -3105,11 +3151,11 @@
       </c>
       <c r="F31" s="14">
         <f>'[26]MD20000.18-DEC'!$K$1</f>
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G31" s="14">
         <f>'[26]MD20000.18-DEC'!$K$2</f>
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H31" s="14"/>
       <c r="I31" s="14"/>
@@ -3122,11 +3168,11 @@
       </c>
       <c r="L31" s="16">
         <f>'[26]MD20000.18-DEC'!$O$2</f>
-        <v>30600</v>
+        <v>29400</v>
       </c>
       <c r="M31" s="16">
         <f>'[26]MD20000.18-DEC'!$O$1</f>
-        <v>5400</v>
+        <v>6600</v>
       </c>
       <c r="N31" s="1">
         <v>2100</v>
@@ -3150,11 +3196,11 @@
       <c r="G32" s="14"/>
       <c r="H32" s="14">
         <f>'[27]MD10000.10-JAN'!$K$1</f>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I32" s="14">
         <f>'[27]MD10000.10-JAN'!$K$2</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J32" s="17" t="s">
         <v>12</v>
@@ -3165,11 +3211,11 @@
       </c>
       <c r="L32" s="16">
         <f>'[27]MD10000.10-JAN'!$O$2</f>
-        <v>16100</v>
+        <v>15750</v>
       </c>
       <c r="M32" s="16">
         <f>'[27]MD10000.10-JAN'!$O$1</f>
-        <v>700</v>
+        <v>1050</v>
       </c>
       <c r="N32" s="1">
         <v>350</v>
@@ -3193,29 +3239,72 @@
       <c r="G33" s="14"/>
       <c r="H33" s="14">
         <f>'[28]MD20000.15-DEc'!$K$1</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I33" s="14">
         <f>'[28]MD20000.15-DEc'!$K$2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" s="17" t="s">
         <v>12</v>
       </c>
       <c r="K33" s="15">
         <f>'[28]MD20000.15-DEc'!$B$3</f>
-        <v>0</v>
+        <v>45380</v>
       </c>
       <c r="L33" s="16">
         <f>'[28]MD20000.15-DEc'!$O$2</f>
-        <v>24000</v>
+        <v>22400</v>
       </c>
       <c r="M33" s="16">
         <f>'[28]MD20000.15-DEc'!$O$1</f>
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="N33" s="1">
         <v>1400</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" ht="22.5" customHeight="1">
+      <c r="B34" s="13">
+        <v>30</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E34" s="16">
+        <f>'[29]MD10000.10-JAN'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14">
+        <f>'[29]MD10000.10-JAN'!$K$1</f>
+        <v>48</v>
+      </c>
+      <c r="I34" s="14">
+        <f>'[29]MD10000.10-JAN'!$K$2</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="K34" s="15">
+        <f>'[29]MD10000.10-JAN'!$B$3</f>
+        <v>0</v>
+      </c>
+      <c r="L34" s="16">
+        <f>'[29]MD10000.10-JAN'!$O$2</f>
+        <v>16800</v>
+      </c>
+      <c r="M34" s="16">
+        <f>'[29]MD10000.10-JAN'!$O$1</f>
+        <v>0</v>
+      </c>
+      <c r="N34" s="1">
+        <v>350</v>
       </c>
     </row>
   </sheetData>

--- a/LoanOfficer-A/LoanBook.xlsx
+++ b/LoanOfficer-A/LoanBook.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3600" windowWidth="20640" windowHeight="11760"/>
@@ -39,8 +39,13 @@
     <externalReference r:id="rId28"/>
     <externalReference r:id="rId29"/>
     <externalReference r:id="rId30"/>
+    <externalReference r:id="rId31"/>
+    <externalReference r:id="rId32"/>
+    <externalReference r:id="rId33"/>
+    <externalReference r:id="rId34"/>
+    <externalReference r:id="rId35"/>
   </externalReferences>
-  <calcPr calcId="124519" iterateDelta="1E-4"/>
+  <calcPr calcId="145621" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -50,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="63">
   <si>
     <t>Code</t>
   </si>
@@ -218,18 +223,39 @@
   </si>
   <si>
     <t>Sheenarani</t>
+  </si>
+  <si>
+    <t>Lourembam Ibeyaima</t>
+  </si>
+  <si>
+    <t>Minakumari</t>
+  </si>
+  <si>
+    <t>K. Kamala</t>
+  </si>
+  <si>
+    <t>Ibemcha</t>
+  </si>
+  <si>
+    <t>L50000W17P350-Wed</t>
+  </si>
+  <si>
+    <t>Salam Sunanda</t>
+  </si>
+  <si>
+    <t>L40000W48P1400-Sat</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="166" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -466,7 +492,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanform1"/>
@@ -543,7 +569,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
@@ -558,18 +584,18 @@
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>33</v>
+            <v>29</v>
           </cell>
           <cell r="O1">
-            <v>26250</v>
+            <v>33250</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>15</v>
+            <v>19</v>
           </cell>
           <cell r="O2">
-            <v>57750</v>
+            <v>50750</v>
           </cell>
         </row>
         <row r="3">
@@ -585,7 +611,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
@@ -625,7 +651,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
@@ -639,18 +665,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>28</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
-            <v>18400</v>
+            <v>24000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>92</v>
+            <v>120</v>
           </cell>
           <cell r="O2">
-            <v>5600</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -665,7 +691,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
@@ -680,18 +706,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>36</v>
+            <v>32</v>
           </cell>
           <cell r="O1">
-            <v>4200</v>
+            <v>5600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>12</v>
+            <v>16</v>
           </cell>
           <cell r="O2">
-            <v>12600</v>
+            <v>11200</v>
           </cell>
         </row>
         <row r="3">
@@ -707,7 +733,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
@@ -721,18 +747,18 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>33</v>
+            <v>12</v>
           </cell>
           <cell r="O1">
-            <v>2700</v>
+            <v>4800</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>27</v>
+            <v>48</v>
           </cell>
           <cell r="O2">
-            <v>3300</v>
+            <v>1200</v>
           </cell>
         </row>
         <row r="3">
@@ -747,7 +773,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
@@ -762,18 +788,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>37</v>
+            <v>32</v>
           </cell>
           <cell r="O1">
-            <v>3850</v>
+            <v>5600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>11</v>
+            <v>16</v>
           </cell>
           <cell r="O2">
-            <v>12950</v>
+            <v>11200</v>
           </cell>
         </row>
         <row r="3">
@@ -789,7 +815,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
@@ -804,18 +830,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>37</v>
+            <v>32</v>
           </cell>
           <cell r="O1">
-            <v>3850</v>
+            <v>5600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>11</v>
+            <v>16</v>
           </cell>
           <cell r="O2">
-            <v>12950</v>
+            <v>11200</v>
           </cell>
         </row>
         <row r="3">
@@ -831,7 +857,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
@@ -845,18 +871,18 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>7</v>
+            <v>3</v>
           </cell>
           <cell r="O1">
-            <v>3550</v>
+            <v>4950</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>10</v>
+            <v>14</v>
           </cell>
           <cell r="O2">
-            <v>2450</v>
+            <v>1050</v>
           </cell>
         </row>
         <row r="3">
@@ -871,7 +897,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
@@ -885,18 +911,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>39</v>
+            <v>35</v>
           </cell>
           <cell r="O1">
-            <v>3150</v>
+            <v>4550</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>9</v>
+            <v>13</v>
           </cell>
           <cell r="O2">
-            <v>13650</v>
+            <v>12250</v>
           </cell>
         </row>
         <row r="3">
@@ -911,7 +937,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
@@ -926,18 +952,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>40</v>
+            <v>35</v>
           </cell>
           <cell r="O1">
-            <v>2800</v>
+            <v>4550</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>8</v>
+            <v>13</v>
           </cell>
           <cell r="O2">
-            <v>14000</v>
+            <v>12250</v>
           </cell>
         </row>
         <row r="3">
@@ -953,7 +979,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
@@ -993,7 +1019,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanform1"/>
@@ -1009,18 +1035,18 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>29</v>
+            <v>17</v>
           </cell>
           <cell r="O1">
-            <v>3100</v>
+            <v>4300</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>31</v>
+            <v>43</v>
           </cell>
           <cell r="O2">
-            <v>2900</v>
+            <v>1700</v>
           </cell>
         </row>
         <row r="3">
@@ -1035,7 +1061,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
@@ -1049,18 +1075,18 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>10</v>
+            <v>5</v>
           </cell>
           <cell r="O1">
-            <v>2500</v>
+            <v>4250</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>7</v>
+            <v>12</v>
           </cell>
           <cell r="O2">
-            <v>3500</v>
+            <v>1750</v>
           </cell>
         </row>
         <row r="3">
@@ -1075,7 +1101,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
@@ -1089,18 +1115,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>80</v>
+            <v>61</v>
           </cell>
           <cell r="O1">
-            <v>4000</v>
+            <v>5900</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>40</v>
+            <v>59</v>
           </cell>
           <cell r="O2">
-            <v>8000</v>
+            <v>6100</v>
           </cell>
         </row>
         <row r="3">
@@ -1115,7 +1141,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
@@ -1129,18 +1155,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>73</v>
+            <v>41</v>
           </cell>
           <cell r="O1">
-            <v>4700</v>
+            <v>7900</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>47</v>
+            <v>79</v>
           </cell>
           <cell r="O2">
-            <v>7300</v>
+            <v>4100</v>
           </cell>
         </row>
         <row r="3">
@@ -1155,7 +1181,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
@@ -1170,18 +1196,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>10</v>
+            <v>5</v>
           </cell>
           <cell r="O1">
-            <v>10000</v>
+            <v>17000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>7</v>
+            <v>12</v>
           </cell>
           <cell r="O2">
-            <v>14000</v>
+            <v>7000</v>
           </cell>
         </row>
         <row r="3">
@@ -1197,7 +1223,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
@@ -1212,18 +1238,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>11</v>
+            <v>7</v>
           </cell>
           <cell r="O1">
-            <v>8400</v>
+            <v>14000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>6</v>
+            <v>10</v>
           </cell>
           <cell r="O2">
-            <v>15600</v>
+            <v>10000</v>
           </cell>
         </row>
         <row r="3">
@@ -1239,7 +1265,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
@@ -1253,18 +1279,18 @@
             <v>30000</v>
           </cell>
           <cell r="K1">
-            <v>98</v>
+            <v>72</v>
           </cell>
           <cell r="O1">
-            <v>6600</v>
+            <v>14400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>22</v>
+            <v>48</v>
           </cell>
           <cell r="O2">
-            <v>29400</v>
+            <v>21600</v>
           </cell>
         </row>
         <row r="3">
@@ -1279,7 +1305,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
@@ -1294,18 +1320,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>45</v>
+            <v>41</v>
           </cell>
           <cell r="O1">
-            <v>1050</v>
+            <v>2450</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>3</v>
+            <v>7</v>
           </cell>
           <cell r="O2">
-            <v>15750</v>
+            <v>14350</v>
           </cell>
         </row>
         <row r="3">
@@ -1321,7 +1347,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
@@ -1336,18 +1362,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>16</v>
+            <v>12</v>
           </cell>
           <cell r="O1">
-            <v>1600</v>
+            <v>7200</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>1</v>
+            <v>5</v>
           </cell>
           <cell r="O2">
-            <v>22400</v>
+            <v>16800</v>
           </cell>
         </row>
         <row r="3">
@@ -1363,7 +1389,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
@@ -1378,18 +1404,23 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>48</v>
+            <v>44</v>
           </cell>
           <cell r="O1">
-            <v>0</v>
+            <v>1400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>0</v>
+            <v>4</v>
           </cell>
           <cell r="O2">
-            <v>16800</v>
+            <v>15400</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45389</v>
           </cell>
         </row>
       </sheetData>
@@ -1400,7 +1431,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
@@ -1439,8 +1470,211 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEc"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="G1">
+            <v>17</v>
+          </cell>
+          <cell r="O1">
+            <v>4400</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>3</v>
+          </cell>
+          <cell r="O2">
+            <v>19600</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45394</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.10-JAN"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="G1">
+            <v>48</v>
+          </cell>
+          <cell r="O1">
+            <v>1050</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>3</v>
+          </cell>
+          <cell r="O2">
+            <v>15750</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45399</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEc"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="G1">
+            <v>17</v>
+          </cell>
+          <cell r="O1">
+            <v>3000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>2</v>
+          </cell>
+          <cell r="O2">
+            <v>21000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45406</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.20-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>5000</v>
+          </cell>
+          <cell r="G1">
+            <v>17</v>
+          </cell>
+          <cell r="O1">
+            <v>700</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>2</v>
+          </cell>
+          <cell r="O2">
+            <v>5300</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45406</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD50000.15-DEC"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>40000</v>
+          </cell>
+          <cell r="K1">
+            <v>48</v>
+          </cell>
+          <cell r="O1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>0</v>
+          </cell>
+          <cell r="O2">
+            <v>67200</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
@@ -1480,7 +1714,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanform1"/>
@@ -1522,7 +1756,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
@@ -1562,7 +1796,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
@@ -1604,7 +1838,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
@@ -1619,18 +1853,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
-            <v>19800</v>
+            <v>24000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>14</v>
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>4200</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -1646,7 +1880,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
@@ -1661,18 +1895,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
-            <v>21200</v>
+            <v>24000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>15</v>
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>2800</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -1942,16 +2176,16 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:Q34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:Q39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="6.7109375" style="1" customWidth="1"/>
@@ -1972,7 +2206,7 @@
     <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="22.5" customHeight="1">
+    <row r="2" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="23" t="s">
         <v>8</v>
       </c>
@@ -1984,19 +2218,19 @@
       <c r="K2" s="22"/>
       <c r="L2" s="18">
         <f>SUM(L5:L48)</f>
-        <v>277900</v>
+        <v>338750</v>
       </c>
       <c r="M2" s="19"/>
       <c r="N2" s="1">
         <f>SUM(N9:N35)</f>
-        <v>18200</v>
+        <v>16800</v>
       </c>
       <c r="Q2" s="1">
         <f>14900+260750</f>
         <v>275650</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="18">
+    <row r="3" spans="2:17" ht="18" x14ac:dyDescent="0.2">
       <c r="C3" s="2"/>
       <c r="D3" s="3"/>
       <c r="E3" s="4"/>
@@ -2006,7 +2240,7 @@
       <c r="K3" s="3"/>
       <c r="M3" s="3"/>
     </row>
-    <row r="4" spans="2:17" ht="40.5" customHeight="1">
+    <row r="4" spans="2:17" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="12" t="s">
         <v>6</v>
       </c>
@@ -2044,7 +2278,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:17" ht="22.5" customHeight="1">
+    <row r="5" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="6">
         <v>1</v>
       </c>
@@ -2084,7 +2318,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="22.5" customHeight="1">
+    <row r="6" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13">
         <v>2</v>
       </c>
@@ -2124,7 +2358,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="22.5" customHeight="1">
+    <row r="7" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="6">
         <v>3</v>
       </c>
@@ -2164,7 +2398,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="8" spans="2:17" ht="22.5" customHeight="1">
+    <row r="8" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="13">
         <v>4</v>
       </c>
@@ -2204,7 +2438,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="22.5" customHeight="1">
+    <row r="9" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="6">
         <v>5</v>
       </c>
@@ -2244,7 +2478,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="10" spans="2:17" ht="22.5" customHeight="1">
+    <row r="10" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="13">
         <v>6</v>
       </c>
@@ -2284,7 +2518,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="11" spans="2:17" ht="22.5" customHeight="1">
+    <row r="11" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="6">
         <v>7</v>
       </c>
@@ -2324,7 +2558,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="12" spans="2:17" ht="22.5" customHeight="1">
+    <row r="12" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="13">
         <v>8</v>
       </c>
@@ -2364,7 +2598,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="13" spans="2:17" ht="22.5" customHeight="1">
+    <row r="13" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="6">
         <v>9</v>
       </c>
@@ -2382,14 +2616,14 @@
       <c r="G13" s="9"/>
       <c r="H13" s="9">
         <f>'[8]MD20000.15-DEC'!$K$1</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I13" s="9">
         <f>'[8]MD20000.15-DEC'!$K$2</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="K13" s="11">
         <f>'[8]MD20000.15-DEC'!$B$3</f>
@@ -2397,17 +2631,17 @@
       </c>
       <c r="L13" s="8">
         <f>'[8]MD20000.15-DEC'!$O$2</f>
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="M13" s="8">
         <f>'[8]MD20000.15-DEC'!$O$1</f>
-        <v>19800</v>
+        <v>24000</v>
       </c>
       <c r="N13" s="1">
         <v>1400</v>
       </c>
     </row>
-    <row r="14" spans="2:17" ht="22.5" customHeight="1">
+    <row r="14" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="13">
         <v>10</v>
       </c>
@@ -2425,14 +2659,14 @@
       <c r="G14" s="14"/>
       <c r="H14" s="14">
         <f>'[9]MD20000.15-DEc'!$K$1</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" s="14">
         <f>'[9]MD20000.15-DEc'!$K$2</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J14" s="17" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="K14" s="15">
         <f>'[9]MD20000.15-DEc'!$B$3</f>
@@ -2440,17 +2674,14 @@
       </c>
       <c r="L14" s="16">
         <f>'[9]MD20000.15-DEc'!$O$2</f>
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="M14" s="16">
         <f>'[9]MD20000.15-DEc'!$O$1</f>
-        <v>21200</v>
-      </c>
-      <c r="N14" s="1">
-        <v>1400</v>
+        <v>24000</v>
       </c>
     </row>
-    <row r="15" spans="2:17" ht="22.5" customHeight="1">
+    <row r="15" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="6">
         <v>11</v>
       </c>
@@ -2468,11 +2699,11 @@
       <c r="G15" s="9"/>
       <c r="H15" s="9">
         <f>'[10]MD50000.15-DEC'!$K$1</f>
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I15" s="9">
         <f>'[10]MD50000.15-DEC'!$K$2</f>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J15" s="10" t="s">
         <v>12</v>
@@ -2483,17 +2714,17 @@
       </c>
       <c r="L15" s="8">
         <f>'[10]MD50000.15-DEC'!$O$2</f>
-        <v>57750</v>
+        <v>50750</v>
       </c>
       <c r="M15" s="8">
         <f>'[10]MD50000.15-DEC'!$O$1</f>
-        <v>26250</v>
+        <v>33250</v>
       </c>
       <c r="N15" s="1">
         <v>1750</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="22.5" customHeight="1">
+    <row r="16" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="13">
         <v>12</v>
       </c>
@@ -2533,7 +2764,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="22.5" customHeight="1">
+    <row r="17" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="6">
         <v>13</v>
       </c>
@@ -2549,11 +2780,11 @@
       </c>
       <c r="F17" s="9">
         <f>'[12]MD20000.22-DEC'!$K$1</f>
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G17" s="9">
         <f>'[12]MD20000.22-DEC'!$K$2</f>
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
@@ -2566,17 +2797,17 @@
       </c>
       <c r="L17" s="8">
         <f>'[12]MD20000.22-DEC'!$O$2</f>
-        <v>5600</v>
+        <v>0</v>
       </c>
       <c r="M17" s="8">
         <f>'[12]MD20000.22-DEC'!$O$1</f>
-        <v>18400</v>
+        <v>24000</v>
       </c>
       <c r="N17" s="1">
         <v>1400</v>
       </c>
     </row>
-    <row r="18" spans="2:14" ht="22.5" customHeight="1">
+    <row r="18" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="13">
         <v>14</v>
       </c>
@@ -2594,11 +2825,11 @@
       <c r="G18" s="14"/>
       <c r="H18" s="14">
         <f>'[13]MD50000.15-DEC'!$K$1</f>
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I18" s="14">
         <f>'[13]MD50000.15-DEC'!$K$2</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J18" s="17" t="s">
         <v>12</v>
@@ -2609,17 +2840,17 @@
       </c>
       <c r="L18" s="16">
         <f>'[13]MD50000.15-DEC'!$O$2</f>
-        <v>12600</v>
+        <v>11200</v>
       </c>
       <c r="M18" s="16">
         <f>'[13]MD50000.15-DEC'!$O$1</f>
-        <v>4200</v>
+        <v>5600</v>
       </c>
       <c r="N18" s="1">
         <v>350</v>
       </c>
     </row>
-    <row r="19" spans="2:14" ht="22.5" customHeight="1">
+    <row r="19" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="6">
         <v>15</v>
       </c>
@@ -2635,11 +2866,11 @@
       </c>
       <c r="F19" s="9">
         <f>'[14]MD5000-Jan24'!$K$1</f>
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G19" s="9">
         <f>'[14]MD5000-Jan24'!$K$2</f>
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
@@ -2652,17 +2883,17 @@
       </c>
       <c r="L19" s="8">
         <f>'[14]MD5000-Jan24'!$O$2</f>
-        <v>3300</v>
+        <v>1200</v>
       </c>
       <c r="M19" s="8">
         <f>'[14]MD5000-Jan24'!$O$1</f>
-        <v>2700</v>
+        <v>4800</v>
       </c>
       <c r="N19" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="20" spans="2:14" ht="22.5" customHeight="1">
+    <row r="20" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="13">
         <v>16</v>
       </c>
@@ -2680,11 +2911,11 @@
       <c r="G20" s="14"/>
       <c r="H20" s="14">
         <f>'[15]MD10000.10-JAN'!$K$1</f>
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="I20" s="14">
         <f>'[15]MD10000.10-JAN'!$K$2</f>
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J20" s="17" t="s">
         <v>12</v>
@@ -2695,17 +2926,17 @@
       </c>
       <c r="L20" s="16">
         <f>'[15]MD10000.10-JAN'!$O$2</f>
-        <v>12950</v>
+        <v>11200</v>
       </c>
       <c r="M20" s="16">
         <f>'[15]MD10000.10-JAN'!$O$1</f>
-        <v>3850</v>
+        <v>5600</v>
       </c>
       <c r="N20" s="1">
         <v>350</v>
       </c>
     </row>
-    <row r="21" spans="2:14" ht="22.5" customHeight="1">
+    <row r="21" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="6">
         <v>17</v>
       </c>
@@ -2723,11 +2954,11 @@
       <c r="G21" s="9"/>
       <c r="H21" s="9">
         <f>'[16]MD10000.10-JAN'!$K$1</f>
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="I21" s="9">
         <f>'[16]MD10000.10-JAN'!$K$2</f>
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J21" s="10" t="s">
         <v>12</v>
@@ -2738,17 +2969,17 @@
       </c>
       <c r="L21" s="8">
         <f>'[16]MD10000.10-JAN'!$O$2</f>
-        <v>12950</v>
+        <v>11200</v>
       </c>
       <c r="M21" s="8">
         <f>'[16]MD10000.10-JAN'!$O$1</f>
-        <v>3850</v>
+        <v>5600</v>
       </c>
       <c r="N21" s="1">
         <v>350</v>
       </c>
     </row>
-    <row r="22" spans="2:14" ht="22.5" customHeight="1">
+    <row r="22" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="13">
         <v>18</v>
       </c>
@@ -2766,11 +2997,11 @@
       <c r="G22" s="14"/>
       <c r="H22" s="14">
         <f>'[17]MD10000.20-OCT'!$K$1</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I22" s="14">
         <f>'[17]MD10000.20-OCT'!$K$2</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J22" s="17" t="s">
         <v>12</v>
@@ -2781,17 +3012,17 @@
       </c>
       <c r="L22" s="16">
         <f>'[17]MD10000.20-OCT'!$O$2</f>
-        <v>2450</v>
+        <v>1050</v>
       </c>
       <c r="M22" s="16">
         <f>'[17]MD10000.20-OCT'!$O$1</f>
-        <v>3550</v>
+        <v>4950</v>
       </c>
       <c r="N22" s="1">
         <v>350</v>
       </c>
     </row>
-    <row r="23" spans="2:14" ht="22.5" customHeight="1">
+    <row r="23" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="6">
         <v>19</v>
       </c>
@@ -2809,11 +3040,11 @@
       <c r="G23" s="9"/>
       <c r="H23" s="9">
         <f>'[18]MD10000.20-OCT'!$K$1</f>
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I23" s="9">
         <f>'[18]MD10000.20-OCT'!$K$2</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J23" s="10" t="s">
         <v>12</v>
@@ -2824,17 +3055,17 @@
       </c>
       <c r="L23" s="8">
         <f>'[18]MD10000.20-OCT'!$O$2</f>
-        <v>13650</v>
+        <v>12250</v>
       </c>
       <c r="M23" s="8">
         <f>'[18]MD10000.20-OCT'!$O$1</f>
-        <v>3150</v>
+        <v>4550</v>
       </c>
       <c r="N23" s="1">
         <v>350</v>
       </c>
     </row>
-    <row r="24" spans="2:14" ht="22.5" customHeight="1">
+    <row r="24" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="6">
         <v>20</v>
       </c>
@@ -2852,11 +3083,11 @@
       <c r="G24" s="9"/>
       <c r="H24" s="9">
         <f>'[19]MD10000.20-OCT'!$K$1</f>
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I24" s="9">
         <f>'[19]MD10000.20-OCT'!$K$2</f>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J24" s="10" t="s">
         <v>12</v>
@@ -2867,17 +3098,17 @@
       </c>
       <c r="L24" s="8">
         <f>'[19]MD10000.20-OCT'!$O$2</f>
-        <v>14000</v>
+        <v>12250</v>
       </c>
       <c r="M24" s="8">
         <f>'[19]MD10000.20-OCT'!$O$1</f>
-        <v>2800</v>
+        <v>4550</v>
       </c>
       <c r="N24" s="1">
         <v>350</v>
       </c>
     </row>
-    <row r="25" spans="2:14" ht="22.5" customHeight="1">
+    <row r="25" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="6">
         <v>21</v>
       </c>
@@ -2893,11 +3124,11 @@
       </c>
       <c r="F25" s="9">
         <f>'[20]SM5000.1-oct'!$K$1</f>
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G25" s="9">
         <f>'[20]SM5000.1-oct'!$K$2</f>
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
@@ -2910,17 +3141,17 @@
       </c>
       <c r="L25" s="8">
         <f>'[20]SM5000.1-oct'!$O$2</f>
-        <v>2900</v>
+        <v>1700</v>
       </c>
       <c r="M25" s="8">
         <f>'[20]SM5000.1-oct'!$O$1</f>
-        <v>3100</v>
+        <v>4300</v>
       </c>
       <c r="N25" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="26" spans="2:14" ht="22.5" customHeight="1">
+    <row r="26" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="6">
         <v>22</v>
       </c>
@@ -2938,11 +3169,11 @@
       <c r="G26" s="9"/>
       <c r="H26" s="9">
         <f>'[21]MD10000.20-OCT'!$K$1</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I26" s="9">
         <f>'[21]MD10000.20-OCT'!$K$2</f>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J26" s="10" t="s">
         <v>12</v>
@@ -2953,17 +3184,17 @@
       </c>
       <c r="L26" s="8">
         <f>'[21]MD10000.20-OCT'!$O$2</f>
-        <v>3500</v>
+        <v>1750</v>
       </c>
       <c r="M26" s="8">
         <f>'[21]MD10000.20-OCT'!$O$1</f>
-        <v>2500</v>
+        <v>4250</v>
       </c>
       <c r="N26" s="1">
         <v>350</v>
       </c>
     </row>
-    <row r="27" spans="2:14">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B27" s="13">
         <v>23</v>
       </c>
@@ -2979,11 +3210,11 @@
       </c>
       <c r="F27" s="14">
         <f>'[22]MD10000.1-OCT'!$K$1</f>
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="G27" s="14">
         <f>'[22]MD10000.1-OCT'!$K$2</f>
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="H27" s="14"/>
       <c r="I27" s="14"/>
@@ -2996,17 +3227,17 @@
       </c>
       <c r="L27" s="16">
         <f>'[22]MD10000.1-OCT'!$O$2</f>
-        <v>8000</v>
+        <v>6100</v>
       </c>
       <c r="M27" s="16">
         <f>'[22]MD10000.1-OCT'!$O$1</f>
-        <v>4000</v>
+        <v>5900</v>
       </c>
       <c r="N27" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="28" spans="2:14" ht="22.5" customHeight="1">
+    <row r="28" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="6">
         <v>24</v>
       </c>
@@ -3022,11 +3253,11 @@
       </c>
       <c r="F28" s="9">
         <f>'[23]MD10000.1-OCT'!$K$1</f>
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="G28" s="9">
         <f>'[23]MD10000.1-OCT'!$K$2</f>
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="H28" s="9"/>
       <c r="I28" s="9"/>
@@ -3039,17 +3270,17 @@
       </c>
       <c r="L28" s="8">
         <f>'[23]MD10000.1-OCT'!$O$2</f>
-        <v>7300</v>
+        <v>4100</v>
       </c>
       <c r="M28" s="8">
         <f>'[23]MD10000.1-OCT'!$O$1</f>
-        <v>4700</v>
+        <v>7900</v>
       </c>
       <c r="N28" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="29" spans="2:14" ht="22.5" customHeight="1">
+    <row r="29" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="6">
         <v>25</v>
       </c>
@@ -3067,11 +3298,11 @@
       <c r="G29" s="9"/>
       <c r="H29" s="9">
         <f>'[24]MD20000.15-DEC'!$K$1</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I29" s="9">
         <f>'[24]MD20000.15-DEC'!$K$2</f>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J29" s="10" t="s">
         <v>12</v>
@@ -3082,17 +3313,17 @@
       </c>
       <c r="L29" s="8">
         <f>'[24]MD20000.15-DEC'!$O$2</f>
-        <v>14000</v>
+        <v>7000</v>
       </c>
       <c r="M29" s="8">
         <f>'[24]MD20000.15-DEC'!$O$1</f>
-        <v>10000</v>
+        <v>17000</v>
       </c>
       <c r="N29" s="1">
         <v>1400</v>
       </c>
     </row>
-    <row r="30" spans="2:14" ht="22.5" customHeight="1">
+    <row r="30" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="6">
         <v>26</v>
       </c>
@@ -3110,11 +3341,11 @@
       <c r="G30" s="9"/>
       <c r="H30" s="9">
         <f>'[25]MD20000.15-DEC'!$K$1</f>
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I30" s="9">
         <f>'[25]MD20000.15-DEC'!$K$2</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J30" s="10" t="s">
         <v>12</v>
@@ -3125,17 +3356,17 @@
       </c>
       <c r="L30" s="8">
         <f>'[25]MD20000.15-DEC'!$O$2</f>
-        <v>15600</v>
+        <v>10000</v>
       </c>
       <c r="M30" s="8">
         <f>'[25]MD20000.15-DEC'!$O$1</f>
-        <v>8400</v>
+        <v>14000</v>
       </c>
       <c r="N30" s="1">
         <v>1400</v>
       </c>
     </row>
-    <row r="31" spans="2:14" ht="22.5" customHeight="1">
+    <row r="31" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="13">
         <v>27</v>
       </c>
@@ -3151,11 +3382,11 @@
       </c>
       <c r="F31" s="14">
         <f>'[26]MD20000.18-DEC'!$K$1</f>
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="G31" s="14">
         <f>'[26]MD20000.18-DEC'!$K$2</f>
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="H31" s="14"/>
       <c r="I31" s="14"/>
@@ -3168,17 +3399,17 @@
       </c>
       <c r="L31" s="16">
         <f>'[26]MD20000.18-DEC'!$O$2</f>
-        <v>29400</v>
+        <v>21600</v>
       </c>
       <c r="M31" s="16">
         <f>'[26]MD20000.18-DEC'!$O$1</f>
-        <v>6600</v>
+        <v>14400</v>
       </c>
       <c r="N31" s="1">
         <v>2100</v>
       </c>
     </row>
-    <row r="32" spans="2:14" ht="22.5" customHeight="1">
+    <row r="32" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="13">
         <v>28</v>
       </c>
@@ -3196,11 +3427,11 @@
       <c r="G32" s="14"/>
       <c r="H32" s="14">
         <f>'[27]MD10000.10-JAN'!$K$1</f>
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="I32" s="14">
         <f>'[27]MD10000.10-JAN'!$K$2</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J32" s="17" t="s">
         <v>12</v>
@@ -3211,17 +3442,17 @@
       </c>
       <c r="L32" s="16">
         <f>'[27]MD10000.10-JAN'!$O$2</f>
-        <v>15750</v>
+        <v>14350</v>
       </c>
       <c r="M32" s="16">
         <f>'[27]MD10000.10-JAN'!$O$1</f>
-        <v>1050</v>
+        <v>2450</v>
       </c>
       <c r="N32" s="1">
         <v>350</v>
       </c>
     </row>
-    <row r="33" spans="2:14" ht="22.5" customHeight="1">
+    <row r="33" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="13">
         <v>29</v>
       </c>
@@ -3239,11 +3470,11 @@
       <c r="G33" s="14"/>
       <c r="H33" s="14">
         <f>'[28]MD20000.15-DEc'!$K$1</f>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I33" s="14">
         <f>'[28]MD20000.15-DEc'!$K$2</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J33" s="17" t="s">
         <v>12</v>
@@ -3254,17 +3485,17 @@
       </c>
       <c r="L33" s="16">
         <f>'[28]MD20000.15-DEc'!$O$2</f>
-        <v>22400</v>
+        <v>16800</v>
       </c>
       <c r="M33" s="16">
         <f>'[28]MD20000.15-DEc'!$O$1</f>
-        <v>1600</v>
+        <v>7200</v>
       </c>
       <c r="N33" s="1">
         <v>1400</v>
       </c>
     </row>
-    <row r="34" spans="2:14" ht="22.5" customHeight="1">
+    <row r="34" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="13">
         <v>30</v>
       </c>
@@ -3282,29 +3513,229 @@
       <c r="G34" s="14"/>
       <c r="H34" s="14">
         <f>'[29]MD10000.10-JAN'!$K$1</f>
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I34" s="14">
         <f>'[29]MD10000.10-JAN'!$K$2</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J34" s="17" t="s">
         <v>12</v>
       </c>
       <c r="K34" s="15">
         <f>'[29]MD10000.10-JAN'!$B$3</f>
-        <v>0</v>
+        <v>45389</v>
       </c>
       <c r="L34" s="16">
         <f>'[29]MD10000.10-JAN'!$O$2</f>
-        <v>16800</v>
+        <v>15400</v>
       </c>
       <c r="M34" s="16">
         <f>'[29]MD10000.10-JAN'!$O$1</f>
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="N34" s="1">
         <v>350</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="6">
+        <v>31</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" s="8">
+        <f>'[30]MD20000.15-DEc'!$C$1</f>
+        <v>20000</v>
+      </c>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9">
+        <f>'[30]MD20000.15-DEc'!$G$1</f>
+        <v>17</v>
+      </c>
+      <c r="I35" s="9">
+        <f>'[30]MD20000.15-DEc'!$K$2</f>
+        <v>3</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K35" s="11">
+        <f>'[30]MD20000.15-DEc'!$B$3</f>
+        <v>45394</v>
+      </c>
+      <c r="L35" s="8">
+        <f>'[30]MD20000.15-DEc'!$O$2</f>
+        <v>19600</v>
+      </c>
+      <c r="M35" s="8">
+        <f>'[30]MD20000.15-DEc'!$O$1</f>
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="13">
+        <v>32</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E36" s="16">
+        <f>'[31]MD10000.10-JAN'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14">
+        <f>'[31]MD10000.10-JAN'!$G$1</f>
+        <v>48</v>
+      </c>
+      <c r="I36" s="14">
+        <f>'[31]MD10000.10-JAN'!$K$2</f>
+        <v>3</v>
+      </c>
+      <c r="J36" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="K36" s="15">
+        <f>'[31]MD10000.10-JAN'!$B$3</f>
+        <v>45399</v>
+      </c>
+      <c r="L36" s="16">
+        <f>'[31]MD10000.10-JAN'!$O$2</f>
+        <v>15750</v>
+      </c>
+      <c r="M36" s="16">
+        <f>'[31]MD10000.10-JAN'!$O$1</f>
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="6">
+        <v>33</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E37" s="8">
+        <f>'[32]MD20000.15-DEc'!$C$1</f>
+        <v>20000</v>
+      </c>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9">
+        <f>'[32]MD20000.15-DEc'!$G$1</f>
+        <v>17</v>
+      </c>
+      <c r="I37" s="9">
+        <f>'[32]MD20000.15-DEc'!$K$2</f>
+        <v>2</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K37" s="11">
+        <f>'[32]MD20000.15-DEc'!$B$3</f>
+        <v>45406</v>
+      </c>
+      <c r="L37" s="8">
+        <f>'[32]MD20000.15-DEc'!$O$2</f>
+        <v>21000</v>
+      </c>
+      <c r="M37" s="8">
+        <f>'[32]MD20000.15-DEc'!$O$1</f>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="38" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="13">
+        <v>34</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E38" s="16">
+        <f>'[33]MD10000.20-OCT'!$C$1</f>
+        <v>5000</v>
+      </c>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14">
+        <f>'[33]MD10000.20-OCT'!$G$1</f>
+        <v>17</v>
+      </c>
+      <c r="I38" s="14">
+        <f>'[33]MD10000.20-OCT'!$K$2</f>
+        <v>2</v>
+      </c>
+      <c r="J38" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="K38" s="15">
+        <f>'[33]MD10000.20-OCT'!$B$3</f>
+        <v>45406</v>
+      </c>
+      <c r="L38" s="16">
+        <f>'[33]MD10000.20-OCT'!$O$2</f>
+        <v>5300</v>
+      </c>
+      <c r="M38" s="16">
+        <f>'[33]MD10000.20-OCT'!$O$1</f>
+        <v>700</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="6">
+        <v>35</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E39" s="8">
+        <f>'[34]MD50000.15-DEC'!$C$1</f>
+        <v>40000</v>
+      </c>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9">
+        <f>'[34]MD50000.15-DEC'!$K$1</f>
+        <v>48</v>
+      </c>
+      <c r="I39" s="9">
+        <f>'[34]MD50000.15-DEC'!$K$2</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K39" s="11">
+        <f>'[34]MD50000.15-DEC'!$B$3</f>
+        <v>0</v>
+      </c>
+      <c r="L39" s="8">
+        <f>'[34]MD50000.15-DEC'!$O$2</f>
+        <v>67200</v>
+      </c>
+      <c r="M39" s="8">
+        <f>'[34]MD50000.15-DEC'!$O$1</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/LoanOfficer-A/LoanBook.xlsx
+++ b/LoanOfficer-A/LoanBook.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3600" windowWidth="20640" windowHeight="11760"/>
+    <workbookView xWindow="0" yWindow="3600" windowWidth="20520" windowHeight="4425"/>
   </bookViews>
   <sheets>
     <sheet name="2023" sheetId="6" r:id="rId1"/>
@@ -44,6 +44,7 @@
     <externalReference r:id="rId33"/>
     <externalReference r:id="rId34"/>
     <externalReference r:id="rId35"/>
+    <externalReference r:id="rId36"/>
   </externalReferences>
   <calcPr calcId="145621" iterateDelta="1E-4"/>
   <extLst>
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="64">
   <si>
     <t>Code</t>
   </si>
@@ -244,6 +245,9 @@
   </si>
   <si>
     <t>L40000W48P1400-Sat</t>
+  </si>
+  <si>
+    <t>Haodijam Bidyarani</t>
   </si>
 </sst>
 </file>
@@ -584,18 +588,18 @@
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>29</v>
+            <v>28</v>
           </cell>
           <cell r="O1">
-            <v>33250</v>
+            <v>35000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>19</v>
+            <v>20</v>
           </cell>
           <cell r="O2">
-            <v>50750</v>
+            <v>49000</v>
           </cell>
         </row>
         <row r="3">
@@ -706,18 +710,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>32</v>
+            <v>31</v>
           </cell>
           <cell r="O1">
-            <v>5600</v>
+            <v>5950</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>16</v>
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>11200</v>
+            <v>10850</v>
           </cell>
         </row>
         <row r="3">
@@ -747,18 +751,18 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>12</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
-            <v>4800</v>
+            <v>6000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>48</v>
+            <v>60</v>
           </cell>
           <cell r="O2">
-            <v>1200</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -788,18 +792,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>32</v>
+            <v>31</v>
           </cell>
           <cell r="O1">
-            <v>5600</v>
+            <v>5950</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>16</v>
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>11200</v>
+            <v>10850</v>
           </cell>
         </row>
         <row r="3">
@@ -830,18 +834,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>32</v>
+            <v>31</v>
           </cell>
           <cell r="O1">
-            <v>5600</v>
+            <v>5950</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>16</v>
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>11200</v>
+            <v>10850</v>
           </cell>
         </row>
         <row r="3">
@@ -871,18 +875,18 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>3</v>
+            <v>1</v>
           </cell>
           <cell r="O1">
-            <v>4950</v>
+            <v>5650</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>14</v>
+            <v>16</v>
           </cell>
           <cell r="O2">
-            <v>1050</v>
+            <v>350</v>
           </cell>
         </row>
         <row r="3">
@@ -911,18 +915,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>35</v>
+            <v>34</v>
           </cell>
           <cell r="O1">
-            <v>4550</v>
+            <v>4900</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>13</v>
+            <v>14</v>
           </cell>
           <cell r="O2">
-            <v>12250</v>
+            <v>11900</v>
           </cell>
         </row>
         <row r="3">
@@ -952,18 +956,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>35</v>
+            <v>34</v>
           </cell>
           <cell r="O1">
-            <v>4550</v>
+            <v>4900</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>13</v>
+            <v>14</v>
           </cell>
           <cell r="O2">
-            <v>12250</v>
+            <v>11900</v>
           </cell>
         </row>
         <row r="3">
@@ -1035,18 +1039,18 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>17</v>
+            <v>14</v>
           </cell>
           <cell r="O1">
-            <v>4300</v>
+            <v>4600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>43</v>
+            <v>46</v>
           </cell>
           <cell r="O2">
-            <v>1700</v>
+            <v>1400</v>
           </cell>
         </row>
         <row r="3">
@@ -1075,18 +1079,18 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>5</v>
+            <v>3</v>
           </cell>
           <cell r="O1">
-            <v>4250</v>
+            <v>4950</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>12</v>
+            <v>14</v>
           </cell>
           <cell r="O2">
-            <v>1750</v>
+            <v>1050</v>
           </cell>
         </row>
         <row r="3">
@@ -1155,18 +1159,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>41</v>
+            <v>33</v>
           </cell>
           <cell r="O1">
-            <v>7900</v>
+            <v>8700</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>79</v>
+            <v>87</v>
           </cell>
           <cell r="O2">
-            <v>4100</v>
+            <v>3300</v>
           </cell>
         </row>
         <row r="3">
@@ -1238,18 +1242,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>7</v>
+            <v>6</v>
           </cell>
           <cell r="O1">
-            <v>14000</v>
+            <v>15400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>10</v>
+            <v>11</v>
           </cell>
           <cell r="O2">
-            <v>10000</v>
+            <v>8600</v>
           </cell>
         </row>
         <row r="3">
@@ -1279,18 +1283,18 @@
             <v>30000</v>
           </cell>
           <cell r="K1">
-            <v>72</v>
+            <v>66</v>
           </cell>
           <cell r="O1">
-            <v>14400</v>
+            <v>16200</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>48</v>
+            <v>54</v>
           </cell>
           <cell r="O2">
-            <v>21600</v>
+            <v>19800</v>
           </cell>
         </row>
         <row r="3">
@@ -1320,18 +1324,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>41</v>
+            <v>40</v>
           </cell>
           <cell r="O1">
-            <v>2450</v>
+            <v>2800</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>7</v>
+            <v>8</v>
           </cell>
           <cell r="O2">
-            <v>14350</v>
+            <v>14000</v>
           </cell>
         </row>
         <row r="3">
@@ -1362,18 +1366,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>12</v>
+            <v>11</v>
           </cell>
           <cell r="O1">
-            <v>7200</v>
+            <v>8600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>5</v>
+            <v>6</v>
           </cell>
           <cell r="O2">
-            <v>16800</v>
+            <v>15400</v>
           </cell>
         </row>
         <row r="3">
@@ -1404,18 +1408,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>44</v>
+            <v>43</v>
           </cell>
           <cell r="O1">
-            <v>1400</v>
+            <v>1750</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>4</v>
+            <v>5</v>
           </cell>
           <cell r="O2">
-            <v>15400</v>
+            <v>15050</v>
           </cell>
         </row>
         <row r="3">
@@ -1489,15 +1493,15 @@
             <v>17</v>
           </cell>
           <cell r="O1">
-            <v>4400</v>
+            <v>5800</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>3</v>
+            <v>4</v>
           </cell>
           <cell r="O2">
-            <v>19600</v>
+            <v>18200</v>
           </cell>
         </row>
         <row r="3">
@@ -1531,15 +1535,15 @@
             <v>48</v>
           </cell>
           <cell r="O1">
-            <v>1050</v>
+            <v>1400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>3</v>
+            <v>4</v>
           </cell>
           <cell r="O2">
-            <v>15750</v>
+            <v>15400</v>
           </cell>
         </row>
         <row r="3">
@@ -1614,15 +1618,15 @@
             <v>17</v>
           </cell>
           <cell r="O1">
-            <v>700</v>
+            <v>1050</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="O2">
-            <v>5300</v>
+            <v>4950</v>
           </cell>
         </row>
         <row r="3">
@@ -1645,14 +1649,55 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>40000</v>
+          </cell>
+          <cell r="K1">
+            <v>47</v>
+          </cell>
+          <cell r="O1">
+            <v>1400</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>1</v>
+          </cell>
+          <cell r="O2">
+            <v>65800</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45416</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.20-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
-            <v>40000</v>
+            <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>48</v>
+            <v>17</v>
           </cell>
           <cell r="O1">
             <v>0</v>
@@ -1663,11 +1708,10 @@
             <v>0</v>
           </cell>
           <cell r="O2">
-            <v>67200</v>
+            <v>6000</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2184,7 +2228,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:Q39"/>
+  <dimension ref="B2:Q40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="1" customWidth="1"/>
@@ -2218,12 +2262,12 @@
       <c r="K2" s="22"/>
       <c r="L2" s="18">
         <f>SUM(L5:L48)</f>
-        <v>338750</v>
+        <v>328750</v>
       </c>
       <c r="M2" s="19"/>
       <c r="N2" s="1">
-        <f>SUM(N9:N35)</f>
-        <v>16800</v>
+        <f>SUM(N5:N49)</f>
+        <v>18550</v>
       </c>
       <c r="Q2" s="1">
         <f>14900+260750</f>
@@ -2637,9 +2681,6 @@
         <f>'[8]MD20000.15-DEC'!$O$1</f>
         <v>24000</v>
       </c>
-      <c r="N13" s="1">
-        <v>1400</v>
-      </c>
     </row>
     <row r="14" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="13">
@@ -2699,11 +2740,11 @@
       <c r="G15" s="9"/>
       <c r="H15" s="9">
         <f>'[10]MD50000.15-DEC'!$K$1</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I15" s="9">
         <f>'[10]MD50000.15-DEC'!$K$2</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J15" s="10" t="s">
         <v>12</v>
@@ -2714,11 +2755,11 @@
       </c>
       <c r="L15" s="8">
         <f>'[10]MD50000.15-DEC'!$O$2</f>
-        <v>50750</v>
+        <v>49000</v>
       </c>
       <c r="M15" s="8">
         <f>'[10]MD50000.15-DEC'!$O$1</f>
-        <v>33250</v>
+        <v>35000</v>
       </c>
       <c r="N15" s="1">
         <v>1750</v>
@@ -2803,9 +2844,6 @@
         <f>'[12]MD20000.22-DEC'!$O$1</f>
         <v>24000</v>
       </c>
-      <c r="N17" s="1">
-        <v>1400</v>
-      </c>
     </row>
     <row r="18" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="13">
@@ -2825,11 +2863,11 @@
       <c r="G18" s="14"/>
       <c r="H18" s="14">
         <f>'[13]MD50000.15-DEC'!$K$1</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I18" s="14">
         <f>'[13]MD50000.15-DEC'!$K$2</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J18" s="17" t="s">
         <v>12</v>
@@ -2840,11 +2878,11 @@
       </c>
       <c r="L18" s="16">
         <f>'[13]MD50000.15-DEC'!$O$2</f>
-        <v>11200</v>
+        <v>10850</v>
       </c>
       <c r="M18" s="16">
         <f>'[13]MD50000.15-DEC'!$O$1</f>
-        <v>5600</v>
+        <v>5950</v>
       </c>
       <c r="N18" s="1">
         <v>350</v>
@@ -2866,16 +2904,16 @@
       </c>
       <c r="F19" s="9">
         <f>'[14]MD5000-Jan24'!$K$1</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G19" s="9">
         <f>'[14]MD5000-Jan24'!$K$2</f>
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
       <c r="J19" s="10" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="K19" s="11">
         <f>'[14]MD5000-Jan24'!$B$3</f>
@@ -2883,14 +2921,11 @@
       </c>
       <c r="L19" s="8">
         <f>'[14]MD5000-Jan24'!$O$2</f>
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="M19" s="8">
         <f>'[14]MD5000-Jan24'!$O$1</f>
-        <v>4800</v>
-      </c>
-      <c r="N19" s="1">
-        <v>700</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="20" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2911,11 +2946,11 @@
       <c r="G20" s="14"/>
       <c r="H20" s="14">
         <f>'[15]MD10000.10-JAN'!$K$1</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I20" s="14">
         <f>'[15]MD10000.10-JAN'!$K$2</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J20" s="17" t="s">
         <v>12</v>
@@ -2926,11 +2961,11 @@
       </c>
       <c r="L20" s="16">
         <f>'[15]MD10000.10-JAN'!$O$2</f>
-        <v>11200</v>
+        <v>10850</v>
       </c>
       <c r="M20" s="16">
         <f>'[15]MD10000.10-JAN'!$O$1</f>
-        <v>5600</v>
+        <v>5950</v>
       </c>
       <c r="N20" s="1">
         <v>350</v>
@@ -2954,11 +2989,11 @@
       <c r="G21" s="9"/>
       <c r="H21" s="9">
         <f>'[16]MD10000.10-JAN'!$K$1</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I21" s="9">
         <f>'[16]MD10000.10-JAN'!$K$2</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J21" s="10" t="s">
         <v>12</v>
@@ -2969,11 +3004,11 @@
       </c>
       <c r="L21" s="8">
         <f>'[16]MD10000.10-JAN'!$O$2</f>
-        <v>11200</v>
+        <v>10850</v>
       </c>
       <c r="M21" s="8">
         <f>'[16]MD10000.10-JAN'!$O$1</f>
-        <v>5600</v>
+        <v>5950</v>
       </c>
       <c r="N21" s="1">
         <v>350</v>
@@ -2997,11 +3032,11 @@
       <c r="G22" s="14"/>
       <c r="H22" s="14">
         <f>'[17]MD10000.20-OCT'!$K$1</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I22" s="14">
         <f>'[17]MD10000.20-OCT'!$K$2</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J22" s="17" t="s">
         <v>12</v>
@@ -3012,11 +3047,11 @@
       </c>
       <c r="L22" s="16">
         <f>'[17]MD10000.20-OCT'!$O$2</f>
-        <v>1050</v>
+        <v>350</v>
       </c>
       <c r="M22" s="16">
         <f>'[17]MD10000.20-OCT'!$O$1</f>
-        <v>4950</v>
+        <v>5650</v>
       </c>
       <c r="N22" s="1">
         <v>350</v>
@@ -3040,11 +3075,11 @@
       <c r="G23" s="9"/>
       <c r="H23" s="9">
         <f>'[18]MD10000.20-OCT'!$K$1</f>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I23" s="9">
         <f>'[18]MD10000.20-OCT'!$K$2</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J23" s="10" t="s">
         <v>12</v>
@@ -3055,11 +3090,11 @@
       </c>
       <c r="L23" s="8">
         <f>'[18]MD10000.20-OCT'!$O$2</f>
-        <v>12250</v>
+        <v>11900</v>
       </c>
       <c r="M23" s="8">
         <f>'[18]MD10000.20-OCT'!$O$1</f>
-        <v>4550</v>
+        <v>4900</v>
       </c>
       <c r="N23" s="1">
         <v>350</v>
@@ -3083,11 +3118,11 @@
       <c r="G24" s="9"/>
       <c r="H24" s="9">
         <f>'[19]MD10000.20-OCT'!$K$1</f>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I24" s="9">
         <f>'[19]MD10000.20-OCT'!$K$2</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J24" s="10" t="s">
         <v>12</v>
@@ -3098,11 +3133,11 @@
       </c>
       <c r="L24" s="8">
         <f>'[19]MD10000.20-OCT'!$O$2</f>
-        <v>12250</v>
+        <v>11900</v>
       </c>
       <c r="M24" s="8">
         <f>'[19]MD10000.20-OCT'!$O$1</f>
-        <v>4550</v>
+        <v>4900</v>
       </c>
       <c r="N24" s="1">
         <v>350</v>
@@ -3124,11 +3159,11 @@
       </c>
       <c r="F25" s="9">
         <f>'[20]SM5000.1-oct'!$K$1</f>
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G25" s="9">
         <f>'[20]SM5000.1-oct'!$K$2</f>
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
@@ -3141,11 +3176,11 @@
       </c>
       <c r="L25" s="8">
         <f>'[20]SM5000.1-oct'!$O$2</f>
-        <v>1700</v>
+        <v>1400</v>
       </c>
       <c r="M25" s="8">
         <f>'[20]SM5000.1-oct'!$O$1</f>
-        <v>4300</v>
+        <v>4600</v>
       </c>
       <c r="N25" s="1">
         <v>700</v>
@@ -3169,11 +3204,11 @@
       <c r="G26" s="9"/>
       <c r="H26" s="9">
         <f>'[21]MD10000.20-OCT'!$K$1</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I26" s="9">
         <f>'[21]MD10000.20-OCT'!$K$2</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J26" s="10" t="s">
         <v>12</v>
@@ -3184,11 +3219,11 @@
       </c>
       <c r="L26" s="8">
         <f>'[21]MD10000.20-OCT'!$O$2</f>
-        <v>1750</v>
+        <v>1050</v>
       </c>
       <c r="M26" s="8">
         <f>'[21]MD10000.20-OCT'!$O$1</f>
-        <v>4250</v>
+        <v>4950</v>
       </c>
       <c r="N26" s="1">
         <v>350</v>
@@ -3253,11 +3288,11 @@
       </c>
       <c r="F28" s="9">
         <f>'[23]MD10000.1-OCT'!$K$1</f>
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G28" s="9">
         <f>'[23]MD10000.1-OCT'!$K$2</f>
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H28" s="9"/>
       <c r="I28" s="9"/>
@@ -3270,11 +3305,11 @@
       </c>
       <c r="L28" s="8">
         <f>'[23]MD10000.1-OCT'!$O$2</f>
-        <v>4100</v>
+        <v>3300</v>
       </c>
       <c r="M28" s="8">
         <f>'[23]MD10000.1-OCT'!$O$1</f>
-        <v>7900</v>
+        <v>8700</v>
       </c>
       <c r="N28" s="1">
         <v>700</v>
@@ -3341,11 +3376,11 @@
       <c r="G30" s="9"/>
       <c r="H30" s="9">
         <f>'[25]MD20000.15-DEC'!$K$1</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I30" s="9">
         <f>'[25]MD20000.15-DEC'!$K$2</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J30" s="10" t="s">
         <v>12</v>
@@ -3356,11 +3391,11 @@
       </c>
       <c r="L30" s="8">
         <f>'[25]MD20000.15-DEC'!$O$2</f>
-        <v>10000</v>
+        <v>8600</v>
       </c>
       <c r="M30" s="8">
         <f>'[25]MD20000.15-DEC'!$O$1</f>
-        <v>14000</v>
+        <v>15400</v>
       </c>
       <c r="N30" s="1">
         <v>1400</v>
@@ -3382,11 +3417,11 @@
       </c>
       <c r="F31" s="14">
         <f>'[26]MD20000.18-DEC'!$K$1</f>
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="G31" s="14">
         <f>'[26]MD20000.18-DEC'!$K$2</f>
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="H31" s="14"/>
       <c r="I31" s="14"/>
@@ -3399,11 +3434,11 @@
       </c>
       <c r="L31" s="16">
         <f>'[26]MD20000.18-DEC'!$O$2</f>
-        <v>21600</v>
+        <v>19800</v>
       </c>
       <c r="M31" s="16">
         <f>'[26]MD20000.18-DEC'!$O$1</f>
-        <v>14400</v>
+        <v>16200</v>
       </c>
       <c r="N31" s="1">
         <v>2100</v>
@@ -3427,11 +3462,11 @@
       <c r="G32" s="14"/>
       <c r="H32" s="14">
         <f>'[27]MD10000.10-JAN'!$K$1</f>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I32" s="14">
         <f>'[27]MD10000.10-JAN'!$K$2</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J32" s="17" t="s">
         <v>12</v>
@@ -3442,11 +3477,11 @@
       </c>
       <c r="L32" s="16">
         <f>'[27]MD10000.10-JAN'!$O$2</f>
-        <v>14350</v>
+        <v>14000</v>
       </c>
       <c r="M32" s="16">
         <f>'[27]MD10000.10-JAN'!$O$1</f>
-        <v>2450</v>
+        <v>2800</v>
       </c>
       <c r="N32" s="1">
         <v>350</v>
@@ -3470,11 +3505,11 @@
       <c r="G33" s="14"/>
       <c r="H33" s="14">
         <f>'[28]MD20000.15-DEc'!$K$1</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I33" s="14">
         <f>'[28]MD20000.15-DEc'!$K$2</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J33" s="17" t="s">
         <v>12</v>
@@ -3485,11 +3520,11 @@
       </c>
       <c r="L33" s="16">
         <f>'[28]MD20000.15-DEc'!$O$2</f>
-        <v>16800</v>
+        <v>15400</v>
       </c>
       <c r="M33" s="16">
         <f>'[28]MD20000.15-DEc'!$O$1</f>
-        <v>7200</v>
+        <v>8600</v>
       </c>
       <c r="N33" s="1">
         <v>1400</v>
@@ -3513,11 +3548,11 @@
       <c r="G34" s="14"/>
       <c r="H34" s="14">
         <f>'[29]MD10000.10-JAN'!$K$1</f>
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I34" s="14">
         <f>'[29]MD10000.10-JAN'!$K$2</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J34" s="17" t="s">
         <v>12</v>
@@ -3528,11 +3563,11 @@
       </c>
       <c r="L34" s="16">
         <f>'[29]MD10000.10-JAN'!$O$2</f>
-        <v>15400</v>
+        <v>15050</v>
       </c>
       <c r="M34" s="16">
         <f>'[29]MD10000.10-JAN'!$O$1</f>
-        <v>1400</v>
+        <v>1750</v>
       </c>
       <c r="N34" s="1">
         <v>350</v>
@@ -3560,7 +3595,7 @@
       </c>
       <c r="I35" s="9">
         <f>'[30]MD20000.15-DEc'!$K$2</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J35" s="10" t="s">
         <v>12</v>
@@ -3571,11 +3606,14 @@
       </c>
       <c r="L35" s="8">
         <f>'[30]MD20000.15-DEc'!$O$2</f>
-        <v>19600</v>
+        <v>18200</v>
       </c>
       <c r="M35" s="8">
         <f>'[30]MD20000.15-DEc'!$O$1</f>
-        <v>4400</v>
+        <v>5800</v>
+      </c>
+      <c r="N35" s="1">
+        <v>1400</v>
       </c>
     </row>
     <row r="36" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3600,7 +3638,7 @@
       </c>
       <c r="I36" s="14">
         <f>'[31]MD10000.10-JAN'!$K$2</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J36" s="17" t="s">
         <v>12</v>
@@ -3611,11 +3649,14 @@
       </c>
       <c r="L36" s="16">
         <f>'[31]MD10000.10-JAN'!$O$2</f>
-        <v>15750</v>
+        <v>15400</v>
       </c>
       <c r="M36" s="16">
         <f>'[31]MD10000.10-JAN'!$O$1</f>
-        <v>1050</v>
+        <v>1400</v>
+      </c>
+      <c r="N36" s="1">
+        <v>350</v>
       </c>
     </row>
     <row r="37" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3657,6 +3698,9 @@
         <f>'[32]MD20000.15-DEc'!$O$1</f>
         <v>3000</v>
       </c>
+      <c r="N37" s="1">
+        <v>1400</v>
+      </c>
     </row>
     <row r="38" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B38" s="13">
@@ -3680,7 +3724,7 @@
       </c>
       <c r="I38" s="14">
         <f>'[33]MD10000.20-OCT'!$K$2</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J38" s="17" t="s">
         <v>12</v>
@@ -3691,11 +3735,14 @@
       </c>
       <c r="L38" s="16">
         <f>'[33]MD10000.20-OCT'!$O$2</f>
-        <v>5300</v>
+        <v>4950</v>
       </c>
       <c r="M38" s="16">
         <f>'[33]MD10000.20-OCT'!$O$1</f>
-        <v>700</v>
+        <v>1050</v>
+      </c>
+      <c r="N38" s="1">
+        <v>350</v>
       </c>
     </row>
     <row r="39" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3716,26 +3763,72 @@
       <c r="G39" s="9"/>
       <c r="H39" s="9">
         <f>'[34]MD50000.15-DEC'!$K$1</f>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I39" s="9">
         <f>'[34]MD50000.15-DEC'!$K$2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K39" s="11">
         <f>'[34]MD50000.15-DEC'!$B$3</f>
-        <v>0</v>
+        <v>45416</v>
       </c>
       <c r="L39" s="8">
         <f>'[34]MD50000.15-DEC'!$O$2</f>
-        <v>67200</v>
+        <v>65800</v>
       </c>
       <c r="M39" s="8">
         <f>'[34]MD50000.15-DEC'!$O$1</f>
+        <v>1400</v>
+      </c>
+      <c r="N39" s="1">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="6">
+        <v>36</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E40" s="8">
+        <f>'[35]MD10000.20-OCT'!$C$1</f>
+        <v>5000</v>
+      </c>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9">
+        <f>'[35]MD10000.20-OCT'!$K$1</f>
+        <v>17</v>
+      </c>
+      <c r="I40" s="9">
+        <f>'[35]MD10000.20-OCT'!$K$2</f>
         <v>0</v>
+      </c>
+      <c r="J40" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K40" s="11">
+        <f>'[35]MD10000.20-OCT'!$B$3</f>
+        <v>0</v>
+      </c>
+      <c r="L40" s="8">
+        <f>'[35]MD10000.20-OCT'!$O$2</f>
+        <v>6000</v>
+      </c>
+      <c r="M40" s="8">
+        <f>'[35]MD10000.20-OCT'!$O$1</f>
+        <v>0</v>
+      </c>
+      <c r="N40" s="1">
+        <v>350</v>
       </c>
     </row>
   </sheetData>

--- a/LoanOfficer-A/LoanBook.xlsx
+++ b/LoanOfficer-A/LoanBook.xlsx
@@ -45,6 +45,11 @@
     <externalReference r:id="rId34"/>
     <externalReference r:id="rId35"/>
     <externalReference r:id="rId36"/>
+    <externalReference r:id="rId37"/>
+    <externalReference r:id="rId38"/>
+    <externalReference r:id="rId39"/>
+    <externalReference r:id="rId40"/>
+    <externalReference r:id="rId41"/>
   </externalReferences>
   <calcPr calcId="145621" iterateDelta="1E-4"/>
   <extLst>
@@ -56,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="67">
   <si>
     <t>Code</t>
   </si>
@@ -248,6 +253,15 @@
   </si>
   <si>
     <t>Haodijam Bidyarani</t>
+  </si>
+  <si>
+    <t>Asiqi</t>
+  </si>
+  <si>
+    <t>Pishak</t>
+  </si>
+  <si>
+    <t>L50000W17P350-FRI</t>
   </si>
 </sst>
 </file>
@@ -392,7 +406,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -464,6 +478,7 @@
     <xf numFmtId="166" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -588,18 +603,18 @@
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>28</v>
+            <v>26</v>
           </cell>
           <cell r="O1">
-            <v>35000</v>
+            <v>38500</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>20</v>
+            <v>22</v>
           </cell>
           <cell r="O2">
-            <v>49000</v>
+            <v>45500</v>
           </cell>
         </row>
         <row r="3">
@@ -669,23 +684,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
+            <v>120</v>
+          </cell>
+          <cell r="O1">
             <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>120</v>
+            <v>0</v>
           </cell>
           <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45283</v>
+            <v>24000</v>
           </cell>
         </row>
       </sheetData>
@@ -710,18 +720,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>31</v>
+            <v>29</v>
           </cell>
           <cell r="O1">
-            <v>5950</v>
+            <v>6650</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>17</v>
+            <v>19</v>
           </cell>
           <cell r="O2">
-            <v>10850</v>
+            <v>10150</v>
           </cell>
         </row>
         <row r="3">
@@ -792,18 +802,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>31</v>
+            <v>30</v>
           </cell>
           <cell r="O1">
-            <v>5950</v>
+            <v>6300</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>17</v>
+            <v>18</v>
           </cell>
           <cell r="O2">
-            <v>10850</v>
+            <v>10500</v>
           </cell>
         </row>
         <row r="3">
@@ -834,18 +844,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>31</v>
+            <v>30</v>
           </cell>
           <cell r="O1">
-            <v>5950</v>
+            <v>6300</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>17</v>
+            <v>18</v>
           </cell>
           <cell r="O2">
-            <v>10850</v>
+            <v>10500</v>
           </cell>
         </row>
         <row r="3">
@@ -875,18 +885,18 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
-            <v>5650</v>
+            <v>6000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>16</v>
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>350</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -915,18 +925,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>34</v>
+            <v>32</v>
           </cell>
           <cell r="O1">
-            <v>4900</v>
+            <v>5600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>14</v>
+            <v>16</v>
           </cell>
           <cell r="O2">
-            <v>11900</v>
+            <v>11200</v>
           </cell>
         </row>
         <row r="3">
@@ -956,18 +966,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>34</v>
+            <v>32</v>
           </cell>
           <cell r="O1">
-            <v>4900</v>
+            <v>5600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>14</v>
+            <v>16</v>
           </cell>
           <cell r="O2">
-            <v>11900</v>
+            <v>11200</v>
           </cell>
         </row>
         <row r="3">
@@ -1039,18 +1049,18 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>14</v>
+            <v>13</v>
           </cell>
           <cell r="O1">
-            <v>4600</v>
+            <v>4700</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>46</v>
+            <v>47</v>
           </cell>
           <cell r="O2">
-            <v>1400</v>
+            <v>1300</v>
           </cell>
         </row>
         <row r="3">
@@ -1079,18 +1089,18 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="O1">
-            <v>4950</v>
+            <v>5300</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>14</v>
+            <v>15</v>
           </cell>
           <cell r="O2">
-            <v>1050</v>
+            <v>700</v>
           </cell>
         </row>
         <row r="3">
@@ -1159,18 +1169,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>33</v>
+            <v>21</v>
           </cell>
           <cell r="O1">
-            <v>8700</v>
+            <v>9900</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>87</v>
+            <v>99</v>
           </cell>
           <cell r="O2">
-            <v>3300</v>
+            <v>2100</v>
           </cell>
         </row>
         <row r="3">
@@ -1210,9 +1220,6 @@
           <cell r="K2">
             <v>12</v>
           </cell>
-          <cell r="O2">
-            <v>7000</v>
-          </cell>
         </row>
         <row r="3">
           <cell r="B3">
@@ -1242,18 +1249,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>6</v>
+            <v>4</v>
           </cell>
           <cell r="O1">
-            <v>15400</v>
+            <v>18200</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>11</v>
+            <v>13</v>
           </cell>
           <cell r="O2">
-            <v>8600</v>
+            <v>5800</v>
           </cell>
         </row>
         <row r="3">
@@ -1283,18 +1290,18 @@
             <v>30000</v>
           </cell>
           <cell r="K1">
-            <v>66</v>
+            <v>41</v>
           </cell>
           <cell r="O1">
-            <v>16200</v>
+            <v>23700</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>54</v>
+            <v>79</v>
           </cell>
           <cell r="O2">
-            <v>19800</v>
+            <v>12300</v>
           </cell>
         </row>
         <row r="3">
@@ -1324,18 +1331,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>40</v>
+            <v>38</v>
           </cell>
           <cell r="O1">
-            <v>2800</v>
+            <v>3500</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>8</v>
+            <v>10</v>
           </cell>
           <cell r="O2">
-            <v>14000</v>
+            <v>13300</v>
           </cell>
         </row>
         <row r="3">
@@ -1366,18 +1373,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>11</v>
+            <v>9</v>
           </cell>
           <cell r="O1">
-            <v>8600</v>
+            <v>11400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>6</v>
+            <v>8</v>
           </cell>
           <cell r="O2">
-            <v>15400</v>
+            <v>12600</v>
           </cell>
         </row>
         <row r="3">
@@ -1408,18 +1415,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>43</v>
+            <v>41</v>
           </cell>
           <cell r="O1">
-            <v>1750</v>
+            <v>2450</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>5</v>
+            <v>7</v>
           </cell>
           <cell r="O2">
-            <v>15050</v>
+            <v>14350</v>
           </cell>
         </row>
         <row r="3">
@@ -1493,15 +1500,15 @@
             <v>17</v>
           </cell>
           <cell r="O1">
-            <v>5800</v>
+            <v>8600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>4</v>
+            <v>6</v>
           </cell>
           <cell r="O2">
-            <v>18200</v>
+            <v>15400</v>
           </cell>
         </row>
         <row r="3">
@@ -1535,15 +1542,15 @@
             <v>48</v>
           </cell>
           <cell r="O1">
-            <v>1400</v>
+            <v>1750</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>4</v>
+            <v>5</v>
           </cell>
           <cell r="O2">
-            <v>15400</v>
+            <v>15050</v>
           </cell>
         </row>
         <row r="3">
@@ -1577,15 +1584,15 @@
             <v>17</v>
           </cell>
           <cell r="O1">
-            <v>3000</v>
+            <v>4400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="O2">
-            <v>21000</v>
+            <v>19600</v>
           </cell>
         </row>
         <row r="3">
@@ -1618,15 +1625,15 @@
             <v>17</v>
           </cell>
           <cell r="O1">
-            <v>1050</v>
+            <v>1400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>3</v>
+            <v>4</v>
           </cell>
           <cell r="O2">
-            <v>4950</v>
+            <v>4600</v>
           </cell>
         </row>
         <row r="3">
@@ -1666,9 +1673,6 @@
           <cell r="K2">
             <v>1</v>
           </cell>
-          <cell r="O2">
-            <v>65800</v>
-          </cell>
         </row>
         <row r="3">
           <cell r="B3">
@@ -1690,13 +1694,93 @@
       <sheetName val="MD10000.20-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>5000</v>
           </cell>
           <cell r="K1">
+            <v>16</v>
+          </cell>
+          <cell r="O1">
+            <v>350</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>1</v>
+          </cell>
+          <cell r="O2">
+            <v>5650</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45427</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>110</v>
+          </cell>
+          <cell r="O1">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>10</v>
+          </cell>
+          <cell r="O2">
+            <v>22000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45425</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.20-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>5000</v>
+          </cell>
+          <cell r="K1">
             <v>17</v>
           </cell>
           <cell r="O1">
@@ -1712,6 +1796,69 @@
           </cell>
         </row>
       </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.22-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>119</v>
+          </cell>
+          <cell r="O1">
+            <v>200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>1</v>
+          </cell>
+          <cell r="O2">
+            <v>23800</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45432</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEC"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="O2">
+            <v>4200</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1752,6 +1899,29 @@
           </cell>
         </row>
       </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD50000.15-DEC"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="O2">
+            <v>63000</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2220,7 +2390,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2228,7 +2398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:Q40"/>
+  <dimension ref="B2:Q43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="1" customWidth="1"/>
@@ -2247,7 +2417,8 @@
     <col min="14" max="14" width="15.28515625" style="1" customWidth="1"/>
     <col min="15" max="15" width="11.85546875" style="1" customWidth="1"/>
     <col min="16" max="16" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="17" max="17" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2262,12 +2433,12 @@
       <c r="K2" s="22"/>
       <c r="L2" s="18">
         <f>SUM(L5:L48)</f>
-        <v>328750</v>
+        <v>370900</v>
       </c>
       <c r="M2" s="19"/>
       <c r="N2" s="1">
         <f>SUM(N5:N49)</f>
-        <v>18550</v>
+        <v>21350</v>
       </c>
       <c r="Q2" s="1">
         <f>14900+260750</f>
@@ -2681,6 +2852,7 @@
         <f>'[8]MD20000.15-DEC'!$O$1</f>
         <v>24000</v>
       </c>
+      <c r="Q13" s="25"/>
     </row>
     <row r="14" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="13">
@@ -2740,11 +2912,11 @@
       <c r="G15" s="9"/>
       <c r="H15" s="9">
         <f>'[10]MD50000.15-DEC'!$K$1</f>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I15" s="9">
         <f>'[10]MD50000.15-DEC'!$K$2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J15" s="10" t="s">
         <v>12</v>
@@ -2755,11 +2927,11 @@
       </c>
       <c r="L15" s="8">
         <f>'[10]MD50000.15-DEC'!$O$2</f>
-        <v>49000</v>
+        <v>45500</v>
       </c>
       <c r="M15" s="8">
         <f>'[10]MD50000.15-DEC'!$O$1</f>
-        <v>35000</v>
+        <v>38500</v>
       </c>
       <c r="N15" s="1">
         <v>1750</v>
@@ -2821,11 +2993,11 @@
       </c>
       <c r="F17" s="9">
         <f>'[12]MD20000.22-DEC'!$K$1</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="G17" s="9">
         <f>'[12]MD20000.22-DEC'!$K$2</f>
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
@@ -2834,15 +3006,15 @@
       </c>
       <c r="K17" s="11">
         <f>'[12]MD20000.22-DEC'!$B$3</f>
-        <v>45283</v>
+        <v>0</v>
       </c>
       <c r="L17" s="8">
         <f>'[12]MD20000.22-DEC'!$O$2</f>
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="M17" s="8">
         <f>'[12]MD20000.22-DEC'!$O$1</f>
-        <v>24000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2863,11 +3035,11 @@
       <c r="G18" s="14"/>
       <c r="H18" s="14">
         <f>'[13]MD50000.15-DEC'!$K$1</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I18" s="14">
         <f>'[13]MD50000.15-DEC'!$K$2</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J18" s="17" t="s">
         <v>12</v>
@@ -2878,11 +3050,11 @@
       </c>
       <c r="L18" s="16">
         <f>'[13]MD50000.15-DEC'!$O$2</f>
-        <v>10850</v>
+        <v>10150</v>
       </c>
       <c r="M18" s="16">
         <f>'[13]MD50000.15-DEC'!$O$1</f>
-        <v>5950</v>
+        <v>6650</v>
       </c>
       <c r="N18" s="1">
         <v>350</v>
@@ -2946,11 +3118,11 @@
       <c r="G20" s="14"/>
       <c r="H20" s="14">
         <f>'[15]MD10000.10-JAN'!$K$1</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I20" s="14">
         <f>'[15]MD10000.10-JAN'!$K$2</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J20" s="17" t="s">
         <v>12</v>
@@ -2961,11 +3133,11 @@
       </c>
       <c r="L20" s="16">
         <f>'[15]MD10000.10-JAN'!$O$2</f>
-        <v>10850</v>
+        <v>10500</v>
       </c>
       <c r="M20" s="16">
         <f>'[15]MD10000.10-JAN'!$O$1</f>
-        <v>5950</v>
+        <v>6300</v>
       </c>
       <c r="N20" s="1">
         <v>350</v>
@@ -2989,11 +3161,11 @@
       <c r="G21" s="9"/>
       <c r="H21" s="9">
         <f>'[16]MD10000.10-JAN'!$K$1</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I21" s="9">
         <f>'[16]MD10000.10-JAN'!$K$2</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J21" s="10" t="s">
         <v>12</v>
@@ -3004,11 +3176,11 @@
       </c>
       <c r="L21" s="8">
         <f>'[16]MD10000.10-JAN'!$O$2</f>
-        <v>10850</v>
+        <v>10500</v>
       </c>
       <c r="M21" s="8">
         <f>'[16]MD10000.10-JAN'!$O$1</f>
-        <v>5950</v>
+        <v>6300</v>
       </c>
       <c r="N21" s="1">
         <v>350</v>
@@ -3032,14 +3204,14 @@
       <c r="G22" s="14"/>
       <c r="H22" s="14">
         <f>'[17]MD10000.20-OCT'!$K$1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <f>'[17]MD10000.20-OCT'!$K$2</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J22" s="17" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="K22" s="15">
         <f>'[17]MD10000.20-OCT'!$B$3</f>
@@ -3047,14 +3219,11 @@
       </c>
       <c r="L22" s="16">
         <f>'[17]MD10000.20-OCT'!$O$2</f>
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="M22" s="16">
         <f>'[17]MD10000.20-OCT'!$O$1</f>
-        <v>5650</v>
-      </c>
-      <c r="N22" s="1">
-        <v>350</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="23" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3075,11 +3244,11 @@
       <c r="G23" s="9"/>
       <c r="H23" s="9">
         <f>'[18]MD10000.20-OCT'!$K$1</f>
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I23" s="9">
         <f>'[18]MD10000.20-OCT'!$K$2</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J23" s="10" t="s">
         <v>12</v>
@@ -3090,11 +3259,11 @@
       </c>
       <c r="L23" s="8">
         <f>'[18]MD10000.20-OCT'!$O$2</f>
-        <v>11900</v>
+        <v>11200</v>
       </c>
       <c r="M23" s="8">
         <f>'[18]MD10000.20-OCT'!$O$1</f>
-        <v>4900</v>
+        <v>5600</v>
       </c>
       <c r="N23" s="1">
         <v>350</v>
@@ -3118,11 +3287,11 @@
       <c r="G24" s="9"/>
       <c r="H24" s="9">
         <f>'[19]MD10000.20-OCT'!$K$1</f>
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I24" s="9">
         <f>'[19]MD10000.20-OCT'!$K$2</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J24" s="10" t="s">
         <v>12</v>
@@ -3133,11 +3302,11 @@
       </c>
       <c r="L24" s="8">
         <f>'[19]MD10000.20-OCT'!$O$2</f>
-        <v>11900</v>
+        <v>11200</v>
       </c>
       <c r="M24" s="8">
         <f>'[19]MD10000.20-OCT'!$O$1</f>
-        <v>4900</v>
+        <v>5600</v>
       </c>
       <c r="N24" s="1">
         <v>350</v>
@@ -3159,11 +3328,11 @@
       </c>
       <c r="F25" s="9">
         <f>'[20]SM5000.1-oct'!$K$1</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G25" s="9">
         <f>'[20]SM5000.1-oct'!$K$2</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
@@ -3176,11 +3345,11 @@
       </c>
       <c r="L25" s="8">
         <f>'[20]SM5000.1-oct'!$O$2</f>
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="M25" s="8">
         <f>'[20]SM5000.1-oct'!$O$1</f>
-        <v>4600</v>
+        <v>4700</v>
       </c>
       <c r="N25" s="1">
         <v>700</v>
@@ -3204,11 +3373,11 @@
       <c r="G26" s="9"/>
       <c r="H26" s="9">
         <f>'[21]MD10000.20-OCT'!$K$1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I26" s="9">
         <f>'[21]MD10000.20-OCT'!$K$2</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J26" s="10" t="s">
         <v>12</v>
@@ -3219,11 +3388,11 @@
       </c>
       <c r="L26" s="8">
         <f>'[21]MD10000.20-OCT'!$O$2</f>
-        <v>1050</v>
+        <v>700</v>
       </c>
       <c r="M26" s="8">
         <f>'[21]MD10000.20-OCT'!$O$1</f>
-        <v>4950</v>
+        <v>5300</v>
       </c>
       <c r="N26" s="1">
         <v>350</v>
@@ -3288,11 +3457,11 @@
       </c>
       <c r="F28" s="9">
         <f>'[23]MD10000.1-OCT'!$K$1</f>
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G28" s="9">
         <f>'[23]MD10000.1-OCT'!$K$2</f>
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="H28" s="9"/>
       <c r="I28" s="9"/>
@@ -3305,11 +3474,11 @@
       </c>
       <c r="L28" s="8">
         <f>'[23]MD10000.1-OCT'!$O$2</f>
-        <v>3300</v>
+        <v>2100</v>
       </c>
       <c r="M28" s="8">
         <f>'[23]MD10000.1-OCT'!$O$1</f>
-        <v>8700</v>
+        <v>9900</v>
       </c>
       <c r="N28" s="1">
         <v>700</v>
@@ -3347,8 +3516,8 @@
         <v>45337</v>
       </c>
       <c r="L29" s="8">
-        <f>'[24]MD20000.15-DEC'!$O$2</f>
-        <v>7000</v>
+        <f>'[39]MD20000.15-DEC'!$O$2</f>
+        <v>4200</v>
       </c>
       <c r="M29" s="8">
         <f>'[24]MD20000.15-DEC'!$O$1</f>
@@ -3376,11 +3545,11 @@
       <c r="G30" s="9"/>
       <c r="H30" s="9">
         <f>'[25]MD20000.15-DEC'!$K$1</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I30" s="9">
         <f>'[25]MD20000.15-DEC'!$K$2</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J30" s="10" t="s">
         <v>12</v>
@@ -3391,11 +3560,11 @@
       </c>
       <c r="L30" s="8">
         <f>'[25]MD20000.15-DEC'!$O$2</f>
-        <v>8600</v>
+        <v>5800</v>
       </c>
       <c r="M30" s="8">
         <f>'[25]MD20000.15-DEC'!$O$1</f>
-        <v>15400</v>
+        <v>18200</v>
       </c>
       <c r="N30" s="1">
         <v>1400</v>
@@ -3417,11 +3586,11 @@
       </c>
       <c r="F31" s="14">
         <f>'[26]MD20000.18-DEC'!$K$1</f>
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="G31" s="14">
         <f>'[26]MD20000.18-DEC'!$K$2</f>
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="H31" s="14"/>
       <c r="I31" s="14"/>
@@ -3434,11 +3603,11 @@
       </c>
       <c r="L31" s="16">
         <f>'[26]MD20000.18-DEC'!$O$2</f>
-        <v>19800</v>
+        <v>12300</v>
       </c>
       <c r="M31" s="16">
         <f>'[26]MD20000.18-DEC'!$O$1</f>
-        <v>16200</v>
+        <v>23700</v>
       </c>
       <c r="N31" s="1">
         <v>2100</v>
@@ -3462,11 +3631,11 @@
       <c r="G32" s="14"/>
       <c r="H32" s="14">
         <f>'[27]MD10000.10-JAN'!$K$1</f>
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I32" s="14">
         <f>'[27]MD10000.10-JAN'!$K$2</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J32" s="17" t="s">
         <v>12</v>
@@ -3477,11 +3646,11 @@
       </c>
       <c r="L32" s="16">
         <f>'[27]MD10000.10-JAN'!$O$2</f>
-        <v>14000</v>
+        <v>13300</v>
       </c>
       <c r="M32" s="16">
         <f>'[27]MD10000.10-JAN'!$O$1</f>
-        <v>2800</v>
+        <v>3500</v>
       </c>
       <c r="N32" s="1">
         <v>350</v>
@@ -3505,11 +3674,11 @@
       <c r="G33" s="14"/>
       <c r="H33" s="14">
         <f>'[28]MD20000.15-DEc'!$K$1</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I33" s="14">
         <f>'[28]MD20000.15-DEc'!$K$2</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J33" s="17" t="s">
         <v>12</v>
@@ -3520,11 +3689,11 @@
       </c>
       <c r="L33" s="16">
         <f>'[28]MD20000.15-DEc'!$O$2</f>
-        <v>15400</v>
+        <v>12600</v>
       </c>
       <c r="M33" s="16">
         <f>'[28]MD20000.15-DEc'!$O$1</f>
-        <v>8600</v>
+        <v>11400</v>
       </c>
       <c r="N33" s="1">
         <v>1400</v>
@@ -3548,11 +3717,11 @@
       <c r="G34" s="14"/>
       <c r="H34" s="14">
         <f>'[29]MD10000.10-JAN'!$K$1</f>
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I34" s="14">
         <f>'[29]MD10000.10-JAN'!$K$2</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J34" s="17" t="s">
         <v>12</v>
@@ -3563,11 +3732,11 @@
       </c>
       <c r="L34" s="16">
         <f>'[29]MD10000.10-JAN'!$O$2</f>
-        <v>15050</v>
+        <v>14350</v>
       </c>
       <c r="M34" s="16">
         <f>'[29]MD10000.10-JAN'!$O$1</f>
-        <v>1750</v>
+        <v>2450</v>
       </c>
       <c r="N34" s="1">
         <v>350</v>
@@ -3595,7 +3764,7 @@
       </c>
       <c r="I35" s="9">
         <f>'[30]MD20000.15-DEc'!$K$2</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J35" s="10" t="s">
         <v>12</v>
@@ -3606,11 +3775,11 @@
       </c>
       <c r="L35" s="8">
         <f>'[30]MD20000.15-DEc'!$O$2</f>
-        <v>18200</v>
+        <v>15400</v>
       </c>
       <c r="M35" s="8">
         <f>'[30]MD20000.15-DEc'!$O$1</f>
-        <v>5800</v>
+        <v>8600</v>
       </c>
       <c r="N35" s="1">
         <v>1400</v>
@@ -3638,7 +3807,7 @@
       </c>
       <c r="I36" s="14">
         <f>'[31]MD10000.10-JAN'!$K$2</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J36" s="17" t="s">
         <v>12</v>
@@ -3649,11 +3818,11 @@
       </c>
       <c r="L36" s="16">
         <f>'[31]MD10000.10-JAN'!$O$2</f>
-        <v>15400</v>
+        <v>15050</v>
       </c>
       <c r="M36" s="16">
         <f>'[31]MD10000.10-JAN'!$O$1</f>
-        <v>1400</v>
+        <v>1750</v>
       </c>
       <c r="N36" s="1">
         <v>350</v>
@@ -3681,7 +3850,7 @@
       </c>
       <c r="I37" s="9">
         <f>'[32]MD20000.15-DEc'!$K$2</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J37" s="10" t="s">
         <v>12</v>
@@ -3692,11 +3861,11 @@
       </c>
       <c r="L37" s="8">
         <f>'[32]MD20000.15-DEc'!$O$2</f>
-        <v>21000</v>
+        <v>19600</v>
       </c>
       <c r="M37" s="8">
         <f>'[32]MD20000.15-DEc'!$O$1</f>
-        <v>3000</v>
+        <v>4400</v>
       </c>
       <c r="N37" s="1">
         <v>1400</v>
@@ -3724,7 +3893,7 @@
       </c>
       <c r="I38" s="14">
         <f>'[33]MD10000.20-OCT'!$K$2</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J38" s="17" t="s">
         <v>12</v>
@@ -3735,11 +3904,11 @@
       </c>
       <c r="L38" s="16">
         <f>'[33]MD10000.20-OCT'!$O$2</f>
-        <v>4950</v>
+        <v>4600</v>
       </c>
       <c r="M38" s="16">
         <f>'[33]MD10000.20-OCT'!$O$1</f>
-        <v>1050</v>
+        <v>1400</v>
       </c>
       <c r="N38" s="1">
         <v>350</v>
@@ -3777,8 +3946,8 @@
         <v>45416</v>
       </c>
       <c r="L39" s="8">
-        <f>'[34]MD50000.15-DEC'!$O$2</f>
-        <v>65800</v>
+        <f>'[40]MD50000.15-DEC'!$O$2</f>
+        <v>63000</v>
       </c>
       <c r="M39" s="8">
         <f>'[34]MD50000.15-DEC'!$O$1</f>
@@ -3806,29 +3975,158 @@
       <c r="G40" s="9"/>
       <c r="H40" s="9">
         <f>'[35]MD10000.20-OCT'!$K$1</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I40" s="9">
         <f>'[35]MD10000.20-OCT'!$K$2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K40" s="11">
         <f>'[35]MD10000.20-OCT'!$B$3</f>
-        <v>0</v>
+        <v>45427</v>
       </c>
       <c r="L40" s="8">
         <f>'[35]MD10000.20-OCT'!$O$2</f>
-        <v>6000</v>
+        <v>5650</v>
       </c>
       <c r="M40" s="8">
         <f>'[35]MD10000.20-OCT'!$O$1</f>
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="N40" s="1">
         <v>350</v>
+      </c>
+    </row>
+    <row r="41" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="6">
+        <v>37</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E41" s="8">
+        <f>'[36]MD20000.18-DEC'!$C$1</f>
+        <v>20000</v>
+      </c>
+      <c r="F41" s="9">
+        <f>'[36]MD20000.18-DEC'!$K$1</f>
+        <v>110</v>
+      </c>
+      <c r="G41" s="9">
+        <f>'[36]MD20000.18-DEC'!$K$2</f>
+        <v>10</v>
+      </c>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K41" s="11">
+        <f>'[36]MD20000.18-DEC'!$B$3</f>
+        <v>45425</v>
+      </c>
+      <c r="L41" s="8">
+        <f>'[36]MD20000.18-DEC'!$O$2</f>
+        <v>22000</v>
+      </c>
+      <c r="M41" s="8">
+        <f>'[36]MD20000.18-DEC'!$O$1</f>
+        <v>2000</v>
+      </c>
+      <c r="N41" s="1">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="6">
+        <v>38</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="E42" s="8">
+        <f>'[37]MD10000.20-OCT'!$C$1</f>
+        <v>5000</v>
+      </c>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9">
+        <f>'[37]MD10000.20-OCT'!$K$1</f>
+        <v>17</v>
+      </c>
+      <c r="I42" s="9">
+        <f>'[37]MD10000.20-OCT'!$K$2</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K42" s="11">
+        <f>'[37]MD10000.20-OCT'!$B$3</f>
+        <v>0</v>
+      </c>
+      <c r="L42" s="8">
+        <f>'[37]MD10000.20-OCT'!$O$2</f>
+        <v>6000</v>
+      </c>
+      <c r="M42" s="8">
+        <f>'[37]MD10000.20-OCT'!$O$1</f>
+        <v>0</v>
+      </c>
+      <c r="N42" s="1">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="6">
+        <v>39</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E43" s="8">
+        <f>'[38]MD20000.22-DEC'!$C$1</f>
+        <v>20000</v>
+      </c>
+      <c r="F43" s="9">
+        <f>'[38]MD20000.22-DEC'!$K$1</f>
+        <v>119</v>
+      </c>
+      <c r="G43" s="9">
+        <f>'[38]MD20000.22-DEC'!$K$2</f>
+        <v>1</v>
+      </c>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K43" s="11">
+        <f>'[38]MD20000.22-DEC'!$B$3</f>
+        <v>45432</v>
+      </c>
+      <c r="L43" s="8">
+        <f>'[38]MD20000.22-DEC'!$O$2</f>
+        <v>23800</v>
+      </c>
+      <c r="M43" s="8">
+        <f>'[38]MD20000.22-DEC'!$O$1</f>
+        <v>200</v>
+      </c>
+      <c r="N43" s="1">
+        <v>1400</v>
       </c>
     </row>
   </sheetData>

--- a/LoanOfficer-A/LoanBook.xlsx
+++ b/LoanOfficer-A/LoanBook.xlsx
@@ -50,6 +50,10 @@
     <externalReference r:id="rId39"/>
     <externalReference r:id="rId40"/>
     <externalReference r:id="rId41"/>
+    <externalReference r:id="rId42"/>
+    <externalReference r:id="rId43"/>
+    <externalReference r:id="rId44"/>
+    <externalReference r:id="rId45"/>
   </externalReferences>
   <calcPr calcId="145621" iterateDelta="1E-4"/>
   <extLst>
@@ -61,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="73">
   <si>
     <t>Code</t>
   </si>
@@ -262,6 +266,24 @@
   </si>
   <si>
     <t>L50000W17P350-FRI</t>
+  </si>
+  <si>
+    <t>Ranita</t>
+  </si>
+  <si>
+    <t>L10000p120</t>
+  </si>
+  <si>
+    <t>tombi</t>
+  </si>
+  <si>
+    <t>Pratima</t>
+  </si>
+  <si>
+    <t>L10000w17P700-FRI</t>
+  </si>
+  <si>
+    <t>Priya daily</t>
   </si>
 </sst>
 </file>
@@ -457,6 +479,7 @@
     <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -478,7 +501,6 @@
     <xf numFmtId="166" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -603,18 +625,18 @@
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>26</v>
+            <v>24</v>
           </cell>
           <cell r="O1">
-            <v>38500</v>
+            <v>42000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>22</v>
+            <v>24</v>
           </cell>
           <cell r="O2">
-            <v>45500</v>
+            <v>42000</v>
           </cell>
         </row>
         <row r="3">
@@ -693,9 +715,6 @@
         <row r="2">
           <cell r="K2">
             <v>0</v>
-          </cell>
-          <cell r="O2">
-            <v>24000</v>
           </cell>
         </row>
       </sheetData>
@@ -720,18 +739,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>29</v>
+            <v>27</v>
           </cell>
           <cell r="O1">
-            <v>6650</v>
+            <v>7350</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>19</v>
+            <v>21</v>
           </cell>
           <cell r="O2">
-            <v>10150</v>
+            <v>9450</v>
           </cell>
         </row>
         <row r="3">
@@ -802,18 +821,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>30</v>
+            <v>28</v>
           </cell>
           <cell r="O1">
-            <v>6300</v>
+            <v>7000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>18</v>
+            <v>20</v>
           </cell>
           <cell r="O2">
-            <v>10500</v>
+            <v>9800</v>
           </cell>
         </row>
         <row r="3">
@@ -844,18 +863,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>30</v>
+            <v>28</v>
           </cell>
           <cell r="O1">
-            <v>6300</v>
+            <v>7000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>18</v>
+            <v>20</v>
           </cell>
           <cell r="O2">
-            <v>10500</v>
+            <v>9800</v>
           </cell>
         </row>
         <row r="3">
@@ -925,18 +944,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>32</v>
+            <v>30</v>
           </cell>
           <cell r="O1">
-            <v>5600</v>
+            <v>6300</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>16</v>
+            <v>18</v>
           </cell>
           <cell r="O2">
-            <v>11200</v>
+            <v>10500</v>
           </cell>
         </row>
         <row r="3">
@@ -966,18 +985,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>32</v>
+            <v>30</v>
           </cell>
           <cell r="O1">
-            <v>5600</v>
+            <v>6300</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>16</v>
+            <v>18</v>
           </cell>
           <cell r="O2">
-            <v>11200</v>
+            <v>10500</v>
           </cell>
         </row>
         <row r="3">
@@ -1049,18 +1068,18 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>13</v>
+            <v>11</v>
           </cell>
           <cell r="O1">
-            <v>4700</v>
+            <v>4900</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>47</v>
+            <v>49</v>
           </cell>
           <cell r="O2">
-            <v>1300</v>
+            <v>1100</v>
           </cell>
         </row>
         <row r="3">
@@ -1089,18 +1108,18 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
-            <v>5300</v>
+            <v>6000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>15</v>
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>700</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -1169,18 +1188,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>21</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
-            <v>9900</v>
+            <v>12000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>99</v>
+            <v>120</v>
           </cell>
           <cell r="O2">
-            <v>2100</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -1244,28 +1263,9 @@
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>4</v>
-          </cell>
-          <cell r="O1">
-            <v>18200</v>
-          </cell>
-        </row>
         <row r="2">
-          <cell r="K2">
-            <v>13</v>
-          </cell>
           <cell r="O2">
-            <v>5800</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45345</v>
+            <v>1400</v>
           </cell>
         </row>
       </sheetData>
@@ -1276,6 +1276,48 @@
 </file>
 
 <file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEC"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>2</v>
+          </cell>
+          <cell r="O1">
+            <v>21000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>15</v>
+          </cell>
+          <cell r="O2">
+            <v>3000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45345</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1290,18 +1332,18 @@
             <v>30000</v>
           </cell>
           <cell r="K1">
-            <v>41</v>
+            <v>30</v>
           </cell>
           <cell r="O1">
-            <v>23700</v>
+            <v>27000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>79</v>
+            <v>90</v>
           </cell>
           <cell r="O2">
-            <v>12300</v>
+            <v>9000</v>
           </cell>
         </row>
         <row r="3">
@@ -1315,7 +1357,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1331,18 +1373,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>38</v>
+            <v>36</v>
           </cell>
           <cell r="O1">
-            <v>3500</v>
+            <v>4200</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>10</v>
+            <v>12</v>
           </cell>
           <cell r="O2">
-            <v>13300</v>
+            <v>12600</v>
           </cell>
         </row>
         <row r="3">
@@ -1357,7 +1399,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1373,18 +1415,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>9</v>
+            <v>7</v>
           </cell>
           <cell r="O1">
-            <v>11400</v>
+            <v>14200</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>8</v>
+            <v>10</v>
           </cell>
           <cell r="O2">
-            <v>12600</v>
+            <v>9800</v>
           </cell>
         </row>
         <row r="3">
@@ -1399,7 +1441,47 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45213</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1415,18 +1497,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>41</v>
+            <v>39</v>
           </cell>
           <cell r="O1">
-            <v>2450</v>
+            <v>3150</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>7</v>
+            <v>9</v>
           </cell>
           <cell r="O2">
-            <v>14350</v>
+            <v>13650</v>
           </cell>
         </row>
         <row r="3">
@@ -1441,47 +1523,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.1-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>12000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45213</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1500,15 +1542,15 @@
             <v>17</v>
           </cell>
           <cell r="O1">
-            <v>8600</v>
+            <v>11400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>6</v>
+            <v>8</v>
           </cell>
           <cell r="O2">
-            <v>15400</v>
+            <v>12600</v>
           </cell>
         </row>
         <row r="3">
@@ -1523,7 +1565,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1542,15 +1584,15 @@
             <v>48</v>
           </cell>
           <cell r="O1">
-            <v>1750</v>
+            <v>2450</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>5</v>
+            <v>7</v>
           </cell>
           <cell r="O2">
-            <v>15050</v>
+            <v>14350</v>
           </cell>
         </row>
         <row r="3">
@@ -1565,7 +1607,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1584,15 +1626,15 @@
             <v>17</v>
           </cell>
           <cell r="O1">
-            <v>4400</v>
+            <v>7200</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="O2">
-            <v>19600</v>
+            <v>16800</v>
           </cell>
         </row>
         <row r="3">
@@ -1607,7 +1649,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1625,15 +1667,15 @@
             <v>17</v>
           </cell>
           <cell r="O1">
-            <v>1400</v>
+            <v>2100</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>4</v>
+            <v>6</v>
           </cell>
           <cell r="O2">
-            <v>4600</v>
+            <v>3900</v>
           </cell>
         </row>
         <row r="3">
@@ -1647,7 +1689,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1686,81 +1728,24 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.20-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>5000</v>
-          </cell>
-          <cell r="K1">
-            <v>16</v>
-          </cell>
-          <cell r="O1">
-            <v>350</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>1</v>
-          </cell>
-          <cell r="O2">
-            <v>5650</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45427</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
+      <sheetName val="MD50000.15-DEC"/>
+      <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>110</v>
-          </cell>
-          <cell r="O1">
-            <v>2000</v>
-          </cell>
-        </row>
         <row r="2">
-          <cell r="K2">
-            <v>10</v>
-          </cell>
           <cell r="O2">
-            <v>22000</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45425</v>
-          </cell>
-        </row>
-      </sheetData>
+            <v>60200</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1781,18 +1766,23 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>17</v>
+            <v>14</v>
           </cell>
           <cell r="O1">
-            <v>0</v>
+            <v>1050</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="O2">
-            <v>6000</v>
+            <v>4950</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45427</v>
           </cell>
         </row>
       </sheetData>
@@ -1806,7 +1796,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
-      <sheetName val="MD20000.22-DEC"/>
+      <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -1816,23 +1806,23 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>119</v>
+            <v>95</v>
           </cell>
           <cell r="O1">
-            <v>200</v>
+            <v>5000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>1</v>
+            <v>25</v>
           </cell>
           <cell r="O2">
-            <v>23800</v>
+            <v>19000</v>
           </cell>
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45432</v>
+            <v>45425</v>
           </cell>
         </row>
       </sheetData>
@@ -1846,19 +1836,36 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
-      <sheetName val="MD20000.15-DEC"/>
-      <sheetName val="Sheet1"/>
+      <sheetName val="MD10000.20-OCT"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>5000</v>
+          </cell>
+          <cell r="K1">
+            <v>15</v>
+          </cell>
+          <cell r="O1">
+            <v>700</v>
+          </cell>
+        </row>
         <row r="2">
+          <cell r="K2">
+            <v>2</v>
+          </cell>
           <cell r="O2">
-            <v>4200</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+            <v>5300</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45436</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1909,19 +1916,191 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
-      <sheetName val="MD50000.15-DEC"/>
-      <sheetName val="Sheet1"/>
+      <sheetName val="MD20000.22-DEC"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>106</v>
+          </cell>
+          <cell r="O1">
+            <v>2800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>14</v>
+          </cell>
+          <cell r="O2">
+            <v>21200</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45432</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="G1">
+            <v>120</v>
+          </cell>
+          <cell r="K1">
+            <v>110</v>
+          </cell>
+          <cell r="O1">
+            <v>1000</v>
+          </cell>
+        </row>
         <row r="2">
           <cell r="O2">
-            <v>63000</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+            <v>11000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45437</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.20-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>5000</v>
+          </cell>
+          <cell r="K1">
+            <v>16</v>
+          </cell>
+          <cell r="O1">
+            <v>350</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>1</v>
+          </cell>
+          <cell r="O2">
+            <v>5650</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45444</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>17</v>
+          </cell>
+          <cell r="O1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>0</v>
+          </cell>
+          <cell r="O2">
+            <v>12000</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.22-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>118</v>
+          </cell>
+          <cell r="O1">
+            <v>400</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>2</v>
+          </cell>
+          <cell r="O2">
+            <v>23600</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45446</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2398,7 +2577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:Q43"/>
+  <dimension ref="B2:Q47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="1" customWidth="1"/>
@@ -2422,23 +2601,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="I2" s="20" t="s">
+      <c r="C2" s="25"/>
+      <c r="I2" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="21"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="18">
+      <c r="J2" s="22"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="19">
         <f>SUM(L5:L48)</f>
-        <v>370900</v>
-      </c>
-      <c r="M2" s="19"/>
+        <v>359250</v>
+      </c>
+      <c r="M2" s="20"/>
       <c r="N2" s="1">
         <f>SUM(N5:N49)</f>
-        <v>21350</v>
+        <v>23450</v>
       </c>
       <c r="Q2" s="1">
         <f>14900+260750</f>
@@ -2852,7 +3031,7 @@
         <f>'[8]MD20000.15-DEC'!$O$1</f>
         <v>24000</v>
       </c>
-      <c r="Q13" s="25"/>
+      <c r="Q13" s="18"/>
     </row>
     <row r="14" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="13">
@@ -2912,11 +3091,11 @@
       <c r="G15" s="9"/>
       <c r="H15" s="9">
         <f>'[10]MD50000.15-DEC'!$K$1</f>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I15" s="9">
         <f>'[10]MD50000.15-DEC'!$K$2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J15" s="10" t="s">
         <v>12</v>
@@ -2927,11 +3106,11 @@
       </c>
       <c r="L15" s="8">
         <f>'[10]MD50000.15-DEC'!$O$2</f>
-        <v>45500</v>
+        <v>42000</v>
       </c>
       <c r="M15" s="8">
         <f>'[10]MD50000.15-DEC'!$O$1</f>
-        <v>38500</v>
+        <v>42000</v>
       </c>
       <c r="N15" s="1">
         <v>1750</v>
@@ -3002,16 +3181,13 @@
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
       <c r="J17" s="10" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="K17" s="11">
         <f>'[12]MD20000.22-DEC'!$B$3</f>
         <v>0</v>
       </c>
-      <c r="L17" s="8">
-        <f>'[12]MD20000.22-DEC'!$O$2</f>
-        <v>24000</v>
-      </c>
+      <c r="L17" s="8"/>
       <c r="M17" s="8">
         <f>'[12]MD20000.22-DEC'!$O$1</f>
         <v>0</v>
@@ -3035,11 +3211,11 @@
       <c r="G18" s="14"/>
       <c r="H18" s="14">
         <f>'[13]MD50000.15-DEC'!$K$1</f>
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I18" s="14">
         <f>'[13]MD50000.15-DEC'!$K$2</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J18" s="17" t="s">
         <v>12</v>
@@ -3050,11 +3226,11 @@
       </c>
       <c r="L18" s="16">
         <f>'[13]MD50000.15-DEC'!$O$2</f>
-        <v>10150</v>
+        <v>9450</v>
       </c>
       <c r="M18" s="16">
         <f>'[13]MD50000.15-DEC'!$O$1</f>
-        <v>6650</v>
+        <v>7350</v>
       </c>
       <c r="N18" s="1">
         <v>350</v>
@@ -3118,11 +3294,11 @@
       <c r="G20" s="14"/>
       <c r="H20" s="14">
         <f>'[15]MD10000.10-JAN'!$K$1</f>
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I20" s="14">
         <f>'[15]MD10000.10-JAN'!$K$2</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J20" s="17" t="s">
         <v>12</v>
@@ -3133,11 +3309,11 @@
       </c>
       <c r="L20" s="16">
         <f>'[15]MD10000.10-JAN'!$O$2</f>
-        <v>10500</v>
+        <v>9800</v>
       </c>
       <c r="M20" s="16">
         <f>'[15]MD10000.10-JAN'!$O$1</f>
-        <v>6300</v>
+        <v>7000</v>
       </c>
       <c r="N20" s="1">
         <v>350</v>
@@ -3161,11 +3337,11 @@
       <c r="G21" s="9"/>
       <c r="H21" s="9">
         <f>'[16]MD10000.10-JAN'!$K$1</f>
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I21" s="9">
         <f>'[16]MD10000.10-JAN'!$K$2</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J21" s="10" t="s">
         <v>12</v>
@@ -3176,11 +3352,11 @@
       </c>
       <c r="L21" s="8">
         <f>'[16]MD10000.10-JAN'!$O$2</f>
-        <v>10500</v>
+        <v>9800</v>
       </c>
       <c r="M21" s="8">
         <f>'[16]MD10000.10-JAN'!$O$1</f>
-        <v>6300</v>
+        <v>7000</v>
       </c>
       <c r="N21" s="1">
         <v>350</v>
@@ -3244,11 +3420,11 @@
       <c r="G23" s="9"/>
       <c r="H23" s="9">
         <f>'[18]MD10000.20-OCT'!$K$1</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I23" s="9">
         <f>'[18]MD10000.20-OCT'!$K$2</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J23" s="10" t="s">
         <v>12</v>
@@ -3259,11 +3435,11 @@
       </c>
       <c r="L23" s="8">
         <f>'[18]MD10000.20-OCT'!$O$2</f>
-        <v>11200</v>
+        <v>10500</v>
       </c>
       <c r="M23" s="8">
         <f>'[18]MD10000.20-OCT'!$O$1</f>
-        <v>5600</v>
+        <v>6300</v>
       </c>
       <c r="N23" s="1">
         <v>350</v>
@@ -3287,11 +3463,11 @@
       <c r="G24" s="9"/>
       <c r="H24" s="9">
         <f>'[19]MD10000.20-OCT'!$K$1</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I24" s="9">
         <f>'[19]MD10000.20-OCT'!$K$2</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J24" s="10" t="s">
         <v>12</v>
@@ -3302,11 +3478,11 @@
       </c>
       <c r="L24" s="8">
         <f>'[19]MD10000.20-OCT'!$O$2</f>
-        <v>11200</v>
+        <v>10500</v>
       </c>
       <c r="M24" s="8">
         <f>'[19]MD10000.20-OCT'!$O$1</f>
-        <v>5600</v>
+        <v>6300</v>
       </c>
       <c r="N24" s="1">
         <v>350</v>
@@ -3328,11 +3504,11 @@
       </c>
       <c r="F25" s="9">
         <f>'[20]SM5000.1-oct'!$K$1</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G25" s="9">
         <f>'[20]SM5000.1-oct'!$K$2</f>
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
@@ -3345,11 +3521,11 @@
       </c>
       <c r="L25" s="8">
         <f>'[20]SM5000.1-oct'!$O$2</f>
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="M25" s="8">
         <f>'[20]SM5000.1-oct'!$O$1</f>
-        <v>4700</v>
+        <v>4900</v>
       </c>
       <c r="N25" s="1">
         <v>700</v>
@@ -3373,14 +3549,14 @@
       <c r="G26" s="9"/>
       <c r="H26" s="9">
         <f>'[21]MD10000.20-OCT'!$K$1</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I26" s="9">
         <f>'[21]MD10000.20-OCT'!$K$2</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="K26" s="11">
         <f>'[21]MD10000.20-OCT'!$B$3</f>
@@ -3388,14 +3564,11 @@
       </c>
       <c r="L26" s="8">
         <f>'[21]MD10000.20-OCT'!$O$2</f>
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="M26" s="8">
         <f>'[21]MD10000.20-OCT'!$O$1</f>
-        <v>5300</v>
-      </c>
-      <c r="N26" s="1">
-        <v>350</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -3457,16 +3630,16 @@
       </c>
       <c r="F28" s="9">
         <f>'[23]MD10000.1-OCT'!$K$1</f>
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G28" s="9">
         <f>'[23]MD10000.1-OCT'!$K$2</f>
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="H28" s="9"/>
       <c r="I28" s="9"/>
       <c r="J28" s="10" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="K28" s="11">
         <f>'[23]MD10000.1-OCT'!$B$3</f>
@@ -3474,14 +3647,11 @@
       </c>
       <c r="L28" s="8">
         <f>'[23]MD10000.1-OCT'!$O$2</f>
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="M28" s="8">
         <f>'[23]MD10000.1-OCT'!$O$1</f>
-        <v>9900</v>
-      </c>
-      <c r="N28" s="1">
-        <v>700</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="29" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3516,8 +3686,8 @@
         <v>45337</v>
       </c>
       <c r="L29" s="8">
-        <f>'[39]MD20000.15-DEC'!$O$2</f>
-        <v>4200</v>
+        <f>'[25]MD20000.15-DEC'!$O$2</f>
+        <v>1400</v>
       </c>
       <c r="M29" s="8">
         <f>'[24]MD20000.15-DEC'!$O$1</f>
@@ -3538,33 +3708,33 @@
         <v>52</v>
       </c>
       <c r="E30" s="8">
-        <f>'[25]MD20000.15-DEC'!$C$1</f>
+        <f>'[26]MD20000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9">
-        <f>'[25]MD20000.15-DEC'!$K$1</f>
-        <v>4</v>
+        <f>'[26]MD20000.15-DEC'!$K$1</f>
+        <v>2</v>
       </c>
       <c r="I30" s="9">
-        <f>'[25]MD20000.15-DEC'!$K$2</f>
-        <v>13</v>
+        <f>'[26]MD20000.15-DEC'!$K$2</f>
+        <v>15</v>
       </c>
       <c r="J30" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K30" s="11">
-        <f>'[25]MD20000.15-DEC'!$B$3</f>
+        <f>'[26]MD20000.15-DEC'!$B$3</f>
         <v>45345</v>
       </c>
       <c r="L30" s="8">
-        <f>'[25]MD20000.15-DEC'!$O$2</f>
-        <v>5800</v>
+        <f>'[26]MD20000.15-DEC'!$O$2</f>
+        <v>3000</v>
       </c>
       <c r="M30" s="8">
-        <f>'[25]MD20000.15-DEC'!$O$1</f>
-        <v>18200</v>
+        <f>'[26]MD20000.15-DEC'!$O$1</f>
+        <v>21000</v>
       </c>
       <c r="N30" s="1">
         <v>1400</v>
@@ -3581,16 +3751,16 @@
         <v>33</v>
       </c>
       <c r="E31" s="16">
-        <f>'[26]MD20000.18-DEC'!$C$1</f>
+        <f>'[27]MD20000.18-DEC'!$C$1</f>
         <v>30000</v>
       </c>
       <c r="F31" s="14">
-        <f>'[26]MD20000.18-DEC'!$K$1</f>
-        <v>41</v>
+        <f>'[27]MD20000.18-DEC'!$K$1</f>
+        <v>30</v>
       </c>
       <c r="G31" s="14">
-        <f>'[26]MD20000.18-DEC'!$K$2</f>
-        <v>79</v>
+        <f>'[27]MD20000.18-DEC'!$K$2</f>
+        <v>90</v>
       </c>
       <c r="H31" s="14"/>
       <c r="I31" s="14"/>
@@ -3598,16 +3768,16 @@
         <v>12</v>
       </c>
       <c r="K31" s="15">
-        <f>'[26]MD20000.18-DEC'!$B$3</f>
+        <f>'[27]MD20000.18-DEC'!$B$3</f>
         <v>45354</v>
       </c>
       <c r="L31" s="16">
-        <f>'[26]MD20000.18-DEC'!$O$2</f>
-        <v>12300</v>
+        <f>'[27]MD20000.18-DEC'!$O$2</f>
+        <v>9000</v>
       </c>
       <c r="M31" s="16">
-        <f>'[26]MD20000.18-DEC'!$O$1</f>
-        <v>23700</v>
+        <f>'[27]MD20000.18-DEC'!$O$1</f>
+        <v>27000</v>
       </c>
       <c r="N31" s="1">
         <v>2100</v>
@@ -3624,33 +3794,33 @@
         <v>36</v>
       </c>
       <c r="E32" s="16">
-        <f>'[27]MD10000.10-JAN'!$C$1</f>
+        <f>'[28]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F32" s="14"/>
       <c r="G32" s="14"/>
       <c r="H32" s="14">
-        <f>'[27]MD10000.10-JAN'!$K$1</f>
-        <v>38</v>
+        <f>'[28]MD10000.10-JAN'!$K$1</f>
+        <v>36</v>
       </c>
       <c r="I32" s="14">
-        <f>'[27]MD10000.10-JAN'!$K$2</f>
-        <v>10</v>
+        <f>'[28]MD10000.10-JAN'!$K$2</f>
+        <v>12</v>
       </c>
       <c r="J32" s="17" t="s">
         <v>12</v>
       </c>
       <c r="K32" s="15">
-        <f>'[27]MD10000.10-JAN'!$B$3</f>
+        <f>'[28]MD10000.10-JAN'!$B$3</f>
         <v>45366</v>
       </c>
       <c r="L32" s="16">
-        <f>'[27]MD10000.10-JAN'!$O$2</f>
-        <v>13300</v>
+        <f>'[28]MD10000.10-JAN'!$O$2</f>
+        <v>12600</v>
       </c>
       <c r="M32" s="16">
-        <f>'[27]MD10000.10-JAN'!$O$1</f>
-        <v>3500</v>
+        <f>'[28]MD10000.10-JAN'!$O$1</f>
+        <v>4200</v>
       </c>
       <c r="N32" s="1">
         <v>350</v>
@@ -3667,33 +3837,33 @@
         <v>52</v>
       </c>
       <c r="E33" s="16">
-        <f>'[28]MD20000.15-DEc'!$C$1</f>
+        <f>'[29]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F33" s="14"/>
       <c r="G33" s="14"/>
       <c r="H33" s="14">
-        <f>'[28]MD20000.15-DEc'!$K$1</f>
-        <v>9</v>
+        <f>'[29]MD20000.15-DEc'!$K$1</f>
+        <v>7</v>
       </c>
       <c r="I33" s="14">
-        <f>'[28]MD20000.15-DEc'!$K$2</f>
-        <v>8</v>
+        <f>'[29]MD20000.15-DEc'!$K$2</f>
+        <v>10</v>
       </c>
       <c r="J33" s="17" t="s">
         <v>12</v>
       </c>
       <c r="K33" s="15">
-        <f>'[28]MD20000.15-DEc'!$B$3</f>
+        <f>'[29]MD20000.15-DEc'!$B$3</f>
         <v>45380</v>
       </c>
       <c r="L33" s="16">
-        <f>'[28]MD20000.15-DEc'!$O$2</f>
-        <v>12600</v>
+        <f>'[29]MD20000.15-DEc'!$O$2</f>
+        <v>9800</v>
       </c>
       <c r="M33" s="16">
-        <f>'[28]MD20000.15-DEc'!$O$1</f>
-        <v>11400</v>
+        <f>'[29]MD20000.15-DEc'!$O$1</f>
+        <v>14200</v>
       </c>
       <c r="N33" s="1">
         <v>1400</v>
@@ -3710,33 +3880,33 @@
         <v>36</v>
       </c>
       <c r="E34" s="16">
-        <f>'[29]MD10000.10-JAN'!$C$1</f>
+        <f>'[30]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F34" s="14"/>
       <c r="G34" s="14"/>
       <c r="H34" s="14">
-        <f>'[29]MD10000.10-JAN'!$K$1</f>
-        <v>41</v>
+        <f>'[30]MD10000.10-JAN'!$K$1</f>
+        <v>39</v>
       </c>
       <c r="I34" s="14">
-        <f>'[29]MD10000.10-JAN'!$K$2</f>
-        <v>7</v>
+        <f>'[30]MD10000.10-JAN'!$K$2</f>
+        <v>9</v>
       </c>
       <c r="J34" s="17" t="s">
         <v>12</v>
       </c>
       <c r="K34" s="15">
-        <f>'[29]MD10000.10-JAN'!$B$3</f>
+        <f>'[30]MD10000.10-JAN'!$B$3</f>
         <v>45389</v>
       </c>
       <c r="L34" s="16">
-        <f>'[29]MD10000.10-JAN'!$O$2</f>
-        <v>14350</v>
+        <f>'[30]MD10000.10-JAN'!$O$2</f>
+        <v>13650</v>
       </c>
       <c r="M34" s="16">
-        <f>'[29]MD10000.10-JAN'!$O$1</f>
-        <v>2450</v>
+        <f>'[30]MD10000.10-JAN'!$O$1</f>
+        <v>3150</v>
       </c>
       <c r="N34" s="1">
         <v>350</v>
@@ -3753,33 +3923,33 @@
         <v>52</v>
       </c>
       <c r="E35" s="8">
-        <f>'[30]MD20000.15-DEc'!$C$1</f>
+        <f>'[31]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>
       <c r="H35" s="9">
-        <f>'[30]MD20000.15-DEc'!$G$1</f>
+        <f>'[31]MD20000.15-DEc'!$G$1</f>
         <v>17</v>
       </c>
       <c r="I35" s="9">
-        <f>'[30]MD20000.15-DEc'!$K$2</f>
-        <v>6</v>
+        <f>'[31]MD20000.15-DEc'!$K$2</f>
+        <v>8</v>
       </c>
       <c r="J35" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K35" s="11">
-        <f>'[30]MD20000.15-DEc'!$B$3</f>
+        <f>'[31]MD20000.15-DEc'!$B$3</f>
         <v>45394</v>
       </c>
       <c r="L35" s="8">
-        <f>'[30]MD20000.15-DEc'!$O$2</f>
-        <v>15400</v>
+        <f>'[31]MD20000.15-DEc'!$O$2</f>
+        <v>12600</v>
       </c>
       <c r="M35" s="8">
-        <f>'[30]MD20000.15-DEc'!$O$1</f>
-        <v>8600</v>
+        <f>'[31]MD20000.15-DEc'!$O$1</f>
+        <v>11400</v>
       </c>
       <c r="N35" s="1">
         <v>1400</v>
@@ -3796,33 +3966,33 @@
         <v>39</v>
       </c>
       <c r="E36" s="16">
-        <f>'[31]MD10000.10-JAN'!$C$1</f>
+        <f>'[32]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F36" s="14"/>
       <c r="G36" s="14"/>
       <c r="H36" s="14">
-        <f>'[31]MD10000.10-JAN'!$G$1</f>
+        <f>'[32]MD10000.10-JAN'!$G$1</f>
         <v>48</v>
       </c>
       <c r="I36" s="14">
-        <f>'[31]MD10000.10-JAN'!$K$2</f>
-        <v>5</v>
+        <f>'[32]MD10000.10-JAN'!$K$2</f>
+        <v>7</v>
       </c>
       <c r="J36" s="17" t="s">
         <v>12</v>
       </c>
       <c r="K36" s="15">
-        <f>'[31]MD10000.10-JAN'!$B$3</f>
+        <f>'[32]MD10000.10-JAN'!$B$3</f>
         <v>45399</v>
       </c>
       <c r="L36" s="16">
-        <f>'[31]MD10000.10-JAN'!$O$2</f>
-        <v>15050</v>
+        <f>'[32]MD10000.10-JAN'!$O$2</f>
+        <v>14350</v>
       </c>
       <c r="M36" s="16">
-        <f>'[31]MD10000.10-JAN'!$O$1</f>
-        <v>1750</v>
+        <f>'[32]MD10000.10-JAN'!$O$1</f>
+        <v>2450</v>
       </c>
       <c r="N36" s="1">
         <v>350</v>
@@ -3839,33 +4009,33 @@
         <v>52</v>
       </c>
       <c r="E37" s="8">
-        <f>'[32]MD20000.15-DEc'!$C$1</f>
+        <f>'[33]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F37" s="9"/>
       <c r="G37" s="9"/>
       <c r="H37" s="9">
-        <f>'[32]MD20000.15-DEc'!$G$1</f>
+        <f>'[33]MD20000.15-DEc'!$G$1</f>
         <v>17</v>
       </c>
       <c r="I37" s="9">
-        <f>'[32]MD20000.15-DEc'!$K$2</f>
-        <v>3</v>
+        <f>'[33]MD20000.15-DEc'!$K$2</f>
+        <v>5</v>
       </c>
       <c r="J37" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K37" s="11">
-        <f>'[32]MD20000.15-DEc'!$B$3</f>
+        <f>'[33]MD20000.15-DEc'!$B$3</f>
         <v>45406</v>
       </c>
       <c r="L37" s="8">
-        <f>'[32]MD20000.15-DEc'!$O$2</f>
-        <v>19600</v>
+        <f>'[33]MD20000.15-DEc'!$O$2</f>
+        <v>16800</v>
       </c>
       <c r="M37" s="8">
-        <f>'[32]MD20000.15-DEc'!$O$1</f>
-        <v>4400</v>
+        <f>'[33]MD20000.15-DEc'!$O$1</f>
+        <v>7200</v>
       </c>
       <c r="N37" s="1">
         <v>1400</v>
@@ -3882,33 +4052,33 @@
         <v>60</v>
       </c>
       <c r="E38" s="16">
-        <f>'[33]MD10000.20-OCT'!$C$1</f>
+        <f>'[34]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F38" s="14"/>
       <c r="G38" s="14"/>
       <c r="H38" s="14">
-        <f>'[33]MD10000.20-OCT'!$G$1</f>
+        <f>'[34]MD10000.20-OCT'!$G$1</f>
         <v>17</v>
       </c>
       <c r="I38" s="14">
-        <f>'[33]MD10000.20-OCT'!$K$2</f>
-        <v>4</v>
+        <f>'[34]MD10000.20-OCT'!$K$2</f>
+        <v>6</v>
       </c>
       <c r="J38" s="17" t="s">
         <v>12</v>
       </c>
       <c r="K38" s="15">
-        <f>'[33]MD10000.20-OCT'!$B$3</f>
+        <f>'[34]MD10000.20-OCT'!$B$3</f>
         <v>45406</v>
       </c>
       <c r="L38" s="16">
-        <f>'[33]MD10000.20-OCT'!$O$2</f>
-        <v>4600</v>
+        <f>'[34]MD10000.20-OCT'!$O$2</f>
+        <v>3900</v>
       </c>
       <c r="M38" s="16">
-        <f>'[33]MD10000.20-OCT'!$O$1</f>
-        <v>1400</v>
+        <f>'[34]MD10000.20-OCT'!$O$1</f>
+        <v>2100</v>
       </c>
       <c r="N38" s="1">
         <v>350</v>
@@ -3925,32 +4095,32 @@
         <v>62</v>
       </c>
       <c r="E39" s="8">
-        <f>'[34]MD50000.15-DEC'!$C$1</f>
+        <f>'[35]MD50000.15-DEC'!$C$1</f>
         <v>40000</v>
       </c>
       <c r="F39" s="9"/>
       <c r="G39" s="9"/>
       <c r="H39" s="9">
-        <f>'[34]MD50000.15-DEC'!$K$1</f>
+        <f>'[35]MD50000.15-DEC'!$K$1</f>
         <v>47</v>
       </c>
       <c r="I39" s="9">
-        <f>'[34]MD50000.15-DEC'!$K$2</f>
+        <f>'[35]MD50000.15-DEC'!$K$2</f>
         <v>1</v>
       </c>
       <c r="J39" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K39" s="11">
-        <f>'[34]MD50000.15-DEC'!$B$3</f>
+        <f>'[35]MD50000.15-DEC'!$B$3</f>
         <v>45416</v>
       </c>
       <c r="L39" s="8">
-        <f>'[40]MD50000.15-DEC'!$O$2</f>
-        <v>63000</v>
+        <f>'[36]MD50000.15-DEC'!$O$2</f>
+        <v>60200</v>
       </c>
       <c r="M39" s="8">
-        <f>'[34]MD50000.15-DEC'!$O$1</f>
+        <f>'[35]MD50000.15-DEC'!$O$1</f>
         <v>1400</v>
       </c>
       <c r="N39" s="1">
@@ -3968,33 +4138,33 @@
         <v>43</v>
       </c>
       <c r="E40" s="8">
-        <f>'[35]MD10000.20-OCT'!$C$1</f>
+        <f>'[37]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F40" s="9"/>
       <c r="G40" s="9"/>
       <c r="H40" s="9">
-        <f>'[35]MD10000.20-OCT'!$K$1</f>
-        <v>16</v>
+        <f>'[37]MD10000.20-OCT'!$K$1</f>
+        <v>14</v>
       </c>
       <c r="I40" s="9">
-        <f>'[35]MD10000.20-OCT'!$K$2</f>
-        <v>1</v>
+        <f>'[37]MD10000.20-OCT'!$K$2</f>
+        <v>3</v>
       </c>
       <c r="J40" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K40" s="11">
-        <f>'[35]MD10000.20-OCT'!$B$3</f>
+        <f>'[37]MD10000.20-OCT'!$B$3</f>
         <v>45427</v>
       </c>
       <c r="L40" s="8">
-        <f>'[35]MD10000.20-OCT'!$O$2</f>
-        <v>5650</v>
+        <f>'[37]MD10000.20-OCT'!$O$2</f>
+        <v>4950</v>
       </c>
       <c r="M40" s="8">
-        <f>'[35]MD10000.20-OCT'!$O$1</f>
-        <v>350</v>
+        <f>'[37]MD10000.20-OCT'!$O$1</f>
+        <v>1050</v>
       </c>
       <c r="N40" s="1">
         <v>350</v>
@@ -4011,16 +4181,16 @@
         <v>33</v>
       </c>
       <c r="E41" s="8">
-        <f>'[36]MD20000.18-DEC'!$C$1</f>
+        <f>'[38]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F41" s="9">
-        <f>'[36]MD20000.18-DEC'!$K$1</f>
-        <v>110</v>
+        <f>'[38]MD20000.18-DEC'!$K$1</f>
+        <v>95</v>
       </c>
       <c r="G41" s="9">
-        <f>'[36]MD20000.18-DEC'!$K$2</f>
-        <v>10</v>
+        <f>'[38]MD20000.18-DEC'!$K$2</f>
+        <v>25</v>
       </c>
       <c r="H41" s="9"/>
       <c r="I41" s="9"/>
@@ -4028,16 +4198,16 @@
         <v>12</v>
       </c>
       <c r="K41" s="11">
-        <f>'[36]MD20000.18-DEC'!$B$3</f>
+        <f>'[38]MD20000.18-DEC'!$B$3</f>
         <v>45425</v>
       </c>
       <c r="L41" s="8">
-        <f>'[36]MD20000.18-DEC'!$O$2</f>
-        <v>22000</v>
+        <f>'[38]MD20000.18-DEC'!$O$2</f>
+        <v>19000</v>
       </c>
       <c r="M41" s="8">
-        <f>'[36]MD20000.18-DEC'!$O$1</f>
-        <v>2000</v>
+        <f>'[38]MD20000.18-DEC'!$O$1</f>
+        <v>5000</v>
       </c>
       <c r="N41" s="1">
         <v>1400</v>
@@ -4054,33 +4224,33 @@
         <v>66</v>
       </c>
       <c r="E42" s="8">
-        <f>'[37]MD10000.20-OCT'!$C$1</f>
+        <f>'[39]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F42" s="9"/>
       <c r="G42" s="9"/>
       <c r="H42" s="9">
-        <f>'[37]MD10000.20-OCT'!$K$1</f>
-        <v>17</v>
+        <f>'[39]MD10000.20-OCT'!$K$1</f>
+        <v>15</v>
       </c>
       <c r="I42" s="9">
-        <f>'[37]MD10000.20-OCT'!$K$2</f>
-        <v>0</v>
+        <f>'[39]MD10000.20-OCT'!$K$2</f>
+        <v>2</v>
       </c>
       <c r="J42" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K42" s="11">
-        <f>'[37]MD10000.20-OCT'!$B$3</f>
-        <v>0</v>
+        <f>'[39]MD10000.20-OCT'!$B$3</f>
+        <v>45436</v>
       </c>
       <c r="L42" s="8">
-        <f>'[37]MD10000.20-OCT'!$O$2</f>
-        <v>6000</v>
+        <f>'[39]MD10000.20-OCT'!$O$2</f>
+        <v>5300</v>
       </c>
       <c r="M42" s="8">
-        <f>'[37]MD10000.20-OCT'!$O$1</f>
-        <v>0</v>
+        <f>'[39]MD10000.20-OCT'!$O$1</f>
+        <v>700</v>
       </c>
       <c r="N42" s="1">
         <v>350</v>
@@ -4097,16 +4267,16 @@
         <v>33</v>
       </c>
       <c r="E43" s="8">
-        <f>'[38]MD20000.22-DEC'!$C$1</f>
+        <f>'[40]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F43" s="9">
-        <f>'[38]MD20000.22-DEC'!$K$1</f>
-        <v>119</v>
+        <f>'[40]MD20000.22-DEC'!$K$1</f>
+        <v>106</v>
       </c>
       <c r="G43" s="9">
-        <f>'[38]MD20000.22-DEC'!$K$2</f>
-        <v>1</v>
+        <f>'[40]MD20000.22-DEC'!$K$2</f>
+        <v>14</v>
       </c>
       <c r="H43" s="9"/>
       <c r="I43" s="9"/>
@@ -4114,18 +4284,190 @@
         <v>12</v>
       </c>
       <c r="K43" s="11">
-        <f>'[38]MD20000.22-DEC'!$B$3</f>
+        <f>'[40]MD20000.22-DEC'!$B$3</f>
         <v>45432</v>
       </c>
       <c r="L43" s="8">
-        <f>'[38]MD20000.22-DEC'!$O$2</f>
-        <v>23800</v>
+        <f>'[40]MD20000.22-DEC'!$O$2</f>
+        <v>21200</v>
       </c>
       <c r="M43" s="8">
-        <f>'[38]MD20000.22-DEC'!$O$1</f>
-        <v>200</v>
+        <f>'[40]MD20000.22-DEC'!$O$1</f>
+        <v>2800</v>
       </c>
       <c r="N43" s="1">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="6">
+        <v>40</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E44" s="8">
+        <f>'[41]MD10000.1-OCT'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F44" s="9">
+        <f>'[41]MD10000.1-OCT'!$G$1</f>
+        <v>120</v>
+      </c>
+      <c r="G44" s="9">
+        <f>'[41]MD10000.1-OCT'!$K$1</f>
+        <v>110</v>
+      </c>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K44" s="11">
+        <f>'[41]MD10000.1-OCT'!$B$3</f>
+        <v>45437</v>
+      </c>
+      <c r="L44" s="8">
+        <f>'[41]MD10000.1-OCT'!$O$2</f>
+        <v>11000</v>
+      </c>
+      <c r="M44" s="8">
+        <f>'[41]MD10000.1-OCT'!$O$1</f>
+        <v>1000</v>
+      </c>
+      <c r="N44" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="6">
+        <v>41</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E45" s="8">
+        <f>'[42]MD10000.20-OCT'!$C$1</f>
+        <v>5000</v>
+      </c>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9">
+        <f>'[42]MD10000.20-OCT'!$K$1</f>
+        <v>16</v>
+      </c>
+      <c r="I45" s="9">
+        <f>'[42]MD10000.20-OCT'!$K$2</f>
+        <v>1</v>
+      </c>
+      <c r="J45" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K45" s="11">
+        <f>'[42]MD10000.20-OCT'!$B$3</f>
+        <v>45444</v>
+      </c>
+      <c r="L45" s="8">
+        <f>'[42]MD10000.20-OCT'!$O$2</f>
+        <v>5650</v>
+      </c>
+      <c r="M45" s="8">
+        <f>'[42]MD10000.20-OCT'!$O$1</f>
+        <v>350</v>
+      </c>
+      <c r="N45" s="1">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="6">
+        <v>42</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E46" s="8">
+        <f>'[43]MD10000.1-OCT'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9">
+        <f>'[43]MD10000.1-OCT'!$K$1</f>
+        <v>17</v>
+      </c>
+      <c r="I46" s="9">
+        <f>'[43]MD10000.1-OCT'!$K$2</f>
+        <v>0</v>
+      </c>
+      <c r="J46" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K46" s="11">
+        <f>'[43]MD10000.1-OCT'!$B$3</f>
+        <v>0</v>
+      </c>
+      <c r="L46" s="8">
+        <f>'[43]MD10000.1-OCT'!$O$2</f>
+        <v>12000</v>
+      </c>
+      <c r="M46" s="8">
+        <f>'[43]MD10000.1-OCT'!$O$1</f>
+        <v>0</v>
+      </c>
+      <c r="N46" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="6">
+        <v>43</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E47" s="8">
+        <f>'[44]MD20000.22-DEC'!$C$1</f>
+        <v>20000</v>
+      </c>
+      <c r="F47" s="9">
+        <f>'[44]MD20000.22-DEC'!$K$1</f>
+        <v>118</v>
+      </c>
+      <c r="G47" s="9">
+        <f>'[44]MD20000.22-DEC'!$K$2</f>
+        <v>2</v>
+      </c>
+      <c r="H47" s="9"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K47" s="11">
+        <f>'[44]MD20000.22-DEC'!$B$3</f>
+        <v>45446</v>
+      </c>
+      <c r="L47" s="8">
+        <f>'[44]MD20000.22-DEC'!$O$2</f>
+        <v>23600</v>
+      </c>
+      <c r="M47" s="8">
+        <f>'[44]MD20000.22-DEC'!$O$1</f>
+        <v>400</v>
+      </c>
+      <c r="N47" s="1">
         <v>1400</v>
       </c>
     </row>

--- a/LoanOfficer-A/LoanBook.xlsx
+++ b/LoanOfficer-A/LoanBook.xlsx
@@ -54,6 +54,9 @@
     <externalReference r:id="rId43"/>
     <externalReference r:id="rId44"/>
     <externalReference r:id="rId45"/>
+    <externalReference r:id="rId46"/>
+    <externalReference r:id="rId47"/>
+    <externalReference r:id="rId48"/>
   </externalReferences>
   <calcPr calcId="145621" iterateDelta="1E-4"/>
   <extLst>
@@ -65,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="74">
   <si>
     <t>Code</t>
   </si>
@@ -284,6 +287,9 @@
   </si>
   <si>
     <t>Priya daily</t>
+  </si>
+  <si>
+    <t>Rambhabati ricky</t>
   </si>
 </sst>
 </file>
@@ -625,18 +631,18 @@
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>24</v>
+            <v>19</v>
           </cell>
           <cell r="O1">
-            <v>42000</v>
+            <v>50750</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>24</v>
+            <v>29</v>
           </cell>
           <cell r="O2">
-            <v>42000</v>
+            <v>33250</v>
           </cell>
         </row>
         <row r="3">
@@ -739,18 +745,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>27</v>
+            <v>22</v>
           </cell>
           <cell r="O1">
-            <v>7350</v>
+            <v>9100</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>21</v>
+            <v>26</v>
           </cell>
           <cell r="O2">
-            <v>9450</v>
+            <v>7700</v>
           </cell>
         </row>
         <row r="3">
@@ -821,18 +827,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>28</v>
+            <v>22</v>
           </cell>
           <cell r="O1">
-            <v>7000</v>
+            <v>9100</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>20</v>
+            <v>26</v>
           </cell>
           <cell r="O2">
-            <v>9800</v>
+            <v>7700</v>
           </cell>
         </row>
         <row r="3">
@@ -863,18 +869,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>28</v>
+            <v>22</v>
           </cell>
           <cell r="O1">
-            <v>7000</v>
+            <v>9100</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>20</v>
+            <v>26</v>
           </cell>
           <cell r="O2">
-            <v>9800</v>
+            <v>7700</v>
           </cell>
         </row>
         <row r="3">
@@ -944,18 +950,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>30</v>
+            <v>25</v>
           </cell>
           <cell r="O1">
-            <v>6300</v>
+            <v>8050</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>18</v>
+            <v>23</v>
           </cell>
           <cell r="O2">
-            <v>10500</v>
+            <v>8750</v>
           </cell>
         </row>
         <row r="3">
@@ -985,18 +991,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>30</v>
+            <v>25</v>
           </cell>
           <cell r="O1">
-            <v>6300</v>
+            <v>8050</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>18</v>
+            <v>23</v>
           </cell>
           <cell r="O2">
-            <v>10500</v>
+            <v>8750</v>
           </cell>
         </row>
         <row r="3">
@@ -1068,18 +1074,18 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>11</v>
+            <v>9</v>
           </cell>
           <cell r="O1">
-            <v>4900</v>
+            <v>5100</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>49</v>
+            <v>51</v>
           </cell>
           <cell r="O2">
-            <v>1100</v>
+            <v>900</v>
           </cell>
         </row>
         <row r="3">
@@ -1148,18 +1154,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>61</v>
+            <v>54</v>
           </cell>
           <cell r="O1">
-            <v>5900</v>
+            <v>6600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>59</v>
+            <v>66</v>
           </cell>
           <cell r="O2">
-            <v>6100</v>
+            <v>5400</v>
           </cell>
         </row>
         <row r="3">
@@ -1231,9 +1237,6 @@
           <cell r="K1">
             <v>5</v>
           </cell>
-          <cell r="O1">
-            <v>17000</v>
-          </cell>
         </row>
         <row r="2">
           <cell r="K2">
@@ -1263,9 +1266,14 @@
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
+        <row r="1">
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
         <row r="2">
           <cell r="O2">
-            <v>1400</v>
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
@@ -1291,18 +1299,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
-            <v>21000</v>
+            <v>24000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>15</v>
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>3000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -1332,18 +1340,18 @@
             <v>30000</v>
           </cell>
           <cell r="K1">
-            <v>30</v>
+            <v>3</v>
           </cell>
           <cell r="O1">
-            <v>27000</v>
+            <v>35100</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>90</v>
+            <v>117</v>
           </cell>
           <cell r="O2">
-            <v>9000</v>
+            <v>900</v>
           </cell>
         </row>
         <row r="3">
@@ -1373,18 +1381,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>36</v>
+            <v>31</v>
           </cell>
           <cell r="O1">
-            <v>4200</v>
+            <v>5950</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>12</v>
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>12600</v>
+            <v>10850</v>
           </cell>
         </row>
         <row r="3">
@@ -1415,18 +1423,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>7</v>
+            <v>2</v>
           </cell>
           <cell r="O1">
-            <v>14200</v>
+            <v>21200</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>10</v>
+            <v>15</v>
           </cell>
           <cell r="O2">
-            <v>9800</v>
+            <v>2800</v>
           </cell>
         </row>
         <row r="3">
@@ -1497,18 +1505,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>39</v>
+            <v>34</v>
           </cell>
           <cell r="O1">
-            <v>3150</v>
+            <v>4900</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>9</v>
+            <v>14</v>
           </cell>
           <cell r="O2">
-            <v>13650</v>
+            <v>11900</v>
           </cell>
         </row>
         <row r="3">
@@ -1542,15 +1550,15 @@
             <v>17</v>
           </cell>
           <cell r="O1">
-            <v>11400</v>
+            <v>18400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>8</v>
+            <v>13</v>
           </cell>
           <cell r="O2">
-            <v>12600</v>
+            <v>5600</v>
           </cell>
         </row>
         <row r="3">
@@ -1584,15 +1592,15 @@
             <v>48</v>
           </cell>
           <cell r="O1">
-            <v>2450</v>
+            <v>4550</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>7</v>
+            <v>13</v>
           </cell>
           <cell r="O2">
-            <v>14350</v>
+            <v>12250</v>
           </cell>
         </row>
         <row r="3">
@@ -1626,15 +1634,15 @@
             <v>17</v>
           </cell>
           <cell r="O1">
-            <v>7200</v>
+            <v>15600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>5</v>
+            <v>11</v>
           </cell>
           <cell r="O2">
-            <v>16800</v>
+            <v>8400</v>
           </cell>
         </row>
         <row r="3">
@@ -1657,7 +1665,7 @@
       <sheetName val="MD10000.20-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -1667,15 +1675,15 @@
             <v>17</v>
           </cell>
           <cell r="O1">
-            <v>2100</v>
+            <v>4200</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>6</v>
+            <v>12</v>
           </cell>
           <cell r="O2">
-            <v>3900</v>
+            <v>1800</v>
           </cell>
         </row>
         <row r="3">
@@ -1741,7 +1749,7 @@
       <sheetData sheetId="1">
         <row r="2">
           <cell r="O2">
-            <v>60200</v>
+            <v>54600</v>
           </cell>
         </row>
       </sheetData>
@@ -1766,18 +1774,18 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>14</v>
+            <v>9</v>
           </cell>
           <cell r="O1">
-            <v>1050</v>
+            <v>2800</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>3</v>
+            <v>8</v>
           </cell>
           <cell r="O2">
-            <v>4950</v>
+            <v>3200</v>
           </cell>
         </row>
         <row r="3">
@@ -1806,18 +1814,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>95</v>
+            <v>60</v>
           </cell>
           <cell r="O1">
-            <v>5000</v>
+            <v>12000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>25</v>
+            <v>60</v>
           </cell>
           <cell r="O2">
-            <v>19000</v>
+            <v>12000</v>
           </cell>
         </row>
         <row r="3">
@@ -1846,18 +1854,18 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>15</v>
+            <v>11</v>
           </cell>
           <cell r="O1">
-            <v>700</v>
+            <v>2100</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>2</v>
+            <v>6</v>
           </cell>
           <cell r="O2">
-            <v>5300</v>
+            <v>3900</v>
           </cell>
         </row>
         <row r="3">
@@ -1926,18 +1934,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>106</v>
+            <v>77</v>
           </cell>
           <cell r="O1">
-            <v>2800</v>
+            <v>8600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>14</v>
+            <v>43</v>
           </cell>
           <cell r="O2">
-            <v>21200</v>
+            <v>15400</v>
           </cell>
         </row>
         <row r="3">
@@ -1969,15 +1977,15 @@
             <v>120</v>
           </cell>
           <cell r="K1">
-            <v>110</v>
+            <v>83</v>
           </cell>
           <cell r="O1">
-            <v>1000</v>
+            <v>3700</v>
           </cell>
         </row>
         <row r="2">
           <cell r="O2">
-            <v>11000</v>
+            <v>8300</v>
           </cell>
         </row>
         <row r="3">
@@ -2006,18 +2014,18 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>16</v>
+            <v>12</v>
           </cell>
           <cell r="O1">
-            <v>350</v>
+            <v>1750</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>1</v>
+            <v>5</v>
           </cell>
           <cell r="O2">
-            <v>5650</v>
+            <v>4250</v>
           </cell>
         </row>
         <row r="3">
@@ -2049,15 +2057,17 @@
             <v>17</v>
           </cell>
           <cell r="O1">
-            <v>0</v>
+            <v>2900</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>0</v>
-          </cell>
-          <cell r="O2">
-            <v>12000</v>
+            <v>4</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45450</v>
           </cell>
         </row>
       </sheetData>
@@ -2067,6 +2077,27 @@
 </file>
 
 <file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="O2">
+            <v>8400</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2081,18 +2112,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>118</v>
+            <v>84</v>
           </cell>
           <cell r="O1">
-            <v>400</v>
+            <v>7200</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>2</v>
+            <v>36</v>
           </cell>
           <cell r="O2">
-            <v>23600</v>
+            <v>16800</v>
           </cell>
         </row>
         <row r="3">
@@ -2101,6 +2132,83 @@
           </cell>
         </row>
       </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.22-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>112</v>
+          </cell>
+          <cell r="O1">
+            <v>800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>8</v>
+          </cell>
+          <cell r="O2">
+            <v>11200</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45473</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEc"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>17</v>
+          </cell>
+          <cell r="O1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>0</v>
+          </cell>
+          <cell r="O2">
+            <v>24000</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2577,7 +2685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:Q47"/>
+  <dimension ref="B2:Q49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="1" customWidth="1"/>
@@ -2611,13 +2719,13 @@
       <c r="J2" s="22"/>
       <c r="K2" s="23"/>
       <c r="L2" s="19">
-        <f>SUM(L5:L48)</f>
-        <v>359250</v>
+        <f>SUM(L5:L60)</f>
+        <v>296700</v>
       </c>
       <c r="M2" s="20"/>
       <c r="N2" s="1">
-        <f>SUM(N5:N49)</f>
-        <v>23450</v>
+        <f>SUM(N5:N61)</f>
+        <v>22750</v>
       </c>
       <c r="Q2" s="1">
         <f>14900+260750</f>
@@ -3091,11 +3199,11 @@
       <c r="G15" s="9"/>
       <c r="H15" s="9">
         <f>'[10]MD50000.15-DEC'!$K$1</f>
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I15" s="9">
         <f>'[10]MD50000.15-DEC'!$K$2</f>
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J15" s="10" t="s">
         <v>12</v>
@@ -3106,11 +3214,11 @@
       </c>
       <c r="L15" s="8">
         <f>'[10]MD50000.15-DEC'!$O$2</f>
-        <v>42000</v>
+        <v>33250</v>
       </c>
       <c r="M15" s="8">
         <f>'[10]MD50000.15-DEC'!$O$1</f>
-        <v>42000</v>
+        <v>50750</v>
       </c>
       <c r="N15" s="1">
         <v>1750</v>
@@ -3211,11 +3319,11 @@
       <c r="G18" s="14"/>
       <c r="H18" s="14">
         <f>'[13]MD50000.15-DEC'!$K$1</f>
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I18" s="14">
         <f>'[13]MD50000.15-DEC'!$K$2</f>
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J18" s="17" t="s">
         <v>12</v>
@@ -3226,11 +3334,11 @@
       </c>
       <c r="L18" s="16">
         <f>'[13]MD50000.15-DEC'!$O$2</f>
-        <v>9450</v>
+        <v>7700</v>
       </c>
       <c r="M18" s="16">
         <f>'[13]MD50000.15-DEC'!$O$1</f>
-        <v>7350</v>
+        <v>9100</v>
       </c>
       <c r="N18" s="1">
         <v>350</v>
@@ -3294,11 +3402,11 @@
       <c r="G20" s="14"/>
       <c r="H20" s="14">
         <f>'[15]MD10000.10-JAN'!$K$1</f>
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I20" s="14">
         <f>'[15]MD10000.10-JAN'!$K$2</f>
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J20" s="17" t="s">
         <v>12</v>
@@ -3309,11 +3417,11 @@
       </c>
       <c r="L20" s="16">
         <f>'[15]MD10000.10-JAN'!$O$2</f>
-        <v>9800</v>
+        <v>7700</v>
       </c>
       <c r="M20" s="16">
         <f>'[15]MD10000.10-JAN'!$O$1</f>
-        <v>7000</v>
+        <v>9100</v>
       </c>
       <c r="N20" s="1">
         <v>350</v>
@@ -3337,11 +3445,11 @@
       <c r="G21" s="9"/>
       <c r="H21" s="9">
         <f>'[16]MD10000.10-JAN'!$K$1</f>
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I21" s="9">
         <f>'[16]MD10000.10-JAN'!$K$2</f>
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J21" s="10" t="s">
         <v>12</v>
@@ -3352,11 +3460,11 @@
       </c>
       <c r="L21" s="8">
         <f>'[16]MD10000.10-JAN'!$O$2</f>
-        <v>9800</v>
+        <v>7700</v>
       </c>
       <c r="M21" s="8">
         <f>'[16]MD10000.10-JAN'!$O$1</f>
-        <v>7000</v>
+        <v>9100</v>
       </c>
       <c r="N21" s="1">
         <v>350</v>
@@ -3420,11 +3528,11 @@
       <c r="G23" s="9"/>
       <c r="H23" s="9">
         <f>'[18]MD10000.20-OCT'!$K$1</f>
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I23" s="9">
         <f>'[18]MD10000.20-OCT'!$K$2</f>
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J23" s="10" t="s">
         <v>12</v>
@@ -3435,11 +3543,11 @@
       </c>
       <c r="L23" s="8">
         <f>'[18]MD10000.20-OCT'!$O$2</f>
-        <v>10500</v>
+        <v>8750</v>
       </c>
       <c r="M23" s="8">
         <f>'[18]MD10000.20-OCT'!$O$1</f>
-        <v>6300</v>
+        <v>8050</v>
       </c>
       <c r="N23" s="1">
         <v>350</v>
@@ -3463,11 +3571,11 @@
       <c r="G24" s="9"/>
       <c r="H24" s="9">
         <f>'[19]MD10000.20-OCT'!$K$1</f>
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I24" s="9">
         <f>'[19]MD10000.20-OCT'!$K$2</f>
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J24" s="10" t="s">
         <v>12</v>
@@ -3478,11 +3586,11 @@
       </c>
       <c r="L24" s="8">
         <f>'[19]MD10000.20-OCT'!$O$2</f>
-        <v>10500</v>
+        <v>8750</v>
       </c>
       <c r="M24" s="8">
         <f>'[19]MD10000.20-OCT'!$O$1</f>
-        <v>6300</v>
+        <v>8050</v>
       </c>
       <c r="N24" s="1">
         <v>350</v>
@@ -3504,11 +3612,11 @@
       </c>
       <c r="F25" s="9">
         <f>'[20]SM5000.1-oct'!$K$1</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G25" s="9">
         <f>'[20]SM5000.1-oct'!$K$2</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
@@ -3521,11 +3629,11 @@
       </c>
       <c r="L25" s="8">
         <f>'[20]SM5000.1-oct'!$O$2</f>
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="M25" s="8">
         <f>'[20]SM5000.1-oct'!$O$1</f>
-        <v>4900</v>
+        <v>5100</v>
       </c>
       <c r="N25" s="1">
         <v>700</v>
@@ -3587,11 +3695,11 @@
       </c>
       <c r="F27" s="14">
         <f>'[22]MD10000.1-OCT'!$K$1</f>
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="G27" s="14">
         <f>'[22]MD10000.1-OCT'!$K$2</f>
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H27" s="14"/>
       <c r="I27" s="14"/>
@@ -3604,11 +3712,11 @@
       </c>
       <c r="L27" s="16">
         <f>'[22]MD10000.1-OCT'!$O$2</f>
-        <v>6100</v>
+        <v>5400</v>
       </c>
       <c r="M27" s="16">
         <f>'[22]MD10000.1-OCT'!$O$1</f>
-        <v>5900</v>
+        <v>6600</v>
       </c>
       <c r="N27" s="1">
         <v>700</v>
@@ -3679,7 +3787,7 @@
         <v>12</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="K29" s="11">
         <f>'[24]MD20000.15-DEC'!$B$3</f>
@@ -3687,14 +3795,11 @@
       </c>
       <c r="L29" s="8">
         <f>'[25]MD20000.15-DEC'!$O$2</f>
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="M29" s="8">
-        <f>'[24]MD20000.15-DEC'!$O$1</f>
-        <v>17000</v>
-      </c>
-      <c r="N29" s="1">
-        <v>1400</v>
+        <f>'[25]MD20000.15-DEC'!$O$1</f>
+        <v>24000</v>
       </c>
     </row>
     <row r="30" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3715,14 +3820,14 @@
       <c r="G30" s="9"/>
       <c r="H30" s="9">
         <f>'[26]MD20000.15-DEC'!$K$1</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I30" s="9">
         <f>'[26]MD20000.15-DEC'!$K$2</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="K30" s="11">
         <f>'[26]MD20000.15-DEC'!$B$3</f>
@@ -3730,14 +3835,11 @@
       </c>
       <c r="L30" s="8">
         <f>'[26]MD20000.15-DEC'!$O$2</f>
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="M30" s="8">
         <f>'[26]MD20000.15-DEC'!$O$1</f>
-        <v>21000</v>
-      </c>
-      <c r="N30" s="1">
-        <v>1400</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="31" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3756,11 +3858,11 @@
       </c>
       <c r="F31" s="14">
         <f>'[27]MD20000.18-DEC'!$K$1</f>
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="G31" s="14">
         <f>'[27]MD20000.18-DEC'!$K$2</f>
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="H31" s="14"/>
       <c r="I31" s="14"/>
@@ -3773,11 +3875,11 @@
       </c>
       <c r="L31" s="16">
         <f>'[27]MD20000.18-DEC'!$O$2</f>
-        <v>9000</v>
+        <v>900</v>
       </c>
       <c r="M31" s="16">
         <f>'[27]MD20000.18-DEC'!$O$1</f>
-        <v>27000</v>
+        <v>35100</v>
       </c>
       <c r="N31" s="1">
         <v>2100</v>
@@ -3801,11 +3903,11 @@
       <c r="G32" s="14"/>
       <c r="H32" s="14">
         <f>'[28]MD10000.10-JAN'!$K$1</f>
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I32" s="14">
         <f>'[28]MD10000.10-JAN'!$K$2</f>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J32" s="17" t="s">
         <v>12</v>
@@ -3816,11 +3918,11 @@
       </c>
       <c r="L32" s="16">
         <f>'[28]MD10000.10-JAN'!$O$2</f>
-        <v>12600</v>
+        <v>10850</v>
       </c>
       <c r="M32" s="16">
         <f>'[28]MD10000.10-JAN'!$O$1</f>
-        <v>4200</v>
+        <v>5950</v>
       </c>
       <c r="N32" s="1">
         <v>350</v>
@@ -3844,11 +3946,11 @@
       <c r="G33" s="14"/>
       <c r="H33" s="14">
         <f>'[29]MD20000.15-DEc'!$K$1</f>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I33" s="14">
         <f>'[29]MD20000.15-DEc'!$K$2</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J33" s="17" t="s">
         <v>12</v>
@@ -3859,11 +3961,11 @@
       </c>
       <c r="L33" s="16">
         <f>'[29]MD20000.15-DEc'!$O$2</f>
-        <v>9800</v>
+        <v>2800</v>
       </c>
       <c r="M33" s="16">
         <f>'[29]MD20000.15-DEc'!$O$1</f>
-        <v>14200</v>
+        <v>21200</v>
       </c>
       <c r="N33" s="1">
         <v>1400</v>
@@ -3887,11 +3989,11 @@
       <c r="G34" s="14"/>
       <c r="H34" s="14">
         <f>'[30]MD10000.10-JAN'!$K$1</f>
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I34" s="14">
         <f>'[30]MD10000.10-JAN'!$K$2</f>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J34" s="17" t="s">
         <v>12</v>
@@ -3902,11 +4004,11 @@
       </c>
       <c r="L34" s="16">
         <f>'[30]MD10000.10-JAN'!$O$2</f>
-        <v>13650</v>
+        <v>11900</v>
       </c>
       <c r="M34" s="16">
         <f>'[30]MD10000.10-JAN'!$O$1</f>
-        <v>3150</v>
+        <v>4900</v>
       </c>
       <c r="N34" s="1">
         <v>350</v>
@@ -3934,7 +4036,7 @@
       </c>
       <c r="I35" s="9">
         <f>'[31]MD20000.15-DEc'!$K$2</f>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J35" s="10" t="s">
         <v>12</v>
@@ -3945,11 +4047,11 @@
       </c>
       <c r="L35" s="8">
         <f>'[31]MD20000.15-DEc'!$O$2</f>
-        <v>12600</v>
+        <v>5600</v>
       </c>
       <c r="M35" s="8">
         <f>'[31]MD20000.15-DEc'!$O$1</f>
-        <v>11400</v>
+        <v>18400</v>
       </c>
       <c r="N35" s="1">
         <v>1400</v>
@@ -3977,7 +4079,7 @@
       </c>
       <c r="I36" s="14">
         <f>'[32]MD10000.10-JAN'!$K$2</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J36" s="17" t="s">
         <v>12</v>
@@ -3988,11 +4090,11 @@
       </c>
       <c r="L36" s="16">
         <f>'[32]MD10000.10-JAN'!$O$2</f>
-        <v>14350</v>
+        <v>12250</v>
       </c>
       <c r="M36" s="16">
         <f>'[32]MD10000.10-JAN'!$O$1</f>
-        <v>2450</v>
+        <v>4550</v>
       </c>
       <c r="N36" s="1">
         <v>350</v>
@@ -4020,7 +4122,7 @@
       </c>
       <c r="I37" s="9">
         <f>'[33]MD20000.15-DEc'!$K$2</f>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J37" s="10" t="s">
         <v>12</v>
@@ -4031,11 +4133,11 @@
       </c>
       <c r="L37" s="8">
         <f>'[33]MD20000.15-DEc'!$O$2</f>
-        <v>16800</v>
+        <v>8400</v>
       </c>
       <c r="M37" s="8">
         <f>'[33]MD20000.15-DEc'!$O$1</f>
-        <v>7200</v>
+        <v>15600</v>
       </c>
       <c r="N37" s="1">
         <v>1400</v>
@@ -4063,7 +4165,7 @@
       </c>
       <c r="I38" s="14">
         <f>'[34]MD10000.20-OCT'!$K$2</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J38" s="17" t="s">
         <v>12</v>
@@ -4074,11 +4176,11 @@
       </c>
       <c r="L38" s="16">
         <f>'[34]MD10000.20-OCT'!$O$2</f>
-        <v>3900</v>
+        <v>1800</v>
       </c>
       <c r="M38" s="16">
         <f>'[34]MD10000.20-OCT'!$O$1</f>
-        <v>2100</v>
+        <v>4200</v>
       </c>
       <c r="N38" s="1">
         <v>350</v>
@@ -4117,7 +4219,7 @@
       </c>
       <c r="L39" s="8">
         <f>'[36]MD50000.15-DEC'!$O$2</f>
-        <v>60200</v>
+        <v>54600</v>
       </c>
       <c r="M39" s="8">
         <f>'[35]MD50000.15-DEC'!$O$1</f>
@@ -4145,11 +4247,11 @@
       <c r="G40" s="9"/>
       <c r="H40" s="9">
         <f>'[37]MD10000.20-OCT'!$K$1</f>
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I40" s="9">
         <f>'[37]MD10000.20-OCT'!$K$2</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J40" s="10" t="s">
         <v>12</v>
@@ -4160,11 +4262,11 @@
       </c>
       <c r="L40" s="8">
         <f>'[37]MD10000.20-OCT'!$O$2</f>
-        <v>4950</v>
+        <v>3200</v>
       </c>
       <c r="M40" s="8">
         <f>'[37]MD10000.20-OCT'!$O$1</f>
-        <v>1050</v>
+        <v>2800</v>
       </c>
       <c r="N40" s="1">
         <v>350</v>
@@ -4186,11 +4288,11 @@
       </c>
       <c r="F41" s="9">
         <f>'[38]MD20000.18-DEC'!$K$1</f>
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="G41" s="9">
         <f>'[38]MD20000.18-DEC'!$K$2</f>
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="H41" s="9"/>
       <c r="I41" s="9"/>
@@ -4203,11 +4305,11 @@
       </c>
       <c r="L41" s="8">
         <f>'[38]MD20000.18-DEC'!$O$2</f>
-        <v>19000</v>
+        <v>12000</v>
       </c>
       <c r="M41" s="8">
         <f>'[38]MD20000.18-DEC'!$O$1</f>
-        <v>5000</v>
+        <v>12000</v>
       </c>
       <c r="N41" s="1">
         <v>1400</v>
@@ -4231,11 +4333,11 @@
       <c r="G42" s="9"/>
       <c r="H42" s="9">
         <f>'[39]MD10000.20-OCT'!$K$1</f>
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I42" s="9">
         <f>'[39]MD10000.20-OCT'!$K$2</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J42" s="10" t="s">
         <v>12</v>
@@ -4246,11 +4348,11 @@
       </c>
       <c r="L42" s="8">
         <f>'[39]MD10000.20-OCT'!$O$2</f>
-        <v>5300</v>
+        <v>3900</v>
       </c>
       <c r="M42" s="8">
         <f>'[39]MD10000.20-OCT'!$O$1</f>
-        <v>700</v>
+        <v>2100</v>
       </c>
       <c r="N42" s="1">
         <v>350</v>
@@ -4272,11 +4374,11 @@
       </c>
       <c r="F43" s="9">
         <f>'[40]MD20000.22-DEC'!$K$1</f>
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="G43" s="9">
         <f>'[40]MD20000.22-DEC'!$K$2</f>
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="H43" s="9"/>
       <c r="I43" s="9"/>
@@ -4289,11 +4391,11 @@
       </c>
       <c r="L43" s="8">
         <f>'[40]MD20000.22-DEC'!$O$2</f>
-        <v>21200</v>
+        <v>15400</v>
       </c>
       <c r="M43" s="8">
         <f>'[40]MD20000.22-DEC'!$O$1</f>
-        <v>2800</v>
+        <v>8600</v>
       </c>
       <c r="N43" s="1">
         <v>1400</v>
@@ -4319,7 +4421,7 @@
       </c>
       <c r="G44" s="9">
         <f>'[41]MD10000.1-OCT'!$K$1</f>
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
@@ -4332,11 +4434,11 @@
       </c>
       <c r="L44" s="8">
         <f>'[41]MD10000.1-OCT'!$O$2</f>
-        <v>11000</v>
+        <v>8300</v>
       </c>
       <c r="M44" s="8">
         <f>'[41]MD10000.1-OCT'!$O$1</f>
-        <v>1000</v>
+        <v>3700</v>
       </c>
       <c r="N44" s="1">
         <v>700</v>
@@ -4360,11 +4462,11 @@
       <c r="G45" s="9"/>
       <c r="H45" s="9">
         <f>'[42]MD10000.20-OCT'!$K$1</f>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I45" s="9">
         <f>'[42]MD10000.20-OCT'!$K$2</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J45" s="10" t="s">
         <v>12</v>
@@ -4375,11 +4477,11 @@
       </c>
       <c r="L45" s="8">
         <f>'[42]MD10000.20-OCT'!$O$2</f>
-        <v>5650</v>
+        <v>4250</v>
       </c>
       <c r="M45" s="8">
         <f>'[42]MD10000.20-OCT'!$O$1</f>
-        <v>350</v>
+        <v>1750</v>
       </c>
       <c r="N45" s="1">
         <v>350</v>
@@ -4407,22 +4509,22 @@
       </c>
       <c r="I46" s="9">
         <f>'[43]MD10000.1-OCT'!$K$2</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J46" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K46" s="11">
         <f>'[43]MD10000.1-OCT'!$B$3</f>
-        <v>0</v>
+        <v>45450</v>
       </c>
       <c r="L46" s="8">
-        <f>'[43]MD10000.1-OCT'!$O$2</f>
-        <v>12000</v>
+        <f>'[44]MD10000.1-OCT'!$O$2</f>
+        <v>8400</v>
       </c>
       <c r="M46" s="8">
         <f>'[43]MD10000.1-OCT'!$O$1</f>
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="N46" s="1">
         <v>700</v>
@@ -4439,16 +4541,16 @@
         <v>33</v>
       </c>
       <c r="E47" s="8">
-        <f>'[44]MD20000.22-DEC'!$C$1</f>
+        <f>'[45]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F47" s="9">
-        <f>'[44]MD20000.22-DEC'!$K$1</f>
-        <v>118</v>
+        <f>'[45]MD20000.22-DEC'!$K$1</f>
+        <v>84</v>
       </c>
       <c r="G47" s="9">
-        <f>'[44]MD20000.22-DEC'!$K$2</f>
-        <v>2</v>
+        <f>'[45]MD20000.22-DEC'!$K$2</f>
+        <v>36</v>
       </c>
       <c r="H47" s="9"/>
       <c r="I47" s="9"/>
@@ -4456,18 +4558,104 @@
         <v>12</v>
       </c>
       <c r="K47" s="11">
-        <f>'[44]MD20000.22-DEC'!$B$3</f>
+        <f>'[45]MD20000.22-DEC'!$B$3</f>
         <v>45446</v>
       </c>
       <c r="L47" s="8">
-        <f>'[44]MD20000.22-DEC'!$O$2</f>
-        <v>23600</v>
+        <f>'[45]MD20000.22-DEC'!$O$2</f>
+        <v>16800</v>
       </c>
       <c r="M47" s="8">
-        <f>'[44]MD20000.22-DEC'!$O$1</f>
-        <v>400</v>
+        <f>'[45]MD20000.22-DEC'!$O$1</f>
+        <v>7200</v>
       </c>
       <c r="N47" s="1">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B48" s="6">
+        <v>44</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E48" s="8">
+        <f>'[46]MD20000.22-DEC'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F48" s="9">
+        <f>'[46]MD20000.22-DEC'!$K$1</f>
+        <v>112</v>
+      </c>
+      <c r="G48" s="9">
+        <f>'[46]MD20000.22-DEC'!$K$2</f>
+        <v>8</v>
+      </c>
+      <c r="H48" s="9"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K48" s="11">
+        <f>'[46]MD20000.22-DEC'!$B$3</f>
+        <v>45473</v>
+      </c>
+      <c r="L48" s="8">
+        <f>'[46]MD20000.22-DEC'!$O$2</f>
+        <v>11200</v>
+      </c>
+      <c r="M48" s="8">
+        <f>'[46]MD20000.22-DEC'!$O$1</f>
+        <v>800</v>
+      </c>
+      <c r="N48" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="49" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="6">
+        <v>45</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E49" s="8">
+        <f>'[47]MD20000.15-DEc'!$C$1</f>
+        <v>20000</v>
+      </c>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="9">
+        <f>'[47]MD20000.15-DEc'!$K$1</f>
+        <v>17</v>
+      </c>
+      <c r="I49" s="9">
+        <f>'[47]MD20000.15-DEc'!$K$2</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K49" s="11">
+        <f>'[47]MD20000.15-DEc'!$B$3</f>
+        <v>0</v>
+      </c>
+      <c r="L49" s="8">
+        <f>'[47]MD20000.15-DEc'!$O$2</f>
+        <v>24000</v>
+      </c>
+      <c r="M49" s="8">
+        <f>'[47]MD20000.15-DEc'!$O$1</f>
+        <v>0</v>
+      </c>
+      <c r="N49" s="1">
         <v>1400</v>
       </c>
     </row>

--- a/LoanOfficer-A/LoanBook.xlsx
+++ b/LoanOfficer-A/LoanBook.xlsx
@@ -57,6 +57,10 @@
     <externalReference r:id="rId46"/>
     <externalReference r:id="rId47"/>
     <externalReference r:id="rId48"/>
+    <externalReference r:id="rId49"/>
+    <externalReference r:id="rId50"/>
+    <externalReference r:id="rId51"/>
+    <externalReference r:id="rId52"/>
   </externalReferences>
   <calcPr calcId="145621" iterateDelta="1E-4"/>
   <extLst>
@@ -68,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="77">
   <si>
     <t>Code</t>
   </si>
@@ -290,6 +294,15 @@
   </si>
   <si>
     <t>Rambhabati ricky</t>
+  </si>
+  <si>
+    <t>Sonia</t>
+  </si>
+  <si>
+    <t>L10000W17P700-wed</t>
+  </si>
+  <si>
+    <t>L10000W17P700-mon</t>
   </si>
 </sst>
 </file>
@@ -631,18 +644,18 @@
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>19</v>
+            <v>16</v>
           </cell>
           <cell r="O1">
-            <v>50750</v>
+            <v>56000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>29</v>
+            <v>32</v>
           </cell>
           <cell r="O2">
-            <v>33250</v>
+            <v>28000</v>
           </cell>
         </row>
         <row r="3">
@@ -745,18 +758,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>22</v>
+            <v>19</v>
           </cell>
           <cell r="O1">
-            <v>9100</v>
+            <v>10150</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>26</v>
+            <v>29</v>
           </cell>
           <cell r="O2">
-            <v>7700</v>
+            <v>6650</v>
           </cell>
         </row>
         <row r="3">
@@ -827,18 +840,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>22</v>
+            <v>20</v>
           </cell>
           <cell r="O1">
-            <v>9100</v>
+            <v>9800</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>26</v>
+            <v>28</v>
           </cell>
           <cell r="O2">
-            <v>7700</v>
+            <v>7000</v>
           </cell>
         </row>
         <row r="3">
@@ -869,18 +882,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>22</v>
+            <v>20</v>
           </cell>
           <cell r="O1">
-            <v>9100</v>
+            <v>9800</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>26</v>
+            <v>28</v>
           </cell>
           <cell r="O2">
-            <v>7700</v>
+            <v>7000</v>
           </cell>
         </row>
         <row r="3">
@@ -950,18 +963,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>25</v>
+            <v>22</v>
           </cell>
           <cell r="O1">
-            <v>8050</v>
+            <v>9100</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>23</v>
+            <v>26</v>
           </cell>
           <cell r="O2">
-            <v>8750</v>
+            <v>7700</v>
           </cell>
         </row>
         <row r="3">
@@ -991,18 +1004,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
+            <v>23</v>
+          </cell>
+          <cell r="O1">
+            <v>8750</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
             <v>25</v>
           </cell>
-          <cell r="O1">
+          <cell r="O2">
             <v>8050</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>23</v>
-          </cell>
-          <cell r="O2">
-            <v>8750</v>
           </cell>
         </row>
         <row r="3">
@@ -1147,25 +1160,25 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>54</v>
+            <v>44</v>
           </cell>
           <cell r="O1">
-            <v>6600</v>
+            <v>7600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>66</v>
+            <v>76</v>
           </cell>
           <cell r="O2">
-            <v>5400</v>
+            <v>4400</v>
           </cell>
         </row>
         <row r="3">
@@ -1340,18 +1353,18 @@
             <v>30000</v>
           </cell>
           <cell r="K1">
-            <v>3</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
-            <v>35100</v>
+            <v>36000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>117</v>
+            <v>120</v>
           </cell>
           <cell r="O2">
-            <v>900</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -1381,18 +1394,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>31</v>
+            <v>28</v>
           </cell>
           <cell r="O1">
-            <v>5950</v>
+            <v>7000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>17</v>
+            <v>20</v>
           </cell>
           <cell r="O2">
-            <v>10850</v>
+            <v>9800</v>
           </cell>
         </row>
         <row r="3">
@@ -1423,18 +1436,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
-            <v>21200</v>
+            <v>24000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>15</v>
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>2800</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -1505,18 +1518,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>34</v>
+            <v>32</v>
           </cell>
           <cell r="O1">
-            <v>4900</v>
+            <v>5600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>14</v>
+            <v>16</v>
           </cell>
           <cell r="O2">
-            <v>11900</v>
+            <v>11200</v>
           </cell>
         </row>
         <row r="3">
@@ -1550,15 +1563,15 @@
             <v>17</v>
           </cell>
           <cell r="O1">
-            <v>18400</v>
+            <v>22600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>13</v>
+            <v>16</v>
           </cell>
           <cell r="O2">
-            <v>5600</v>
+            <v>1400</v>
           </cell>
         </row>
         <row r="3">
@@ -1592,15 +1605,15 @@
             <v>48</v>
           </cell>
           <cell r="O1">
-            <v>4550</v>
+            <v>5250</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>13</v>
+            <v>15</v>
           </cell>
           <cell r="O2">
-            <v>12250</v>
+            <v>11550</v>
           </cell>
         </row>
         <row r="3">
@@ -1634,15 +1647,15 @@
             <v>17</v>
           </cell>
           <cell r="O1">
-            <v>15600</v>
+            <v>19800</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>11</v>
+            <v>14</v>
           </cell>
           <cell r="O2">
-            <v>8400</v>
+            <v>4200</v>
           </cell>
         </row>
         <row r="3">
@@ -1665,7 +1678,7 @@
       <sheetName val="MD10000.20-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -1675,15 +1688,15 @@
             <v>17</v>
           </cell>
           <cell r="O1">
-            <v>4200</v>
+            <v>5250</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>12</v>
+            <v>15</v>
           </cell>
           <cell r="O2">
-            <v>1800</v>
+            <v>750</v>
           </cell>
         </row>
         <row r="3">
@@ -1749,7 +1762,7 @@
       <sheetData sheetId="1">
         <row r="2">
           <cell r="O2">
-            <v>54600</v>
+            <v>49000</v>
           </cell>
         </row>
       </sheetData>
@@ -1774,18 +1787,18 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>9</v>
+            <v>5</v>
           </cell>
           <cell r="O1">
-            <v>2800</v>
+            <v>4200</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>8</v>
+            <v>12</v>
           </cell>
           <cell r="O2">
-            <v>3200</v>
+            <v>1800</v>
           </cell>
         </row>
         <row r="3">
@@ -1814,18 +1827,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>60</v>
+            <v>40</v>
           </cell>
           <cell r="O1">
-            <v>12000</v>
+            <v>16000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>60</v>
+            <v>80</v>
           </cell>
           <cell r="O2">
-            <v>12000</v>
+            <v>8000</v>
           </cell>
         </row>
         <row r="3">
@@ -1854,18 +1867,18 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>11</v>
+            <v>7</v>
           </cell>
           <cell r="O1">
-            <v>2100</v>
+            <v>3500</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>6</v>
+            <v>10</v>
           </cell>
           <cell r="O2">
-            <v>3900</v>
+            <v>2500</v>
           </cell>
         </row>
         <row r="3">
@@ -1934,18 +1947,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>77</v>
+            <v>50</v>
           </cell>
           <cell r="O1">
-            <v>8600</v>
+            <v>14000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>43</v>
+            <v>70</v>
           </cell>
           <cell r="O2">
-            <v>15400</v>
+            <v>10000</v>
           </cell>
         </row>
         <row r="3">
@@ -1977,15 +1990,15 @@
             <v>120</v>
           </cell>
           <cell r="K1">
-            <v>83</v>
+            <v>64</v>
           </cell>
           <cell r="O1">
-            <v>3700</v>
+            <v>5600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="O2">
-            <v>8300</v>
+            <v>6400</v>
           </cell>
         </row>
         <row r="3">
@@ -2014,18 +2027,18 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>12</v>
+            <v>9</v>
           </cell>
           <cell r="O1">
-            <v>1750</v>
+            <v>2800</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>5</v>
+            <v>8</v>
           </cell>
           <cell r="O2">
-            <v>4250</v>
+            <v>3200</v>
           </cell>
         </row>
         <row r="3">
@@ -2084,11 +2097,11 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="2">
           <cell r="O2">
-            <v>8400</v>
+            <v>6300</v>
           </cell>
         </row>
       </sheetData>
@@ -2112,18 +2125,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>84</v>
+            <v>68</v>
           </cell>
           <cell r="O1">
-            <v>7200</v>
+            <v>10400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>36</v>
+            <v>52</v>
           </cell>
           <cell r="O2">
-            <v>16800</v>
+            <v>13600</v>
           </cell>
         </row>
         <row r="3">
@@ -2152,18 +2165,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>112</v>
+            <v>92</v>
           </cell>
           <cell r="O1">
-            <v>800</v>
+            <v>2800</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>8</v>
+            <v>28</v>
           </cell>
           <cell r="O2">
-            <v>11200</v>
+            <v>9200</v>
           </cell>
         </row>
         <row r="3">
@@ -2186,29 +2199,116 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>17</v>
+            <v>15</v>
           </cell>
           <cell r="O1">
-            <v>0</v>
+            <v>3000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>0</v>
+            <v>2</v>
           </cell>
           <cell r="O2">
-            <v>24000</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
+            <v>21000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45495</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEc"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>16</v>
+          </cell>
+          <cell r="O1">
+            <v>800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>1</v>
+          </cell>
+          <cell r="O2">
+            <v>11200</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45496</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>113</v>
+          </cell>
+          <cell r="O1">
+            <v>1400</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>7</v>
+          </cell>
+          <cell r="O2">
+            <v>22600</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45493</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2251,6 +2351,80 @@
           </cell>
         </row>
       </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEc"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>17</v>
+          </cell>
+          <cell r="O1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>0</v>
+          </cell>
+          <cell r="O2">
+            <v>12000</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD50000.15-DEC"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>17</v>
+          </cell>
+          <cell r="O1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>0</v>
+          </cell>
+          <cell r="O2">
+            <v>24000</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2677,7 +2851,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2685,7 +2859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:Q49"/>
+  <dimension ref="B2:Q54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="1" customWidth="1"/>
@@ -2719,13 +2893,13 @@
       <c r="J2" s="22"/>
       <c r="K2" s="23"/>
       <c r="L2" s="19">
-        <f>SUM(L5:L60)</f>
-        <v>296700</v>
+        <f>SUM(L5:L57)</f>
+        <v>309400</v>
       </c>
       <c r="M2" s="20"/>
       <c r="N2" s="1">
-        <f>SUM(N5:N61)</f>
-        <v>22750</v>
+        <f>SUM(N5:N58)</f>
+        <v>23450</v>
       </c>
       <c r="Q2" s="1">
         <f>14900+260750</f>
@@ -3199,11 +3373,11 @@
       <c r="G15" s="9"/>
       <c r="H15" s="9">
         <f>'[10]MD50000.15-DEC'!$K$1</f>
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I15" s="9">
         <f>'[10]MD50000.15-DEC'!$K$2</f>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J15" s="10" t="s">
         <v>12</v>
@@ -3214,11 +3388,11 @@
       </c>
       <c r="L15" s="8">
         <f>'[10]MD50000.15-DEC'!$O$2</f>
-        <v>33250</v>
+        <v>28000</v>
       </c>
       <c r="M15" s="8">
         <f>'[10]MD50000.15-DEC'!$O$1</f>
-        <v>50750</v>
+        <v>56000</v>
       </c>
       <c r="N15" s="1">
         <v>1750</v>
@@ -3319,11 +3493,11 @@
       <c r="G18" s="14"/>
       <c r="H18" s="14">
         <f>'[13]MD50000.15-DEC'!$K$1</f>
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I18" s="14">
         <f>'[13]MD50000.15-DEC'!$K$2</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J18" s="17" t="s">
         <v>12</v>
@@ -3334,11 +3508,11 @@
       </c>
       <c r="L18" s="16">
         <f>'[13]MD50000.15-DEC'!$O$2</f>
-        <v>7700</v>
+        <v>6650</v>
       </c>
       <c r="M18" s="16">
         <f>'[13]MD50000.15-DEC'!$O$1</f>
-        <v>9100</v>
+        <v>10150</v>
       </c>
       <c r="N18" s="1">
         <v>350</v>
@@ -3402,11 +3576,11 @@
       <c r="G20" s="14"/>
       <c r="H20" s="14">
         <f>'[15]MD10000.10-JAN'!$K$1</f>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I20" s="14">
         <f>'[15]MD10000.10-JAN'!$K$2</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J20" s="17" t="s">
         <v>12</v>
@@ -3417,11 +3591,11 @@
       </c>
       <c r="L20" s="16">
         <f>'[15]MD10000.10-JAN'!$O$2</f>
-        <v>7700</v>
+        <v>7000</v>
       </c>
       <c r="M20" s="16">
         <f>'[15]MD10000.10-JAN'!$O$1</f>
-        <v>9100</v>
+        <v>9800</v>
       </c>
       <c r="N20" s="1">
         <v>350</v>
@@ -3445,11 +3619,11 @@
       <c r="G21" s="9"/>
       <c r="H21" s="9">
         <f>'[16]MD10000.10-JAN'!$K$1</f>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I21" s="9">
         <f>'[16]MD10000.10-JAN'!$K$2</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J21" s="10" t="s">
         <v>12</v>
@@ -3460,11 +3634,11 @@
       </c>
       <c r="L21" s="8">
         <f>'[16]MD10000.10-JAN'!$O$2</f>
-        <v>7700</v>
+        <v>7000</v>
       </c>
       <c r="M21" s="8">
         <f>'[16]MD10000.10-JAN'!$O$1</f>
-        <v>9100</v>
+        <v>9800</v>
       </c>
       <c r="N21" s="1">
         <v>350</v>
@@ -3528,11 +3702,11 @@
       <c r="G23" s="9"/>
       <c r="H23" s="9">
         <f>'[18]MD10000.20-OCT'!$K$1</f>
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I23" s="9">
         <f>'[18]MD10000.20-OCT'!$K$2</f>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J23" s="10" t="s">
         <v>12</v>
@@ -3543,11 +3717,11 @@
       </c>
       <c r="L23" s="8">
         <f>'[18]MD10000.20-OCT'!$O$2</f>
-        <v>8750</v>
+        <v>7700</v>
       </c>
       <c r="M23" s="8">
         <f>'[18]MD10000.20-OCT'!$O$1</f>
-        <v>8050</v>
+        <v>9100</v>
       </c>
       <c r="N23" s="1">
         <v>350</v>
@@ -3571,11 +3745,11 @@
       <c r="G24" s="9"/>
       <c r="H24" s="9">
         <f>'[19]MD10000.20-OCT'!$K$1</f>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I24" s="9">
         <f>'[19]MD10000.20-OCT'!$K$2</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J24" s="10" t="s">
         <v>12</v>
@@ -3586,11 +3760,11 @@
       </c>
       <c r="L24" s="8">
         <f>'[19]MD10000.20-OCT'!$O$2</f>
-        <v>8750</v>
+        <v>8050</v>
       </c>
       <c r="M24" s="8">
         <f>'[19]MD10000.20-OCT'!$O$1</f>
-        <v>8050</v>
+        <v>8750</v>
       </c>
       <c r="N24" s="1">
         <v>350</v>
@@ -3695,11 +3869,11 @@
       </c>
       <c r="F27" s="14">
         <f>'[22]MD10000.1-OCT'!$K$1</f>
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="G27" s="14">
         <f>'[22]MD10000.1-OCT'!$K$2</f>
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="H27" s="14"/>
       <c r="I27" s="14"/>
@@ -3712,11 +3886,11 @@
       </c>
       <c r="L27" s="16">
         <f>'[22]MD10000.1-OCT'!$O$2</f>
-        <v>5400</v>
+        <v>4400</v>
       </c>
       <c r="M27" s="16">
         <f>'[22]MD10000.1-OCT'!$O$1</f>
-        <v>6600</v>
+        <v>7600</v>
       </c>
       <c r="N27" s="1">
         <v>700</v>
@@ -3858,16 +4032,16 @@
       </c>
       <c r="F31" s="14">
         <f>'[27]MD20000.18-DEC'!$K$1</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G31" s="14">
         <f>'[27]MD20000.18-DEC'!$K$2</f>
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H31" s="14"/>
       <c r="I31" s="14"/>
       <c r="J31" s="17" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="K31" s="15">
         <f>'[27]MD20000.18-DEC'!$B$3</f>
@@ -3875,14 +4049,11 @@
       </c>
       <c r="L31" s="16">
         <f>'[27]MD20000.18-DEC'!$O$2</f>
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="M31" s="16">
         <f>'[27]MD20000.18-DEC'!$O$1</f>
-        <v>35100</v>
-      </c>
-      <c r="N31" s="1">
-        <v>2100</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="32" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3903,11 +4074,11 @@
       <c r="G32" s="14"/>
       <c r="H32" s="14">
         <f>'[28]MD10000.10-JAN'!$K$1</f>
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I32" s="14">
         <f>'[28]MD10000.10-JAN'!$K$2</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J32" s="17" t="s">
         <v>12</v>
@@ -3918,11 +4089,11 @@
       </c>
       <c r="L32" s="16">
         <f>'[28]MD10000.10-JAN'!$O$2</f>
-        <v>10850</v>
+        <v>9800</v>
       </c>
       <c r="M32" s="16">
         <f>'[28]MD10000.10-JAN'!$O$1</f>
-        <v>5950</v>
+        <v>7000</v>
       </c>
       <c r="N32" s="1">
         <v>350</v>
@@ -3946,14 +4117,14 @@
       <c r="G33" s="14"/>
       <c r="H33" s="14">
         <f>'[29]MD20000.15-DEc'!$K$1</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I33" s="14">
         <f>'[29]MD20000.15-DEc'!$K$2</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="K33" s="15">
         <f>'[29]MD20000.15-DEc'!$B$3</f>
@@ -3961,14 +4132,11 @@
       </c>
       <c r="L33" s="16">
         <f>'[29]MD20000.15-DEc'!$O$2</f>
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="M33" s="16">
         <f>'[29]MD20000.15-DEc'!$O$1</f>
-        <v>21200</v>
-      </c>
-      <c r="N33" s="1">
-        <v>1400</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="34" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3989,11 +4157,11 @@
       <c r="G34" s="14"/>
       <c r="H34" s="14">
         <f>'[30]MD10000.10-JAN'!$K$1</f>
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I34" s="14">
         <f>'[30]MD10000.10-JAN'!$K$2</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J34" s="17" t="s">
         <v>12</v>
@@ -4004,11 +4172,11 @@
       </c>
       <c r="L34" s="16">
         <f>'[30]MD10000.10-JAN'!$O$2</f>
-        <v>11900</v>
+        <v>11200</v>
       </c>
       <c r="M34" s="16">
         <f>'[30]MD10000.10-JAN'!$O$1</f>
-        <v>4900</v>
+        <v>5600</v>
       </c>
       <c r="N34" s="1">
         <v>350</v>
@@ -4036,7 +4204,7 @@
       </c>
       <c r="I35" s="9">
         <f>'[31]MD20000.15-DEc'!$K$2</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J35" s="10" t="s">
         <v>12</v>
@@ -4047,11 +4215,11 @@
       </c>
       <c r="L35" s="8">
         <f>'[31]MD20000.15-DEc'!$O$2</f>
-        <v>5600</v>
+        <v>1400</v>
       </c>
       <c r="M35" s="8">
         <f>'[31]MD20000.15-DEc'!$O$1</f>
-        <v>18400</v>
+        <v>22600</v>
       </c>
       <c r="N35" s="1">
         <v>1400</v>
@@ -4079,7 +4247,7 @@
       </c>
       <c r="I36" s="14">
         <f>'[32]MD10000.10-JAN'!$K$2</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J36" s="17" t="s">
         <v>12</v>
@@ -4090,11 +4258,11 @@
       </c>
       <c r="L36" s="16">
         <f>'[32]MD10000.10-JAN'!$O$2</f>
-        <v>12250</v>
+        <v>11550</v>
       </c>
       <c r="M36" s="16">
         <f>'[32]MD10000.10-JAN'!$O$1</f>
-        <v>4550</v>
+        <v>5250</v>
       </c>
       <c r="N36" s="1">
         <v>350</v>
@@ -4122,7 +4290,7 @@
       </c>
       <c r="I37" s="9">
         <f>'[33]MD20000.15-DEc'!$K$2</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J37" s="10" t="s">
         <v>12</v>
@@ -4133,11 +4301,11 @@
       </c>
       <c r="L37" s="8">
         <f>'[33]MD20000.15-DEc'!$O$2</f>
-        <v>8400</v>
+        <v>4200</v>
       </c>
       <c r="M37" s="8">
         <f>'[33]MD20000.15-DEc'!$O$1</f>
-        <v>15600</v>
+        <v>19800</v>
       </c>
       <c r="N37" s="1">
         <v>1400</v>
@@ -4165,7 +4333,7 @@
       </c>
       <c r="I38" s="14">
         <f>'[34]MD10000.20-OCT'!$K$2</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J38" s="17" t="s">
         <v>12</v>
@@ -4176,11 +4344,11 @@
       </c>
       <c r="L38" s="16">
         <f>'[34]MD10000.20-OCT'!$O$2</f>
-        <v>1800</v>
+        <v>750</v>
       </c>
       <c r="M38" s="16">
         <f>'[34]MD10000.20-OCT'!$O$1</f>
-        <v>4200</v>
+        <v>5250</v>
       </c>
       <c r="N38" s="1">
         <v>350</v>
@@ -4219,7 +4387,7 @@
       </c>
       <c r="L39" s="8">
         <f>'[36]MD50000.15-DEC'!$O$2</f>
-        <v>54600</v>
+        <v>49000</v>
       </c>
       <c r="M39" s="8">
         <f>'[35]MD50000.15-DEC'!$O$1</f>
@@ -4247,11 +4415,11 @@
       <c r="G40" s="9"/>
       <c r="H40" s="9">
         <f>'[37]MD10000.20-OCT'!$K$1</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I40" s="9">
         <f>'[37]MD10000.20-OCT'!$K$2</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J40" s="10" t="s">
         <v>12</v>
@@ -4262,11 +4430,11 @@
       </c>
       <c r="L40" s="8">
         <f>'[37]MD10000.20-OCT'!$O$2</f>
-        <v>3200</v>
+        <v>1800</v>
       </c>
       <c r="M40" s="8">
         <f>'[37]MD10000.20-OCT'!$O$1</f>
-        <v>2800</v>
+        <v>4200</v>
       </c>
       <c r="N40" s="1">
         <v>350</v>
@@ -4288,11 +4456,11 @@
       </c>
       <c r="F41" s="9">
         <f>'[38]MD20000.18-DEC'!$K$1</f>
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G41" s="9">
         <f>'[38]MD20000.18-DEC'!$K$2</f>
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H41" s="9"/>
       <c r="I41" s="9"/>
@@ -4305,11 +4473,11 @@
       </c>
       <c r="L41" s="8">
         <f>'[38]MD20000.18-DEC'!$O$2</f>
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="M41" s="8">
         <f>'[38]MD20000.18-DEC'!$O$1</f>
-        <v>12000</v>
+        <v>16000</v>
       </c>
       <c r="N41" s="1">
         <v>1400</v>
@@ -4333,11 +4501,11 @@
       <c r="G42" s="9"/>
       <c r="H42" s="9">
         <f>'[39]MD10000.20-OCT'!$K$1</f>
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I42" s="9">
         <f>'[39]MD10000.20-OCT'!$K$2</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J42" s="10" t="s">
         <v>12</v>
@@ -4348,11 +4516,11 @@
       </c>
       <c r="L42" s="8">
         <f>'[39]MD10000.20-OCT'!$O$2</f>
-        <v>3900</v>
+        <v>2500</v>
       </c>
       <c r="M42" s="8">
         <f>'[39]MD10000.20-OCT'!$O$1</f>
-        <v>2100</v>
+        <v>3500</v>
       </c>
       <c r="N42" s="1">
         <v>350</v>
@@ -4374,11 +4542,11 @@
       </c>
       <c r="F43" s="9">
         <f>'[40]MD20000.22-DEC'!$K$1</f>
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="G43" s="9">
         <f>'[40]MD20000.22-DEC'!$K$2</f>
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H43" s="9"/>
       <c r="I43" s="9"/>
@@ -4391,11 +4559,11 @@
       </c>
       <c r="L43" s="8">
         <f>'[40]MD20000.22-DEC'!$O$2</f>
-        <v>15400</v>
+        <v>10000</v>
       </c>
       <c r="M43" s="8">
         <f>'[40]MD20000.22-DEC'!$O$1</f>
-        <v>8600</v>
+        <v>14000</v>
       </c>
       <c r="N43" s="1">
         <v>1400</v>
@@ -4421,7 +4589,7 @@
       </c>
       <c r="G44" s="9">
         <f>'[41]MD10000.1-OCT'!$K$1</f>
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
@@ -4434,11 +4602,11 @@
       </c>
       <c r="L44" s="8">
         <f>'[41]MD10000.1-OCT'!$O$2</f>
-        <v>8300</v>
+        <v>6400</v>
       </c>
       <c r="M44" s="8">
         <f>'[41]MD10000.1-OCT'!$O$1</f>
-        <v>3700</v>
+        <v>5600</v>
       </c>
       <c r="N44" s="1">
         <v>700</v>
@@ -4462,11 +4630,11 @@
       <c r="G45" s="9"/>
       <c r="H45" s="9">
         <f>'[42]MD10000.20-OCT'!$K$1</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I45" s="9">
         <f>'[42]MD10000.20-OCT'!$K$2</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J45" s="10" t="s">
         <v>12</v>
@@ -4477,11 +4645,11 @@
       </c>
       <c r="L45" s="8">
         <f>'[42]MD10000.20-OCT'!$O$2</f>
-        <v>4250</v>
+        <v>3200</v>
       </c>
       <c r="M45" s="8">
         <f>'[42]MD10000.20-OCT'!$O$1</f>
-        <v>1750</v>
+        <v>2800</v>
       </c>
       <c r="N45" s="1">
         <v>350</v>
@@ -4520,7 +4688,7 @@
       </c>
       <c r="L46" s="8">
         <f>'[44]MD10000.1-OCT'!$O$2</f>
-        <v>8400</v>
+        <v>6300</v>
       </c>
       <c r="M46" s="8">
         <f>'[43]MD10000.1-OCT'!$O$1</f>
@@ -4546,11 +4714,11 @@
       </c>
       <c r="F47" s="9">
         <f>'[45]MD20000.22-DEC'!$K$1</f>
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="G47" s="9">
         <f>'[45]MD20000.22-DEC'!$K$2</f>
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="H47" s="9"/>
       <c r="I47" s="9"/>
@@ -4563,11 +4731,11 @@
       </c>
       <c r="L47" s="8">
         <f>'[45]MD20000.22-DEC'!$O$2</f>
-        <v>16800</v>
+        <v>13600</v>
       </c>
       <c r="M47" s="8">
         <f>'[45]MD20000.22-DEC'!$O$1</f>
-        <v>7200</v>
+        <v>10400</v>
       </c>
       <c r="N47" s="1">
         <v>1400</v>
@@ -4589,11 +4757,11 @@
       </c>
       <c r="F48" s="9">
         <f>'[46]MD20000.22-DEC'!$K$1</f>
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="G48" s="9">
         <f>'[46]MD20000.22-DEC'!$K$2</f>
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="H48" s="9"/>
       <c r="I48" s="9"/>
@@ -4606,11 +4774,11 @@
       </c>
       <c r="L48" s="8">
         <f>'[46]MD20000.22-DEC'!$O$2</f>
-        <v>11200</v>
+        <v>9200</v>
       </c>
       <c r="M48" s="8">
         <f>'[46]MD20000.22-DEC'!$O$1</f>
-        <v>800</v>
+        <v>2800</v>
       </c>
       <c r="N48" s="1">
         <v>700</v>
@@ -4634,30 +4802,218 @@
       <c r="G49" s="9"/>
       <c r="H49" s="9">
         <f>'[47]MD20000.15-DEc'!$K$1</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I49" s="9">
         <f>'[47]MD20000.15-DEc'!$K$2</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J49" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K49" s="11">
         <f>'[47]MD20000.15-DEc'!$B$3</f>
-        <v>0</v>
+        <v>45495</v>
       </c>
       <c r="L49" s="8">
         <f>'[47]MD20000.15-DEc'!$O$2</f>
-        <v>24000</v>
+        <v>21000</v>
       </c>
       <c r="M49" s="8">
         <f>'[47]MD20000.15-DEc'!$O$1</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="N49" s="1">
         <v>1400</v>
       </c>
+    </row>
+    <row r="50" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B50" s="6">
+        <v>46</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E50" s="8">
+        <f>'[48]MD20000.15-DEc'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F50" s="9"/>
+      <c r="G50" s="9"/>
+      <c r="H50" s="9">
+        <f>'[48]MD20000.15-DEc'!$K$1</f>
+        <v>16</v>
+      </c>
+      <c r="I50" s="9">
+        <f>'[48]MD20000.15-DEc'!$K$2</f>
+        <v>1</v>
+      </c>
+      <c r="J50" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K50" s="11">
+        <f>'[48]MD20000.15-DEc'!$B$3</f>
+        <v>45496</v>
+      </c>
+      <c r="L50" s="8">
+        <f>'[48]MD20000.15-DEc'!$O$2</f>
+        <v>11200</v>
+      </c>
+      <c r="M50" s="8">
+        <f>'[48]MD20000.15-DEc'!$O$1</f>
+        <v>800</v>
+      </c>
+      <c r="N50" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="51" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="6">
+        <v>47</v>
+      </c>
+      <c r="C51" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E51" s="8">
+        <f>'[49]MD20000.18-DEC'!$C$1</f>
+        <v>20000</v>
+      </c>
+      <c r="F51" s="9">
+        <f>'[49]MD20000.18-DEC'!$K$1</f>
+        <v>113</v>
+      </c>
+      <c r="G51" s="9">
+        <f>'[49]MD20000.18-DEC'!$K$2</f>
+        <v>7</v>
+      </c>
+      <c r="H51" s="9"/>
+      <c r="I51" s="9"/>
+      <c r="J51" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K51" s="11">
+        <f>'[49]MD20000.18-DEC'!$B$3</f>
+        <v>45493</v>
+      </c>
+      <c r="L51" s="8">
+        <f>'[49]MD20000.18-DEC'!$O$2</f>
+        <v>22600</v>
+      </c>
+      <c r="M51" s="8">
+        <f>'[49]MD20000.18-DEC'!$O$1</f>
+        <v>1400</v>
+      </c>
+      <c r="N51" s="1">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="52" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B52" s="6">
+        <v>48</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E52" s="8">
+        <f>'[50]MD20000.15-DEc'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F52" s="9"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="9">
+        <f>'[50]MD20000.15-DEc'!$K$1</f>
+        <v>17</v>
+      </c>
+      <c r="I52" s="9">
+        <f>'[50]MD20000.15-DEc'!$K$2</f>
+        <v>0</v>
+      </c>
+      <c r="J52" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K52" s="11">
+        <f>'[50]MD20000.15-DEc'!$B$3</f>
+        <v>0</v>
+      </c>
+      <c r="L52" s="8">
+        <f>'[50]MD20000.15-DEc'!$O$2</f>
+        <v>12000</v>
+      </c>
+      <c r="M52" s="8">
+        <f>'[50]MD20000.15-DEc'!$O$1</f>
+        <v>0</v>
+      </c>
+      <c r="N52" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="53" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="6">
+        <v>49</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E53" s="8">
+        <f>'[51]MD50000.15-DEC'!$C$1</f>
+        <v>20000</v>
+      </c>
+      <c r="F53" s="9"/>
+      <c r="G53" s="9"/>
+      <c r="H53" s="9">
+        <f>'[51]MD50000.15-DEC'!$K$1</f>
+        <v>17</v>
+      </c>
+      <c r="I53" s="9">
+        <f>'[51]MD50000.15-DEC'!$K$2</f>
+        <v>0</v>
+      </c>
+      <c r="J53" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K53" s="11">
+        <f>'[51]MD50000.15-DEC'!$B$3</f>
+        <v>0</v>
+      </c>
+      <c r="L53" s="8">
+        <f>'[51]MD50000.15-DEC'!$O$2</f>
+        <v>24000</v>
+      </c>
+      <c r="M53" s="8">
+        <f>'[51]MD50000.15-DEC'!$O$1</f>
+        <v>0</v>
+      </c>
+      <c r="N53" s="1">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="54" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="6">
+        <v>50</v>
+      </c>
+      <c r="C54" s="9"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9"/>
+      <c r="I54" s="9"/>
+      <c r="J54" s="10"/>
+      <c r="K54" s="11"/>
+      <c r="L54" s="8"/>
+      <c r="M54" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/LoanOfficer-A/LoanBook.xlsx
+++ b/LoanOfficer-A/LoanBook.xlsx
@@ -61,18 +61,29 @@
     <externalReference r:id="rId50"/>
     <externalReference r:id="rId51"/>
     <externalReference r:id="rId52"/>
+    <externalReference r:id="rId53"/>
+    <externalReference r:id="rId54"/>
+    <externalReference r:id="rId55"/>
+    <externalReference r:id="rId56"/>
+    <externalReference r:id="rId57"/>
+    <externalReference r:id="rId58"/>
+    <externalReference r:id="rId59"/>
+    <externalReference r:id="rId60"/>
+    <externalReference r:id="rId61"/>
+    <externalReference r:id="rId62"/>
+    <externalReference r:id="rId63"/>
+    <externalReference r:id="rId64"/>
+    <externalReference r:id="rId65"/>
+    <externalReference r:id="rId66"/>
+    <externalReference r:id="rId67"/>
+    <externalReference r:id="rId68"/>
   </externalReferences>
   <calcPr calcId="145621" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="93">
   <si>
     <t>Code</t>
   </si>
@@ -303,6 +314,54 @@
   </si>
   <si>
     <t>L10000W17P700-mon</t>
+  </si>
+  <si>
+    <t>iActive</t>
+  </si>
+  <si>
+    <t>Ibecha</t>
+  </si>
+  <si>
+    <t>L5000W17P350-tues</t>
+  </si>
+  <si>
+    <t>L30000P120</t>
+  </si>
+  <si>
+    <t>Bimola</t>
+  </si>
+  <si>
+    <t>L10000P120</t>
+  </si>
+  <si>
+    <t>Induleikha</t>
+  </si>
+  <si>
+    <t>bidyarani</t>
+  </si>
+  <si>
+    <t>L5000W17P350-WED</t>
+  </si>
+  <si>
+    <t>sweety</t>
+  </si>
+  <si>
+    <t>L5000W17P350-FRI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tombi</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ricky</t>
+  </si>
+  <si>
+    <t>L20000p120</t>
+  </si>
+  <si>
+    <t>Romila</t>
+  </si>
+  <si>
+    <t>Ibeyaima</t>
   </si>
 </sst>
 </file>
@@ -544,9 +603,6 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -644,18 +700,18 @@
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>16</v>
+            <v>8</v>
           </cell>
           <cell r="O1">
-            <v>56000</v>
+            <v>70000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>32</v>
+            <v>40</v>
           </cell>
           <cell r="O2">
-            <v>28000</v>
+            <v>14000</v>
           </cell>
         </row>
         <row r="3">
@@ -758,18 +814,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>19</v>
+            <v>10</v>
           </cell>
           <cell r="O1">
-            <v>10150</v>
+            <v>13300</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>29</v>
+            <v>38</v>
           </cell>
           <cell r="O2">
-            <v>6650</v>
+            <v>3500</v>
           </cell>
         </row>
         <row r="3">
@@ -840,18 +896,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>20</v>
+            <v>11</v>
           </cell>
           <cell r="O1">
-            <v>9800</v>
+            <v>12950</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>28</v>
+            <v>37</v>
           </cell>
           <cell r="O2">
-            <v>7000</v>
+            <v>3850</v>
           </cell>
         </row>
         <row r="3">
@@ -882,18 +938,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>20</v>
+            <v>11</v>
           </cell>
           <cell r="O1">
-            <v>9800</v>
+            <v>12950</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>28</v>
+            <v>37</v>
           </cell>
           <cell r="O2">
-            <v>7000</v>
+            <v>3850</v>
           </cell>
         </row>
         <row r="3">
@@ -963,18 +1019,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>22</v>
+            <v>13</v>
           </cell>
           <cell r="O1">
-            <v>9100</v>
+            <v>12250</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>26</v>
+            <v>35</v>
           </cell>
           <cell r="O2">
-            <v>7700</v>
+            <v>4550</v>
           </cell>
         </row>
         <row r="3">
@@ -1004,18 +1060,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>23</v>
+            <v>14</v>
           </cell>
           <cell r="O1">
-            <v>8750</v>
+            <v>11900</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>25</v>
+            <v>34</v>
           </cell>
           <cell r="O2">
-            <v>8050</v>
+            <v>4900</v>
           </cell>
         </row>
         <row r="3">
@@ -1079,8 +1135,8 @@
       <sheetName val="SM5000.1-oct"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
       <sheetData sheetId="2">
         <row r="1">
           <cell r="C1">
@@ -1167,18 +1223,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>44</v>
+            <v>25</v>
           </cell>
           <cell r="O1">
-            <v>7600</v>
+            <v>9500</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>76</v>
+            <v>95</v>
           </cell>
           <cell r="O2">
-            <v>4400</v>
+            <v>2500</v>
           </cell>
         </row>
         <row r="3">
@@ -1394,18 +1450,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>28</v>
+            <v>19</v>
           </cell>
           <cell r="O1">
-            <v>7000</v>
+            <v>10150</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>20</v>
+            <v>29</v>
           </cell>
           <cell r="O2">
-            <v>9800</v>
+            <v>6650</v>
           </cell>
         </row>
         <row r="3">
@@ -1518,18 +1574,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>32</v>
+            <v>23</v>
           </cell>
           <cell r="O1">
-            <v>5600</v>
+            <v>8750</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>16</v>
+            <v>25</v>
           </cell>
           <cell r="O2">
-            <v>11200</v>
+            <v>8050</v>
           </cell>
         </row>
         <row r="3">
@@ -1563,15 +1619,15 @@
             <v>17</v>
           </cell>
           <cell r="O1">
-            <v>22600</v>
+            <v>24000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>16</v>
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>1400</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -1605,15 +1661,15 @@
             <v>48</v>
           </cell>
           <cell r="O1">
-            <v>5250</v>
+            <v>8400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>15</v>
+            <v>24</v>
           </cell>
           <cell r="O2">
-            <v>11550</v>
+            <v>8400</v>
           </cell>
         </row>
         <row r="3">
@@ -1647,15 +1703,15 @@
             <v>17</v>
           </cell>
           <cell r="O1">
-            <v>19800</v>
+            <v>24000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>14</v>
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>4200</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -1688,15 +1744,15 @@
             <v>17</v>
           </cell>
           <cell r="O1">
-            <v>5250</v>
+            <v>5950</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>15</v>
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>750</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -1762,7 +1818,7 @@
       <sheetData sheetId="1">
         <row r="2">
           <cell r="O2">
-            <v>49000</v>
+            <v>46200</v>
           </cell>
         </row>
       </sheetData>
@@ -1787,18 +1843,18 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>5</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
-            <v>4200</v>
+            <v>6000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>12</v>
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>1800</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -1827,18 +1883,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>40</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
-            <v>16000</v>
+            <v>24000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>80</v>
+            <v>120</v>
           </cell>
           <cell r="O2">
-            <v>8000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -1867,18 +1923,18 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>7</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
-            <v>3500</v>
+            <v>6000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>10</v>
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>2500</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -1947,18 +2003,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>50</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
-            <v>14000</v>
+            <v>24000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>70</v>
+            <v>120</v>
           </cell>
           <cell r="O2">
-            <v>10000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -1990,15 +2046,15 @@
             <v>120</v>
           </cell>
           <cell r="K1">
-            <v>64</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
-            <v>5600</v>
+            <v>12000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="O2">
-            <v>6400</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -2020,25 +2076,22 @@
       <sheetName val="MD10000.20-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>9</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
-            <v>2800</v>
+            <v>5950</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>8</v>
-          </cell>
-          <cell r="O2">
-            <v>3200</v>
+            <v>17</v>
           </cell>
         </row>
         <row r="3">
@@ -2101,7 +2154,7 @@
       <sheetData sheetId="1">
         <row r="2">
           <cell r="O2">
-            <v>6300</v>
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
@@ -2125,18 +2178,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>68</v>
+            <v>10</v>
           </cell>
           <cell r="O1">
-            <v>10400</v>
+            <v>22000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>52</v>
+            <v>110</v>
           </cell>
           <cell r="O2">
-            <v>13600</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="3">
@@ -2165,18 +2218,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>92</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
-            <v>2800</v>
+            <v>12000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>28</v>
+            <v>120</v>
           </cell>
           <cell r="O2">
-            <v>9200</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -2206,18 +2259,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>15</v>
+            <v>6</v>
           </cell>
           <cell r="O1">
-            <v>3000</v>
+            <v>15600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>2</v>
+            <v>11</v>
           </cell>
           <cell r="O2">
-            <v>21000</v>
+            <v>8400</v>
           </cell>
         </row>
         <row r="3">
@@ -2248,18 +2301,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>16</v>
+            <v>7</v>
           </cell>
           <cell r="O1">
-            <v>800</v>
+            <v>7100</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>1</v>
+            <v>10</v>
           </cell>
           <cell r="O2">
-            <v>11200</v>
+            <v>4900</v>
           </cell>
         </row>
         <row r="3">
@@ -2289,18 +2342,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>113</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
-            <v>1400</v>
+            <v>24000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>7</v>
+            <v>120</v>
           </cell>
           <cell r="O2">
-            <v>22600</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -2372,18 +2425,23 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>17</v>
+            <v>8</v>
           </cell>
           <cell r="O1">
-            <v>0</v>
+            <v>6400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>0</v>
+            <v>9</v>
           </cell>
           <cell r="O2">
-            <v>12000</v>
+            <v>5600</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45502</v>
           </cell>
         </row>
       </sheetData>
@@ -2409,22 +2467,353 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
+            <v>13</v>
+          </cell>
+          <cell r="O1">
+            <v>5800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>4</v>
+          </cell>
+          <cell r="O2">
+            <v>18200</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45504</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.20-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>5000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>5950</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
             <v>17</v>
           </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45511</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>30000</v>
+          </cell>
+          <cell r="K1">
+            <v>62</v>
+          </cell>
           <cell r="O1">
-            <v>0</v>
+            <v>17400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>0</v>
+            <v>58</v>
           </cell>
           <cell r="O2">
-            <v>24000</v>
+            <v>18600</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45508</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>75</v>
+          </cell>
+          <cell r="O1">
+            <v>4500</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>45</v>
+          </cell>
+          <cell r="O2">
+            <v>7500</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45514</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEc"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>12</v>
+          </cell>
+          <cell r="O1">
+            <v>7200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>5</v>
+          </cell>
+          <cell r="O2">
+            <v>16800</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45527</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEc"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>12</v>
+          </cell>
+          <cell r="O1">
+            <v>3600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>5</v>
+          </cell>
+          <cell r="O2">
+            <v>8400</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45531</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.20-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>5000</v>
+          </cell>
+          <cell r="K1">
+            <v>12</v>
+          </cell>
+          <cell r="O1">
+            <v>1800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>5</v>
+          </cell>
+          <cell r="O2">
+            <v>4200</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45532</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEc"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>13</v>
+          </cell>
+          <cell r="O1">
+            <v>2900</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>4</v>
+          </cell>
+          <cell r="O2">
+            <v>9100</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45534</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.20-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>5000</v>
+          </cell>
+          <cell r="K1">
+            <v>13</v>
+          </cell>
+          <cell r="O1">
+            <v>1450</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>4</v>
+          </cell>
+          <cell r="O2">
+            <v>4550</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45536</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2462,6 +2851,321 @@
         <row r="3">
           <cell r="B3">
             <v>45245</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.22-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>94</v>
+          </cell>
+          <cell r="O1">
+            <v>5200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>26</v>
+          </cell>
+          <cell r="O2">
+            <v>18800</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45535</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.20-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>5000</v>
+          </cell>
+          <cell r="K1">
+            <v>15</v>
+          </cell>
+          <cell r="O1">
+            <v>750</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>2</v>
+          </cell>
+          <cell r="O2">
+            <v>5250</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45549</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.22-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>109</v>
+          </cell>
+          <cell r="O1">
+            <v>2200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>11</v>
+          </cell>
+          <cell r="O2">
+            <v>21800</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="B13">
+            <v>45562</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>114</v>
+          </cell>
+          <cell r="O1">
+            <v>600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>6</v>
+          </cell>
+          <cell r="O2">
+            <v>11400</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45557</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>114</v>
+          </cell>
+          <cell r="O1">
+            <v>600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>6</v>
+          </cell>
+          <cell r="O2">
+            <v>11400</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45557</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>118</v>
+          </cell>
+          <cell r="O1">
+            <v>200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>2</v>
+          </cell>
+          <cell r="O2">
+            <v>11800</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45561</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>119</v>
+          </cell>
+          <cell r="O1">
+            <v>200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>1</v>
+          </cell>
+          <cell r="O2">
+            <v>23800</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45562</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>120</v>
+          </cell>
+          <cell r="O1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>0</v>
+          </cell>
+          <cell r="O2">
+            <v>12000</v>
           </cell>
         </row>
       </sheetData>
@@ -2859,7 +3563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:Q54"/>
+  <dimension ref="B2:Q78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="1" customWidth="1"/>
@@ -2893,13 +3597,13 @@
       <c r="J2" s="22"/>
       <c r="K2" s="23"/>
       <c r="L2" s="19">
-        <f>SUM(L5:L57)</f>
-        <v>309400</v>
+        <f>SUM(L5:L86)</f>
+        <v>331850</v>
       </c>
       <c r="M2" s="20"/>
       <c r="N2" s="1">
-        <f>SUM(N5:N58)</f>
-        <v>23450</v>
+        <f>SUM(N5:N71)</f>
+        <v>25200</v>
       </c>
       <c r="Q2" s="1">
         <f>14900+260750</f>
@@ -3373,11 +4077,11 @@
       <c r="G15" s="9"/>
       <c r="H15" s="9">
         <f>'[10]MD50000.15-DEC'!$K$1</f>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I15" s="9">
         <f>'[10]MD50000.15-DEC'!$K$2</f>
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="J15" s="10" t="s">
         <v>12</v>
@@ -3388,11 +4092,11 @@
       </c>
       <c r="L15" s="8">
         <f>'[10]MD50000.15-DEC'!$O$2</f>
-        <v>28000</v>
+        <v>14000</v>
       </c>
       <c r="M15" s="8">
         <f>'[10]MD50000.15-DEC'!$O$1</f>
-        <v>56000</v>
+        <v>70000</v>
       </c>
       <c r="N15" s="1">
         <v>1750</v>
@@ -3493,11 +4197,11 @@
       <c r="G18" s="14"/>
       <c r="H18" s="14">
         <f>'[13]MD50000.15-DEC'!$K$1</f>
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I18" s="14">
         <f>'[13]MD50000.15-DEC'!$K$2</f>
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="J18" s="17" t="s">
         <v>12</v>
@@ -3508,11 +4212,11 @@
       </c>
       <c r="L18" s="16">
         <f>'[13]MD50000.15-DEC'!$O$2</f>
-        <v>6650</v>
+        <v>3500</v>
       </c>
       <c r="M18" s="16">
         <f>'[13]MD50000.15-DEC'!$O$1</f>
-        <v>10150</v>
+        <v>13300</v>
       </c>
       <c r="N18" s="1">
         <v>350</v>
@@ -3576,11 +4280,11 @@
       <c r="G20" s="14"/>
       <c r="H20" s="14">
         <f>'[15]MD10000.10-JAN'!$K$1</f>
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I20" s="14">
         <f>'[15]MD10000.10-JAN'!$K$2</f>
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="J20" s="17" t="s">
         <v>12</v>
@@ -3591,11 +4295,11 @@
       </c>
       <c r="L20" s="16">
         <f>'[15]MD10000.10-JAN'!$O$2</f>
-        <v>7000</v>
+        <v>3850</v>
       </c>
       <c r="M20" s="16">
         <f>'[15]MD10000.10-JAN'!$O$1</f>
-        <v>9800</v>
+        <v>12950</v>
       </c>
       <c r="N20" s="1">
         <v>350</v>
@@ -3619,11 +4323,11 @@
       <c r="G21" s="9"/>
       <c r="H21" s="9">
         <f>'[16]MD10000.10-JAN'!$K$1</f>
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I21" s="9">
         <f>'[16]MD10000.10-JAN'!$K$2</f>
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="J21" s="10" t="s">
         <v>12</v>
@@ -3634,11 +4338,11 @@
       </c>
       <c r="L21" s="8">
         <f>'[16]MD10000.10-JAN'!$O$2</f>
-        <v>7000</v>
+        <v>3850</v>
       </c>
       <c r="M21" s="8">
         <f>'[16]MD10000.10-JAN'!$O$1</f>
-        <v>9800</v>
+        <v>12950</v>
       </c>
       <c r="N21" s="1">
         <v>350</v>
@@ -3702,11 +4406,11 @@
       <c r="G23" s="9"/>
       <c r="H23" s="9">
         <f>'[18]MD10000.20-OCT'!$K$1</f>
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="I23" s="9">
         <f>'[18]MD10000.20-OCT'!$K$2</f>
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="J23" s="10" t="s">
         <v>12</v>
@@ -3717,11 +4421,11 @@
       </c>
       <c r="L23" s="8">
         <f>'[18]MD10000.20-OCT'!$O$2</f>
-        <v>7700</v>
+        <v>4550</v>
       </c>
       <c r="M23" s="8">
         <f>'[18]MD10000.20-OCT'!$O$1</f>
-        <v>9100</v>
+        <v>12250</v>
       </c>
       <c r="N23" s="1">
         <v>350</v>
@@ -3745,11 +4449,11 @@
       <c r="G24" s="9"/>
       <c r="H24" s="9">
         <f>'[19]MD10000.20-OCT'!$K$1</f>
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="I24" s="9">
         <f>'[19]MD10000.20-OCT'!$K$2</f>
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J24" s="10" t="s">
         <v>12</v>
@@ -3760,11 +4464,11 @@
       </c>
       <c r="L24" s="8">
         <f>'[19]MD10000.20-OCT'!$O$2</f>
-        <v>8050</v>
+        <v>4900</v>
       </c>
       <c r="M24" s="8">
         <f>'[19]MD10000.20-OCT'!$O$1</f>
-        <v>8750</v>
+        <v>11900</v>
       </c>
       <c r="N24" s="1">
         <v>350</v>
@@ -3808,9 +4512,6 @@
       <c r="M25" s="8">
         <f>'[20]SM5000.1-oct'!$O$1</f>
         <v>5100</v>
-      </c>
-      <c r="N25" s="1">
-        <v>700</v>
       </c>
     </row>
     <row r="26" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3869,11 +4570,11 @@
       </c>
       <c r="F27" s="14">
         <f>'[22]MD10000.1-OCT'!$K$1</f>
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="G27" s="14">
         <f>'[22]MD10000.1-OCT'!$K$2</f>
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="H27" s="14"/>
       <c r="I27" s="14"/>
@@ -3886,14 +4587,14 @@
       </c>
       <c r="L27" s="16">
         <f>'[22]MD10000.1-OCT'!$O$2</f>
-        <v>4400</v>
+        <v>2500</v>
       </c>
       <c r="M27" s="16">
         <f>'[22]MD10000.1-OCT'!$O$1</f>
-        <v>7600</v>
+        <v>9500</v>
       </c>
       <c r="N27" s="1">
-        <v>700</v>
+        <v>350</v>
       </c>
     </row>
     <row r="28" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4074,11 +4775,11 @@
       <c r="G32" s="14"/>
       <c r="H32" s="14">
         <f>'[28]MD10000.10-JAN'!$K$1</f>
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I32" s="14">
         <f>'[28]MD10000.10-JAN'!$K$2</f>
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J32" s="17" t="s">
         <v>12</v>
@@ -4089,11 +4790,11 @@
       </c>
       <c r="L32" s="16">
         <f>'[28]MD10000.10-JAN'!$O$2</f>
-        <v>9800</v>
+        <v>6650</v>
       </c>
       <c r="M32" s="16">
         <f>'[28]MD10000.10-JAN'!$O$1</f>
-        <v>7000</v>
+        <v>10150</v>
       </c>
       <c r="N32" s="1">
         <v>350</v>
@@ -4157,11 +4858,11 @@
       <c r="G34" s="14"/>
       <c r="H34" s="14">
         <f>'[30]MD10000.10-JAN'!$K$1</f>
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I34" s="14">
         <f>'[30]MD10000.10-JAN'!$K$2</f>
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J34" s="17" t="s">
         <v>12</v>
@@ -4172,11 +4873,11 @@
       </c>
       <c r="L34" s="16">
         <f>'[30]MD10000.10-JAN'!$O$2</f>
-        <v>11200</v>
+        <v>8050</v>
       </c>
       <c r="M34" s="16">
         <f>'[30]MD10000.10-JAN'!$O$1</f>
-        <v>5600</v>
+        <v>8750</v>
       </c>
       <c r="N34" s="1">
         <v>350</v>
@@ -4204,10 +4905,10 @@
       </c>
       <c r="I35" s="9">
         <f>'[31]MD20000.15-DEc'!$K$2</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="K35" s="11">
         <f>'[31]MD20000.15-DEc'!$B$3</f>
@@ -4215,14 +4916,11 @@
       </c>
       <c r="L35" s="8">
         <f>'[31]MD20000.15-DEc'!$O$2</f>
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="M35" s="8">
         <f>'[31]MD20000.15-DEc'!$O$1</f>
-        <v>22600</v>
-      </c>
-      <c r="N35" s="1">
-        <v>1400</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="36" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4247,7 +4945,7 @@
       </c>
       <c r="I36" s="14">
         <f>'[32]MD10000.10-JAN'!$K$2</f>
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="J36" s="17" t="s">
         <v>12</v>
@@ -4258,11 +4956,11 @@
       </c>
       <c r="L36" s="16">
         <f>'[32]MD10000.10-JAN'!$O$2</f>
-        <v>11550</v>
+        <v>8400</v>
       </c>
       <c r="M36" s="16">
         <f>'[32]MD10000.10-JAN'!$O$1</f>
-        <v>5250</v>
+        <v>8400</v>
       </c>
       <c r="N36" s="1">
         <v>350</v>
@@ -4290,7 +4988,7 @@
       </c>
       <c r="I37" s="9">
         <f>'[33]MD20000.15-DEc'!$K$2</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J37" s="10" t="s">
         <v>12</v>
@@ -4301,14 +4999,11 @@
       </c>
       <c r="L37" s="8">
         <f>'[33]MD20000.15-DEc'!$O$2</f>
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="M37" s="8">
         <f>'[33]MD20000.15-DEc'!$O$1</f>
-        <v>19800</v>
-      </c>
-      <c r="N37" s="1">
-        <v>1400</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="38" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4333,10 +5028,10 @@
       </c>
       <c r="I38" s="14">
         <f>'[34]MD10000.20-OCT'!$K$2</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J38" s="17" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="K38" s="15">
         <f>'[34]MD10000.20-OCT'!$B$3</f>
@@ -4344,14 +5039,11 @@
       </c>
       <c r="L38" s="16">
         <f>'[34]MD10000.20-OCT'!$O$2</f>
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="M38" s="16">
         <f>'[34]MD10000.20-OCT'!$O$1</f>
-        <v>5250</v>
-      </c>
-      <c r="N38" s="1">
-        <v>350</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="39" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4387,7 +5079,7 @@
       </c>
       <c r="L39" s="8">
         <f>'[36]MD50000.15-DEC'!$O$2</f>
-        <v>49000</v>
+        <v>46200</v>
       </c>
       <c r="M39" s="8">
         <f>'[35]MD50000.15-DEC'!$O$1</f>
@@ -4405,7 +5097,7 @@
         <v>63</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="E40" s="8">
         <f>'[37]MD10000.20-OCT'!$C$1</f>
@@ -4415,14 +5107,14 @@
       <c r="G40" s="9"/>
       <c r="H40" s="9">
         <f>'[37]MD10000.20-OCT'!$K$1</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I40" s="9">
         <f>'[37]MD10000.20-OCT'!$K$2</f>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="K40" s="11">
         <f>'[37]MD10000.20-OCT'!$B$3</f>
@@ -4430,14 +5122,11 @@
       </c>
       <c r="L40" s="8">
         <f>'[37]MD10000.20-OCT'!$O$2</f>
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="M40" s="8">
         <f>'[37]MD10000.20-OCT'!$O$1</f>
-        <v>4200</v>
-      </c>
-      <c r="N40" s="1">
-        <v>350</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="41" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4456,16 +5145,16 @@
       </c>
       <c r="F41" s="9">
         <f>'[38]MD20000.18-DEC'!$K$1</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G41" s="9">
         <f>'[38]MD20000.18-DEC'!$K$2</f>
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="H41" s="9"/>
       <c r="I41" s="9"/>
       <c r="J41" s="10" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="K41" s="11">
         <f>'[38]MD20000.18-DEC'!$B$3</f>
@@ -4473,14 +5162,11 @@
       </c>
       <c r="L41" s="8">
         <f>'[38]MD20000.18-DEC'!$O$2</f>
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="M41" s="8">
         <f>'[38]MD20000.18-DEC'!$O$1</f>
-        <v>16000</v>
-      </c>
-      <c r="N41" s="1">
-        <v>1400</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="42" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4501,14 +5187,14 @@
       <c r="G42" s="9"/>
       <c r="H42" s="9">
         <f>'[39]MD10000.20-OCT'!$K$1</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I42" s="9">
         <f>'[39]MD10000.20-OCT'!$K$2</f>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="K42" s="11">
         <f>'[39]MD10000.20-OCT'!$B$3</f>
@@ -4516,14 +5202,11 @@
       </c>
       <c r="L42" s="8">
         <f>'[39]MD10000.20-OCT'!$O$2</f>
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="M42" s="8">
         <f>'[39]MD10000.20-OCT'!$O$1</f>
-        <v>3500</v>
-      </c>
-      <c r="N42" s="1">
-        <v>350</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="43" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4542,11 +5225,11 @@
       </c>
       <c r="F43" s="9">
         <f>'[40]MD20000.22-DEC'!$K$1</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G43" s="9">
         <f>'[40]MD20000.22-DEC'!$K$2</f>
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="H43" s="9"/>
       <c r="I43" s="9"/>
@@ -4559,14 +5242,11 @@
       </c>
       <c r="L43" s="8">
         <f>'[40]MD20000.22-DEC'!$O$2</f>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="M43" s="8">
         <f>'[40]MD20000.22-DEC'!$O$1</f>
-        <v>14000</v>
-      </c>
-      <c r="N43" s="1">
-        <v>1400</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="44" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4589,12 +5269,12 @@
       </c>
       <c r="G44" s="9">
         <f>'[41]MD10000.1-OCT'!$K$1</f>
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
       <c r="J44" s="10" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="K44" s="11">
         <f>'[41]MD10000.1-OCT'!$B$3</f>
@@ -4602,14 +5282,11 @@
       </c>
       <c r="L44" s="8">
         <f>'[41]MD10000.1-OCT'!$O$2</f>
-        <v>6400</v>
+        <v>0</v>
       </c>
       <c r="M44" s="8">
         <f>'[41]MD10000.1-OCT'!$O$1</f>
-        <v>5600</v>
-      </c>
-      <c r="N44" s="1">
-        <v>700</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="45" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4630,29 +5307,23 @@
       <c r="G45" s="9"/>
       <c r="H45" s="9">
         <f>'[42]MD10000.20-OCT'!$K$1</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I45" s="9">
         <f>'[42]MD10000.20-OCT'!$K$2</f>
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="K45" s="11">
         <f>'[42]MD10000.20-OCT'!$B$3</f>
         <v>45444</v>
       </c>
-      <c r="L45" s="8">
-        <f>'[42]MD10000.20-OCT'!$O$2</f>
-        <v>3200</v>
-      </c>
+      <c r="L45" s="8"/>
       <c r="M45" s="8">
         <f>'[42]MD10000.20-OCT'!$O$1</f>
-        <v>2800</v>
-      </c>
-      <c r="N45" s="1">
-        <v>350</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4688,7 +5359,7 @@
       </c>
       <c r="L46" s="8">
         <f>'[44]MD10000.1-OCT'!$O$2</f>
-        <v>6300</v>
+        <v>0</v>
       </c>
       <c r="M46" s="8">
         <f>'[43]MD10000.1-OCT'!$O$1</f>
@@ -4714,11 +5385,11 @@
       </c>
       <c r="F47" s="9">
         <f>'[45]MD20000.22-DEC'!$K$1</f>
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="G47" s="9">
         <f>'[45]MD20000.22-DEC'!$K$2</f>
-        <v>52</v>
+        <v>110</v>
       </c>
       <c r="H47" s="9"/>
       <c r="I47" s="9"/>
@@ -4731,11 +5402,11 @@
       </c>
       <c r="L47" s="8">
         <f>'[45]MD20000.22-DEC'!$O$2</f>
-        <v>13600</v>
+        <v>2000</v>
       </c>
       <c r="M47" s="8">
         <f>'[45]MD20000.22-DEC'!$O$1</f>
-        <v>10400</v>
+        <v>22000</v>
       </c>
       <c r="N47" s="1">
         <v>1400</v>
@@ -4757,16 +5428,16 @@
       </c>
       <c r="F48" s="9">
         <f>'[46]MD20000.22-DEC'!$K$1</f>
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="G48" s="9">
         <f>'[46]MD20000.22-DEC'!$K$2</f>
-        <v>28</v>
+        <v>120</v>
       </c>
       <c r="H48" s="9"/>
       <c r="I48" s="9"/>
       <c r="J48" s="10" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="K48" s="11">
         <f>'[46]MD20000.22-DEC'!$B$3</f>
@@ -4774,14 +5445,11 @@
       </c>
       <c r="L48" s="8">
         <f>'[46]MD20000.22-DEC'!$O$2</f>
-        <v>9200</v>
+        <v>0</v>
       </c>
       <c r="M48" s="8">
         <f>'[46]MD20000.22-DEC'!$O$1</f>
-        <v>2800</v>
-      </c>
-      <c r="N48" s="1">
-        <v>700</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="49" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4802,11 +5470,11 @@
       <c r="G49" s="9"/>
       <c r="H49" s="9">
         <f>'[47]MD20000.15-DEc'!$K$1</f>
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I49" s="9">
         <f>'[47]MD20000.15-DEc'!$K$2</f>
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J49" s="10" t="s">
         <v>12</v>
@@ -4817,11 +5485,11 @@
       </c>
       <c r="L49" s="8">
         <f>'[47]MD20000.15-DEc'!$O$2</f>
-        <v>21000</v>
+        <v>8400</v>
       </c>
       <c r="M49" s="8">
         <f>'[47]MD20000.15-DEc'!$O$1</f>
-        <v>3000</v>
+        <v>15600</v>
       </c>
       <c r="N49" s="1">
         <v>1400</v>
@@ -4845,11 +5513,11 @@
       <c r="G50" s="9"/>
       <c r="H50" s="9">
         <f>'[48]MD20000.15-DEc'!$K$1</f>
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I50" s="9">
         <f>'[48]MD20000.15-DEc'!$K$2</f>
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J50" s="10" t="s">
         <v>12</v>
@@ -4860,11 +5528,11 @@
       </c>
       <c r="L50" s="8">
         <f>'[48]MD20000.15-DEc'!$O$2</f>
-        <v>11200</v>
+        <v>4900</v>
       </c>
       <c r="M50" s="8">
         <f>'[48]MD20000.15-DEc'!$O$1</f>
-        <v>800</v>
+        <v>7100</v>
       </c>
       <c r="N50" s="1">
         <v>700</v>
@@ -4886,11 +5554,11 @@
       </c>
       <c r="F51" s="9">
         <f>'[49]MD20000.18-DEC'!$K$1</f>
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="G51" s="9">
         <f>'[49]MD20000.18-DEC'!$K$2</f>
-        <v>7</v>
+        <v>120</v>
       </c>
       <c r="H51" s="9"/>
       <c r="I51" s="9"/>
@@ -4903,14 +5571,11 @@
       </c>
       <c r="L51" s="8">
         <f>'[49]MD20000.18-DEC'!$O$2</f>
-        <v>22600</v>
+        <v>0</v>
       </c>
       <c r="M51" s="8">
         <f>'[49]MD20000.18-DEC'!$O$1</f>
-        <v>1400</v>
-      </c>
-      <c r="N51" s="1">
-        <v>1400</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4931,26 +5596,26 @@
       <c r="G52" s="9"/>
       <c r="H52" s="9">
         <f>'[50]MD20000.15-DEc'!$K$1</f>
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I52" s="9">
         <f>'[50]MD20000.15-DEc'!$K$2</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J52" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K52" s="11">
         <f>'[50]MD20000.15-DEc'!$B$3</f>
-        <v>0</v>
+        <v>45502</v>
       </c>
       <c r="L52" s="8">
         <f>'[50]MD20000.15-DEc'!$O$2</f>
-        <v>12000</v>
+        <v>5600</v>
       </c>
       <c r="M52" s="8">
         <f>'[50]MD20000.15-DEc'!$O$1</f>
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="N52" s="1">
         <v>700</v>
@@ -4974,46 +5639,838 @@
       <c r="G53" s="9"/>
       <c r="H53" s="9">
         <f>'[51]MD50000.15-DEC'!$K$1</f>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I53" s="9">
         <f>'[51]MD50000.15-DEC'!$K$2</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J53" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K53" s="11">
         <f>'[51]MD50000.15-DEC'!$B$3</f>
-        <v>0</v>
+        <v>45504</v>
       </c>
       <c r="L53" s="8">
         <f>'[51]MD50000.15-DEC'!$O$2</f>
-        <v>24000</v>
+        <v>18200</v>
       </c>
       <c r="M53" s="8">
         <f>'[51]MD50000.15-DEC'!$O$1</f>
-        <v>0</v>
-      </c>
-      <c r="N53" s="1">
-        <v>1400</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B54" s="6">
         <v>50</v>
       </c>
-      <c r="C54" s="9"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="8"/>
+      <c r="C54" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="E54" s="8">
+        <f>'[52]MD10000.20-OCT'!$C$1</f>
+        <v>5000</v>
+      </c>
       <c r="F54" s="9"/>
       <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="9"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="11"/>
-      <c r="L54" s="8"/>
-      <c r="M54" s="8"/>
+      <c r="H54" s="9">
+        <f>'[52]MD10000.20-OCT'!$K$1</f>
+        <v>0</v>
+      </c>
+      <c r="I54" s="9">
+        <f>'[52]MD10000.20-OCT'!$K$2</f>
+        <v>17</v>
+      </c>
+      <c r="J54" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="K54" s="11">
+        <f>'[52]MD10000.20-OCT'!$B$3</f>
+        <v>45511</v>
+      </c>
+      <c r="L54" s="8">
+        <f>'[52]MD10000.20-OCT'!$O$2</f>
+        <v>0</v>
+      </c>
+      <c r="M54" s="8">
+        <f>'[52]MD10000.20-OCT'!$O$1</f>
+        <v>5950</v>
+      </c>
+    </row>
+    <row r="55" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="6">
+        <v>51</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="E55" s="8">
+        <f>'[53]MD20000.18-DEC'!$C$1</f>
+        <v>30000</v>
+      </c>
+      <c r="F55" s="9">
+        <f>'[53]MD20000.18-DEC'!$K$1</f>
+        <v>62</v>
+      </c>
+      <c r="G55" s="9">
+        <f>'[53]MD20000.18-DEC'!$K$2</f>
+        <v>58</v>
+      </c>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K55" s="11">
+        <f>'[53]MD20000.18-DEC'!$B$3</f>
+        <v>45508</v>
+      </c>
+      <c r="L55" s="8">
+        <f>'[53]MD20000.18-DEC'!$O$2</f>
+        <v>18600</v>
+      </c>
+      <c r="M55" s="8">
+        <f>'[53]MD20000.18-DEC'!$O$1</f>
+        <v>17400</v>
+      </c>
+      <c r="N55" s="1">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="56" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="6">
+        <v>52</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E56" s="8">
+        <f>'[54]MD20000.18-DEC'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F56" s="9">
+        <f>'[54]MD20000.18-DEC'!$K$1</f>
+        <v>75</v>
+      </c>
+      <c r="G56" s="9">
+        <f>'[54]MD20000.18-DEC'!$K$2</f>
+        <v>45</v>
+      </c>
+      <c r="H56" s="9"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K56" s="11">
+        <f>'[54]MD20000.18-DEC'!$B$3</f>
+        <v>45514</v>
+      </c>
+      <c r="L56" s="8">
+        <f>'[54]MD20000.18-DEC'!$O$2</f>
+        <v>7500</v>
+      </c>
+      <c r="M56" s="8">
+        <f>'[54]MD20000.18-DEC'!$O$1</f>
+        <v>4500</v>
+      </c>
+      <c r="N56" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="57" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B57" s="6">
+        <v>53</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E57" s="8">
+        <f>'[55]MD20000.15-DEc'!$C$1</f>
+        <v>20000</v>
+      </c>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9">
+        <f>'[55]MD20000.15-DEc'!$K$1</f>
+        <v>12</v>
+      </c>
+      <c r="I57" s="9">
+        <f>'[55]MD20000.15-DEc'!$K$2</f>
+        <v>5</v>
+      </c>
+      <c r="J57" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K57" s="11">
+        <f>'[55]MD20000.15-DEc'!$B$3</f>
+        <v>45527</v>
+      </c>
+      <c r="L57" s="8">
+        <f>'[55]MD20000.15-DEc'!$O$2</f>
+        <v>16800</v>
+      </c>
+      <c r="M57" s="8">
+        <f>'[55]MD20000.15-DEc'!$O$1</f>
+        <v>7200</v>
+      </c>
+      <c r="N57" s="1">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="58" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B58" s="6">
+        <v>54</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E58" s="8">
+        <f>'[56]MD20000.15-DEc'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9">
+        <f>'[56]MD20000.15-DEc'!$K$1</f>
+        <v>12</v>
+      </c>
+      <c r="I58" s="9">
+        <f>'[56]MD20000.15-DEc'!$K$2</f>
+        <v>5</v>
+      </c>
+      <c r="J58" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K58" s="11">
+        <f>'[56]MD20000.15-DEc'!$B$3</f>
+        <v>45531</v>
+      </c>
+      <c r="L58" s="8">
+        <f>'[56]MD20000.15-DEc'!$O$2</f>
+        <v>8400</v>
+      </c>
+      <c r="M58" s="8">
+        <f>'[56]MD20000.15-DEc'!$O$1</f>
+        <v>3600</v>
+      </c>
+      <c r="N58" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="59" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="6">
+        <v>55</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="E59" s="8">
+        <f>'[57]MD10000.20-OCT'!$C$1</f>
+        <v>5000</v>
+      </c>
+      <c r="F59" s="9"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9">
+        <f>'[57]MD10000.20-OCT'!$K$1</f>
+        <v>12</v>
+      </c>
+      <c r="I59" s="9">
+        <f>'[57]MD10000.20-OCT'!$K$2</f>
+        <v>5</v>
+      </c>
+      <c r="J59" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K59" s="11">
+        <f>'[57]MD10000.20-OCT'!$B$3</f>
+        <v>45532</v>
+      </c>
+      <c r="L59" s="8">
+        <f>'[57]MD10000.20-OCT'!$O$2</f>
+        <v>4200</v>
+      </c>
+      <c r="M59" s="8">
+        <f>'[57]MD10000.20-OCT'!$O$1</f>
+        <v>1800</v>
+      </c>
+      <c r="N59" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="60" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="6">
+        <v>56</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E60" s="8">
+        <f>'[58]MD20000.15-DEc'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F60" s="9"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9">
+        <f>'[58]MD20000.15-DEc'!$K$1</f>
+        <v>13</v>
+      </c>
+      <c r="I60" s="9">
+        <f>'[58]MD20000.15-DEc'!$K$2</f>
+        <v>4</v>
+      </c>
+      <c r="J60" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K60" s="11">
+        <f>'[58]MD20000.15-DEc'!$B$3</f>
+        <v>45534</v>
+      </c>
+      <c r="L60" s="8">
+        <f>'[58]MD20000.15-DEc'!$O$2</f>
+        <v>9100</v>
+      </c>
+      <c r="M60" s="8">
+        <f>'[58]MD20000.15-DEc'!$O$1</f>
+        <v>2900</v>
+      </c>
+      <c r="N60" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="61" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B61" s="6">
+        <v>57</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D61" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="E61" s="8">
+        <f>'[59]MD10000.20-OCT'!$C$1</f>
+        <v>5000</v>
+      </c>
+      <c r="F61" s="9"/>
+      <c r="G61" s="9"/>
+      <c r="H61" s="9">
+        <f>'[59]MD10000.20-OCT'!$K$1</f>
+        <v>13</v>
+      </c>
+      <c r="I61" s="9">
+        <f>'[59]MD10000.20-OCT'!$K$2</f>
+        <v>4</v>
+      </c>
+      <c r="J61" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K61" s="11">
+        <f>'[59]MD10000.20-OCT'!$B$3</f>
+        <v>45536</v>
+      </c>
+      <c r="L61" s="8">
+        <f>'[59]MD10000.20-OCT'!$O$2</f>
+        <v>4550</v>
+      </c>
+      <c r="M61" s="8">
+        <f>'[59]MD10000.20-OCT'!$O$1</f>
+        <v>1450</v>
+      </c>
+      <c r="N61" s="1">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="62" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="6">
+        <v>58</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E62" s="8">
+        <f>'[60]MD20000.22-DEC'!$C$1</f>
+        <v>20000</v>
+      </c>
+      <c r="F62" s="9">
+        <f>'[60]MD20000.22-DEC'!$K$1</f>
+        <v>94</v>
+      </c>
+      <c r="G62" s="9">
+        <f>'[60]MD20000.22-DEC'!$K$2</f>
+        <v>26</v>
+      </c>
+      <c r="H62" s="9"/>
+      <c r="I62" s="9"/>
+      <c r="J62" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K62" s="11">
+        <f>'[60]MD20000.22-DEC'!$B$3</f>
+        <v>45535</v>
+      </c>
+      <c r="L62" s="8">
+        <f>'[60]MD20000.22-DEC'!$O$2</f>
+        <v>18800</v>
+      </c>
+      <c r="M62" s="8">
+        <f>'[60]MD20000.22-DEC'!$O$1</f>
+        <v>5200</v>
+      </c>
+      <c r="N62" s="1">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="63" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="6">
+        <v>59</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E63" s="8">
+        <f>'[61]MD10000.20-OCT'!$C$1</f>
+        <v>5000</v>
+      </c>
+      <c r="F63" s="9"/>
+      <c r="G63" s="9"/>
+      <c r="H63" s="9">
+        <f>'[61]MD10000.20-OCT'!$K$1</f>
+        <v>15</v>
+      </c>
+      <c r="I63" s="9">
+        <f>'[61]MD10000.20-OCT'!$K$2</f>
+        <v>2</v>
+      </c>
+      <c r="J63" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K63" s="11">
+        <f>'[61]MD10000.20-OCT'!$B$3</f>
+        <v>45549</v>
+      </c>
+      <c r="L63" s="8">
+        <f>'[61]MD10000.20-OCT'!$O$2</f>
+        <v>5250</v>
+      </c>
+      <c r="M63" s="8">
+        <f>'[61]MD10000.20-OCT'!$O$1</f>
+        <v>750</v>
+      </c>
+      <c r="N63" s="1">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="64" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B64" s="6">
+        <v>60</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D64" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E64" s="8">
+        <f>'[62]MD20000.22-DEC'!$C$1</f>
+        <v>20000</v>
+      </c>
+      <c r="F64" s="9">
+        <f>'[62]MD20000.22-DEC'!$K$1</f>
+        <v>109</v>
+      </c>
+      <c r="G64" s="9">
+        <f>'[62]MD20000.22-DEC'!$K$2</f>
+        <v>11</v>
+      </c>
+      <c r="H64" s="9"/>
+      <c r="I64" s="9"/>
+      <c r="J64" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K64" s="11">
+        <f>'[62]MD20000.22-DEC'!$B$13</f>
+        <v>45562</v>
+      </c>
+      <c r="L64" s="8">
+        <f>'[62]MD20000.22-DEC'!$O$2</f>
+        <v>21800</v>
+      </c>
+      <c r="M64" s="8">
+        <f>'[62]MD20000.22-DEC'!$O$1</f>
+        <v>2200</v>
+      </c>
+      <c r="N64" s="1">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="6">
+        <v>61</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D65" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E65" s="8">
+        <f>'[63]MD10000.1-OCT'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F65" s="9">
+        <f>'[63]MD10000.1-OCT'!$K$1</f>
+        <v>114</v>
+      </c>
+      <c r="G65" s="9">
+        <f>'[63]MD10000.1-OCT'!$K$2</f>
+        <v>6</v>
+      </c>
+      <c r="H65" s="9"/>
+      <c r="I65" s="9"/>
+      <c r="J65" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K65" s="11">
+        <f>'[63]MD10000.1-OCT'!$B$3</f>
+        <v>45557</v>
+      </c>
+      <c r="L65" s="8">
+        <f>'[63]MD10000.1-OCT'!$O$2</f>
+        <v>11400</v>
+      </c>
+      <c r="M65" s="8">
+        <f>'[63]MD10000.1-OCT'!$O$1</f>
+        <v>600</v>
+      </c>
+      <c r="N65" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B66" s="6">
+        <v>62</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D66" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E66" s="8">
+        <f>'[64]MD10000.1-OCT'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F66" s="9">
+        <f>'[64]MD10000.1-OCT'!$K$1</f>
+        <v>114</v>
+      </c>
+      <c r="G66" s="9">
+        <f>'[64]MD10000.1-OCT'!$K$2</f>
+        <v>6</v>
+      </c>
+      <c r="H66" s="9"/>
+      <c r="I66" s="9"/>
+      <c r="J66" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K66" s="11">
+        <f>'[64]MD10000.1-OCT'!$B$3</f>
+        <v>45557</v>
+      </c>
+      <c r="L66" s="8">
+        <f>'[64]MD10000.1-OCT'!$O$2</f>
+        <v>11400</v>
+      </c>
+      <c r="M66" s="8">
+        <f>'[64]MD10000.1-OCT'!$O$1</f>
+        <v>600</v>
+      </c>
+      <c r="N66" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B67" s="6">
+        <v>63</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D67" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E67" s="8">
+        <f>'[65]MD10000.1-OCT'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F67" s="9">
+        <f>'[65]MD10000.1-OCT'!$K$1</f>
+        <v>118</v>
+      </c>
+      <c r="G67" s="9">
+        <f>'[65]MD10000.1-OCT'!$K$2</f>
+        <v>2</v>
+      </c>
+      <c r="H67" s="9"/>
+      <c r="I67" s="9"/>
+      <c r="J67" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K67" s="11">
+        <f>'[65]MD10000.1-OCT'!$B$3</f>
+        <v>45561</v>
+      </c>
+      <c r="L67" s="8">
+        <f>'[65]MD10000.1-OCT'!$O$2</f>
+        <v>11800</v>
+      </c>
+      <c r="M67" s="8">
+        <f>'[65]MD10000.1-OCT'!$O$1</f>
+        <v>200</v>
+      </c>
+      <c r="N67" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="68" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B68" s="6">
+        <v>64</v>
+      </c>
+      <c r="C68" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D68" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E68" s="8">
+        <f>'[66]MD20000.18-DEC'!$C$1</f>
+        <v>20000</v>
+      </c>
+      <c r="F68" s="9">
+        <f>'[66]MD20000.18-DEC'!$K$1</f>
+        <v>119</v>
+      </c>
+      <c r="G68" s="9">
+        <f>'[66]MD20000.18-DEC'!$K$2</f>
+        <v>1</v>
+      </c>
+      <c r="H68" s="9"/>
+      <c r="I68" s="9"/>
+      <c r="J68" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K68" s="11">
+        <f>'[66]MD20000.18-DEC'!$B$3</f>
+        <v>45562</v>
+      </c>
+      <c r="L68" s="8">
+        <f>'[66]MD20000.18-DEC'!$O$2</f>
+        <v>23800</v>
+      </c>
+      <c r="M68" s="8">
+        <f>'[66]MD20000.18-DEC'!$O$1</f>
+        <v>200</v>
+      </c>
+      <c r="N68" s="1">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B69" s="6">
+        <v>64</v>
+      </c>
+      <c r="C69" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D69" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E69" s="8">
+        <f>'[67]MD10000.1-OCT'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F69" s="9">
+        <f>'[67]MD10000.1-OCT'!$K$1</f>
+        <v>120</v>
+      </c>
+      <c r="G69" s="9">
+        <f>'[67]MD10000.1-OCT'!$K$2</f>
+        <v>0</v>
+      </c>
+      <c r="H69" s="9"/>
+      <c r="I69" s="9"/>
+      <c r="J69" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K69" s="11">
+        <f>'[67]MD10000.1-OCT'!$B$3</f>
+        <v>0</v>
+      </c>
+      <c r="L69" s="8">
+        <f>'[67]MD10000.1-OCT'!$O$2</f>
+        <v>12000</v>
+      </c>
+      <c r="M69" s="8">
+        <f>'[67]MD10000.1-OCT'!$O$1</f>
+        <v>0</v>
+      </c>
+      <c r="N69" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B70" s="6"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="9"/>
+      <c r="G70" s="9"/>
+      <c r="H70" s="9"/>
+      <c r="I70" s="9"/>
+      <c r="J70" s="10"/>
+      <c r="K70" s="11"/>
+      <c r="L70" s="8"/>
+      <c r="M70" s="8"/>
+    </row>
+    <row r="71" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B71" s="6"/>
+      <c r="C71" s="9"/>
+      <c r="D71" s="15"/>
+      <c r="E71" s="8"/>
+      <c r="F71" s="9"/>
+      <c r="G71" s="9"/>
+      <c r="H71" s="9"/>
+      <c r="I71" s="9"/>
+      <c r="J71" s="10"/>
+      <c r="K71" s="11"/>
+      <c r="L71" s="8"/>
+      <c r="M71" s="8"/>
+    </row>
+    <row r="72" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B72" s="6"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="15"/>
+      <c r="E72" s="8"/>
+      <c r="F72" s="9"/>
+      <c r="G72" s="9"/>
+      <c r="H72" s="9"/>
+      <c r="I72" s="9"/>
+      <c r="J72" s="10"/>
+      <c r="K72" s="11"/>
+      <c r="L72" s="8"/>
+      <c r="M72" s="8"/>
+    </row>
+    <row r="73" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B73" s="6"/>
+      <c r="C73" s="9"/>
+      <c r="D73" s="15"/>
+      <c r="E73" s="8"/>
+      <c r="F73" s="9"/>
+      <c r="G73" s="9"/>
+      <c r="H73" s="9"/>
+      <c r="I73" s="9"/>
+      <c r="J73" s="10"/>
+      <c r="K73" s="11"/>
+      <c r="L73" s="8"/>
+      <c r="M73" s="8"/>
+    </row>
+    <row r="74" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B74" s="6"/>
+      <c r="C74" s="9"/>
+      <c r="D74" s="15"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="9"/>
+      <c r="G74" s="9"/>
+      <c r="H74" s="9"/>
+      <c r="I74" s="9"/>
+      <c r="J74" s="10"/>
+      <c r="K74" s="11"/>
+      <c r="L74" s="8"/>
+      <c r="M74" s="8"/>
+    </row>
+    <row r="75" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B75" s="6"/>
+      <c r="C75" s="9"/>
+      <c r="D75" s="15"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="9"/>
+      <c r="G75" s="9"/>
+      <c r="H75" s="9"/>
+      <c r="I75" s="9"/>
+      <c r="J75" s="10"/>
+      <c r="K75" s="11"/>
+      <c r="L75" s="8"/>
+      <c r="M75" s="8"/>
+    </row>
+    <row r="76" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B76" s="6"/>
+      <c r="C76" s="9"/>
+      <c r="D76" s="15"/>
+      <c r="E76" s="8"/>
+      <c r="F76" s="9"/>
+      <c r="G76" s="9"/>
+      <c r="H76" s="9"/>
+      <c r="I76" s="9"/>
+      <c r="J76" s="10"/>
+      <c r="K76" s="11"/>
+      <c r="L76" s="8"/>
+      <c r="M76" s="8"/>
+    </row>
+    <row r="77" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B77" s="6"/>
+      <c r="C77" s="9"/>
+      <c r="D77" s="15"/>
+      <c r="E77" s="8"/>
+      <c r="F77" s="9"/>
+      <c r="G77" s="9"/>
+      <c r="H77" s="9"/>
+      <c r="I77" s="9"/>
+      <c r="J77" s="10"/>
+      <c r="K77" s="11"/>
+      <c r="L77" s="8"/>
+      <c r="M77" s="8"/>
+    </row>
+    <row r="78" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B78" s="6"/>
+      <c r="C78" s="9"/>
+      <c r="D78" s="15"/>
+      <c r="E78" s="8"/>
+      <c r="F78" s="9"/>
+      <c r="G78" s="9"/>
+      <c r="H78" s="9"/>
+      <c r="I78" s="9"/>
+      <c r="J78" s="10"/>
+      <c r="K78" s="11"/>
+      <c r="L78" s="8"/>
+      <c r="M78" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/LoanOfficer-A/LoanBook.xlsx
+++ b/LoanOfficer-A/LoanBook.xlsx
@@ -77,13 +77,15 @@
     <externalReference r:id="rId66"/>
     <externalReference r:id="rId67"/>
     <externalReference r:id="rId68"/>
+    <externalReference r:id="rId69"/>
+    <externalReference r:id="rId70"/>
   </externalReferences>
   <calcPr calcId="145621" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="97">
   <si>
     <t>Code</t>
   </si>
@@ -362,6 +364,18 @@
   </si>
   <si>
     <t>Ibeyaima</t>
+  </si>
+  <si>
+    <t>Renita</t>
+  </si>
+  <si>
+    <t>L15000p120</t>
+  </si>
+  <si>
+    <t>Puyam Anita</t>
+  </si>
+  <si>
+    <t>L50000p120</t>
   </si>
 </sst>
 </file>
@@ -693,25 +707,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>8</v>
+            <v>5</v>
           </cell>
           <cell r="O1">
-            <v>70000</v>
+            <v>75250</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>40</v>
+            <v>43</v>
           </cell>
           <cell r="O2">
-            <v>14000</v>
+            <v>8750</v>
           </cell>
         </row>
         <row r="3">
@@ -720,7 +734,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -807,25 +821,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>10</v>
+            <v>7</v>
           </cell>
           <cell r="O1">
-            <v>13300</v>
+            <v>14350</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>38</v>
+            <v>41</v>
           </cell>
           <cell r="O2">
-            <v>3500</v>
+            <v>2450</v>
           </cell>
         </row>
         <row r="3">
@@ -834,7 +848,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -889,25 +903,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>11</v>
+            <v>9</v>
           </cell>
           <cell r="O1">
-            <v>12950</v>
+            <v>13650</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>37</v>
+            <v>39</v>
           </cell>
           <cell r="O2">
-            <v>3850</v>
+            <v>3150</v>
           </cell>
         </row>
         <row r="3">
@@ -916,7 +930,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -931,25 +945,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>11</v>
+            <v>9</v>
           </cell>
           <cell r="O1">
-            <v>12950</v>
+            <v>13650</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>37</v>
+            <v>39</v>
           </cell>
           <cell r="O2">
-            <v>3850</v>
+            <v>3150</v>
           </cell>
         </row>
         <row r="3">
@@ -958,7 +972,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1012,25 +1026,25 @@
       <sheetName val="MD10000.20-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>13</v>
+            <v>10</v>
           </cell>
           <cell r="O1">
-            <v>12250</v>
+            <v>13300</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>35</v>
+            <v>38</v>
           </cell>
           <cell r="O2">
-            <v>4550</v>
+            <v>3500</v>
           </cell>
         </row>
         <row r="3">
@@ -1053,25 +1067,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>14</v>
+            <v>12</v>
           </cell>
           <cell r="O1">
-            <v>11900</v>
+            <v>12600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>34</v>
+            <v>36</v>
           </cell>
           <cell r="O2">
-            <v>4900</v>
+            <v>4200</v>
           </cell>
         </row>
         <row r="3">
@@ -1080,7 +1094,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1143,18 +1157,18 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>9</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
-            <v>5100</v>
+            <v>6000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>51</v>
+            <v>60</v>
           </cell>
           <cell r="O2">
-            <v>900</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -1443,25 +1457,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>19</v>
+            <v>16</v>
           </cell>
           <cell r="O1">
-            <v>10150</v>
+            <v>11200</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>29</v>
+            <v>32</v>
           </cell>
           <cell r="O2">
-            <v>6650</v>
+            <v>5600</v>
           </cell>
         </row>
         <row r="3">
@@ -1470,7 +1484,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1567,25 +1581,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>23</v>
+            <v>21</v>
           </cell>
           <cell r="O1">
-            <v>8750</v>
+            <v>9450</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>25</v>
+            <v>27</v>
           </cell>
           <cell r="O2">
-            <v>8050</v>
+            <v>7350</v>
           </cell>
         </row>
         <row r="3">
@@ -1594,7 +1608,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1651,7 +1665,7 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -1661,15 +1675,15 @@
             <v>48</v>
           </cell>
           <cell r="O1">
-            <v>8400</v>
+            <v>9100</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>24</v>
+            <v>26</v>
           </cell>
           <cell r="O2">
-            <v>8400</v>
+            <v>7700</v>
           </cell>
         </row>
         <row r="3">
@@ -1678,7 +1692,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1814,7 +1828,7 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="2">
           <cell r="O2">
@@ -1822,7 +1836,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2119,17 +2133,6 @@
           <cell r="C1">
             <v>10000</v>
           </cell>
-          <cell r="K1">
-            <v>17</v>
-          </cell>
-          <cell r="O1">
-            <v>2900</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>4</v>
-          </cell>
         </row>
         <row r="3">
           <cell r="B3">
@@ -2150,9 +2153,20 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
-        <row r="2">
+        <row r="1">
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
           <cell r="O2">
             <v>0</v>
           </cell>
@@ -2171,25 +2185,25 @@
       <sheetName val="MD20000.22-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>10</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
-            <v>22000</v>
+            <v>24000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>110</v>
+            <v>120</v>
           </cell>
           <cell r="O2">
-            <v>2000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -2252,25 +2266,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>6</v>
+            <v>4</v>
           </cell>
           <cell r="O1">
-            <v>15600</v>
+            <v>18400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>11</v>
+            <v>13</v>
           </cell>
           <cell r="O2">
-            <v>8400</v>
+            <v>5600</v>
           </cell>
         </row>
         <row r="3">
@@ -2279,7 +2293,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2294,25 +2308,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>7</v>
+            <v>4</v>
           </cell>
           <cell r="O1">
-            <v>7100</v>
+            <v>9200</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>10</v>
+            <v>13</v>
           </cell>
           <cell r="O2">
-            <v>4900</v>
+            <v>2800</v>
           </cell>
         </row>
         <row r="3">
@@ -2321,7 +2335,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2335,7 +2349,7 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -2418,25 +2432,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>8</v>
+            <v>6</v>
           </cell>
           <cell r="O1">
-            <v>6400</v>
+            <v>7800</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>9</v>
+            <v>11</v>
           </cell>
           <cell r="O2">
-            <v>5600</v>
+            <v>4200</v>
           </cell>
         </row>
         <row r="3">
@@ -2445,7 +2459,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2460,7 +2474,7 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -2487,7 +2501,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2541,25 +2555,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>30000</v>
           </cell>
           <cell r="K1">
-            <v>62</v>
+            <v>47</v>
           </cell>
           <cell r="O1">
-            <v>17400</v>
+            <v>21900</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>58</v>
+            <v>73</v>
           </cell>
           <cell r="O2">
-            <v>18600</v>
+            <v>14100</v>
           </cell>
         </row>
         <row r="3">
@@ -2581,25 +2595,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>75</v>
+            <v>58</v>
           </cell>
           <cell r="O1">
-            <v>4500</v>
+            <v>6200</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>45</v>
+            <v>62</v>
           </cell>
           <cell r="O2">
-            <v>7500</v>
+            <v>5800</v>
           </cell>
         </row>
         <row r="3">
@@ -2622,25 +2636,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>12</v>
+            <v>9</v>
           </cell>
           <cell r="O1">
-            <v>7200</v>
+            <v>11400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>5</v>
+            <v>8</v>
           </cell>
           <cell r="O2">
-            <v>16800</v>
+            <v>12600</v>
           </cell>
         </row>
         <row r="3">
@@ -2649,7 +2663,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2664,25 +2678,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>12</v>
+            <v>10</v>
           </cell>
           <cell r="O1">
-            <v>3600</v>
+            <v>5000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>5</v>
+            <v>7</v>
           </cell>
           <cell r="O2">
-            <v>8400</v>
+            <v>7000</v>
           </cell>
         </row>
         <row r="3">
@@ -2691,7 +2705,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2705,25 +2719,25 @@
       <sheetName val="MD10000.20-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>12</v>
+            <v>10</v>
           </cell>
           <cell r="O1">
-            <v>1800</v>
+            <v>2500</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>5</v>
+            <v>7</v>
           </cell>
           <cell r="O2">
-            <v>4200</v>
+            <v>3500</v>
           </cell>
         </row>
         <row r="3">
@@ -2746,25 +2760,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>13</v>
+            <v>10</v>
           </cell>
           <cell r="O1">
-            <v>2900</v>
+            <v>5000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>4</v>
+            <v>7</v>
           </cell>
           <cell r="O2">
-            <v>9100</v>
+            <v>7000</v>
           </cell>
         </row>
         <row r="3">
@@ -2773,7 +2787,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2787,25 +2801,25 @@
       <sheetName val="MD10000.20-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>13</v>
+            <v>10</v>
           </cell>
           <cell r="O1">
-            <v>1450</v>
+            <v>2500</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>4</v>
+            <v>7</v>
           </cell>
           <cell r="O2">
-            <v>4550</v>
+            <v>3500</v>
           </cell>
         </row>
         <row r="3">
@@ -2867,25 +2881,25 @@
       <sheetName val="MD20000.22-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>94</v>
+            <v>76</v>
           </cell>
           <cell r="O1">
-            <v>5200</v>
+            <v>8800</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>26</v>
+            <v>44</v>
           </cell>
           <cell r="O2">
-            <v>18800</v>
+            <v>15200</v>
           </cell>
         </row>
         <row r="3">
@@ -2907,25 +2921,25 @@
       <sheetName val="MD10000.20-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>15</v>
+            <v>12</v>
           </cell>
           <cell r="O1">
-            <v>750</v>
+            <v>1800</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>2</v>
+            <v>5</v>
           </cell>
           <cell r="O2">
-            <v>5250</v>
+            <v>4200</v>
           </cell>
         </row>
         <row r="3">
@@ -2947,25 +2961,25 @@
       <sheetName val="MD20000.22-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>109</v>
+            <v>92</v>
           </cell>
           <cell r="O1">
-            <v>2200</v>
+            <v>5600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>11</v>
+            <v>28</v>
           </cell>
           <cell r="O2">
-            <v>21800</v>
+            <v>18400</v>
           </cell>
         </row>
         <row r="13">
@@ -2987,25 +3001,25 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>114</v>
+            <v>96</v>
           </cell>
           <cell r="O1">
-            <v>600</v>
+            <v>2400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>6</v>
+            <v>24</v>
           </cell>
           <cell r="O2">
-            <v>11400</v>
+            <v>9600</v>
           </cell>
         </row>
         <row r="3">
@@ -3027,25 +3041,25 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>114</v>
+            <v>96</v>
           </cell>
           <cell r="O1">
-            <v>600</v>
+            <v>2400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>6</v>
+            <v>24</v>
           </cell>
           <cell r="O2">
-            <v>11400</v>
+            <v>9600</v>
           </cell>
         </row>
         <row r="3">
@@ -3067,25 +3081,25 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>118</v>
+            <v>100</v>
           </cell>
           <cell r="O1">
-            <v>200</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>2</v>
+            <v>20</v>
           </cell>
           <cell r="O2">
-            <v>11800</v>
+            <v>10000</v>
           </cell>
         </row>
         <row r="3">
@@ -3107,25 +3121,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>119</v>
+            <v>101</v>
           </cell>
           <cell r="O1">
-            <v>200</v>
+            <v>3800</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>1</v>
+            <v>19</v>
           </cell>
           <cell r="O2">
-            <v>23800</v>
+            <v>20200</v>
           </cell>
         </row>
         <row r="3">
@@ -3154,18 +3168,103 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>120</v>
+            <v>103</v>
           </cell>
           <cell r="O1">
-            <v>0</v>
+            <v>1700</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>0</v>
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>12000</v>
+            <v>10300</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45563</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>15000</v>
+          </cell>
+          <cell r="K1">
+            <v>113</v>
+          </cell>
+          <cell r="O1">
+            <v>1050</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>7</v>
+          </cell>
+          <cell r="O2">
+            <v>16950</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45570</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>50000</v>
+          </cell>
+          <cell r="K1">
+            <v>117</v>
+          </cell>
+          <cell r="O1">
+            <v>1500</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>3</v>
+          </cell>
+          <cell r="O2">
+            <v>58500</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45579</v>
           </cell>
         </row>
       </sheetData>
@@ -3555,7 +3654,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3598,12 +3697,12 @@
       <c r="K2" s="23"/>
       <c r="L2" s="19">
         <f>SUM(L5:L86)</f>
-        <v>331850</v>
+        <v>351800</v>
       </c>
       <c r="M2" s="20"/>
       <c r="N2" s="1">
         <f>SUM(N5:N71)</f>
-        <v>25200</v>
+        <v>27300</v>
       </c>
       <c r="Q2" s="1">
         <f>14900+260750</f>
@@ -4077,11 +4176,11 @@
       <c r="G15" s="9"/>
       <c r="H15" s="9">
         <f>'[10]MD50000.15-DEC'!$K$1</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I15" s="9">
         <f>'[10]MD50000.15-DEC'!$K$2</f>
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J15" s="10" t="s">
         <v>12</v>
@@ -4092,11 +4191,11 @@
       </c>
       <c r="L15" s="8">
         <f>'[10]MD50000.15-DEC'!$O$2</f>
-        <v>14000</v>
+        <v>8750</v>
       </c>
       <c r="M15" s="8">
         <f>'[10]MD50000.15-DEC'!$O$1</f>
-        <v>70000</v>
+        <v>75250</v>
       </c>
       <c r="N15" s="1">
         <v>1750</v>
@@ -4197,11 +4296,11 @@
       <c r="G18" s="14"/>
       <c r="H18" s="14">
         <f>'[13]MD50000.15-DEC'!$K$1</f>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I18" s="14">
         <f>'[13]MD50000.15-DEC'!$K$2</f>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J18" s="17" t="s">
         <v>12</v>
@@ -4212,11 +4311,11 @@
       </c>
       <c r="L18" s="16">
         <f>'[13]MD50000.15-DEC'!$O$2</f>
-        <v>3500</v>
+        <v>2450</v>
       </c>
       <c r="M18" s="16">
         <f>'[13]MD50000.15-DEC'!$O$1</f>
-        <v>13300</v>
+        <v>14350</v>
       </c>
       <c r="N18" s="1">
         <v>350</v>
@@ -4280,11 +4379,11 @@
       <c r="G20" s="14"/>
       <c r="H20" s="14">
         <f>'[15]MD10000.10-JAN'!$K$1</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I20" s="14">
         <f>'[15]MD10000.10-JAN'!$K$2</f>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J20" s="17" t="s">
         <v>12</v>
@@ -4295,11 +4394,11 @@
       </c>
       <c r="L20" s="16">
         <f>'[15]MD10000.10-JAN'!$O$2</f>
-        <v>3850</v>
+        <v>3150</v>
       </c>
       <c r="M20" s="16">
         <f>'[15]MD10000.10-JAN'!$O$1</f>
-        <v>12950</v>
+        <v>13650</v>
       </c>
       <c r="N20" s="1">
         <v>350</v>
@@ -4323,11 +4422,11 @@
       <c r="G21" s="9"/>
       <c r="H21" s="9">
         <f>'[16]MD10000.10-JAN'!$K$1</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I21" s="9">
         <f>'[16]MD10000.10-JAN'!$K$2</f>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J21" s="10" t="s">
         <v>12</v>
@@ -4338,11 +4437,11 @@
       </c>
       <c r="L21" s="8">
         <f>'[16]MD10000.10-JAN'!$O$2</f>
-        <v>3850</v>
+        <v>3150</v>
       </c>
       <c r="M21" s="8">
         <f>'[16]MD10000.10-JAN'!$O$1</f>
-        <v>12950</v>
+        <v>13650</v>
       </c>
       <c r="N21" s="1">
         <v>350</v>
@@ -4406,11 +4505,11 @@
       <c r="G23" s="9"/>
       <c r="H23" s="9">
         <f>'[18]MD10000.20-OCT'!$K$1</f>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I23" s="9">
         <f>'[18]MD10000.20-OCT'!$K$2</f>
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J23" s="10" t="s">
         <v>12</v>
@@ -4421,11 +4520,11 @@
       </c>
       <c r="L23" s="8">
         <f>'[18]MD10000.20-OCT'!$O$2</f>
-        <v>4550</v>
+        <v>3500</v>
       </c>
       <c r="M23" s="8">
         <f>'[18]MD10000.20-OCT'!$O$1</f>
-        <v>12250</v>
+        <v>13300</v>
       </c>
       <c r="N23" s="1">
         <v>350</v>
@@ -4449,11 +4548,11 @@
       <c r="G24" s="9"/>
       <c r="H24" s="9">
         <f>'[19]MD10000.20-OCT'!$K$1</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I24" s="9">
         <f>'[19]MD10000.20-OCT'!$K$2</f>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J24" s="10" t="s">
         <v>12</v>
@@ -4464,11 +4563,11 @@
       </c>
       <c r="L24" s="8">
         <f>'[19]MD10000.20-OCT'!$O$2</f>
-        <v>4900</v>
+        <v>4200</v>
       </c>
       <c r="M24" s="8">
         <f>'[19]MD10000.20-OCT'!$O$1</f>
-        <v>11900</v>
+        <v>12600</v>
       </c>
       <c r="N24" s="1">
         <v>350</v>
@@ -4490,11 +4589,11 @@
       </c>
       <c r="F25" s="9">
         <f>'[20]SM5000.1-oct'!$K$1</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G25" s="9">
         <f>'[20]SM5000.1-oct'!$K$2</f>
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
@@ -4507,11 +4606,11 @@
       </c>
       <c r="L25" s="8">
         <f>'[20]SM5000.1-oct'!$O$2</f>
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="M25" s="8">
         <f>'[20]SM5000.1-oct'!$O$1</f>
-        <v>5100</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="26" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4593,9 +4692,6 @@
         <f>'[22]MD10000.1-OCT'!$O$1</f>
         <v>9500</v>
       </c>
-      <c r="N27" s="1">
-        <v>350</v>
-      </c>
     </row>
     <row r="28" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="6">
@@ -4775,11 +4871,11 @@
       <c r="G32" s="14"/>
       <c r="H32" s="14">
         <f>'[28]MD10000.10-JAN'!$K$1</f>
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I32" s="14">
         <f>'[28]MD10000.10-JAN'!$K$2</f>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J32" s="17" t="s">
         <v>12</v>
@@ -4790,11 +4886,11 @@
       </c>
       <c r="L32" s="16">
         <f>'[28]MD10000.10-JAN'!$O$2</f>
-        <v>6650</v>
+        <v>5600</v>
       </c>
       <c r="M32" s="16">
         <f>'[28]MD10000.10-JAN'!$O$1</f>
-        <v>10150</v>
+        <v>11200</v>
       </c>
       <c r="N32" s="1">
         <v>350</v>
@@ -4858,11 +4954,11 @@
       <c r="G34" s="14"/>
       <c r="H34" s="14">
         <f>'[30]MD10000.10-JAN'!$K$1</f>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I34" s="14">
         <f>'[30]MD10000.10-JAN'!$K$2</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J34" s="17" t="s">
         <v>12</v>
@@ -4873,11 +4969,11 @@
       </c>
       <c r="L34" s="16">
         <f>'[30]MD10000.10-JAN'!$O$2</f>
-        <v>8050</v>
+        <v>7350</v>
       </c>
       <c r="M34" s="16">
         <f>'[30]MD10000.10-JAN'!$O$1</f>
-        <v>8750</v>
+        <v>9450</v>
       </c>
       <c r="N34" s="1">
         <v>350</v>
@@ -4945,7 +5041,7 @@
       </c>
       <c r="I36" s="14">
         <f>'[32]MD10000.10-JAN'!$K$2</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J36" s="17" t="s">
         <v>12</v>
@@ -4956,11 +5052,11 @@
       </c>
       <c r="L36" s="16">
         <f>'[32]MD10000.10-JAN'!$O$2</f>
-        <v>8400</v>
+        <v>7700</v>
       </c>
       <c r="M36" s="16">
         <f>'[32]MD10000.10-JAN'!$O$1</f>
-        <v>8400</v>
+        <v>9100</v>
       </c>
       <c r="N36" s="1">
         <v>350</v>
@@ -5343,15 +5439,15 @@
       <c r="F46" s="9"/>
       <c r="G46" s="9"/>
       <c r="H46" s="9">
-        <f>'[43]MD10000.1-OCT'!$K$1</f>
+        <f>'[44]MD10000.1-OCT'!$K$1</f>
+        <v>0</v>
+      </c>
+      <c r="I46" s="9">
+        <f>'[44]MD10000.1-OCT'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="I46" s="9">
-        <f>'[43]MD10000.1-OCT'!$K$2</f>
-        <v>4</v>
-      </c>
       <c r="J46" s="10" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="K46" s="11">
         <f>'[43]MD10000.1-OCT'!$B$3</f>
@@ -5362,11 +5458,8 @@
         <v>0</v>
       </c>
       <c r="M46" s="8">
-        <f>'[43]MD10000.1-OCT'!$O$1</f>
-        <v>2900</v>
-      </c>
-      <c r="N46" s="1">
-        <v>700</v>
+        <f>'[44]MD10000.1-OCT'!$O$1</f>
+        <v>12000</v>
       </c>
     </row>
     <row r="47" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5385,16 +5478,16 @@
       </c>
       <c r="F47" s="9">
         <f>'[45]MD20000.22-DEC'!$K$1</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G47" s="9">
         <f>'[45]MD20000.22-DEC'!$K$2</f>
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H47" s="9"/>
       <c r="I47" s="9"/>
       <c r="J47" s="10" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="K47" s="11">
         <f>'[45]MD20000.22-DEC'!$B$3</f>
@@ -5402,14 +5495,11 @@
       </c>
       <c r="L47" s="8">
         <f>'[45]MD20000.22-DEC'!$O$2</f>
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="M47" s="8">
         <f>'[45]MD20000.22-DEC'!$O$1</f>
-        <v>22000</v>
-      </c>
-      <c r="N47" s="1">
-        <v>1400</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5470,11 +5560,11 @@
       <c r="G49" s="9"/>
       <c r="H49" s="9">
         <f>'[47]MD20000.15-DEc'!$K$1</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I49" s="9">
         <f>'[47]MD20000.15-DEc'!$K$2</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J49" s="10" t="s">
         <v>12</v>
@@ -5485,11 +5575,11 @@
       </c>
       <c r="L49" s="8">
         <f>'[47]MD20000.15-DEc'!$O$2</f>
-        <v>8400</v>
+        <v>5600</v>
       </c>
       <c r="M49" s="8">
         <f>'[47]MD20000.15-DEc'!$O$1</f>
-        <v>15600</v>
+        <v>18400</v>
       </c>
       <c r="N49" s="1">
         <v>1400</v>
@@ -5513,11 +5603,11 @@
       <c r="G50" s="9"/>
       <c r="H50" s="9">
         <f>'[48]MD20000.15-DEc'!$K$1</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I50" s="9">
         <f>'[48]MD20000.15-DEc'!$K$2</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J50" s="10" t="s">
         <v>12</v>
@@ -5528,11 +5618,11 @@
       </c>
       <c r="L50" s="8">
         <f>'[48]MD20000.15-DEc'!$O$2</f>
-        <v>4900</v>
+        <v>2800</v>
       </c>
       <c r="M50" s="8">
         <f>'[48]MD20000.15-DEc'!$O$1</f>
-        <v>7100</v>
+        <v>9200</v>
       </c>
       <c r="N50" s="1">
         <v>700</v>
@@ -5596,11 +5686,11 @@
       <c r="G52" s="9"/>
       <c r="H52" s="9">
         <f>'[50]MD20000.15-DEc'!$K$1</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I52" s="9">
         <f>'[50]MD20000.15-DEc'!$K$2</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J52" s="10" t="s">
         <v>12</v>
@@ -5611,11 +5701,11 @@
       </c>
       <c r="L52" s="8">
         <f>'[50]MD20000.15-DEc'!$O$2</f>
-        <v>5600</v>
+        <v>4200</v>
       </c>
       <c r="M52" s="8">
         <f>'[50]MD20000.15-DEc'!$O$1</f>
-        <v>6400</v>
+        <v>7800</v>
       </c>
       <c r="N52" s="1">
         <v>700</v>
@@ -5717,11 +5807,11 @@
       </c>
       <c r="F55" s="9">
         <f>'[53]MD20000.18-DEC'!$K$1</f>
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="G55" s="9">
         <f>'[53]MD20000.18-DEC'!$K$2</f>
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="H55" s="9"/>
       <c r="I55" s="9"/>
@@ -5734,11 +5824,11 @@
       </c>
       <c r="L55" s="8">
         <f>'[53]MD20000.18-DEC'!$O$2</f>
-        <v>18600</v>
+        <v>14100</v>
       </c>
       <c r="M55" s="8">
         <f>'[53]MD20000.18-DEC'!$O$1</f>
-        <v>17400</v>
+        <v>21900</v>
       </c>
       <c r="N55" s="1">
         <v>2100</v>
@@ -5760,11 +5850,11 @@
       </c>
       <c r="F56" s="9">
         <f>'[54]MD20000.18-DEC'!$K$1</f>
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="G56" s="9">
         <f>'[54]MD20000.18-DEC'!$K$2</f>
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="H56" s="9"/>
       <c r="I56" s="9"/>
@@ -5777,11 +5867,11 @@
       </c>
       <c r="L56" s="8">
         <f>'[54]MD20000.18-DEC'!$O$2</f>
-        <v>7500</v>
+        <v>5800</v>
       </c>
       <c r="M56" s="8">
         <f>'[54]MD20000.18-DEC'!$O$1</f>
-        <v>4500</v>
+        <v>6200</v>
       </c>
       <c r="N56" s="1">
         <v>700</v>
@@ -5805,11 +5895,11 @@
       <c r="G57" s="9"/>
       <c r="H57" s="9">
         <f>'[55]MD20000.15-DEc'!$K$1</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I57" s="9">
         <f>'[55]MD20000.15-DEc'!$K$2</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J57" s="10" t="s">
         <v>12</v>
@@ -5820,11 +5910,11 @@
       </c>
       <c r="L57" s="8">
         <f>'[55]MD20000.15-DEc'!$O$2</f>
-        <v>16800</v>
+        <v>12600</v>
       </c>
       <c r="M57" s="8">
         <f>'[55]MD20000.15-DEc'!$O$1</f>
-        <v>7200</v>
+        <v>11400</v>
       </c>
       <c r="N57" s="1">
         <v>1400</v>
@@ -5848,11 +5938,11 @@
       <c r="G58" s="9"/>
       <c r="H58" s="9">
         <f>'[56]MD20000.15-DEc'!$K$1</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I58" s="9">
         <f>'[56]MD20000.15-DEc'!$K$2</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J58" s="10" t="s">
         <v>12</v>
@@ -5863,11 +5953,11 @@
       </c>
       <c r="L58" s="8">
         <f>'[56]MD20000.15-DEc'!$O$2</f>
-        <v>8400</v>
+        <v>7000</v>
       </c>
       <c r="M58" s="8">
         <f>'[56]MD20000.15-DEc'!$O$1</f>
-        <v>3600</v>
+        <v>5000</v>
       </c>
       <c r="N58" s="1">
         <v>700</v>
@@ -5891,11 +5981,11 @@
       <c r="G59" s="9"/>
       <c r="H59" s="9">
         <f>'[57]MD10000.20-OCT'!$K$1</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I59" s="9">
         <f>'[57]MD10000.20-OCT'!$K$2</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J59" s="10" t="s">
         <v>12</v>
@@ -5906,11 +5996,11 @@
       </c>
       <c r="L59" s="8">
         <f>'[57]MD10000.20-OCT'!$O$2</f>
-        <v>4200</v>
+        <v>3500</v>
       </c>
       <c r="M59" s="8">
         <f>'[57]MD10000.20-OCT'!$O$1</f>
-        <v>1800</v>
+        <v>2500</v>
       </c>
       <c r="N59" s="1">
         <v>700</v>
@@ -5934,11 +6024,11 @@
       <c r="G60" s="9"/>
       <c r="H60" s="9">
         <f>'[58]MD20000.15-DEc'!$K$1</f>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I60" s="9">
         <f>'[58]MD20000.15-DEc'!$K$2</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J60" s="10" t="s">
         <v>12</v>
@@ -5949,11 +6039,11 @@
       </c>
       <c r="L60" s="8">
         <f>'[58]MD20000.15-DEc'!$O$2</f>
-        <v>9100</v>
+        <v>7000</v>
       </c>
       <c r="M60" s="8">
         <f>'[58]MD20000.15-DEc'!$O$1</f>
-        <v>2900</v>
+        <v>5000</v>
       </c>
       <c r="N60" s="1">
         <v>700</v>
@@ -5977,11 +6067,11 @@
       <c r="G61" s="9"/>
       <c r="H61" s="9">
         <f>'[59]MD10000.20-OCT'!$K$1</f>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I61" s="9">
         <f>'[59]MD10000.20-OCT'!$K$2</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J61" s="10" t="s">
         <v>12</v>
@@ -5992,11 +6082,11 @@
       </c>
       <c r="L61" s="8">
         <f>'[59]MD10000.20-OCT'!$O$2</f>
-        <v>4550</v>
+        <v>3500</v>
       </c>
       <c r="M61" s="8">
         <f>'[59]MD10000.20-OCT'!$O$1</f>
-        <v>1450</v>
+        <v>2500</v>
       </c>
       <c r="N61" s="1">
         <v>350</v>
@@ -6018,11 +6108,11 @@
       </c>
       <c r="F62" s="9">
         <f>'[60]MD20000.22-DEC'!$K$1</f>
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G62" s="9">
         <f>'[60]MD20000.22-DEC'!$K$2</f>
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="H62" s="9"/>
       <c r="I62" s="9"/>
@@ -6035,11 +6125,11 @@
       </c>
       <c r="L62" s="8">
         <f>'[60]MD20000.22-DEC'!$O$2</f>
-        <v>18800</v>
+        <v>15200</v>
       </c>
       <c r="M62" s="8">
         <f>'[60]MD20000.22-DEC'!$O$1</f>
-        <v>5200</v>
+        <v>8800</v>
       </c>
       <c r="N62" s="1">
         <v>1400</v>
@@ -6063,11 +6153,11 @@
       <c r="G63" s="9"/>
       <c r="H63" s="9">
         <f>'[61]MD10000.20-OCT'!$K$1</f>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I63" s="9">
         <f>'[61]MD10000.20-OCT'!$K$2</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J63" s="10" t="s">
         <v>12</v>
@@ -6078,11 +6168,11 @@
       </c>
       <c r="L63" s="8">
         <f>'[61]MD10000.20-OCT'!$O$2</f>
-        <v>5250</v>
+        <v>4200</v>
       </c>
       <c r="M63" s="8">
         <f>'[61]MD10000.20-OCT'!$O$1</f>
-        <v>750</v>
+        <v>1800</v>
       </c>
       <c r="N63" s="1">
         <v>350</v>
@@ -6104,11 +6194,11 @@
       </c>
       <c r="F64" s="9">
         <f>'[62]MD20000.22-DEC'!$K$1</f>
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="G64" s="9">
         <f>'[62]MD20000.22-DEC'!$K$2</f>
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H64" s="9"/>
       <c r="I64" s="9"/>
@@ -6121,11 +6211,11 @@
       </c>
       <c r="L64" s="8">
         <f>'[62]MD20000.22-DEC'!$O$2</f>
-        <v>21800</v>
+        <v>18400</v>
       </c>
       <c r="M64" s="8">
         <f>'[62]MD20000.22-DEC'!$O$1</f>
-        <v>2200</v>
+        <v>5600</v>
       </c>
       <c r="N64" s="1">
         <v>1400</v>
@@ -6147,11 +6237,11 @@
       </c>
       <c r="F65" s="9">
         <f>'[63]MD10000.1-OCT'!$K$1</f>
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="G65" s="9">
         <f>'[63]MD10000.1-OCT'!$K$2</f>
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="H65" s="9"/>
       <c r="I65" s="9"/>
@@ -6164,11 +6254,11 @@
       </c>
       <c r="L65" s="8">
         <f>'[63]MD10000.1-OCT'!$O$2</f>
-        <v>11400</v>
+        <v>9600</v>
       </c>
       <c r="M65" s="8">
         <f>'[63]MD10000.1-OCT'!$O$1</f>
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="N65" s="1">
         <v>700</v>
@@ -6190,11 +6280,11 @@
       </c>
       <c r="F66" s="9">
         <f>'[64]MD10000.1-OCT'!$K$1</f>
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="G66" s="9">
         <f>'[64]MD10000.1-OCT'!$K$2</f>
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="H66" s="9"/>
       <c r="I66" s="9"/>
@@ -6207,11 +6297,11 @@
       </c>
       <c r="L66" s="8">
         <f>'[64]MD10000.1-OCT'!$O$2</f>
-        <v>11400</v>
+        <v>9600</v>
       </c>
       <c r="M66" s="8">
         <f>'[64]MD10000.1-OCT'!$O$1</f>
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="N66" s="1">
         <v>700</v>
@@ -6233,11 +6323,11 @@
       </c>
       <c r="F67" s="9">
         <f>'[65]MD10000.1-OCT'!$K$1</f>
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="G67" s="9">
         <f>'[65]MD10000.1-OCT'!$K$2</f>
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H67" s="9"/>
       <c r="I67" s="9"/>
@@ -6250,11 +6340,11 @@
       </c>
       <c r="L67" s="8">
         <f>'[65]MD10000.1-OCT'!$O$2</f>
-        <v>11800</v>
+        <v>10000</v>
       </c>
       <c r="M67" s="8">
         <f>'[65]MD10000.1-OCT'!$O$1</f>
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="N67" s="1">
         <v>700</v>
@@ -6276,11 +6366,11 @@
       </c>
       <c r="F68" s="9">
         <f>'[66]MD20000.18-DEC'!$K$1</f>
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="G68" s="9">
         <f>'[66]MD20000.18-DEC'!$K$2</f>
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="H68" s="9"/>
       <c r="I68" s="9"/>
@@ -6293,11 +6383,11 @@
       </c>
       <c r="L68" s="8">
         <f>'[66]MD20000.18-DEC'!$O$2</f>
-        <v>23800</v>
+        <v>20200</v>
       </c>
       <c r="M68" s="8">
         <f>'[66]MD20000.18-DEC'!$O$1</f>
-        <v>200</v>
+        <v>3800</v>
       </c>
       <c r="N68" s="1">
         <v>1400</v>
@@ -6305,7 +6395,7 @@
     </row>
     <row r="69" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B69" s="6">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C69" s="14" t="s">
         <v>70</v>
@@ -6319,11 +6409,11 @@
       </c>
       <c r="F69" s="9">
         <f>'[67]MD10000.1-OCT'!$K$1</f>
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="G69" s="9">
         <f>'[67]MD10000.1-OCT'!$K$2</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H69" s="9"/>
       <c r="I69" s="9"/>
@@ -6332,47 +6422,105 @@
       </c>
       <c r="K69" s="11">
         <f>'[67]MD10000.1-OCT'!$B$3</f>
-        <v>0</v>
+        <v>45563</v>
       </c>
       <c r="L69" s="8">
         <f>'[67]MD10000.1-OCT'!$O$2</f>
-        <v>12000</v>
+        <v>10300</v>
       </c>
       <c r="M69" s="8">
         <f>'[67]MD10000.1-OCT'!$O$1</f>
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="N69" s="1">
         <v>700</v>
       </c>
     </row>
     <row r="70" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="6"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="15"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="9"/>
-      <c r="G70" s="9"/>
+      <c r="B70" s="6">
+        <v>66</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D70" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="E70" s="8">
+        <f>'[68]MD10000.1-OCT'!$C$1</f>
+        <v>15000</v>
+      </c>
+      <c r="F70" s="9">
+        <f>'[68]MD10000.1-OCT'!$K$1</f>
+        <v>113</v>
+      </c>
+      <c r="G70" s="9">
+        <f>'[68]MD10000.1-OCT'!$K$2</f>
+        <v>7</v>
+      </c>
       <c r="H70" s="9"/>
       <c r="I70" s="9"/>
-      <c r="J70" s="10"/>
-      <c r="K70" s="11"/>
-      <c r="L70" s="8"/>
-      <c r="M70" s="8"/>
+      <c r="J70" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K70" s="11">
+        <f>'[68]MD10000.1-OCT'!$B$3</f>
+        <v>45570</v>
+      </c>
+      <c r="L70" s="8">
+        <f>'[68]MD10000.1-OCT'!$O$2</f>
+        <v>16950</v>
+      </c>
+      <c r="M70" s="8">
+        <f>'[68]MD10000.1-OCT'!$O$1</f>
+        <v>1050</v>
+      </c>
+      <c r="N70" s="1">
+        <v>1050</v>
+      </c>
     </row>
     <row r="71" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="6"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="15"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="9"/>
+      <c r="B71" s="6">
+        <v>67</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D71" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="E71" s="8">
+        <f>'[69]MD20000.18-DEC'!$C$1</f>
+        <v>50000</v>
+      </c>
+      <c r="F71" s="9">
+        <f>'[69]MD20000.18-DEC'!$K$1</f>
+        <v>117</v>
+      </c>
+      <c r="G71" s="9">
+        <f>'[69]MD20000.18-DEC'!$K$2</f>
+        <v>3</v>
+      </c>
       <c r="H71" s="9"/>
       <c r="I71" s="9"/>
-      <c r="J71" s="10"/>
-      <c r="K71" s="11"/>
-      <c r="L71" s="8"/>
-      <c r="M71" s="8"/>
+      <c r="J71" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K71" s="11">
+        <f>'[69]MD20000.18-DEC'!$B$3</f>
+        <v>45579</v>
+      </c>
+      <c r="L71" s="8">
+        <f>'[69]MD20000.18-DEC'!$O$2</f>
+        <v>58500</v>
+      </c>
+      <c r="M71" s="8">
+        <f>'[69]MD20000.18-DEC'!$O$1</f>
+        <v>1500</v>
+      </c>
+      <c r="N71" s="1">
+        <v>3500</v>
+      </c>
     </row>
     <row r="72" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B72" s="6"/>

--- a/LoanOfficer-A/LoanBook.xlsx
+++ b/LoanOfficer-A/LoanBook.xlsx
@@ -79,13 +79,21 @@
     <externalReference r:id="rId68"/>
     <externalReference r:id="rId69"/>
     <externalReference r:id="rId70"/>
+    <externalReference r:id="rId71"/>
+    <externalReference r:id="rId72"/>
+    <externalReference r:id="rId73"/>
+    <externalReference r:id="rId74"/>
+    <externalReference r:id="rId75"/>
+    <externalReference r:id="rId76"/>
+    <externalReference r:id="rId77"/>
+    <externalReference r:id="rId78"/>
   </externalReferences>
   <calcPr calcId="145621" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="103">
   <si>
     <t>Code</t>
   </si>
@@ -376,6 +384,24 @@
   </si>
   <si>
     <t>L50000p120</t>
+  </si>
+  <si>
+    <t>Kh priyadarsini</t>
+  </si>
+  <si>
+    <t>L100000p40</t>
+  </si>
+  <si>
+    <t>kh Shaya</t>
+  </si>
+  <si>
+    <t>Shantibala</t>
+  </si>
+  <si>
+    <t>Joychandra</t>
+  </si>
+  <si>
+    <t>Sanatombi</t>
   </si>
 </sst>
 </file>
@@ -707,25 +733,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>5</v>
-          </cell>
-          <cell r="O1">
-            <v>75250</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>43</v>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>84000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>48</v>
           </cell>
           <cell r="O2">
-            <v>8750</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -734,7 +760,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -821,25 +847,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>7</v>
-          </cell>
-          <cell r="O1">
-            <v>14350</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>41</v>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>16800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>48</v>
           </cell>
           <cell r="O2">
-            <v>2450</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -848,7 +874,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -910,18 +936,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>9</v>
-          </cell>
-          <cell r="O1">
-            <v>13650</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>39</v>
+            <v>8</v>
+          </cell>
+          <cell r="O1">
+            <v>14000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>40</v>
           </cell>
           <cell r="O2">
-            <v>3150</v>
+            <v>2800</v>
           </cell>
         </row>
         <row r="3">
@@ -952,18 +978,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>9</v>
-          </cell>
-          <cell r="O1">
-            <v>13650</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>39</v>
+            <v>8</v>
+          </cell>
+          <cell r="O1">
+            <v>14000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>40</v>
           </cell>
           <cell r="O2">
-            <v>3150</v>
+            <v>2800</v>
           </cell>
         </row>
         <row r="3">
@@ -987,7 +1013,7 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
+      <sheetData sheetId="1" refreshError="1">
         <row r="1">
           <cell r="C1">
             <v>5000</v>
@@ -1033,18 +1059,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>10</v>
-          </cell>
-          <cell r="O1">
-            <v>13300</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>38</v>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>16800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>48</v>
           </cell>
           <cell r="O2">
-            <v>3500</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -1067,25 +1093,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>12</v>
-          </cell>
-          <cell r="O1">
-            <v>12600</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>36</v>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>16800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>48</v>
           </cell>
           <cell r="O2">
-            <v>4200</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -1094,7 +1120,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1149,6 +1175,1247 @@
       <sheetName val="SM5000.1-oct"/>
     </sheetNames>
     <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>5000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>6000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>60</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45323</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.20-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>5000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>6000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45332</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45339</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45334</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEC"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>12</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45337</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEC"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEC"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45345</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>30000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>36000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45354</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.10-JAN"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>16800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>48</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45366</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEc"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45380</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45213</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.10-JAN"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>16800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>48</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45389</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEc"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="G1">
+            <v>17</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45394</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.10-JAN"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="G1">
+            <v>48</v>
+          </cell>
+          <cell r="O1">
+            <v>9450</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>27</v>
+          </cell>
+          <cell r="O2">
+            <v>7350</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45399</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEc"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="G1">
+            <v>17</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45406</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.20-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>5000</v>
+          </cell>
+          <cell r="G1">
+            <v>17</v>
+          </cell>
+          <cell r="O1">
+            <v>5950</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45406</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD50000.15-DEC"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>40000</v>
+          </cell>
+          <cell r="K1">
+            <v>47</v>
+          </cell>
+          <cell r="O1">
+            <v>1400</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45416</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD50000.15-DEC"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="O2">
+            <v>46200</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.20-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>5000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>6000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45427</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45425</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.20-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>5000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>6000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45436</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.20-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45226</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.22-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45432</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="G1">
+            <v>120</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45437</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.20-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>5000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>5950</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45444</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45450</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.22-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45446</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.22-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45473</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEc"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>3</v>
+          </cell>
+          <cell r="O1">
+            <v>19800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>14</v>
+          </cell>
+          <cell r="O2">
+            <v>4200</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45495</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEc"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45496</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45493</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanform1"/>
+      <sheetName val="loanform2"/>
+      <sheetName val="SM5000.1-SEPT (2)"/>
+    </sheetNames>
+    <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2">
@@ -1173,324 +2440,16 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45323</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.20-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>5000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>6000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45332</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.1-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>25</v>
-          </cell>
-          <cell r="O1">
-            <v>9500</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>95</v>
-          </cell>
-          <cell r="O2">
-            <v>2500</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45339</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.1-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>12000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45334</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.15-DEC"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>12</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45337</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.15-DEC"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.15-DEC"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45345</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>30000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>36000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45354</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.10-JAN"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>16</v>
-          </cell>
-          <cell r="O1">
-            <v>11200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>32</v>
-          </cell>
-          <cell r="O2">
-            <v>5600</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45366</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+            <v>45243</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1500,16 +2459,16 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
           </cell>
           <cell r="K1">
             <v>0</v>
           </cell>
           <cell r="O1">
-            <v>24000</v>
+            <v>12000</v>
           </cell>
         </row>
         <row r="2">
@@ -1518,939 +2477,6 @@
           </cell>
           <cell r="O2">
             <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45380</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.1-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>12000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45213</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.10-JAN"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>21</v>
-          </cell>
-          <cell r="O1">
-            <v>9450</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>27</v>
-          </cell>
-          <cell r="O2">
-            <v>7350</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45389</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.15-DEc"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="G1">
-            <v>17</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45394</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.10-JAN"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="G1">
-            <v>48</v>
-          </cell>
-          <cell r="O1">
-            <v>9100</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>26</v>
-          </cell>
-          <cell r="O2">
-            <v>7700</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45399</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.15-DEc"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="G1">
-            <v>17</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45406</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.20-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>5000</v>
-          </cell>
-          <cell r="G1">
-            <v>17</v>
-          </cell>
-          <cell r="O1">
-            <v>5950</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45406</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD50000.15-DEC"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>40000</v>
-          </cell>
-          <cell r="K1">
-            <v>47</v>
-          </cell>
-          <cell r="O1">
-            <v>1400</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45416</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD50000.15-DEC"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="O2">
-            <v>46200</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.20-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>5000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>6000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45427</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45425</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.20-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>5000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>6000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45436</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.20-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>12000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45226</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.22-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45432</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.1-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="G1">
-            <v>120</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>12000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45437</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.20-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>5000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>5950</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45444</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.1-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45450</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.1-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>12000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.22-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45446</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.22-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>12000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45473</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.15-DEc"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>4</v>
-          </cell>
-          <cell r="O1">
-            <v>18400</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>13</v>
-          </cell>
-          <cell r="O2">
-            <v>5600</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45495</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.15-DEc"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>4</v>
-          </cell>
-          <cell r="O1">
-            <v>9200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>13</v>
-          </cell>
-          <cell r="O2">
-            <v>2800</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45496</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45493</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanform1"/>
-      <sheetName val="loanform2"/>
-      <sheetName val="SM5000.1-SEPT (2)"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="1">
-          <cell r="C1">
-            <v>5000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>6000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>60</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45243</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.15-DEc"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>6</v>
-          </cell>
-          <cell r="O1">
-            <v>7800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>11</v>
-          </cell>
-          <cell r="O2">
-            <v>4200</v>
           </cell>
         </row>
         <row r="3">
@@ -2459,7 +2485,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2516,7 +2542,7 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
+      <sheetData sheetId="1" refreshError="1">
         <row r="1">
           <cell r="C1">
             <v>5000</v>
@@ -2595,25 +2621,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>58</v>
-          </cell>
-          <cell r="O1">
-            <v>6200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>62</v>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
           </cell>
           <cell r="O2">
-            <v>5800</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -2643,18 +2669,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
+            <v>8</v>
+          </cell>
+          <cell r="O1">
+            <v>12800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
             <v>9</v>
           </cell>
-          <cell r="O1">
-            <v>11400</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>8</v>
-          </cell>
           <cell r="O2">
-            <v>12600</v>
+            <v>11200</v>
           </cell>
         </row>
         <row r="3">
@@ -2726,18 +2752,18 @@
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>10</v>
-          </cell>
-          <cell r="O1">
-            <v>2500</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>7</v>
+            <v>9</v>
+          </cell>
+          <cell r="O1">
+            <v>2850</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>8</v>
           </cell>
           <cell r="O2">
-            <v>3500</v>
+            <v>3150</v>
           </cell>
         </row>
         <row r="3">
@@ -2767,18 +2793,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>10</v>
-          </cell>
-          <cell r="O1">
-            <v>5000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>7</v>
+            <v>9</v>
+          </cell>
+          <cell r="O1">
+            <v>5700</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>8</v>
           </cell>
           <cell r="O2">
-            <v>7000</v>
+            <v>6300</v>
           </cell>
         </row>
         <row r="3">
@@ -2888,18 +2914,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>76</v>
-          </cell>
-          <cell r="O1">
-            <v>8800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>44</v>
+            <v>74</v>
+          </cell>
+          <cell r="O1">
+            <v>9200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>46</v>
           </cell>
           <cell r="O2">
-            <v>15200</v>
+            <v>14800</v>
           </cell>
         </row>
         <row r="3">
@@ -2968,18 +2994,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>92</v>
-          </cell>
-          <cell r="O1">
-            <v>5600</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>28</v>
+            <v>89</v>
+          </cell>
+          <cell r="O1">
+            <v>6200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>31</v>
           </cell>
           <cell r="O2">
-            <v>18400</v>
+            <v>17800</v>
           </cell>
         </row>
         <row r="13">
@@ -3008,18 +3034,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>96</v>
-          </cell>
-          <cell r="O1">
-            <v>2400</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>24</v>
+            <v>94</v>
+          </cell>
+          <cell r="O1">
+            <v>2600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>26</v>
           </cell>
           <cell r="O2">
-            <v>9600</v>
+            <v>9400</v>
           </cell>
         </row>
         <row r="3">
@@ -3048,18 +3074,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>96</v>
-          </cell>
-          <cell r="O1">
-            <v>2400</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>24</v>
+            <v>94</v>
+          </cell>
+          <cell r="O1">
+            <v>2600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>26</v>
           </cell>
           <cell r="O2">
-            <v>9600</v>
+            <v>9400</v>
           </cell>
         </row>
         <row r="3">
@@ -3088,18 +3114,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>100</v>
-          </cell>
-          <cell r="O1">
-            <v>2000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>20</v>
+            <v>98</v>
+          </cell>
+          <cell r="O1">
+            <v>2200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>22</v>
           </cell>
           <cell r="O2">
-            <v>10000</v>
+            <v>9800</v>
           </cell>
         </row>
         <row r="3">
@@ -3128,18 +3154,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>101</v>
-          </cell>
-          <cell r="O1">
-            <v>3800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>19</v>
+            <v>99</v>
+          </cell>
+          <cell r="O1">
+            <v>4200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>21</v>
           </cell>
           <cell r="O2">
-            <v>20200</v>
+            <v>19800</v>
           </cell>
         </row>
         <row r="3">
@@ -3168,18 +3194,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>103</v>
-          </cell>
-          <cell r="O1">
-            <v>1700</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
+            <v>100</v>
+          </cell>
+          <cell r="O1">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>20</v>
           </cell>
           <cell r="O2">
-            <v>10300</v>
+            <v>10000</v>
           </cell>
         </row>
         <row r="3">
@@ -3208,18 +3234,18 @@
             <v>15000</v>
           </cell>
           <cell r="K1">
-            <v>113</v>
-          </cell>
-          <cell r="O1">
-            <v>1050</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>7</v>
+            <v>111</v>
+          </cell>
+          <cell r="O1">
+            <v>1350</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>9</v>
           </cell>
           <cell r="O2">
-            <v>16950</v>
+            <v>16650</v>
           </cell>
         </row>
         <row r="3">
@@ -3248,18 +3274,18 @@
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>117</v>
-          </cell>
-          <cell r="O1">
-            <v>1500</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>3</v>
+            <v>115</v>
+          </cell>
+          <cell r="O1">
+            <v>2500</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>5</v>
           </cell>
           <cell r="O2">
-            <v>58500</v>
+            <v>57500</v>
           </cell>
         </row>
         <row r="3">
@@ -3310,6 +3336,286 @@
         </row>
       </sheetData>
       <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>100000</v>
+          </cell>
+          <cell r="K1">
+            <v>40</v>
+          </cell>
+          <cell r="O1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>0</v>
+          </cell>
+          <cell r="O2">
+            <v>160000</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink71.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>50000</v>
+          </cell>
+          <cell r="K1">
+            <v>120</v>
+          </cell>
+          <cell r="O1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>0</v>
+          </cell>
+          <cell r="O2">
+            <v>60000</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink72.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>120</v>
+          </cell>
+          <cell r="O1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>0</v>
+          </cell>
+          <cell r="O2">
+            <v>24000</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink73.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>120</v>
+          </cell>
+          <cell r="O1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>0</v>
+          </cell>
+          <cell r="O2">
+            <v>24000</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink74.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>120</v>
+          </cell>
+          <cell r="O1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>0</v>
+          </cell>
+          <cell r="O2">
+            <v>24000</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink75.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>120</v>
+          </cell>
+          <cell r="O1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>0</v>
+          </cell>
+          <cell r="O2">
+            <v>24000</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink76.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>120</v>
+          </cell>
+          <cell r="O1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>0</v>
+          </cell>
+          <cell r="O2">
+            <v>12000</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink77.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>120</v>
+          </cell>
+          <cell r="O1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>0</v>
+          </cell>
+          <cell r="O2">
+            <v>12000</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3654,7 +3960,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3662,7 +3968,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:Q78"/>
+  <dimension ref="B2:Q89"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="1" customWidth="1"/>
@@ -3696,13 +4002,13 @@
       <c r="J2" s="22"/>
       <c r="K2" s="23"/>
       <c r="L2" s="19">
-        <f>SUM(L5:L86)</f>
-        <v>351800</v>
+        <f>SUM(L5:L97)</f>
+        <v>636150</v>
       </c>
       <c r="M2" s="20"/>
       <c r="N2" s="1">
-        <f>SUM(N5:N71)</f>
-        <v>27300</v>
+        <f>SUM(N5:N106)</f>
+        <v>36200</v>
       </c>
       <c r="Q2" s="1">
         <f>14900+260750</f>
@@ -4176,14 +4482,14 @@
       <c r="G15" s="9"/>
       <c r="H15" s="9">
         <f>'[10]MD50000.15-DEC'!$K$1</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I15" s="9">
         <f>'[10]MD50000.15-DEC'!$K$2</f>
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="K15" s="11">
         <f>'[10]MD50000.15-DEC'!$B$3</f>
@@ -4191,14 +4497,11 @@
       </c>
       <c r="L15" s="8">
         <f>'[10]MD50000.15-DEC'!$O$2</f>
-        <v>8750</v>
+        <v>0</v>
       </c>
       <c r="M15" s="8">
         <f>'[10]MD50000.15-DEC'!$O$1</f>
-        <v>75250</v>
-      </c>
-      <c r="N15" s="1">
-        <v>1750</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="16" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4296,14 +4599,14 @@
       <c r="G18" s="14"/>
       <c r="H18" s="14">
         <f>'[13]MD50000.15-DEC'!$K$1</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
         <f>'[13]MD50000.15-DEC'!$K$2</f>
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="K18" s="15">
         <f>'[13]MD50000.15-DEC'!$B$3</f>
@@ -4311,14 +4614,11 @@
       </c>
       <c r="L18" s="16">
         <f>'[13]MD50000.15-DEC'!$O$2</f>
-        <v>2450</v>
+        <v>0</v>
       </c>
       <c r="M18" s="16">
         <f>'[13]MD50000.15-DEC'!$O$1</f>
-        <v>14350</v>
-      </c>
-      <c r="N18" s="1">
-        <v>350</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="19" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4379,11 +4679,11 @@
       <c r="G20" s="14"/>
       <c r="H20" s="14">
         <f>'[15]MD10000.10-JAN'!$K$1</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I20" s="14">
         <f>'[15]MD10000.10-JAN'!$K$2</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J20" s="17" t="s">
         <v>12</v>
@@ -4394,11 +4694,11 @@
       </c>
       <c r="L20" s="16">
         <f>'[15]MD10000.10-JAN'!$O$2</f>
-        <v>3150</v>
+        <v>2800</v>
       </c>
       <c r="M20" s="16">
         <f>'[15]MD10000.10-JAN'!$O$1</f>
-        <v>13650</v>
+        <v>14000</v>
       </c>
       <c r="N20" s="1">
         <v>350</v>
@@ -4422,11 +4722,11 @@
       <c r="G21" s="9"/>
       <c r="H21" s="9">
         <f>'[16]MD10000.10-JAN'!$K$1</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I21" s="9">
         <f>'[16]MD10000.10-JAN'!$K$2</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J21" s="10" t="s">
         <v>12</v>
@@ -4437,11 +4737,11 @@
       </c>
       <c r="L21" s="8">
         <f>'[16]MD10000.10-JAN'!$O$2</f>
-        <v>3150</v>
+        <v>2800</v>
       </c>
       <c r="M21" s="8">
         <f>'[16]MD10000.10-JAN'!$O$1</f>
-        <v>13650</v>
+        <v>14000</v>
       </c>
       <c r="N21" s="1">
         <v>350</v>
@@ -4505,14 +4805,14 @@
       <c r="G23" s="9"/>
       <c r="H23" s="9">
         <f>'[18]MD10000.20-OCT'!$K$1</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I23" s="9">
         <f>'[18]MD10000.20-OCT'!$K$2</f>
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="K23" s="11">
         <f>'[18]MD10000.20-OCT'!$B$3</f>
@@ -4520,14 +4820,11 @@
       </c>
       <c r="L23" s="8">
         <f>'[18]MD10000.20-OCT'!$O$2</f>
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="M23" s="8">
         <f>'[18]MD10000.20-OCT'!$O$1</f>
-        <v>13300</v>
-      </c>
-      <c r="N23" s="1">
-        <v>350</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="24" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4548,14 +4845,14 @@
       <c r="G24" s="9"/>
       <c r="H24" s="9">
         <f>'[19]MD10000.20-OCT'!$K$1</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I24" s="9">
         <f>'[19]MD10000.20-OCT'!$K$2</f>
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="K24" s="11">
         <f>'[19]MD10000.20-OCT'!$B$3</f>
@@ -4563,14 +4860,11 @@
       </c>
       <c r="L24" s="8">
         <f>'[19]MD10000.20-OCT'!$O$2</f>
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="M24" s="8">
         <f>'[19]MD10000.20-OCT'!$O$1</f>
-        <v>12600</v>
-      </c>
-      <c r="N24" s="1">
-        <v>350</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="25" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4669,11 +4963,11 @@
       </c>
       <c r="F27" s="14">
         <f>'[22]MD10000.1-OCT'!$K$1</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G27" s="14">
         <f>'[22]MD10000.1-OCT'!$K$2</f>
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="H27" s="14"/>
       <c r="I27" s="14"/>
@@ -4686,11 +4980,11 @@
       </c>
       <c r="L27" s="16">
         <f>'[22]MD10000.1-OCT'!$O$2</f>
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="M27" s="16">
         <f>'[22]MD10000.1-OCT'!$O$1</f>
-        <v>9500</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="28" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4871,11 +5165,11 @@
       <c r="G32" s="14"/>
       <c r="H32" s="14">
         <f>'[28]MD10000.10-JAN'!$K$1</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I32" s="14">
         <f>'[28]MD10000.10-JAN'!$K$2</f>
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="J32" s="17" t="s">
         <v>12</v>
@@ -4886,14 +5180,11 @@
       </c>
       <c r="L32" s="16">
         <f>'[28]MD10000.10-JAN'!$O$2</f>
-        <v>5600</v>
+        <v>0</v>
       </c>
       <c r="M32" s="16">
         <f>'[28]MD10000.10-JAN'!$O$1</f>
-        <v>11200</v>
-      </c>
-      <c r="N32" s="1">
-        <v>350</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="33" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4954,11 +5245,11 @@
       <c r="G34" s="14"/>
       <c r="H34" s="14">
         <f>'[30]MD10000.10-JAN'!$K$1</f>
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I34" s="14">
         <f>'[30]MD10000.10-JAN'!$K$2</f>
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="J34" s="17" t="s">
         <v>12</v>
@@ -4969,14 +5260,11 @@
       </c>
       <c r="L34" s="16">
         <f>'[30]MD10000.10-JAN'!$O$2</f>
-        <v>7350</v>
+        <v>0</v>
       </c>
       <c r="M34" s="16">
         <f>'[30]MD10000.10-JAN'!$O$1</f>
-        <v>9450</v>
-      </c>
-      <c r="N34" s="1">
-        <v>350</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="35" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5041,7 +5329,7 @@
       </c>
       <c r="I36" s="14">
         <f>'[32]MD10000.10-JAN'!$K$2</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J36" s="17" t="s">
         <v>12</v>
@@ -5052,11 +5340,11 @@
       </c>
       <c r="L36" s="16">
         <f>'[32]MD10000.10-JAN'!$O$2</f>
-        <v>7700</v>
+        <v>7350</v>
       </c>
       <c r="M36" s="16">
         <f>'[32]MD10000.10-JAN'!$O$1</f>
-        <v>9100</v>
+        <v>9450</v>
       </c>
       <c r="N36" s="1">
         <v>350</v>
@@ -5560,11 +5848,11 @@
       <c r="G49" s="9"/>
       <c r="H49" s="9">
         <f>'[47]MD20000.15-DEc'!$K$1</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I49" s="9">
         <f>'[47]MD20000.15-DEc'!$K$2</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J49" s="10" t="s">
         <v>12</v>
@@ -5575,11 +5863,11 @@
       </c>
       <c r="L49" s="8">
         <f>'[47]MD20000.15-DEc'!$O$2</f>
-        <v>5600</v>
+        <v>4200</v>
       </c>
       <c r="M49" s="8">
         <f>'[47]MD20000.15-DEc'!$O$1</f>
-        <v>18400</v>
+        <v>19800</v>
       </c>
       <c r="N49" s="1">
         <v>1400</v>
@@ -5603,11 +5891,11 @@
       <c r="G50" s="9"/>
       <c r="H50" s="9">
         <f>'[48]MD20000.15-DEc'!$K$1</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I50" s="9">
         <f>'[48]MD20000.15-DEc'!$K$2</f>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J50" s="10" t="s">
         <v>12</v>
@@ -5618,14 +5906,11 @@
       </c>
       <c r="L50" s="8">
         <f>'[48]MD20000.15-DEc'!$O$2</f>
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="M50" s="8">
         <f>'[48]MD20000.15-DEc'!$O$1</f>
-        <v>9200</v>
-      </c>
-      <c r="N50" s="1">
-        <v>700</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="51" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5686,11 +5971,11 @@
       <c r="G52" s="9"/>
       <c r="H52" s="9">
         <f>'[50]MD20000.15-DEc'!$K$1</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I52" s="9">
         <f>'[50]MD20000.15-DEc'!$K$2</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J52" s="10" t="s">
         <v>12</v>
@@ -5701,14 +5986,11 @@
       </c>
       <c r="L52" s="8">
         <f>'[50]MD20000.15-DEc'!$O$2</f>
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="M52" s="8">
         <f>'[50]MD20000.15-DEc'!$O$1</f>
-        <v>7800</v>
-      </c>
-      <c r="N52" s="1">
-        <v>700</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5850,11 +6132,11 @@
       </c>
       <c r="F56" s="9">
         <f>'[54]MD20000.18-DEC'!$K$1</f>
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="G56" s="9">
         <f>'[54]MD20000.18-DEC'!$K$2</f>
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="H56" s="9"/>
       <c r="I56" s="9"/>
@@ -5867,14 +6149,11 @@
       </c>
       <c r="L56" s="8">
         <f>'[54]MD20000.18-DEC'!$O$2</f>
-        <v>5800</v>
+        <v>0</v>
       </c>
       <c r="M56" s="8">
         <f>'[54]MD20000.18-DEC'!$O$1</f>
-        <v>6200</v>
-      </c>
-      <c r="N56" s="1">
-        <v>700</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5895,11 +6174,11 @@
       <c r="G57" s="9"/>
       <c r="H57" s="9">
         <f>'[55]MD20000.15-DEc'!$K$1</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I57" s="9">
         <f>'[55]MD20000.15-DEc'!$K$2</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J57" s="10" t="s">
         <v>12</v>
@@ -5910,11 +6189,11 @@
       </c>
       <c r="L57" s="8">
         <f>'[55]MD20000.15-DEc'!$O$2</f>
-        <v>12600</v>
+        <v>11200</v>
       </c>
       <c r="M57" s="8">
         <f>'[55]MD20000.15-DEc'!$O$1</f>
-        <v>11400</v>
+        <v>12800</v>
       </c>
       <c r="N57" s="1">
         <v>1400</v>
@@ -5981,11 +6260,11 @@
       <c r="G59" s="9"/>
       <c r="H59" s="9">
         <f>'[57]MD10000.20-OCT'!$K$1</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I59" s="9">
         <f>'[57]MD10000.20-OCT'!$K$2</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J59" s="10" t="s">
         <v>12</v>
@@ -5996,11 +6275,11 @@
       </c>
       <c r="L59" s="8">
         <f>'[57]MD10000.20-OCT'!$O$2</f>
-        <v>3500</v>
+        <v>3150</v>
       </c>
       <c r="M59" s="8">
         <f>'[57]MD10000.20-OCT'!$O$1</f>
-        <v>2500</v>
+        <v>2850</v>
       </c>
       <c r="N59" s="1">
         <v>700</v>
@@ -6024,11 +6303,11 @@
       <c r="G60" s="9"/>
       <c r="H60" s="9">
         <f>'[58]MD20000.15-DEc'!$K$1</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I60" s="9">
         <f>'[58]MD20000.15-DEc'!$K$2</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J60" s="10" t="s">
         <v>12</v>
@@ -6039,11 +6318,11 @@
       </c>
       <c r="L60" s="8">
         <f>'[58]MD20000.15-DEc'!$O$2</f>
-        <v>7000</v>
+        <v>6300</v>
       </c>
       <c r="M60" s="8">
         <f>'[58]MD20000.15-DEc'!$O$1</f>
-        <v>5000</v>
+        <v>5700</v>
       </c>
       <c r="N60" s="1">
         <v>700</v>
@@ -6108,11 +6387,11 @@
       </c>
       <c r="F62" s="9">
         <f>'[60]MD20000.22-DEC'!$K$1</f>
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G62" s="9">
         <f>'[60]MD20000.22-DEC'!$K$2</f>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H62" s="9"/>
       <c r="I62" s="9"/>
@@ -6125,11 +6404,11 @@
       </c>
       <c r="L62" s="8">
         <f>'[60]MD20000.22-DEC'!$O$2</f>
-        <v>15200</v>
+        <v>14800</v>
       </c>
       <c r="M62" s="8">
         <f>'[60]MD20000.22-DEC'!$O$1</f>
-        <v>8800</v>
+        <v>9200</v>
       </c>
       <c r="N62" s="1">
         <v>1400</v>
@@ -6194,11 +6473,11 @@
       </c>
       <c r="F64" s="9">
         <f>'[62]MD20000.22-DEC'!$K$1</f>
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G64" s="9">
         <f>'[62]MD20000.22-DEC'!$K$2</f>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H64" s="9"/>
       <c r="I64" s="9"/>
@@ -6211,11 +6490,11 @@
       </c>
       <c r="L64" s="8">
         <f>'[62]MD20000.22-DEC'!$O$2</f>
-        <v>18400</v>
+        <v>17800</v>
       </c>
       <c r="M64" s="8">
         <f>'[62]MD20000.22-DEC'!$O$1</f>
-        <v>5600</v>
+        <v>6200</v>
       </c>
       <c r="N64" s="1">
         <v>1400</v>
@@ -6237,11 +6516,11 @@
       </c>
       <c r="F65" s="9">
         <f>'[63]MD10000.1-OCT'!$K$1</f>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G65" s="9">
         <f>'[63]MD10000.1-OCT'!$K$2</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H65" s="9"/>
       <c r="I65" s="9"/>
@@ -6254,11 +6533,11 @@
       </c>
       <c r="L65" s="8">
         <f>'[63]MD10000.1-OCT'!$O$2</f>
-        <v>9600</v>
+        <v>9400</v>
       </c>
       <c r="M65" s="8">
         <f>'[63]MD10000.1-OCT'!$O$1</f>
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="N65" s="1">
         <v>700</v>
@@ -6280,11 +6559,11 @@
       </c>
       <c r="F66" s="9">
         <f>'[64]MD10000.1-OCT'!$K$1</f>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G66" s="9">
         <f>'[64]MD10000.1-OCT'!$K$2</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H66" s="9"/>
       <c r="I66" s="9"/>
@@ -6297,11 +6576,11 @@
       </c>
       <c r="L66" s="8">
         <f>'[64]MD10000.1-OCT'!$O$2</f>
-        <v>9600</v>
+        <v>9400</v>
       </c>
       <c r="M66" s="8">
         <f>'[64]MD10000.1-OCT'!$O$1</f>
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="N66" s="1">
         <v>700</v>
@@ -6323,11 +6602,11 @@
       </c>
       <c r="F67" s="9">
         <f>'[65]MD10000.1-OCT'!$K$1</f>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G67" s="9">
         <f>'[65]MD10000.1-OCT'!$K$2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H67" s="9"/>
       <c r="I67" s="9"/>
@@ -6340,11 +6619,11 @@
       </c>
       <c r="L67" s="8">
         <f>'[65]MD10000.1-OCT'!$O$2</f>
-        <v>10000</v>
+        <v>9800</v>
       </c>
       <c r="M67" s="8">
         <f>'[65]MD10000.1-OCT'!$O$1</f>
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="N67" s="1">
         <v>700</v>
@@ -6366,11 +6645,11 @@
       </c>
       <c r="F68" s="9">
         <f>'[66]MD20000.18-DEC'!$K$1</f>
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G68" s="9">
         <f>'[66]MD20000.18-DEC'!$K$2</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H68" s="9"/>
       <c r="I68" s="9"/>
@@ -6383,11 +6662,11 @@
       </c>
       <c r="L68" s="8">
         <f>'[66]MD20000.18-DEC'!$O$2</f>
-        <v>20200</v>
+        <v>19800</v>
       </c>
       <c r="M68" s="8">
         <f>'[66]MD20000.18-DEC'!$O$1</f>
-        <v>3800</v>
+        <v>4200</v>
       </c>
       <c r="N68" s="1">
         <v>1400</v>
@@ -6409,11 +6688,11 @@
       </c>
       <c r="F69" s="9">
         <f>'[67]MD10000.1-OCT'!$K$1</f>
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G69" s="9">
         <f>'[67]MD10000.1-OCT'!$K$2</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H69" s="9"/>
       <c r="I69" s="9"/>
@@ -6426,11 +6705,11 @@
       </c>
       <c r="L69" s="8">
         <f>'[67]MD10000.1-OCT'!$O$2</f>
-        <v>10300</v>
+        <v>10000</v>
       </c>
       <c r="M69" s="8">
         <f>'[67]MD10000.1-OCT'!$O$1</f>
-        <v>1700</v>
+        <v>2000</v>
       </c>
       <c r="N69" s="1">
         <v>700</v>
@@ -6452,11 +6731,11 @@
       </c>
       <c r="F70" s="9">
         <f>'[68]MD10000.1-OCT'!$K$1</f>
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G70" s="9">
         <f>'[68]MD10000.1-OCT'!$K$2</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H70" s="9"/>
       <c r="I70" s="9"/>
@@ -6469,11 +6748,11 @@
       </c>
       <c r="L70" s="8">
         <f>'[68]MD10000.1-OCT'!$O$2</f>
-        <v>16950</v>
+        <v>16650</v>
       </c>
       <c r="M70" s="8">
         <f>'[68]MD10000.1-OCT'!$O$1</f>
-        <v>1050</v>
+        <v>1350</v>
       </c>
       <c r="N70" s="1">
         <v>1050</v>
@@ -6495,11 +6774,11 @@
       </c>
       <c r="F71" s="9">
         <f>'[69]MD20000.18-DEC'!$K$1</f>
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G71" s="9">
         <f>'[69]MD20000.18-DEC'!$K$2</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H71" s="9"/>
       <c r="I71" s="9"/>
@@ -6512,113 +6791,499 @@
       </c>
       <c r="L71" s="8">
         <f>'[69]MD20000.18-DEC'!$O$2</f>
-        <v>58500</v>
+        <v>57500</v>
       </c>
       <c r="M71" s="8">
         <f>'[69]MD20000.18-DEC'!$O$1</f>
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="N71" s="1">
         <v>3500</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="6"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="15"/>
-      <c r="E72" s="8"/>
+      <c r="B72" s="6">
+        <v>68</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D72" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="E72" s="8">
+        <f>'[70]MD20000.18-DEC'!$C$1</f>
+        <v>100000</v>
+      </c>
       <c r="F72" s="9"/>
       <c r="G72" s="9"/>
-      <c r="H72" s="9"/>
-      <c r="I72" s="9"/>
-      <c r="J72" s="10"/>
-      <c r="K72" s="11"/>
-      <c r="L72" s="8"/>
-      <c r="M72" s="8"/>
+      <c r="H72" s="9">
+        <f>'[70]MD20000.18-DEC'!$K$1</f>
+        <v>40</v>
+      </c>
+      <c r="I72" s="9">
+        <f>'[70]MD20000.18-DEC'!$K$2</f>
+        <v>0</v>
+      </c>
+      <c r="J72" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K72" s="11">
+        <f>'[70]MD20000.18-DEC'!$B$3</f>
+        <v>0</v>
+      </c>
+      <c r="L72" s="8">
+        <f>'[70]MD20000.18-DEC'!$O$2</f>
+        <v>160000</v>
+      </c>
+      <c r="M72" s="8">
+        <f>'[70]MD20000.18-DEC'!$O$1</f>
+        <v>0</v>
+      </c>
+      <c r="N72" s="1">
+        <v>4000</v>
+      </c>
     </row>
     <row r="73" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="6"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="15"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="9"/>
-      <c r="G73" s="9"/>
+      <c r="B73" s="6">
+        <v>69</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="D73" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="E73" s="8">
+        <f>'[71]MD20000.18-DEC'!$C$1</f>
+        <v>50000</v>
+      </c>
+      <c r="F73" s="9">
+        <f>'[71]MD20000.18-DEC'!$K$1</f>
+        <v>120</v>
+      </c>
+      <c r="G73" s="9">
+        <f>'[71]MD20000.18-DEC'!$K$2</f>
+        <v>0</v>
+      </c>
       <c r="H73" s="9"/>
       <c r="I73" s="9"/>
-      <c r="J73" s="10"/>
-      <c r="K73" s="11"/>
-      <c r="L73" s="8"/>
-      <c r="M73" s="8"/>
+      <c r="J73" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K73" s="11">
+        <f>'[71]MD20000.18-DEC'!$B$3</f>
+        <v>0</v>
+      </c>
+      <c r="L73" s="8">
+        <f>'[71]MD20000.18-DEC'!$O$2</f>
+        <v>60000</v>
+      </c>
+      <c r="M73" s="8">
+        <f>'[71]MD20000.18-DEC'!$O$1</f>
+        <v>0</v>
+      </c>
+      <c r="N73" s="1">
+        <v>3500</v>
+      </c>
     </row>
     <row r="74" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="6"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="15"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="9"/>
+      <c r="B74" s="6">
+        <v>70</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D74" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E74" s="8">
+        <f>'[72]MD20000.18-DEC'!$C$1</f>
+        <v>20000</v>
+      </c>
+      <c r="F74" s="9">
+        <f>'[72]MD20000.18-DEC'!$K$1</f>
+        <v>120</v>
+      </c>
+      <c r="G74" s="9">
+        <f>'[72]MD20000.18-DEC'!$K$2</f>
+        <v>0</v>
+      </c>
       <c r="H74" s="9"/>
       <c r="I74" s="9"/>
-      <c r="J74" s="10"/>
-      <c r="K74" s="11"/>
-      <c r="L74" s="8"/>
-      <c r="M74" s="8"/>
+      <c r="J74" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K74" s="11">
+        <f>'[72]MD20000.18-DEC'!$B$3</f>
+        <v>0</v>
+      </c>
+      <c r="L74" s="8">
+        <f>'[72]MD20000.18-DEC'!$O$2</f>
+        <v>24000</v>
+      </c>
+      <c r="M74" s="8">
+        <f>'[72]MD20000.18-DEC'!$O$1</f>
+        <v>0</v>
+      </c>
+      <c r="N74" s="1">
+        <v>1400</v>
+      </c>
     </row>
     <row r="75" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="6"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="15"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
+      <c r="B75" s="6">
+        <v>71</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="D75" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E75" s="8">
+        <f>'[73]MD20000.18-DEC'!$C$1</f>
+        <v>20000</v>
+      </c>
+      <c r="F75" s="9">
+        <f>'[73]MD20000.18-DEC'!$K$1</f>
+        <v>120</v>
+      </c>
+      <c r="G75" s="9">
+        <f>'[73]MD20000.18-DEC'!$K$2</f>
+        <v>0</v>
+      </c>
       <c r="H75" s="9"/>
       <c r="I75" s="9"/>
-      <c r="J75" s="10"/>
-      <c r="K75" s="11"/>
-      <c r="L75" s="8"/>
-      <c r="M75" s="8"/>
+      <c r="J75" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K75" s="11">
+        <f>'[73]MD20000.18-DEC'!$B$3</f>
+        <v>0</v>
+      </c>
+      <c r="L75" s="8">
+        <f>'[73]MD20000.18-DEC'!$O$2</f>
+        <v>24000</v>
+      </c>
+      <c r="M75" s="8">
+        <f>'[73]MD20000.18-DEC'!$O$1</f>
+        <v>0</v>
+      </c>
+      <c r="N75" s="1">
+        <v>1400</v>
+      </c>
     </row>
     <row r="76" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="6"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="15"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="9"/>
-      <c r="G76" s="9"/>
+      <c r="B76" s="6">
+        <v>72</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D76" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E76" s="8">
+        <f>'[74]MD20000.18-DEC'!$C$1</f>
+        <v>20000</v>
+      </c>
+      <c r="F76" s="9">
+        <f>'[74]MD20000.18-DEC'!$K$1</f>
+        <v>120</v>
+      </c>
+      <c r="G76" s="9">
+        <f>'[74]MD20000.18-DEC'!$K$2</f>
+        <v>0</v>
+      </c>
       <c r="H76" s="9"/>
       <c r="I76" s="9"/>
-      <c r="J76" s="10"/>
-      <c r="K76" s="11"/>
-      <c r="L76" s="8"/>
-      <c r="M76" s="8"/>
+      <c r="J76" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K76" s="11">
+        <f>'[74]MD20000.18-DEC'!$B$3</f>
+        <v>0</v>
+      </c>
+      <c r="L76" s="8">
+        <f>'[74]MD20000.18-DEC'!$O$2</f>
+        <v>24000</v>
+      </c>
+      <c r="M76" s="8">
+        <f>'[74]MD20000.18-DEC'!$O$1</f>
+        <v>0</v>
+      </c>
+      <c r="N76" s="1">
+        <v>1400</v>
+      </c>
     </row>
     <row r="77" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B77" s="6"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="15"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="9"/>
-      <c r="G77" s="9"/>
+      <c r="B77" s="6">
+        <v>73</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D77" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E77" s="8">
+        <f>'[75]MD20000.18-DEC'!$C$1</f>
+        <v>20000</v>
+      </c>
+      <c r="F77" s="9">
+        <f>'[75]MD20000.18-DEC'!$K$1</f>
+        <v>120</v>
+      </c>
+      <c r="G77" s="9">
+        <f>'[75]MD20000.18-DEC'!$K$2</f>
+        <v>0</v>
+      </c>
       <c r="H77" s="9"/>
       <c r="I77" s="9"/>
-      <c r="J77" s="10"/>
-      <c r="K77" s="11"/>
-      <c r="L77" s="8"/>
-      <c r="M77" s="8"/>
+      <c r="J77" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K77" s="11">
+        <f>'[75]MD20000.18-DEC'!$B$3</f>
+        <v>0</v>
+      </c>
+      <c r="L77" s="8">
+        <f>'[75]MD20000.18-DEC'!$O$2</f>
+        <v>24000</v>
+      </c>
+      <c r="M77" s="8">
+        <f>'[75]MD20000.18-DEC'!$O$1</f>
+        <v>0</v>
+      </c>
+      <c r="N77" s="1">
+        <v>1400</v>
+      </c>
     </row>
     <row r="78" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="6"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="15"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="9"/>
+      <c r="B78" s="6">
+        <v>74</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D78" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E78" s="8">
+        <f>'[76]MD20000.18-DEC'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F78" s="9">
+        <f>'[76]MD20000.18-DEC'!$K$1</f>
+        <v>120</v>
+      </c>
+      <c r="G78" s="9">
+        <f>'[76]MD20000.18-DEC'!$K$2</f>
+        <v>0</v>
+      </c>
       <c r="H78" s="9"/>
       <c r="I78" s="9"/>
-      <c r="J78" s="10"/>
-      <c r="K78" s="11"/>
-      <c r="L78" s="8"/>
-      <c r="M78" s="8"/>
+      <c r="J78" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K78" s="11">
+        <f>'[76]MD20000.18-DEC'!$B$3</f>
+        <v>0</v>
+      </c>
+      <c r="L78" s="8">
+        <f>'[76]MD20000.18-DEC'!$O$2</f>
+        <v>12000</v>
+      </c>
+      <c r="M78" s="8">
+        <f>'[76]MD20000.18-DEC'!$O$1</f>
+        <v>0</v>
+      </c>
+      <c r="N78" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B79" s="6">
+        <v>75</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E79" s="8">
+        <f>'[77]MD20000.18-DEC'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F79" s="9">
+        <f>'[77]MD20000.18-DEC'!$K$1</f>
+        <v>120</v>
+      </c>
+      <c r="G79" s="9">
+        <f>'[77]MD20000.18-DEC'!$K$2</f>
+        <v>0</v>
+      </c>
+      <c r="H79" s="9"/>
+      <c r="I79" s="9"/>
+      <c r="J79" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K79" s="11">
+        <f>'[77]MD20000.18-DEC'!$B$3</f>
+        <v>0</v>
+      </c>
+      <c r="L79" s="8">
+        <f>'[77]MD20000.18-DEC'!$O$2</f>
+        <v>12000</v>
+      </c>
+      <c r="M79" s="8">
+        <f>'[77]MD20000.18-DEC'!$O$1</f>
+        <v>0</v>
+      </c>
+      <c r="N79" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="80" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B80" s="6"/>
+      <c r="C80" s="9"/>
+      <c r="D80" s="15"/>
+      <c r="E80" s="8"/>
+      <c r="F80" s="9"/>
+      <c r="G80" s="9"/>
+      <c r="H80" s="9"/>
+      <c r="I80" s="9"/>
+      <c r="J80" s="10"/>
+      <c r="K80" s="11"/>
+      <c r="L80" s="8"/>
+      <c r="M80" s="8"/>
+    </row>
+    <row r="81" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B81" s="6"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="15"/>
+      <c r="E81" s="8"/>
+      <c r="F81" s="9"/>
+      <c r="G81" s="9"/>
+      <c r="H81" s="9"/>
+      <c r="I81" s="9"/>
+      <c r="J81" s="10"/>
+      <c r="K81" s="11"/>
+      <c r="L81" s="8"/>
+      <c r="M81" s="8"/>
+    </row>
+    <row r="82" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B82" s="6"/>
+      <c r="C82" s="9"/>
+      <c r="D82" s="15"/>
+      <c r="E82" s="8"/>
+      <c r="F82" s="9"/>
+      <c r="G82" s="9"/>
+      <c r="H82" s="9"/>
+      <c r="I82" s="9"/>
+      <c r="J82" s="10"/>
+      <c r="K82" s="11"/>
+      <c r="L82" s="8"/>
+      <c r="M82" s="8"/>
+    </row>
+    <row r="83" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B83" s="6"/>
+      <c r="C83" s="9"/>
+      <c r="D83" s="15"/>
+      <c r="E83" s="8"/>
+      <c r="F83" s="9"/>
+      <c r="G83" s="9"/>
+      <c r="H83" s="9"/>
+      <c r="I83" s="9"/>
+      <c r="J83" s="10"/>
+      <c r="K83" s="11"/>
+      <c r="L83" s="8"/>
+      <c r="M83" s="8"/>
+    </row>
+    <row r="84" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B84" s="6"/>
+      <c r="C84" s="9"/>
+      <c r="D84" s="15"/>
+      <c r="E84" s="8"/>
+      <c r="F84" s="9"/>
+      <c r="G84" s="9"/>
+      <c r="H84" s="9"/>
+      <c r="I84" s="9"/>
+      <c r="J84" s="10"/>
+      <c r="K84" s="11"/>
+      <c r="L84" s="8"/>
+      <c r="M84" s="8"/>
+    </row>
+    <row r="85" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B85" s="6"/>
+      <c r="C85" s="9"/>
+      <c r="D85" s="15"/>
+      <c r="E85" s="8"/>
+      <c r="F85" s="9"/>
+      <c r="G85" s="9"/>
+      <c r="H85" s="9"/>
+      <c r="I85" s="9"/>
+      <c r="J85" s="10"/>
+      <c r="K85" s="11"/>
+      <c r="L85" s="8"/>
+      <c r="M85" s="8"/>
+    </row>
+    <row r="86" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B86" s="6"/>
+      <c r="C86" s="9"/>
+      <c r="D86" s="15"/>
+      <c r="E86" s="8"/>
+      <c r="F86" s="9"/>
+      <c r="G86" s="9"/>
+      <c r="H86" s="9"/>
+      <c r="I86" s="9"/>
+      <c r="J86" s="10"/>
+      <c r="K86" s="11"/>
+      <c r="L86" s="8"/>
+      <c r="M86" s="8"/>
+    </row>
+    <row r="87" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B87" s="6"/>
+      <c r="C87" s="9"/>
+      <c r="D87" s="15"/>
+      <c r="E87" s="8"/>
+      <c r="F87" s="9"/>
+      <c r="G87" s="9"/>
+      <c r="H87" s="9"/>
+      <c r="I87" s="9"/>
+      <c r="J87" s="10"/>
+      <c r="K87" s="11"/>
+      <c r="L87" s="8"/>
+      <c r="M87" s="8"/>
+    </row>
+    <row r="88" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B88" s="6"/>
+      <c r="C88" s="9"/>
+      <c r="D88" s="15"/>
+      <c r="E88" s="8"/>
+      <c r="F88" s="9"/>
+      <c r="G88" s="9"/>
+      <c r="H88" s="9"/>
+      <c r="I88" s="9"/>
+      <c r="J88" s="10"/>
+      <c r="K88" s="11"/>
+      <c r="L88" s="8"/>
+      <c r="M88" s="8"/>
+    </row>
+    <row r="89" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B89" s="6"/>
+      <c r="C89" s="9"/>
+      <c r="D89" s="15"/>
+      <c r="E89" s="8"/>
+      <c r="F89" s="9"/>
+      <c r="G89" s="9"/>
+      <c r="H89" s="9"/>
+      <c r="I89" s="9"/>
+      <c r="J89" s="10"/>
+      <c r="K89" s="11"/>
+      <c r="L89" s="8"/>
+      <c r="M89" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/LoanOfficer-A/LoanBook.xlsx
+++ b/LoanOfficer-A/LoanBook.xlsx
@@ -87,13 +87,18 @@
     <externalReference r:id="rId76"/>
     <externalReference r:id="rId77"/>
     <externalReference r:id="rId78"/>
+    <externalReference r:id="rId79"/>
+    <externalReference r:id="rId80"/>
+    <externalReference r:id="rId81"/>
+    <externalReference r:id="rId82"/>
+    <externalReference r:id="rId83"/>
   </externalReferences>
   <calcPr calcId="145621" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="109">
   <si>
     <t>Code</t>
   </si>
@@ -402,6 +407,24 @@
   </si>
   <si>
     <t>Sanatombi</t>
+  </si>
+  <si>
+    <t>huirem sunamani</t>
+  </si>
+  <si>
+    <t>bijenti</t>
+  </si>
+  <si>
+    <t>Bidyapati</t>
+  </si>
+  <si>
+    <t>L20000W 17 1400 Wed</t>
+  </si>
+  <si>
+    <t>Thasana</t>
+  </si>
+  <si>
+    <t>Haobijam joyshree</t>
   </si>
 </sst>
 </file>
@@ -449,7 +472,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -477,6 +500,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF009999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -546,7 +575,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -562,9 +591,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -597,7 +623,6 @@
     <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -617,6 +642,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -929,25 +972,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>8</v>
-          </cell>
-          <cell r="O1">
-            <v>14000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>40</v>
+            <v>5</v>
+          </cell>
+          <cell r="O1">
+            <v>15050</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>43</v>
           </cell>
           <cell r="O2">
-            <v>2800</v>
+            <v>1750</v>
           </cell>
         </row>
         <row r="3">
@@ -956,7 +999,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -971,25 +1014,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>8</v>
-          </cell>
-          <cell r="O1">
-            <v>14000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>40</v>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>16800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>48</v>
           </cell>
           <cell r="O2">
-            <v>2800</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -998,7 +1041,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1691,7 +1734,7 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -1701,15 +1744,15 @@
             <v>48</v>
           </cell>
           <cell r="O1">
-            <v>9450</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>27</v>
+            <v>10500</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>30</v>
           </cell>
           <cell r="O2">
-            <v>7350</v>
+            <v>6300</v>
           </cell>
         </row>
         <row r="3">
@@ -1718,7 +1761,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2292,25 +2335,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>3</v>
-          </cell>
-          <cell r="O1">
-            <v>19800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>14</v>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>4200</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -2319,7 +2362,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2581,25 +2624,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>30000</v>
           </cell>
           <cell r="K1">
-            <v>47</v>
-          </cell>
-          <cell r="O1">
-            <v>21900</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>73</v>
+            <v>24</v>
+          </cell>
+          <cell r="O1">
+            <v>28800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>96</v>
           </cell>
           <cell r="O2">
-            <v>14100</v>
+            <v>7200</v>
           </cell>
         </row>
         <row r="3">
@@ -2662,25 +2705,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>8</v>
-          </cell>
-          <cell r="O1">
-            <v>12800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>9</v>
+            <v>6</v>
+          </cell>
+          <cell r="O1">
+            <v>15600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>11</v>
           </cell>
           <cell r="O2">
-            <v>11200</v>
+            <v>8400</v>
           </cell>
         </row>
         <row r="3">
@@ -2689,7 +2732,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2704,25 +2747,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
+            <v>7</v>
+          </cell>
+          <cell r="O1">
+            <v>7100</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
             <v>10</v>
           </cell>
-          <cell r="O1">
-            <v>5000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>7</v>
-          </cell>
           <cell r="O2">
-            <v>7000</v>
+            <v>4900</v>
           </cell>
         </row>
         <row r="3">
@@ -2731,7 +2774,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2745,25 +2788,25 @@
       <sheetName val="MD10000.20-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>9</v>
-          </cell>
-          <cell r="O1">
-            <v>2850</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>8</v>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>6000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>3150</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -2786,25 +2829,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>9</v>
-          </cell>
-          <cell r="O1">
-            <v>5700</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>8</v>
+            <v>7</v>
+          </cell>
+          <cell r="O1">
+            <v>7100</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>10</v>
           </cell>
           <cell r="O2">
-            <v>6300</v>
+            <v>4900</v>
           </cell>
         </row>
         <row r="3">
@@ -2813,7 +2856,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2827,25 +2870,25 @@
       <sheetName val="MD10000.20-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>10</v>
-          </cell>
-          <cell r="O1">
-            <v>2500</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>7</v>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>6000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>3500</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -2907,25 +2950,25 @@
       <sheetName val="MD20000.22-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>74</v>
-          </cell>
-          <cell r="O1">
-            <v>9200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>46</v>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
           </cell>
           <cell r="O2">
-            <v>14800</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -2947,25 +2990,25 @@
       <sheetName val="MD10000.20-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>5000</v>
           </cell>
           <cell r="K1">
-            <v>12</v>
-          </cell>
-          <cell r="O1">
-            <v>1800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>5</v>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>6000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>4200</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -2987,25 +3030,25 @@
       <sheetName val="MD20000.22-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>89</v>
-          </cell>
-          <cell r="O1">
-            <v>6200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>31</v>
+            <v>72</v>
+          </cell>
+          <cell r="O1">
+            <v>9600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>48</v>
           </cell>
           <cell r="O2">
-            <v>17800</v>
+            <v>14400</v>
           </cell>
         </row>
         <row r="13">
@@ -3027,25 +3070,25 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>94</v>
-          </cell>
-          <cell r="O1">
-            <v>2600</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>26</v>
+            <v>77</v>
+          </cell>
+          <cell r="O1">
+            <v>4300</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>43</v>
           </cell>
           <cell r="O2">
-            <v>9400</v>
+            <v>7700</v>
           </cell>
         </row>
         <row r="3">
@@ -3067,25 +3110,25 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>94</v>
-          </cell>
-          <cell r="O1">
-            <v>2600</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>26</v>
+            <v>78</v>
+          </cell>
+          <cell r="O1">
+            <v>4200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>42</v>
           </cell>
           <cell r="O2">
-            <v>9400</v>
+            <v>7800</v>
           </cell>
         </row>
         <row r="3">
@@ -3107,25 +3150,25 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>98</v>
-          </cell>
-          <cell r="O1">
-            <v>2200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>22</v>
+            <v>82</v>
+          </cell>
+          <cell r="O1">
+            <v>3800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>38</v>
           </cell>
           <cell r="O2">
-            <v>9800</v>
+            <v>8200</v>
           </cell>
         </row>
         <row r="3">
@@ -3147,25 +3190,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>99</v>
-          </cell>
-          <cell r="O1">
-            <v>4200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>21</v>
+            <v>82</v>
+          </cell>
+          <cell r="O1">
+            <v>7600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>38</v>
           </cell>
           <cell r="O2">
-            <v>19800</v>
+            <v>16400</v>
           </cell>
         </row>
         <row r="3">
@@ -3187,25 +3230,25 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>100</v>
-          </cell>
-          <cell r="O1">
-            <v>2000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>20</v>
+            <v>82</v>
+          </cell>
+          <cell r="O1">
+            <v>3800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>38</v>
           </cell>
           <cell r="O2">
-            <v>10000</v>
+            <v>8200</v>
           </cell>
         </row>
         <row r="3">
@@ -3227,25 +3270,25 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>15000</v>
           </cell>
           <cell r="K1">
-            <v>111</v>
-          </cell>
-          <cell r="O1">
-            <v>1350</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>9</v>
+            <v>103</v>
+          </cell>
+          <cell r="O1">
+            <v>2550</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>16650</v>
+            <v>15450</v>
           </cell>
         </row>
         <row r="3">
@@ -3267,25 +3310,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>115</v>
-          </cell>
-          <cell r="O1">
-            <v>2500</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>5</v>
+            <v>96</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>24</v>
           </cell>
           <cell r="O2">
-            <v>57500</v>
+            <v>48000</v>
           </cell>
         </row>
         <row r="3">
@@ -3349,25 +3392,30 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>100000</v>
           </cell>
           <cell r="K1">
-            <v>40</v>
-          </cell>
-          <cell r="O1">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>0</v>
+            <v>38</v>
+          </cell>
+          <cell r="O1">
+            <v>8000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>2</v>
           </cell>
           <cell r="O2">
-            <v>160000</v>
+            <v>152000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45590</v>
           </cell>
         </row>
       </sheetData>
@@ -3384,25 +3432,30 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>120</v>
-          </cell>
-          <cell r="O1">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>0</v>
+            <v>103</v>
+          </cell>
+          <cell r="O1">
+            <v>8500</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>60000</v>
+            <v>51500</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45584</v>
           </cell>
         </row>
       </sheetData>
@@ -3419,25 +3472,30 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>120</v>
-          </cell>
-          <cell r="O1">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>0</v>
+            <v>103</v>
+          </cell>
+          <cell r="O1">
+            <v>3400</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>24000</v>
+            <v>20600</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45584</v>
           </cell>
         </row>
       </sheetData>
@@ -3454,25 +3512,30 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>120</v>
-          </cell>
-          <cell r="O1">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>0</v>
+            <v>102</v>
+          </cell>
+          <cell r="O1">
+            <v>3600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>18</v>
           </cell>
           <cell r="O2">
-            <v>24000</v>
+            <v>20400</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45584</v>
           </cell>
         </row>
       </sheetData>
@@ -3489,25 +3552,30 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>120</v>
-          </cell>
-          <cell r="O1">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>0</v>
+            <v>103</v>
+          </cell>
+          <cell r="O1">
+            <v>3400</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>24000</v>
+            <v>20600</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45584</v>
           </cell>
         </row>
       </sheetData>
@@ -3524,25 +3592,30 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>120</v>
-          </cell>
-          <cell r="O1">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>0</v>
+            <v>106</v>
+          </cell>
+          <cell r="O1">
+            <v>2800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>14</v>
           </cell>
           <cell r="O2">
-            <v>24000</v>
+            <v>21200</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7">
+            <v>45587</v>
           </cell>
         </row>
       </sheetData>
@@ -3559,25 +3632,30 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>120</v>
-          </cell>
-          <cell r="O1">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>0</v>
+            <v>110</v>
+          </cell>
+          <cell r="O1">
+            <v>1000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>10</v>
           </cell>
           <cell r="O2">
-            <v>12000</v>
+            <v>11000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45584</v>
           </cell>
         </row>
       </sheetData>
@@ -3594,28 +3672,113 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>120</v>
-          </cell>
-          <cell r="O1">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>0</v>
+            <v>101</v>
+          </cell>
+          <cell r="O1">
+            <v>1900</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>19</v>
           </cell>
           <cell r="O2">
-            <v>12000</v>
-          </cell>
-        </row>
-      </sheetData>
+            <v>10100</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45584</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink78.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>106</v>
+          </cell>
+          <cell r="O1">
+            <v>1400</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>14</v>
+          </cell>
+          <cell r="O2">
+            <v>10600</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45587</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink79.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEc"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>16</v>
+          </cell>
+          <cell r="O1">
+            <v>1600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>1</v>
+          </cell>
+          <cell r="O2">
+            <v>22400</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45595</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3658,6 +3821,128 @@
         </row>
       </sheetData>
       <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink80.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.10-JAN"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>16</v>
+          </cell>
+          <cell r="O1">
+            <v>1600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>1</v>
+          </cell>
+          <cell r="O2">
+            <v>22400</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45571</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink81.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.22-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>116</v>
+          </cell>
+          <cell r="O1">
+            <v>800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>4</v>
+          </cell>
+          <cell r="O2">
+            <v>23200</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45597</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink82.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>30000</v>
+          </cell>
+          <cell r="K1">
+            <v>119</v>
+          </cell>
+          <cell r="O1">
+            <v>300</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>1</v>
+          </cell>
+          <cell r="O2">
+            <v>35700</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45602</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3992,23 +4277,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="25"/>
-      <c r="I2" s="21" t="s">
+      <c r="C2" s="23"/>
+      <c r="I2" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="22"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="19">
+      <c r="J2" s="20"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="17">
         <f>SUM(L5:L97)</f>
-        <v>636150</v>
-      </c>
-      <c r="M2" s="20"/>
+        <v>645700</v>
+      </c>
+      <c r="M2" s="18"/>
       <c r="N2" s="1">
         <f>SUM(N5:N106)</f>
-        <v>36200</v>
+        <v>38650</v>
       </c>
       <c r="Q2" s="1">
         <f>14900+260750</f>
@@ -4026,1406 +4311,1402 @@
       <c r="M3" s="3"/>
     </row>
     <row r="4" spans="2:17" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="12" t="s">
+      <c r="D4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="12" t="s">
+      <c r="L4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="M4" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="6">
+      <c r="B5" s="24">
         <v>1</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="26">
         <f>'[1]SM5000.1-SEPT'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="27">
         <f>'[1]SM5000.1-SEPT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="27">
         <f>'[1]SM5000.1-SEPT'!$K$2</f>
         <v>60</v>
       </c>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="10" t="s">
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="K5" s="11">
+      <c r="K5" s="29">
         <f>'[1]SM5000.1-SEPT'!$B$3</f>
         <v>45180</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="26">
         <f>'[1]SM5000.1-SEPT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M5" s="8">
+      <c r="M5" s="26">
         <f>'[1]SM5000.1-SEPT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
     <row r="6" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="13">
+      <c r="B6" s="24">
         <v>2</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="26">
         <f>'[1]SM5000.1-oct'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="27">
         <f>'[1]SM5000.1-oct'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="27">
         <f>'[1]SM5000.1-oct'!$K$2</f>
         <v>60</v>
       </c>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="17" t="s">
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="K6" s="15">
+      <c r="K6" s="29">
         <f>'[1]SM5000.1-oct'!$B$3</f>
         <v>45201</v>
       </c>
-      <c r="L6" s="16">
+      <c r="L6" s="26">
         <f>'[1]SM5000.1-oct'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M6" s="16">
+      <c r="M6" s="26">
         <f>'[1]SM5000.1-oct'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
     <row r="7" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="6">
+      <c r="B7" s="24">
         <v>3</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="26">
         <f>'[2]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="27">
         <f>'[2]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="27">
         <f>'[2]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="10" t="s">
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="11">
+      <c r="K7" s="29">
         <f>'[2]MD10000.1-OCT'!$B$3</f>
         <v>45212</v>
       </c>
-      <c r="L7" s="8">
+      <c r="L7" s="26">
         <f>'[2]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M7" s="8">
+      <c r="M7" s="26">
         <f>'[2]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
     <row r="8" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="13">
+      <c r="B8" s="24">
         <v>4</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="26">
         <f>'[3]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="27">
         <f>'[3]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="27">
         <f>'[3]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="17" t="s">
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="15">
+      <c r="K8" s="29">
         <f>'[3]MD10000.1-OCT'!$B$3</f>
         <v>45213</v>
       </c>
-      <c r="L8" s="16">
+      <c r="L8" s="26">
         <f>'[3]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M8" s="16">
+      <c r="M8" s="26">
         <f>'[3]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
     <row r="9" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="6">
+      <c r="B9" s="24">
         <v>5</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="26">
         <f>'[4]MD10000.20-OCT'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9">
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27">
         <f>'[4]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="27">
         <f>'[4]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J9" s="10" t="s">
+      <c r="J9" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="K9" s="11">
+      <c r="K9" s="29">
         <f>'[4]MD10000.20-OCT'!$B$3</f>
         <v>45226</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="26">
         <f>'[4]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M9" s="8">
+      <c r="M9" s="26">
         <f>'[4]MD10000.20-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
     <row r="10" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="13">
+      <c r="B10" s="24">
         <v>6</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="26">
         <f>'[5]SM5000.1-SEPT (2)'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="27">
         <f>'[5]SM5000.1-SEPT (2)'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="27">
         <f>'[5]SM5000.1-SEPT (2)'!$K$2</f>
         <v>60</v>
       </c>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="10" t="s">
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="29">
         <f>'[5]SM5000.1-SEPT (2)'!$B$3</f>
         <v>45243</v>
       </c>
-      <c r="L10" s="16">
+      <c r="L10" s="26">
         <f>'[5]SM5000.1-SEPT (2)'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M10" s="16">
+      <c r="M10" s="26">
         <f>'[5]SM5000.1-SEPT (2)'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
     <row r="11" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="6">
+      <c r="B11" s="24">
         <v>7</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="26">
         <f>'[6]MD10000.20-OCT'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9">
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27">
         <f>'[6]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="27">
         <f>'[6]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J11" s="10" t="s">
+      <c r="J11" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="K11" s="11">
+      <c r="K11" s="29">
         <f>'[6]MD10000.20-OCT'!$B$3</f>
         <v>45245</v>
       </c>
-      <c r="L11" s="8">
+      <c r="L11" s="26">
         <f>'[6]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M11" s="8">
+      <c r="M11" s="26">
         <f>'[6]MD10000.20-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
     <row r="12" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="13">
+      <c r="B12" s="24">
         <v>8</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="26">
         <f>'[7]MD15000.27-NOV'!$C$1</f>
         <v>15000</v>
       </c>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14">
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27">
         <f>'[7]MD15000.27-NOV'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="27">
         <f>'[7]MD15000.27-NOV'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J12" s="17" t="s">
+      <c r="J12" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="K12" s="15">
+      <c r="K12" s="29">
         <f>'[7]MD15000.27-NOV'!$B$3</f>
         <v>45266</v>
       </c>
-      <c r="L12" s="16">
+      <c r="L12" s="26">
         <f>'[7]MD15000.27-NOV'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M12" s="16">
+      <c r="M12" s="26">
         <f>'[7]MD15000.27-NOV'!$O$1</f>
         <v>18000</v>
       </c>
     </row>
     <row r="13" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="6">
+      <c r="B13" s="24">
         <v>9</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="26">
         <f>'[8]MD20000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9">
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27">
         <f>'[8]MD20000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="27">
         <f>'[8]MD20000.15-DEC'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J13" s="10" t="s">
+      <c r="J13" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="K13" s="11">
+      <c r="K13" s="29">
         <f>'[8]MD20000.15-DEC'!$B$3</f>
         <v>45649</v>
       </c>
-      <c r="L13" s="8">
+      <c r="L13" s="26">
         <f>'[8]MD20000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M13" s="8">
+      <c r="M13" s="26">
         <f>'[8]MD20000.15-DEC'!$O$1</f>
         <v>24000</v>
       </c>
-      <c r="Q13" s="18"/>
     </row>
     <row r="14" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="13">
+      <c r="B14" s="24">
         <v>10</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="26">
         <f>'[9]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14">
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27">
         <f>'[9]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="27">
         <f>'[9]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J14" s="17" t="s">
+      <c r="J14" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="K14" s="15">
+      <c r="K14" s="29">
         <f>'[9]MD20000.15-DEc'!$B$3</f>
         <v>45646</v>
       </c>
-      <c r="L14" s="16">
+      <c r="L14" s="26">
         <f>'[9]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M14" s="16">
+      <c r="M14" s="26">
         <f>'[9]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
     <row r="15" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="6">
+      <c r="B15" s="24">
         <v>11</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="26">
         <f>'[10]MD50000.15-DEC'!$C$1</f>
         <v>50000</v>
       </c>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9">
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27">
         <f>'[10]MD50000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="27">
         <f>'[10]MD50000.15-DEC'!$K$2</f>
         <v>48</v>
       </c>
-      <c r="J15" s="10" t="s">
+      <c r="J15" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="K15" s="11">
+      <c r="K15" s="29">
         <f>'[10]MD50000.15-DEC'!$B$3</f>
         <v>45648</v>
       </c>
-      <c r="L15" s="8">
+      <c r="L15" s="26">
         <f>'[10]MD50000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M15" s="8">
+      <c r="M15" s="26">
         <f>'[10]MD50000.15-DEC'!$O$1</f>
         <v>84000</v>
       </c>
     </row>
     <row r="16" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="13">
+      <c r="B16" s="24">
         <v>12</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="26">
         <f>'[11]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="27">
         <f>'[11]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="27">
         <f>'[11]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="17" t="s">
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="K16" s="15">
+      <c r="K16" s="29">
         <f>'[11]MD20000.18-DEC'!$B$3</f>
         <v>45279</v>
       </c>
-      <c r="L16" s="16">
+      <c r="L16" s="26">
         <f>'[11]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M16" s="16">
+      <c r="M16" s="26">
         <f>'[11]MD20000.18-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
     <row r="17" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="6">
+      <c r="B17" s="24">
         <v>13</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="26">
         <f>'[12]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="27">
         <f>'[12]MD20000.22-DEC'!$K$1</f>
         <v>120</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="27">
         <f>'[12]MD20000.22-DEC'!$K$2</f>
         <v>0</v>
       </c>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="10" t="s">
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="K17" s="11">
+      <c r="K17" s="29">
         <f>'[12]MD20000.22-DEC'!$B$3</f>
         <v>0</v>
       </c>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8">
+      <c r="L17" s="26"/>
+      <c r="M17" s="26">
         <f>'[12]MD20000.22-DEC'!$O$1</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="13">
+      <c r="B18" s="24">
         <v>14</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="26">
         <f>'[13]MD50000.15-DEC'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14">
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27">
         <f>'[13]MD50000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I18" s="14">
+      <c r="I18" s="27">
         <f>'[13]MD50000.15-DEC'!$K$2</f>
         <v>48</v>
       </c>
-      <c r="J18" s="17" t="s">
+      <c r="J18" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="K18" s="15">
+      <c r="K18" s="29">
         <f>'[13]MD50000.15-DEC'!$B$3</f>
         <v>45310</v>
       </c>
-      <c r="L18" s="16">
+      <c r="L18" s="26">
         <f>'[13]MD50000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M18" s="16">
+      <c r="M18" s="26">
         <f>'[13]MD50000.15-DEC'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
     <row r="19" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="6">
+      <c r="B19" s="24">
         <v>15</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="26">
         <f>'[14]MD5000-Jan24'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="27">
         <f>'[14]MD5000-Jan24'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="27">
         <f>'[14]MD5000-Jan24'!$K$2</f>
         <v>60</v>
       </c>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="10" t="s">
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="K19" s="11">
+      <c r="K19" s="29">
         <f>'[14]MD5000-Jan24'!$B$3</f>
         <v>45302</v>
       </c>
-      <c r="L19" s="8">
+      <c r="L19" s="26">
         <f>'[14]MD5000-Jan24'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M19" s="8">
+      <c r="M19" s="26">
         <f>'[14]MD5000-Jan24'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
     <row r="20" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="13">
+      <c r="B20" s="12">
         <v>16</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="15">
         <f>'[15]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14">
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13">
         <f>'[15]MD10000.10-JAN'!$K$1</f>
-        <v>8</v>
-      </c>
-      <c r="I20" s="14">
+        <v>5</v>
+      </c>
+      <c r="I20" s="13">
         <f>'[15]MD10000.10-JAN'!$K$2</f>
-        <v>40</v>
-      </c>
-      <c r="J20" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="J20" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="K20" s="15">
+      <c r="K20" s="14">
         <f>'[15]MD10000.10-JAN'!$B$3</f>
         <v>45308</v>
       </c>
-      <c r="L20" s="16">
+      <c r="L20" s="15">
         <f>'[15]MD10000.10-JAN'!$O$2</f>
-        <v>2800</v>
-      </c>
-      <c r="M20" s="16">
+        <v>1750</v>
+      </c>
+      <c r="M20" s="15">
         <f>'[15]MD10000.10-JAN'!$O$1</f>
-        <v>14000</v>
+        <v>15050</v>
       </c>
       <c r="N20" s="1">
         <v>350</v>
       </c>
     </row>
     <row r="21" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="6">
+      <c r="B21" s="24">
         <v>17</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="26">
         <f>'[16]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9">
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27">
         <f>'[16]MD10000.10-JAN'!$K$1</f>
-        <v>8</v>
-      </c>
-      <c r="I21" s="9">
+        <v>0</v>
+      </c>
+      <c r="I21" s="27">
         <f>'[16]MD10000.10-JAN'!$K$2</f>
-        <v>40</v>
-      </c>
-      <c r="J21" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K21" s="11">
+        <v>48</v>
+      </c>
+      <c r="J21" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="K21" s="29">
         <f>'[16]MD10000.10-JAN'!$B$3</f>
         <v>45308</v>
       </c>
-      <c r="L21" s="8">
+      <c r="L21" s="26">
         <f>'[16]MD10000.10-JAN'!$O$2</f>
-        <v>2800</v>
-      </c>
-      <c r="M21" s="8">
+        <v>0</v>
+      </c>
+      <c r="M21" s="26">
         <f>'[16]MD10000.10-JAN'!$O$1</f>
-        <v>14000</v>
-      </c>
-      <c r="N21" s="1">
-        <v>350</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="22" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="13">
+      <c r="B22" s="24">
         <v>18</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="26">
         <f>'[17]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14">
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27">
         <f>'[17]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I22" s="14">
+      <c r="I22" s="27">
         <f>'[17]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J22" s="17" t="s">
+      <c r="J22" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="K22" s="15">
+      <c r="K22" s="29">
         <f>'[17]MD10000.20-OCT'!$B$3</f>
         <v>45316</v>
       </c>
-      <c r="L22" s="16">
+      <c r="L22" s="26">
         <f>'[17]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M22" s="16">
+      <c r="M22" s="26">
         <f>'[17]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
     <row r="23" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="6">
+      <c r="B23" s="24">
         <v>19</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="26">
         <f>'[18]MD10000.20-OCT'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9">
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27">
         <f>'[18]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="27">
         <f>'[18]MD10000.20-OCT'!$K$2</f>
         <v>48</v>
       </c>
-      <c r="J23" s="10" t="s">
+      <c r="J23" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="K23" s="11">
+      <c r="K23" s="29">
         <f>'[18]MD10000.20-OCT'!$B$3</f>
         <v>45324</v>
       </c>
-      <c r="L23" s="8">
+      <c r="L23" s="26">
         <f>'[18]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M23" s="8">
+      <c r="M23" s="26">
         <f>'[18]MD10000.20-OCT'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
     <row r="24" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="6">
+      <c r="B24" s="24">
         <v>20</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="26">
         <f>'[19]MD10000.20-OCT'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9">
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27">
         <f>'[19]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I24" s="9">
+      <c r="I24" s="27">
         <f>'[19]MD10000.20-OCT'!$K$2</f>
         <v>48</v>
       </c>
-      <c r="J24" s="10" t="s">
+      <c r="J24" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="K24" s="11">
+      <c r="K24" s="29">
         <f>'[19]MD10000.20-OCT'!$B$3</f>
         <v>45327</v>
       </c>
-      <c r="L24" s="8">
+      <c r="L24" s="26">
         <f>'[19]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M24" s="8">
+      <c r="M24" s="26">
         <f>'[19]MD10000.20-OCT'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
     <row r="25" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="6">
+      <c r="B25" s="24">
         <v>21</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E25" s="26">
         <f>'[20]SM5000.1-oct'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F25" s="9">
+      <c r="F25" s="27">
         <f>'[20]SM5000.1-oct'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G25" s="9">
+      <c r="G25" s="27">
         <f>'[20]SM5000.1-oct'!$K$2</f>
         <v>60</v>
       </c>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="10" t="s">
+      <c r="H25" s="27"/>
+      <c r="I25" s="27"/>
+      <c r="J25" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="K25" s="11">
+      <c r="K25" s="29">
         <f>'[20]SM5000.1-oct'!$B$3</f>
         <v>45323</v>
       </c>
-      <c r="L25" s="8">
+      <c r="L25" s="26">
         <f>'[20]SM5000.1-oct'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M25" s="8">
+      <c r="M25" s="26">
         <f>'[20]SM5000.1-oct'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
     <row r="26" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="6">
+      <c r="B26" s="24">
         <v>22</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="26">
         <f>'[21]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9">
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27">
         <f>'[21]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" s="27">
         <f>'[21]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J26" s="10" t="s">
+      <c r="J26" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="K26" s="11">
+      <c r="K26" s="29">
         <f>'[21]MD10000.20-OCT'!$B$3</f>
         <v>45332</v>
       </c>
-      <c r="L26" s="8">
+      <c r="L26" s="26">
         <f>'[21]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M26" s="8">
+      <c r="M26" s="26">
         <f>'[21]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B27" s="13">
+    <row r="27" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="24">
         <v>23</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="E27" s="16">
+      <c r="E27" s="26">
         <f>'[22]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F27" s="14">
+      <c r="F27" s="27">
         <f>'[22]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G27" s="14">
+      <c r="G27" s="27">
         <f>'[22]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="17" t="s">
+      <c r="H27" s="27"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="K27" s="15">
+      <c r="K27" s="29">
         <f>'[22]MD10000.1-OCT'!$B$3</f>
         <v>45339</v>
       </c>
-      <c r="L27" s="16">
+      <c r="L27" s="26">
         <f>'[22]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M27" s="16">
+      <c r="M27" s="26">
         <f>'[22]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
     <row r="28" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="6">
+      <c r="B28" s="24">
         <v>24</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28" s="26">
         <f>'[23]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="27">
         <f>'[23]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="27">
         <f>'[23]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="10" t="s">
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="K28" s="11">
+      <c r="K28" s="29">
         <f>'[23]MD10000.1-OCT'!$B$3</f>
         <v>45334</v>
       </c>
-      <c r="L28" s="8">
+      <c r="L28" s="26">
         <f>'[23]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M28" s="8">
+      <c r="M28" s="26">
         <f>'[23]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
     <row r="29" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="6">
+      <c r="B29" s="24">
         <v>25</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="D29" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="26">
         <f>'[24]MD20000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9">
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27">
         <f>'[24]MD20000.15-DEC'!$K$1</f>
         <v>5</v>
       </c>
-      <c r="I29" s="9">
+      <c r="I29" s="27">
         <f>'[24]MD20000.15-DEC'!$K$2</f>
         <v>12</v>
       </c>
-      <c r="J29" s="10" t="s">
+      <c r="J29" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="K29" s="11">
+      <c r="K29" s="29">
         <f>'[24]MD20000.15-DEC'!$B$3</f>
         <v>45337</v>
       </c>
-      <c r="L29" s="8">
+      <c r="L29" s="26">
         <f>'[25]MD20000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M29" s="8">
+      <c r="M29" s="26">
         <f>'[25]MD20000.15-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
     <row r="30" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="6">
+      <c r="B30" s="24">
         <v>26</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E30" s="26">
         <f>'[26]MD20000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9">
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27">
         <f>'[26]MD20000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I30" s="9">
+      <c r="I30" s="27">
         <f>'[26]MD20000.15-DEC'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J30" s="10" t="s">
+      <c r="J30" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="K30" s="11">
+      <c r="K30" s="29">
         <f>'[26]MD20000.15-DEC'!$B$3</f>
         <v>45345</v>
       </c>
-      <c r="L30" s="8">
+      <c r="L30" s="26">
         <f>'[26]MD20000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M30" s="8">
+      <c r="M30" s="26">
         <f>'[26]MD20000.15-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
     <row r="31" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="13">
+      <c r="B31" s="24">
         <v>27</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="26">
         <f>'[27]MD20000.18-DEC'!$C$1</f>
         <v>30000</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="27">
         <f>'[27]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G31" s="14">
+      <c r="G31" s="27">
         <f>'[27]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="17" t="s">
+      <c r="H31" s="27"/>
+      <c r="I31" s="27"/>
+      <c r="J31" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="K31" s="15">
+      <c r="K31" s="29">
         <f>'[27]MD20000.18-DEC'!$B$3</f>
         <v>45354</v>
       </c>
-      <c r="L31" s="16">
+      <c r="L31" s="26">
         <f>'[27]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M31" s="16">
+      <c r="M31" s="26">
         <f>'[27]MD20000.18-DEC'!$O$1</f>
         <v>36000</v>
       </c>
     </row>
     <row r="32" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="13">
+      <c r="B32" s="24">
         <v>28</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="26">
         <f>'[28]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14">
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27">
         <f>'[28]MD10000.10-JAN'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I32" s="14">
+      <c r="I32" s="27">
         <f>'[28]MD10000.10-JAN'!$K$2</f>
         <v>48</v>
       </c>
-      <c r="J32" s="17" t="s">
+      <c r="J32" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="K32" s="15">
+      <c r="K32" s="29">
         <f>'[28]MD10000.10-JAN'!$B$3</f>
         <v>45366</v>
       </c>
-      <c r="L32" s="16">
+      <c r="L32" s="26">
         <f>'[28]MD10000.10-JAN'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M32" s="16">
+      <c r="M32" s="26">
         <f>'[28]MD10000.10-JAN'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
     <row r="33" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="13">
+      <c r="B33" s="24">
         <v>29</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="E33" s="16">
+      <c r="E33" s="26">
         <f>'[29]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14">
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27">
         <f>'[29]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I33" s="14">
+      <c r="I33" s="27">
         <f>'[29]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J33" s="17" t="s">
+      <c r="J33" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="K33" s="15">
+      <c r="K33" s="29">
         <f>'[29]MD20000.15-DEc'!$B$3</f>
         <v>45380</v>
       </c>
-      <c r="L33" s="16">
+      <c r="L33" s="26">
         <f>'[29]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M33" s="16">
+      <c r="M33" s="26">
         <f>'[29]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
     <row r="34" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="13">
+      <c r="B34" s="24">
         <v>30</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="E34" s="16">
+      <c r="E34" s="26">
         <f>'[30]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14">
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="27">
         <f>'[30]MD10000.10-JAN'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I34" s="14">
+      <c r="I34" s="27">
         <f>'[30]MD10000.10-JAN'!$K$2</f>
         <v>48</v>
       </c>
-      <c r="J34" s="17" t="s">
+      <c r="J34" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="K34" s="15">
+      <c r="K34" s="29">
         <f>'[30]MD10000.10-JAN'!$B$3</f>
         <v>45389</v>
       </c>
-      <c r="L34" s="16">
+      <c r="L34" s="26">
         <f>'[30]MD10000.10-JAN'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M34" s="16">
+      <c r="M34" s="26">
         <f>'[30]MD10000.10-JAN'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
     <row r="35" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="6">
+      <c r="B35" s="24">
         <v>31</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D35" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="E35" s="8">
+      <c r="E35" s="26">
         <f>'[31]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9">
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="27">
         <f>'[31]MD20000.15-DEc'!$G$1</f>
         <v>17</v>
       </c>
-      <c r="I35" s="9">
+      <c r="I35" s="27">
         <f>'[31]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J35" s="10" t="s">
+      <c r="J35" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="K35" s="11">
+      <c r="K35" s="29">
         <f>'[31]MD20000.15-DEc'!$B$3</f>
         <v>45394</v>
       </c>
-      <c r="L35" s="8">
+      <c r="L35" s="26">
         <f>'[31]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M35" s="8">
+      <c r="M35" s="26">
         <f>'[31]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
     <row r="36" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="13">
+      <c r="B36" s="12">
         <v>32</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="D36" s="15" t="s">
+      <c r="D36" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E36" s="16">
+      <c r="E36" s="15">
         <f>'[32]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14">
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13">
         <f>'[32]MD10000.10-JAN'!$G$1</f>
         <v>48</v>
       </c>
-      <c r="I36" s="14">
+      <c r="I36" s="13">
         <f>'[32]MD10000.10-JAN'!$K$2</f>
-        <v>27</v>
-      </c>
-      <c r="J36" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="J36" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="K36" s="15">
+      <c r="K36" s="14">
         <f>'[32]MD10000.10-JAN'!$B$3</f>
         <v>45399</v>
       </c>
-      <c r="L36" s="16">
+      <c r="L36" s="15">
         <f>'[32]MD10000.10-JAN'!$O$2</f>
-        <v>7350</v>
-      </c>
-      <c r="M36" s="16">
+        <v>6300</v>
+      </c>
+      <c r="M36" s="15">
         <f>'[32]MD10000.10-JAN'!$O$1</f>
-        <v>9450</v>
+        <v>10500</v>
       </c>
       <c r="N36" s="1">
         <v>350</v>
       </c>
     </row>
     <row r="37" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="6">
+      <c r="B37" s="24">
         <v>33</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C37" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D37" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="E37" s="8">
+      <c r="E37" s="26">
         <f>'[33]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9">
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="27">
         <f>'[33]MD20000.15-DEc'!$G$1</f>
         <v>17</v>
       </c>
-      <c r="I37" s="9">
+      <c r="I37" s="27">
         <f>'[33]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J37" s="10" t="s">
+      <c r="J37" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="K37" s="11">
+      <c r="K37" s="29">
         <f>'[33]MD20000.15-DEc'!$B$3</f>
         <v>45406</v>
       </c>
-      <c r="L37" s="8">
+      <c r="L37" s="26">
         <f>'[33]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M37" s="8">
+      <c r="M37" s="26">
         <f>'[33]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
     <row r="38" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="13">
+      <c r="B38" s="24">
         <v>34</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C38" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D38" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="E38" s="16">
+      <c r="E38" s="26">
         <f>'[34]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14">
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="27">
         <f>'[34]MD10000.20-OCT'!$G$1</f>
         <v>17</v>
       </c>
-      <c r="I38" s="14">
+      <c r="I38" s="27">
         <f>'[34]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J38" s="17" t="s">
+      <c r="J38" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="K38" s="15">
+      <c r="K38" s="29">
         <f>'[34]MD10000.20-OCT'!$B$3</f>
         <v>45406</v>
       </c>
-      <c r="L38" s="16">
+      <c r="L38" s="26">
         <f>'[34]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M38" s="16">
+      <c r="M38" s="26">
         <f>'[34]MD10000.20-OCT'!$O$1</f>
         <v>5950</v>
       </c>
@@ -5434,38 +5715,38 @@
       <c r="B39" s="6">
         <v>35</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="D39" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="E39" s="8">
+      <c r="E39" s="7">
         <f>'[35]MD50000.15-DEC'!$C$1</f>
         <v>40000</v>
       </c>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9">
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8">
         <f>'[35]MD50000.15-DEC'!$K$1</f>
         <v>47</v>
       </c>
-      <c r="I39" s="9">
+      <c r="I39" s="8">
         <f>'[35]MD50000.15-DEC'!$K$2</f>
         <v>1</v>
       </c>
-      <c r="J39" s="10" t="s">
+      <c r="J39" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K39" s="11">
+      <c r="K39" s="10">
         <f>'[35]MD50000.15-DEC'!$B$3</f>
         <v>45416</v>
       </c>
-      <c r="L39" s="8">
+      <c r="L39" s="7">
         <f>'[36]MD50000.15-DEC'!$O$2</f>
         <v>46200</v>
       </c>
-      <c r="M39" s="8">
+      <c r="M39" s="7">
         <f>'[35]MD50000.15-DEC'!$O$1</f>
         <v>1400</v>
       </c>
@@ -5474,521 +5755,518 @@
       </c>
     </row>
     <row r="40" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="6">
+      <c r="B40" s="24">
         <v>36</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D40" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="E40" s="8">
+      <c r="E40" s="26">
         <f>'[37]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9">
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27">
         <f>'[37]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I40" s="9">
+      <c r="I40" s="27">
         <f>'[37]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J40" s="10" t="s">
+      <c r="J40" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="K40" s="11">
+      <c r="K40" s="29">
         <f>'[37]MD10000.20-OCT'!$B$3</f>
         <v>45427</v>
       </c>
-      <c r="L40" s="8">
+      <c r="L40" s="26">
         <f>'[37]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M40" s="8">
+      <c r="M40" s="26">
         <f>'[37]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
     <row r="41" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="6">
+      <c r="B41" s="24">
         <v>37</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C41" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="D41" s="15" t="s">
+      <c r="D41" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="8">
+      <c r="E41" s="26">
         <f>'[38]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F41" s="9">
+      <c r="F41" s="27">
         <f>'[38]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G41" s="9">
+      <c r="G41" s="27">
         <f>'[38]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-      <c r="J41" s="10" t="s">
+      <c r="H41" s="27"/>
+      <c r="I41" s="27"/>
+      <c r="J41" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="K41" s="11">
+      <c r="K41" s="29">
         <f>'[38]MD20000.18-DEC'!$B$3</f>
         <v>45425</v>
       </c>
-      <c r="L41" s="8">
+      <c r="L41" s="26">
         <f>'[38]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M41" s="8">
+      <c r="M41" s="26">
         <f>'[38]MD20000.18-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
     <row r="42" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="6">
+      <c r="B42" s="24">
         <v>38</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C42" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D42" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E42" s="8">
+      <c r="E42" s="26">
         <f>'[39]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9">
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="27">
         <f>'[39]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I42" s="9">
+      <c r="I42" s="27">
         <f>'[39]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J42" s="10" t="s">
+      <c r="J42" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="K42" s="11">
+      <c r="K42" s="29">
         <f>'[39]MD10000.20-OCT'!$B$3</f>
         <v>45436</v>
       </c>
-      <c r="L42" s="8">
+      <c r="L42" s="26">
         <f>'[39]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M42" s="8">
+      <c r="M42" s="26">
         <f>'[39]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
     <row r="43" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="6">
+      <c r="B43" s="24">
         <v>39</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C43" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="D43" s="11" t="s">
+      <c r="D43" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E43" s="8">
+      <c r="E43" s="26">
         <f>'[40]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F43" s="9">
+      <c r="F43" s="27">
         <f>'[40]MD20000.22-DEC'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G43" s="9">
+      <c r="G43" s="27">
         <f>'[40]MD20000.22-DEC'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="H43" s="9"/>
-      <c r="I43" s="9"/>
-      <c r="J43" s="10" t="s">
+      <c r="H43" s="27"/>
+      <c r="I43" s="27"/>
+      <c r="J43" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="K43" s="11">
+      <c r="K43" s="29">
         <f>'[40]MD20000.22-DEC'!$B$3</f>
         <v>45432</v>
       </c>
-      <c r="L43" s="8">
+      <c r="L43" s="26">
         <f>'[40]MD20000.22-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M43" s="8">
+      <c r="M43" s="26">
         <f>'[40]MD20000.22-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
     <row r="44" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="6">
+      <c r="B44" s="24">
         <v>40</v>
       </c>
-      <c r="C44" s="9" t="s">
+      <c r="C44" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="D44" s="15" t="s">
+      <c r="D44" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="E44" s="8">
+      <c r="E44" s="26">
         <f>'[41]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F44" s="9">
+      <c r="F44" s="27">
         <f>'[41]MD10000.1-OCT'!$G$1</f>
         <v>120</v>
       </c>
-      <c r="G44" s="9">
+      <c r="G44" s="27">
         <f>'[41]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
-      <c r="J44" s="10" t="s">
+      <c r="H44" s="27"/>
+      <c r="I44" s="27"/>
+      <c r="J44" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="K44" s="11">
+      <c r="K44" s="29">
         <f>'[41]MD10000.1-OCT'!$B$3</f>
         <v>45437</v>
       </c>
-      <c r="L44" s="8">
+      <c r="L44" s="26">
         <f>'[41]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M44" s="8">
+      <c r="M44" s="26">
         <f>'[41]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
     <row r="45" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="6">
+      <c r="B45" s="24">
         <v>41</v>
       </c>
-      <c r="C45" s="9" t="s">
+      <c r="C45" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="D45" s="15" t="s">
+      <c r="D45" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E45" s="8">
+      <c r="E45" s="26">
         <f>'[42]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9">
+      <c r="F45" s="27"/>
+      <c r="G45" s="27"/>
+      <c r="H45" s="27">
         <f>'[42]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I45" s="9">
+      <c r="I45" s="27">
         <f>'[42]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J45" s="10" t="s">
+      <c r="J45" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="K45" s="11">
+      <c r="K45" s="29">
         <f>'[42]MD10000.20-OCT'!$B$3</f>
         <v>45444</v>
       </c>
-      <c r="L45" s="8"/>
-      <c r="M45" s="8">
+      <c r="L45" s="26"/>
+      <c r="M45" s="26">
         <f>'[42]MD10000.20-OCT'!$O$1</f>
         <v>5950</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="6">
+      <c r="B46" s="24">
         <v>42</v>
       </c>
-      <c r="C46" s="9" t="s">
+      <c r="C46" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="D46" s="15" t="s">
+      <c r="D46" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="E46" s="8">
+      <c r="E46" s="26">
         <f>'[43]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9">
+      <c r="F46" s="27"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="27">
         <f>'[44]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I46" s="9">
+      <c r="I46" s="27">
         <f>'[44]MD10000.1-OCT'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J46" s="10" t="s">
+      <c r="J46" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="K46" s="11">
+      <c r="K46" s="29">
         <f>'[43]MD10000.1-OCT'!$B$3</f>
         <v>45450</v>
       </c>
-      <c r="L46" s="8">
+      <c r="L46" s="26">
         <f>'[44]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M46" s="8">
+      <c r="M46" s="26">
         <f>'[44]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
     <row r="47" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="6">
+      <c r="B47" s="24">
         <v>43</v>
       </c>
-      <c r="C47" s="9" t="s">
+      <c r="C47" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="D47" s="15" t="s">
+      <c r="D47" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E47" s="8">
+      <c r="E47" s="26">
         <f>'[45]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F47" s="9">
+      <c r="F47" s="27">
         <f>'[45]MD20000.22-DEC'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G47" s="9">
+      <c r="G47" s="27">
         <f>'[45]MD20000.22-DEC'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="H47" s="9"/>
-      <c r="I47" s="9"/>
-      <c r="J47" s="10" t="s">
+      <c r="H47" s="27"/>
+      <c r="I47" s="27"/>
+      <c r="J47" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="K47" s="11">
+      <c r="K47" s="29">
         <f>'[45]MD20000.22-DEC'!$B$3</f>
         <v>45446</v>
       </c>
-      <c r="L47" s="8">
+      <c r="L47" s="26">
         <f>'[45]MD20000.22-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M47" s="8">
+      <c r="M47" s="26">
         <f>'[45]MD20000.22-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="6">
+      <c r="B48" s="24">
         <v>44</v>
       </c>
-      <c r="C48" s="9" t="s">
+      <c r="C48" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="D48" s="15" t="s">
+      <c r="D48" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="E48" s="8">
+      <c r="E48" s="26">
         <f>'[46]MD20000.22-DEC'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F48" s="9">
+      <c r="F48" s="27">
         <f>'[46]MD20000.22-DEC'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G48" s="9">
+      <c r="G48" s="27">
         <f>'[46]MD20000.22-DEC'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="H48" s="9"/>
-      <c r="I48" s="9"/>
-      <c r="J48" s="10" t="s">
+      <c r="H48" s="27"/>
+      <c r="I48" s="27"/>
+      <c r="J48" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="K48" s="11">
+      <c r="K48" s="29">
         <f>'[46]MD20000.22-DEC'!$B$3</f>
         <v>45473</v>
       </c>
-      <c r="L48" s="8">
+      <c r="L48" s="26">
         <f>'[46]MD20000.22-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M48" s="8">
+      <c r="M48" s="26">
         <f>'[46]MD20000.22-DEC'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
     <row r="49" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="6">
+      <c r="B49" s="24">
         <v>45</v>
       </c>
-      <c r="C49" s="9" t="s">
+      <c r="C49" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D49" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="E49" s="8">
+      <c r="E49" s="26">
         <f>'[47]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="9">
+      <c r="F49" s="27"/>
+      <c r="G49" s="27"/>
+      <c r="H49" s="27">
         <f>'[47]MD20000.15-DEc'!$K$1</f>
-        <v>3</v>
-      </c>
-      <c r="I49" s="9">
+        <v>0</v>
+      </c>
+      <c r="I49" s="27">
         <f>'[47]MD20000.15-DEc'!$K$2</f>
-        <v>14</v>
-      </c>
-      <c r="J49" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J49" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="K49" s="11">
+      <c r="K49" s="29">
         <f>'[47]MD20000.15-DEc'!$B$3</f>
         <v>45495</v>
       </c>
-      <c r="L49" s="8">
+      <c r="L49" s="26">
         <f>'[47]MD20000.15-DEc'!$O$2</f>
-        <v>4200</v>
-      </c>
-      <c r="M49" s="8">
+        <v>0</v>
+      </c>
+      <c r="M49" s="26">
         <f>'[47]MD20000.15-DEc'!$O$1</f>
-        <v>19800</v>
-      </c>
-      <c r="N49" s="1">
-        <v>1400</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="6">
+      <c r="B50" s="24">
         <v>46</v>
       </c>
-      <c r="C50" s="9" t="s">
+      <c r="C50" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="D50" s="11" t="s">
+      <c r="D50" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="E50" s="8">
+      <c r="E50" s="26">
         <f>'[48]MD20000.15-DEc'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9">
+      <c r="F50" s="27"/>
+      <c r="G50" s="27"/>
+      <c r="H50" s="27">
         <f>'[48]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I50" s="9">
+      <c r="I50" s="27">
         <f>'[48]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J50" s="10" t="s">
+      <c r="J50" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="K50" s="11">
+      <c r="K50" s="29">
         <f>'[48]MD20000.15-DEc'!$B$3</f>
         <v>45496</v>
       </c>
-      <c r="L50" s="8">
+      <c r="L50" s="26">
         <f>'[48]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M50" s="8">
+      <c r="M50" s="26">
         <f>'[48]MD20000.15-DEc'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
     <row r="51" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="6">
+      <c r="B51" s="24">
         <v>47</v>
       </c>
-      <c r="C51" s="14" t="s">
+      <c r="C51" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D51" s="15" t="s">
+      <c r="D51" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E51" s="8">
+      <c r="E51" s="26">
         <f>'[49]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F51" s="9">
+      <c r="F51" s="27">
         <f>'[49]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G51" s="9">
+      <c r="G51" s="27">
         <f>'[49]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="H51" s="9"/>
-      <c r="I51" s="9"/>
-      <c r="J51" s="10" t="s">
+      <c r="H51" s="27"/>
+      <c r="I51" s="27"/>
+      <c r="J51" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="K51" s="11">
+      <c r="K51" s="29">
         <f>'[49]MD20000.18-DEC'!$B$3</f>
         <v>45493</v>
       </c>
-      <c r="L51" s="8">
+      <c r="L51" s="26">
         <f>'[49]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M51" s="8">
+      <c r="M51" s="26">
         <f>'[49]MD20000.18-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="6">
+      <c r="B52" s="24">
         <v>48</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="C52" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="D52" s="11" t="s">
+      <c r="D52" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="E52" s="8">
+      <c r="E52" s="26">
         <f>'[50]MD20000.15-DEc'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="9">
+      <c r="F52" s="27"/>
+      <c r="G52" s="27"/>
+      <c r="H52" s="27">
         <f>'[50]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I52" s="9">
+      <c r="I52" s="27">
         <f>'[50]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J52" s="10" t="s">
+      <c r="J52" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="K52" s="11">
+      <c r="K52" s="29">
         <f>'[50]MD20000.15-DEc'!$B$3</f>
         <v>45502</v>
       </c>
-      <c r="L52" s="8">
+      <c r="L52" s="26">
         <f>'[50]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M52" s="8">
+      <c r="M52" s="26">
         <f>'[50]MD20000.15-DEc'!$O$1</f>
         <v>12000</v>
       </c>
@@ -5997,78 +6275,78 @@
       <c r="B53" s="6">
         <v>49</v>
       </c>
-      <c r="C53" s="9" t="s">
+      <c r="C53" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D53" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E53" s="8">
+      <c r="E53" s="7">
         <f>'[51]MD50000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F53" s="9"/>
-      <c r="G53" s="9"/>
-      <c r="H53" s="9">
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8">
         <f>'[51]MD50000.15-DEC'!$K$1</f>
         <v>13</v>
       </c>
-      <c r="I53" s="9">
+      <c r="I53" s="8">
         <f>'[51]MD50000.15-DEC'!$K$2</f>
         <v>4</v>
       </c>
-      <c r="J53" s="10" t="s">
+      <c r="J53" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K53" s="11">
+      <c r="K53" s="10">
         <f>'[51]MD50000.15-DEC'!$B$3</f>
         <v>45504</v>
       </c>
-      <c r="L53" s="8">
+      <c r="L53" s="7">
         <f>'[51]MD50000.15-DEC'!$O$2</f>
         <v>18200</v>
       </c>
-      <c r="M53" s="8">
+      <c r="M53" s="7">
         <f>'[51]MD50000.15-DEC'!$O$1</f>
         <v>5800</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="6">
+      <c r="B54" s="24">
         <v>50</v>
       </c>
-      <c r="C54" s="9" t="s">
+      <c r="C54" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="D54" s="15" t="s">
+      <c r="D54" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="E54" s="8">
+      <c r="E54" s="26">
         <f>'[52]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9">
+      <c r="F54" s="27"/>
+      <c r="G54" s="27"/>
+      <c r="H54" s="27">
         <f>'[52]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I54" s="9">
+      <c r="I54" s="27">
         <f>'[52]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J54" s="10" t="s">
+      <c r="J54" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="K54" s="11">
+      <c r="K54" s="29">
         <f>'[52]MD10000.20-OCT'!$B$3</f>
         <v>45511</v>
       </c>
-      <c r="L54" s="8">
+      <c r="L54" s="26">
         <f>'[52]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M54" s="8">
+      <c r="M54" s="26">
         <f>'[52]MD10000.20-OCT'!$O$1</f>
         <v>5950</v>
       </c>
@@ -6077,81 +6355,81 @@
       <c r="B55" s="6">
         <v>51</v>
       </c>
-      <c r="C55" s="9" t="s">
+      <c r="C55" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D55" s="15" t="s">
+      <c r="D55" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="E55" s="8">
+      <c r="E55" s="7">
         <f>'[53]MD20000.18-DEC'!$C$1</f>
         <v>30000</v>
       </c>
-      <c r="F55" s="9">
+      <c r="F55" s="8">
         <f>'[53]MD20000.18-DEC'!$K$1</f>
-        <v>47</v>
-      </c>
-      <c r="G55" s="9">
+        <v>24</v>
+      </c>
+      <c r="G55" s="8">
         <f>'[53]MD20000.18-DEC'!$K$2</f>
-        <v>73</v>
-      </c>
-      <c r="H55" s="9"/>
-      <c r="I55" s="9"/>
-      <c r="J55" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H55" s="8"/>
+      <c r="I55" s="8"/>
+      <c r="J55" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K55" s="11">
+      <c r="K55" s="10">
         <f>'[53]MD20000.18-DEC'!$B$3</f>
         <v>45508</v>
       </c>
-      <c r="L55" s="8">
+      <c r="L55" s="7">
         <f>'[53]MD20000.18-DEC'!$O$2</f>
-        <v>14100</v>
-      </c>
-      <c r="M55" s="8">
+        <v>7200</v>
+      </c>
+      <c r="M55" s="7">
         <f>'[53]MD20000.18-DEC'!$O$1</f>
-        <v>21900</v>
+        <v>28800</v>
       </c>
       <c r="N55" s="1">
         <v>2100</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="6">
+      <c r="B56" s="24">
         <v>52</v>
       </c>
-      <c r="C56" s="9" t="s">
+      <c r="C56" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="D56" s="15" t="s">
+      <c r="D56" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="E56" s="8">
+      <c r="E56" s="26">
         <f>'[54]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F56" s="9">
+      <c r="F56" s="27">
         <f>'[54]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G56" s="9">
+      <c r="G56" s="27">
         <f>'[54]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="H56" s="9"/>
-      <c r="I56" s="9"/>
-      <c r="J56" s="10" t="s">
+      <c r="H56" s="27"/>
+      <c r="I56" s="27"/>
+      <c r="J56" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="K56" s="11">
+      <c r="K56" s="29">
         <f>'[54]MD20000.18-DEC'!$B$3</f>
         <v>45514</v>
       </c>
-      <c r="L56" s="8">
+      <c r="L56" s="26">
         <f>'[54]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M56" s="8">
+      <c r="M56" s="26">
         <f>'[54]MD20000.18-DEC'!$O$1</f>
         <v>12000</v>
       </c>
@@ -6160,40 +6438,40 @@
       <c r="B57" s="6">
         <v>53</v>
       </c>
-      <c r="C57" s="9" t="s">
+      <c r="C57" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="D57" s="11" t="s">
+      <c r="D57" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="E57" s="8">
+      <c r="E57" s="7">
         <f>'[55]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9">
+      <c r="F57" s="8"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="8">
         <f>'[55]MD20000.15-DEc'!$K$1</f>
-        <v>8</v>
-      </c>
-      <c r="I57" s="9">
+        <v>6</v>
+      </c>
+      <c r="I57" s="8">
         <f>'[55]MD20000.15-DEc'!$K$2</f>
-        <v>9</v>
-      </c>
-      <c r="J57" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="J57" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K57" s="11">
+      <c r="K57" s="10">
         <f>'[55]MD20000.15-DEc'!$B$3</f>
         <v>45527</v>
       </c>
-      <c r="L57" s="8">
+      <c r="L57" s="7">
         <f>'[55]MD20000.15-DEc'!$O$2</f>
-        <v>11200</v>
-      </c>
-      <c r="M57" s="8">
+        <v>8400</v>
+      </c>
+      <c r="M57" s="7">
         <f>'[55]MD20000.15-DEc'!$O$1</f>
-        <v>12800</v>
+        <v>15600</v>
       </c>
       <c r="N57" s="1">
         <v>1400</v>
@@ -6203,298 +6481,286 @@
       <c r="B58" s="6">
         <v>54</v>
       </c>
-      <c r="C58" s="9" t="s">
+      <c r="C58" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D58" s="11" t="s">
+      <c r="D58" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="E58" s="8">
+      <c r="E58" s="7">
         <f>'[56]MD20000.15-DEc'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9">
+      <c r="F58" s="8"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="8">
         <f>'[56]MD20000.15-DEc'!$K$1</f>
+        <v>7</v>
+      </c>
+      <c r="I58" s="8">
+        <f>'[56]MD20000.15-DEc'!$K$2</f>
         <v>10</v>
       </c>
-      <c r="I58" s="9">
-        <f>'[56]MD20000.15-DEc'!$K$2</f>
-        <v>7</v>
-      </c>
-      <c r="J58" s="10" t="s">
+      <c r="J58" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K58" s="11">
+      <c r="K58" s="10">
         <f>'[56]MD20000.15-DEc'!$B$3</f>
         <v>45531</v>
       </c>
-      <c r="L58" s="8">
+      <c r="L58" s="7">
         <f>'[56]MD20000.15-DEc'!$O$2</f>
-        <v>7000</v>
-      </c>
-      <c r="M58" s="8">
+        <v>4900</v>
+      </c>
+      <c r="M58" s="7">
         <f>'[56]MD20000.15-DEc'!$O$1</f>
-        <v>5000</v>
+        <v>7100</v>
       </c>
       <c r="N58" s="1">
         <v>700</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="6">
+      <c r="B59" s="24">
         <v>55</v>
       </c>
-      <c r="C59" s="9" t="s">
+      <c r="C59" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="D59" s="15" t="s">
+      <c r="D59" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="E59" s="8">
+      <c r="E59" s="26">
         <f>'[57]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="9">
+      <c r="F59" s="27"/>
+      <c r="G59" s="27"/>
+      <c r="H59" s="27">
         <f>'[57]MD10000.20-OCT'!$K$1</f>
-        <v>9</v>
-      </c>
-      <c r="I59" s="9">
+        <v>0</v>
+      </c>
+      <c r="I59" s="27">
         <f>'[57]MD10000.20-OCT'!$K$2</f>
-        <v>8</v>
-      </c>
-      <c r="J59" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K59" s="11">
+        <v>17</v>
+      </c>
+      <c r="J59" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="K59" s="29">
         <f>'[57]MD10000.20-OCT'!$B$3</f>
         <v>45532</v>
       </c>
-      <c r="L59" s="8">
+      <c r="L59" s="26">
         <f>'[57]MD10000.20-OCT'!$O$2</f>
-        <v>3150</v>
-      </c>
-      <c r="M59" s="8">
+        <v>0</v>
+      </c>
+      <c r="M59" s="26">
         <f>'[57]MD10000.20-OCT'!$O$1</f>
-        <v>2850</v>
-      </c>
-      <c r="N59" s="1">
-        <v>700</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="60" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B60" s="6">
         <v>56</v>
       </c>
-      <c r="C60" s="9" t="s">
+      <c r="C60" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="D60" s="11" t="s">
+      <c r="D60" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="E60" s="8">
+      <c r="E60" s="7">
         <f>'[58]MD20000.15-DEc'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
-      <c r="H60" s="9">
+      <c r="F60" s="8"/>
+      <c r="G60" s="8"/>
+      <c r="H60" s="8">
         <f>'[58]MD20000.15-DEc'!$K$1</f>
-        <v>9</v>
-      </c>
-      <c r="I60" s="9">
+        <v>7</v>
+      </c>
+      <c r="I60" s="8">
         <f>'[58]MD20000.15-DEc'!$K$2</f>
-        <v>8</v>
-      </c>
-      <c r="J60" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="J60" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K60" s="11">
+      <c r="K60" s="10">
         <f>'[58]MD20000.15-DEc'!$B$3</f>
         <v>45534</v>
       </c>
-      <c r="L60" s="8">
+      <c r="L60" s="7">
         <f>'[58]MD20000.15-DEc'!$O$2</f>
-        <v>6300</v>
-      </c>
-      <c r="M60" s="8">
+        <v>4900</v>
+      </c>
+      <c r="M60" s="7">
         <f>'[58]MD20000.15-DEc'!$O$1</f>
-        <v>5700</v>
+        <v>7100</v>
       </c>
       <c r="N60" s="1">
         <v>700</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="6">
+      <c r="B61" s="24">
         <v>57</v>
       </c>
-      <c r="C61" s="9" t="s">
+      <c r="C61" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D61" s="15" t="s">
+      <c r="D61" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="E61" s="8">
+      <c r="E61" s="26">
         <f>'[59]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F61" s="9"/>
-      <c r="G61" s="9"/>
-      <c r="H61" s="9">
+      <c r="F61" s="27"/>
+      <c r="G61" s="27"/>
+      <c r="H61" s="27">
         <f>'[59]MD10000.20-OCT'!$K$1</f>
-        <v>10</v>
-      </c>
-      <c r="I61" s="9">
+        <v>0</v>
+      </c>
+      <c r="I61" s="27">
         <f>'[59]MD10000.20-OCT'!$K$2</f>
-        <v>7</v>
-      </c>
-      <c r="J61" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K61" s="11">
+        <v>17</v>
+      </c>
+      <c r="J61" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="K61" s="29">
         <f>'[59]MD10000.20-OCT'!$B$3</f>
         <v>45536</v>
       </c>
-      <c r="L61" s="8">
+      <c r="L61" s="26">
         <f>'[59]MD10000.20-OCT'!$O$2</f>
-        <v>3500</v>
-      </c>
-      <c r="M61" s="8">
+        <v>0</v>
+      </c>
+      <c r="M61" s="26">
         <f>'[59]MD10000.20-OCT'!$O$1</f>
-        <v>2500</v>
-      </c>
-      <c r="N61" s="1">
-        <v>350</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="6">
+      <c r="B62" s="24">
         <v>58</v>
       </c>
-      <c r="C62" s="9" t="s">
+      <c r="C62" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="D62" s="11" t="s">
+      <c r="D62" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E62" s="8">
+      <c r="E62" s="26">
         <f>'[60]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F62" s="9">
+      <c r="F62" s="27">
         <f>'[60]MD20000.22-DEC'!$K$1</f>
-        <v>74</v>
-      </c>
-      <c r="G62" s="9">
+        <v>0</v>
+      </c>
+      <c r="G62" s="27">
         <f>'[60]MD20000.22-DEC'!$K$2</f>
-        <v>46</v>
-      </c>
-      <c r="H62" s="9"/>
-      <c r="I62" s="9"/>
-      <c r="J62" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K62" s="11">
+        <v>120</v>
+      </c>
+      <c r="H62" s="27"/>
+      <c r="I62" s="27"/>
+      <c r="J62" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="K62" s="29">
         <f>'[60]MD20000.22-DEC'!$B$3</f>
         <v>45535</v>
       </c>
-      <c r="L62" s="8">
+      <c r="L62" s="26">
         <f>'[60]MD20000.22-DEC'!$O$2</f>
-        <v>14800</v>
-      </c>
-      <c r="M62" s="8">
+        <v>0</v>
+      </c>
+      <c r="M62" s="26">
         <f>'[60]MD20000.22-DEC'!$O$1</f>
-        <v>9200</v>
-      </c>
-      <c r="N62" s="1">
-        <v>1400</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="6">
+      <c r="B63" s="24">
         <v>59</v>
       </c>
-      <c r="C63" s="9" t="s">
+      <c r="C63" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="D63" s="15" t="s">
+      <c r="D63" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E63" s="8">
+      <c r="E63" s="26">
         <f>'[61]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F63" s="9"/>
-      <c r="G63" s="9"/>
-      <c r="H63" s="9">
+      <c r="F63" s="27"/>
+      <c r="G63" s="27"/>
+      <c r="H63" s="27">
         <f>'[61]MD10000.20-OCT'!$K$1</f>
-        <v>12</v>
-      </c>
-      <c r="I63" s="9">
+        <v>0</v>
+      </c>
+      <c r="I63" s="27">
         <f>'[61]MD10000.20-OCT'!$K$2</f>
-        <v>5</v>
-      </c>
-      <c r="J63" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K63" s="11">
+        <v>17</v>
+      </c>
+      <c r="J63" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="K63" s="29">
         <f>'[61]MD10000.20-OCT'!$B$3</f>
         <v>45549</v>
       </c>
-      <c r="L63" s="8">
+      <c r="L63" s="26">
         <f>'[61]MD10000.20-OCT'!$O$2</f>
-        <v>4200</v>
-      </c>
-      <c r="M63" s="8">
+        <v>0</v>
+      </c>
+      <c r="M63" s="26">
         <f>'[61]MD10000.20-OCT'!$O$1</f>
-        <v>1800</v>
-      </c>
-      <c r="N63" s="1">
-        <v>350</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B64" s="6">
         <v>60</v>
       </c>
-      <c r="C64" s="9" t="s">
+      <c r="C64" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="D64" s="15" t="s">
+      <c r="D64" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="E64" s="8">
+      <c r="E64" s="7">
         <f>'[62]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F64" s="9">
+      <c r="F64" s="8">
         <f>'[62]MD20000.22-DEC'!$K$1</f>
-        <v>89</v>
-      </c>
-      <c r="G64" s="9">
+        <v>72</v>
+      </c>
+      <c r="G64" s="8">
         <f>'[62]MD20000.22-DEC'!$K$2</f>
-        <v>31</v>
-      </c>
-      <c r="H64" s="9"/>
-      <c r="I64" s="9"/>
-      <c r="J64" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="H64" s="8"/>
+      <c r="I64" s="8"/>
+      <c r="J64" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K64" s="11">
+      <c r="K64" s="10">
         <f>'[62]MD20000.22-DEC'!$B$13</f>
         <v>45562</v>
       </c>
-      <c r="L64" s="8">
+      <c r="L64" s="7">
         <f>'[62]MD20000.22-DEC'!$O$2</f>
-        <v>17800</v>
-      </c>
-      <c r="M64" s="8">
+        <v>14400</v>
+      </c>
+      <c r="M64" s="7">
         <f>'[62]MD20000.22-DEC'!$O$1</f>
-        <v>6200</v>
+        <v>9600</v>
       </c>
       <c r="N64" s="1">
         <v>1400</v>
@@ -6504,40 +6770,40 @@
       <c r="B65" s="6">
         <v>61</v>
       </c>
-      <c r="C65" s="9" t="s">
+      <c r="C65" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D65" s="15" t="s">
+      <c r="D65" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="E65" s="8">
+      <c r="E65" s="7">
         <f>'[63]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F65" s="9">
+      <c r="F65" s="8">
         <f>'[63]MD10000.1-OCT'!$K$1</f>
-        <v>94</v>
-      </c>
-      <c r="G65" s="9">
+        <v>77</v>
+      </c>
+      <c r="G65" s="8">
         <f>'[63]MD10000.1-OCT'!$K$2</f>
-        <v>26</v>
-      </c>
-      <c r="H65" s="9"/>
-      <c r="I65" s="9"/>
-      <c r="J65" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H65" s="8"/>
+      <c r="I65" s="8"/>
+      <c r="J65" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K65" s="11">
+      <c r="K65" s="10">
         <f>'[63]MD10000.1-OCT'!$B$3</f>
         <v>45557</v>
       </c>
-      <c r="L65" s="8">
+      <c r="L65" s="7">
         <f>'[63]MD10000.1-OCT'!$O$2</f>
-        <v>9400</v>
-      </c>
-      <c r="M65" s="8">
+        <v>7700</v>
+      </c>
+      <c r="M65" s="7">
         <f>'[63]MD10000.1-OCT'!$O$1</f>
-        <v>2600</v>
+        <v>4300</v>
       </c>
       <c r="N65" s="1">
         <v>700</v>
@@ -6547,40 +6813,40 @@
       <c r="B66" s="6">
         <v>62</v>
       </c>
-      <c r="C66" s="9" t="s">
+      <c r="C66" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D66" s="15" t="s">
+      <c r="D66" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="E66" s="8">
+      <c r="E66" s="7">
         <f>'[64]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F66" s="9">
+      <c r="F66" s="8">
         <f>'[64]MD10000.1-OCT'!$K$1</f>
-        <v>94</v>
-      </c>
-      <c r="G66" s="9">
+        <v>78</v>
+      </c>
+      <c r="G66" s="8">
         <f>'[64]MD10000.1-OCT'!$K$2</f>
-        <v>26</v>
-      </c>
-      <c r="H66" s="9"/>
-      <c r="I66" s="9"/>
-      <c r="J66" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="H66" s="8"/>
+      <c r="I66" s="8"/>
+      <c r="J66" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K66" s="11">
+      <c r="K66" s="10">
         <f>'[64]MD10000.1-OCT'!$B$3</f>
         <v>45557</v>
       </c>
-      <c r="L66" s="8">
+      <c r="L66" s="7">
         <f>'[64]MD10000.1-OCT'!$O$2</f>
-        <v>9400</v>
-      </c>
-      <c r="M66" s="8">
+        <v>7800</v>
+      </c>
+      <c r="M66" s="7">
         <f>'[64]MD10000.1-OCT'!$O$1</f>
-        <v>2600</v>
+        <v>4200</v>
       </c>
       <c r="N66" s="1">
         <v>700</v>
@@ -6590,40 +6856,40 @@
       <c r="B67" s="6">
         <v>63</v>
       </c>
-      <c r="C67" s="9" t="s">
+      <c r="C67" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D67" s="15" t="s">
+      <c r="D67" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="E67" s="8">
+      <c r="E67" s="7">
         <f>'[65]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F67" s="9">
+      <c r="F67" s="8">
         <f>'[65]MD10000.1-OCT'!$K$1</f>
-        <v>98</v>
-      </c>
-      <c r="G67" s="9">
+        <v>82</v>
+      </c>
+      <c r="G67" s="8">
         <f>'[65]MD10000.1-OCT'!$K$2</f>
-        <v>22</v>
-      </c>
-      <c r="H67" s="9"/>
-      <c r="I67" s="9"/>
-      <c r="J67" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H67" s="8"/>
+      <c r="I67" s="8"/>
+      <c r="J67" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K67" s="11">
+      <c r="K67" s="10">
         <f>'[65]MD10000.1-OCT'!$B$3</f>
         <v>45561</v>
       </c>
-      <c r="L67" s="8">
+      <c r="L67" s="7">
         <f>'[65]MD10000.1-OCT'!$O$2</f>
-        <v>9800</v>
-      </c>
-      <c r="M67" s="8">
+        <v>8200</v>
+      </c>
+      <c r="M67" s="7">
         <f>'[65]MD10000.1-OCT'!$O$1</f>
-        <v>2200</v>
+        <v>3800</v>
       </c>
       <c r="N67" s="1">
         <v>700</v>
@@ -6633,40 +6899,40 @@
       <c r="B68" s="6">
         <v>64</v>
       </c>
-      <c r="C68" s="14" t="s">
+      <c r="C68" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D68" s="15" t="s">
+      <c r="D68" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E68" s="8">
+      <c r="E68" s="7">
         <f>'[66]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F68" s="9">
+      <c r="F68" s="8">
         <f>'[66]MD20000.18-DEC'!$K$1</f>
-        <v>99</v>
-      </c>
-      <c r="G68" s="9">
+        <v>82</v>
+      </c>
+      <c r="G68" s="8">
         <f>'[66]MD20000.18-DEC'!$K$2</f>
-        <v>21</v>
-      </c>
-      <c r="H68" s="9"/>
-      <c r="I68" s="9"/>
-      <c r="J68" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H68" s="8"/>
+      <c r="I68" s="8"/>
+      <c r="J68" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K68" s="11">
+      <c r="K68" s="10">
         <f>'[66]MD20000.18-DEC'!$B$3</f>
         <v>45562</v>
       </c>
-      <c r="L68" s="8">
+      <c r="L68" s="7">
         <f>'[66]MD20000.18-DEC'!$O$2</f>
-        <v>19800</v>
-      </c>
-      <c r="M68" s="8">
+        <v>16400</v>
+      </c>
+      <c r="M68" s="7">
         <f>'[66]MD20000.18-DEC'!$O$1</f>
-        <v>4200</v>
+        <v>7600</v>
       </c>
       <c r="N68" s="1">
         <v>1400</v>
@@ -6676,40 +6942,40 @@
       <c r="B69" s="6">
         <v>65</v>
       </c>
-      <c r="C69" s="14" t="s">
+      <c r="C69" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D69" s="15" t="s">
+      <c r="D69" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="E69" s="8">
+      <c r="E69" s="7">
         <f>'[67]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F69" s="9">
+      <c r="F69" s="8">
         <f>'[67]MD10000.1-OCT'!$K$1</f>
-        <v>100</v>
-      </c>
-      <c r="G69" s="9">
+        <v>82</v>
+      </c>
+      <c r="G69" s="8">
         <f>'[67]MD10000.1-OCT'!$K$2</f>
-        <v>20</v>
-      </c>
-      <c r="H69" s="9"/>
-      <c r="I69" s="9"/>
-      <c r="J69" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H69" s="8"/>
+      <c r="I69" s="8"/>
+      <c r="J69" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K69" s="11">
+      <c r="K69" s="10">
         <f>'[67]MD10000.1-OCT'!$B$3</f>
         <v>45563</v>
       </c>
-      <c r="L69" s="8">
+      <c r="L69" s="7">
         <f>'[67]MD10000.1-OCT'!$O$2</f>
-        <v>10000</v>
-      </c>
-      <c r="M69" s="8">
+        <v>8200</v>
+      </c>
+      <c r="M69" s="7">
         <f>'[67]MD10000.1-OCT'!$O$1</f>
-        <v>2000</v>
+        <v>3800</v>
       </c>
       <c r="N69" s="1">
         <v>700</v>
@@ -6719,40 +6985,40 @@
       <c r="B70" s="6">
         <v>66</v>
       </c>
-      <c r="C70" s="9" t="s">
+      <c r="C70" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D70" s="15" t="s">
+      <c r="D70" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="E70" s="8">
+      <c r="E70" s="7">
         <f>'[68]MD10000.1-OCT'!$C$1</f>
         <v>15000</v>
       </c>
-      <c r="F70" s="9">
+      <c r="F70" s="8">
         <f>'[68]MD10000.1-OCT'!$K$1</f>
-        <v>111</v>
-      </c>
-      <c r="G70" s="9">
+        <v>103</v>
+      </c>
+      <c r="G70" s="8">
         <f>'[68]MD10000.1-OCT'!$K$2</f>
-        <v>9</v>
-      </c>
-      <c r="H70" s="9"/>
-      <c r="I70" s="9"/>
-      <c r="J70" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H70" s="8"/>
+      <c r="I70" s="8"/>
+      <c r="J70" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K70" s="11">
+      <c r="K70" s="10">
         <f>'[68]MD10000.1-OCT'!$B$3</f>
         <v>45570</v>
       </c>
-      <c r="L70" s="8">
+      <c r="L70" s="7">
         <f>'[68]MD10000.1-OCT'!$O$2</f>
-        <v>16650</v>
-      </c>
-      <c r="M70" s="8">
+        <v>15450</v>
+      </c>
+      <c r="M70" s="7">
         <f>'[68]MD10000.1-OCT'!$O$1</f>
-        <v>1350</v>
+        <v>2550</v>
       </c>
       <c r="N70" s="1">
         <v>1050</v>
@@ -6762,40 +7028,40 @@
       <c r="B71" s="6">
         <v>67</v>
       </c>
-      <c r="C71" s="9" t="s">
+      <c r="C71" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="D71" s="15" t="s">
+      <c r="D71" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="E71" s="8">
+      <c r="E71" s="7">
         <f>'[69]MD20000.18-DEC'!$C$1</f>
         <v>50000</v>
       </c>
-      <c r="F71" s="9">
+      <c r="F71" s="8">
         <f>'[69]MD20000.18-DEC'!$K$1</f>
-        <v>115</v>
-      </c>
-      <c r="G71" s="9">
+        <v>96</v>
+      </c>
+      <c r="G71" s="8">
         <f>'[69]MD20000.18-DEC'!$K$2</f>
-        <v>5</v>
-      </c>
-      <c r="H71" s="9"/>
-      <c r="I71" s="9"/>
-      <c r="J71" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H71" s="8"/>
+      <c r="I71" s="8"/>
+      <c r="J71" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K71" s="11">
+      <c r="K71" s="10">
         <f>'[69]MD20000.18-DEC'!$B$3</f>
         <v>45579</v>
       </c>
-      <c r="L71" s="8">
+      <c r="L71" s="7">
         <f>'[69]MD20000.18-DEC'!$O$2</f>
-        <v>57500</v>
-      </c>
-      <c r="M71" s="8">
+        <v>48000</v>
+      </c>
+      <c r="M71" s="7">
         <f>'[69]MD20000.18-DEC'!$O$1</f>
-        <v>2500</v>
+        <v>12000</v>
       </c>
       <c r="N71" s="1">
         <v>3500</v>
@@ -6805,40 +7071,40 @@
       <c r="B72" s="6">
         <v>68</v>
       </c>
-      <c r="C72" s="9" t="s">
+      <c r="C72" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="D72" s="15" t="s">
+      <c r="D72" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="E72" s="8">
+      <c r="E72" s="7">
         <f>'[70]MD20000.18-DEC'!$C$1</f>
         <v>100000</v>
       </c>
-      <c r="F72" s="9"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="9">
+      <c r="F72" s="8"/>
+      <c r="G72" s="8"/>
+      <c r="H72" s="8">
         <f>'[70]MD20000.18-DEC'!$K$1</f>
-        <v>40</v>
-      </c>
-      <c r="I72" s="9">
+        <v>38</v>
+      </c>
+      <c r="I72" s="8">
         <f>'[70]MD20000.18-DEC'!$K$2</f>
-        <v>0</v>
-      </c>
-      <c r="J72" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="J72" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K72" s="11">
+      <c r="K72" s="10">
         <f>'[70]MD20000.18-DEC'!$B$3</f>
-        <v>0</v>
-      </c>
-      <c r="L72" s="8">
+        <v>45590</v>
+      </c>
+      <c r="L72" s="7">
         <f>'[70]MD20000.18-DEC'!$O$2</f>
-        <v>160000</v>
-      </c>
-      <c r="M72" s="8">
+        <v>152000</v>
+      </c>
+      <c r="M72" s="7">
         <f>'[70]MD20000.18-DEC'!$O$1</f>
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="N72" s="1">
         <v>4000</v>
@@ -6848,40 +7114,40 @@
       <c r="B73" s="6">
         <v>69</v>
       </c>
-      <c r="C73" s="9" t="s">
+      <c r="C73" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D73" s="15" t="s">
+      <c r="D73" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="E73" s="8">
+      <c r="E73" s="7">
         <f>'[71]MD20000.18-DEC'!$C$1</f>
         <v>50000</v>
       </c>
-      <c r="F73" s="9">
+      <c r="F73" s="8">
         <f>'[71]MD20000.18-DEC'!$K$1</f>
-        <v>120</v>
-      </c>
-      <c r="G73" s="9">
+        <v>103</v>
+      </c>
+      <c r="G73" s="8">
         <f>'[71]MD20000.18-DEC'!$K$2</f>
-        <v>0</v>
-      </c>
-      <c r="H73" s="9"/>
-      <c r="I73" s="9"/>
-      <c r="J73" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H73" s="8"/>
+      <c r="I73" s="8"/>
+      <c r="J73" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K73" s="11">
+      <c r="K73" s="10">
         <f>'[71]MD20000.18-DEC'!$B$3</f>
-        <v>0</v>
-      </c>
-      <c r="L73" s="8">
+        <v>45584</v>
+      </c>
+      <c r="L73" s="7">
         <f>'[71]MD20000.18-DEC'!$O$2</f>
-        <v>60000</v>
-      </c>
-      <c r="M73" s="8">
+        <v>51500</v>
+      </c>
+      <c r="M73" s="7">
         <f>'[71]MD20000.18-DEC'!$O$1</f>
-        <v>0</v>
+        <v>8500</v>
       </c>
       <c r="N73" s="1">
         <v>3500</v>
@@ -6891,40 +7157,40 @@
       <c r="B74" s="6">
         <v>70</v>
       </c>
-      <c r="C74" s="9" t="s">
+      <c r="C74" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D74" s="15" t="s">
+      <c r="D74" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="E74" s="8">
+      <c r="E74" s="7">
         <f>'[72]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F74" s="9">
+      <c r="F74" s="8">
         <f>'[72]MD20000.18-DEC'!$K$1</f>
-        <v>120</v>
-      </c>
-      <c r="G74" s="9">
+        <v>103</v>
+      </c>
+      <c r="G74" s="8">
         <f>'[72]MD20000.18-DEC'!$K$2</f>
-        <v>0</v>
-      </c>
-      <c r="H74" s="9"/>
-      <c r="I74" s="9"/>
-      <c r="J74" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H74" s="8"/>
+      <c r="I74" s="8"/>
+      <c r="J74" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K74" s="11">
+      <c r="K74" s="10">
         <f>'[72]MD20000.18-DEC'!$B$3</f>
-        <v>0</v>
-      </c>
-      <c r="L74" s="8">
+        <v>45584</v>
+      </c>
+      <c r="L74" s="7">
         <f>'[72]MD20000.18-DEC'!$O$2</f>
-        <v>24000</v>
-      </c>
-      <c r="M74" s="8">
+        <v>20600</v>
+      </c>
+      <c r="M74" s="7">
         <f>'[72]MD20000.18-DEC'!$O$1</f>
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="N74" s="1">
         <v>1400</v>
@@ -6934,40 +7200,40 @@
       <c r="B75" s="6">
         <v>71</v>
       </c>
-      <c r="C75" s="9" t="s">
+      <c r="C75" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D75" s="15" t="s">
+      <c r="D75" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="E75" s="8">
+      <c r="E75" s="7">
         <f>'[73]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F75" s="9">
+      <c r="F75" s="8">
         <f>'[73]MD20000.18-DEC'!$K$1</f>
-        <v>120</v>
-      </c>
-      <c r="G75" s="9">
+        <v>102</v>
+      </c>
+      <c r="G75" s="8">
         <f>'[73]MD20000.18-DEC'!$K$2</f>
-        <v>0</v>
-      </c>
-      <c r="H75" s="9"/>
-      <c r="I75" s="9"/>
-      <c r="J75" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H75" s="8"/>
+      <c r="I75" s="8"/>
+      <c r="J75" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K75" s="11">
+      <c r="K75" s="10">
         <f>'[73]MD20000.18-DEC'!$B$3</f>
-        <v>0</v>
-      </c>
-      <c r="L75" s="8">
+        <v>45584</v>
+      </c>
+      <c r="L75" s="7">
         <f>'[73]MD20000.18-DEC'!$O$2</f>
-        <v>24000</v>
-      </c>
-      <c r="M75" s="8">
+        <v>20400</v>
+      </c>
+      <c r="M75" s="7">
         <f>'[73]MD20000.18-DEC'!$O$1</f>
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="N75" s="1">
         <v>1400</v>
@@ -6977,40 +7243,40 @@
       <c r="B76" s="6">
         <v>72</v>
       </c>
-      <c r="C76" s="9" t="s">
+      <c r="C76" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D76" s="15" t="s">
+      <c r="D76" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="E76" s="8">
+      <c r="E76" s="7">
         <f>'[74]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F76" s="9">
+      <c r="F76" s="8">
         <f>'[74]MD20000.18-DEC'!$K$1</f>
-        <v>120</v>
-      </c>
-      <c r="G76" s="9">
+        <v>103</v>
+      </c>
+      <c r="G76" s="8">
         <f>'[74]MD20000.18-DEC'!$K$2</f>
-        <v>0</v>
-      </c>
-      <c r="H76" s="9"/>
-      <c r="I76" s="9"/>
-      <c r="J76" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H76" s="8"/>
+      <c r="I76" s="8"/>
+      <c r="J76" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K76" s="11">
+      <c r="K76" s="10">
         <f>'[74]MD20000.18-DEC'!$B$3</f>
-        <v>0</v>
-      </c>
-      <c r="L76" s="8">
+        <v>45584</v>
+      </c>
+      <c r="L76" s="7">
         <f>'[74]MD20000.18-DEC'!$O$2</f>
-        <v>24000</v>
-      </c>
-      <c r="M76" s="8">
+        <v>20600</v>
+      </c>
+      <c r="M76" s="7">
         <f>'[74]MD20000.18-DEC'!$O$1</f>
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="N76" s="1">
         <v>1400</v>
@@ -7020,40 +7286,40 @@
       <c r="B77" s="6">
         <v>73</v>
       </c>
-      <c r="C77" s="9" t="s">
+      <c r="C77" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D77" s="15" t="s">
+      <c r="D77" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="E77" s="8">
+      <c r="E77" s="7">
         <f>'[75]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F77" s="9">
+      <c r="F77" s="8">
         <f>'[75]MD20000.18-DEC'!$K$1</f>
-        <v>120</v>
-      </c>
-      <c r="G77" s="9">
+        <v>106</v>
+      </c>
+      <c r="G77" s="8">
         <f>'[75]MD20000.18-DEC'!$K$2</f>
-        <v>0</v>
-      </c>
-      <c r="H77" s="9"/>
-      <c r="I77" s="9"/>
-      <c r="J77" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H77" s="8"/>
+      <c r="I77" s="8"/>
+      <c r="J77" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K77" s="11">
-        <f>'[75]MD20000.18-DEC'!$B$3</f>
-        <v>0</v>
-      </c>
-      <c r="L77" s="8">
+      <c r="K77" s="10">
+        <f>'[75]MD20000.18-DEC'!$B$7</f>
+        <v>45587</v>
+      </c>
+      <c r="L77" s="7">
         <f>'[75]MD20000.18-DEC'!$O$2</f>
-        <v>24000</v>
-      </c>
-      <c r="M77" s="8">
+        <v>21200</v>
+      </c>
+      <c r="M77" s="7">
         <f>'[75]MD20000.18-DEC'!$O$1</f>
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="N77" s="1">
         <v>1400</v>
@@ -7063,40 +7329,40 @@
       <c r="B78" s="6">
         <v>74</v>
       </c>
-      <c r="C78" s="9" t="s">
+      <c r="C78" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="D78" s="15" t="s">
+      <c r="D78" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="E78" s="8">
+      <c r="E78" s="7">
         <f>'[76]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F78" s="9">
+      <c r="F78" s="8">
         <f>'[76]MD20000.18-DEC'!$K$1</f>
-        <v>120</v>
-      </c>
-      <c r="G78" s="9">
+        <v>110</v>
+      </c>
+      <c r="G78" s="8">
         <f>'[76]MD20000.18-DEC'!$K$2</f>
-        <v>0</v>
-      </c>
-      <c r="H78" s="9"/>
-      <c r="I78" s="9"/>
-      <c r="J78" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H78" s="8"/>
+      <c r="I78" s="8"/>
+      <c r="J78" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K78" s="11">
+      <c r="K78" s="10">
         <f>'[76]MD20000.18-DEC'!$B$3</f>
-        <v>0</v>
-      </c>
-      <c r="L78" s="8">
+        <v>45584</v>
+      </c>
+      <c r="L78" s="7">
         <f>'[76]MD20000.18-DEC'!$O$2</f>
-        <v>12000</v>
-      </c>
-      <c r="M78" s="8">
+        <v>11000</v>
+      </c>
+      <c r="M78" s="7">
         <f>'[76]MD20000.18-DEC'!$O$1</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="N78" s="1">
         <v>700</v>
@@ -7106,184 +7372,329 @@
       <c r="B79" s="6">
         <v>75</v>
       </c>
-      <c r="C79" s="9" t="s">
+      <c r="C79" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D79" s="15" t="s">
+      <c r="D79" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="E79" s="8">
+      <c r="E79" s="7">
         <f>'[77]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F79" s="9">
+      <c r="F79" s="8">
         <f>'[77]MD20000.18-DEC'!$K$1</f>
-        <v>120</v>
-      </c>
-      <c r="G79" s="9">
+        <v>101</v>
+      </c>
+      <c r="G79" s="8">
         <f>'[77]MD20000.18-DEC'!$K$2</f>
-        <v>0</v>
-      </c>
-      <c r="H79" s="9"/>
-      <c r="I79" s="9"/>
-      <c r="J79" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H79" s="8"/>
+      <c r="I79" s="8"/>
+      <c r="J79" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K79" s="11">
+      <c r="K79" s="10">
         <f>'[77]MD20000.18-DEC'!$B$3</f>
-        <v>0</v>
-      </c>
-      <c r="L79" s="8">
+        <v>45584</v>
+      </c>
+      <c r="L79" s="7">
         <f>'[77]MD20000.18-DEC'!$O$2</f>
-        <v>12000</v>
-      </c>
-      <c r="M79" s="8">
+        <v>10100</v>
+      </c>
+      <c r="M79" s="7">
         <f>'[77]MD20000.18-DEC'!$O$1</f>
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="N79" s="1">
         <v>700</v>
       </c>
     </row>
     <row r="80" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="6"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="15"/>
-      <c r="E80" s="8"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="9"/>
-      <c r="H80" s="9"/>
-      <c r="I80" s="9"/>
-      <c r="J80" s="10"/>
-      <c r="K80" s="11"/>
-      <c r="L80" s="8"/>
-      <c r="M80" s="8"/>
-    </row>
-    <row r="81" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="6"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="15"/>
-      <c r="E81" s="8"/>
-      <c r="F81" s="9"/>
-      <c r="G81" s="9"/>
-      <c r="H81" s="9"/>
-      <c r="I81" s="9"/>
-      <c r="J81" s="10"/>
-      <c r="K81" s="11"/>
-      <c r="L81" s="8"/>
-      <c r="M81" s="8"/>
-    </row>
-    <row r="82" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="6"/>
-      <c r="C82" s="9"/>
-      <c r="D82" s="15"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="9"/>
-      <c r="G82" s="9"/>
-      <c r="H82" s="9"/>
-      <c r="I82" s="9"/>
-      <c r="J82" s="10"/>
-      <c r="K82" s="11"/>
-      <c r="L82" s="8"/>
-      <c r="M82" s="8"/>
-    </row>
-    <row r="83" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B83" s="6"/>
-      <c r="C83" s="9"/>
-      <c r="D83" s="15"/>
-      <c r="E83" s="8"/>
-      <c r="F83" s="9"/>
-      <c r="G83" s="9"/>
-      <c r="H83" s="9"/>
-      <c r="I83" s="9"/>
-      <c r="J83" s="10"/>
-      <c r="K83" s="11"/>
-      <c r="L83" s="8"/>
-      <c r="M83" s="8"/>
-    </row>
-    <row r="84" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B84" s="6"/>
-      <c r="C84" s="9"/>
-      <c r="D84" s="15"/>
-      <c r="E84" s="8"/>
-      <c r="F84" s="9"/>
-      <c r="G84" s="9"/>
-      <c r="H84" s="9"/>
-      <c r="I84" s="9"/>
-      <c r="J84" s="10"/>
-      <c r="K84" s="11"/>
-      <c r="L84" s="8"/>
-      <c r="M84" s="8"/>
-    </row>
-    <row r="85" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B80" s="6">
+        <v>76</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D80" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E80" s="7">
+        <f>'[78]MD20000.18-DEC'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F80" s="8">
+        <f>'[78]MD20000.18-DEC'!$K$1</f>
+        <v>106</v>
+      </c>
+      <c r="G80" s="8">
+        <f>'[78]MD20000.18-DEC'!$K$2</f>
+        <v>14</v>
+      </c>
+      <c r="H80" s="8"/>
+      <c r="I80" s="8"/>
+      <c r="J80" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K80" s="10">
+        <f>'[78]MD20000.18-DEC'!$B$3</f>
+        <v>45587</v>
+      </c>
+      <c r="L80" s="7">
+        <f>'[78]MD20000.18-DEC'!$O$2</f>
+        <v>10600</v>
+      </c>
+      <c r="M80" s="7">
+        <f>'[78]MD20000.18-DEC'!$O$1</f>
+        <v>1400</v>
+      </c>
+      <c r="N80" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="81" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B81" s="6">
+        <v>77</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D81" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E81" s="7">
+        <f>'[79]MD20000.15-DEc'!$C$1</f>
+        <v>20000</v>
+      </c>
+      <c r="F81" s="8"/>
+      <c r="G81" s="8"/>
+      <c r="H81" s="8">
+        <f>'[79]MD20000.15-DEc'!$K$1</f>
+        <v>16</v>
+      </c>
+      <c r="I81" s="8">
+        <f>'[79]MD20000.15-DEc'!$K$2</f>
+        <v>1</v>
+      </c>
+      <c r="J81" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K81" s="10">
+        <f>'[79]MD20000.15-DEc'!$B$3</f>
+        <v>45595</v>
+      </c>
+      <c r="L81" s="7">
+        <f>'[79]MD20000.15-DEc'!$O$2</f>
+        <v>22400</v>
+      </c>
+      <c r="M81" s="7">
+        <f>'[79]MD20000.15-DEc'!$O$1</f>
+        <v>1600</v>
+      </c>
+      <c r="N81" s="1">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="82" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B82" s="6">
+        <v>78</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D82" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="E82" s="7">
+        <f>'[80]MD10000.10-JAN'!$C$1</f>
+        <v>20000</v>
+      </c>
+      <c r="F82" s="8"/>
+      <c r="G82" s="8"/>
+      <c r="H82" s="8">
+        <f>'[80]MD10000.10-JAN'!$K$1</f>
+        <v>16</v>
+      </c>
+      <c r="I82" s="8">
+        <f>'[80]MD10000.10-JAN'!$K$2</f>
+        <v>1</v>
+      </c>
+      <c r="J82" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K82" s="10">
+        <f>'[80]MD10000.10-JAN'!$B$3</f>
+        <v>45571</v>
+      </c>
+      <c r="L82" s="7">
+        <f>'[80]MD10000.10-JAN'!$O$2</f>
+        <v>22400</v>
+      </c>
+      <c r="M82" s="7">
+        <f>'[80]MD10000.10-JAN'!$O$1</f>
+        <v>1600</v>
+      </c>
+      <c r="N82" s="1">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="83" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B83" s="6">
+        <v>79</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D83" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E83" s="7">
+        <f>'[81]MD20000.22-DEC'!$C$1</f>
+        <v>20000</v>
+      </c>
+      <c r="F83" s="8">
+        <f>'[81]MD20000.22-DEC'!$K$1</f>
+        <v>116</v>
+      </c>
+      <c r="G83" s="8">
+        <f>'[81]MD20000.22-DEC'!$K$2</f>
+        <v>4</v>
+      </c>
+      <c r="H83" s="8"/>
+      <c r="I83" s="8"/>
+      <c r="J83" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K83" s="10">
+        <f>'[81]MD20000.22-DEC'!$B$3</f>
+        <v>45597</v>
+      </c>
+      <c r="L83" s="7">
+        <f>'[81]MD20000.22-DEC'!$O$2</f>
+        <v>23200</v>
+      </c>
+      <c r="M83" s="7">
+        <f>'[81]MD20000.22-DEC'!$O$1</f>
+        <v>800</v>
+      </c>
+      <c r="N83" s="1">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="84" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B84" s="6">
+        <v>80</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D84" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E84" s="7">
+        <f>'[82]MD20000.18-DEC'!$C$1</f>
+        <v>30000</v>
+      </c>
+      <c r="F84" s="8">
+        <f>'[82]MD20000.18-DEC'!$K$1</f>
+        <v>119</v>
+      </c>
+      <c r="G84" s="8">
+        <f>'[82]MD20000.18-DEC'!$K$2</f>
+        <v>1</v>
+      </c>
+      <c r="H84" s="8"/>
+      <c r="I84" s="8"/>
+      <c r="J84" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K84" s="10">
+        <f>'[82]MD20000.18-DEC'!$B$3</f>
+        <v>45602</v>
+      </c>
+      <c r="L84" s="7">
+        <f>'[82]MD20000.18-DEC'!$O$2</f>
+        <v>35700</v>
+      </c>
+      <c r="M84" s="7">
+        <f>'[82]MD20000.18-DEC'!$O$1</f>
+        <v>300</v>
+      </c>
+      <c r="N84" s="1">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="85" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B85" s="6"/>
-      <c r="C85" s="9"/>
-      <c r="D85" s="15"/>
-      <c r="E85" s="8"/>
-      <c r="F85" s="9"/>
-      <c r="G85" s="9"/>
-      <c r="H85" s="9"/>
-      <c r="I85" s="9"/>
-      <c r="J85" s="10"/>
-      <c r="K85" s="11"/>
-      <c r="L85" s="8"/>
-      <c r="M85" s="8"/>
-    </row>
-    <row r="86" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C85" s="8"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="7"/>
+      <c r="F85" s="8"/>
+      <c r="G85" s="8"/>
+      <c r="H85" s="8"/>
+      <c r="I85" s="8"/>
+      <c r="J85" s="9"/>
+      <c r="K85" s="10"/>
+      <c r="L85" s="7"/>
+      <c r="M85" s="7"/>
+    </row>
+    <row r="86" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B86" s="6"/>
-      <c r="C86" s="9"/>
-      <c r="D86" s="15"/>
-      <c r="E86" s="8"/>
-      <c r="F86" s="9"/>
-      <c r="G86" s="9"/>
-      <c r="H86" s="9"/>
-      <c r="I86" s="9"/>
-      <c r="J86" s="10"/>
-      <c r="K86" s="11"/>
-      <c r="L86" s="8"/>
-      <c r="M86" s="8"/>
-    </row>
-    <row r="87" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C86" s="8"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="8"/>
+      <c r="G86" s="8"/>
+      <c r="H86" s="8"/>
+      <c r="I86" s="8"/>
+      <c r="J86" s="9"/>
+      <c r="K86" s="10"/>
+      <c r="L86" s="7"/>
+      <c r="M86" s="7"/>
+    </row>
+    <row r="87" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B87" s="6"/>
-      <c r="C87" s="9"/>
-      <c r="D87" s="15"/>
-      <c r="E87" s="8"/>
-      <c r="F87" s="9"/>
-      <c r="G87" s="9"/>
-      <c r="H87" s="9"/>
-      <c r="I87" s="9"/>
-      <c r="J87" s="10"/>
-      <c r="K87" s="11"/>
-      <c r="L87" s="8"/>
-      <c r="M87" s="8"/>
-    </row>
-    <row r="88" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C87" s="8"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="8"/>
+      <c r="G87" s="8"/>
+      <c r="H87" s="8"/>
+      <c r="I87" s="8"/>
+      <c r="J87" s="9"/>
+      <c r="K87" s="10"/>
+      <c r="L87" s="7"/>
+      <c r="M87" s="7"/>
+    </row>
+    <row r="88" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B88" s="6"/>
-      <c r="C88" s="9"/>
-      <c r="D88" s="15"/>
-      <c r="E88" s="8"/>
-      <c r="F88" s="9"/>
-      <c r="G88" s="9"/>
-      <c r="H88" s="9"/>
-      <c r="I88" s="9"/>
-      <c r="J88" s="10"/>
-      <c r="K88" s="11"/>
-      <c r="L88" s="8"/>
-      <c r="M88" s="8"/>
-    </row>
-    <row r="89" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C88" s="8"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="7"/>
+      <c r="F88" s="8"/>
+      <c r="G88" s="8"/>
+      <c r="H88" s="8"/>
+      <c r="I88" s="8"/>
+      <c r="J88" s="9"/>
+      <c r="K88" s="10"/>
+      <c r="L88" s="7"/>
+      <c r="M88" s="7"/>
+    </row>
+    <row r="89" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B89" s="6"/>
-      <c r="C89" s="9"/>
-      <c r="D89" s="15"/>
-      <c r="E89" s="8"/>
-      <c r="F89" s="9"/>
-      <c r="G89" s="9"/>
-      <c r="H89" s="9"/>
-      <c r="I89" s="9"/>
-      <c r="J89" s="10"/>
-      <c r="K89" s="11"/>
-      <c r="L89" s="8"/>
-      <c r="M89" s="8"/>
+      <c r="C89" s="8"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="7"/>
+      <c r="F89" s="8"/>
+      <c r="G89" s="8"/>
+      <c r="H89" s="8"/>
+      <c r="I89" s="8"/>
+      <c r="J89" s="9"/>
+      <c r="K89" s="10"/>
+      <c r="L89" s="7"/>
+      <c r="M89" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/LoanOfficer-A/LoanBook.xlsx
+++ b/LoanOfficer-A/LoanBook.xlsx
@@ -92,13 +92,16 @@
     <externalReference r:id="rId81"/>
     <externalReference r:id="rId82"/>
     <externalReference r:id="rId83"/>
+    <externalReference r:id="rId84"/>
+    <externalReference r:id="rId85"/>
+    <externalReference r:id="rId86"/>
   </externalReferences>
   <calcPr calcId="145621" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="112">
   <si>
     <t>Code</t>
   </si>
@@ -425,6 +428,15 @@
   </si>
   <si>
     <t>Haobijam joyshree</t>
+  </si>
+  <si>
+    <t>L50000P120</t>
+  </si>
+  <si>
+    <t>Takhellambam  kiranmala</t>
+  </si>
+  <si>
+    <t>L100000D267</t>
   </si>
 </sst>
 </file>
@@ -623,6 +635,24 @@
     <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -642,24 +672,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -979,18 +991,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>5</v>
-          </cell>
-          <cell r="O1">
-            <v>15050</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>43</v>
-          </cell>
-          <cell r="O2">
-            <v>1750</v>
+            <v>3</v>
+          </cell>
+          <cell r="O1">
+            <v>15750</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>45</v>
+          </cell>
+          <cell r="O2">
+            <v>1050</v>
           </cell>
         </row>
         <row r="3">
@@ -1744,15 +1756,15 @@
             <v>48</v>
           </cell>
           <cell r="O1">
-            <v>10500</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>30</v>
-          </cell>
-          <cell r="O2">
-            <v>6300</v>
+            <v>11200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>32</v>
+          </cell>
+          <cell r="O2">
+            <v>5600</v>
           </cell>
         </row>
         <row r="3">
@@ -1897,15 +1909,15 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="2">
           <cell r="O2">
-            <v>46200</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2543,25 +2555,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>13</v>
-          </cell>
-          <cell r="O1">
-            <v>5800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>4</v>
-          </cell>
-          <cell r="O2">
-            <v>18200</v>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -2570,7 +2582,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2631,18 +2643,18 @@
             <v>30000</v>
           </cell>
           <cell r="K1">
-            <v>24</v>
-          </cell>
-          <cell r="O1">
-            <v>28800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>96</v>
-          </cell>
-          <cell r="O2">
-            <v>7200</v>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>36000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -2712,18 +2724,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>6</v>
-          </cell>
-          <cell r="O1">
-            <v>15600</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>11</v>
-          </cell>
-          <cell r="O2">
-            <v>8400</v>
+            <v>3</v>
+          </cell>
+          <cell r="O1">
+            <v>19800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>14</v>
+          </cell>
+          <cell r="O2">
+            <v>4200</v>
           </cell>
         </row>
         <row r="3">
@@ -2754,18 +2766,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>7</v>
-          </cell>
-          <cell r="O1">
-            <v>7100</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>10</v>
-          </cell>
-          <cell r="O2">
-            <v>4900</v>
+            <v>5</v>
+          </cell>
+          <cell r="O1">
+            <v>8500</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>12</v>
+          </cell>
+          <cell r="O2">
+            <v>3500</v>
           </cell>
         </row>
         <row r="3">
@@ -2788,7 +2800,7 @@
       <sheetName val="MD10000.20-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -2836,18 +2848,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>7</v>
-          </cell>
-          <cell r="O1">
-            <v>7100</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>10</v>
-          </cell>
-          <cell r="O2">
-            <v>4900</v>
+            <v>4</v>
+          </cell>
+          <cell r="O1">
+            <v>9200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>13</v>
+          </cell>
+          <cell r="O2">
+            <v>2800</v>
           </cell>
         </row>
         <row r="3">
@@ -2870,7 +2882,7 @@
       <sheetName val="MD10000.20-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -2990,7 +3002,7 @@
       <sheetName val="MD10000.20-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -3037,18 +3049,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>72</v>
-          </cell>
-          <cell r="O1">
-            <v>9600</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>48</v>
-          </cell>
-          <cell r="O2">
-            <v>14400</v>
+            <v>59</v>
+          </cell>
+          <cell r="O1">
+            <v>12200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>61</v>
+          </cell>
+          <cell r="O2">
+            <v>11800</v>
           </cell>
         </row>
         <row r="13">
@@ -3077,18 +3089,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>77</v>
-          </cell>
-          <cell r="O1">
-            <v>4300</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>43</v>
-          </cell>
-          <cell r="O2">
-            <v>7700</v>
+            <v>65</v>
+          </cell>
+          <cell r="O1">
+            <v>5500</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>55</v>
+          </cell>
+          <cell r="O2">
+            <v>6500</v>
           </cell>
         </row>
         <row r="3">
@@ -3117,18 +3129,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>78</v>
-          </cell>
-          <cell r="O1">
-            <v>4200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>42</v>
-          </cell>
-          <cell r="O2">
-            <v>7800</v>
+            <v>65</v>
+          </cell>
+          <cell r="O1">
+            <v>5500</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>55</v>
+          </cell>
+          <cell r="O2">
+            <v>6500</v>
           </cell>
         </row>
         <row r="3">
@@ -3157,18 +3169,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>82</v>
-          </cell>
-          <cell r="O1">
-            <v>3800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>38</v>
-          </cell>
-          <cell r="O2">
-            <v>8200</v>
+            <v>54</v>
+          </cell>
+          <cell r="O1">
+            <v>6600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>66</v>
+          </cell>
+          <cell r="O2">
+            <v>5400</v>
           </cell>
         </row>
         <row r="3">
@@ -3197,18 +3209,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>82</v>
-          </cell>
-          <cell r="O1">
-            <v>7600</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>38</v>
-          </cell>
-          <cell r="O2">
-            <v>16400</v>
+            <v>70</v>
+          </cell>
+          <cell r="O1">
+            <v>10000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>50</v>
+          </cell>
+          <cell r="O2">
+            <v>14000</v>
           </cell>
         </row>
         <row r="3">
@@ -3237,18 +3249,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>82</v>
-          </cell>
-          <cell r="O1">
-            <v>3800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>38</v>
-          </cell>
-          <cell r="O2">
-            <v>8200</v>
+            <v>69</v>
+          </cell>
+          <cell r="O1">
+            <v>5100</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>51</v>
+          </cell>
+          <cell r="O2">
+            <v>6900</v>
           </cell>
         </row>
         <row r="3">
@@ -3277,18 +3289,18 @@
             <v>15000</v>
           </cell>
           <cell r="K1">
-            <v>103</v>
-          </cell>
-          <cell r="O1">
-            <v>2550</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>15450</v>
+            <v>90</v>
+          </cell>
+          <cell r="O1">
+            <v>4500</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>30</v>
+          </cell>
+          <cell r="O2">
+            <v>13500</v>
           </cell>
         </row>
         <row r="3">
@@ -3317,18 +3329,18 @@
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>96</v>
-          </cell>
-          <cell r="O1">
-            <v>12000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>24</v>
-          </cell>
-          <cell r="O2">
-            <v>48000</v>
+            <v>81</v>
+          </cell>
+          <cell r="O1">
+            <v>19500</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>39</v>
+          </cell>
+          <cell r="O2">
+            <v>40500</v>
           </cell>
         </row>
         <row r="3">
@@ -3399,18 +3411,18 @@
             <v>100000</v>
           </cell>
           <cell r="K1">
-            <v>38</v>
-          </cell>
-          <cell r="O1">
-            <v>8000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>2</v>
-          </cell>
-          <cell r="O2">
-            <v>152000</v>
+            <v>35</v>
+          </cell>
+          <cell r="O1">
+            <v>20000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>5</v>
+          </cell>
+          <cell r="O2">
+            <v>140000</v>
           </cell>
         </row>
         <row r="3">
@@ -3439,18 +3451,18 @@
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>103</v>
-          </cell>
-          <cell r="O1">
-            <v>8500</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>51500</v>
+            <v>86</v>
+          </cell>
+          <cell r="O1">
+            <v>17000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>34</v>
+          </cell>
+          <cell r="O2">
+            <v>43000</v>
           </cell>
         </row>
         <row r="3">
@@ -3479,18 +3491,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>103</v>
-          </cell>
-          <cell r="O1">
-            <v>3400</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>20600</v>
+            <v>91</v>
+          </cell>
+          <cell r="O1">
+            <v>5800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>29</v>
+          </cell>
+          <cell r="O2">
+            <v>18200</v>
           </cell>
         </row>
         <row r="3">
@@ -3519,18 +3531,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>102</v>
-          </cell>
-          <cell r="O1">
-            <v>3600</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>18</v>
-          </cell>
-          <cell r="O2">
-            <v>20400</v>
+            <v>93</v>
+          </cell>
+          <cell r="O1">
+            <v>5400</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>27</v>
+          </cell>
+          <cell r="O2">
+            <v>18600</v>
           </cell>
         </row>
         <row r="3">
@@ -3559,18 +3571,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>103</v>
-          </cell>
-          <cell r="O1">
-            <v>3400</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>20600</v>
+            <v>91</v>
+          </cell>
+          <cell r="O1">
+            <v>5800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>29</v>
+          </cell>
+          <cell r="O2">
+            <v>18200</v>
           </cell>
         </row>
         <row r="3">
@@ -3599,18 +3611,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>106</v>
-          </cell>
-          <cell r="O1">
-            <v>2800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>14</v>
-          </cell>
-          <cell r="O2">
-            <v>21200</v>
+            <v>86</v>
+          </cell>
+          <cell r="O1">
+            <v>6800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>34</v>
+          </cell>
+          <cell r="O2">
+            <v>17200</v>
           </cell>
         </row>
         <row r="7">
@@ -3639,18 +3651,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>110</v>
-          </cell>
-          <cell r="O1">
-            <v>1000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>10</v>
-          </cell>
-          <cell r="O2">
-            <v>11000</v>
+            <v>109</v>
+          </cell>
+          <cell r="O1">
+            <v>1100</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>11</v>
+          </cell>
+          <cell r="O2">
+            <v>10900</v>
           </cell>
         </row>
         <row r="3">
@@ -3679,18 +3691,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>101</v>
-          </cell>
-          <cell r="O1">
-            <v>1900</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>19</v>
-          </cell>
-          <cell r="O2">
-            <v>10100</v>
+            <v>95</v>
+          </cell>
+          <cell r="O1">
+            <v>2500</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>25</v>
+          </cell>
+          <cell r="O2">
+            <v>9500</v>
           </cell>
         </row>
         <row r="3">
@@ -3717,18 +3729,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>106</v>
-          </cell>
-          <cell r="O1">
-            <v>1400</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>14</v>
-          </cell>
-          <cell r="O2">
-            <v>10600</v>
+            <v>94</v>
+          </cell>
+          <cell r="O1">
+            <v>2600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>26</v>
+          </cell>
+          <cell r="O2">
+            <v>9400</v>
           </cell>
         </row>
         <row r="3">
@@ -3758,18 +3770,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>16</v>
-          </cell>
-          <cell r="O1">
-            <v>1600</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>1</v>
-          </cell>
-          <cell r="O2">
-            <v>22400</v>
+            <v>13</v>
+          </cell>
+          <cell r="O1">
+            <v>5800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>4</v>
+          </cell>
+          <cell r="O2">
+            <v>18200</v>
           </cell>
         </row>
         <row r="3">
@@ -3842,23 +3854,23 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>16</v>
-          </cell>
-          <cell r="O1">
-            <v>1600</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>1</v>
-          </cell>
-          <cell r="O2">
-            <v>22400</v>
+            <v>14</v>
+          </cell>
+          <cell r="O1">
+            <v>4400</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>3</v>
+          </cell>
+          <cell r="O2">
+            <v>19600</v>
           </cell>
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45571</v>
+            <v>45602</v>
           </cell>
         </row>
       </sheetData>
@@ -3883,18 +3895,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>116</v>
-          </cell>
-          <cell r="O1">
-            <v>800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>4</v>
-          </cell>
-          <cell r="O2">
-            <v>23200</v>
+            <v>104</v>
+          </cell>
+          <cell r="O1">
+            <v>3200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>16</v>
+          </cell>
+          <cell r="O2">
+            <v>20800</v>
           </cell>
         </row>
         <row r="3">
@@ -3923,18 +3935,18 @@
             <v>30000</v>
           </cell>
           <cell r="K1">
-            <v>119</v>
-          </cell>
-          <cell r="O1">
-            <v>300</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>1</v>
-          </cell>
-          <cell r="O2">
-            <v>35700</v>
+            <v>107</v>
+          </cell>
+          <cell r="O1">
+            <v>3900</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>13</v>
+          </cell>
+          <cell r="O2">
+            <v>32100</v>
           </cell>
         </row>
         <row r="3">
@@ -3943,6 +3955,128 @@
           </cell>
         </row>
       </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink83.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>50000</v>
+          </cell>
+          <cell r="K1">
+            <v>108</v>
+          </cell>
+          <cell r="O1">
+            <v>6000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>12</v>
+          </cell>
+          <cell r="O2">
+            <v>54000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45612</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink84.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>113</v>
+          </cell>
+          <cell r="O1">
+            <v>700</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>7</v>
+          </cell>
+          <cell r="O2">
+            <v>11300</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45612</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink85.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD50000.15-DEC"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>100000</v>
+          </cell>
+          <cell r="K1">
+            <v>264</v>
+          </cell>
+          <cell r="O1">
+            <v>1800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>3</v>
+          </cell>
+          <cell r="O2">
+            <v>158400</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45619</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4245,7 +4379,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4277,23 +4411,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="I2" s="19" t="s">
+      <c r="C2" s="29"/>
+      <c r="I2" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="20"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="17">
+      <c r="J2" s="26"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="23">
         <f>SUM(L5:L97)</f>
-        <v>645700</v>
-      </c>
-      <c r="M2" s="18"/>
+        <v>721650</v>
+      </c>
+      <c r="M2" s="24"/>
       <c r="N2" s="1">
         <f>SUM(N5:N106)</f>
-        <v>38650</v>
+        <v>43550</v>
       </c>
       <c r="Q2" s="1">
         <f>14900+260750</f>
@@ -4349,598 +4483,598 @@
       </c>
     </row>
     <row r="5" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="24">
+      <c r="B5" s="17">
         <v>1</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="19">
         <f>'[1]SM5000.1-SEPT'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="20">
         <f>'[1]SM5000.1-SEPT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="20">
         <f>'[1]SM5000.1-SEPT'!$K$2</f>
         <v>60</v>
       </c>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="28" t="s">
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="K5" s="29">
+      <c r="K5" s="22">
         <f>'[1]SM5000.1-SEPT'!$B$3</f>
         <v>45180</v>
       </c>
-      <c r="L5" s="26">
+      <c r="L5" s="19">
         <f>'[1]SM5000.1-SEPT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M5" s="26">
+      <c r="M5" s="19">
         <f>'[1]SM5000.1-SEPT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
     <row r="6" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="24">
+      <c r="B6" s="17">
         <v>2</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="19">
         <f>'[1]SM5000.1-oct'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="20">
         <f>'[1]SM5000.1-oct'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="20">
         <f>'[1]SM5000.1-oct'!$K$2</f>
         <v>60</v>
       </c>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="28" t="s">
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="K6" s="29">
+      <c r="K6" s="22">
         <f>'[1]SM5000.1-oct'!$B$3</f>
         <v>45201</v>
       </c>
-      <c r="L6" s="26">
+      <c r="L6" s="19">
         <f>'[1]SM5000.1-oct'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M6" s="26">
+      <c r="M6" s="19">
         <f>'[1]SM5000.1-oct'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
     <row r="7" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="24">
+      <c r="B7" s="17">
         <v>3</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="19">
         <f>'[2]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="20">
         <f>'[2]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="20">
         <f>'[2]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="28" t="s">
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="29">
+      <c r="K7" s="22">
         <f>'[2]MD10000.1-OCT'!$B$3</f>
         <v>45212</v>
       </c>
-      <c r="L7" s="26">
+      <c r="L7" s="19">
         <f>'[2]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M7" s="26">
+      <c r="M7" s="19">
         <f>'[2]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
     <row r="8" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="24">
+      <c r="B8" s="17">
         <v>4</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="19">
         <f>'[3]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="20">
         <f>'[3]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="20">
         <f>'[3]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="28" t="s">
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="29">
+      <c r="K8" s="22">
         <f>'[3]MD10000.1-OCT'!$B$3</f>
         <v>45213</v>
       </c>
-      <c r="L8" s="26">
+      <c r="L8" s="19">
         <f>'[3]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M8" s="26">
+      <c r="M8" s="19">
         <f>'[3]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
     <row r="9" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="24">
+      <c r="B9" s="17">
         <v>5</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D9" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="19">
         <f>'[4]MD10000.20-OCT'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27">
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20">
         <f>'[4]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I9" s="27">
+      <c r="I9" s="20">
         <f>'[4]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J9" s="28" t="s">
+      <c r="J9" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K9" s="29">
+      <c r="K9" s="22">
         <f>'[4]MD10000.20-OCT'!$B$3</f>
         <v>45226</v>
       </c>
-      <c r="L9" s="26">
+      <c r="L9" s="19">
         <f>'[4]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M9" s="26">
+      <c r="M9" s="19">
         <f>'[4]MD10000.20-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
     <row r="10" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="24">
+      <c r="B10" s="17">
         <v>6</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="19">
         <f>'[5]SM5000.1-SEPT (2)'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="20">
         <f>'[5]SM5000.1-SEPT (2)'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="20">
         <f>'[5]SM5000.1-SEPT (2)'!$K$2</f>
         <v>60</v>
       </c>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="28" t="s">
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="K10" s="29">
+      <c r="K10" s="22">
         <f>'[5]SM5000.1-SEPT (2)'!$B$3</f>
         <v>45243</v>
       </c>
-      <c r="L10" s="26">
+      <c r="L10" s="19">
         <f>'[5]SM5000.1-SEPT (2)'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M10" s="26">
+      <c r="M10" s="19">
         <f>'[5]SM5000.1-SEPT (2)'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
     <row r="11" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="24">
+      <c r="B11" s="17">
         <v>7</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="19">
         <f>'[6]MD10000.20-OCT'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27">
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20">
         <f>'[6]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="20">
         <f>'[6]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J11" s="28" t="s">
+      <c r="J11" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K11" s="29">
+      <c r="K11" s="22">
         <f>'[6]MD10000.20-OCT'!$B$3</f>
         <v>45245</v>
       </c>
-      <c r="L11" s="26">
+      <c r="L11" s="19">
         <f>'[6]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M11" s="26">
+      <c r="M11" s="19">
         <f>'[6]MD10000.20-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
     <row r="12" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="24">
+      <c r="B12" s="17">
         <v>8</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="D12" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="19">
         <f>'[7]MD15000.27-NOV'!$C$1</f>
         <v>15000</v>
       </c>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27">
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20">
         <f>'[7]MD15000.27-NOV'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I12" s="27">
+      <c r="I12" s="20">
         <f>'[7]MD15000.27-NOV'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J12" s="28" t="s">
+      <c r="J12" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K12" s="29">
+      <c r="K12" s="22">
         <f>'[7]MD15000.27-NOV'!$B$3</f>
         <v>45266</v>
       </c>
-      <c r="L12" s="26">
+      <c r="L12" s="19">
         <f>'[7]MD15000.27-NOV'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M12" s="26">
+      <c r="M12" s="19">
         <f>'[7]MD15000.27-NOV'!$O$1</f>
         <v>18000</v>
       </c>
     </row>
     <row r="13" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="24">
+      <c r="B13" s="17">
         <v>9</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="19">
         <f>'[8]MD20000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27">
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20">
         <f>'[8]MD20000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I13" s="27">
+      <c r="I13" s="20">
         <f>'[8]MD20000.15-DEC'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J13" s="28" t="s">
+      <c r="J13" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K13" s="29">
+      <c r="K13" s="22">
         <f>'[8]MD20000.15-DEC'!$B$3</f>
         <v>45649</v>
       </c>
-      <c r="L13" s="26">
+      <c r="L13" s="19">
         <f>'[8]MD20000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M13" s="26">
+      <c r="M13" s="19">
         <f>'[8]MD20000.15-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
     <row r="14" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="24">
+      <c r="B14" s="17">
         <v>10</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="25" t="s">
+      <c r="D14" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="19">
         <f>'[9]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27">
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20">
         <f>'[9]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I14" s="27">
+      <c r="I14" s="20">
         <f>'[9]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J14" s="28" t="s">
+      <c r="J14" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K14" s="29">
+      <c r="K14" s="22">
         <f>'[9]MD20000.15-DEc'!$B$3</f>
         <v>45646</v>
       </c>
-      <c r="L14" s="26">
+      <c r="L14" s="19">
         <f>'[9]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M14" s="26">
+      <c r="M14" s="19">
         <f>'[9]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
     <row r="15" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="24">
+      <c r="B15" s="17">
         <v>11</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="D15" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="19">
         <f>'[10]MD50000.15-DEC'!$C$1</f>
         <v>50000</v>
       </c>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27">
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20">
         <f>'[10]MD50000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I15" s="27">
+      <c r="I15" s="20">
         <f>'[10]MD50000.15-DEC'!$K$2</f>
         <v>48</v>
       </c>
-      <c r="J15" s="28" t="s">
+      <c r="J15" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K15" s="29">
+      <c r="K15" s="22">
         <f>'[10]MD50000.15-DEC'!$B$3</f>
         <v>45648</v>
       </c>
-      <c r="L15" s="26">
+      <c r="L15" s="19">
         <f>'[10]MD50000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M15" s="26">
+      <c r="M15" s="19">
         <f>'[10]MD50000.15-DEC'!$O$1</f>
         <v>84000</v>
       </c>
     </row>
     <row r="16" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="24">
+      <c r="B16" s="17">
         <v>12</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D16" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="19">
         <f>'[11]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="20">
         <f>'[11]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G16" s="27">
+      <c r="G16" s="20">
         <f>'[11]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="H16" s="27"/>
-      <c r="I16" s="27"/>
-      <c r="J16" s="28" t="s">
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="K16" s="29">
+      <c r="K16" s="22">
         <f>'[11]MD20000.18-DEC'!$B$3</f>
         <v>45279</v>
       </c>
-      <c r="L16" s="26">
+      <c r="L16" s="19">
         <f>'[11]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M16" s="26">
+      <c r="M16" s="19">
         <f>'[11]MD20000.18-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
     <row r="17" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="24">
+      <c r="B17" s="17">
         <v>13</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="25" t="s">
+      <c r="D17" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="19">
         <f>'[12]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="20">
         <f>'[12]MD20000.22-DEC'!$K$1</f>
         <v>120</v>
       </c>
-      <c r="G17" s="27">
+      <c r="G17" s="20">
         <f>'[12]MD20000.22-DEC'!$K$2</f>
         <v>0</v>
       </c>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="28" t="s">
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K17" s="29">
+      <c r="K17" s="22">
         <f>'[12]MD20000.22-DEC'!$B$3</f>
         <v>0</v>
       </c>
-      <c r="L17" s="26"/>
-      <c r="M17" s="26">
+      <c r="L17" s="19"/>
+      <c r="M17" s="19">
         <f>'[12]MD20000.22-DEC'!$O$1</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="24">
+      <c r="B18" s="17">
         <v>14</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="25" t="s">
+      <c r="D18" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="19">
         <f>'[13]MD50000.15-DEC'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27">
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20">
         <f>'[13]MD50000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I18" s="27">
+      <c r="I18" s="20">
         <f>'[13]MD50000.15-DEC'!$K$2</f>
         <v>48</v>
       </c>
-      <c r="J18" s="28" t="s">
+      <c r="J18" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K18" s="29">
+      <c r="K18" s="22">
         <f>'[13]MD50000.15-DEC'!$B$3</f>
         <v>45310</v>
       </c>
-      <c r="L18" s="26">
+      <c r="L18" s="19">
         <f>'[13]MD50000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M18" s="26">
+      <c r="M18" s="19">
         <f>'[13]MD50000.15-DEC'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
     <row r="19" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="24">
+      <c r="B19" s="17">
         <v>15</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="C19" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="25" t="s">
+      <c r="D19" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="19">
         <f>'[14]MD5000-Jan24'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F19" s="27">
+      <c r="F19" s="20">
         <f>'[14]MD5000-Jan24'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G19" s="27">
+      <c r="G19" s="20">
         <f>'[14]MD5000-Jan24'!$K$2</f>
         <v>60</v>
       </c>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="28" t="s">
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K19" s="29">
+      <c r="K19" s="22">
         <f>'[14]MD5000-Jan24'!$B$3</f>
         <v>45302</v>
       </c>
-      <c r="L19" s="26">
+      <c r="L19" s="19">
         <f>'[14]MD5000-Jan24'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M19" s="26">
+      <c r="M19" s="19">
         <f>'[14]MD5000-Jan24'!$O$1</f>
         <v>6000</v>
       </c>
@@ -4963,11 +5097,11 @@
       <c r="G20" s="13"/>
       <c r="H20" s="13">
         <f>'[15]MD10000.10-JAN'!$K$1</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I20" s="13">
         <f>'[15]MD10000.10-JAN'!$K$2</f>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J20" s="16" t="s">
         <v>12</v>
@@ -4978,612 +5112,612 @@
       </c>
       <c r="L20" s="15">
         <f>'[15]MD10000.10-JAN'!$O$2</f>
-        <v>1750</v>
+        <v>1050</v>
       </c>
       <c r="M20" s="15">
         <f>'[15]MD10000.10-JAN'!$O$1</f>
-        <v>15050</v>
+        <v>15750</v>
       </c>
       <c r="N20" s="1">
         <v>350</v>
       </c>
     </row>
     <row r="21" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="24">
+      <c r="B21" s="17">
         <v>17</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="D21" s="25" t="s">
+      <c r="D21" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="19">
         <f>'[16]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27">
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20">
         <f>'[16]MD10000.10-JAN'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I21" s="27">
+      <c r="I21" s="20">
         <f>'[16]MD10000.10-JAN'!$K$2</f>
         <v>48</v>
       </c>
-      <c r="J21" s="28" t="s">
+      <c r="J21" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K21" s="29">
+      <c r="K21" s="22">
         <f>'[16]MD10000.10-JAN'!$B$3</f>
         <v>45308</v>
       </c>
-      <c r="L21" s="26">
+      <c r="L21" s="19">
         <f>'[16]MD10000.10-JAN'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M21" s="26">
+      <c r="M21" s="19">
         <f>'[16]MD10000.10-JAN'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
     <row r="22" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="24">
+      <c r="B22" s="17">
         <v>18</v>
       </c>
-      <c r="C22" s="25" t="s">
+      <c r="C22" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D22" s="25" t="s">
+      <c r="D22" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="19">
         <f>'[17]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27">
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20">
         <f>'[17]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I22" s="27">
+      <c r="I22" s="20">
         <f>'[17]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J22" s="28" t="s">
+      <c r="J22" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K22" s="29">
+      <c r="K22" s="22">
         <f>'[17]MD10000.20-OCT'!$B$3</f>
         <v>45316</v>
       </c>
-      <c r="L22" s="26">
+      <c r="L22" s="19">
         <f>'[17]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M22" s="26">
+      <c r="M22" s="19">
         <f>'[17]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
     <row r="23" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="24">
+      <c r="B23" s="17">
         <v>19</v>
       </c>
-      <c r="C23" s="25" t="s">
+      <c r="C23" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D23" s="25" t="s">
+      <c r="D23" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="E23" s="26">
+      <c r="E23" s="19">
         <f>'[18]MD10000.20-OCT'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27">
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20">
         <f>'[18]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I23" s="27">
+      <c r="I23" s="20">
         <f>'[18]MD10000.20-OCT'!$K$2</f>
         <v>48</v>
       </c>
-      <c r="J23" s="28" t="s">
+      <c r="J23" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K23" s="29">
+      <c r="K23" s="22">
         <f>'[18]MD10000.20-OCT'!$B$3</f>
         <v>45324</v>
       </c>
-      <c r="L23" s="26">
+      <c r="L23" s="19">
         <f>'[18]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M23" s="26">
+      <c r="M23" s="19">
         <f>'[18]MD10000.20-OCT'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
     <row r="24" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="24">
+      <c r="B24" s="17">
         <v>20</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="C24" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D24" s="25" t="s">
+      <c r="D24" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="19">
         <f>'[19]MD10000.20-OCT'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="27">
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20">
         <f>'[19]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I24" s="27">
+      <c r="I24" s="20">
         <f>'[19]MD10000.20-OCT'!$K$2</f>
         <v>48</v>
       </c>
-      <c r="J24" s="28" t="s">
+      <c r="J24" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K24" s="29">
+      <c r="K24" s="22">
         <f>'[19]MD10000.20-OCT'!$B$3</f>
         <v>45327</v>
       </c>
-      <c r="L24" s="26">
+      <c r="L24" s="19">
         <f>'[19]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M24" s="26">
+      <c r="M24" s="19">
         <f>'[19]MD10000.20-OCT'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
     <row r="25" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="24">
+      <c r="B25" s="17">
         <v>21</v>
       </c>
-      <c r="C25" s="25" t="s">
+      <c r="C25" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D25" s="25" t="s">
+      <c r="D25" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="19">
         <f>'[20]SM5000.1-oct'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F25" s="27">
+      <c r="F25" s="20">
         <f>'[20]SM5000.1-oct'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G25" s="27">
+      <c r="G25" s="20">
         <f>'[20]SM5000.1-oct'!$K$2</f>
         <v>60</v>
       </c>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="28" t="s">
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K25" s="29">
+      <c r="K25" s="22">
         <f>'[20]SM5000.1-oct'!$B$3</f>
         <v>45323</v>
       </c>
-      <c r="L25" s="26">
+      <c r="L25" s="19">
         <f>'[20]SM5000.1-oct'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M25" s="26">
+      <c r="M25" s="19">
         <f>'[20]SM5000.1-oct'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
     <row r="26" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="24">
+      <c r="B26" s="17">
         <v>22</v>
       </c>
-      <c r="C26" s="25" t="s">
+      <c r="C26" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="D26" s="25" t="s">
+      <c r="D26" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="E26" s="26">
+      <c r="E26" s="19">
         <f>'[21]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27">
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20">
         <f>'[21]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I26" s="27">
+      <c r="I26" s="20">
         <f>'[21]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J26" s="28" t="s">
+      <c r="J26" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K26" s="29">
+      <c r="K26" s="22">
         <f>'[21]MD10000.20-OCT'!$B$3</f>
         <v>45332</v>
       </c>
-      <c r="L26" s="26">
+      <c r="L26" s="19">
         <f>'[21]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M26" s="26">
+      <c r="M26" s="19">
         <f>'[21]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
     <row r="27" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="24">
+      <c r="B27" s="17">
         <v>23</v>
       </c>
-      <c r="C27" s="25" t="s">
+      <c r="C27" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D27" s="25" t="s">
+      <c r="D27" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E27" s="26">
+      <c r="E27" s="19">
         <f>'[22]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F27" s="27">
+      <c r="F27" s="20">
         <f>'[22]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G27" s="27">
+      <c r="G27" s="20">
         <f>'[22]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="H27" s="27"/>
-      <c r="I27" s="27"/>
-      <c r="J27" s="28" t="s">
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K27" s="29">
+      <c r="K27" s="22">
         <f>'[22]MD10000.1-OCT'!$B$3</f>
         <v>45339</v>
       </c>
-      <c r="L27" s="26">
+      <c r="L27" s="19">
         <f>'[22]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M27" s="26">
+      <c r="M27" s="19">
         <f>'[22]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
     <row r="28" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="24">
+      <c r="B28" s="17">
         <v>24</v>
       </c>
-      <c r="C28" s="25" t="s">
+      <c r="C28" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D28" s="25" t="s">
+      <c r="D28" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E28" s="26">
+      <c r="E28" s="19">
         <f>'[23]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F28" s="27">
+      <c r="F28" s="20">
         <f>'[23]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G28" s="27">
+      <c r="G28" s="20">
         <f>'[23]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
-      <c r="J28" s="28" t="s">
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K28" s="29">
+      <c r="K28" s="22">
         <f>'[23]MD10000.1-OCT'!$B$3</f>
         <v>45334</v>
       </c>
-      <c r="L28" s="26">
+      <c r="L28" s="19">
         <f>'[23]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M28" s="26">
+      <c r="M28" s="19">
         <f>'[23]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
     <row r="29" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="24">
+      <c r="B29" s="17">
         <v>25</v>
       </c>
-      <c r="C29" s="25" t="s">
+      <c r="C29" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="25" t="s">
+      <c r="D29" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E29" s="26">
+      <c r="E29" s="19">
         <f>'[24]MD20000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27">
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20">
         <f>'[24]MD20000.15-DEC'!$K$1</f>
         <v>5</v>
       </c>
-      <c r="I29" s="27">
+      <c r="I29" s="20">
         <f>'[24]MD20000.15-DEC'!$K$2</f>
         <v>12</v>
       </c>
-      <c r="J29" s="28" t="s">
+      <c r="J29" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K29" s="29">
+      <c r="K29" s="22">
         <f>'[24]MD20000.15-DEC'!$B$3</f>
         <v>45337</v>
       </c>
-      <c r="L29" s="26">
+      <c r="L29" s="19">
         <f>'[25]MD20000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M29" s="26">
+      <c r="M29" s="19">
         <f>'[25]MD20000.15-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
     <row r="30" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="24">
+      <c r="B30" s="17">
         <v>26</v>
       </c>
-      <c r="C30" s="25" t="s">
+      <c r="C30" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D30" s="25" t="s">
+      <c r="D30" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="E30" s="26">
+      <c r="E30" s="19">
         <f>'[26]MD20000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27">
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20">
         <f>'[26]MD20000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I30" s="27">
+      <c r="I30" s="20">
         <f>'[26]MD20000.15-DEC'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J30" s="28" t="s">
+      <c r="J30" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K30" s="29">
+      <c r="K30" s="22">
         <f>'[26]MD20000.15-DEC'!$B$3</f>
         <v>45345</v>
       </c>
-      <c r="L30" s="26">
+      <c r="L30" s="19">
         <f>'[26]MD20000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M30" s="26">
+      <c r="M30" s="19">
         <f>'[26]MD20000.15-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
     <row r="31" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="24">
+      <c r="B31" s="17">
         <v>27</v>
       </c>
-      <c r="C31" s="25" t="s">
+      <c r="C31" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D31" s="25" t="s">
+      <c r="D31" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E31" s="26">
+      <c r="E31" s="19">
         <f>'[27]MD20000.18-DEC'!$C$1</f>
         <v>30000</v>
       </c>
-      <c r="F31" s="27">
+      <c r="F31" s="20">
         <f>'[27]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G31" s="27">
+      <c r="G31" s="20">
         <f>'[27]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="28" t="s">
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K31" s="29">
+      <c r="K31" s="22">
         <f>'[27]MD20000.18-DEC'!$B$3</f>
         <v>45354</v>
       </c>
-      <c r="L31" s="26">
+      <c r="L31" s="19">
         <f>'[27]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M31" s="26">
+      <c r="M31" s="19">
         <f>'[27]MD20000.18-DEC'!$O$1</f>
         <v>36000</v>
       </c>
     </row>
     <row r="32" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="24">
+      <c r="B32" s="17">
         <v>28</v>
       </c>
-      <c r="C32" s="25" t="s">
+      <c r="C32" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D32" s="25" t="s">
+      <c r="D32" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="E32" s="26">
+      <c r="E32" s="19">
         <f>'[28]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="27">
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20">
         <f>'[28]MD10000.10-JAN'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I32" s="27">
+      <c r="I32" s="20">
         <f>'[28]MD10000.10-JAN'!$K$2</f>
         <v>48</v>
       </c>
-      <c r="J32" s="28" t="s">
+      <c r="J32" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K32" s="29">
+      <c r="K32" s="22">
         <f>'[28]MD10000.10-JAN'!$B$3</f>
         <v>45366</v>
       </c>
-      <c r="L32" s="26">
+      <c r="L32" s="19">
         <f>'[28]MD10000.10-JAN'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M32" s="26">
+      <c r="M32" s="19">
         <f>'[28]MD10000.10-JAN'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
     <row r="33" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="24">
+      <c r="B33" s="17">
         <v>29</v>
       </c>
-      <c r="C33" s="25" t="s">
+      <c r="C33" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="25" t="s">
+      <c r="D33" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="E33" s="26">
+      <c r="E33" s="19">
         <f>'[29]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="27">
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20">
         <f>'[29]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I33" s="27">
+      <c r="I33" s="20">
         <f>'[29]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J33" s="28" t="s">
+      <c r="J33" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K33" s="29">
+      <c r="K33" s="22">
         <f>'[29]MD20000.15-DEc'!$B$3</f>
         <v>45380</v>
       </c>
-      <c r="L33" s="26">
+      <c r="L33" s="19">
         <f>'[29]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M33" s="26">
+      <c r="M33" s="19">
         <f>'[29]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
     <row r="34" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="24">
+      <c r="B34" s="17">
         <v>30</v>
       </c>
-      <c r="C34" s="25" t="s">
+      <c r="C34" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D34" s="25" t="s">
+      <c r="D34" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="E34" s="26">
+      <c r="E34" s="19">
         <f>'[30]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="27">
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20">
         <f>'[30]MD10000.10-JAN'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I34" s="27">
+      <c r="I34" s="20">
         <f>'[30]MD10000.10-JAN'!$K$2</f>
         <v>48</v>
       </c>
-      <c r="J34" s="28" t="s">
+      <c r="J34" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K34" s="29">
+      <c r="K34" s="22">
         <f>'[30]MD10000.10-JAN'!$B$3</f>
         <v>45389</v>
       </c>
-      <c r="L34" s="26">
+      <c r="L34" s="19">
         <f>'[30]MD10000.10-JAN'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M34" s="26">
+      <c r="M34" s="19">
         <f>'[30]MD10000.10-JAN'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
     <row r="35" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="24">
+      <c r="B35" s="17">
         <v>31</v>
       </c>
-      <c r="C35" s="25" t="s">
+      <c r="C35" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D35" s="25" t="s">
+      <c r="D35" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="E35" s="26">
+      <c r="E35" s="19">
         <f>'[31]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="27">
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20">
         <f>'[31]MD20000.15-DEc'!$G$1</f>
         <v>17</v>
       </c>
-      <c r="I35" s="27">
+      <c r="I35" s="20">
         <f>'[31]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J35" s="28" t="s">
+      <c r="J35" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="K35" s="29">
+      <c r="K35" s="22">
         <f>'[31]MD20000.15-DEc'!$B$3</f>
         <v>45394</v>
       </c>
-      <c r="L35" s="26">
+      <c r="L35" s="19">
         <f>'[31]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M35" s="26">
+      <c r="M35" s="19">
         <f>'[31]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
@@ -5610,7 +5744,7 @@
       </c>
       <c r="I36" s="13">
         <f>'[32]MD10000.10-JAN'!$K$2</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J36" s="16" t="s">
         <v>12</v>
@@ -5621,815 +5755,809 @@
       </c>
       <c r="L36" s="15">
         <f>'[32]MD10000.10-JAN'!$O$2</f>
-        <v>6300</v>
+        <v>5600</v>
       </c>
       <c r="M36" s="15">
         <f>'[32]MD10000.10-JAN'!$O$1</f>
-        <v>10500</v>
+        <v>11200</v>
       </c>
       <c r="N36" s="1">
         <v>350</v>
       </c>
     </row>
     <row r="37" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="24">
+      <c r="B37" s="17">
         <v>33</v>
       </c>
-      <c r="C37" s="25" t="s">
+      <c r="C37" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D37" s="25" t="s">
+      <c r="D37" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="E37" s="26">
+      <c r="E37" s="19">
         <f>'[33]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27">
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="20">
         <f>'[33]MD20000.15-DEc'!$G$1</f>
         <v>17</v>
       </c>
-      <c r="I37" s="27">
+      <c r="I37" s="20">
         <f>'[33]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J37" s="28" t="s">
+      <c r="J37" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K37" s="29">
+      <c r="K37" s="22">
         <f>'[33]MD20000.15-DEc'!$B$3</f>
         <v>45406</v>
       </c>
-      <c r="L37" s="26">
+      <c r="L37" s="19">
         <f>'[33]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M37" s="26">
+      <c r="M37" s="19">
         <f>'[33]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
     <row r="38" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="24">
+      <c r="B38" s="17">
         <v>34</v>
       </c>
-      <c r="C38" s="25" t="s">
+      <c r="C38" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="D38" s="25" t="s">
+      <c r="D38" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="E38" s="26">
+      <c r="E38" s="19">
         <f>'[34]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27">
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="20">
         <f>'[34]MD10000.20-OCT'!$G$1</f>
         <v>17</v>
       </c>
-      <c r="I38" s="27">
+      <c r="I38" s="20">
         <f>'[34]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J38" s="28" t="s">
+      <c r="J38" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="K38" s="29">
+      <c r="K38" s="22">
         <f>'[34]MD10000.20-OCT'!$B$3</f>
         <v>45406</v>
       </c>
-      <c r="L38" s="26">
+      <c r="L38" s="19">
         <f>'[34]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M38" s="26">
+      <c r="M38" s="19">
         <f>'[34]MD10000.20-OCT'!$O$1</f>
         <v>5950</v>
       </c>
     </row>
     <row r="39" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="6">
+      <c r="B39" s="17">
         <v>35</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="E39" s="7">
+      <c r="E39" s="19">
         <f>'[35]MD50000.15-DEC'!$C$1</f>
         <v>40000</v>
       </c>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8">
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
+      <c r="H39" s="20">
         <f>'[35]MD50000.15-DEC'!$K$1</f>
         <v>47</v>
       </c>
-      <c r="I39" s="8">
+      <c r="I39" s="20">
         <f>'[35]MD50000.15-DEC'!$K$2</f>
         <v>1</v>
       </c>
-      <c r="J39" s="9" t="s">
+      <c r="J39" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K39" s="10">
+      <c r="K39" s="22">
         <f>'[35]MD50000.15-DEC'!$B$3</f>
         <v>45416</v>
       </c>
-      <c r="L39" s="7">
+      <c r="L39" s="19">
         <f>'[36]MD50000.15-DEC'!$O$2</f>
-        <v>46200</v>
-      </c>
-      <c r="M39" s="7">
+        <v>0</v>
+      </c>
+      <c r="M39" s="19">
         <f>'[35]MD50000.15-DEC'!$O$1</f>
         <v>1400</v>
       </c>
-      <c r="N39" s="1">
-        <v>1400</v>
-      </c>
     </row>
     <row r="40" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="24">
+      <c r="B40" s="17">
         <v>36</v>
       </c>
-      <c r="C40" s="25" t="s">
+      <c r="C40" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="D40" s="25" t="s">
+      <c r="D40" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="E40" s="26">
+      <c r="E40" s="19">
         <f>'[37]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27">
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20">
         <f>'[37]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I40" s="27">
+      <c r="I40" s="20">
         <f>'[37]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J40" s="28" t="s">
+      <c r="J40" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K40" s="29">
+      <c r="K40" s="22">
         <f>'[37]MD10000.20-OCT'!$B$3</f>
         <v>45427</v>
       </c>
-      <c r="L40" s="26">
+      <c r="L40" s="19">
         <f>'[37]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M40" s="26">
+      <c r="M40" s="19">
         <f>'[37]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
     <row r="41" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="24">
+      <c r="B41" s="17">
         <v>37</v>
       </c>
-      <c r="C41" s="25" t="s">
+      <c r="C41" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D41" s="25" t="s">
+      <c r="D41" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="26">
+      <c r="E41" s="19">
         <f>'[38]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F41" s="27">
+      <c r="F41" s="20">
         <f>'[38]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G41" s="27">
+      <c r="G41" s="20">
         <f>'[38]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="H41" s="27"/>
-      <c r="I41" s="27"/>
-      <c r="J41" s="28" t="s">
+      <c r="H41" s="20"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="K41" s="29">
+      <c r="K41" s="22">
         <f>'[38]MD20000.18-DEC'!$B$3</f>
         <v>45425</v>
       </c>
-      <c r="L41" s="26">
+      <c r="L41" s="19">
         <f>'[38]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M41" s="26">
+      <c r="M41" s="19">
         <f>'[38]MD20000.18-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
     <row r="42" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="24">
+      <c r="B42" s="17">
         <v>38</v>
       </c>
-      <c r="C42" s="25" t="s">
+      <c r="C42" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D42" s="25" t="s">
+      <c r="D42" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="E42" s="26">
+      <c r="E42" s="19">
         <f>'[39]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F42" s="27"/>
-      <c r="G42" s="27"/>
-      <c r="H42" s="27">
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="20">
         <f>'[39]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I42" s="27">
+      <c r="I42" s="20">
         <f>'[39]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J42" s="28" t="s">
+      <c r="J42" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K42" s="29">
+      <c r="K42" s="22">
         <f>'[39]MD10000.20-OCT'!$B$3</f>
         <v>45436</v>
       </c>
-      <c r="L42" s="26">
+      <c r="L42" s="19">
         <f>'[39]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M42" s="26">
+      <c r="M42" s="19">
         <f>'[39]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
     <row r="43" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="24">
+      <c r="B43" s="17">
         <v>39</v>
       </c>
-      <c r="C43" s="25" t="s">
+      <c r="C43" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D43" s="25" t="s">
+      <c r="D43" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E43" s="26">
+      <c r="E43" s="19">
         <f>'[40]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F43" s="27">
+      <c r="F43" s="20">
         <f>'[40]MD20000.22-DEC'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G43" s="27">
+      <c r="G43" s="20">
         <f>'[40]MD20000.22-DEC'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
-      <c r="J43" s="28" t="s">
+      <c r="H43" s="20"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K43" s="29">
+      <c r="K43" s="22">
         <f>'[40]MD20000.22-DEC'!$B$3</f>
         <v>45432</v>
       </c>
-      <c r="L43" s="26">
+      <c r="L43" s="19">
         <f>'[40]MD20000.22-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M43" s="26">
+      <c r="M43" s="19">
         <f>'[40]MD20000.22-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
     <row r="44" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="24">
+      <c r="B44" s="17">
         <v>40</v>
       </c>
-      <c r="C44" s="25" t="s">
+      <c r="C44" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="D44" s="25" t="s">
+      <c r="D44" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="E44" s="26">
+      <c r="E44" s="19">
         <f>'[41]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F44" s="27">
+      <c r="F44" s="20">
         <f>'[41]MD10000.1-OCT'!$G$1</f>
         <v>120</v>
       </c>
-      <c r="G44" s="27">
+      <c r="G44" s="20">
         <f>'[41]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="H44" s="27"/>
-      <c r="I44" s="27"/>
-      <c r="J44" s="28" t="s">
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="K44" s="29">
+      <c r="K44" s="22">
         <f>'[41]MD10000.1-OCT'!$B$3</f>
         <v>45437</v>
       </c>
-      <c r="L44" s="26">
+      <c r="L44" s="19">
         <f>'[41]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M44" s="26">
+      <c r="M44" s="19">
         <f>'[41]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
     <row r="45" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="24">
+      <c r="B45" s="17">
         <v>41</v>
       </c>
-      <c r="C45" s="25" t="s">
+      <c r="C45" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="D45" s="25" t="s">
+      <c r="D45" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="E45" s="26">
+      <c r="E45" s="19">
         <f>'[42]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F45" s="27"/>
-      <c r="G45" s="27"/>
-      <c r="H45" s="27">
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
+      <c r="H45" s="20">
         <f>'[42]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I45" s="27">
+      <c r="I45" s="20">
         <f>'[42]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J45" s="28" t="s">
+      <c r="J45" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K45" s="29">
+      <c r="K45" s="22">
         <f>'[42]MD10000.20-OCT'!$B$3</f>
         <v>45444</v>
       </c>
-      <c r="L45" s="26"/>
-      <c r="M45" s="26">
+      <c r="L45" s="19"/>
+      <c r="M45" s="19">
         <f>'[42]MD10000.20-OCT'!$O$1</f>
         <v>5950</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="24">
+      <c r="B46" s="17">
         <v>42</v>
       </c>
-      <c r="C46" s="25" t="s">
+      <c r="C46" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D46" s="25" t="s">
+      <c r="D46" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="E46" s="26">
+      <c r="E46" s="19">
         <f>'[43]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="27">
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="20">
         <f>'[44]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I46" s="27">
+      <c r="I46" s="20">
         <f>'[44]MD10000.1-OCT'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J46" s="28" t="s">
+      <c r="J46" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="K46" s="29">
+      <c r="K46" s="22">
         <f>'[43]MD10000.1-OCT'!$B$3</f>
         <v>45450</v>
       </c>
-      <c r="L46" s="26">
+      <c r="L46" s="19">
         <f>'[44]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M46" s="26">
+      <c r="M46" s="19">
         <f>'[44]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
     <row r="47" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="24">
+      <c r="B47" s="17">
         <v>43</v>
       </c>
-      <c r="C47" s="25" t="s">
+      <c r="C47" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D47" s="25" t="s">
+      <c r="D47" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E47" s="26">
+      <c r="E47" s="19">
         <f>'[45]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F47" s="27">
+      <c r="F47" s="20">
         <f>'[45]MD20000.22-DEC'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G47" s="27">
+      <c r="G47" s="20">
         <f>'[45]MD20000.22-DEC'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="H47" s="27"/>
-      <c r="I47" s="27"/>
-      <c r="J47" s="28" t="s">
+      <c r="H47" s="20"/>
+      <c r="I47" s="20"/>
+      <c r="J47" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="K47" s="29">
+      <c r="K47" s="22">
         <f>'[45]MD20000.22-DEC'!$B$3</f>
         <v>45446</v>
       </c>
-      <c r="L47" s="26">
+      <c r="L47" s="19">
         <f>'[45]MD20000.22-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M47" s="26">
+      <c r="M47" s="19">
         <f>'[45]MD20000.22-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="24">
+      <c r="B48" s="17">
         <v>44</v>
       </c>
-      <c r="C48" s="25" t="s">
+      <c r="C48" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="D48" s="25" t="s">
+      <c r="D48" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="E48" s="26">
+      <c r="E48" s="19">
         <f>'[46]MD20000.22-DEC'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F48" s="27">
+      <c r="F48" s="20">
         <f>'[46]MD20000.22-DEC'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G48" s="27">
+      <c r="G48" s="20">
         <f>'[46]MD20000.22-DEC'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="H48" s="27"/>
-      <c r="I48" s="27"/>
-      <c r="J48" s="28" t="s">
+      <c r="H48" s="20"/>
+      <c r="I48" s="20"/>
+      <c r="J48" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="K48" s="29">
+      <c r="K48" s="22">
         <f>'[46]MD20000.22-DEC'!$B$3</f>
         <v>45473</v>
       </c>
-      <c r="L48" s="26">
+      <c r="L48" s="19">
         <f>'[46]MD20000.22-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M48" s="26">
+      <c r="M48" s="19">
         <f>'[46]MD20000.22-DEC'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
     <row r="49" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="24">
+      <c r="B49" s="17">
         <v>45</v>
       </c>
-      <c r="C49" s="25" t="s">
+      <c r="C49" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D49" s="25" t="s">
+      <c r="D49" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E49" s="26">
+      <c r="E49" s="19">
         <f>'[47]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
-      <c r="H49" s="27">
+      <c r="F49" s="20"/>
+      <c r="G49" s="20"/>
+      <c r="H49" s="20">
         <f>'[47]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I49" s="27">
+      <c r="I49" s="20">
         <f>'[47]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J49" s="28" t="s">
+      <c r="J49" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K49" s="29">
+      <c r="K49" s="22">
         <f>'[47]MD20000.15-DEc'!$B$3</f>
         <v>45495</v>
       </c>
-      <c r="L49" s="26">
+      <c r="L49" s="19">
         <f>'[47]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M49" s="26">
+      <c r="M49" s="19">
         <f>'[47]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
     <row r="50" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="24">
+      <c r="B50" s="17">
         <v>46</v>
       </c>
-      <c r="C50" s="25" t="s">
+      <c r="C50" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="D50" s="25" t="s">
+      <c r="D50" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="E50" s="26">
+      <c r="E50" s="19">
         <f>'[48]MD20000.15-DEc'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F50" s="27"/>
-      <c r="G50" s="27"/>
-      <c r="H50" s="27">
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="20">
         <f>'[48]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I50" s="27">
+      <c r="I50" s="20">
         <f>'[48]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J50" s="28" t="s">
+      <c r="J50" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K50" s="29">
+      <c r="K50" s="22">
         <f>'[48]MD20000.15-DEc'!$B$3</f>
         <v>45496</v>
       </c>
-      <c r="L50" s="26">
+      <c r="L50" s="19">
         <f>'[48]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M50" s="26">
+      <c r="M50" s="19">
         <f>'[48]MD20000.15-DEc'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
     <row r="51" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="24">
+      <c r="B51" s="17">
         <v>47</v>
       </c>
-      <c r="C51" s="25" t="s">
+      <c r="C51" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D51" s="25" t="s">
+      <c r="D51" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E51" s="26">
+      <c r="E51" s="19">
         <f>'[49]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F51" s="27">
+      <c r="F51" s="20">
         <f>'[49]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G51" s="27">
+      <c r="G51" s="20">
         <f>'[49]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="H51" s="27"/>
-      <c r="I51" s="27"/>
-      <c r="J51" s="28" t="s">
+      <c r="H51" s="20"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K51" s="29">
+      <c r="K51" s="22">
         <f>'[49]MD20000.18-DEC'!$B$3</f>
         <v>45493</v>
       </c>
-      <c r="L51" s="26">
+      <c r="L51" s="19">
         <f>'[49]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M51" s="26">
+      <c r="M51" s="19">
         <f>'[49]MD20000.18-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="24">
+      <c r="B52" s="17">
         <v>48</v>
       </c>
-      <c r="C52" s="25" t="s">
+      <c r="C52" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D52" s="25" t="s">
+      <c r="D52" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="E52" s="26">
+      <c r="E52" s="19">
         <f>'[50]MD20000.15-DEc'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F52" s="27"/>
-      <c r="G52" s="27"/>
-      <c r="H52" s="27">
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="20">
         <f>'[50]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I52" s="27">
+      <c r="I52" s="20">
         <f>'[50]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J52" s="28" t="s">
+      <c r="J52" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K52" s="29">
+      <c r="K52" s="22">
         <f>'[50]MD20000.15-DEc'!$B$3</f>
         <v>45502</v>
       </c>
-      <c r="L52" s="26">
+      <c r="L52" s="19">
         <f>'[50]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M52" s="26">
+      <c r="M52" s="19">
         <f>'[50]MD20000.15-DEc'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="6">
+      <c r="B53" s="17">
         <v>49</v>
       </c>
-      <c r="C53" s="8" t="s">
+      <c r="C53" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D53" s="10" t="s">
+      <c r="D53" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E53" s="7">
+      <c r="E53" s="19">
         <f>'[51]MD50000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F53" s="8"/>
-      <c r="G53" s="8"/>
-      <c r="H53" s="8">
+      <c r="F53" s="20"/>
+      <c r="G53" s="20"/>
+      <c r="H53" s="20">
         <f>'[51]MD50000.15-DEC'!$K$1</f>
-        <v>13</v>
-      </c>
-      <c r="I53" s="8">
+        <v>0</v>
+      </c>
+      <c r="I53" s="20">
         <f>'[51]MD50000.15-DEC'!$K$2</f>
-        <v>4</v>
-      </c>
-      <c r="J53" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J53" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K53" s="10">
+      <c r="K53" s="22">
         <f>'[51]MD50000.15-DEC'!$B$3</f>
         <v>45504</v>
       </c>
-      <c r="L53" s="7">
+      <c r="L53" s="19">
         <f>'[51]MD50000.15-DEC'!$O$2</f>
-        <v>18200</v>
-      </c>
-      <c r="M53" s="7">
+        <v>0</v>
+      </c>
+      <c r="M53" s="19">
         <f>'[51]MD50000.15-DEC'!$O$1</f>
-        <v>5800</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="24">
+      <c r="B54" s="17">
         <v>50</v>
       </c>
-      <c r="C54" s="25" t="s">
+      <c r="C54" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D54" s="25" t="s">
+      <c r="D54" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="E54" s="26">
+      <c r="E54" s="19">
         <f>'[52]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F54" s="27"/>
-      <c r="G54" s="27"/>
-      <c r="H54" s="27">
+      <c r="F54" s="20"/>
+      <c r="G54" s="20"/>
+      <c r="H54" s="20">
         <f>'[52]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I54" s="27">
+      <c r="I54" s="20">
         <f>'[52]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J54" s="28" t="s">
+      <c r="J54" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K54" s="29">
+      <c r="K54" s="22">
         <f>'[52]MD10000.20-OCT'!$B$3</f>
         <v>45511</v>
       </c>
-      <c r="L54" s="26">
+      <c r="L54" s="19">
         <f>'[52]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M54" s="26">
+      <c r="M54" s="19">
         <f>'[52]MD10000.20-OCT'!$O$1</f>
         <v>5950</v>
       </c>
     </row>
     <row r="55" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="6">
+      <c r="B55" s="17">
         <v>51</v>
       </c>
-      <c r="C55" s="8" t="s">
+      <c r="C55" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D55" s="14" t="s">
+      <c r="D55" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="E55" s="7">
+      <c r="E55" s="19">
         <f>'[53]MD20000.18-DEC'!$C$1</f>
         <v>30000</v>
       </c>
-      <c r="F55" s="8">
+      <c r="F55" s="20">
         <f>'[53]MD20000.18-DEC'!$K$1</f>
-        <v>24</v>
-      </c>
-      <c r="G55" s="8">
+        <v>0</v>
+      </c>
+      <c r="G55" s="20">
         <f>'[53]MD20000.18-DEC'!$K$2</f>
-        <v>96</v>
-      </c>
-      <c r="H55" s="8"/>
-      <c r="I55" s="8"/>
-      <c r="J55" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="K55" s="10">
+        <v>120</v>
+      </c>
+      <c r="H55" s="20"/>
+      <c r="I55" s="20"/>
+      <c r="J55" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="K55" s="22">
         <f>'[53]MD20000.18-DEC'!$B$3</f>
         <v>45508</v>
       </c>
-      <c r="L55" s="7">
+      <c r="L55" s="19">
         <f>'[53]MD20000.18-DEC'!$O$2</f>
-        <v>7200</v>
-      </c>
-      <c r="M55" s="7">
+        <v>0</v>
+      </c>
+      <c r="M55" s="19">
         <f>'[53]MD20000.18-DEC'!$O$1</f>
-        <v>28800</v>
-      </c>
-      <c r="N55" s="1">
-        <v>2100</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="56" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="24">
+      <c r="B56" s="17">
         <v>52</v>
       </c>
-      <c r="C56" s="25" t="s">
+      <c r="C56" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="D56" s="25" t="s">
+      <c r="D56" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="E56" s="26">
+      <c r="E56" s="19">
         <f>'[54]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F56" s="27">
+      <c r="F56" s="20">
         <f>'[54]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G56" s="27">
+      <c r="G56" s="20">
         <f>'[54]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="H56" s="27"/>
-      <c r="I56" s="27"/>
-      <c r="J56" s="28" t="s">
+      <c r="H56" s="20"/>
+      <c r="I56" s="20"/>
+      <c r="J56" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K56" s="29">
+      <c r="K56" s="22">
         <f>'[54]MD20000.18-DEC'!$B$3</f>
         <v>45514</v>
       </c>
-      <c r="L56" s="26">
+      <c r="L56" s="19">
         <f>'[54]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M56" s="26">
+      <c r="M56" s="19">
         <f>'[54]MD20000.18-DEC'!$O$1</f>
         <v>12000</v>
       </c>
@@ -6452,11 +6580,11 @@
       <c r="G57" s="8"/>
       <c r="H57" s="8">
         <f>'[55]MD20000.15-DEc'!$K$1</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I57" s="8">
         <f>'[55]MD20000.15-DEc'!$K$2</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J57" s="9" t="s">
         <v>12</v>
@@ -6467,11 +6595,11 @@
       </c>
       <c r="L57" s="7">
         <f>'[55]MD20000.15-DEc'!$O$2</f>
-        <v>8400</v>
+        <v>4200</v>
       </c>
       <c r="M57" s="7">
         <f>'[55]MD20000.15-DEc'!$O$1</f>
-        <v>15600</v>
+        <v>19800</v>
       </c>
       <c r="N57" s="1">
         <v>1400</v>
@@ -6495,11 +6623,11 @@
       <c r="G58" s="8"/>
       <c r="H58" s="8">
         <f>'[56]MD20000.15-DEc'!$K$1</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I58" s="8">
         <f>'[56]MD20000.15-DEc'!$K$2</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J58" s="9" t="s">
         <v>12</v>
@@ -6510,52 +6638,52 @@
       </c>
       <c r="L58" s="7">
         <f>'[56]MD20000.15-DEc'!$O$2</f>
-        <v>4900</v>
+        <v>3500</v>
       </c>
       <c r="M58" s="7">
         <f>'[56]MD20000.15-DEc'!$O$1</f>
-        <v>7100</v>
+        <v>8500</v>
       </c>
       <c r="N58" s="1">
         <v>700</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="24">
+      <c r="B59" s="17">
         <v>55</v>
       </c>
-      <c r="C59" s="25" t="s">
+      <c r="C59" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="D59" s="25" t="s">
+      <c r="D59" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="E59" s="26">
+      <c r="E59" s="19">
         <f>'[57]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F59" s="27"/>
-      <c r="G59" s="27"/>
-      <c r="H59" s="27">
+      <c r="F59" s="20"/>
+      <c r="G59" s="20"/>
+      <c r="H59" s="20">
         <f>'[57]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I59" s="27">
+      <c r="I59" s="20">
         <f>'[57]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J59" s="28" t="s">
+      <c r="J59" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K59" s="29">
+      <c r="K59" s="22">
         <f>'[57]MD10000.20-OCT'!$B$3</f>
         <v>45532</v>
       </c>
-      <c r="L59" s="26">
+      <c r="L59" s="19">
         <f>'[57]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M59" s="26">
+      <c r="M59" s="19">
         <f>'[57]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
@@ -6578,11 +6706,11 @@
       <c r="G60" s="8"/>
       <c r="H60" s="8">
         <f>'[58]MD20000.15-DEc'!$K$1</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I60" s="8">
         <f>'[58]MD20000.15-DEc'!$K$2</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J60" s="9" t="s">
         <v>12</v>
@@ -6593,132 +6721,132 @@
       </c>
       <c r="L60" s="7">
         <f>'[58]MD20000.15-DEc'!$O$2</f>
-        <v>4900</v>
+        <v>2800</v>
       </c>
       <c r="M60" s="7">
         <f>'[58]MD20000.15-DEc'!$O$1</f>
-        <v>7100</v>
+        <v>9200</v>
       </c>
       <c r="N60" s="1">
         <v>700</v>
       </c>
     </row>
     <row r="61" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="24">
+      <c r="B61" s="17">
         <v>57</v>
       </c>
-      <c r="C61" s="25" t="s">
+      <c r="C61" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D61" s="25" t="s">
+      <c r="D61" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="E61" s="26">
+      <c r="E61" s="19">
         <f>'[59]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F61" s="27"/>
-      <c r="G61" s="27"/>
-      <c r="H61" s="27">
+      <c r="F61" s="20"/>
+      <c r="G61" s="20"/>
+      <c r="H61" s="20">
         <f>'[59]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I61" s="27">
+      <c r="I61" s="20">
         <f>'[59]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J61" s="28" t="s">
+      <c r="J61" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K61" s="29">
+      <c r="K61" s="22">
         <f>'[59]MD10000.20-OCT'!$B$3</f>
         <v>45536</v>
       </c>
-      <c r="L61" s="26">
+      <c r="L61" s="19">
         <f>'[59]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M61" s="26">
+      <c r="M61" s="19">
         <f>'[59]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
     <row r="62" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="24">
+      <c r="B62" s="17">
         <v>58</v>
       </c>
-      <c r="C62" s="25" t="s">
+      <c r="C62" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D62" s="25" t="s">
+      <c r="D62" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E62" s="26">
+      <c r="E62" s="19">
         <f>'[60]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F62" s="27">
+      <c r="F62" s="20">
         <f>'[60]MD20000.22-DEC'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G62" s="27">
+      <c r="G62" s="20">
         <f>'[60]MD20000.22-DEC'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="H62" s="27"/>
-      <c r="I62" s="27"/>
-      <c r="J62" s="28" t="s">
+      <c r="H62" s="20"/>
+      <c r="I62" s="20"/>
+      <c r="J62" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K62" s="29">
+      <c r="K62" s="22">
         <f>'[60]MD20000.22-DEC'!$B$3</f>
         <v>45535</v>
       </c>
-      <c r="L62" s="26">
+      <c r="L62" s="19">
         <f>'[60]MD20000.22-DEC'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M62" s="26">
+      <c r="M62" s="19">
         <f>'[60]MD20000.22-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
     <row r="63" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="24">
+      <c r="B63" s="17">
         <v>59</v>
       </c>
-      <c r="C63" s="25" t="s">
+      <c r="C63" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="D63" s="25" t="s">
+      <c r="D63" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="E63" s="26">
+      <c r="E63" s="19">
         <f>'[61]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
-      <c r="F63" s="27"/>
-      <c r="G63" s="27"/>
-      <c r="H63" s="27">
+      <c r="F63" s="20"/>
+      <c r="G63" s="20"/>
+      <c r="H63" s="20">
         <f>'[61]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="I63" s="27">
+      <c r="I63" s="20">
         <f>'[61]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
-      <c r="J63" s="28" t="s">
+      <c r="J63" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="K63" s="29">
+      <c r="K63" s="22">
         <f>'[61]MD10000.20-OCT'!$B$3</f>
         <v>45549</v>
       </c>
-      <c r="L63" s="26">
+      <c r="L63" s="19">
         <f>'[61]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M63" s="26">
+      <c r="M63" s="19">
         <f>'[61]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
@@ -6739,11 +6867,11 @@
       </c>
       <c r="F64" s="8">
         <f>'[62]MD20000.22-DEC'!$K$1</f>
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="G64" s="8">
         <f>'[62]MD20000.22-DEC'!$K$2</f>
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
@@ -6756,11 +6884,11 @@
       </c>
       <c r="L64" s="7">
         <f>'[62]MD20000.22-DEC'!$O$2</f>
-        <v>14400</v>
+        <v>11800</v>
       </c>
       <c r="M64" s="7">
         <f>'[62]MD20000.22-DEC'!$O$1</f>
-        <v>9600</v>
+        <v>12200</v>
       </c>
       <c r="N64" s="1">
         <v>1400</v>
@@ -6782,11 +6910,11 @@
       </c>
       <c r="F65" s="8">
         <f>'[63]MD10000.1-OCT'!$K$1</f>
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="G65" s="8">
         <f>'[63]MD10000.1-OCT'!$K$2</f>
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="H65" s="8"/>
       <c r="I65" s="8"/>
@@ -6799,11 +6927,11 @@
       </c>
       <c r="L65" s="7">
         <f>'[63]MD10000.1-OCT'!$O$2</f>
-        <v>7700</v>
+        <v>6500</v>
       </c>
       <c r="M65" s="7">
         <f>'[63]MD10000.1-OCT'!$O$1</f>
-        <v>4300</v>
+        <v>5500</v>
       </c>
       <c r="N65" s="1">
         <v>700</v>
@@ -6825,11 +6953,11 @@
       </c>
       <c r="F66" s="8">
         <f>'[64]MD10000.1-OCT'!$K$1</f>
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="G66" s="8">
         <f>'[64]MD10000.1-OCT'!$K$2</f>
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
@@ -6842,11 +6970,11 @@
       </c>
       <c r="L66" s="7">
         <f>'[64]MD10000.1-OCT'!$O$2</f>
-        <v>7800</v>
+        <v>6500</v>
       </c>
       <c r="M66" s="7">
         <f>'[64]MD10000.1-OCT'!$O$1</f>
-        <v>4200</v>
+        <v>5500</v>
       </c>
       <c r="N66" s="1">
         <v>700</v>
@@ -6868,11 +6996,11 @@
       </c>
       <c r="F67" s="8">
         <f>'[65]MD10000.1-OCT'!$K$1</f>
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="G67" s="8">
         <f>'[65]MD10000.1-OCT'!$K$2</f>
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
@@ -6885,11 +7013,11 @@
       </c>
       <c r="L67" s="7">
         <f>'[65]MD10000.1-OCT'!$O$2</f>
-        <v>8200</v>
+        <v>5400</v>
       </c>
       <c r="M67" s="7">
         <f>'[65]MD10000.1-OCT'!$O$1</f>
-        <v>3800</v>
+        <v>6600</v>
       </c>
       <c r="N67" s="1">
         <v>700</v>
@@ -6911,11 +7039,11 @@
       </c>
       <c r="F68" s="8">
         <f>'[66]MD20000.18-DEC'!$K$1</f>
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="G68" s="8">
         <f>'[66]MD20000.18-DEC'!$K$2</f>
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
@@ -6928,11 +7056,11 @@
       </c>
       <c r="L68" s="7">
         <f>'[66]MD20000.18-DEC'!$O$2</f>
-        <v>16400</v>
+        <v>14000</v>
       </c>
       <c r="M68" s="7">
         <f>'[66]MD20000.18-DEC'!$O$1</f>
-        <v>7600</v>
+        <v>10000</v>
       </c>
       <c r="N68" s="1">
         <v>1400</v>
@@ -6954,11 +7082,11 @@
       </c>
       <c r="F69" s="8">
         <f>'[67]MD10000.1-OCT'!$K$1</f>
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="G69" s="8">
         <f>'[67]MD10000.1-OCT'!$K$2</f>
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="H69" s="8"/>
       <c r="I69" s="8"/>
@@ -6971,11 +7099,11 @@
       </c>
       <c r="L69" s="7">
         <f>'[67]MD10000.1-OCT'!$O$2</f>
-        <v>8200</v>
+        <v>6900</v>
       </c>
       <c r="M69" s="7">
         <f>'[67]MD10000.1-OCT'!$O$1</f>
-        <v>3800</v>
+        <v>5100</v>
       </c>
       <c r="N69" s="1">
         <v>700</v>
@@ -6997,11 +7125,11 @@
       </c>
       <c r="F70" s="8">
         <f>'[68]MD10000.1-OCT'!$K$1</f>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G70" s="8">
         <f>'[68]MD10000.1-OCT'!$K$2</f>
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
@@ -7014,11 +7142,11 @@
       </c>
       <c r="L70" s="7">
         <f>'[68]MD10000.1-OCT'!$O$2</f>
-        <v>15450</v>
+        <v>13500</v>
       </c>
       <c r="M70" s="7">
         <f>'[68]MD10000.1-OCT'!$O$1</f>
-        <v>2550</v>
+        <v>4500</v>
       </c>
       <c r="N70" s="1">
         <v>1050</v>
@@ -7040,11 +7168,11 @@
       </c>
       <c r="F71" s="8">
         <f>'[69]MD20000.18-DEC'!$K$1</f>
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="G71" s="8">
         <f>'[69]MD20000.18-DEC'!$K$2</f>
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H71" s="8"/>
       <c r="I71" s="8"/>
@@ -7057,11 +7185,11 @@
       </c>
       <c r="L71" s="7">
         <f>'[69]MD20000.18-DEC'!$O$2</f>
-        <v>48000</v>
+        <v>40500</v>
       </c>
       <c r="M71" s="7">
         <f>'[69]MD20000.18-DEC'!$O$1</f>
-        <v>12000</v>
+        <v>19500</v>
       </c>
       <c r="N71" s="1">
         <v>3500</v>
@@ -7085,11 +7213,11 @@
       <c r="G72" s="8"/>
       <c r="H72" s="8">
         <f>'[70]MD20000.18-DEC'!$K$1</f>
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I72" s="8">
         <f>'[70]MD20000.18-DEC'!$K$2</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J72" s="9" t="s">
         <v>12</v>
@@ -7100,11 +7228,11 @@
       </c>
       <c r="L72" s="7">
         <f>'[70]MD20000.18-DEC'!$O$2</f>
-        <v>152000</v>
+        <v>140000</v>
       </c>
       <c r="M72" s="7">
         <f>'[70]MD20000.18-DEC'!$O$1</f>
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="N72" s="1">
         <v>4000</v>
@@ -7126,11 +7254,11 @@
       </c>
       <c r="F73" s="8">
         <f>'[71]MD20000.18-DEC'!$K$1</f>
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="G73" s="8">
         <f>'[71]MD20000.18-DEC'!$K$2</f>
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="H73" s="8"/>
       <c r="I73" s="8"/>
@@ -7143,11 +7271,11 @@
       </c>
       <c r="L73" s="7">
         <f>'[71]MD20000.18-DEC'!$O$2</f>
-        <v>51500</v>
+        <v>43000</v>
       </c>
       <c r="M73" s="7">
         <f>'[71]MD20000.18-DEC'!$O$1</f>
-        <v>8500</v>
+        <v>17000</v>
       </c>
       <c r="N73" s="1">
         <v>3500</v>
@@ -7169,11 +7297,11 @@
       </c>
       <c r="F74" s="8">
         <f>'[72]MD20000.18-DEC'!$K$1</f>
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G74" s="8">
         <f>'[72]MD20000.18-DEC'!$K$2</f>
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="H74" s="8"/>
       <c r="I74" s="8"/>
@@ -7186,11 +7314,11 @@
       </c>
       <c r="L74" s="7">
         <f>'[72]MD20000.18-DEC'!$O$2</f>
-        <v>20600</v>
+        <v>18200</v>
       </c>
       <c r="M74" s="7">
         <f>'[72]MD20000.18-DEC'!$O$1</f>
-        <v>3400</v>
+        <v>5800</v>
       </c>
       <c r="N74" s="1">
         <v>1400</v>
@@ -7212,11 +7340,11 @@
       </c>
       <c r="F75" s="8">
         <f>'[73]MD20000.18-DEC'!$K$1</f>
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="G75" s="8">
         <f>'[73]MD20000.18-DEC'!$K$2</f>
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H75" s="8"/>
       <c r="I75" s="8"/>
@@ -7229,11 +7357,11 @@
       </c>
       <c r="L75" s="7">
         <f>'[73]MD20000.18-DEC'!$O$2</f>
-        <v>20400</v>
+        <v>18600</v>
       </c>
       <c r="M75" s="7">
         <f>'[73]MD20000.18-DEC'!$O$1</f>
-        <v>3600</v>
+        <v>5400</v>
       </c>
       <c r="N75" s="1">
         <v>1400</v>
@@ -7255,11 +7383,11 @@
       </c>
       <c r="F76" s="8">
         <f>'[74]MD20000.18-DEC'!$K$1</f>
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G76" s="8">
         <f>'[74]MD20000.18-DEC'!$K$2</f>
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="H76" s="8"/>
       <c r="I76" s="8"/>
@@ -7272,11 +7400,11 @@
       </c>
       <c r="L76" s="7">
         <f>'[74]MD20000.18-DEC'!$O$2</f>
-        <v>20600</v>
+        <v>18200</v>
       </c>
       <c r="M76" s="7">
         <f>'[74]MD20000.18-DEC'!$O$1</f>
-        <v>3400</v>
+        <v>5800</v>
       </c>
       <c r="N76" s="1">
         <v>1400</v>
@@ -7298,11 +7426,11 @@
       </c>
       <c r="F77" s="8">
         <f>'[75]MD20000.18-DEC'!$K$1</f>
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="G77" s="8">
         <f>'[75]MD20000.18-DEC'!$K$2</f>
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="H77" s="8"/>
       <c r="I77" s="8"/>
@@ -7315,11 +7443,11 @@
       </c>
       <c r="L77" s="7">
         <f>'[75]MD20000.18-DEC'!$O$2</f>
-        <v>21200</v>
+        <v>17200</v>
       </c>
       <c r="M77" s="7">
         <f>'[75]MD20000.18-DEC'!$O$1</f>
-        <v>2800</v>
+        <v>6800</v>
       </c>
       <c r="N77" s="1">
         <v>1400</v>
@@ -7341,11 +7469,11 @@
       </c>
       <c r="F78" s="8">
         <f>'[76]MD20000.18-DEC'!$K$1</f>
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G78" s="8">
         <f>'[76]MD20000.18-DEC'!$K$2</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H78" s="8"/>
       <c r="I78" s="8"/>
@@ -7358,11 +7486,11 @@
       </c>
       <c r="L78" s="7">
         <f>'[76]MD20000.18-DEC'!$O$2</f>
-        <v>11000</v>
+        <v>10900</v>
       </c>
       <c r="M78" s="7">
         <f>'[76]MD20000.18-DEC'!$O$1</f>
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="N78" s="1">
         <v>700</v>
@@ -7384,11 +7512,11 @@
       </c>
       <c r="F79" s="8">
         <f>'[77]MD20000.18-DEC'!$K$1</f>
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G79" s="8">
         <f>'[77]MD20000.18-DEC'!$K$2</f>
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H79" s="8"/>
       <c r="I79" s="8"/>
@@ -7401,11 +7529,11 @@
       </c>
       <c r="L79" s="7">
         <f>'[77]MD20000.18-DEC'!$O$2</f>
-        <v>10100</v>
+        <v>9500</v>
       </c>
       <c r="M79" s="7">
         <f>'[77]MD20000.18-DEC'!$O$1</f>
-        <v>1900</v>
+        <v>2500</v>
       </c>
       <c r="N79" s="1">
         <v>700</v>
@@ -7427,11 +7555,11 @@
       </c>
       <c r="F80" s="8">
         <f>'[78]MD20000.18-DEC'!$K$1</f>
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="G80" s="8">
         <f>'[78]MD20000.18-DEC'!$K$2</f>
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H80" s="8"/>
       <c r="I80" s="8"/>
@@ -7444,11 +7572,11 @@
       </c>
       <c r="L80" s="7">
         <f>'[78]MD20000.18-DEC'!$O$2</f>
-        <v>10600</v>
+        <v>9400</v>
       </c>
       <c r="M80" s="7">
         <f>'[78]MD20000.18-DEC'!$O$1</f>
-        <v>1400</v>
+        <v>2600</v>
       </c>
       <c r="N80" s="1">
         <v>700</v>
@@ -7472,11 +7600,11 @@
       <c r="G81" s="8"/>
       <c r="H81" s="8">
         <f>'[79]MD20000.15-DEc'!$K$1</f>
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I81" s="8">
         <f>'[79]MD20000.15-DEc'!$K$2</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J81" s="9" t="s">
         <v>12</v>
@@ -7487,11 +7615,11 @@
       </c>
       <c r="L81" s="7">
         <f>'[79]MD20000.15-DEc'!$O$2</f>
-        <v>22400</v>
+        <v>18200</v>
       </c>
       <c r="M81" s="7">
         <f>'[79]MD20000.15-DEc'!$O$1</f>
-        <v>1600</v>
+        <v>5800</v>
       </c>
       <c r="N81" s="1">
         <v>1400</v>
@@ -7515,26 +7643,26 @@
       <c r="G82" s="8"/>
       <c r="H82" s="8">
         <f>'[80]MD10000.10-JAN'!$K$1</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I82" s="8">
         <f>'[80]MD10000.10-JAN'!$K$2</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J82" s="9" t="s">
         <v>12</v>
       </c>
       <c r="K82" s="10">
         <f>'[80]MD10000.10-JAN'!$B$3</f>
-        <v>45571</v>
+        <v>45602</v>
       </c>
       <c r="L82" s="7">
         <f>'[80]MD10000.10-JAN'!$O$2</f>
-        <v>22400</v>
+        <v>19600</v>
       </c>
       <c r="M82" s="7">
         <f>'[80]MD10000.10-JAN'!$O$1</f>
-        <v>1600</v>
+        <v>4400</v>
       </c>
       <c r="N82" s="1">
         <v>1400</v>
@@ -7556,11 +7684,11 @@
       </c>
       <c r="F83" s="8">
         <f>'[81]MD20000.22-DEC'!$K$1</f>
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="G83" s="8">
         <f>'[81]MD20000.22-DEC'!$K$2</f>
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H83" s="8"/>
       <c r="I83" s="8"/>
@@ -7573,11 +7701,11 @@
       </c>
       <c r="L83" s="7">
         <f>'[81]MD20000.22-DEC'!$O$2</f>
-        <v>23200</v>
+        <v>20800</v>
       </c>
       <c r="M83" s="7">
         <f>'[81]MD20000.22-DEC'!$O$1</f>
-        <v>800</v>
+        <v>3200</v>
       </c>
       <c r="N83" s="1">
         <v>1400</v>
@@ -7599,11 +7727,11 @@
       </c>
       <c r="F84" s="8">
         <f>'[82]MD20000.18-DEC'!$K$1</f>
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="G84" s="8">
         <f>'[82]MD20000.18-DEC'!$K$2</f>
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H84" s="8"/>
       <c r="I84" s="8"/>
@@ -7616,57 +7744,144 @@
       </c>
       <c r="L84" s="7">
         <f>'[82]MD20000.18-DEC'!$O$2</f>
-        <v>35700</v>
+        <v>32100</v>
       </c>
       <c r="M84" s="7">
         <f>'[82]MD20000.18-DEC'!$O$1</f>
-        <v>300</v>
+        <v>3900</v>
       </c>
       <c r="N84" s="1">
         <v>2100</v>
       </c>
     </row>
     <row r="85" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="6"/>
-      <c r="C85" s="8"/>
-      <c r="D85" s="14"/>
-      <c r="E85" s="7"/>
-      <c r="F85" s="8"/>
-      <c r="G85" s="8"/>
+      <c r="B85" s="6">
+        <v>81</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D85" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E85" s="7">
+        <f>'[83]MD20000.18-DEC'!$C$1</f>
+        <v>50000</v>
+      </c>
+      <c r="F85" s="8">
+        <f>'[83]MD20000.18-DEC'!$K$1</f>
+        <v>108</v>
+      </c>
+      <c r="G85" s="8">
+        <f>'[83]MD20000.18-DEC'!$K$2</f>
+        <v>12</v>
+      </c>
       <c r="H85" s="8"/>
       <c r="I85" s="8"/>
-      <c r="J85" s="9"/>
-      <c r="K85" s="10"/>
-      <c r="L85" s="7"/>
-      <c r="M85" s="7"/>
+      <c r="J85" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K85" s="10">
+        <f>'[83]MD20000.18-DEC'!$B$3</f>
+        <v>45612</v>
+      </c>
+      <c r="L85" s="7">
+        <f>'[83]MD20000.18-DEC'!$O$2</f>
+        <v>54000</v>
+      </c>
+      <c r="M85" s="7">
+        <f>'[83]MD20000.18-DEC'!$O$1</f>
+        <v>6000</v>
+      </c>
+      <c r="N85" s="1">
+        <v>3500</v>
+      </c>
     </row>
     <row r="86" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="6"/>
-      <c r="C86" s="8"/>
-      <c r="D86" s="14"/>
-      <c r="E86" s="7"/>
-      <c r="F86" s="8"/>
-      <c r="G86" s="8"/>
+      <c r="B86" s="6">
+        <v>82</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D86" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E86" s="7">
+        <f>'[84]MD20000.18-DEC'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F86" s="8">
+        <f>'[84]MD20000.18-DEC'!$K$1</f>
+        <v>113</v>
+      </c>
+      <c r="G86" s="8">
+        <f>'[84]MD20000.18-DEC'!$K$2</f>
+        <v>7</v>
+      </c>
       <c r="H86" s="8"/>
       <c r="I86" s="8"/>
-      <c r="J86" s="9"/>
-      <c r="K86" s="10"/>
-      <c r="L86" s="7"/>
-      <c r="M86" s="7"/>
+      <c r="J86" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K86" s="10">
+        <f>'[84]MD20000.18-DEC'!$B$3</f>
+        <v>45612</v>
+      </c>
+      <c r="L86" s="7">
+        <f>'[84]MD20000.18-DEC'!$O$2</f>
+        <v>11300</v>
+      </c>
+      <c r="M86" s="7">
+        <f>'[84]MD20000.18-DEC'!$O$1</f>
+        <v>700</v>
+      </c>
+      <c r="N86" s="1">
+        <v>700</v>
+      </c>
     </row>
     <row r="87" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="6"/>
-      <c r="C87" s="8"/>
-      <c r="D87" s="14"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="8"/>
-      <c r="G87" s="8"/>
+      <c r="B87" s="6">
+        <v>83</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D87" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="E87" s="7">
+        <f>'[85]MD50000.15-DEC'!$C$1</f>
+        <v>100000</v>
+      </c>
+      <c r="F87" s="8">
+        <f>'[85]MD50000.15-DEC'!$K$1</f>
+        <v>264</v>
+      </c>
+      <c r="G87" s="8">
+        <f>'[85]MD50000.15-DEC'!$K$2</f>
+        <v>3</v>
+      </c>
       <c r="H87" s="8"/>
       <c r="I87" s="8"/>
-      <c r="J87" s="9"/>
-      <c r="K87" s="10"/>
-      <c r="L87" s="7"/>
-      <c r="M87" s="7"/>
+      <c r="J87" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K87" s="10">
+        <f>'[85]MD50000.15-DEC'!$B$3</f>
+        <v>45619</v>
+      </c>
+      <c r="L87" s="7">
+        <f>'[85]MD50000.15-DEC'!$O$2</f>
+        <v>158400</v>
+      </c>
+      <c r="M87" s="7">
+        <f>'[85]MD50000.15-DEC'!$O$1</f>
+        <v>1800</v>
+      </c>
+      <c r="N87" s="1">
+        <v>4200</v>
+      </c>
     </row>
     <row r="88" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B88" s="6"/>

--- a/LoanOfficer-A/LoanBook.xlsx
+++ b/LoanOfficer-A/LoanBook.xlsx
@@ -95,13 +95,14 @@
     <externalReference r:id="rId84"/>
     <externalReference r:id="rId85"/>
     <externalReference r:id="rId86"/>
+    <externalReference r:id="rId87"/>
   </externalReferences>
   <calcPr calcId="145621" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="113">
   <si>
     <t>Code</t>
   </si>
@@ -437,6 +438,9 @@
   </si>
   <si>
     <t>L100000D267</t>
+  </si>
+  <si>
+    <t>kamala</t>
   </si>
 </sst>
 </file>
@@ -991,18 +995,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>3</v>
-          </cell>
-          <cell r="O1">
-            <v>15750</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>45</v>
+            <v>2</v>
+          </cell>
+          <cell r="O1">
+            <v>16100</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>46</v>
           </cell>
           <cell r="O2">
-            <v>1050</v>
+            <v>700</v>
           </cell>
         </row>
         <row r="3">
@@ -1756,15 +1760,15 @@
             <v>48</v>
           </cell>
           <cell r="O1">
-            <v>11200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>32</v>
+            <v>11550</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>33</v>
           </cell>
           <cell r="O2">
-            <v>5600</v>
+            <v>5250</v>
           </cell>
         </row>
         <row r="3">
@@ -2724,18 +2728,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>3</v>
-          </cell>
-          <cell r="O1">
-            <v>19800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>14</v>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>4200</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -2766,18 +2770,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>5</v>
-          </cell>
-          <cell r="O1">
-            <v>8500</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>12</v>
+            <v>4</v>
+          </cell>
+          <cell r="O1">
+            <v>9200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>13</v>
           </cell>
           <cell r="O2">
-            <v>3500</v>
+            <v>2800</v>
           </cell>
         </row>
         <row r="3">
@@ -2848,18 +2852,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>4</v>
-          </cell>
-          <cell r="O1">
-            <v>9200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>13</v>
+            <v>3</v>
+          </cell>
+          <cell r="O1">
+            <v>9900</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>14</v>
           </cell>
           <cell r="O2">
-            <v>2800</v>
+            <v>2100</v>
           </cell>
         </row>
         <row r="3">
@@ -3042,7 +3046,7 @@
       <sheetName val="MD20000.22-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -3082,7 +3086,7 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -3129,18 +3133,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>65</v>
-          </cell>
-          <cell r="O1">
-            <v>5500</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>55</v>
+            <v>60</v>
+          </cell>
+          <cell r="O1">
+            <v>6000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>60</v>
           </cell>
           <cell r="O2">
-            <v>6500</v>
+            <v>6000</v>
           </cell>
         </row>
         <row r="3">
@@ -3169,18 +3173,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>54</v>
-          </cell>
-          <cell r="O1">
-            <v>6600</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>66</v>
+            <v>38</v>
+          </cell>
+          <cell r="O1">
+            <v>8200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>82</v>
           </cell>
           <cell r="O2">
-            <v>5400</v>
+            <v>3800</v>
           </cell>
         </row>
         <row r="3">
@@ -3202,7 +3206,7 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -3249,18 +3253,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>69</v>
-          </cell>
-          <cell r="O1">
-            <v>5100</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>51</v>
+            <v>58</v>
+          </cell>
+          <cell r="O1">
+            <v>6200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>62</v>
           </cell>
           <cell r="O2">
-            <v>6900</v>
+            <v>5800</v>
           </cell>
         </row>
         <row r="3">
@@ -3289,18 +3293,18 @@
             <v>15000</v>
           </cell>
           <cell r="K1">
-            <v>90</v>
-          </cell>
-          <cell r="O1">
-            <v>4500</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>30</v>
+            <v>85</v>
+          </cell>
+          <cell r="O1">
+            <v>5250</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>35</v>
           </cell>
           <cell r="O2">
-            <v>13500</v>
+            <v>12750</v>
           </cell>
         </row>
         <row r="3">
@@ -3329,18 +3333,18 @@
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>81</v>
-          </cell>
-          <cell r="O1">
-            <v>19500</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>39</v>
+            <v>71</v>
+          </cell>
+          <cell r="O1">
+            <v>24500</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>49</v>
           </cell>
           <cell r="O2">
-            <v>40500</v>
+            <v>35500</v>
           </cell>
         </row>
         <row r="3">
@@ -3411,18 +3415,18 @@
             <v>100000</v>
           </cell>
           <cell r="K1">
-            <v>35</v>
-          </cell>
-          <cell r="O1">
-            <v>20000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>5</v>
+            <v>34</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>6</v>
           </cell>
           <cell r="O2">
-            <v>140000</v>
+            <v>136000</v>
           </cell>
         </row>
         <row r="3">
@@ -3451,18 +3455,18 @@
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>86</v>
-          </cell>
-          <cell r="O1">
-            <v>17000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>34</v>
+            <v>81</v>
+          </cell>
+          <cell r="O1">
+            <v>19500</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>39</v>
           </cell>
           <cell r="O2">
-            <v>43000</v>
+            <v>40500</v>
           </cell>
         </row>
         <row r="3">
@@ -3484,7 +3488,7 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -3531,18 +3535,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>93</v>
-          </cell>
-          <cell r="O1">
-            <v>5400</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>27</v>
+            <v>89</v>
+          </cell>
+          <cell r="O1">
+            <v>6200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>31</v>
           </cell>
           <cell r="O2">
-            <v>18600</v>
+            <v>17800</v>
           </cell>
         </row>
         <row r="3">
@@ -3564,7 +3568,7 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -3611,18 +3615,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>86</v>
-          </cell>
-          <cell r="O1">
-            <v>6800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>34</v>
+            <v>81</v>
+          </cell>
+          <cell r="O1">
+            <v>7800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>39</v>
           </cell>
           <cell r="O2">
-            <v>17200</v>
+            <v>16200</v>
           </cell>
         </row>
         <row r="7">
@@ -3651,18 +3655,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>109</v>
-          </cell>
-          <cell r="O1">
-            <v>1100</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>11</v>
+            <v>104</v>
+          </cell>
+          <cell r="O1">
+            <v>1600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>16</v>
           </cell>
           <cell r="O2">
-            <v>10900</v>
+            <v>10400</v>
           </cell>
         </row>
         <row r="3">
@@ -3691,18 +3695,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>95</v>
-          </cell>
-          <cell r="O1">
-            <v>2500</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>25</v>
+            <v>89</v>
+          </cell>
+          <cell r="O1">
+            <v>3100</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>31</v>
           </cell>
           <cell r="O2">
-            <v>9500</v>
+            <v>8900</v>
           </cell>
         </row>
         <row r="3">
@@ -3770,18 +3774,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>13</v>
-          </cell>
-          <cell r="O1">
-            <v>5800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>4</v>
+            <v>12</v>
+          </cell>
+          <cell r="O1">
+            <v>7200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>5</v>
           </cell>
           <cell r="O2">
-            <v>18200</v>
+            <v>16800</v>
           </cell>
         </row>
         <row r="3">
@@ -3854,18 +3858,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>14</v>
-          </cell>
-          <cell r="O1">
-            <v>4400</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>3</v>
+            <v>13</v>
+          </cell>
+          <cell r="O1">
+            <v>5800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>4</v>
           </cell>
           <cell r="O2">
-            <v>19600</v>
+            <v>18200</v>
           </cell>
         </row>
         <row r="3">
@@ -3888,7 +3892,7 @@
       <sheetName val="MD20000.22-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -3928,7 +3932,7 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -3975,18 +3979,18 @@
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>108</v>
-          </cell>
-          <cell r="O1">
-            <v>6000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>12</v>
+            <v>105</v>
+          </cell>
+          <cell r="O1">
+            <v>7500</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>15</v>
           </cell>
           <cell r="O2">
-            <v>54000</v>
+            <v>52500</v>
           </cell>
         </row>
         <row r="3">
@@ -4015,18 +4019,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>113</v>
-          </cell>
-          <cell r="O1">
-            <v>700</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>7</v>
+            <v>102</v>
+          </cell>
+          <cell r="O1">
+            <v>1800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>18</v>
           </cell>
           <cell r="O2">
-            <v>11300</v>
+            <v>10200</v>
           </cell>
         </row>
         <row r="3">
@@ -4056,18 +4060,18 @@
             <v>100000</v>
           </cell>
           <cell r="K1">
-            <v>264</v>
-          </cell>
-          <cell r="O1">
-            <v>1800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>3</v>
+            <v>258</v>
+          </cell>
+          <cell r="O1">
+            <v>5400</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>9</v>
           </cell>
           <cell r="O2">
-            <v>158400</v>
+            <v>154800</v>
           </cell>
         </row>
         <row r="3">
@@ -4077,6 +4081,46 @@
         </row>
       </sheetData>
       <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink86.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>50000</v>
+          </cell>
+          <cell r="K1">
+            <v>118</v>
+          </cell>
+          <cell r="O1">
+            <v>1000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>2</v>
+          </cell>
+          <cell r="O2">
+            <v>59000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45628</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4379,7 +4423,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4387,7 +4431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:Q89"/>
+  <dimension ref="B2:Q100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="1" customWidth="1"/>
@@ -4421,13 +4465,13 @@
       <c r="J2" s="26"/>
       <c r="K2" s="27"/>
       <c r="L2" s="23">
-        <f>SUM(L5:L97)</f>
-        <v>721650</v>
+        <f>SUM(L5:L108)</f>
+        <v>747000</v>
       </c>
       <c r="M2" s="24"/>
       <c r="N2" s="1">
-        <f>SUM(N5:N106)</f>
-        <v>43550</v>
+        <f>SUM(N5:N117)</f>
+        <v>45650</v>
       </c>
       <c r="Q2" s="1">
         <f>14900+260750</f>
@@ -5097,11 +5141,11 @@
       <c r="G20" s="13"/>
       <c r="H20" s="13">
         <f>'[15]MD10000.10-JAN'!$K$1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I20" s="13">
         <f>'[15]MD10000.10-JAN'!$K$2</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J20" s="16" t="s">
         <v>12</v>
@@ -5112,11 +5156,11 @@
       </c>
       <c r="L20" s="15">
         <f>'[15]MD10000.10-JAN'!$O$2</f>
-        <v>1050</v>
+        <v>700</v>
       </c>
       <c r="M20" s="15">
         <f>'[15]MD10000.10-JAN'!$O$1</f>
-        <v>15750</v>
+        <v>16100</v>
       </c>
       <c r="N20" s="1">
         <v>350</v>
@@ -5744,7 +5788,7 @@
       </c>
       <c r="I36" s="13">
         <f>'[32]MD10000.10-JAN'!$K$2</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J36" s="16" t="s">
         <v>12</v>
@@ -5755,11 +5799,11 @@
       </c>
       <c r="L36" s="15">
         <f>'[32]MD10000.10-JAN'!$O$2</f>
-        <v>5600</v>
+        <v>5250</v>
       </c>
       <c r="M36" s="15">
         <f>'[32]MD10000.10-JAN'!$O$1</f>
-        <v>11200</v>
+        <v>11550</v>
       </c>
       <c r="N36" s="1">
         <v>350</v>
@@ -6563,46 +6607,43 @@
       </c>
     </row>
     <row r="57" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="6">
+      <c r="B57" s="17">
         <v>53</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D57" s="10" t="s">
+      <c r="D57" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="E57" s="7">
+      <c r="E57" s="19">
         <f>'[55]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F57" s="8"/>
-      <c r="G57" s="8"/>
-      <c r="H57" s="8">
+      <c r="F57" s="20"/>
+      <c r="G57" s="20"/>
+      <c r="H57" s="20">
         <f>'[55]MD20000.15-DEc'!$K$1</f>
-        <v>3</v>
-      </c>
-      <c r="I57" s="8">
+        <v>0</v>
+      </c>
+      <c r="I57" s="20">
         <f>'[55]MD20000.15-DEc'!$K$2</f>
-        <v>14</v>
-      </c>
-      <c r="J57" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K57" s="10">
+      <c r="K57" s="22">
         <f>'[55]MD20000.15-DEc'!$B$3</f>
         <v>45527</v>
       </c>
-      <c r="L57" s="7">
+      <c r="L57" s="19">
         <f>'[55]MD20000.15-DEc'!$O$2</f>
-        <v>4200</v>
-      </c>
-      <c r="M57" s="7">
+        <v>0</v>
+      </c>
+      <c r="M57" s="19">
         <f>'[55]MD20000.15-DEc'!$O$1</f>
-        <v>19800</v>
-      </c>
-      <c r="N57" s="1">
-        <v>1400</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="58" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6623,11 +6664,11 @@
       <c r="G58" s="8"/>
       <c r="H58" s="8">
         <f>'[56]MD20000.15-DEc'!$K$1</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I58" s="8">
         <f>'[56]MD20000.15-DEc'!$K$2</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J58" s="9" t="s">
         <v>12</v>
@@ -6638,11 +6679,11 @@
       </c>
       <c r="L58" s="7">
         <f>'[56]MD20000.15-DEc'!$O$2</f>
-        <v>3500</v>
+        <v>2800</v>
       </c>
       <c r="M58" s="7">
         <f>'[56]MD20000.15-DEc'!$O$1</f>
-        <v>8500</v>
+        <v>9200</v>
       </c>
       <c r="N58" s="1">
         <v>700</v>
@@ -6706,11 +6747,11 @@
       <c r="G60" s="8"/>
       <c r="H60" s="8">
         <f>'[58]MD20000.15-DEc'!$K$1</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I60" s="8">
         <f>'[58]MD20000.15-DEc'!$K$2</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J60" s="9" t="s">
         <v>12</v>
@@ -6721,11 +6762,11 @@
       </c>
       <c r="L60" s="7">
         <f>'[58]MD20000.15-DEc'!$O$2</f>
-        <v>2800</v>
+        <v>2100</v>
       </c>
       <c r="M60" s="7">
         <f>'[58]MD20000.15-DEc'!$O$1</f>
-        <v>9200</v>
+        <v>9900</v>
       </c>
       <c r="N60" s="1">
         <v>700</v>
@@ -6953,11 +6994,11 @@
       </c>
       <c r="F66" s="8">
         <f>'[64]MD10000.1-OCT'!$K$1</f>
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G66" s="8">
         <f>'[64]MD10000.1-OCT'!$K$2</f>
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
@@ -6970,11 +7011,11 @@
       </c>
       <c r="L66" s="7">
         <f>'[64]MD10000.1-OCT'!$O$2</f>
-        <v>6500</v>
+        <v>6000</v>
       </c>
       <c r="M66" s="7">
         <f>'[64]MD10000.1-OCT'!$O$1</f>
-        <v>5500</v>
+        <v>6000</v>
       </c>
       <c r="N66" s="1">
         <v>700</v>
@@ -6996,11 +7037,11 @@
       </c>
       <c r="F67" s="8">
         <f>'[65]MD10000.1-OCT'!$K$1</f>
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="G67" s="8">
         <f>'[65]MD10000.1-OCT'!$K$2</f>
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
@@ -7013,11 +7054,11 @@
       </c>
       <c r="L67" s="7">
         <f>'[65]MD10000.1-OCT'!$O$2</f>
-        <v>5400</v>
+        <v>3800</v>
       </c>
       <c r="M67" s="7">
         <f>'[65]MD10000.1-OCT'!$O$1</f>
-        <v>6600</v>
+        <v>8200</v>
       </c>
       <c r="N67" s="1">
         <v>700</v>
@@ -7082,11 +7123,11 @@
       </c>
       <c r="F69" s="8">
         <f>'[67]MD10000.1-OCT'!$K$1</f>
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="G69" s="8">
         <f>'[67]MD10000.1-OCT'!$K$2</f>
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="H69" s="8"/>
       <c r="I69" s="8"/>
@@ -7099,11 +7140,11 @@
       </c>
       <c r="L69" s="7">
         <f>'[67]MD10000.1-OCT'!$O$2</f>
-        <v>6900</v>
+        <v>5800</v>
       </c>
       <c r="M69" s="7">
         <f>'[67]MD10000.1-OCT'!$O$1</f>
-        <v>5100</v>
+        <v>6200</v>
       </c>
       <c r="N69" s="1">
         <v>700</v>
@@ -7125,11 +7166,11 @@
       </c>
       <c r="F70" s="8">
         <f>'[68]MD10000.1-OCT'!$K$1</f>
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G70" s="8">
         <f>'[68]MD10000.1-OCT'!$K$2</f>
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
@@ -7142,11 +7183,11 @@
       </c>
       <c r="L70" s="7">
         <f>'[68]MD10000.1-OCT'!$O$2</f>
-        <v>13500</v>
+        <v>12750</v>
       </c>
       <c r="M70" s="7">
         <f>'[68]MD10000.1-OCT'!$O$1</f>
-        <v>4500</v>
+        <v>5250</v>
       </c>
       <c r="N70" s="1">
         <v>1050</v>
@@ -7168,11 +7209,11 @@
       </c>
       <c r="F71" s="8">
         <f>'[69]MD20000.18-DEC'!$K$1</f>
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="G71" s="8">
         <f>'[69]MD20000.18-DEC'!$K$2</f>
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H71" s="8"/>
       <c r="I71" s="8"/>
@@ -7185,11 +7226,11 @@
       </c>
       <c r="L71" s="7">
         <f>'[69]MD20000.18-DEC'!$O$2</f>
-        <v>40500</v>
+        <v>35500</v>
       </c>
       <c r="M71" s="7">
         <f>'[69]MD20000.18-DEC'!$O$1</f>
-        <v>19500</v>
+        <v>24500</v>
       </c>
       <c r="N71" s="1">
         <v>3500</v>
@@ -7213,11 +7254,11 @@
       <c r="G72" s="8"/>
       <c r="H72" s="8">
         <f>'[70]MD20000.18-DEC'!$K$1</f>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I72" s="8">
         <f>'[70]MD20000.18-DEC'!$K$2</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J72" s="9" t="s">
         <v>12</v>
@@ -7228,11 +7269,11 @@
       </c>
       <c r="L72" s="7">
         <f>'[70]MD20000.18-DEC'!$O$2</f>
-        <v>140000</v>
+        <v>136000</v>
       </c>
       <c r="M72" s="7">
         <f>'[70]MD20000.18-DEC'!$O$1</f>
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="N72" s="1">
         <v>4000</v>
@@ -7254,11 +7295,11 @@
       </c>
       <c r="F73" s="8">
         <f>'[71]MD20000.18-DEC'!$K$1</f>
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G73" s="8">
         <f>'[71]MD20000.18-DEC'!$K$2</f>
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H73" s="8"/>
       <c r="I73" s="8"/>
@@ -7271,11 +7312,11 @@
       </c>
       <c r="L73" s="7">
         <f>'[71]MD20000.18-DEC'!$O$2</f>
-        <v>43000</v>
+        <v>40500</v>
       </c>
       <c r="M73" s="7">
         <f>'[71]MD20000.18-DEC'!$O$1</f>
-        <v>17000</v>
+        <v>19500</v>
       </c>
       <c r="N73" s="1">
         <v>3500</v>
@@ -7340,11 +7381,11 @@
       </c>
       <c r="F75" s="8">
         <f>'[73]MD20000.18-DEC'!$K$1</f>
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G75" s="8">
         <f>'[73]MD20000.18-DEC'!$K$2</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H75" s="8"/>
       <c r="I75" s="8"/>
@@ -7357,11 +7398,11 @@
       </c>
       <c r="L75" s="7">
         <f>'[73]MD20000.18-DEC'!$O$2</f>
-        <v>18600</v>
+        <v>17800</v>
       </c>
       <c r="M75" s="7">
         <f>'[73]MD20000.18-DEC'!$O$1</f>
-        <v>5400</v>
+        <v>6200</v>
       </c>
       <c r="N75" s="1">
         <v>1400</v>
@@ -7426,11 +7467,11 @@
       </c>
       <c r="F77" s="8">
         <f>'[75]MD20000.18-DEC'!$K$1</f>
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G77" s="8">
         <f>'[75]MD20000.18-DEC'!$K$2</f>
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H77" s="8"/>
       <c r="I77" s="8"/>
@@ -7443,11 +7484,11 @@
       </c>
       <c r="L77" s="7">
         <f>'[75]MD20000.18-DEC'!$O$2</f>
-        <v>17200</v>
+        <v>16200</v>
       </c>
       <c r="M77" s="7">
         <f>'[75]MD20000.18-DEC'!$O$1</f>
-        <v>6800</v>
+        <v>7800</v>
       </c>
       <c r="N77" s="1">
         <v>1400</v>
@@ -7469,11 +7510,11 @@
       </c>
       <c r="F78" s="8">
         <f>'[76]MD20000.18-DEC'!$K$1</f>
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G78" s="8">
         <f>'[76]MD20000.18-DEC'!$K$2</f>
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H78" s="8"/>
       <c r="I78" s="8"/>
@@ -7486,11 +7527,11 @@
       </c>
       <c r="L78" s="7">
         <f>'[76]MD20000.18-DEC'!$O$2</f>
-        <v>10900</v>
+        <v>10400</v>
       </c>
       <c r="M78" s="7">
         <f>'[76]MD20000.18-DEC'!$O$1</f>
-        <v>1100</v>
+        <v>1600</v>
       </c>
       <c r="N78" s="1">
         <v>700</v>
@@ -7512,11 +7553,11 @@
       </c>
       <c r="F79" s="8">
         <f>'[77]MD20000.18-DEC'!$K$1</f>
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="G79" s="8">
         <f>'[77]MD20000.18-DEC'!$K$2</f>
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H79" s="8"/>
       <c r="I79" s="8"/>
@@ -7529,11 +7570,11 @@
       </c>
       <c r="L79" s="7">
         <f>'[77]MD20000.18-DEC'!$O$2</f>
-        <v>9500</v>
+        <v>8900</v>
       </c>
       <c r="M79" s="7">
         <f>'[77]MD20000.18-DEC'!$O$1</f>
-        <v>2500</v>
+        <v>3100</v>
       </c>
       <c r="N79" s="1">
         <v>700</v>
@@ -7600,11 +7641,11 @@
       <c r="G81" s="8"/>
       <c r="H81" s="8">
         <f>'[79]MD20000.15-DEc'!$K$1</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I81" s="8">
         <f>'[79]MD20000.15-DEc'!$K$2</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J81" s="9" t="s">
         <v>12</v>
@@ -7615,11 +7656,11 @@
       </c>
       <c r="L81" s="7">
         <f>'[79]MD20000.15-DEc'!$O$2</f>
-        <v>18200</v>
+        <v>16800</v>
       </c>
       <c r="M81" s="7">
         <f>'[79]MD20000.15-DEc'!$O$1</f>
-        <v>5800</v>
+        <v>7200</v>
       </c>
       <c r="N81" s="1">
         <v>1400</v>
@@ -7643,11 +7684,11 @@
       <c r="G82" s="8"/>
       <c r="H82" s="8">
         <f>'[80]MD10000.10-JAN'!$K$1</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I82" s="8">
         <f>'[80]MD10000.10-JAN'!$K$2</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J82" s="9" t="s">
         <v>12</v>
@@ -7658,11 +7699,11 @@
       </c>
       <c r="L82" s="7">
         <f>'[80]MD10000.10-JAN'!$O$2</f>
-        <v>19600</v>
+        <v>18200</v>
       </c>
       <c r="M82" s="7">
         <f>'[80]MD10000.10-JAN'!$O$1</f>
-        <v>4400</v>
+        <v>5800</v>
       </c>
       <c r="N82" s="1">
         <v>1400</v>
@@ -7770,11 +7811,11 @@
       </c>
       <c r="F85" s="8">
         <f>'[83]MD20000.18-DEC'!$K$1</f>
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G85" s="8">
         <f>'[83]MD20000.18-DEC'!$K$2</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H85" s="8"/>
       <c r="I85" s="8"/>
@@ -7787,11 +7828,11 @@
       </c>
       <c r="L85" s="7">
         <f>'[83]MD20000.18-DEC'!$O$2</f>
-        <v>54000</v>
+        <v>52500</v>
       </c>
       <c r="M85" s="7">
         <f>'[83]MD20000.18-DEC'!$O$1</f>
-        <v>6000</v>
+        <v>7500</v>
       </c>
       <c r="N85" s="1">
         <v>3500</v>
@@ -7813,11 +7854,11 @@
       </c>
       <c r="F86" s="8">
         <f>'[84]MD20000.18-DEC'!$K$1</f>
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="G86" s="8">
         <f>'[84]MD20000.18-DEC'!$K$2</f>
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H86" s="8"/>
       <c r="I86" s="8"/>
@@ -7830,11 +7871,11 @@
       </c>
       <c r="L86" s="7">
         <f>'[84]MD20000.18-DEC'!$O$2</f>
-        <v>11300</v>
+        <v>10200</v>
       </c>
       <c r="M86" s="7">
         <f>'[84]MD20000.18-DEC'!$O$1</f>
-        <v>700</v>
+        <v>1800</v>
       </c>
       <c r="N86" s="1">
         <v>700</v>
@@ -7856,11 +7897,11 @@
       </c>
       <c r="F87" s="8">
         <f>'[85]MD50000.15-DEC'!$K$1</f>
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="G87" s="8">
         <f>'[85]MD50000.15-DEC'!$K$2</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H87" s="8"/>
       <c r="I87" s="8"/>
@@ -7873,29 +7914,58 @@
       </c>
       <c r="L87" s="7">
         <f>'[85]MD50000.15-DEC'!$O$2</f>
-        <v>158400</v>
+        <v>154800</v>
       </c>
       <c r="M87" s="7">
         <f>'[85]MD50000.15-DEC'!$O$1</f>
-        <v>1800</v>
+        <v>5400</v>
       </c>
       <c r="N87" s="1">
         <v>4200</v>
       </c>
     </row>
     <row r="88" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B88" s="6"/>
-      <c r="C88" s="8"/>
-      <c r="D88" s="14"/>
-      <c r="E88" s="7"/>
-      <c r="F88" s="8"/>
-      <c r="G88" s="8"/>
+      <c r="B88" s="6">
+        <v>84</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D88" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="E88" s="7">
+        <f>'[86]MD20000.18-DEC'!$C$1</f>
+        <v>50000</v>
+      </c>
+      <c r="F88" s="8">
+        <f>'[86]MD20000.18-DEC'!$K$1</f>
+        <v>118</v>
+      </c>
+      <c r="G88" s="8">
+        <f>'[86]MD20000.18-DEC'!$K$2</f>
+        <v>2</v>
+      </c>
       <c r="H88" s="8"/>
       <c r="I88" s="8"/>
-      <c r="J88" s="9"/>
-      <c r="K88" s="10"/>
-      <c r="L88" s="7"/>
-      <c r="M88" s="7"/>
+      <c r="J88" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K88" s="10">
+        <f>'[86]MD20000.18-DEC'!$B$3</f>
+        <v>45628</v>
+      </c>
+      <c r="L88" s="7">
+        <f>'[86]MD20000.18-DEC'!$O$2</f>
+        <v>59000</v>
+      </c>
+      <c r="M88" s="7">
+        <f>'[86]MD20000.18-DEC'!$O$1</f>
+        <v>1000</v>
+      </c>
+      <c r="N88" s="1">
+        <v>3500</v>
+      </c>
     </row>
     <row r="89" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B89" s="6"/>
@@ -7911,6 +7981,160 @@
       <c r="L89" s="7"/>
       <c r="M89" s="7"/>
     </row>
+    <row r="90" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B90" s="6"/>
+      <c r="C90" s="8"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="7"/>
+      <c r="F90" s="8"/>
+      <c r="G90" s="8"/>
+      <c r="H90" s="8"/>
+      <c r="I90" s="8"/>
+      <c r="J90" s="9"/>
+      <c r="K90" s="10"/>
+      <c r="L90" s="7"/>
+      <c r="M90" s="7"/>
+    </row>
+    <row r="91" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B91" s="6"/>
+      <c r="C91" s="8"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="8"/>
+      <c r="G91" s="8"/>
+      <c r="H91" s="8"/>
+      <c r="I91" s="8"/>
+      <c r="J91" s="9"/>
+      <c r="K91" s="10"/>
+      <c r="L91" s="7"/>
+      <c r="M91" s="7"/>
+    </row>
+    <row r="92" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B92" s="6"/>
+      <c r="C92" s="8"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="7"/>
+      <c r="F92" s="8"/>
+      <c r="G92" s="8"/>
+      <c r="H92" s="8"/>
+      <c r="I92" s="8"/>
+      <c r="J92" s="9"/>
+      <c r="K92" s="10"/>
+      <c r="L92" s="7"/>
+      <c r="M92" s="7"/>
+    </row>
+    <row r="93" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B93" s="6"/>
+      <c r="C93" s="8"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="7"/>
+      <c r="F93" s="8"/>
+      <c r="G93" s="8"/>
+      <c r="H93" s="8"/>
+      <c r="I93" s="8"/>
+      <c r="J93" s="9"/>
+      <c r="K93" s="10"/>
+      <c r="L93" s="7"/>
+      <c r="M93" s="7"/>
+    </row>
+    <row r="94" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B94" s="6"/>
+      <c r="C94" s="8"/>
+      <c r="D94" s="14"/>
+      <c r="E94" s="7"/>
+      <c r="F94" s="8"/>
+      <c r="G94" s="8"/>
+      <c r="H94" s="8"/>
+      <c r="I94" s="8"/>
+      <c r="J94" s="9"/>
+      <c r="K94" s="10"/>
+      <c r="L94" s="7"/>
+      <c r="M94" s="7"/>
+    </row>
+    <row r="95" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B95" s="6"/>
+      <c r="C95" s="8"/>
+      <c r="D95" s="14"/>
+      <c r="E95" s="7"/>
+      <c r="F95" s="8"/>
+      <c r="G95" s="8"/>
+      <c r="H95" s="8"/>
+      <c r="I95" s="8"/>
+      <c r="J95" s="9"/>
+      <c r="K95" s="10"/>
+      <c r="L95" s="7"/>
+      <c r="M95" s="7"/>
+    </row>
+    <row r="96" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B96" s="6"/>
+      <c r="C96" s="8"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="7"/>
+      <c r="F96" s="8"/>
+      <c r="G96" s="8"/>
+      <c r="H96" s="8"/>
+      <c r="I96" s="8"/>
+      <c r="J96" s="9"/>
+      <c r="K96" s="10"/>
+      <c r="L96" s="7"/>
+      <c r="M96" s="7"/>
+    </row>
+    <row r="97" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B97" s="6"/>
+      <c r="C97" s="8"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="7"/>
+      <c r="F97" s="8"/>
+      <c r="G97" s="8"/>
+      <c r="H97" s="8"/>
+      <c r="I97" s="8"/>
+      <c r="J97" s="9"/>
+      <c r="K97" s="10"/>
+      <c r="L97" s="7"/>
+      <c r="M97" s="7"/>
+    </row>
+    <row r="98" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B98" s="6"/>
+      <c r="C98" s="8"/>
+      <c r="D98" s="14"/>
+      <c r="E98" s="7"/>
+      <c r="F98" s="8"/>
+      <c r="G98" s="8"/>
+      <c r="H98" s="8"/>
+      <c r="I98" s="8"/>
+      <c r="J98" s="9"/>
+      <c r="K98" s="10"/>
+      <c r="L98" s="7"/>
+      <c r="M98" s="7"/>
+    </row>
+    <row r="99" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B99" s="6"/>
+      <c r="C99" s="8"/>
+      <c r="D99" s="14"/>
+      <c r="E99" s="7"/>
+      <c r="F99" s="8"/>
+      <c r="G99" s="8"/>
+      <c r="H99" s="8"/>
+      <c r="I99" s="8"/>
+      <c r="J99" s="9"/>
+      <c r="K99" s="10"/>
+      <c r="L99" s="7"/>
+      <c r="M99" s="7"/>
+    </row>
+    <row r="100" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B100" s="6"/>
+      <c r="C100" s="8"/>
+      <c r="D100" s="14"/>
+      <c r="E100" s="7"/>
+      <c r="F100" s="8"/>
+      <c r="G100" s="8"/>
+      <c r="H100" s="8"/>
+      <c r="I100" s="8"/>
+      <c r="J100" s="9"/>
+      <c r="K100" s="10"/>
+      <c r="L100" s="7"/>
+      <c r="M100" s="7"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="L2:M2"/>

--- a/LoanOfficer-A/LoanBook.xlsx
+++ b/LoanOfficer-A/LoanBook.xlsx
@@ -96,13 +96,16 @@
     <externalReference r:id="rId85"/>
     <externalReference r:id="rId86"/>
     <externalReference r:id="rId87"/>
+    <externalReference r:id="rId88"/>
+    <externalReference r:id="rId89"/>
+    <externalReference r:id="rId90"/>
   </externalReferences>
   <calcPr calcId="145621" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="116">
   <si>
     <t>Code</t>
   </si>
@@ -441,6 +444,15 @@
   </si>
   <si>
     <t>kamala</t>
+  </si>
+  <si>
+    <t>Ibobi</t>
+  </si>
+  <si>
+    <t>Dinita</t>
+  </si>
+  <si>
+    <t>Sandhyarani</t>
   </si>
 </sst>
 </file>
@@ -988,25 +1000,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>2</v>
-          </cell>
-          <cell r="O1">
-            <v>16100</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>46</v>
-          </cell>
-          <cell r="O2">
-            <v>700</v>
+            <v>1</v>
+          </cell>
+          <cell r="O1">
+            <v>16450</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>47</v>
+          </cell>
+          <cell r="O2">
+            <v>350</v>
           </cell>
         </row>
         <row r="3">
@@ -1015,7 +1027,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1750,7 +1762,7 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -1760,15 +1772,15 @@
             <v>48</v>
           </cell>
           <cell r="O1">
-            <v>11550</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>33</v>
-          </cell>
-          <cell r="O2">
-            <v>5250</v>
+            <v>11900</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>34</v>
+          </cell>
+          <cell r="O2">
+            <v>4900</v>
           </cell>
         </row>
         <row r="3">
@@ -1777,7 +1789,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2763,25 +2775,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>4</v>
-          </cell>
-          <cell r="O1">
-            <v>9200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>13</v>
-          </cell>
-          <cell r="O2">
-            <v>2800</v>
+            <v>3</v>
+          </cell>
+          <cell r="O1">
+            <v>9900</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>14</v>
+          </cell>
+          <cell r="O2">
+            <v>2100</v>
           </cell>
         </row>
         <row r="3">
@@ -2790,7 +2802,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2845,25 +2857,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>3</v>
-          </cell>
-          <cell r="O1">
-            <v>9900</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>14</v>
-          </cell>
-          <cell r="O2">
-            <v>2100</v>
+            <v>2</v>
+          </cell>
+          <cell r="O1">
+            <v>10600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>15</v>
+          </cell>
+          <cell r="O2">
+            <v>1400</v>
           </cell>
         </row>
         <row r="3">
@@ -2872,7 +2884,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3053,18 +3065,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>59</v>
-          </cell>
-          <cell r="O1">
-            <v>12200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>61</v>
-          </cell>
-          <cell r="O2">
-            <v>11800</v>
+            <v>43</v>
+          </cell>
+          <cell r="O1">
+            <v>15400</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>77</v>
+          </cell>
+          <cell r="O2">
+            <v>8600</v>
           </cell>
         </row>
         <row r="13">
@@ -3093,18 +3105,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>65</v>
-          </cell>
-          <cell r="O1">
-            <v>5500</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>55</v>
-          </cell>
-          <cell r="O2">
-            <v>6500</v>
+            <v>48</v>
+          </cell>
+          <cell r="O1">
+            <v>7200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>72</v>
+          </cell>
+          <cell r="O2">
+            <v>4800</v>
           </cell>
         </row>
         <row r="3">
@@ -3126,25 +3138,25 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>60</v>
-          </cell>
-          <cell r="O1">
-            <v>6000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>60</v>
-          </cell>
-          <cell r="O2">
-            <v>6000</v>
+            <v>58</v>
+          </cell>
+          <cell r="O1">
+            <v>6200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>62</v>
+          </cell>
+          <cell r="O2">
+            <v>5800</v>
           </cell>
         </row>
         <row r="3">
@@ -3166,25 +3178,25 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>38</v>
-          </cell>
-          <cell r="O1">
-            <v>8200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>82</v>
-          </cell>
-          <cell r="O2">
-            <v>3800</v>
+            <v>32</v>
+          </cell>
+          <cell r="O1">
+            <v>8800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>88</v>
+          </cell>
+          <cell r="O2">
+            <v>3200</v>
           </cell>
         </row>
         <row r="3">
@@ -3213,18 +3225,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>70</v>
-          </cell>
-          <cell r="O1">
-            <v>10000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>50</v>
-          </cell>
-          <cell r="O2">
-            <v>14000</v>
+            <v>53</v>
+          </cell>
+          <cell r="O1">
+            <v>13400</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>67</v>
+          </cell>
+          <cell r="O2">
+            <v>10600</v>
           </cell>
         </row>
         <row r="3">
@@ -3246,7 +3258,7 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -3286,25 +3298,25 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>15000</v>
           </cell>
           <cell r="K1">
-            <v>85</v>
-          </cell>
-          <cell r="O1">
-            <v>5250</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>35</v>
-          </cell>
-          <cell r="O2">
-            <v>12750</v>
+            <v>83</v>
+          </cell>
+          <cell r="O1">
+            <v>5550</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>37</v>
+          </cell>
+          <cell r="O2">
+            <v>12450</v>
           </cell>
         </row>
         <row r="3">
@@ -3326,25 +3338,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>71</v>
-          </cell>
-          <cell r="O1">
-            <v>24500</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>49</v>
-          </cell>
-          <cell r="O2">
-            <v>35500</v>
+            <v>66</v>
+          </cell>
+          <cell r="O1">
+            <v>27000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>54</v>
+          </cell>
+          <cell r="O2">
+            <v>33000</v>
           </cell>
         </row>
         <row r="3">
@@ -3408,25 +3420,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>100000</v>
           </cell>
           <cell r="K1">
-            <v>34</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>6</v>
-          </cell>
-          <cell r="O2">
-            <v>136000</v>
+            <v>33</v>
+          </cell>
+          <cell r="O1">
+            <v>28000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>7</v>
+          </cell>
+          <cell r="O2">
+            <v>132000</v>
           </cell>
         </row>
         <row r="3">
@@ -3448,25 +3460,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>81</v>
-          </cell>
-          <cell r="O1">
-            <v>19500</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>39</v>
-          </cell>
-          <cell r="O2">
-            <v>40500</v>
+            <v>66</v>
+          </cell>
+          <cell r="O1">
+            <v>27000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>54</v>
+          </cell>
+          <cell r="O2">
+            <v>33000</v>
           </cell>
         </row>
         <row r="3">
@@ -3495,18 +3507,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>91</v>
-          </cell>
-          <cell r="O1">
-            <v>5800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>29</v>
-          </cell>
-          <cell r="O2">
-            <v>18200</v>
+            <v>74</v>
+          </cell>
+          <cell r="O1">
+            <v>9200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>46</v>
+          </cell>
+          <cell r="O2">
+            <v>14800</v>
           </cell>
         </row>
         <row r="3">
@@ -3528,25 +3540,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>89</v>
-          </cell>
-          <cell r="O1">
-            <v>6200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>31</v>
-          </cell>
-          <cell r="O2">
-            <v>17800</v>
+            <v>86</v>
+          </cell>
+          <cell r="O1">
+            <v>6800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>34</v>
+          </cell>
+          <cell r="O2">
+            <v>17200</v>
           </cell>
         </row>
         <row r="3">
@@ -3575,18 +3587,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>91</v>
-          </cell>
-          <cell r="O1">
-            <v>5800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>29</v>
-          </cell>
-          <cell r="O2">
-            <v>18200</v>
+            <v>74</v>
+          </cell>
+          <cell r="O1">
+            <v>9200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>46</v>
+          </cell>
+          <cell r="O2">
+            <v>14800</v>
           </cell>
         </row>
         <row r="3">
@@ -3608,25 +3620,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>81</v>
-          </cell>
-          <cell r="O1">
-            <v>7800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>39</v>
-          </cell>
-          <cell r="O2">
-            <v>16200</v>
+            <v>76</v>
+          </cell>
+          <cell r="O1">
+            <v>8800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>44</v>
+          </cell>
+          <cell r="O2">
+            <v>15200</v>
           </cell>
         </row>
         <row r="7">
@@ -3648,7 +3660,7 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -3688,7 +3700,7 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -3733,18 +3745,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>94</v>
-          </cell>
-          <cell r="O1">
-            <v>2600</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>26</v>
-          </cell>
-          <cell r="O2">
-            <v>9400</v>
+            <v>77</v>
+          </cell>
+          <cell r="O1">
+            <v>4300</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>43</v>
+          </cell>
+          <cell r="O2">
+            <v>7700</v>
           </cell>
         </row>
         <row r="3">
@@ -3767,25 +3779,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>12</v>
-          </cell>
-          <cell r="O1">
-            <v>7200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>5</v>
-          </cell>
-          <cell r="O2">
-            <v>16800</v>
+            <v>11</v>
+          </cell>
+          <cell r="O1">
+            <v>8600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>6</v>
+          </cell>
+          <cell r="O2">
+            <v>15400</v>
           </cell>
         </row>
         <row r="3">
@@ -3794,7 +3806,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3851,25 +3863,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>13</v>
-          </cell>
-          <cell r="O1">
-            <v>5800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>4</v>
-          </cell>
-          <cell r="O2">
-            <v>18200</v>
+            <v>12</v>
+          </cell>
+          <cell r="O1">
+            <v>7200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>5</v>
+          </cell>
+          <cell r="O2">
+            <v>16800</v>
           </cell>
         </row>
         <row r="3">
@@ -3878,7 +3890,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3899,18 +3911,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>104</v>
-          </cell>
-          <cell r="O1">
-            <v>3200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>16</v>
-          </cell>
-          <cell r="O2">
-            <v>20800</v>
+            <v>87</v>
+          </cell>
+          <cell r="O1">
+            <v>6600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>33</v>
+          </cell>
+          <cell r="O2">
+            <v>17400</v>
           </cell>
         </row>
         <row r="3">
@@ -3939,18 +3951,18 @@
             <v>30000</v>
           </cell>
           <cell r="K1">
-            <v>107</v>
-          </cell>
-          <cell r="O1">
-            <v>3900</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>13</v>
-          </cell>
-          <cell r="O2">
-            <v>32100</v>
+            <v>90</v>
+          </cell>
+          <cell r="O1">
+            <v>9000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>30</v>
+          </cell>
+          <cell r="O2">
+            <v>27000</v>
           </cell>
         </row>
         <row r="3">
@@ -3972,25 +3984,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>105</v>
-          </cell>
-          <cell r="O1">
-            <v>7500</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>15</v>
-          </cell>
-          <cell r="O2">
-            <v>52500</v>
+            <v>100</v>
+          </cell>
+          <cell r="O1">
+            <v>10000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>20</v>
+          </cell>
+          <cell r="O2">
+            <v>50000</v>
           </cell>
         </row>
         <row r="3">
@@ -4012,25 +4024,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>102</v>
-          </cell>
-          <cell r="O1">
-            <v>1800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>18</v>
-          </cell>
-          <cell r="O2">
-            <v>10200</v>
+            <v>99</v>
+          </cell>
+          <cell r="O1">
+            <v>2100</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>21</v>
+          </cell>
+          <cell r="O2">
+            <v>9900</v>
           </cell>
         </row>
         <row r="3">
@@ -4053,25 +4065,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>100000</v>
           </cell>
           <cell r="K1">
-            <v>258</v>
-          </cell>
-          <cell r="O1">
-            <v>5400</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>9</v>
-          </cell>
-          <cell r="O2">
-            <v>154800</v>
+            <v>254</v>
+          </cell>
+          <cell r="O1">
+            <v>7800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>13</v>
+          </cell>
+          <cell r="O2">
+            <v>152400</v>
           </cell>
         </row>
         <row r="3">
@@ -4080,7 +4092,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4094,31 +4106,145 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>118</v>
-          </cell>
-          <cell r="O1">
-            <v>1000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>2</v>
-          </cell>
-          <cell r="O2">
-            <v>59000</v>
+            <v>115</v>
+          </cell>
+          <cell r="O1">
+            <v>2500</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>5</v>
+          </cell>
+          <cell r="O2">
+            <v>57500</v>
           </cell>
         </row>
         <row r="3">
           <cell r="B3">
             <v>45628</v>
           </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink87.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>30000</v>
+          </cell>
+          <cell r="K1">
+            <v>120</v>
+          </cell>
+          <cell r="O1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>0</v>
+          </cell>
+          <cell r="O2">
+            <v>36000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3"/>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink88.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>120</v>
+          </cell>
+          <cell r="O1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>0</v>
+          </cell>
+          <cell r="O2">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3"/>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink89.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>120</v>
+          </cell>
+          <cell r="O1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>0</v>
+          </cell>
+          <cell r="O2">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3"/>
         </row>
       </sheetData>
     </sheetDataSet>
@@ -4466,12 +4592,12 @@
       <c r="K2" s="27"/>
       <c r="L2" s="23">
         <f>SUM(L5:L108)</f>
-        <v>747000</v>
+        <v>753400</v>
       </c>
       <c r="M2" s="24"/>
       <c r="N2" s="1">
         <f>SUM(N5:N117)</f>
-        <v>45650</v>
+        <v>49150</v>
       </c>
       <c r="Q2" s="1">
         <f>14900+260750</f>
@@ -5141,11 +5267,11 @@
       <c r="G20" s="13"/>
       <c r="H20" s="13">
         <f>'[15]MD10000.10-JAN'!$K$1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" s="13">
         <f>'[15]MD10000.10-JAN'!$K$2</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J20" s="16" t="s">
         <v>12</v>
@@ -5156,11 +5282,11 @@
       </c>
       <c r="L20" s="15">
         <f>'[15]MD10000.10-JAN'!$O$2</f>
-        <v>700</v>
+        <v>350</v>
       </c>
       <c r="M20" s="15">
         <f>'[15]MD10000.10-JAN'!$O$1</f>
-        <v>16100</v>
+        <v>16450</v>
       </c>
       <c r="N20" s="1">
         <v>350</v>
@@ -5788,7 +5914,7 @@
       </c>
       <c r="I36" s="13">
         <f>'[32]MD10000.10-JAN'!$K$2</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J36" s="16" t="s">
         <v>12</v>
@@ -5799,11 +5925,11 @@
       </c>
       <c r="L36" s="15">
         <f>'[32]MD10000.10-JAN'!$O$2</f>
-        <v>5250</v>
+        <v>4900</v>
       </c>
       <c r="M36" s="15">
         <f>'[32]MD10000.10-JAN'!$O$1</f>
-        <v>11550</v>
+        <v>11900</v>
       </c>
       <c r="N36" s="1">
         <v>350</v>
@@ -6664,11 +6790,11 @@
       <c r="G58" s="8"/>
       <c r="H58" s="8">
         <f>'[56]MD20000.15-DEc'!$K$1</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I58" s="8">
         <f>'[56]MD20000.15-DEc'!$K$2</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J58" s="9" t="s">
         <v>12</v>
@@ -6679,11 +6805,11 @@
       </c>
       <c r="L58" s="7">
         <f>'[56]MD20000.15-DEc'!$O$2</f>
-        <v>2800</v>
+        <v>2100</v>
       </c>
       <c r="M58" s="7">
         <f>'[56]MD20000.15-DEc'!$O$1</f>
-        <v>9200</v>
+        <v>9900</v>
       </c>
       <c r="N58" s="1">
         <v>700</v>
@@ -6747,11 +6873,11 @@
       <c r="G60" s="8"/>
       <c r="H60" s="8">
         <f>'[58]MD20000.15-DEc'!$K$1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I60" s="8">
         <f>'[58]MD20000.15-DEc'!$K$2</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J60" s="9" t="s">
         <v>12</v>
@@ -6762,11 +6888,11 @@
       </c>
       <c r="L60" s="7">
         <f>'[58]MD20000.15-DEc'!$O$2</f>
-        <v>2100</v>
+        <v>1400</v>
       </c>
       <c r="M60" s="7">
         <f>'[58]MD20000.15-DEc'!$O$1</f>
-        <v>9900</v>
+        <v>10600</v>
       </c>
       <c r="N60" s="1">
         <v>700</v>
@@ -6908,11 +7034,11 @@
       </c>
       <c r="F64" s="8">
         <f>'[62]MD20000.22-DEC'!$K$1</f>
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="G64" s="8">
         <f>'[62]MD20000.22-DEC'!$K$2</f>
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
@@ -6925,11 +7051,11 @@
       </c>
       <c r="L64" s="7">
         <f>'[62]MD20000.22-DEC'!$O$2</f>
-        <v>11800</v>
+        <v>8600</v>
       </c>
       <c r="M64" s="7">
         <f>'[62]MD20000.22-DEC'!$O$1</f>
-        <v>12200</v>
+        <v>15400</v>
       </c>
       <c r="N64" s="1">
         <v>1400</v>
@@ -6951,11 +7077,11 @@
       </c>
       <c r="F65" s="8">
         <f>'[63]MD10000.1-OCT'!$K$1</f>
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="G65" s="8">
         <f>'[63]MD10000.1-OCT'!$K$2</f>
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="H65" s="8"/>
       <c r="I65" s="8"/>
@@ -6968,11 +7094,11 @@
       </c>
       <c r="L65" s="7">
         <f>'[63]MD10000.1-OCT'!$O$2</f>
-        <v>6500</v>
+        <v>4800</v>
       </c>
       <c r="M65" s="7">
         <f>'[63]MD10000.1-OCT'!$O$1</f>
-        <v>5500</v>
+        <v>7200</v>
       </c>
       <c r="N65" s="1">
         <v>700</v>
@@ -6994,11 +7120,11 @@
       </c>
       <c r="F66" s="8">
         <f>'[64]MD10000.1-OCT'!$K$1</f>
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G66" s="8">
         <f>'[64]MD10000.1-OCT'!$K$2</f>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
@@ -7011,11 +7137,11 @@
       </c>
       <c r="L66" s="7">
         <f>'[64]MD10000.1-OCT'!$O$2</f>
-        <v>6000</v>
+        <v>5800</v>
       </c>
       <c r="M66" s="7">
         <f>'[64]MD10000.1-OCT'!$O$1</f>
-        <v>6000</v>
+        <v>6200</v>
       </c>
       <c r="N66" s="1">
         <v>700</v>
@@ -7037,11 +7163,11 @@
       </c>
       <c r="F67" s="8">
         <f>'[65]MD10000.1-OCT'!$K$1</f>
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G67" s="8">
         <f>'[65]MD10000.1-OCT'!$K$2</f>
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
@@ -7054,11 +7180,11 @@
       </c>
       <c r="L67" s="7">
         <f>'[65]MD10000.1-OCT'!$O$2</f>
-        <v>3800</v>
+        <v>3200</v>
       </c>
       <c r="M67" s="7">
         <f>'[65]MD10000.1-OCT'!$O$1</f>
-        <v>8200</v>
+        <v>8800</v>
       </c>
       <c r="N67" s="1">
         <v>700</v>
@@ -7080,11 +7206,11 @@
       </c>
       <c r="F68" s="8">
         <f>'[66]MD20000.18-DEC'!$K$1</f>
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="G68" s="8">
         <f>'[66]MD20000.18-DEC'!$K$2</f>
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
@@ -7097,11 +7223,11 @@
       </c>
       <c r="L68" s="7">
         <f>'[66]MD20000.18-DEC'!$O$2</f>
-        <v>14000</v>
+        <v>10600</v>
       </c>
       <c r="M68" s="7">
         <f>'[66]MD20000.18-DEC'!$O$1</f>
-        <v>10000</v>
+        <v>13400</v>
       </c>
       <c r="N68" s="1">
         <v>1400</v>
@@ -7166,11 +7292,11 @@
       </c>
       <c r="F70" s="8">
         <f>'[68]MD10000.1-OCT'!$K$1</f>
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G70" s="8">
         <f>'[68]MD10000.1-OCT'!$K$2</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
@@ -7183,11 +7309,11 @@
       </c>
       <c r="L70" s="7">
         <f>'[68]MD10000.1-OCT'!$O$2</f>
-        <v>12750</v>
+        <v>12450</v>
       </c>
       <c r="M70" s="7">
         <f>'[68]MD10000.1-OCT'!$O$1</f>
-        <v>5250</v>
+        <v>5550</v>
       </c>
       <c r="N70" s="1">
         <v>1050</v>
@@ -7209,11 +7335,11 @@
       </c>
       <c r="F71" s="8">
         <f>'[69]MD20000.18-DEC'!$K$1</f>
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G71" s="8">
         <f>'[69]MD20000.18-DEC'!$K$2</f>
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H71" s="8"/>
       <c r="I71" s="8"/>
@@ -7226,11 +7352,11 @@
       </c>
       <c r="L71" s="7">
         <f>'[69]MD20000.18-DEC'!$O$2</f>
-        <v>35500</v>
+        <v>33000</v>
       </c>
       <c r="M71" s="7">
         <f>'[69]MD20000.18-DEC'!$O$1</f>
-        <v>24500</v>
+        <v>27000</v>
       </c>
       <c r="N71" s="1">
         <v>3500</v>
@@ -7254,11 +7380,11 @@
       <c r="G72" s="8"/>
       <c r="H72" s="8">
         <f>'[70]MD20000.18-DEC'!$K$1</f>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I72" s="8">
         <f>'[70]MD20000.18-DEC'!$K$2</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J72" s="9" t="s">
         <v>12</v>
@@ -7269,11 +7395,11 @@
       </c>
       <c r="L72" s="7">
         <f>'[70]MD20000.18-DEC'!$O$2</f>
-        <v>136000</v>
+        <v>132000</v>
       </c>
       <c r="M72" s="7">
         <f>'[70]MD20000.18-DEC'!$O$1</f>
-        <v>24000</v>
+        <v>28000</v>
       </c>
       <c r="N72" s="1">
         <v>4000</v>
@@ -7295,11 +7421,11 @@
       </c>
       <c r="F73" s="8">
         <f>'[71]MD20000.18-DEC'!$K$1</f>
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="G73" s="8">
         <f>'[71]MD20000.18-DEC'!$K$2</f>
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="H73" s="8"/>
       <c r="I73" s="8"/>
@@ -7312,11 +7438,11 @@
       </c>
       <c r="L73" s="7">
         <f>'[71]MD20000.18-DEC'!$O$2</f>
-        <v>40500</v>
+        <v>33000</v>
       </c>
       <c r="M73" s="7">
         <f>'[71]MD20000.18-DEC'!$O$1</f>
-        <v>19500</v>
+        <v>27000</v>
       </c>
       <c r="N73" s="1">
         <v>3500</v>
@@ -7338,11 +7464,11 @@
       </c>
       <c r="F74" s="8">
         <f>'[72]MD20000.18-DEC'!$K$1</f>
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="G74" s="8">
         <f>'[72]MD20000.18-DEC'!$K$2</f>
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="H74" s="8"/>
       <c r="I74" s="8"/>
@@ -7355,11 +7481,11 @@
       </c>
       <c r="L74" s="7">
         <f>'[72]MD20000.18-DEC'!$O$2</f>
-        <v>18200</v>
+        <v>14800</v>
       </c>
       <c r="M74" s="7">
         <f>'[72]MD20000.18-DEC'!$O$1</f>
-        <v>5800</v>
+        <v>9200</v>
       </c>
       <c r="N74" s="1">
         <v>1400</v>
@@ -7381,11 +7507,11 @@
       </c>
       <c r="F75" s="8">
         <f>'[73]MD20000.18-DEC'!$K$1</f>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G75" s="8">
         <f>'[73]MD20000.18-DEC'!$K$2</f>
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H75" s="8"/>
       <c r="I75" s="8"/>
@@ -7398,11 +7524,11 @@
       </c>
       <c r="L75" s="7">
         <f>'[73]MD20000.18-DEC'!$O$2</f>
-        <v>17800</v>
+        <v>17200</v>
       </c>
       <c r="M75" s="7">
         <f>'[73]MD20000.18-DEC'!$O$1</f>
-        <v>6200</v>
+        <v>6800</v>
       </c>
       <c r="N75" s="1">
         <v>1400</v>
@@ -7424,11 +7550,11 @@
       </c>
       <c r="F76" s="8">
         <f>'[74]MD20000.18-DEC'!$K$1</f>
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="G76" s="8">
         <f>'[74]MD20000.18-DEC'!$K$2</f>
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="H76" s="8"/>
       <c r="I76" s="8"/>
@@ -7441,11 +7567,11 @@
       </c>
       <c r="L76" s="7">
         <f>'[74]MD20000.18-DEC'!$O$2</f>
-        <v>18200</v>
+        <v>14800</v>
       </c>
       <c r="M76" s="7">
         <f>'[74]MD20000.18-DEC'!$O$1</f>
-        <v>5800</v>
+        <v>9200</v>
       </c>
       <c r="N76" s="1">
         <v>1400</v>
@@ -7467,11 +7593,11 @@
       </c>
       <c r="F77" s="8">
         <f>'[75]MD20000.18-DEC'!$K$1</f>
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G77" s="8">
         <f>'[75]MD20000.18-DEC'!$K$2</f>
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H77" s="8"/>
       <c r="I77" s="8"/>
@@ -7484,11 +7610,11 @@
       </c>
       <c r="L77" s="7">
         <f>'[75]MD20000.18-DEC'!$O$2</f>
-        <v>16200</v>
+        <v>15200</v>
       </c>
       <c r="M77" s="7">
         <f>'[75]MD20000.18-DEC'!$O$1</f>
-        <v>7800</v>
+        <v>8800</v>
       </c>
       <c r="N77" s="1">
         <v>1400</v>
@@ -7596,11 +7722,11 @@
       </c>
       <c r="F80" s="8">
         <f>'[78]MD20000.18-DEC'!$K$1</f>
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="G80" s="8">
         <f>'[78]MD20000.18-DEC'!$K$2</f>
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H80" s="8"/>
       <c r="I80" s="8"/>
@@ -7613,11 +7739,11 @@
       </c>
       <c r="L80" s="7">
         <f>'[78]MD20000.18-DEC'!$O$2</f>
-        <v>9400</v>
+        <v>7700</v>
       </c>
       <c r="M80" s="7">
         <f>'[78]MD20000.18-DEC'!$O$1</f>
-        <v>2600</v>
+        <v>4300</v>
       </c>
       <c r="N80" s="1">
         <v>700</v>
@@ -7641,11 +7767,11 @@
       <c r="G81" s="8"/>
       <c r="H81" s="8">
         <f>'[79]MD20000.15-DEc'!$K$1</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I81" s="8">
         <f>'[79]MD20000.15-DEc'!$K$2</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J81" s="9" t="s">
         <v>12</v>
@@ -7656,11 +7782,11 @@
       </c>
       <c r="L81" s="7">
         <f>'[79]MD20000.15-DEc'!$O$2</f>
-        <v>16800</v>
+        <v>15400</v>
       </c>
       <c r="M81" s="7">
         <f>'[79]MD20000.15-DEc'!$O$1</f>
-        <v>7200</v>
+        <v>8600</v>
       </c>
       <c r="N81" s="1">
         <v>1400</v>
@@ -7684,11 +7810,11 @@
       <c r="G82" s="8"/>
       <c r="H82" s="8">
         <f>'[80]MD10000.10-JAN'!$K$1</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I82" s="8">
         <f>'[80]MD10000.10-JAN'!$K$2</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J82" s="9" t="s">
         <v>12</v>
@@ -7699,11 +7825,11 @@
       </c>
       <c r="L82" s="7">
         <f>'[80]MD10000.10-JAN'!$O$2</f>
-        <v>18200</v>
+        <v>16800</v>
       </c>
       <c r="M82" s="7">
         <f>'[80]MD10000.10-JAN'!$O$1</f>
-        <v>5800</v>
+        <v>7200</v>
       </c>
       <c r="N82" s="1">
         <v>1400</v>
@@ -7725,11 +7851,11 @@
       </c>
       <c r="F83" s="8">
         <f>'[81]MD20000.22-DEC'!$K$1</f>
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="G83" s="8">
         <f>'[81]MD20000.22-DEC'!$K$2</f>
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="H83" s="8"/>
       <c r="I83" s="8"/>
@@ -7742,11 +7868,11 @@
       </c>
       <c r="L83" s="7">
         <f>'[81]MD20000.22-DEC'!$O$2</f>
-        <v>20800</v>
+        <v>17400</v>
       </c>
       <c r="M83" s="7">
         <f>'[81]MD20000.22-DEC'!$O$1</f>
-        <v>3200</v>
+        <v>6600</v>
       </c>
       <c r="N83" s="1">
         <v>1400</v>
@@ -7768,11 +7894,11 @@
       </c>
       <c r="F84" s="8">
         <f>'[82]MD20000.18-DEC'!$K$1</f>
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="G84" s="8">
         <f>'[82]MD20000.18-DEC'!$K$2</f>
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="H84" s="8"/>
       <c r="I84" s="8"/>
@@ -7785,11 +7911,11 @@
       </c>
       <c r="L84" s="7">
         <f>'[82]MD20000.18-DEC'!$O$2</f>
-        <v>32100</v>
+        <v>27000</v>
       </c>
       <c r="M84" s="7">
         <f>'[82]MD20000.18-DEC'!$O$1</f>
-        <v>3900</v>
+        <v>9000</v>
       </c>
       <c r="N84" s="1">
         <v>2100</v>
@@ -7811,11 +7937,11 @@
       </c>
       <c r="F85" s="8">
         <f>'[83]MD20000.18-DEC'!$K$1</f>
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="G85" s="8">
         <f>'[83]MD20000.18-DEC'!$K$2</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H85" s="8"/>
       <c r="I85" s="8"/>
@@ -7828,11 +7954,11 @@
       </c>
       <c r="L85" s="7">
         <f>'[83]MD20000.18-DEC'!$O$2</f>
-        <v>52500</v>
+        <v>50000</v>
       </c>
       <c r="M85" s="7">
         <f>'[83]MD20000.18-DEC'!$O$1</f>
-        <v>7500</v>
+        <v>10000</v>
       </c>
       <c r="N85" s="1">
         <v>3500</v>
@@ -7854,11 +7980,11 @@
       </c>
       <c r="F86" s="8">
         <f>'[84]MD20000.18-DEC'!$K$1</f>
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G86" s="8">
         <f>'[84]MD20000.18-DEC'!$K$2</f>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H86" s="8"/>
       <c r="I86" s="8"/>
@@ -7871,11 +7997,11 @@
       </c>
       <c r="L86" s="7">
         <f>'[84]MD20000.18-DEC'!$O$2</f>
-        <v>10200</v>
+        <v>9900</v>
       </c>
       <c r="M86" s="7">
         <f>'[84]MD20000.18-DEC'!$O$1</f>
-        <v>1800</v>
+        <v>2100</v>
       </c>
       <c r="N86" s="1">
         <v>700</v>
@@ -7897,11 +8023,11 @@
       </c>
       <c r="F87" s="8">
         <f>'[85]MD50000.15-DEC'!$K$1</f>
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G87" s="8">
         <f>'[85]MD50000.15-DEC'!$K$2</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H87" s="8"/>
       <c r="I87" s="8"/>
@@ -7914,11 +8040,11 @@
       </c>
       <c r="L87" s="7">
         <f>'[85]MD50000.15-DEC'!$O$2</f>
-        <v>154800</v>
+        <v>152400</v>
       </c>
       <c r="M87" s="7">
         <f>'[85]MD50000.15-DEC'!$O$1</f>
-        <v>5400</v>
+        <v>7800</v>
       </c>
       <c r="N87" s="1">
         <v>4200</v>
@@ -7940,11 +8066,11 @@
       </c>
       <c r="F88" s="8">
         <f>'[86]MD20000.18-DEC'!$K$1</f>
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G88" s="8">
         <f>'[86]MD20000.18-DEC'!$K$2</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H88" s="8"/>
       <c r="I88" s="8"/>
@@ -7957,60 +8083,149 @@
       </c>
       <c r="L88" s="7">
         <f>'[86]MD20000.18-DEC'!$O$2</f>
-        <v>59000</v>
+        <v>57500</v>
       </c>
       <c r="M88" s="7">
         <f>'[86]MD20000.18-DEC'!$O$1</f>
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="N88" s="1">
         <v>3500</v>
       </c>
     </row>
     <row r="89" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B89" s="6"/>
-      <c r="C89" s="8"/>
-      <c r="D89" s="14"/>
-      <c r="E89" s="7"/>
-      <c r="F89" s="8"/>
-      <c r="G89" s="8"/>
+      <c r="B89" s="6">
+        <v>85</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D89" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E89" s="7">
+        <f>'[87]MD20000.18-DEC'!$C$1</f>
+        <v>30000</v>
+      </c>
+      <c r="F89" s="8">
+        <f>'[87]MD20000.18-DEC'!$K$1</f>
+        <v>120</v>
+      </c>
+      <c r="G89" s="8">
+        <f>'[87]MD20000.18-DEC'!$K$2</f>
+        <v>0</v>
+      </c>
       <c r="H89" s="8"/>
       <c r="I89" s="8"/>
-      <c r="J89" s="9"/>
-      <c r="K89" s="10"/>
-      <c r="L89" s="7"/>
-      <c r="M89" s="7"/>
+      <c r="J89" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K89" s="10">
+        <f>'[87]MD20000.18-DEC'!$B$3</f>
+        <v>0</v>
+      </c>
+      <c r="L89" s="7">
+        <f>'[87]MD20000.18-DEC'!$O$2</f>
+        <v>36000</v>
+      </c>
+      <c r="M89" s="7">
+        <f>'[87]MD20000.18-DEC'!$O$1</f>
+        <v>0</v>
+      </c>
+      <c r="N89" s="1">
+        <v>2100</v>
+      </c>
     </row>
     <row r="90" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B90" s="6"/>
-      <c r="C90" s="8"/>
-      <c r="D90" s="14"/>
-      <c r="E90" s="7"/>
-      <c r="F90" s="8"/>
-      <c r="G90" s="8"/>
+      <c r="B90" s="6">
+        <v>86</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D90" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E90" s="7">
+        <f>'[88]MD20000.18-DEC'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F90" s="8">
+        <f>'[88]MD20000.18-DEC'!$K$1</f>
+        <v>120</v>
+      </c>
+      <c r="G90" s="8">
+        <f>'[88]MD20000.18-DEC'!$K$2</f>
+        <v>0</v>
+      </c>
       <c r="H90" s="8"/>
       <c r="I90" s="8"/>
-      <c r="J90" s="9"/>
-      <c r="K90" s="10"/>
-      <c r="L90" s="7"/>
-      <c r="M90" s="7"/>
+      <c r="J90" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K90" s="10">
+        <f>'[88]MD20000.18-DEC'!$B$3</f>
+        <v>0</v>
+      </c>
+      <c r="L90" s="7">
+        <f>'[88]MD20000.18-DEC'!$O$2</f>
+        <v>12000</v>
+      </c>
+      <c r="M90" s="7">
+        <f>'[88]MD20000.18-DEC'!$O$1</f>
+        <v>0</v>
+      </c>
+      <c r="N90" s="1">
+        <v>700</v>
+      </c>
     </row>
     <row r="91" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B91" s="6"/>
-      <c r="C91" s="8"/>
-      <c r="D91" s="14"/>
-      <c r="E91" s="7"/>
-      <c r="F91" s="8"/>
-      <c r="G91" s="8"/>
+      <c r="B91" s="6">
+        <v>87</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D91" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E91" s="7">
+        <f>'[89]MD20000.18-DEC'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F91" s="8">
+        <f>'[89]MD20000.18-DEC'!$K$1</f>
+        <v>120</v>
+      </c>
+      <c r="G91" s="8">
+        <f>'[89]MD20000.18-DEC'!$K$2</f>
+        <v>0</v>
+      </c>
       <c r="H91" s="8"/>
       <c r="I91" s="8"/>
-      <c r="J91" s="9"/>
-      <c r="K91" s="10"/>
-      <c r="L91" s="7"/>
-      <c r="M91" s="7"/>
+      <c r="J91" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K91" s="10">
+        <f>'[89]MD20000.18-DEC'!$B$3</f>
+        <v>0</v>
+      </c>
+      <c r="L91" s="7">
+        <f>'[89]MD20000.18-DEC'!$O$2</f>
+        <v>12000</v>
+      </c>
+      <c r="M91" s="7">
+        <f>'[89]MD20000.18-DEC'!$O$1</f>
+        <v>0</v>
+      </c>
+      <c r="N91" s="1">
+        <v>700</v>
+      </c>
     </row>
     <row r="92" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B92" s="6"/>
+      <c r="B92" s="6">
+        <v>88</v>
+      </c>
       <c r="C92" s="8"/>
       <c r="D92" s="14"/>
       <c r="E92" s="7"/>
@@ -8024,7 +8239,9 @@
       <c r="M92" s="7"/>
     </row>
     <row r="93" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B93" s="6"/>
+      <c r="B93" s="6">
+        <v>89</v>
+      </c>
       <c r="C93" s="8"/>
       <c r="D93" s="14"/>
       <c r="E93" s="7"/>
@@ -8038,7 +8255,9 @@
       <c r="M93" s="7"/>
     </row>
     <row r="94" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B94" s="6"/>
+      <c r="B94" s="6">
+        <v>90</v>
+      </c>
       <c r="C94" s="8"/>
       <c r="D94" s="14"/>
       <c r="E94" s="7"/>
@@ -8052,7 +8271,9 @@
       <c r="M94" s="7"/>
     </row>
     <row r="95" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B95" s="6"/>
+      <c r="B95" s="6">
+        <v>91</v>
+      </c>
       <c r="C95" s="8"/>
       <c r="D95" s="14"/>
       <c r="E95" s="7"/>
@@ -8066,7 +8287,9 @@
       <c r="M95" s="7"/>
     </row>
     <row r="96" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B96" s="6"/>
+      <c r="B96" s="6">
+        <v>92</v>
+      </c>
       <c r="C96" s="8"/>
       <c r="D96" s="14"/>
       <c r="E96" s="7"/>
@@ -8080,7 +8303,9 @@
       <c r="M96" s="7"/>
     </row>
     <row r="97" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B97" s="6"/>
+      <c r="B97" s="6">
+        <v>93</v>
+      </c>
       <c r="C97" s="8"/>
       <c r="D97" s="14"/>
       <c r="E97" s="7"/>
@@ -8094,7 +8319,9 @@
       <c r="M97" s="7"/>
     </row>
     <row r="98" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B98" s="6"/>
+      <c r="B98" s="6">
+        <v>94</v>
+      </c>
       <c r="C98" s="8"/>
       <c r="D98" s="14"/>
       <c r="E98" s="7"/>
@@ -8108,7 +8335,9 @@
       <c r="M98" s="7"/>
     </row>
     <row r="99" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B99" s="6"/>
+      <c r="B99" s="6">
+        <v>95</v>
+      </c>
       <c r="C99" s="8"/>
       <c r="D99" s="14"/>
       <c r="E99" s="7"/>
@@ -8122,7 +8351,9 @@
       <c r="M99" s="7"/>
     </row>
     <row r="100" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B100" s="6"/>
+      <c r="B100" s="6">
+        <v>96</v>
+      </c>
       <c r="C100" s="8"/>
       <c r="D100" s="14"/>
       <c r="E100" s="7"/>

--- a/LoanOfficer-A/LoanBook.xlsx
+++ b/LoanOfficer-A/LoanBook.xlsx
@@ -99,13 +99,15 @@
     <externalReference r:id="rId88"/>
     <externalReference r:id="rId89"/>
     <externalReference r:id="rId90"/>
+    <externalReference r:id="rId91"/>
+    <externalReference r:id="rId92"/>
   </externalReferences>
   <calcPr calcId="145621" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="120">
   <si>
     <t>Code</t>
   </si>
@@ -453,6 +455,18 @@
   </si>
   <si>
     <t>Sandhyarani</t>
+  </si>
+  <si>
+    <t>Rambhabati</t>
+  </si>
+  <si>
+    <t>L200000D267</t>
+  </si>
+  <si>
+    <t>lukhamlu</t>
+  </si>
+  <si>
+    <t>L10000W17P700</t>
   </si>
 </sst>
 </file>
@@ -500,7 +514,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -534,6 +548,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF003366"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -603,7 +623,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -690,6 +710,21 @@
     <xf numFmtId="166" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -699,8 +734,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF003366"/>
       <color rgb="FF006666"/>
-      <color rgb="FF003366"/>
       <color rgb="FF336699"/>
       <color rgb="FF006699"/>
       <color rgb="FF003300"/>
@@ -1000,25 +1035,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>1</v>
-          </cell>
-          <cell r="O1">
-            <v>16450</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>47</v>
-          </cell>
-          <cell r="O2">
-            <v>350</v>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>16800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>48</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -1027,7 +1062,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1762,7 +1797,7 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -1772,15 +1807,15 @@
             <v>48</v>
           </cell>
           <cell r="O1">
-            <v>11900</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>34</v>
-          </cell>
-          <cell r="O2">
-            <v>4900</v>
+            <v>12600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>36</v>
+          </cell>
+          <cell r="O2">
+            <v>4200</v>
           </cell>
         </row>
         <row r="3">
@@ -1789,7 +1824,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2446,7 +2481,7 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -2775,25 +2810,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>3</v>
-          </cell>
-          <cell r="O1">
-            <v>9900</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>14</v>
-          </cell>
-          <cell r="O2">
-            <v>2100</v>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -2802,7 +2837,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2816,7 +2851,7 @@
       <sheetName val="MD10000.20-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -2857,25 +2892,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>2</v>
-          </cell>
-          <cell r="O1">
-            <v>10600</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>15</v>
-          </cell>
-          <cell r="O2">
-            <v>1400</v>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -2884,7 +2919,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2898,7 +2933,7 @@
       <sheetName val="MD10000.20-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -3058,25 +3093,25 @@
       <sheetName val="MD20000.22-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>43</v>
-          </cell>
-          <cell r="O1">
-            <v>15400</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>77</v>
-          </cell>
-          <cell r="O2">
-            <v>8600</v>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
           </cell>
         </row>
         <row r="13">
@@ -3098,25 +3133,25 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>48</v>
-          </cell>
-          <cell r="O1">
-            <v>7200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>72</v>
-          </cell>
-          <cell r="O2">
-            <v>4800</v>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -3138,25 +3173,25 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>58</v>
-          </cell>
-          <cell r="O1">
-            <v>6200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>62</v>
-          </cell>
-          <cell r="O2">
-            <v>5800</v>
+            <v>41</v>
+          </cell>
+          <cell r="O1">
+            <v>7900</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>79</v>
+          </cell>
+          <cell r="O2">
+            <v>4100</v>
           </cell>
         </row>
         <row r="3">
@@ -3178,25 +3213,25 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>32</v>
-          </cell>
-          <cell r="O1">
-            <v>8800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>88</v>
-          </cell>
-          <cell r="O2">
-            <v>3200</v>
+            <v>24</v>
+          </cell>
+          <cell r="O1">
+            <v>9600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>96</v>
+          </cell>
+          <cell r="O2">
+            <v>2400</v>
           </cell>
         </row>
         <row r="3">
@@ -3218,25 +3253,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>53</v>
-          </cell>
-          <cell r="O1">
-            <v>13400</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>67</v>
-          </cell>
-          <cell r="O2">
-            <v>10600</v>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -3258,25 +3293,25 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>58</v>
-          </cell>
-          <cell r="O1">
-            <v>6200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>62</v>
-          </cell>
-          <cell r="O2">
-            <v>5800</v>
+            <v>41</v>
+          </cell>
+          <cell r="O1">
+            <v>7900</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>79</v>
+          </cell>
+          <cell r="O2">
+            <v>4100</v>
           </cell>
         </row>
         <row r="3">
@@ -3298,25 +3333,25 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>15000</v>
           </cell>
           <cell r="K1">
-            <v>83</v>
-          </cell>
-          <cell r="O1">
-            <v>5550</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>37</v>
-          </cell>
-          <cell r="O2">
-            <v>12450</v>
+            <v>66</v>
+          </cell>
+          <cell r="O1">
+            <v>8100</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>54</v>
+          </cell>
+          <cell r="O2">
+            <v>9900</v>
           </cell>
         </row>
         <row r="3">
@@ -3420,25 +3455,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>100000</v>
           </cell>
           <cell r="K1">
-            <v>33</v>
-          </cell>
-          <cell r="O1">
-            <v>28000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>7</v>
-          </cell>
-          <cell r="O2">
-            <v>132000</v>
+            <v>31</v>
+          </cell>
+          <cell r="O1">
+            <v>36000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>9</v>
+          </cell>
+          <cell r="O2">
+            <v>124000</v>
           </cell>
         </row>
         <row r="3">
@@ -3460,25 +3495,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>66</v>
-          </cell>
-          <cell r="O1">
-            <v>27000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>54</v>
-          </cell>
-          <cell r="O2">
-            <v>33000</v>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>60000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -3500,25 +3535,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>74</v>
-          </cell>
-          <cell r="O1">
-            <v>9200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>46</v>
-          </cell>
-          <cell r="O2">
-            <v>14800</v>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -3540,25 +3575,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>86</v>
-          </cell>
-          <cell r="O1">
-            <v>6800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>34</v>
-          </cell>
-          <cell r="O2">
-            <v>17200</v>
+            <v>82</v>
+          </cell>
+          <cell r="O1">
+            <v>7600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>38</v>
+          </cell>
+          <cell r="O2">
+            <v>16400</v>
           </cell>
         </row>
         <row r="3">
@@ -3580,25 +3615,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>74</v>
-          </cell>
-          <cell r="O1">
-            <v>9200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>46</v>
-          </cell>
-          <cell r="O2">
-            <v>14800</v>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -3620,25 +3655,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>76</v>
-          </cell>
-          <cell r="O1">
-            <v>8800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>44</v>
-          </cell>
-          <cell r="O2">
-            <v>15200</v>
+            <v>56</v>
+          </cell>
+          <cell r="O1">
+            <v>12800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>64</v>
+          </cell>
+          <cell r="O2">
+            <v>11200</v>
           </cell>
         </row>
         <row r="7">
@@ -3700,7 +3735,7 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -3745,18 +3780,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>77</v>
-          </cell>
-          <cell r="O1">
-            <v>4300</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>43</v>
-          </cell>
-          <cell r="O2">
-            <v>7700</v>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -3779,25 +3814,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>11</v>
-          </cell>
-          <cell r="O1">
-            <v>8600</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>6</v>
-          </cell>
-          <cell r="O2">
-            <v>15400</v>
+            <v>9</v>
+          </cell>
+          <cell r="O1">
+            <v>11400</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>8</v>
+          </cell>
+          <cell r="O2">
+            <v>12600</v>
           </cell>
         </row>
         <row r="3">
@@ -3806,7 +3841,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3863,25 +3898,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>12</v>
-          </cell>
-          <cell r="O1">
-            <v>7200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>5</v>
-          </cell>
-          <cell r="O2">
-            <v>16800</v>
+            <v>10</v>
+          </cell>
+          <cell r="O1">
+            <v>10000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>7</v>
+          </cell>
+          <cell r="O2">
+            <v>14000</v>
           </cell>
         </row>
         <row r="3">
@@ -3890,7 +3925,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3904,25 +3939,25 @@
       <sheetName val="MD20000.22-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>87</v>
-          </cell>
-          <cell r="O1">
-            <v>6600</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>33</v>
-          </cell>
-          <cell r="O2">
-            <v>17400</v>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -3944,25 +3979,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>30000</v>
           </cell>
           <cell r="K1">
-            <v>90</v>
-          </cell>
-          <cell r="O1">
-            <v>9000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>30</v>
-          </cell>
-          <cell r="O2">
-            <v>27000</v>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>36000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -4024,25 +4059,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>99</v>
-          </cell>
-          <cell r="O1">
-            <v>2100</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>21</v>
-          </cell>
-          <cell r="O2">
-            <v>9900</v>
+            <v>83</v>
+          </cell>
+          <cell r="O1">
+            <v>3700</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>37</v>
+          </cell>
+          <cell r="O2">
+            <v>8300</v>
           </cell>
         </row>
         <row r="3">
@@ -4065,25 +4100,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>100000</v>
           </cell>
           <cell r="K1">
-            <v>254</v>
-          </cell>
-          <cell r="O1">
-            <v>7800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>13</v>
-          </cell>
-          <cell r="O2">
-            <v>152400</v>
+            <v>248</v>
+          </cell>
+          <cell r="O1">
+            <v>11400</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>19</v>
+          </cell>
+          <cell r="O2">
+            <v>148800</v>
           </cell>
         </row>
         <row r="3">
@@ -4092,7 +4127,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4106,25 +4141,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>115</v>
-          </cell>
-          <cell r="O1">
-            <v>2500</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>5</v>
-          </cell>
-          <cell r="O2">
-            <v>57500</v>
+            <v>96</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>24</v>
+          </cell>
+          <cell r="O2">
+            <v>48000</v>
           </cell>
         </row>
         <row r="3">
@@ -4146,29 +4181,31 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>30000</v>
           </cell>
           <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>36000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
             <v>120</v>
           </cell>
-          <cell r="O1">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>0</v>
-          </cell>
-          <cell r="O2">
-            <v>36000</v>
+          <cell r="O2">
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
-          <cell r="B3"/>
+          <cell r="B3">
+            <v>45647</v>
+          </cell>
         </row>
       </sheetData>
     </sheetDataSet>
@@ -4184,29 +4221,31 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>120</v>
-          </cell>
-          <cell r="O1">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>0</v>
-          </cell>
-          <cell r="O2">
-            <v>12000</v>
+            <v>104</v>
+          </cell>
+          <cell r="O1">
+            <v>1600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>16</v>
+          </cell>
+          <cell r="O2">
+            <v>10400</v>
           </cell>
         </row>
         <row r="3">
-          <cell r="B3"/>
+          <cell r="B3">
+            <v>45635</v>
+          </cell>
         </row>
       </sheetData>
     </sheetDataSet>
@@ -4222,29 +4261,31 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>120</v>
-          </cell>
-          <cell r="O1">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>0</v>
-          </cell>
-          <cell r="O2">
-            <v>12000</v>
+            <v>104</v>
+          </cell>
+          <cell r="O1">
+            <v>1600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>16</v>
+          </cell>
+          <cell r="O2">
+            <v>10400</v>
           </cell>
         </row>
         <row r="3">
-          <cell r="B3"/>
+          <cell r="B3">
+            <v>45635</v>
+          </cell>
         </row>
       </sheetData>
     </sheetDataSet>
@@ -4285,6 +4326,90 @@
         <row r="3">
           <cell r="B3">
             <v>45646</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink90.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD50000.15-DEC"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>200000</v>
+          </cell>
+          <cell r="K1">
+            <v>266</v>
+          </cell>
+          <cell r="O1">
+            <v>1200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>1</v>
+          </cell>
+          <cell r="O2">
+            <v>319200</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45648</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink91.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEc"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>14</v>
+          </cell>
+          <cell r="O1">
+            <v>2100</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>3</v>
+          </cell>
+          <cell r="O2">
+            <v>9900</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45649</v>
           </cell>
         </row>
       </sheetData>
@@ -4549,7 +4674,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4592,12 +4717,12 @@
       <c r="K2" s="27"/>
       <c r="L2" s="23">
         <f>SUM(L5:L108)</f>
-        <v>753400</v>
+        <v>860200</v>
       </c>
       <c r="M2" s="24"/>
       <c r="N2" s="1">
         <f>SUM(N5:N117)</f>
-        <v>49150</v>
+        <v>33400</v>
       </c>
       <c r="Q2" s="1">
         <f>14900+260750</f>
@@ -5132,7 +5257,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="17">
         <v>13</v>
       </c>
@@ -5169,7 +5294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="17">
         <v>14</v>
       </c>
@@ -5209,7 +5334,7 @@
         <v>16800</v>
       </c>
     </row>
-    <row r="19" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="17">
         <v>15</v>
       </c>
@@ -5249,50 +5374,47 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="20" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="12">
+    <row r="20" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="17">
         <v>16</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="19">
         <f>'[15]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13">
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20">
         <f>'[15]MD10000.10-JAN'!$K$1</f>
-        <v>1</v>
-      </c>
-      <c r="I20" s="13">
+        <v>0</v>
+      </c>
+      <c r="I20" s="20">
         <f>'[15]MD10000.10-JAN'!$K$2</f>
-        <v>47</v>
-      </c>
-      <c r="J20" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="J20" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K20" s="14">
+      <c r="K20" s="22">
         <f>'[15]MD10000.10-JAN'!$B$3</f>
         <v>45308</v>
       </c>
-      <c r="L20" s="15">
+      <c r="L20" s="19">
         <f>'[15]MD10000.10-JAN'!$O$2</f>
-        <v>350</v>
-      </c>
-      <c r="M20" s="15">
+        <v>0</v>
+      </c>
+      <c r="M20" s="19">
         <f>'[15]MD10000.10-JAN'!$O$1</f>
-        <v>16450</v>
-      </c>
-      <c r="N20" s="1">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="21" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>16800</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="17">
         <v>17</v>
       </c>
@@ -5332,7 +5454,7 @@
         <v>16800</v>
       </c>
     </row>
-    <row r="22" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="17">
         <v>18</v>
       </c>
@@ -5372,7 +5494,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="23" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="17">
         <v>19</v>
       </c>
@@ -5412,7 +5534,7 @@
         <v>16800</v>
       </c>
     </row>
-    <row r="24" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="17">
         <v>20</v>
       </c>
@@ -5452,7 +5574,7 @@
         <v>16800</v>
       </c>
     </row>
-    <row r="25" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="17">
         <v>21</v>
       </c>
@@ -5492,7 +5614,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="26" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="17">
         <v>22</v>
       </c>
@@ -5532,7 +5654,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="27" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="17">
         <v>23</v>
       </c>
@@ -5572,7 +5694,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="28" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="17">
         <v>24</v>
       </c>
@@ -5612,7 +5734,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="29" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="17">
         <v>25</v>
       </c>
@@ -5652,7 +5774,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="30" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="17">
         <v>26</v>
       </c>
@@ -5692,7 +5814,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="31" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="17">
         <v>27</v>
       </c>
@@ -5732,7 +5854,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="32" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="17">
         <v>28</v>
       </c>
@@ -5914,7 +6036,7 @@
       </c>
       <c r="I36" s="13">
         <f>'[32]MD10000.10-JAN'!$K$2</f>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J36" s="16" t="s">
         <v>12</v>
@@ -5925,11 +6047,11 @@
       </c>
       <c r="L36" s="15">
         <f>'[32]MD10000.10-JAN'!$O$2</f>
-        <v>4900</v>
+        <v>4200</v>
       </c>
       <c r="M36" s="15">
         <f>'[32]MD10000.10-JAN'!$O$1</f>
-        <v>11900</v>
+        <v>12600</v>
       </c>
       <c r="N36" s="1">
         <v>350</v>
@@ -6412,7 +6534,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="49" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B49" s="17">
         <v>45</v>
       </c>
@@ -6452,7 +6574,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="50" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B50" s="17">
         <v>46</v>
       </c>
@@ -6492,7 +6614,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="51" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="17">
         <v>47</v>
       </c>
@@ -6532,7 +6654,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="52" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B52" s="17">
         <v>48</v>
       </c>
@@ -6572,7 +6694,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="53" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B53" s="17">
         <v>49</v>
       </c>
@@ -6612,7 +6734,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="54" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B54" s="17">
         <v>50</v>
       </c>
@@ -6652,7 +6774,7 @@
         <v>5950</v>
       </c>
     </row>
-    <row r="55" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B55" s="17">
         <v>51</v>
       </c>
@@ -6692,7 +6814,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="56" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B56" s="17">
         <v>52</v>
       </c>
@@ -6732,7 +6854,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="57" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B57" s="17">
         <v>53</v>
       </c>
@@ -6772,50 +6894,47 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="58" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="6">
+    <row r="58" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B58" s="17">
         <v>54</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="C58" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="D58" s="10" t="s">
+      <c r="D58" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="E58" s="7">
+      <c r="E58" s="19">
         <f>'[56]MD20000.15-DEc'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8">
+      <c r="F58" s="20"/>
+      <c r="G58" s="20"/>
+      <c r="H58" s="20">
         <f>'[56]MD20000.15-DEc'!$K$1</f>
-        <v>3</v>
-      </c>
-      <c r="I58" s="8">
+        <v>0</v>
+      </c>
+      <c r="I58" s="20">
         <f>'[56]MD20000.15-DEc'!$K$2</f>
-        <v>14</v>
-      </c>
-      <c r="J58" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K58" s="10">
+      <c r="K58" s="22">
         <f>'[56]MD20000.15-DEc'!$B$3</f>
         <v>45531</v>
       </c>
-      <c r="L58" s="7">
+      <c r="L58" s="19">
         <f>'[56]MD20000.15-DEc'!$O$2</f>
-        <v>2100</v>
-      </c>
-      <c r="M58" s="7">
+        <v>0</v>
+      </c>
+      <c r="M58" s="19">
         <f>'[56]MD20000.15-DEc'!$O$1</f>
-        <v>9900</v>
-      </c>
-      <c r="N58" s="1">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="59" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="59" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B59" s="17">
         <v>55</v>
       </c>
@@ -6855,50 +6974,47 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="60" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="6">
+    <row r="60" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="17">
         <v>56</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="C60" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="D60" s="10" t="s">
+      <c r="D60" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="E60" s="7">
+      <c r="E60" s="19">
         <f>'[58]MD20000.15-DEc'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F60" s="8"/>
-      <c r="G60" s="8"/>
-      <c r="H60" s="8">
+      <c r="F60" s="20"/>
+      <c r="G60" s="20"/>
+      <c r="H60" s="20">
         <f>'[58]MD20000.15-DEc'!$K$1</f>
-        <v>2</v>
-      </c>
-      <c r="I60" s="8">
+        <v>0</v>
+      </c>
+      <c r="I60" s="20">
         <f>'[58]MD20000.15-DEc'!$K$2</f>
-        <v>15</v>
-      </c>
-      <c r="J60" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K60" s="10">
+      <c r="K60" s="22">
         <f>'[58]MD20000.15-DEc'!$B$3</f>
         <v>45534</v>
       </c>
-      <c r="L60" s="7">
+      <c r="L60" s="19">
         <f>'[58]MD20000.15-DEc'!$O$2</f>
-        <v>1400</v>
-      </c>
-      <c r="M60" s="7">
+        <v>0</v>
+      </c>
+      <c r="M60" s="19">
         <f>'[58]MD20000.15-DEc'!$O$1</f>
-        <v>10600</v>
-      </c>
-      <c r="N60" s="1">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="61" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="61" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B61" s="17">
         <v>57</v>
       </c>
@@ -6938,7 +7054,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="62" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B62" s="17">
         <v>58</v>
       </c>
@@ -6978,7 +7094,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="63" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B63" s="17">
         <v>59</v>
       </c>
@@ -7018,90 +7134,84 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="64" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="6">
+    <row r="64" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B64" s="17">
         <v>60</v>
       </c>
-      <c r="C64" s="8" t="s">
+      <c r="C64" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="D64" s="14" t="s">
+      <c r="D64" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="E64" s="7">
+      <c r="E64" s="19">
         <f>'[62]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F64" s="8">
+      <c r="F64" s="20">
         <f>'[62]MD20000.22-DEC'!$K$1</f>
-        <v>43</v>
-      </c>
-      <c r="G64" s="8">
+        <v>0</v>
+      </c>
+      <c r="G64" s="20">
         <f>'[62]MD20000.22-DEC'!$K$2</f>
-        <v>77</v>
-      </c>
-      <c r="H64" s="8"/>
-      <c r="I64" s="8"/>
-      <c r="J64" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="H64" s="20"/>
+      <c r="I64" s="20"/>
+      <c r="J64" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K64" s="10">
+      <c r="K64" s="22">
         <f>'[62]MD20000.22-DEC'!$B$13</f>
         <v>45562</v>
       </c>
-      <c r="L64" s="7">
+      <c r="L64" s="19">
         <f>'[62]MD20000.22-DEC'!$O$2</f>
-        <v>8600</v>
-      </c>
-      <c r="M64" s="7">
+        <v>0</v>
+      </c>
+      <c r="M64" s="19">
         <f>'[62]MD20000.22-DEC'!$O$1</f>
-        <v>15400</v>
-      </c>
-      <c r="N64" s="1">
-        <v>1400</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="65" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="6">
+      <c r="B65" s="17">
         <v>61</v>
       </c>
-      <c r="C65" s="8" t="s">
+      <c r="C65" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D65" s="14" t="s">
+      <c r="D65" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="E65" s="7">
+      <c r="E65" s="19">
         <f>'[63]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F65" s="8">
+      <c r="F65" s="20">
         <f>'[63]MD10000.1-OCT'!$K$1</f>
-        <v>48</v>
-      </c>
-      <c r="G65" s="8">
+        <v>0</v>
+      </c>
+      <c r="G65" s="20">
         <f>'[63]MD10000.1-OCT'!$K$2</f>
-        <v>72</v>
-      </c>
-      <c r="H65" s="8"/>
-      <c r="I65" s="8"/>
-      <c r="J65" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="H65" s="20"/>
+      <c r="I65" s="20"/>
+      <c r="J65" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K65" s="10">
+      <c r="K65" s="22">
         <f>'[63]MD10000.1-OCT'!$B$3</f>
         <v>45557</v>
       </c>
-      <c r="L65" s="7">
+      <c r="L65" s="19">
         <f>'[63]MD10000.1-OCT'!$O$2</f>
-        <v>4800</v>
-      </c>
-      <c r="M65" s="7">
+        <v>0</v>
+      </c>
+      <c r="M65" s="19">
         <f>'[63]MD10000.1-OCT'!$O$1</f>
-        <v>7200</v>
-      </c>
-      <c r="N65" s="1">
-        <v>700</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="66" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7120,11 +7230,11 @@
       </c>
       <c r="F66" s="8">
         <f>'[64]MD10000.1-OCT'!$K$1</f>
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="G66" s="8">
         <f>'[64]MD10000.1-OCT'!$K$2</f>
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
@@ -7137,11 +7247,11 @@
       </c>
       <c r="L66" s="7">
         <f>'[64]MD10000.1-OCT'!$O$2</f>
-        <v>5800</v>
+        <v>4100</v>
       </c>
       <c r="M66" s="7">
         <f>'[64]MD10000.1-OCT'!$O$1</f>
-        <v>6200</v>
+        <v>7900</v>
       </c>
       <c r="N66" s="1">
         <v>700</v>
@@ -7163,11 +7273,11 @@
       </c>
       <c r="F67" s="8">
         <f>'[65]MD10000.1-OCT'!$K$1</f>
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G67" s="8">
         <f>'[65]MD10000.1-OCT'!$K$2</f>
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
@@ -7180,57 +7290,54 @@
       </c>
       <c r="L67" s="7">
         <f>'[65]MD10000.1-OCT'!$O$2</f>
-        <v>3200</v>
+        <v>2400</v>
       </c>
       <c r="M67" s="7">
         <f>'[65]MD10000.1-OCT'!$O$1</f>
-        <v>8800</v>
+        <v>9600</v>
       </c>
       <c r="N67" s="1">
         <v>700</v>
       </c>
     </row>
     <row r="68" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="6">
+      <c r="B68" s="17">
         <v>64</v>
       </c>
-      <c r="C68" s="13" t="s">
+      <c r="C68" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D68" s="14" t="s">
+      <c r="D68" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E68" s="7">
+      <c r="E68" s="19">
         <f>'[66]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F68" s="8">
+      <c r="F68" s="20">
         <f>'[66]MD20000.18-DEC'!$K$1</f>
-        <v>53</v>
-      </c>
-      <c r="G68" s="8">
+        <v>0</v>
+      </c>
+      <c r="G68" s="20">
         <f>'[66]MD20000.18-DEC'!$K$2</f>
-        <v>67</v>
-      </c>
-      <c r="H68" s="8"/>
-      <c r="I68" s="8"/>
-      <c r="J68" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="H68" s="20"/>
+      <c r="I68" s="20"/>
+      <c r="J68" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K68" s="10">
+      <c r="K68" s="22">
         <f>'[66]MD20000.18-DEC'!$B$3</f>
         <v>45562</v>
       </c>
-      <c r="L68" s="7">
+      <c r="L68" s="19">
         <f>'[66]MD20000.18-DEC'!$O$2</f>
-        <v>10600</v>
-      </c>
-      <c r="M68" s="7">
+        <v>0</v>
+      </c>
+      <c r="M68" s="19">
         <f>'[66]MD20000.18-DEC'!$O$1</f>
-        <v>13400</v>
-      </c>
-      <c r="N68" s="1">
-        <v>1400</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="69" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7249,11 +7356,11 @@
       </c>
       <c r="F69" s="8">
         <f>'[67]MD10000.1-OCT'!$K$1</f>
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="G69" s="8">
         <f>'[67]MD10000.1-OCT'!$K$2</f>
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="H69" s="8"/>
       <c r="I69" s="8"/>
@@ -7266,11 +7373,11 @@
       </c>
       <c r="L69" s="7">
         <f>'[67]MD10000.1-OCT'!$O$2</f>
-        <v>5800</v>
+        <v>4100</v>
       </c>
       <c r="M69" s="7">
         <f>'[67]MD10000.1-OCT'!$O$1</f>
-        <v>6200</v>
+        <v>7900</v>
       </c>
       <c r="N69" s="1">
         <v>700</v>
@@ -7292,11 +7399,11 @@
       </c>
       <c r="F70" s="8">
         <f>'[68]MD10000.1-OCT'!$K$1</f>
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="G70" s="8">
         <f>'[68]MD10000.1-OCT'!$K$2</f>
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
@@ -7309,57 +7416,54 @@
       </c>
       <c r="L70" s="7">
         <f>'[68]MD10000.1-OCT'!$O$2</f>
-        <v>12450</v>
+        <v>9900</v>
       </c>
       <c r="M70" s="7">
         <f>'[68]MD10000.1-OCT'!$O$1</f>
-        <v>5550</v>
+        <v>8100</v>
       </c>
       <c r="N70" s="1">
         <v>1050</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="6">
+      <c r="B71" s="30">
         <v>67</v>
       </c>
-      <c r="C71" s="8" t="s">
+      <c r="C71" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="D71" s="14" t="s">
+      <c r="D71" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="E71" s="7">
+      <c r="E71" s="33">
         <f>'[69]MD20000.18-DEC'!$C$1</f>
         <v>50000</v>
       </c>
-      <c r="F71" s="8">
+      <c r="F71" s="31">
         <f>'[69]MD20000.18-DEC'!$K$1</f>
         <v>66</v>
       </c>
-      <c r="G71" s="8">
+      <c r="G71" s="31">
         <f>'[69]MD20000.18-DEC'!$K$2</f>
         <v>54</v>
       </c>
-      <c r="H71" s="8"/>
-      <c r="I71" s="8"/>
-      <c r="J71" s="9" t="s">
+      <c r="H71" s="31"/>
+      <c r="I71" s="31"/>
+      <c r="J71" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="K71" s="10">
+      <c r="K71" s="32">
         <f>'[69]MD20000.18-DEC'!$B$3</f>
         <v>45579</v>
       </c>
-      <c r="L71" s="7">
+      <c r="L71" s="33">
         <f>'[69]MD20000.18-DEC'!$O$2</f>
         <v>33000</v>
       </c>
-      <c r="M71" s="7">
+      <c r="M71" s="33">
         <f>'[69]MD20000.18-DEC'!$O$1</f>
         <v>27000</v>
-      </c>
-      <c r="N71" s="1">
-        <v>3500</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7380,11 +7484,11 @@
       <c r="G72" s="8"/>
       <c r="H72" s="8">
         <f>'[70]MD20000.18-DEC'!$K$1</f>
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I72" s="8">
         <f>'[70]MD20000.18-DEC'!$K$2</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J72" s="9" t="s">
         <v>12</v>
@@ -7395,100 +7499,94 @@
       </c>
       <c r="L72" s="7">
         <f>'[70]MD20000.18-DEC'!$O$2</f>
-        <v>132000</v>
+        <v>124000</v>
       </c>
       <c r="M72" s="7">
         <f>'[70]MD20000.18-DEC'!$O$1</f>
-        <v>28000</v>
+        <v>36000</v>
       </c>
       <c r="N72" s="1">
         <v>4000</v>
       </c>
     </row>
     <row r="73" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="6">
+      <c r="B73" s="17">
         <v>69</v>
       </c>
-      <c r="C73" s="8" t="s">
+      <c r="C73" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="D73" s="14" t="s">
+      <c r="D73" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="E73" s="7">
+      <c r="E73" s="19">
         <f>'[71]MD20000.18-DEC'!$C$1</f>
         <v>50000</v>
       </c>
-      <c r="F73" s="8">
+      <c r="F73" s="20">
         <f>'[71]MD20000.18-DEC'!$K$1</f>
-        <v>66</v>
-      </c>
-      <c r="G73" s="8">
+        <v>0</v>
+      </c>
+      <c r="G73" s="20">
         <f>'[71]MD20000.18-DEC'!$K$2</f>
-        <v>54</v>
-      </c>
-      <c r="H73" s="8"/>
-      <c r="I73" s="8"/>
-      <c r="J73" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="H73" s="20"/>
+      <c r="I73" s="20"/>
+      <c r="J73" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K73" s="10">
+      <c r="K73" s="22">
         <f>'[71]MD20000.18-DEC'!$B$3</f>
         <v>45584</v>
       </c>
-      <c r="L73" s="7">
+      <c r="L73" s="19">
         <f>'[71]MD20000.18-DEC'!$O$2</f>
-        <v>33000</v>
-      </c>
-      <c r="M73" s="7">
+        <v>0</v>
+      </c>
+      <c r="M73" s="19">
         <f>'[71]MD20000.18-DEC'!$O$1</f>
-        <v>27000</v>
-      </c>
-      <c r="N73" s="1">
-        <v>3500</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="74" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="6">
+      <c r="B74" s="17">
         <v>70</v>
       </c>
-      <c r="C74" s="8" t="s">
+      <c r="C74" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D74" s="14" t="s">
+      <c r="D74" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="E74" s="7">
+      <c r="E74" s="19">
         <f>'[72]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F74" s="8">
+      <c r="F74" s="20">
         <f>'[72]MD20000.18-DEC'!$K$1</f>
-        <v>74</v>
-      </c>
-      <c r="G74" s="8">
+        <v>0</v>
+      </c>
+      <c r="G74" s="20">
         <f>'[72]MD20000.18-DEC'!$K$2</f>
-        <v>46</v>
-      </c>
-      <c r="H74" s="8"/>
-      <c r="I74" s="8"/>
-      <c r="J74" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="H74" s="20"/>
+      <c r="I74" s="20"/>
+      <c r="J74" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K74" s="10">
+      <c r="K74" s="22">
         <f>'[72]MD20000.18-DEC'!$B$3</f>
         <v>45584</v>
       </c>
-      <c r="L74" s="7">
+      <c r="L74" s="19">
         <f>'[72]MD20000.18-DEC'!$O$2</f>
-        <v>14800</v>
-      </c>
-      <c r="M74" s="7">
+        <v>0</v>
+      </c>
+      <c r="M74" s="19">
         <f>'[72]MD20000.18-DEC'!$O$1</f>
-        <v>9200</v>
-      </c>
-      <c r="N74" s="1">
-        <v>1400</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="75" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7507,11 +7605,11 @@
       </c>
       <c r="F75" s="8">
         <f>'[73]MD20000.18-DEC'!$K$1</f>
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G75" s="8">
         <f>'[73]MD20000.18-DEC'!$K$2</f>
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H75" s="8"/>
       <c r="I75" s="8"/>
@@ -7524,57 +7622,54 @@
       </c>
       <c r="L75" s="7">
         <f>'[73]MD20000.18-DEC'!$O$2</f>
-        <v>17200</v>
+        <v>16400</v>
       </c>
       <c r="M75" s="7">
         <f>'[73]MD20000.18-DEC'!$O$1</f>
-        <v>6800</v>
+        <v>7600</v>
       </c>
       <c r="N75" s="1">
         <v>1400</v>
       </c>
     </row>
     <row r="76" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="6">
+      <c r="B76" s="17">
         <v>72</v>
       </c>
-      <c r="C76" s="8" t="s">
+      <c r="C76" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="D76" s="14" t="s">
+      <c r="D76" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="E76" s="7">
+      <c r="E76" s="19">
         <f>'[74]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F76" s="8">
+      <c r="F76" s="20">
         <f>'[74]MD20000.18-DEC'!$K$1</f>
-        <v>74</v>
-      </c>
-      <c r="G76" s="8">
+        <v>0</v>
+      </c>
+      <c r="G76" s="20">
         <f>'[74]MD20000.18-DEC'!$K$2</f>
-        <v>46</v>
-      </c>
-      <c r="H76" s="8"/>
-      <c r="I76" s="8"/>
-      <c r="J76" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="H76" s="20"/>
+      <c r="I76" s="20"/>
+      <c r="J76" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K76" s="10">
+      <c r="K76" s="22">
         <f>'[74]MD20000.18-DEC'!$B$3</f>
         <v>45584</v>
       </c>
-      <c r="L76" s="7">
+      <c r="L76" s="19">
         <f>'[74]MD20000.18-DEC'!$O$2</f>
-        <v>14800</v>
-      </c>
-      <c r="M76" s="7">
+        <v>0</v>
+      </c>
+      <c r="M76" s="19">
         <f>'[74]MD20000.18-DEC'!$O$1</f>
-        <v>9200</v>
-      </c>
-      <c r="N76" s="1">
-        <v>1400</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="77" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7593,11 +7688,11 @@
       </c>
       <c r="F77" s="8">
         <f>'[75]MD20000.18-DEC'!$K$1</f>
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="G77" s="8">
         <f>'[75]MD20000.18-DEC'!$K$2</f>
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="H77" s="8"/>
       <c r="I77" s="8"/>
@@ -7610,11 +7705,11 @@
       </c>
       <c r="L77" s="7">
         <f>'[75]MD20000.18-DEC'!$O$2</f>
-        <v>15200</v>
+        <v>11200</v>
       </c>
       <c r="M77" s="7">
         <f>'[75]MD20000.18-DEC'!$O$1</f>
-        <v>8800</v>
+        <v>12800</v>
       </c>
       <c r="N77" s="1">
         <v>1400</v>
@@ -7707,46 +7802,43 @@
       </c>
     </row>
     <row r="80" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="6">
+      <c r="B80" s="17">
         <v>76</v>
       </c>
-      <c r="C80" s="8" t="s">
+      <c r="C80" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="D80" s="14" t="s">
+      <c r="D80" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="E80" s="7">
+      <c r="E80" s="19">
         <f>'[78]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F80" s="8">
+      <c r="F80" s="20">
         <f>'[78]MD20000.18-DEC'!$K$1</f>
-        <v>77</v>
-      </c>
-      <c r="G80" s="8">
+        <v>0</v>
+      </c>
+      <c r="G80" s="20">
         <f>'[78]MD20000.18-DEC'!$K$2</f>
-        <v>43</v>
-      </c>
-      <c r="H80" s="8"/>
-      <c r="I80" s="8"/>
-      <c r="J80" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="H80" s="20"/>
+      <c r="I80" s="20"/>
+      <c r="J80" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K80" s="10">
+      <c r="K80" s="22">
         <f>'[78]MD20000.18-DEC'!$B$3</f>
         <v>45587</v>
       </c>
-      <c r="L80" s="7">
+      <c r="L80" s="19">
         <f>'[78]MD20000.18-DEC'!$O$2</f>
-        <v>7700</v>
-      </c>
-      <c r="M80" s="7">
+        <v>0</v>
+      </c>
+      <c r="M80" s="19">
         <f>'[78]MD20000.18-DEC'!$O$1</f>
-        <v>4300</v>
-      </c>
-      <c r="N80" s="1">
-        <v>700</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="81" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7767,11 +7859,11 @@
       <c r="G81" s="8"/>
       <c r="H81" s="8">
         <f>'[79]MD20000.15-DEc'!$K$1</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I81" s="8">
         <f>'[79]MD20000.15-DEc'!$K$2</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J81" s="9" t="s">
         <v>12</v>
@@ -7782,11 +7874,11 @@
       </c>
       <c r="L81" s="7">
         <f>'[79]MD20000.15-DEc'!$O$2</f>
-        <v>15400</v>
+        <v>12600</v>
       </c>
       <c r="M81" s="7">
         <f>'[79]MD20000.15-DEc'!$O$1</f>
-        <v>8600</v>
+        <v>11400</v>
       </c>
       <c r="N81" s="1">
         <v>1400</v>
@@ -7810,11 +7902,11 @@
       <c r="G82" s="8"/>
       <c r="H82" s="8">
         <f>'[80]MD10000.10-JAN'!$K$1</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I82" s="8">
         <f>'[80]MD10000.10-JAN'!$K$2</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J82" s="9" t="s">
         <v>12</v>
@@ -7825,143 +7917,134 @@
       </c>
       <c r="L82" s="7">
         <f>'[80]MD10000.10-JAN'!$O$2</f>
-        <v>16800</v>
+        <v>14000</v>
       </c>
       <c r="M82" s="7">
         <f>'[80]MD10000.10-JAN'!$O$1</f>
-        <v>7200</v>
+        <v>10000</v>
       </c>
       <c r="N82" s="1">
         <v>1400</v>
       </c>
     </row>
     <row r="83" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B83" s="6">
+      <c r="B83" s="17">
         <v>79</v>
       </c>
-      <c r="C83" s="8" t="s">
+      <c r="C83" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="D83" s="14" t="s">
+      <c r="D83" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="E83" s="7">
+      <c r="E83" s="19">
         <f>'[81]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F83" s="8">
+      <c r="F83" s="20">
         <f>'[81]MD20000.22-DEC'!$K$1</f>
-        <v>87</v>
-      </c>
-      <c r="G83" s="8">
+        <v>0</v>
+      </c>
+      <c r="G83" s="20">
         <f>'[81]MD20000.22-DEC'!$K$2</f>
-        <v>33</v>
-      </c>
-      <c r="H83" s="8"/>
-      <c r="I83" s="8"/>
-      <c r="J83" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="H83" s="20"/>
+      <c r="I83" s="20"/>
+      <c r="J83" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K83" s="10">
+      <c r="K83" s="22">
         <f>'[81]MD20000.22-DEC'!$B$3</f>
         <v>45597</v>
       </c>
-      <c r="L83" s="7">
+      <c r="L83" s="19">
         <f>'[81]MD20000.22-DEC'!$O$2</f>
-        <v>17400</v>
-      </c>
-      <c r="M83" s="7">
+        <v>0</v>
+      </c>
+      <c r="M83" s="19">
         <f>'[81]MD20000.22-DEC'!$O$1</f>
-        <v>6600</v>
-      </c>
-      <c r="N83" s="1">
-        <v>1400</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="84" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B84" s="6">
+      <c r="B84" s="17">
         <v>80</v>
       </c>
-      <c r="C84" s="8" t="s">
+      <c r="C84" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="D84" s="14" t="s">
+      <c r="D84" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="E84" s="7">
+      <c r="E84" s="19">
         <f>'[82]MD20000.18-DEC'!$C$1</f>
         <v>30000</v>
       </c>
-      <c r="F84" s="8">
+      <c r="F84" s="20">
         <f>'[82]MD20000.18-DEC'!$K$1</f>
-        <v>90</v>
-      </c>
-      <c r="G84" s="8">
+        <v>0</v>
+      </c>
+      <c r="G84" s="20">
         <f>'[82]MD20000.18-DEC'!$K$2</f>
-        <v>30</v>
-      </c>
-      <c r="H84" s="8"/>
-      <c r="I84" s="8"/>
-      <c r="J84" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="H84" s="20"/>
+      <c r="I84" s="20"/>
+      <c r="J84" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K84" s="10">
+      <c r="K84" s="22">
         <f>'[82]MD20000.18-DEC'!$B$3</f>
         <v>45602</v>
       </c>
-      <c r="L84" s="7">
+      <c r="L84" s="19">
         <f>'[82]MD20000.18-DEC'!$O$2</f>
-        <v>27000</v>
-      </c>
-      <c r="M84" s="7">
+        <v>0</v>
+      </c>
+      <c r="M84" s="19">
         <f>'[82]MD20000.18-DEC'!$O$1</f>
-        <v>9000</v>
-      </c>
-      <c r="N84" s="1">
-        <v>2100</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="85" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="6">
+      <c r="B85" s="30">
         <v>81</v>
       </c>
-      <c r="C85" s="8" t="s">
+      <c r="C85" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="D85" s="14" t="s">
+      <c r="D85" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="E85" s="7">
+      <c r="E85" s="33">
         <f>'[83]MD20000.18-DEC'!$C$1</f>
         <v>50000</v>
       </c>
-      <c r="F85" s="8">
+      <c r="F85" s="31">
         <f>'[83]MD20000.18-DEC'!$K$1</f>
         <v>100</v>
       </c>
-      <c r="G85" s="8">
+      <c r="G85" s="31">
         <f>'[83]MD20000.18-DEC'!$K$2</f>
         <v>20</v>
       </c>
-      <c r="H85" s="8"/>
-      <c r="I85" s="8"/>
-      <c r="J85" s="9" t="s">
+      <c r="H85" s="31"/>
+      <c r="I85" s="31"/>
+      <c r="J85" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="K85" s="10">
+      <c r="K85" s="32">
         <f>'[83]MD20000.18-DEC'!$B$3</f>
         <v>45612</v>
       </c>
-      <c r="L85" s="7">
+      <c r="L85" s="33">
         <f>'[83]MD20000.18-DEC'!$O$2</f>
         <v>50000</v>
       </c>
-      <c r="M85" s="7">
+      <c r="M85" s="33">
         <f>'[83]MD20000.18-DEC'!$O$1</f>
         <v>10000</v>
-      </c>
-      <c r="N85" s="1">
-        <v>3500</v>
       </c>
     </row>
     <row r="86" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7980,11 +8063,11 @@
       </c>
       <c r="F86" s="8">
         <f>'[84]MD20000.18-DEC'!$K$1</f>
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="G86" s="8">
         <f>'[84]MD20000.18-DEC'!$K$2</f>
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="H86" s="8"/>
       <c r="I86" s="8"/>
@@ -7997,11 +8080,11 @@
       </c>
       <c r="L86" s="7">
         <f>'[84]MD20000.18-DEC'!$O$2</f>
-        <v>9900</v>
+        <v>8300</v>
       </c>
       <c r="M86" s="7">
         <f>'[84]MD20000.18-DEC'!$O$1</f>
-        <v>2100</v>
+        <v>3700</v>
       </c>
       <c r="N86" s="1">
         <v>700</v>
@@ -8023,11 +8106,11 @@
       </c>
       <c r="F87" s="8">
         <f>'[85]MD50000.15-DEC'!$K$1</f>
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G87" s="8">
         <f>'[85]MD50000.15-DEC'!$K$2</f>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H87" s="8"/>
       <c r="I87" s="8"/>
@@ -8040,11 +8123,11 @@
       </c>
       <c r="L87" s="7">
         <f>'[85]MD50000.15-DEC'!$O$2</f>
-        <v>152400</v>
+        <v>148800</v>
       </c>
       <c r="M87" s="7">
         <f>'[85]MD50000.15-DEC'!$O$1</f>
-        <v>7800</v>
+        <v>11400</v>
       </c>
       <c r="N87" s="1">
         <v>4200</v>
@@ -8066,11 +8149,11 @@
       </c>
       <c r="F88" s="8">
         <f>'[86]MD20000.18-DEC'!$K$1</f>
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="G88" s="8">
         <f>'[86]MD20000.18-DEC'!$K$2</f>
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="H88" s="8"/>
       <c r="I88" s="8"/>
@@ -8083,57 +8166,54 @@
       </c>
       <c r="L88" s="7">
         <f>'[86]MD20000.18-DEC'!$O$2</f>
-        <v>57500</v>
+        <v>48000</v>
       </c>
       <c r="M88" s="7">
         <f>'[86]MD20000.18-DEC'!$O$1</f>
-        <v>2500</v>
+        <v>12000</v>
       </c>
       <c r="N88" s="1">
         <v>3500</v>
       </c>
     </row>
     <row r="89" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B89" s="6">
+      <c r="B89" s="17">
         <v>85</v>
       </c>
-      <c r="C89" s="8" t="s">
+      <c r="C89" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="D89" s="14" t="s">
+      <c r="D89" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="E89" s="7">
+      <c r="E89" s="19">
         <f>'[87]MD20000.18-DEC'!$C$1</f>
         <v>30000</v>
       </c>
-      <c r="F89" s="8">
+      <c r="F89" s="20">
         <f>'[87]MD20000.18-DEC'!$K$1</f>
+        <v>0</v>
+      </c>
+      <c r="G89" s="20">
+        <f>'[87]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="G89" s="8">
-        <f>'[87]MD20000.18-DEC'!$K$2</f>
-        <v>0</v>
-      </c>
-      <c r="H89" s="8"/>
-      <c r="I89" s="8"/>
-      <c r="J89" s="9" t="s">
+      <c r="H89" s="20"/>
+      <c r="I89" s="20"/>
+      <c r="J89" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K89" s="10">
+      <c r="K89" s="22">
         <f>'[87]MD20000.18-DEC'!$B$3</f>
-        <v>0</v>
-      </c>
-      <c r="L89" s="7">
+        <v>45647</v>
+      </c>
+      <c r="L89" s="19">
         <f>'[87]MD20000.18-DEC'!$O$2</f>
+        <v>0</v>
+      </c>
+      <c r="M89" s="19">
+        <f>'[87]MD20000.18-DEC'!$O$1</f>
         <v>36000</v>
-      </c>
-      <c r="M89" s="7">
-        <f>'[87]MD20000.18-DEC'!$O$1</f>
-        <v>0</v>
-      </c>
-      <c r="N89" s="1">
-        <v>2100</v>
       </c>
     </row>
     <row r="90" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8152,11 +8232,11 @@
       </c>
       <c r="F90" s="8">
         <f>'[88]MD20000.18-DEC'!$K$1</f>
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="G90" s="8">
         <f>'[88]MD20000.18-DEC'!$K$2</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H90" s="8"/>
       <c r="I90" s="8"/>
@@ -8165,15 +8245,15 @@
       </c>
       <c r="K90" s="10">
         <f>'[88]MD20000.18-DEC'!$B$3</f>
-        <v>0</v>
+        <v>45635</v>
       </c>
       <c r="L90" s="7">
         <f>'[88]MD20000.18-DEC'!$O$2</f>
-        <v>12000</v>
+        <v>10400</v>
       </c>
       <c r="M90" s="7">
         <f>'[88]MD20000.18-DEC'!$O$1</f>
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="N90" s="1">
         <v>700</v>
@@ -8195,11 +8275,11 @@
       </c>
       <c r="F91" s="8">
         <f>'[89]MD20000.18-DEC'!$K$1</f>
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="G91" s="8">
         <f>'[89]MD20000.18-DEC'!$K$2</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H91" s="8"/>
       <c r="I91" s="8"/>
@@ -8208,15 +8288,15 @@
       </c>
       <c r="K91" s="10">
         <f>'[89]MD20000.18-DEC'!$B$3</f>
-        <v>0</v>
+        <v>45635</v>
       </c>
       <c r="L91" s="7">
         <f>'[89]MD20000.18-DEC'!$O$2</f>
-        <v>12000</v>
+        <v>10400</v>
       </c>
       <c r="M91" s="7">
         <f>'[89]MD20000.18-DEC'!$O$1</f>
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="N91" s="1">
         <v>700</v>
@@ -8226,33 +8306,87 @@
       <c r="B92" s="6">
         <v>88</v>
       </c>
-      <c r="C92" s="8"/>
-      <c r="D92" s="14"/>
-      <c r="E92" s="7"/>
-      <c r="F92" s="8"/>
-      <c r="G92" s="8"/>
+      <c r="C92" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D92" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E92" s="7">
+        <f>'[90]MD50000.15-DEC'!$C$1</f>
+        <v>200000</v>
+      </c>
+      <c r="F92" s="8">
+        <f>'[90]MD50000.15-DEC'!$K$1</f>
+        <v>266</v>
+      </c>
+      <c r="G92" s="8">
+        <f>'[90]MD50000.15-DEC'!$K$2</f>
+        <v>1</v>
+      </c>
       <c r="H92" s="8"/>
       <c r="I92" s="8"/>
-      <c r="J92" s="9"/>
-      <c r="K92" s="10"/>
-      <c r="L92" s="7"/>
-      <c r="M92" s="7"/>
+      <c r="J92" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K92" s="10">
+        <f>'[90]MD50000.15-DEC'!$B$3</f>
+        <v>45648</v>
+      </c>
+      <c r="L92" s="7">
+        <f>'[90]MD50000.15-DEC'!$O$2</f>
+        <v>319200</v>
+      </c>
+      <c r="M92" s="7">
+        <f>'[90]MD50000.15-DEC'!$O$1</f>
+        <v>1200</v>
+      </c>
+      <c r="N92" s="1">
+        <v>8400</v>
+      </c>
     </row>
     <row r="93" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B93" s="6">
         <v>89</v>
       </c>
-      <c r="C93" s="8"/>
-      <c r="D93" s="14"/>
-      <c r="E93" s="7"/>
+      <c r="C93" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D93" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="E93" s="7">
+        <f>'[91]MD20000.15-DEc'!$C$1</f>
+        <v>10000</v>
+      </c>
       <c r="F93" s="8"/>
       <c r="G93" s="8"/>
-      <c r="H93" s="8"/>
-      <c r="I93" s="8"/>
-      <c r="J93" s="9"/>
-      <c r="K93" s="10"/>
-      <c r="L93" s="7"/>
-      <c r="M93" s="7"/>
+      <c r="H93" s="8">
+        <f>'[91]MD20000.15-DEc'!$K$1</f>
+        <v>14</v>
+      </c>
+      <c r="I93" s="8">
+        <f>'[91]MD20000.15-DEc'!$K$2</f>
+        <v>3</v>
+      </c>
+      <c r="J93" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K93" s="10">
+        <f>'[91]MD20000.15-DEc'!$B$3</f>
+        <v>45649</v>
+      </c>
+      <c r="L93" s="7">
+        <f>'[91]MD20000.15-DEc'!$O$2</f>
+        <v>9900</v>
+      </c>
+      <c r="M93" s="7">
+        <f>'[91]MD20000.15-DEc'!$O$1</f>
+        <v>2100</v>
+      </c>
+      <c r="N93" s="1">
+        <v>700</v>
+      </c>
     </row>
     <row r="94" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B94" s="6">

--- a/LoanOfficer-A/LoanBook.xlsx
+++ b/LoanOfficer-A/LoanBook.xlsx
@@ -101,13 +101,14 @@
     <externalReference r:id="rId90"/>
     <externalReference r:id="rId91"/>
     <externalReference r:id="rId92"/>
+    <externalReference r:id="rId93"/>
   </externalReferences>
   <calcPr calcId="145621" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="121">
   <si>
     <t>Code</t>
   </si>
@@ -467,6 +468,9 @@
   </si>
   <si>
     <t>L10000W17P700</t>
+  </si>
+  <si>
+    <t>Angom Bijenty</t>
   </si>
 </sst>
 </file>
@@ -689,6 +693,21 @@
     <xf numFmtId="15" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -708,21 +727,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1807,15 +1811,15 @@
             <v>48</v>
           </cell>
           <cell r="O1">
-            <v>12600</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>36</v>
-          </cell>
-          <cell r="O2">
-            <v>4200</v>
+            <v>12950</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>37</v>
+          </cell>
+          <cell r="O2">
+            <v>3850</v>
           </cell>
         </row>
         <row r="3">
@@ -2810,7 +2814,7 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -2837,7 +2841,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3180,18 +3184,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>41</v>
-          </cell>
-          <cell r="O1">
-            <v>7900</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>79</v>
-          </cell>
-          <cell r="O2">
-            <v>4100</v>
+            <v>38</v>
+          </cell>
+          <cell r="O1">
+            <v>8200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>82</v>
+          </cell>
+          <cell r="O2">
+            <v>3800</v>
           </cell>
         </row>
         <row r="3">
@@ -3220,18 +3224,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>24</v>
-          </cell>
-          <cell r="O1">
-            <v>9600</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>96</v>
-          </cell>
-          <cell r="O2">
-            <v>2400</v>
+            <v>19</v>
+          </cell>
+          <cell r="O1">
+            <v>10100</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>101</v>
+          </cell>
+          <cell r="O2">
+            <v>1900</v>
           </cell>
         </row>
         <row r="3">
@@ -3300,18 +3304,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>41</v>
-          </cell>
-          <cell r="O1">
-            <v>7900</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>79</v>
-          </cell>
-          <cell r="O2">
-            <v>4100</v>
+            <v>37</v>
+          </cell>
+          <cell r="O1">
+            <v>8300</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>83</v>
+          </cell>
+          <cell r="O2">
+            <v>3700</v>
           </cell>
         </row>
         <row r="3">
@@ -3340,10 +3344,50 @@
             <v>15000</v>
           </cell>
           <cell r="K1">
+            <v>63</v>
+          </cell>
+          <cell r="O1">
+            <v>8550</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>57</v>
+          </cell>
+          <cell r="O2">
+            <v>9450</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45570</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>50000</v>
+          </cell>
+          <cell r="K1">
             <v>66</v>
           </cell>
           <cell r="O1">
-            <v>8100</v>
+            <v>27000</v>
           </cell>
         </row>
         <row r="2">
@@ -3351,21 +3395,63 @@
             <v>54</v>
           </cell>
           <cell r="O2">
-            <v>9900</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45570</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
+            <v>33000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45579</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD15000.27-NOV"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>15000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>18000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45266</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3377,77 +3463,75 @@
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
-            <v>50000</v>
+            <v>100000</v>
           </cell>
           <cell r="K1">
-            <v>66</v>
-          </cell>
-          <cell r="O1">
-            <v>27000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>54</v>
-          </cell>
-          <cell r="O2">
-            <v>33000</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45579</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD15000.27-NOV"/>
-      <sheetName val="Sheet1"/>
+            <v>31</v>
+          </cell>
+          <cell r="O1">
+            <v>36000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>9</v>
+          </cell>
+          <cell r="O2">
+            <v>124000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45590</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink71.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
-            <v>15000</v>
+            <v>50000</v>
           </cell>
           <cell r="K1">
             <v>0</v>
           </cell>
           <cell r="O1">
-            <v>18000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45266</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
+            <v>60000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45584</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink72.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3459,35 +3543,35 @@
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
-            <v>100000</v>
+            <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>31</v>
-          </cell>
-          <cell r="O1">
-            <v>36000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>9</v>
-          </cell>
-          <cell r="O2">
-            <v>124000</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45590</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink71.xml><?xml version="1.0" encoding="utf-8"?>
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45584</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink73.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3499,21 +3583,21 @@
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
-            <v>50000</v>
+            <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>60000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
+            <v>82</v>
+          </cell>
+          <cell r="O1">
+            <v>7600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>38</v>
+          </cell>
+          <cell r="O2">
+            <v>16400</v>
           </cell>
         </row>
         <row r="3">
@@ -3527,7 +3611,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink72.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink74.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3567,7 +3651,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink73.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink75.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3582,98 +3666,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>82</v>
-          </cell>
-          <cell r="O1">
-            <v>7600</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>38</v>
-          </cell>
-          <cell r="O2">
-            <v>16400</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45584</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink74.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45584</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink75.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>56</v>
-          </cell>
-          <cell r="O1">
-            <v>12800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>64</v>
-          </cell>
-          <cell r="O2">
-            <v>11200</v>
+            <v>51</v>
+          </cell>
+          <cell r="O1">
+            <v>13800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>69</v>
+          </cell>
+          <cell r="O2">
+            <v>10200</v>
           </cell>
         </row>
         <row r="7">
@@ -3742,18 +3746,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>89</v>
-          </cell>
-          <cell r="O1">
-            <v>3100</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>31</v>
-          </cell>
-          <cell r="O2">
-            <v>8900</v>
+            <v>82</v>
+          </cell>
+          <cell r="O1">
+            <v>3800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>38</v>
+          </cell>
+          <cell r="O2">
+            <v>8200</v>
           </cell>
         </row>
         <row r="3">
@@ -3821,18 +3825,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
+            <v>8</v>
+          </cell>
+          <cell r="O1">
+            <v>12800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
             <v>9</v>
           </cell>
-          <cell r="O1">
-            <v>11400</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>8</v>
-          </cell>
-          <cell r="O2">
-            <v>12600</v>
+          <cell r="O2">
+            <v>11200</v>
           </cell>
         </row>
         <row r="3">
@@ -3905,18 +3909,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>10</v>
-          </cell>
-          <cell r="O1">
-            <v>10000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>7</v>
-          </cell>
-          <cell r="O2">
-            <v>14000</v>
+            <v>9</v>
+          </cell>
+          <cell r="O1">
+            <v>11400</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>8</v>
+          </cell>
+          <cell r="O2">
+            <v>12600</v>
           </cell>
         </row>
         <row r="3">
@@ -4066,18 +4070,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>83</v>
-          </cell>
-          <cell r="O1">
-            <v>3700</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>37</v>
-          </cell>
-          <cell r="O2">
-            <v>8300</v>
+            <v>78</v>
+          </cell>
+          <cell r="O1">
+            <v>4200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>42</v>
+          </cell>
+          <cell r="O2">
+            <v>7800</v>
           </cell>
         </row>
         <row r="3">
@@ -4107,18 +4111,18 @@
             <v>100000</v>
           </cell>
           <cell r="K1">
-            <v>248</v>
-          </cell>
-          <cell r="O1">
-            <v>11400</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>19</v>
-          </cell>
-          <cell r="O2">
-            <v>148800</v>
+            <v>245</v>
+          </cell>
+          <cell r="O1">
+            <v>13200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>22</v>
+          </cell>
+          <cell r="O2">
+            <v>147000</v>
           </cell>
         </row>
         <row r="3">
@@ -4148,18 +4152,18 @@
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>96</v>
-          </cell>
-          <cell r="O1">
-            <v>12000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>24</v>
-          </cell>
-          <cell r="O2">
-            <v>48000</v>
+            <v>92</v>
+          </cell>
+          <cell r="O1">
+            <v>14000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>28</v>
+          </cell>
+          <cell r="O2">
+            <v>46000</v>
           </cell>
         </row>
         <row r="3">
@@ -4228,18 +4232,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>104</v>
-          </cell>
-          <cell r="O1">
-            <v>1600</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>16</v>
-          </cell>
-          <cell r="O2">
-            <v>10400</v>
+            <v>99</v>
+          </cell>
+          <cell r="O1">
+            <v>2100</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>21</v>
+          </cell>
+          <cell r="O2">
+            <v>9900</v>
           </cell>
         </row>
         <row r="3">
@@ -4268,18 +4272,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>104</v>
-          </cell>
-          <cell r="O1">
-            <v>1600</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>16</v>
-          </cell>
-          <cell r="O2">
-            <v>10400</v>
+            <v>99</v>
+          </cell>
+          <cell r="O1">
+            <v>2100</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>21</v>
+          </cell>
+          <cell r="O2">
+            <v>9900</v>
           </cell>
         </row>
         <row r="3">
@@ -4351,18 +4355,18 @@
             <v>200000</v>
           </cell>
           <cell r="K1">
-            <v>266</v>
-          </cell>
-          <cell r="O1">
-            <v>1200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>1</v>
-          </cell>
-          <cell r="O2">
-            <v>319200</v>
+            <v>263</v>
+          </cell>
+          <cell r="O1">
+            <v>4800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>4</v>
+          </cell>
+          <cell r="O2">
+            <v>315600</v>
           </cell>
         </row>
         <row r="3">
@@ -4386,30 +4390,72 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>14</v>
+          </cell>
+          <cell r="O1">
+            <v>2100</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>3</v>
+          </cell>
+          <cell r="O2">
+            <v>9900</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45649</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink92.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD50000.15-DEC"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
-            <v>10000</v>
+            <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>14</v>
-          </cell>
-          <cell r="O1">
-            <v>2100</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>3</v>
-          </cell>
-          <cell r="O2">
-            <v>9900</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45649</v>
+            <v>118</v>
+          </cell>
+          <cell r="O1">
+            <v>1000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>2</v>
+          </cell>
+          <cell r="O2">
+            <v>59000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45652</v>
           </cell>
         </row>
       </sheetData>
@@ -4674,7 +4720,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4706,23 +4752,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="I2" s="25" t="s">
+      <c r="C2" s="34"/>
+      <c r="I2" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="26"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="23">
+      <c r="J2" s="31"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="28">
         <f>SUM(L5:L108)</f>
-        <v>860200</v>
-      </c>
-      <c r="M2" s="24"/>
+        <v>903800</v>
+      </c>
+      <c r="M2" s="29"/>
       <c r="N2" s="1">
         <f>SUM(N5:N117)</f>
-        <v>33400</v>
+        <v>36900</v>
       </c>
       <c r="Q2" s="1">
         <f>14900+260750</f>
@@ -6036,7 +6082,7 @@
       </c>
       <c r="I36" s="13">
         <f>'[32]MD10000.10-JAN'!$K$2</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J36" s="16" t="s">
         <v>12</v>
@@ -6047,11 +6093,11 @@
       </c>
       <c r="L36" s="15">
         <f>'[32]MD10000.10-JAN'!$O$2</f>
-        <v>4200</v>
+        <v>3850</v>
       </c>
       <c r="M36" s="15">
         <f>'[32]MD10000.10-JAN'!$O$1</f>
-        <v>12600</v>
+        <v>12950</v>
       </c>
       <c r="N36" s="1">
         <v>350</v>
@@ -7230,11 +7276,11 @@
       </c>
       <c r="F66" s="8">
         <f>'[64]MD10000.1-OCT'!$K$1</f>
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G66" s="8">
         <f>'[64]MD10000.1-OCT'!$K$2</f>
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
@@ -7247,11 +7293,11 @@
       </c>
       <c r="L66" s="7">
         <f>'[64]MD10000.1-OCT'!$O$2</f>
-        <v>4100</v>
+        <v>3800</v>
       </c>
       <c r="M66" s="7">
         <f>'[64]MD10000.1-OCT'!$O$1</f>
-        <v>7900</v>
+        <v>8200</v>
       </c>
       <c r="N66" s="1">
         <v>700</v>
@@ -7273,11 +7319,11 @@
       </c>
       <c r="F67" s="8">
         <f>'[65]MD10000.1-OCT'!$K$1</f>
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G67" s="8">
         <f>'[65]MD10000.1-OCT'!$K$2</f>
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
@@ -7290,11 +7336,11 @@
       </c>
       <c r="L67" s="7">
         <f>'[65]MD10000.1-OCT'!$O$2</f>
-        <v>2400</v>
+        <v>1900</v>
       </c>
       <c r="M67" s="7">
         <f>'[65]MD10000.1-OCT'!$O$1</f>
-        <v>9600</v>
+        <v>10100</v>
       </c>
       <c r="N67" s="1">
         <v>700</v>
@@ -7356,11 +7402,11 @@
       </c>
       <c r="F69" s="8">
         <f>'[67]MD10000.1-OCT'!$K$1</f>
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G69" s="8">
         <f>'[67]MD10000.1-OCT'!$K$2</f>
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H69" s="8"/>
       <c r="I69" s="8"/>
@@ -7373,11 +7419,11 @@
       </c>
       <c r="L69" s="7">
         <f>'[67]MD10000.1-OCT'!$O$2</f>
-        <v>4100</v>
+        <v>3700</v>
       </c>
       <c r="M69" s="7">
         <f>'[67]MD10000.1-OCT'!$O$1</f>
-        <v>7900</v>
+        <v>8300</v>
       </c>
       <c r="N69" s="1">
         <v>700</v>
@@ -7399,11 +7445,11 @@
       </c>
       <c r="F70" s="8">
         <f>'[68]MD10000.1-OCT'!$K$1</f>
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G70" s="8">
         <f>'[68]MD10000.1-OCT'!$K$2</f>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
@@ -7416,52 +7462,52 @@
       </c>
       <c r="L70" s="7">
         <f>'[68]MD10000.1-OCT'!$O$2</f>
-        <v>9900</v>
+        <v>9450</v>
       </c>
       <c r="M70" s="7">
         <f>'[68]MD10000.1-OCT'!$O$1</f>
-        <v>8100</v>
+        <v>8550</v>
       </c>
       <c r="N70" s="1">
         <v>1050</v>
       </c>
     </row>
     <row r="71" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="30">
+      <c r="B71" s="23">
         <v>67</v>
       </c>
-      <c r="C71" s="31" t="s">
+      <c r="C71" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="D71" s="32" t="s">
+      <c r="D71" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="E71" s="33">
+      <c r="E71" s="26">
         <f>'[69]MD20000.18-DEC'!$C$1</f>
         <v>50000</v>
       </c>
-      <c r="F71" s="31">
+      <c r="F71" s="24">
         <f>'[69]MD20000.18-DEC'!$K$1</f>
         <v>66</v>
       </c>
-      <c r="G71" s="31">
+      <c r="G71" s="24">
         <f>'[69]MD20000.18-DEC'!$K$2</f>
         <v>54</v>
       </c>
-      <c r="H71" s="31"/>
-      <c r="I71" s="31"/>
-      <c r="J71" s="34" t="s">
+      <c r="H71" s="24"/>
+      <c r="I71" s="24"/>
+      <c r="J71" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="K71" s="32">
+      <c r="K71" s="25">
         <f>'[69]MD20000.18-DEC'!$B$3</f>
         <v>45579</v>
       </c>
-      <c r="L71" s="33">
+      <c r="L71" s="26">
         <f>'[69]MD20000.18-DEC'!$O$2</f>
         <v>33000</v>
       </c>
-      <c r="M71" s="33">
+      <c r="M71" s="26">
         <f>'[69]MD20000.18-DEC'!$O$1</f>
         <v>27000</v>
       </c>
@@ -7688,11 +7734,11 @@
       </c>
       <c r="F77" s="8">
         <f>'[75]MD20000.18-DEC'!$K$1</f>
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G77" s="8">
         <f>'[75]MD20000.18-DEC'!$K$2</f>
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H77" s="8"/>
       <c r="I77" s="8"/>
@@ -7705,11 +7751,11 @@
       </c>
       <c r="L77" s="7">
         <f>'[75]MD20000.18-DEC'!$O$2</f>
-        <v>11200</v>
+        <v>10200</v>
       </c>
       <c r="M77" s="7">
         <f>'[75]MD20000.18-DEC'!$O$1</f>
-        <v>12800</v>
+        <v>13800</v>
       </c>
       <c r="N77" s="1">
         <v>1400</v>
@@ -7774,11 +7820,11 @@
       </c>
       <c r="F79" s="8">
         <f>'[77]MD20000.18-DEC'!$K$1</f>
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="G79" s="8">
         <f>'[77]MD20000.18-DEC'!$K$2</f>
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H79" s="8"/>
       <c r="I79" s="8"/>
@@ -7791,11 +7837,11 @@
       </c>
       <c r="L79" s="7">
         <f>'[77]MD20000.18-DEC'!$O$2</f>
-        <v>8900</v>
+        <v>8200</v>
       </c>
       <c r="M79" s="7">
         <f>'[77]MD20000.18-DEC'!$O$1</f>
-        <v>3100</v>
+        <v>3800</v>
       </c>
       <c r="N79" s="1">
         <v>700</v>
@@ -7859,11 +7905,11 @@
       <c r="G81" s="8"/>
       <c r="H81" s="8">
         <f>'[79]MD20000.15-DEc'!$K$1</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I81" s="8">
         <f>'[79]MD20000.15-DEc'!$K$2</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J81" s="9" t="s">
         <v>12</v>
@@ -7874,11 +7920,11 @@
       </c>
       <c r="L81" s="7">
         <f>'[79]MD20000.15-DEc'!$O$2</f>
-        <v>12600</v>
+        <v>11200</v>
       </c>
       <c r="M81" s="7">
         <f>'[79]MD20000.15-DEc'!$O$1</f>
-        <v>11400</v>
+        <v>12800</v>
       </c>
       <c r="N81" s="1">
         <v>1400</v>
@@ -7902,11 +7948,11 @@
       <c r="G82" s="8"/>
       <c r="H82" s="8">
         <f>'[80]MD10000.10-JAN'!$K$1</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I82" s="8">
         <f>'[80]MD10000.10-JAN'!$K$2</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J82" s="9" t="s">
         <v>12</v>
@@ -7917,11 +7963,11 @@
       </c>
       <c r="L82" s="7">
         <f>'[80]MD10000.10-JAN'!$O$2</f>
-        <v>14000</v>
+        <v>12600</v>
       </c>
       <c r="M82" s="7">
         <f>'[80]MD10000.10-JAN'!$O$1</f>
-        <v>10000</v>
+        <v>11400</v>
       </c>
       <c r="N82" s="1">
         <v>1400</v>
@@ -8008,41 +8054,41 @@
       </c>
     </row>
     <row r="85" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="30">
+      <c r="B85" s="23">
         <v>81</v>
       </c>
-      <c r="C85" s="31" t="s">
+      <c r="C85" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="D85" s="32" t="s">
+      <c r="D85" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="E85" s="33">
+      <c r="E85" s="26">
         <f>'[83]MD20000.18-DEC'!$C$1</f>
         <v>50000</v>
       </c>
-      <c r="F85" s="31">
+      <c r="F85" s="24">
         <f>'[83]MD20000.18-DEC'!$K$1</f>
         <v>100</v>
       </c>
-      <c r="G85" s="31">
+      <c r="G85" s="24">
         <f>'[83]MD20000.18-DEC'!$K$2</f>
         <v>20</v>
       </c>
-      <c r="H85" s="31"/>
-      <c r="I85" s="31"/>
-      <c r="J85" s="34" t="s">
+      <c r="H85" s="24"/>
+      <c r="I85" s="24"/>
+      <c r="J85" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="K85" s="32">
+      <c r="K85" s="25">
         <f>'[83]MD20000.18-DEC'!$B$3</f>
         <v>45612</v>
       </c>
-      <c r="L85" s="33">
+      <c r="L85" s="26">
         <f>'[83]MD20000.18-DEC'!$O$2</f>
         <v>50000</v>
       </c>
-      <c r="M85" s="33">
+      <c r="M85" s="26">
         <f>'[83]MD20000.18-DEC'!$O$1</f>
         <v>10000</v>
       </c>
@@ -8063,11 +8109,11 @@
       </c>
       <c r="F86" s="8">
         <f>'[84]MD20000.18-DEC'!$K$1</f>
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G86" s="8">
         <f>'[84]MD20000.18-DEC'!$K$2</f>
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H86" s="8"/>
       <c r="I86" s="8"/>
@@ -8080,11 +8126,11 @@
       </c>
       <c r="L86" s="7">
         <f>'[84]MD20000.18-DEC'!$O$2</f>
-        <v>8300</v>
+        <v>7800</v>
       </c>
       <c r="M86" s="7">
         <f>'[84]MD20000.18-DEC'!$O$1</f>
-        <v>3700</v>
+        <v>4200</v>
       </c>
       <c r="N86" s="1">
         <v>700</v>
@@ -8106,11 +8152,11 @@
       </c>
       <c r="F87" s="8">
         <f>'[85]MD50000.15-DEC'!$K$1</f>
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="G87" s="8">
         <f>'[85]MD50000.15-DEC'!$K$2</f>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H87" s="8"/>
       <c r="I87" s="8"/>
@@ -8123,11 +8169,11 @@
       </c>
       <c r="L87" s="7">
         <f>'[85]MD50000.15-DEC'!$O$2</f>
-        <v>148800</v>
+        <v>147000</v>
       </c>
       <c r="M87" s="7">
         <f>'[85]MD50000.15-DEC'!$O$1</f>
-        <v>11400</v>
+        <v>13200</v>
       </c>
       <c r="N87" s="1">
         <v>4200</v>
@@ -8149,11 +8195,11 @@
       </c>
       <c r="F88" s="8">
         <f>'[86]MD20000.18-DEC'!$K$1</f>
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G88" s="8">
         <f>'[86]MD20000.18-DEC'!$K$2</f>
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H88" s="8"/>
       <c r="I88" s="8"/>
@@ -8166,11 +8212,11 @@
       </c>
       <c r="L88" s="7">
         <f>'[86]MD20000.18-DEC'!$O$2</f>
-        <v>48000</v>
+        <v>46000</v>
       </c>
       <c r="M88" s="7">
         <f>'[86]MD20000.18-DEC'!$O$1</f>
-        <v>12000</v>
+        <v>14000</v>
       </c>
       <c r="N88" s="1">
         <v>3500</v>
@@ -8232,11 +8278,11 @@
       </c>
       <c r="F90" s="8">
         <f>'[88]MD20000.18-DEC'!$K$1</f>
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G90" s="8">
         <f>'[88]MD20000.18-DEC'!$K$2</f>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H90" s="8"/>
       <c r="I90" s="8"/>
@@ -8249,11 +8295,11 @@
       </c>
       <c r="L90" s="7">
         <f>'[88]MD20000.18-DEC'!$O$2</f>
-        <v>10400</v>
+        <v>9900</v>
       </c>
       <c r="M90" s="7">
         <f>'[88]MD20000.18-DEC'!$O$1</f>
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="N90" s="1">
         <v>700</v>
@@ -8275,11 +8321,11 @@
       </c>
       <c r="F91" s="8">
         <f>'[89]MD20000.18-DEC'!$K$1</f>
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G91" s="8">
         <f>'[89]MD20000.18-DEC'!$K$2</f>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H91" s="8"/>
       <c r="I91" s="8"/>
@@ -8292,11 +8338,11 @@
       </c>
       <c r="L91" s="7">
         <f>'[89]MD20000.18-DEC'!$O$2</f>
-        <v>10400</v>
+        <v>9900</v>
       </c>
       <c r="M91" s="7">
         <f>'[89]MD20000.18-DEC'!$O$1</f>
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="N91" s="1">
         <v>700</v>
@@ -8318,11 +8364,11 @@
       </c>
       <c r="F92" s="8">
         <f>'[90]MD50000.15-DEC'!$K$1</f>
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="G92" s="8">
         <f>'[90]MD50000.15-DEC'!$K$2</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H92" s="8"/>
       <c r="I92" s="8"/>
@@ -8335,11 +8381,11 @@
       </c>
       <c r="L92" s="7">
         <f>'[90]MD50000.15-DEC'!$O$2</f>
-        <v>319200</v>
+        <v>315600</v>
       </c>
       <c r="M92" s="7">
         <f>'[90]MD50000.15-DEC'!$O$1</f>
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="N92" s="1">
         <v>8400</v>
@@ -8392,17 +8438,44 @@
       <c r="B94" s="6">
         <v>90</v>
       </c>
-      <c r="C94" s="8"/>
-      <c r="D94" s="14"/>
-      <c r="E94" s="7"/>
-      <c r="F94" s="8"/>
-      <c r="G94" s="8"/>
+      <c r="C94" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D94" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="E94" s="7">
+        <f>'[92]MD50000.15-DEC'!$C$1</f>
+        <v>50000</v>
+      </c>
+      <c r="F94" s="8">
+        <f>'[92]MD50000.15-DEC'!$K$1</f>
+        <v>118</v>
+      </c>
+      <c r="G94" s="8">
+        <f>'[92]MD50000.15-DEC'!$K$2</f>
+        <v>2</v>
+      </c>
       <c r="H94" s="8"/>
       <c r="I94" s="8"/>
-      <c r="J94" s="9"/>
-      <c r="K94" s="10"/>
-      <c r="L94" s="7"/>
-      <c r="M94" s="7"/>
+      <c r="J94" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K94" s="10">
+        <f>'[92]MD50000.15-DEC'!$B$3</f>
+        <v>45652</v>
+      </c>
+      <c r="L94" s="7">
+        <f>'[92]MD50000.15-DEC'!$O$2</f>
+        <v>59000</v>
+      </c>
+      <c r="M94" s="7">
+        <f>'[92]MD50000.15-DEC'!$O$1</f>
+        <v>1000</v>
+      </c>
+      <c r="N94" s="1">
+        <v>3500</v>
+      </c>
     </row>
     <row r="95" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B95" s="6">

--- a/LoanOfficer-A/LoanBook.xlsx
+++ b/LoanOfficer-A/LoanBook.xlsx
@@ -7,10 +7,10 @@
     <workbookView xWindow="0" yWindow="3600" windowWidth="20520" windowHeight="4425"/>
   </bookViews>
   <sheets>
-    <sheet name="2023" sheetId="6" r:id="rId1"/>
+    <sheet name="2025" sheetId="7" r:id="rId1"/>
+    <sheet name="2023" sheetId="6" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
     <externalReference r:id="rId5"/>
@@ -102,13 +102,14 @@
     <externalReference r:id="rId91"/>
     <externalReference r:id="rId92"/>
     <externalReference r:id="rId93"/>
+    <externalReference r:id="rId94"/>
   </externalReferences>
   <calcPr calcId="145621" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="121">
   <si>
     <t>Code</t>
   </si>
@@ -1801,7 +1802,7 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -1828,7 +1829,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3177,25 +3178,25 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>38</v>
+            <v>28</v>
           </cell>
           <cell r="O1">
-            <v>8200</v>
+            <v>9200</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>82</v>
+            <v>92</v>
           </cell>
           <cell r="O2">
-            <v>3800</v>
+            <v>2800</v>
           </cell>
         </row>
         <row r="3">
@@ -3217,25 +3218,25 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>19</v>
+            <v>16</v>
           </cell>
           <cell r="O1">
-            <v>10100</v>
+            <v>10400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>101</v>
+            <v>104</v>
           </cell>
           <cell r="O2">
-            <v>1900</v>
+            <v>1600</v>
           </cell>
         </row>
         <row r="3">
@@ -3297,25 +3298,25 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>37</v>
+            <v>25</v>
           </cell>
           <cell r="O1">
-            <v>8300</v>
+            <v>9500</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>83</v>
+            <v>95</v>
           </cell>
           <cell r="O2">
-            <v>3700</v>
+            <v>2500</v>
           </cell>
         </row>
         <row r="3">
@@ -3337,25 +3338,25 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>15000</v>
           </cell>
           <cell r="K1">
-            <v>63</v>
+            <v>53</v>
           </cell>
           <cell r="O1">
-            <v>8550</v>
+            <v>10050</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>57</v>
+            <v>67</v>
           </cell>
           <cell r="O2">
-            <v>9450</v>
+            <v>7950</v>
           </cell>
         </row>
         <row r="3">
@@ -3377,7 +3378,7 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -3466,18 +3467,18 @@
             <v>100000</v>
           </cell>
           <cell r="K1">
-            <v>31</v>
+            <v>29</v>
           </cell>
           <cell r="O1">
-            <v>36000</v>
+            <v>44000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>9</v>
+            <v>11</v>
           </cell>
           <cell r="O2">
-            <v>124000</v>
+            <v>116000</v>
           </cell>
         </row>
         <row r="3">
@@ -3659,25 +3660,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>51</v>
+            <v>36</v>
           </cell>
           <cell r="O1">
-            <v>13800</v>
+            <v>16800</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>69</v>
+            <v>84</v>
           </cell>
           <cell r="O2">
-            <v>10200</v>
+            <v>7200</v>
           </cell>
         </row>
         <row r="7">
@@ -3739,25 +3740,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>82</v>
+            <v>75</v>
           </cell>
           <cell r="O1">
-            <v>3800</v>
+            <v>4500</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>38</v>
+            <v>45</v>
           </cell>
           <cell r="O2">
-            <v>8200</v>
+            <v>7500</v>
           </cell>
         </row>
         <row r="3">
@@ -3818,25 +3819,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>8</v>
+            <v>7</v>
           </cell>
           <cell r="O1">
-            <v>12800</v>
+            <v>14200</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>9</v>
+            <v>10</v>
           </cell>
           <cell r="O2">
-            <v>11200</v>
+            <v>9800</v>
           </cell>
         </row>
         <row r="3">
@@ -3845,7 +3846,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3902,25 +3903,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>9</v>
+            <v>8</v>
           </cell>
           <cell r="O1">
-            <v>11400</v>
+            <v>12800</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>8</v>
+            <v>9</v>
           </cell>
           <cell r="O2">
-            <v>12600</v>
+            <v>11200</v>
           </cell>
         </row>
         <row r="3">
@@ -3929,7 +3930,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4063,25 +4064,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>78</v>
+            <v>77</v>
           </cell>
           <cell r="O1">
-            <v>4200</v>
+            <v>4300</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>42</v>
+            <v>43</v>
           </cell>
           <cell r="O2">
-            <v>7800</v>
+            <v>7700</v>
           </cell>
         </row>
         <row r="3">
@@ -4104,25 +4105,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>100000</v>
           </cell>
           <cell r="K1">
-            <v>245</v>
+            <v>233</v>
           </cell>
           <cell r="O1">
-            <v>13200</v>
+            <v>20400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>22</v>
+            <v>34</v>
           </cell>
           <cell r="O2">
-            <v>147000</v>
+            <v>139800</v>
           </cell>
         </row>
         <row r="3">
@@ -4131,7 +4132,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4145,25 +4146,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>92</v>
+            <v>80</v>
           </cell>
           <cell r="O1">
-            <v>14000</v>
+            <v>20000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>28</v>
+            <v>40</v>
           </cell>
           <cell r="O2">
-            <v>46000</v>
+            <v>40000</v>
           </cell>
         </row>
         <row r="3">
@@ -4225,7 +4226,7 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -4265,7 +4266,7 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -4348,25 +4349,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>200000</v>
           </cell>
           <cell r="K1">
-            <v>263</v>
+            <v>253</v>
           </cell>
           <cell r="O1">
-            <v>4800</v>
+            <v>16800</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>4</v>
+            <v>14</v>
           </cell>
           <cell r="O2">
-            <v>315600</v>
+            <v>303600</v>
           </cell>
         </row>
         <row r="3">
@@ -4375,7 +4376,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4432,25 +4433,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>118</v>
+            <v>107</v>
           </cell>
           <cell r="O1">
-            <v>1000</v>
+            <v>6500</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>2</v>
+            <v>13</v>
           </cell>
           <cell r="O2">
-            <v>59000</v>
+            <v>53500</v>
           </cell>
         </row>
         <row r="3">
@@ -4459,7 +4460,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4720,13 +4721,1076 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:Q30"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="32.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.42578125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.42578125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="18.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="15" style="1" customWidth="1"/>
+    <col min="14" max="14" width="15.28515625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="11.85546875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="34"/>
+      <c r="I2" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="31"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="28">
+        <f>SUM(L5:L38)</f>
+        <v>771500</v>
+      </c>
+      <c r="M2" s="29"/>
+      <c r="N2" s="1">
+        <f>SUM(N5:N47)</f>
+        <v>36900</v>
+      </c>
+      <c r="Q2" s="1">
+        <f>14900+260750</f>
+        <v>275650</v>
+      </c>
+    </row>
+    <row r="3" spans="2:17" ht="18" x14ac:dyDescent="0.2">
+      <c r="C3" s="2"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="5"/>
+      <c r="K3" s="3"/>
+      <c r="M3" s="3"/>
+    </row>
+    <row r="4" spans="2:17" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="12">
+        <v>32</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="15">
+        <f>'[32]MD10000.10-JAN'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13">
+        <f>'[32]MD10000.10-JAN'!$G$1</f>
+        <v>48</v>
+      </c>
+      <c r="I5" s="13">
+        <f>'[32]MD10000.10-JAN'!$K$2</f>
+        <v>37</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="14">
+        <f>'[32]MD10000.10-JAN'!$B$3</f>
+        <v>45399</v>
+      </c>
+      <c r="L5" s="15">
+        <f>'[32]MD10000.10-JAN'!$O$2</f>
+        <v>3850</v>
+      </c>
+      <c r="M5" s="15">
+        <f>'[32]MD10000.10-JAN'!$O$1</f>
+        <v>12950</v>
+      </c>
+      <c r="N5" s="1">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="6">
+        <v>62</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="7">
+        <f>'[64]MD10000.1-OCT'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F6" s="8">
+        <f>'[64]MD10000.1-OCT'!$K$1</f>
+        <v>28</v>
+      </c>
+      <c r="G6" s="8">
+        <f>'[64]MD10000.1-OCT'!$K$2</f>
+        <v>92</v>
+      </c>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K6" s="10">
+        <f>'[64]MD10000.1-OCT'!$B$3</f>
+        <v>45557</v>
+      </c>
+      <c r="L6" s="7">
+        <f>'[64]MD10000.1-OCT'!$O$2</f>
+        <v>2800</v>
+      </c>
+      <c r="M6" s="7">
+        <f>'[64]MD10000.1-OCT'!$O$1</f>
+        <v>9200</v>
+      </c>
+      <c r="N6" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="6">
+        <v>63</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="7">
+        <f>'[65]MD10000.1-OCT'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F7" s="8">
+        <f>'[65]MD10000.1-OCT'!$K$1</f>
+        <v>16</v>
+      </c>
+      <c r="G7" s="8">
+        <f>'[65]MD10000.1-OCT'!$K$2</f>
+        <v>104</v>
+      </c>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K7" s="10">
+        <f>'[65]MD10000.1-OCT'!$B$3</f>
+        <v>45561</v>
+      </c>
+      <c r="L7" s="7">
+        <f>'[65]MD10000.1-OCT'!$O$2</f>
+        <v>1600</v>
+      </c>
+      <c r="M7" s="7">
+        <f>'[65]MD10000.1-OCT'!$O$1</f>
+        <v>10400</v>
+      </c>
+      <c r="N7" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="6">
+        <v>65</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="7">
+        <f>'[67]MD10000.1-OCT'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F8" s="8">
+        <f>'[67]MD10000.1-OCT'!$K$1</f>
+        <v>25</v>
+      </c>
+      <c r="G8" s="8">
+        <f>'[67]MD10000.1-OCT'!$K$2</f>
+        <v>95</v>
+      </c>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K8" s="10">
+        <f>'[67]MD10000.1-OCT'!$B$3</f>
+        <v>45563</v>
+      </c>
+      <c r="L8" s="7">
+        <f>'[67]MD10000.1-OCT'!$O$2</f>
+        <v>2500</v>
+      </c>
+      <c r="M8" s="7">
+        <f>'[67]MD10000.1-OCT'!$O$1</f>
+        <v>9500</v>
+      </c>
+      <c r="N8" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="6">
+        <v>66</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="7">
+        <f>'[68]MD10000.1-OCT'!$C$1</f>
+        <v>15000</v>
+      </c>
+      <c r="F9" s="8">
+        <f>'[68]MD10000.1-OCT'!$K$1</f>
+        <v>53</v>
+      </c>
+      <c r="G9" s="8">
+        <f>'[68]MD10000.1-OCT'!$K$2</f>
+        <v>67</v>
+      </c>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K9" s="10">
+        <f>'[68]MD10000.1-OCT'!$B$3</f>
+        <v>45570</v>
+      </c>
+      <c r="L9" s="7">
+        <f>'[68]MD10000.1-OCT'!$O$2</f>
+        <v>7950</v>
+      </c>
+      <c r="M9" s="7">
+        <f>'[68]MD10000.1-OCT'!$O$1</f>
+        <v>10050</v>
+      </c>
+      <c r="N9" s="1">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="6">
+        <v>68</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10" s="7">
+        <f>'[70]MD20000.18-DEC'!$C$1</f>
+        <v>100000</v>
+      </c>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8">
+        <f>'[70]MD20000.18-DEC'!$K$1</f>
+        <v>29</v>
+      </c>
+      <c r="I10" s="8">
+        <f>'[70]MD20000.18-DEC'!$K$2</f>
+        <v>11</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K10" s="10">
+        <f>'[70]MD20000.18-DEC'!$B$3</f>
+        <v>45590</v>
+      </c>
+      <c r="L10" s="7">
+        <f>'[70]MD20000.18-DEC'!$O$2</f>
+        <v>116000</v>
+      </c>
+      <c r="M10" s="7">
+        <f>'[70]MD20000.18-DEC'!$O$1</f>
+        <v>44000</v>
+      </c>
+      <c r="N10" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="6">
+        <v>71</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" s="7">
+        <f>'[73]MD20000.18-DEC'!$C$1</f>
+        <v>20000</v>
+      </c>
+      <c r="F11" s="8">
+        <f>'[73]MD20000.18-DEC'!$K$1</f>
+        <v>82</v>
+      </c>
+      <c r="G11" s="8">
+        <f>'[73]MD20000.18-DEC'!$K$2</f>
+        <v>38</v>
+      </c>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K11" s="10">
+        <f>'[73]MD20000.18-DEC'!$B$3</f>
+        <v>45584</v>
+      </c>
+      <c r="L11" s="7">
+        <f>'[73]MD20000.18-DEC'!$O$2</f>
+        <v>16400</v>
+      </c>
+      <c r="M11" s="7">
+        <f>'[73]MD20000.18-DEC'!$O$1</f>
+        <v>7600</v>
+      </c>
+      <c r="N11" s="1">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="6">
+        <v>73</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" s="7">
+        <f>'[75]MD20000.18-DEC'!$C$1</f>
+        <v>20000</v>
+      </c>
+      <c r="F12" s="8">
+        <f>'[75]MD20000.18-DEC'!$K$1</f>
+        <v>36</v>
+      </c>
+      <c r="G12" s="8">
+        <f>'[75]MD20000.18-DEC'!$K$2</f>
+        <v>84</v>
+      </c>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K12" s="10">
+        <f>'[75]MD20000.18-DEC'!$B$7</f>
+        <v>45587</v>
+      </c>
+      <c r="L12" s="7">
+        <f>'[75]MD20000.18-DEC'!$O$2</f>
+        <v>7200</v>
+      </c>
+      <c r="M12" s="7">
+        <f>'[75]MD20000.18-DEC'!$O$1</f>
+        <v>16800</v>
+      </c>
+      <c r="N12" s="1">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="6">
+        <v>74</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="7">
+        <f>'[76]MD20000.18-DEC'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F13" s="8">
+        <f>'[76]MD20000.18-DEC'!$K$1</f>
+        <v>104</v>
+      </c>
+      <c r="G13" s="8">
+        <f>'[76]MD20000.18-DEC'!$K$2</f>
+        <v>16</v>
+      </c>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K13" s="10">
+        <f>'[76]MD20000.18-DEC'!$B$3</f>
+        <v>45584</v>
+      </c>
+      <c r="L13" s="7">
+        <f>'[76]MD20000.18-DEC'!$O$2</f>
+        <v>10400</v>
+      </c>
+      <c r="M13" s="7">
+        <f>'[76]MD20000.18-DEC'!$O$1</f>
+        <v>1600</v>
+      </c>
+      <c r="N13" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="6">
+        <v>75</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="7">
+        <f>'[77]MD20000.18-DEC'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F14" s="8">
+        <f>'[77]MD20000.18-DEC'!$K$1</f>
+        <v>75</v>
+      </c>
+      <c r="G14" s="8">
+        <f>'[77]MD20000.18-DEC'!$K$2</f>
+        <v>45</v>
+      </c>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14" s="10">
+        <f>'[77]MD20000.18-DEC'!$B$3</f>
+        <v>45584</v>
+      </c>
+      <c r="L14" s="7">
+        <f>'[77]MD20000.18-DEC'!$O$2</f>
+        <v>7500</v>
+      </c>
+      <c r="M14" s="7">
+        <f>'[77]MD20000.18-DEC'!$O$1</f>
+        <v>4500</v>
+      </c>
+      <c r="N14" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="15" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="6">
+        <v>77</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="7">
+        <f>'[79]MD20000.15-DEc'!$C$1</f>
+        <v>20000</v>
+      </c>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8">
+        <f>'[79]MD20000.15-DEc'!$K$1</f>
+        <v>7</v>
+      </c>
+      <c r="I15" s="8">
+        <f>'[79]MD20000.15-DEc'!$K$2</f>
+        <v>10</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K15" s="10">
+        <f>'[79]MD20000.15-DEc'!$B$3</f>
+        <v>45595</v>
+      </c>
+      <c r="L15" s="7">
+        <f>'[79]MD20000.15-DEc'!$O$2</f>
+        <v>9800</v>
+      </c>
+      <c r="M15" s="7">
+        <f>'[79]MD20000.15-DEc'!$O$1</f>
+        <v>14200</v>
+      </c>
+      <c r="N15" s="1">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="16" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="6">
+        <v>78</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="E16" s="7">
+        <f>'[80]MD10000.10-JAN'!$C$1</f>
+        <v>20000</v>
+      </c>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8">
+        <f>'[80]MD10000.10-JAN'!$K$1</f>
+        <v>8</v>
+      </c>
+      <c r="I16" s="8">
+        <f>'[80]MD10000.10-JAN'!$K$2</f>
+        <v>9</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K16" s="10">
+        <f>'[80]MD10000.10-JAN'!$B$3</f>
+        <v>45602</v>
+      </c>
+      <c r="L16" s="7">
+        <f>'[80]MD10000.10-JAN'!$O$2</f>
+        <v>11200</v>
+      </c>
+      <c r="M16" s="7">
+        <f>'[80]MD10000.10-JAN'!$O$1</f>
+        <v>12800</v>
+      </c>
+      <c r="N16" s="1">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="6">
+        <v>82</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" s="7">
+        <f>'[84]MD20000.18-DEC'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F17" s="8">
+        <f>'[84]MD20000.18-DEC'!$K$1</f>
+        <v>77</v>
+      </c>
+      <c r="G17" s="8">
+        <f>'[84]MD20000.18-DEC'!$K$2</f>
+        <v>43</v>
+      </c>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K17" s="10">
+        <f>'[84]MD20000.18-DEC'!$B$3</f>
+        <v>45612</v>
+      </c>
+      <c r="L17" s="7">
+        <f>'[84]MD20000.18-DEC'!$O$2</f>
+        <v>7700</v>
+      </c>
+      <c r="M17" s="7">
+        <f>'[84]MD20000.18-DEC'!$O$1</f>
+        <v>4300</v>
+      </c>
+      <c r="N17" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="6">
+        <v>83</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="E18" s="7">
+        <f>'[85]MD50000.15-DEC'!$C$1</f>
+        <v>100000</v>
+      </c>
+      <c r="F18" s="8">
+        <f>'[85]MD50000.15-DEC'!$K$1</f>
+        <v>233</v>
+      </c>
+      <c r="G18" s="8">
+        <f>'[85]MD50000.15-DEC'!$K$2</f>
+        <v>34</v>
+      </c>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K18" s="10">
+        <f>'[85]MD50000.15-DEC'!$B$3</f>
+        <v>45619</v>
+      </c>
+      <c r="L18" s="7">
+        <f>'[85]MD50000.15-DEC'!$O$2</f>
+        <v>139800</v>
+      </c>
+      <c r="M18" s="7">
+        <f>'[85]MD50000.15-DEC'!$O$1</f>
+        <v>20400</v>
+      </c>
+      <c r="N18" s="1">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="6">
+        <v>84</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="E19" s="7">
+        <f>'[86]MD20000.18-DEC'!$C$1</f>
+        <v>50000</v>
+      </c>
+      <c r="F19" s="8">
+        <f>'[86]MD20000.18-DEC'!$K$1</f>
+        <v>80</v>
+      </c>
+      <c r="G19" s="8">
+        <f>'[86]MD20000.18-DEC'!$K$2</f>
+        <v>40</v>
+      </c>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K19" s="10">
+        <f>'[86]MD20000.18-DEC'!$B$3</f>
+        <v>45628</v>
+      </c>
+      <c r="L19" s="7">
+        <f>'[86]MD20000.18-DEC'!$O$2</f>
+        <v>40000</v>
+      </c>
+      <c r="M19" s="7">
+        <f>'[86]MD20000.18-DEC'!$O$1</f>
+        <v>20000</v>
+      </c>
+      <c r="N19" s="1">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="6">
+        <v>86</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="7">
+        <f>'[88]MD20000.18-DEC'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F20" s="8">
+        <f>'[88]MD20000.18-DEC'!$K$1</f>
+        <v>99</v>
+      </c>
+      <c r="G20" s="8">
+        <f>'[88]MD20000.18-DEC'!$K$2</f>
+        <v>21</v>
+      </c>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K20" s="10">
+        <f>'[88]MD20000.18-DEC'!$B$3</f>
+        <v>45635</v>
+      </c>
+      <c r="L20" s="7">
+        <f>'[88]MD20000.18-DEC'!$O$2</f>
+        <v>9900</v>
+      </c>
+      <c r="M20" s="7">
+        <f>'[88]MD20000.18-DEC'!$O$1</f>
+        <v>2100</v>
+      </c>
+      <c r="N20" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="6">
+        <v>87</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="7">
+        <f>'[89]MD20000.18-DEC'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F21" s="8">
+        <f>'[89]MD20000.18-DEC'!$K$1</f>
+        <v>99</v>
+      </c>
+      <c r="G21" s="8">
+        <f>'[89]MD20000.18-DEC'!$K$2</f>
+        <v>21</v>
+      </c>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K21" s="10">
+        <f>'[89]MD20000.18-DEC'!$B$3</f>
+        <v>45635</v>
+      </c>
+      <c r="L21" s="7">
+        <f>'[89]MD20000.18-DEC'!$O$2</f>
+        <v>9900</v>
+      </c>
+      <c r="M21" s="7">
+        <f>'[89]MD20000.18-DEC'!$O$1</f>
+        <v>2100</v>
+      </c>
+      <c r="N21" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="6">
+        <v>88</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" s="7">
+        <f>'[90]MD50000.15-DEC'!$C$1</f>
+        <v>200000</v>
+      </c>
+      <c r="F22" s="8">
+        <f>'[90]MD50000.15-DEC'!$K$1</f>
+        <v>253</v>
+      </c>
+      <c r="G22" s="8">
+        <f>'[90]MD50000.15-DEC'!$K$2</f>
+        <v>14</v>
+      </c>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K22" s="10">
+        <f>'[90]MD50000.15-DEC'!$B$3</f>
+        <v>45648</v>
+      </c>
+      <c r="L22" s="7">
+        <f>'[90]MD50000.15-DEC'!$O$2</f>
+        <v>303600</v>
+      </c>
+      <c r="M22" s="7">
+        <f>'[90]MD50000.15-DEC'!$O$1</f>
+        <v>16800</v>
+      </c>
+      <c r="N22" s="1">
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="6">
+        <v>89</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="E23" s="7">
+        <f>'[91]MD20000.15-DEc'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8">
+        <f>'[91]MD20000.15-DEc'!$K$1</f>
+        <v>14</v>
+      </c>
+      <c r="I23" s="8">
+        <f>'[91]MD20000.15-DEc'!$K$2</f>
+        <v>3</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K23" s="10">
+        <f>'[91]MD20000.15-DEc'!$B$3</f>
+        <v>45649</v>
+      </c>
+      <c r="L23" s="7">
+        <f>'[91]MD20000.15-DEc'!$O$2</f>
+        <v>9900</v>
+      </c>
+      <c r="M23" s="7">
+        <f>'[91]MD20000.15-DEc'!$O$1</f>
+        <v>2100</v>
+      </c>
+      <c r="N23" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="6">
+        <v>90</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="E24" s="7">
+        <f>'[92]MD50000.15-DEC'!$C$1</f>
+        <v>50000</v>
+      </c>
+      <c r="F24" s="8">
+        <f>'[92]MD50000.15-DEC'!$K$1</f>
+        <v>107</v>
+      </c>
+      <c r="G24" s="8">
+        <f>'[92]MD50000.15-DEC'!$K$2</f>
+        <v>13</v>
+      </c>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K24" s="10">
+        <f>'[92]MD50000.15-DEC'!$B$3</f>
+        <v>45652</v>
+      </c>
+      <c r="L24" s="7">
+        <f>'[92]MD50000.15-DEC'!$O$2</f>
+        <v>53500</v>
+      </c>
+      <c r="M24" s="7">
+        <f>'[92]MD50000.15-DEC'!$O$1</f>
+        <v>6500</v>
+      </c>
+      <c r="N24" s="1">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="6">
+        <v>91</v>
+      </c>
+      <c r="C25" s="8"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+    </row>
+    <row r="26" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="6">
+        <v>92</v>
+      </c>
+      <c r="C26" s="8"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+    </row>
+    <row r="27" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="6">
+        <v>93</v>
+      </c>
+      <c r="C27" s="8"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+    </row>
+    <row r="28" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="6">
+        <v>94</v>
+      </c>
+      <c r="C28" s="8"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
+    </row>
+    <row r="29" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="6">
+        <v>95</v>
+      </c>
+      <c r="C29" s="8"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+    </row>
+    <row r="30" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="6">
+        <v>96</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:M2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Q100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -4763,7 +5827,7 @@
       <c r="K2" s="32"/>
       <c r="L2" s="28">
         <f>SUM(L5:L108)</f>
-        <v>903800</v>
+        <v>854500</v>
       </c>
       <c r="M2" s="29"/>
       <c r="N2" s="1">
@@ -7276,11 +8340,11 @@
       </c>
       <c r="F66" s="8">
         <f>'[64]MD10000.1-OCT'!$K$1</f>
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G66" s="8">
         <f>'[64]MD10000.1-OCT'!$K$2</f>
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
@@ -7293,11 +8357,11 @@
       </c>
       <c r="L66" s="7">
         <f>'[64]MD10000.1-OCT'!$O$2</f>
-        <v>3800</v>
+        <v>2800</v>
       </c>
       <c r="M66" s="7">
         <f>'[64]MD10000.1-OCT'!$O$1</f>
-        <v>8200</v>
+        <v>9200</v>
       </c>
       <c r="N66" s="1">
         <v>700</v>
@@ -7319,11 +8383,11 @@
       </c>
       <c r="F67" s="8">
         <f>'[65]MD10000.1-OCT'!$K$1</f>
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G67" s="8">
         <f>'[65]MD10000.1-OCT'!$K$2</f>
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
@@ -7336,11 +8400,11 @@
       </c>
       <c r="L67" s="7">
         <f>'[65]MD10000.1-OCT'!$O$2</f>
-        <v>1900</v>
+        <v>1600</v>
       </c>
       <c r="M67" s="7">
         <f>'[65]MD10000.1-OCT'!$O$1</f>
-        <v>10100</v>
+        <v>10400</v>
       </c>
       <c r="N67" s="1">
         <v>700</v>
@@ -7402,11 +8466,11 @@
       </c>
       <c r="F69" s="8">
         <f>'[67]MD10000.1-OCT'!$K$1</f>
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="G69" s="8">
         <f>'[67]MD10000.1-OCT'!$K$2</f>
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H69" s="8"/>
       <c r="I69" s="8"/>
@@ -7419,11 +8483,11 @@
       </c>
       <c r="L69" s="7">
         <f>'[67]MD10000.1-OCT'!$O$2</f>
-        <v>3700</v>
+        <v>2500</v>
       </c>
       <c r="M69" s="7">
         <f>'[67]MD10000.1-OCT'!$O$1</f>
-        <v>8300</v>
+        <v>9500</v>
       </c>
       <c r="N69" s="1">
         <v>700</v>
@@ -7445,11 +8509,11 @@
       </c>
       <c r="F70" s="8">
         <f>'[68]MD10000.1-OCT'!$K$1</f>
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="G70" s="8">
         <f>'[68]MD10000.1-OCT'!$K$2</f>
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
@@ -7462,11 +8526,11 @@
       </c>
       <c r="L70" s="7">
         <f>'[68]MD10000.1-OCT'!$O$2</f>
-        <v>9450</v>
+        <v>7950</v>
       </c>
       <c r="M70" s="7">
         <f>'[68]MD10000.1-OCT'!$O$1</f>
-        <v>8550</v>
+        <v>10050</v>
       </c>
       <c r="N70" s="1">
         <v>1050</v>
@@ -7530,11 +8594,11 @@
       <c r="G72" s="8"/>
       <c r="H72" s="8">
         <f>'[70]MD20000.18-DEC'!$K$1</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I72" s="8">
         <f>'[70]MD20000.18-DEC'!$K$2</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J72" s="9" t="s">
         <v>12</v>
@@ -7545,11 +8609,11 @@
       </c>
       <c r="L72" s="7">
         <f>'[70]MD20000.18-DEC'!$O$2</f>
-        <v>124000</v>
+        <v>116000</v>
       </c>
       <c r="M72" s="7">
         <f>'[70]MD20000.18-DEC'!$O$1</f>
-        <v>36000</v>
+        <v>44000</v>
       </c>
       <c r="N72" s="1">
         <v>4000</v>
@@ -7734,11 +8798,11 @@
       </c>
       <c r="F77" s="8">
         <f>'[75]MD20000.18-DEC'!$K$1</f>
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="G77" s="8">
         <f>'[75]MD20000.18-DEC'!$K$2</f>
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="H77" s="8"/>
       <c r="I77" s="8"/>
@@ -7751,11 +8815,11 @@
       </c>
       <c r="L77" s="7">
         <f>'[75]MD20000.18-DEC'!$O$2</f>
-        <v>10200</v>
+        <v>7200</v>
       </c>
       <c r="M77" s="7">
         <f>'[75]MD20000.18-DEC'!$O$1</f>
-        <v>13800</v>
+        <v>16800</v>
       </c>
       <c r="N77" s="1">
         <v>1400</v>
@@ -7820,11 +8884,11 @@
       </c>
       <c r="F79" s="8">
         <f>'[77]MD20000.18-DEC'!$K$1</f>
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G79" s="8">
         <f>'[77]MD20000.18-DEC'!$K$2</f>
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="H79" s="8"/>
       <c r="I79" s="8"/>
@@ -7837,11 +8901,11 @@
       </c>
       <c r="L79" s="7">
         <f>'[77]MD20000.18-DEC'!$O$2</f>
-        <v>8200</v>
+        <v>7500</v>
       </c>
       <c r="M79" s="7">
         <f>'[77]MD20000.18-DEC'!$O$1</f>
-        <v>3800</v>
+        <v>4500</v>
       </c>
       <c r="N79" s="1">
         <v>700</v>
@@ -7905,11 +8969,11 @@
       <c r="G81" s="8"/>
       <c r="H81" s="8">
         <f>'[79]MD20000.15-DEc'!$K$1</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I81" s="8">
         <f>'[79]MD20000.15-DEc'!$K$2</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J81" s="9" t="s">
         <v>12</v>
@@ -7920,11 +8984,11 @@
       </c>
       <c r="L81" s="7">
         <f>'[79]MD20000.15-DEc'!$O$2</f>
-        <v>11200</v>
+        <v>9800</v>
       </c>
       <c r="M81" s="7">
         <f>'[79]MD20000.15-DEc'!$O$1</f>
-        <v>12800</v>
+        <v>14200</v>
       </c>
       <c r="N81" s="1">
         <v>1400</v>
@@ -7948,11 +9012,11 @@
       <c r="G82" s="8"/>
       <c r="H82" s="8">
         <f>'[80]MD10000.10-JAN'!$K$1</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I82" s="8">
         <f>'[80]MD10000.10-JAN'!$K$2</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J82" s="9" t="s">
         <v>12</v>
@@ -7963,11 +9027,11 @@
       </c>
       <c r="L82" s="7">
         <f>'[80]MD10000.10-JAN'!$O$2</f>
-        <v>12600</v>
+        <v>11200</v>
       </c>
       <c r="M82" s="7">
         <f>'[80]MD10000.10-JAN'!$O$1</f>
-        <v>11400</v>
+        <v>12800</v>
       </c>
       <c r="N82" s="1">
         <v>1400</v>
@@ -8109,11 +9173,11 @@
       </c>
       <c r="F86" s="8">
         <f>'[84]MD20000.18-DEC'!$K$1</f>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G86" s="8">
         <f>'[84]MD20000.18-DEC'!$K$2</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H86" s="8"/>
       <c r="I86" s="8"/>
@@ -8126,11 +9190,11 @@
       </c>
       <c r="L86" s="7">
         <f>'[84]MD20000.18-DEC'!$O$2</f>
-        <v>7800</v>
+        <v>7700</v>
       </c>
       <c r="M86" s="7">
         <f>'[84]MD20000.18-DEC'!$O$1</f>
-        <v>4200</v>
+        <v>4300</v>
       </c>
       <c r="N86" s="1">
         <v>700</v>
@@ -8152,11 +9216,11 @@
       </c>
       <c r="F87" s="8">
         <f>'[85]MD50000.15-DEC'!$K$1</f>
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="G87" s="8">
         <f>'[85]MD50000.15-DEC'!$K$2</f>
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="H87" s="8"/>
       <c r="I87" s="8"/>
@@ -8169,11 +9233,11 @@
       </c>
       <c r="L87" s="7">
         <f>'[85]MD50000.15-DEC'!$O$2</f>
-        <v>147000</v>
+        <v>139800</v>
       </c>
       <c r="M87" s="7">
         <f>'[85]MD50000.15-DEC'!$O$1</f>
-        <v>13200</v>
+        <v>20400</v>
       </c>
       <c r="N87" s="1">
         <v>4200</v>
@@ -8195,11 +9259,11 @@
       </c>
       <c r="F88" s="8">
         <f>'[86]MD20000.18-DEC'!$K$1</f>
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G88" s="8">
         <f>'[86]MD20000.18-DEC'!$K$2</f>
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="H88" s="8"/>
       <c r="I88" s="8"/>
@@ -8212,11 +9276,11 @@
       </c>
       <c r="L88" s="7">
         <f>'[86]MD20000.18-DEC'!$O$2</f>
-        <v>46000</v>
+        <v>40000</v>
       </c>
       <c r="M88" s="7">
         <f>'[86]MD20000.18-DEC'!$O$1</f>
-        <v>14000</v>
+        <v>20000</v>
       </c>
       <c r="N88" s="1">
         <v>3500</v>
@@ -8364,11 +9428,11 @@
       </c>
       <c r="F92" s="8">
         <f>'[90]MD50000.15-DEC'!$K$1</f>
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="G92" s="8">
         <f>'[90]MD50000.15-DEC'!$K$2</f>
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H92" s="8"/>
       <c r="I92" s="8"/>
@@ -8381,11 +9445,11 @@
       </c>
       <c r="L92" s="7">
         <f>'[90]MD50000.15-DEC'!$O$2</f>
-        <v>315600</v>
+        <v>303600</v>
       </c>
       <c r="M92" s="7">
         <f>'[90]MD50000.15-DEC'!$O$1</f>
-        <v>4800</v>
+        <v>16800</v>
       </c>
       <c r="N92" s="1">
         <v>8400</v>
@@ -8450,11 +9514,11 @@
       </c>
       <c r="F94" s="8">
         <f>'[92]MD50000.15-DEC'!$K$1</f>
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="G94" s="8">
         <f>'[92]MD50000.15-DEC'!$K$2</f>
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H94" s="8"/>
       <c r="I94" s="8"/>
@@ -8467,11 +9531,11 @@
       </c>
       <c r="L94" s="7">
         <f>'[92]MD50000.15-DEC'!$O$2</f>
-        <v>59000</v>
+        <v>53500</v>
       </c>
       <c r="M94" s="7">
         <f>'[92]MD50000.15-DEC'!$O$1</f>
-        <v>1000</v>
+        <v>6500</v>
       </c>
       <c r="N94" s="1">
         <v>3500</v>

--- a/LoanOfficer-A/LoanBook.xlsx
+++ b/LoanOfficer-A/LoanBook.xlsx
@@ -103,13 +103,15 @@
     <externalReference r:id="rId92"/>
     <externalReference r:id="rId93"/>
     <externalReference r:id="rId94"/>
+    <externalReference r:id="rId95"/>
+    <externalReference r:id="rId96"/>
   </externalReferences>
   <calcPr calcId="145621" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="126">
   <si>
     <t>Code</t>
   </si>
@@ -472,6 +474,21 @@
   </si>
   <si>
     <t>Angom Bijenty</t>
+  </si>
+  <si>
+    <t>Sweety</t>
+  </si>
+  <si>
+    <t>L20000W17P1400-mon</t>
+  </si>
+  <si>
+    <t>induleikha</t>
+  </si>
+  <si>
+    <t>L20000W17P1400-sat</t>
+  </si>
+  <si>
+    <t>active</t>
   </si>
 </sst>
 </file>
@@ -709,10 +726,10 @@
     <xf numFmtId="164" fontId="3" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -724,10 +741,10 @@
     <xf numFmtId="164" fontId="3" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -762,6 +779,540 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.10-JAN"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="G1">
+            <v>48</v>
+          </cell>
+          <cell r="O1">
+            <v>14000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>40</v>
+          </cell>
+          <cell r="O2">
+            <v>2800</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45399</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>75</v>
+          </cell>
+          <cell r="O1">
+            <v>4500</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>45</v>
+          </cell>
+          <cell r="O2">
+            <v>7500</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45584</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEc"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>5</v>
+          </cell>
+          <cell r="O1">
+            <v>17000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>12</v>
+          </cell>
+          <cell r="O2">
+            <v>7000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45595</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.10-JAN"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>6</v>
+          </cell>
+          <cell r="O1">
+            <v>15600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>11</v>
+          </cell>
+          <cell r="O2">
+            <v>8400</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45602</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>58</v>
+          </cell>
+          <cell r="O1">
+            <v>6200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>62</v>
+          </cell>
+          <cell r="O2">
+            <v>5800</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45612</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD50000.15-DEC"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>100000</v>
+          </cell>
+          <cell r="K1">
+            <v>228</v>
+          </cell>
+          <cell r="O1">
+            <v>23400</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>39</v>
+          </cell>
+          <cell r="O2">
+            <v>136800</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45619</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>50000</v>
+          </cell>
+          <cell r="K1">
+            <v>74</v>
+          </cell>
+          <cell r="O1">
+            <v>23000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>46</v>
+          </cell>
+          <cell r="O2">
+            <v>37000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45628</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>79</v>
+          </cell>
+          <cell r="O1">
+            <v>4100</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>41</v>
+          </cell>
+          <cell r="O2">
+            <v>7900</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45635</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>79</v>
+          </cell>
+          <cell r="O1">
+            <v>4100</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>41</v>
+          </cell>
+          <cell r="O2">
+            <v>7900</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45635</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD50000.15-DEC"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>200000</v>
+          </cell>
+          <cell r="K1">
+            <v>250</v>
+          </cell>
+          <cell r="O1">
+            <v>20400</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>300000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45648</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEc"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>14</v>
+          </cell>
+          <cell r="O1">
+            <v>2100</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>3</v>
+          </cell>
+          <cell r="O2">
+            <v>9900</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45649</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>22</v>
+          </cell>
+          <cell r="O1">
+            <v>9800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>98</v>
+          </cell>
+          <cell r="O2">
+            <v>2200</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45557</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD50000.15-DEC"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>50000</v>
+          </cell>
+          <cell r="K1">
+            <v>104</v>
+          </cell>
+          <cell r="O1">
+            <v>8000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>16</v>
+          </cell>
+          <cell r="O2">
+            <v>52000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45652</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
       <sheetName val="loanform1"/>
       <sheetName val="loanform2"/>
       <sheetName val="SM5000.1-SEPT"/>
@@ -835,7 +1386,375 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45212</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45213</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.20-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45226</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanform1"/>
+      <sheetName val="loanform2"/>
+      <sheetName val="SM5000.1-SEPT (2)"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2">
+        <row r="1">
+          <cell r="C1">
+            <v>5000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>6000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>60</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45243</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.20-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45245</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD15000.27-NOV"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>15000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>18000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45266</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEC"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45649</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEc"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45646</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>14</v>
+          </cell>
+          <cell r="O1">
+            <v>10600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>106</v>
+          </cell>
+          <cell r="O2">
+            <v>1400</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45561</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -877,7 +1796,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -917,7 +1836,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -949,7 +1868,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -991,7 +1910,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1031,7 +1950,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1073,7 +1992,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1115,7 +2034,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1155,7 +2074,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1195,7 +2114,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1237,7 +2156,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1252,23 +2171,23 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>0</v>
+            <v>18</v>
           </cell>
           <cell r="O1">
-            <v>12000</v>
+            <v>10200</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>120</v>
+            <v>102</v>
           </cell>
           <cell r="O2">
-            <v>0</v>
+            <v>1800</v>
           </cell>
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45212</v>
+            <v>45563</v>
           </cell>
         </row>
       </sheetData>
@@ -1277,7 +2196,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1319,7 +2238,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1359,7 +2278,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1399,7 +2318,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1439,7 +2358,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1475,7 +2394,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1503,7 +2422,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1545,7 +2464,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1585,7 +2504,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1627,7 +2546,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1669,7 +2588,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1678,29 +2597,29 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1">
+      <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
-            <v>10000</v>
+            <v>15000</v>
           </cell>
           <cell r="K1">
-            <v>0</v>
+            <v>47</v>
           </cell>
           <cell r="O1">
-            <v>12000</v>
+            <v>10950</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>120</v>
+            <v>73</v>
           </cell>
           <cell r="O2">
-            <v>0</v>
+            <v>7050</v>
           </cell>
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45213</v>
+            <v>45570</v>
           </cell>
         </row>
       </sheetData>
@@ -1709,7 +2628,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1751,7 +2670,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1793,49 +2712,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.10-JAN"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="G1">
-            <v>48</v>
-          </cell>
-          <cell r="O1">
-            <v>12950</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>37</v>
-          </cell>
-          <cell r="O2">
-            <v>3850</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45399</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1877,7 +2754,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1917,7 +2794,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1956,7 +2833,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1979,7 +2856,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2019,7 +2896,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2059,7 +2936,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2099,47 +2976,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.20-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>12000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45226</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2179,7 +3016,47 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>100000</v>
+          </cell>
+          <cell r="K1">
+            <v>27</v>
+          </cell>
+          <cell r="O1">
+            <v>52000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>13</v>
+          </cell>
+          <cell r="O2">
+            <v>108000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45590</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2219,7 +3096,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2256,7 +3133,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2282,7 +3159,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2314,7 +3191,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2354,7 +3231,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2394,7 +3271,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2436,7 +3313,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2478,7 +3355,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2518,49 +3395,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanform1"/>
-      <sheetName val="loanform2"/>
-      <sheetName val="SM5000.1-SEPT (2)"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="1">
-          <cell r="C1">
-            <v>5000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>6000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>60</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45243</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2602,7 +3437,47 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>82</v>
+          </cell>
+          <cell r="O1">
+            <v>7600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>38</v>
+          </cell>
+          <cell r="O2">
+            <v>16400</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45584</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2644,7 +3519,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink71.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2684,7 +3559,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink72.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2724,7 +3599,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink73.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2764,7 +3639,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink74.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2806,7 +3681,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink75.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2848,7 +3723,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink76.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2888,7 +3763,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink77.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2930,7 +3805,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink78.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2970,47 +3845,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.20-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>12000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45245</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink79.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3050,7 +3885,47 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>36</v>
+          </cell>
+          <cell r="O1">
+            <v>16800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>84</v>
+          </cell>
+          <cell r="O2">
+            <v>7200</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7">
+            <v>45587</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink80.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3085,852 +3960,6 @@
           </cell>
         </row>
       </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.22-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13">
-            <v>45562</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.1-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>12000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45557</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.1-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>28</v>
-          </cell>
-          <cell r="O1">
-            <v>9200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>92</v>
-          </cell>
-          <cell r="O2">
-            <v>2800</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45557</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.1-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>16</v>
-          </cell>
-          <cell r="O1">
-            <v>10400</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>104</v>
-          </cell>
-          <cell r="O2">
-            <v>1600</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45561</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45562</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.1-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>25</v>
-          </cell>
-          <cell r="O1">
-            <v>9500</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>95</v>
-          </cell>
-          <cell r="O2">
-            <v>2500</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45563</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.1-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>15000</v>
-          </cell>
-          <cell r="K1">
-            <v>53</v>
-          </cell>
-          <cell r="O1">
-            <v>10050</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>67</v>
-          </cell>
-          <cell r="O2">
-            <v>7950</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45570</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>50000</v>
-          </cell>
-          <cell r="K1">
-            <v>66</v>
-          </cell>
-          <cell r="O1">
-            <v>27000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>54</v>
-          </cell>
-          <cell r="O2">
-            <v>33000</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45579</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD15000.27-NOV"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>15000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>18000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45266</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>100000</v>
-          </cell>
-          <cell r="K1">
-            <v>29</v>
-          </cell>
-          <cell r="O1">
-            <v>44000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>11</v>
-          </cell>
-          <cell r="O2">
-            <v>116000</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45590</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink71.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>50000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>60000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45584</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink72.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45584</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink73.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>82</v>
-          </cell>
-          <cell r="O1">
-            <v>7600</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>38</v>
-          </cell>
-          <cell r="O2">
-            <v>16400</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45584</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink74.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45584</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink75.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>36</v>
-          </cell>
-          <cell r="O1">
-            <v>16800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>84</v>
-          </cell>
-          <cell r="O2">
-            <v>7200</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7">
-            <v>45587</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink76.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>104</v>
-          </cell>
-          <cell r="O1">
-            <v>1600</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>16</v>
-          </cell>
-          <cell r="O2">
-            <v>10400</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45584</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink77.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>75</v>
-          </cell>
-          <cell r="O1">
-            <v>4500</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>45</v>
-          </cell>
-          <cell r="O2">
-            <v>7500</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45584</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink78.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>12000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45587</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink79.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.15-DEc"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>7</v>
-          </cell>
-          <cell r="O1">
-            <v>14200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>10</v>
-          </cell>
-          <cell r="O2">
-            <v>9800</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45595</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.15-DEC"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45649</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink80.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.10-JAN"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>8</v>
-          </cell>
-          <cell r="O1">
-            <v>12800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>9</v>
-          </cell>
-          <cell r="O2">
-            <v>11200</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45602</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3965,9 +3994,9 @@
             <v>0</v>
           </cell>
         </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45597</v>
+        <row r="13">
+          <cell r="B13">
+            <v>45562</v>
           </cell>
         </row>
       </sheetData>
@@ -3977,6 +4006,364 @@
 </file>
 
 <file path=xl/externalLinks/externalLink82.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45557</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink83.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45562</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink84.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>50000</v>
+          </cell>
+          <cell r="K1">
+            <v>66</v>
+          </cell>
+          <cell r="O1">
+            <v>27000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>54</v>
+          </cell>
+          <cell r="O2">
+            <v>33000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45579</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink85.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>50000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>60000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45584</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink86.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45584</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink87.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45584</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink88.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45587</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink89.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.22-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45597</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>94</v>
+          </cell>
+          <cell r="O1">
+            <v>2600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>26</v>
+          </cell>
+          <cell r="O2">
+            <v>9400</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45584</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink90.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4016,7 +4403,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink83.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink91.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4056,129 +4443,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink84.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>77</v>
-          </cell>
-          <cell r="O1">
-            <v>4300</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>43</v>
-          </cell>
-          <cell r="O2">
-            <v>7700</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45612</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink85.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD50000.15-DEC"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>100000</v>
-          </cell>
-          <cell r="K1">
-            <v>233</v>
-          </cell>
-          <cell r="O1">
-            <v>20400</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>34</v>
-          </cell>
-          <cell r="O2">
-            <v>139800</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45619</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink86.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>50000</v>
-          </cell>
-          <cell r="K1">
-            <v>80</v>
-          </cell>
-          <cell r="O1">
-            <v>20000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>40</v>
-          </cell>
-          <cell r="O2">
-            <v>40000</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45628</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink87.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink92.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4218,92 +4483,12 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink88.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink93.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>99</v>
-          </cell>
-          <cell r="O1">
-            <v>2100</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>21</v>
-          </cell>
-          <cell r="O2">
-            <v>9900</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45635</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink89.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>99</v>
-          </cell>
-          <cell r="O1">
-            <v>2100</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>21</v>
-          </cell>
-          <cell r="O2">
-            <v>9900</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45635</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.15-DEc"/>
+      <sheetName val="MD50000.15-DEC"/>
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
@@ -4314,23 +4499,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>0</v>
+            <v>17</v>
           </cell>
           <cell r="O1">
-            <v>24000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>17</v>
+            <v>0</v>
           </cell>
           <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45646</v>
+            <v>23800</v>
           </cell>
         </row>
       </sheetData>
@@ -4340,7 +4520,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink90.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink94.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4349,118 +4529,29 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
-            <v>200000</v>
+            <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>253</v>
+            <v>17</v>
           </cell>
           <cell r="O1">
-            <v>16800</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>14</v>
+            <v>0</v>
           </cell>
           <cell r="O2">
-            <v>303600</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45648</v>
+            <v>23800</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink91.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.15-DEc"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>14</v>
-          </cell>
-          <cell r="O1">
-            <v>2100</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>3</v>
-          </cell>
-          <cell r="O2">
-            <v>9900</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45649</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink92.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD50000.15-DEC"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>50000</v>
-          </cell>
-          <cell r="K1">
-            <v>107</v>
-          </cell>
-          <cell r="O1">
-            <v>6500</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>13</v>
-          </cell>
-          <cell r="O2">
-            <v>53500</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45652</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4721,7 +4812,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4753,23 +4844,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="34"/>
+      <c r="C2" s="29"/>
       <c r="I2" s="30" t="s">
         <v>21</v>
       </c>
       <c r="J2" s="31"/>
       <c r="K2" s="32"/>
-      <c r="L2" s="28">
+      <c r="L2" s="33">
         <f>SUM(L5:L38)</f>
-        <v>771500</v>
-      </c>
-      <c r="M2" s="29"/>
+        <v>784050</v>
+      </c>
+      <c r="M2" s="34"/>
       <c r="N2" s="1">
         <f>SUM(N5:N47)</f>
-        <v>36900</v>
+        <v>39700</v>
       </c>
       <c r="Q2" s="1">
         <f>14900+260750</f>
@@ -4835,33 +4926,33 @@
         <v>39</v>
       </c>
       <c r="E5" s="15">
-        <f>'[32]MD10000.10-JAN'!$C$1</f>
+        <f>'[1]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
       <c r="H5" s="13">
-        <f>'[32]MD10000.10-JAN'!$G$1</f>
+        <f>'[1]MD10000.10-JAN'!$G$1</f>
         <v>48</v>
       </c>
       <c r="I5" s="13">
-        <f>'[32]MD10000.10-JAN'!$K$2</f>
-        <v>37</v>
+        <f>'[1]MD10000.10-JAN'!$K$2</f>
+        <v>40</v>
       </c>
       <c r="J5" s="16" t="s">
         <v>12</v>
       </c>
       <c r="K5" s="14">
-        <f>'[32]MD10000.10-JAN'!$B$3</f>
+        <f>'[1]MD10000.10-JAN'!$B$3</f>
         <v>45399</v>
       </c>
       <c r="L5" s="15">
-        <f>'[32]MD10000.10-JAN'!$O$2</f>
-        <v>3850</v>
+        <f>'[1]MD10000.10-JAN'!$O$2</f>
+        <v>2800</v>
       </c>
       <c r="M5" s="15">
-        <f>'[32]MD10000.10-JAN'!$O$1</f>
-        <v>12950</v>
+        <f>'[1]MD10000.10-JAN'!$O$1</f>
+        <v>14000</v>
       </c>
       <c r="N5" s="1">
         <v>350</v>
@@ -4878,16 +4969,16 @@
         <v>68</v>
       </c>
       <c r="E6" s="7">
-        <f>'[64]MD10000.1-OCT'!$C$1</f>
+        <f>'[2]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F6" s="8">
-        <f>'[64]MD10000.1-OCT'!$K$1</f>
-        <v>28</v>
+        <f>'[2]MD10000.1-OCT'!$K$1</f>
+        <v>22</v>
       </c>
       <c r="G6" s="8">
-        <f>'[64]MD10000.1-OCT'!$K$2</f>
-        <v>92</v>
+        <f>'[2]MD10000.1-OCT'!$K$2</f>
+        <v>98</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
@@ -4895,16 +4986,16 @@
         <v>12</v>
       </c>
       <c r="K6" s="10">
-        <f>'[64]MD10000.1-OCT'!$B$3</f>
+        <f>'[2]MD10000.1-OCT'!$B$3</f>
         <v>45557</v>
       </c>
       <c r="L6" s="7">
-        <f>'[64]MD10000.1-OCT'!$O$2</f>
-        <v>2800</v>
+        <f>'[2]MD10000.1-OCT'!$O$2</f>
+        <v>2200</v>
       </c>
       <c r="M6" s="7">
-        <f>'[64]MD10000.1-OCT'!$O$1</f>
-        <v>9200</v>
+        <f>'[2]MD10000.1-OCT'!$O$1</f>
+        <v>9800</v>
       </c>
       <c r="N6" s="1">
         <v>700</v>
@@ -4921,16 +5012,16 @@
         <v>68</v>
       </c>
       <c r="E7" s="7">
-        <f>'[65]MD10000.1-OCT'!$C$1</f>
+        <f>'[3]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F7" s="8">
-        <f>'[65]MD10000.1-OCT'!$K$1</f>
-        <v>16</v>
+        <f>'[3]MD10000.1-OCT'!$K$1</f>
+        <v>14</v>
       </c>
       <c r="G7" s="8">
-        <f>'[65]MD10000.1-OCT'!$K$2</f>
-        <v>104</v>
+        <f>'[3]MD10000.1-OCT'!$K$2</f>
+        <v>106</v>
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
@@ -4938,16 +5029,16 @@
         <v>12</v>
       </c>
       <c r="K7" s="10">
-        <f>'[65]MD10000.1-OCT'!$B$3</f>
+        <f>'[3]MD10000.1-OCT'!$B$3</f>
         <v>45561</v>
       </c>
       <c r="L7" s="7">
-        <f>'[65]MD10000.1-OCT'!$O$2</f>
-        <v>1600</v>
+        <f>'[3]MD10000.1-OCT'!$O$2</f>
+        <v>1400</v>
       </c>
       <c r="M7" s="7">
-        <f>'[65]MD10000.1-OCT'!$O$1</f>
-        <v>10400</v>
+        <f>'[3]MD10000.1-OCT'!$O$1</f>
+        <v>10600</v>
       </c>
       <c r="N7" s="1">
         <v>700</v>
@@ -4964,16 +5055,16 @@
         <v>68</v>
       </c>
       <c r="E8" s="7">
-        <f>'[67]MD10000.1-OCT'!$C$1</f>
+        <f>'[4]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F8" s="8">
-        <f>'[67]MD10000.1-OCT'!$K$1</f>
-        <v>25</v>
+        <f>'[4]MD10000.1-OCT'!$K$1</f>
+        <v>18</v>
       </c>
       <c r="G8" s="8">
-        <f>'[67]MD10000.1-OCT'!$K$2</f>
-        <v>95</v>
+        <f>'[4]MD10000.1-OCT'!$K$2</f>
+        <v>102</v>
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
@@ -4981,16 +5072,16 @@
         <v>12</v>
       </c>
       <c r="K8" s="10">
-        <f>'[67]MD10000.1-OCT'!$B$3</f>
+        <f>'[4]MD10000.1-OCT'!$B$3</f>
         <v>45563</v>
       </c>
       <c r="L8" s="7">
-        <f>'[67]MD10000.1-OCT'!$O$2</f>
-        <v>2500</v>
+        <f>'[4]MD10000.1-OCT'!$O$2</f>
+        <v>1800</v>
       </c>
       <c r="M8" s="7">
-        <f>'[67]MD10000.1-OCT'!$O$1</f>
-        <v>9500</v>
+        <f>'[4]MD10000.1-OCT'!$O$1</f>
+        <v>10200</v>
       </c>
       <c r="N8" s="1">
         <v>700</v>
@@ -5007,16 +5098,16 @@
         <v>94</v>
       </c>
       <c r="E9" s="7">
-        <f>'[68]MD10000.1-OCT'!$C$1</f>
+        <f>'[5]MD10000.1-OCT'!$C$1</f>
         <v>15000</v>
       </c>
       <c r="F9" s="8">
-        <f>'[68]MD10000.1-OCT'!$K$1</f>
-        <v>53</v>
+        <f>'[5]MD10000.1-OCT'!$K$1</f>
+        <v>47</v>
       </c>
       <c r="G9" s="8">
-        <f>'[68]MD10000.1-OCT'!$K$2</f>
-        <v>67</v>
+        <f>'[5]MD10000.1-OCT'!$K$2</f>
+        <v>73</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
@@ -5024,16 +5115,16 @@
         <v>12</v>
       </c>
       <c r="K9" s="10">
-        <f>'[68]MD10000.1-OCT'!$B$3</f>
+        <f>'[5]MD10000.1-OCT'!$B$3</f>
         <v>45570</v>
       </c>
       <c r="L9" s="7">
-        <f>'[68]MD10000.1-OCT'!$O$2</f>
-        <v>7950</v>
+        <f>'[5]MD10000.1-OCT'!$O$2</f>
+        <v>7050</v>
       </c>
       <c r="M9" s="7">
-        <f>'[68]MD10000.1-OCT'!$O$1</f>
-        <v>10050</v>
+        <f>'[5]MD10000.1-OCT'!$O$1</f>
+        <v>10950</v>
       </c>
       <c r="N9" s="1">
         <v>1050</v>
@@ -5050,33 +5141,33 @@
         <v>98</v>
       </c>
       <c r="E10" s="7">
-        <f>'[70]MD20000.18-DEC'!$C$1</f>
+        <f>'[6]MD20000.18-DEC'!$C$1</f>
         <v>100000</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
       <c r="H10" s="8">
-        <f>'[70]MD20000.18-DEC'!$K$1</f>
-        <v>29</v>
+        <f>'[6]MD20000.18-DEC'!$K$1</f>
+        <v>27</v>
       </c>
       <c r="I10" s="8">
-        <f>'[70]MD20000.18-DEC'!$K$2</f>
-        <v>11</v>
+        <f>'[6]MD20000.18-DEC'!$K$2</f>
+        <v>13</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>12</v>
       </c>
       <c r="K10" s="10">
-        <f>'[70]MD20000.18-DEC'!$B$3</f>
+        <f>'[6]MD20000.18-DEC'!$B$3</f>
         <v>45590</v>
       </c>
       <c r="L10" s="7">
-        <f>'[70]MD20000.18-DEC'!$O$2</f>
-        <v>116000</v>
+        <f>'[6]MD20000.18-DEC'!$O$2</f>
+        <v>108000</v>
       </c>
       <c r="M10" s="7">
-        <f>'[70]MD20000.18-DEC'!$O$1</f>
-        <v>44000</v>
+        <f>'[6]MD20000.18-DEC'!$O$1</f>
+        <v>52000</v>
       </c>
       <c r="N10" s="1">
         <v>4000</v>
@@ -5093,15 +5184,15 @@
         <v>90</v>
       </c>
       <c r="E11" s="7">
-        <f>'[73]MD20000.18-DEC'!$C$1</f>
+        <f>'[7]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F11" s="8">
-        <f>'[73]MD20000.18-DEC'!$K$1</f>
+        <f>'[7]MD20000.18-DEC'!$K$1</f>
         <v>82</v>
       </c>
       <c r="G11" s="8">
-        <f>'[73]MD20000.18-DEC'!$K$2</f>
+        <f>'[7]MD20000.18-DEC'!$K$2</f>
         <v>38</v>
       </c>
       <c r="H11" s="8"/>
@@ -5110,15 +5201,15 @@
         <v>12</v>
       </c>
       <c r="K11" s="10">
-        <f>'[73]MD20000.18-DEC'!$B$3</f>
+        <f>'[7]MD20000.18-DEC'!$B$3</f>
         <v>45584</v>
       </c>
       <c r="L11" s="7">
-        <f>'[73]MD20000.18-DEC'!$O$2</f>
+        <f>'[7]MD20000.18-DEC'!$O$2</f>
         <v>16400</v>
       </c>
       <c r="M11" s="7">
-        <f>'[73]MD20000.18-DEC'!$O$1</f>
+        <f>'[7]MD20000.18-DEC'!$O$1</f>
         <v>7600</v>
       </c>
       <c r="N11" s="1">
@@ -5136,15 +5227,15 @@
         <v>90</v>
       </c>
       <c r="E12" s="7">
-        <f>'[75]MD20000.18-DEC'!$C$1</f>
+        <f>'[8]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F12" s="8">
-        <f>'[75]MD20000.18-DEC'!$K$1</f>
+        <f>'[8]MD20000.18-DEC'!$K$1</f>
         <v>36</v>
       </c>
       <c r="G12" s="8">
-        <f>'[75]MD20000.18-DEC'!$K$2</f>
+        <f>'[8]MD20000.18-DEC'!$K$2</f>
         <v>84</v>
       </c>
       <c r="H12" s="8"/>
@@ -5153,15 +5244,15 @@
         <v>12</v>
       </c>
       <c r="K12" s="10">
-        <f>'[75]MD20000.18-DEC'!$B$7</f>
+        <f>'[8]MD20000.18-DEC'!$B$7</f>
         <v>45587</v>
       </c>
       <c r="L12" s="7">
-        <f>'[75]MD20000.18-DEC'!$O$2</f>
+        <f>'[8]MD20000.18-DEC'!$O$2</f>
         <v>7200</v>
       </c>
       <c r="M12" s="7">
-        <f>'[75]MD20000.18-DEC'!$O$1</f>
+        <f>'[8]MD20000.18-DEC'!$O$1</f>
         <v>16800</v>
       </c>
       <c r="N12" s="1">
@@ -5179,16 +5270,16 @@
         <v>68</v>
       </c>
       <c r="E13" s="7">
-        <f>'[76]MD20000.18-DEC'!$C$1</f>
+        <f>'[9]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F13" s="8">
-        <f>'[76]MD20000.18-DEC'!$K$1</f>
-        <v>104</v>
+        <f>'[9]MD20000.18-DEC'!$K$1</f>
+        <v>94</v>
       </c>
       <c r="G13" s="8">
-        <f>'[76]MD20000.18-DEC'!$K$2</f>
-        <v>16</v>
+        <f>'[9]MD20000.18-DEC'!$K$2</f>
+        <v>26</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
@@ -5196,16 +5287,16 @@
         <v>12</v>
       </c>
       <c r="K13" s="10">
-        <f>'[76]MD20000.18-DEC'!$B$3</f>
+        <f>'[9]MD20000.18-DEC'!$B$3</f>
         <v>45584</v>
       </c>
       <c r="L13" s="7">
-        <f>'[76]MD20000.18-DEC'!$O$2</f>
-        <v>10400</v>
+        <f>'[9]MD20000.18-DEC'!$O$2</f>
+        <v>9400</v>
       </c>
       <c r="M13" s="7">
-        <f>'[76]MD20000.18-DEC'!$O$1</f>
-        <v>1600</v>
+        <f>'[9]MD20000.18-DEC'!$O$1</f>
+        <v>2600</v>
       </c>
       <c r="N13" s="1">
         <v>700</v>
@@ -5222,15 +5313,15 @@
         <v>68</v>
       </c>
       <c r="E14" s="7">
-        <f>'[77]MD20000.18-DEC'!$C$1</f>
+        <f>'[10]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F14" s="8">
-        <f>'[77]MD20000.18-DEC'!$K$1</f>
+        <f>'[10]MD20000.18-DEC'!$K$1</f>
         <v>75</v>
       </c>
       <c r="G14" s="8">
-        <f>'[77]MD20000.18-DEC'!$K$2</f>
+        <f>'[10]MD20000.18-DEC'!$K$2</f>
         <v>45</v>
       </c>
       <c r="H14" s="8"/>
@@ -5239,15 +5330,15 @@
         <v>12</v>
       </c>
       <c r="K14" s="10">
-        <f>'[77]MD20000.18-DEC'!$B$3</f>
+        <f>'[10]MD20000.18-DEC'!$B$3</f>
         <v>45584</v>
       </c>
       <c r="L14" s="7">
-        <f>'[77]MD20000.18-DEC'!$O$2</f>
+        <f>'[10]MD20000.18-DEC'!$O$2</f>
         <v>7500</v>
       </c>
       <c r="M14" s="7">
-        <f>'[77]MD20000.18-DEC'!$O$1</f>
+        <f>'[10]MD20000.18-DEC'!$O$1</f>
         <v>4500</v>
       </c>
       <c r="N14" s="1">
@@ -5265,33 +5356,33 @@
         <v>52</v>
       </c>
       <c r="E15" s="7">
-        <f>'[79]MD20000.15-DEc'!$C$1</f>
+        <f>'[11]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F15" s="8"/>
       <c r="G15" s="8"/>
       <c r="H15" s="8">
-        <f>'[79]MD20000.15-DEc'!$K$1</f>
-        <v>7</v>
+        <f>'[11]MD20000.15-DEc'!$K$1</f>
+        <v>5</v>
       </c>
       <c r="I15" s="8">
-        <f>'[79]MD20000.15-DEc'!$K$2</f>
-        <v>10</v>
+        <f>'[11]MD20000.15-DEc'!$K$2</f>
+        <v>12</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>12</v>
       </c>
       <c r="K15" s="10">
-        <f>'[79]MD20000.15-DEc'!$B$3</f>
+        <f>'[11]MD20000.15-DEc'!$B$3</f>
         <v>45595</v>
       </c>
       <c r="L15" s="7">
-        <f>'[79]MD20000.15-DEc'!$O$2</f>
-        <v>9800</v>
+        <f>'[11]MD20000.15-DEc'!$O$2</f>
+        <v>7000</v>
       </c>
       <c r="M15" s="7">
-        <f>'[79]MD20000.15-DEc'!$O$1</f>
-        <v>14200</v>
+        <f>'[11]MD20000.15-DEc'!$O$1</f>
+        <v>17000</v>
       </c>
       <c r="N15" s="1">
         <v>1400</v>
@@ -5308,33 +5399,33 @@
         <v>106</v>
       </c>
       <c r="E16" s="7">
-        <f>'[80]MD10000.10-JAN'!$C$1</f>
+        <f>'[12]MD10000.10-JAN'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
       <c r="H16" s="8">
-        <f>'[80]MD10000.10-JAN'!$K$1</f>
-        <v>8</v>
+        <f>'[12]MD10000.10-JAN'!$K$1</f>
+        <v>6</v>
       </c>
       <c r="I16" s="8">
-        <f>'[80]MD10000.10-JAN'!$K$2</f>
-        <v>9</v>
+        <f>'[12]MD10000.10-JAN'!$K$2</f>
+        <v>11</v>
       </c>
       <c r="J16" s="9" t="s">
         <v>12</v>
       </c>
       <c r="K16" s="10">
-        <f>'[80]MD10000.10-JAN'!$B$3</f>
+        <f>'[12]MD10000.10-JAN'!$B$3</f>
         <v>45602</v>
       </c>
       <c r="L16" s="7">
-        <f>'[80]MD10000.10-JAN'!$O$2</f>
-        <v>11200</v>
+        <f>'[12]MD10000.10-JAN'!$O$2</f>
+        <v>8400</v>
       </c>
       <c r="M16" s="7">
-        <f>'[80]MD10000.10-JAN'!$O$1</f>
-        <v>12800</v>
+        <f>'[12]MD10000.10-JAN'!$O$1</f>
+        <v>15600</v>
       </c>
       <c r="N16" s="1">
         <v>1400</v>
@@ -5351,16 +5442,16 @@
         <v>68</v>
       </c>
       <c r="E17" s="7">
-        <f>'[84]MD20000.18-DEC'!$C$1</f>
+        <f>'[13]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F17" s="8">
-        <f>'[84]MD20000.18-DEC'!$K$1</f>
-        <v>77</v>
+        <f>'[13]MD20000.18-DEC'!$K$1</f>
+        <v>58</v>
       </c>
       <c r="G17" s="8">
-        <f>'[84]MD20000.18-DEC'!$K$2</f>
-        <v>43</v>
+        <f>'[13]MD20000.18-DEC'!$K$2</f>
+        <v>62</v>
       </c>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
@@ -5368,16 +5459,16 @@
         <v>12</v>
       </c>
       <c r="K17" s="10">
-        <f>'[84]MD20000.18-DEC'!$B$3</f>
+        <f>'[13]MD20000.18-DEC'!$B$3</f>
         <v>45612</v>
       </c>
       <c r="L17" s="7">
-        <f>'[84]MD20000.18-DEC'!$O$2</f>
-        <v>7700</v>
+        <f>'[13]MD20000.18-DEC'!$O$2</f>
+        <v>5800</v>
       </c>
       <c r="M17" s="7">
-        <f>'[84]MD20000.18-DEC'!$O$1</f>
-        <v>4300</v>
+        <f>'[13]MD20000.18-DEC'!$O$1</f>
+        <v>6200</v>
       </c>
       <c r="N17" s="1">
         <v>700</v>
@@ -5394,16 +5485,16 @@
         <v>111</v>
       </c>
       <c r="E18" s="7">
-        <f>'[85]MD50000.15-DEC'!$C$1</f>
+        <f>'[14]MD50000.15-DEC'!$C$1</f>
         <v>100000</v>
       </c>
       <c r="F18" s="8">
-        <f>'[85]MD50000.15-DEC'!$K$1</f>
-        <v>233</v>
+        <f>'[14]MD50000.15-DEC'!$K$1</f>
+        <v>228</v>
       </c>
       <c r="G18" s="8">
-        <f>'[85]MD50000.15-DEC'!$K$2</f>
-        <v>34</v>
+        <f>'[14]MD50000.15-DEC'!$K$2</f>
+        <v>39</v>
       </c>
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
@@ -5411,16 +5502,16 @@
         <v>12</v>
       </c>
       <c r="K18" s="10">
-        <f>'[85]MD50000.15-DEC'!$B$3</f>
+        <f>'[14]MD50000.15-DEC'!$B$3</f>
         <v>45619</v>
       </c>
       <c r="L18" s="7">
-        <f>'[85]MD50000.15-DEC'!$O$2</f>
-        <v>139800</v>
+        <f>'[14]MD50000.15-DEC'!$O$2</f>
+        <v>136800</v>
       </c>
       <c r="M18" s="7">
-        <f>'[85]MD50000.15-DEC'!$O$1</f>
-        <v>20400</v>
+        <f>'[14]MD50000.15-DEC'!$O$1</f>
+        <v>23400</v>
       </c>
       <c r="N18" s="1">
         <v>4200</v>
@@ -5437,16 +5528,16 @@
         <v>96</v>
       </c>
       <c r="E19" s="7">
-        <f>'[86]MD20000.18-DEC'!$C$1</f>
+        <f>'[15]MD20000.18-DEC'!$C$1</f>
         <v>50000</v>
       </c>
       <c r="F19" s="8">
-        <f>'[86]MD20000.18-DEC'!$K$1</f>
-        <v>80</v>
+        <f>'[15]MD20000.18-DEC'!$K$1</f>
+        <v>74</v>
       </c>
       <c r="G19" s="8">
-        <f>'[86]MD20000.18-DEC'!$K$2</f>
-        <v>40</v>
+        <f>'[15]MD20000.18-DEC'!$K$2</f>
+        <v>46</v>
       </c>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -5454,16 +5545,16 @@
         <v>12</v>
       </c>
       <c r="K19" s="10">
-        <f>'[86]MD20000.18-DEC'!$B$3</f>
+        <f>'[15]MD20000.18-DEC'!$B$3</f>
         <v>45628</v>
       </c>
       <c r="L19" s="7">
-        <f>'[86]MD20000.18-DEC'!$O$2</f>
-        <v>40000</v>
+        <f>'[15]MD20000.18-DEC'!$O$2</f>
+        <v>37000</v>
       </c>
       <c r="M19" s="7">
-        <f>'[86]MD20000.18-DEC'!$O$1</f>
-        <v>20000</v>
+        <f>'[15]MD20000.18-DEC'!$O$1</f>
+        <v>23000</v>
       </c>
       <c r="N19" s="1">
         <v>3500</v>
@@ -5480,16 +5571,16 @@
         <v>68</v>
       </c>
       <c r="E20" s="7">
-        <f>'[88]MD20000.18-DEC'!$C$1</f>
+        <f>'[16]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F20" s="8">
-        <f>'[88]MD20000.18-DEC'!$K$1</f>
-        <v>99</v>
+        <f>'[16]MD20000.18-DEC'!$K$1</f>
+        <v>79</v>
       </c>
       <c r="G20" s="8">
-        <f>'[88]MD20000.18-DEC'!$K$2</f>
-        <v>21</v>
+        <f>'[16]MD20000.18-DEC'!$K$2</f>
+        <v>41</v>
       </c>
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
@@ -5497,16 +5588,16 @@
         <v>12</v>
       </c>
       <c r="K20" s="10">
-        <f>'[88]MD20000.18-DEC'!$B$3</f>
+        <f>'[16]MD20000.18-DEC'!$B$3</f>
         <v>45635</v>
       </c>
       <c r="L20" s="7">
-        <f>'[88]MD20000.18-DEC'!$O$2</f>
-        <v>9900</v>
+        <f>'[16]MD20000.18-DEC'!$O$2</f>
+        <v>7900</v>
       </c>
       <c r="M20" s="7">
-        <f>'[88]MD20000.18-DEC'!$O$1</f>
-        <v>2100</v>
+        <f>'[16]MD20000.18-DEC'!$O$1</f>
+        <v>4100</v>
       </c>
       <c r="N20" s="1">
         <v>700</v>
@@ -5523,16 +5614,16 @@
         <v>68</v>
       </c>
       <c r="E21" s="7">
-        <f>'[89]MD20000.18-DEC'!$C$1</f>
+        <f>'[17]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F21" s="8">
-        <f>'[89]MD20000.18-DEC'!$K$1</f>
-        <v>99</v>
+        <f>'[17]MD20000.18-DEC'!$K$1</f>
+        <v>79</v>
       </c>
       <c r="G21" s="8">
-        <f>'[89]MD20000.18-DEC'!$K$2</f>
-        <v>21</v>
+        <f>'[17]MD20000.18-DEC'!$K$2</f>
+        <v>41</v>
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
@@ -5540,16 +5631,16 @@
         <v>12</v>
       </c>
       <c r="K21" s="10">
-        <f>'[89]MD20000.18-DEC'!$B$3</f>
+        <f>'[17]MD20000.18-DEC'!$B$3</f>
         <v>45635</v>
       </c>
       <c r="L21" s="7">
-        <f>'[89]MD20000.18-DEC'!$O$2</f>
-        <v>9900</v>
+        <f>'[17]MD20000.18-DEC'!$O$2</f>
+        <v>7900</v>
       </c>
       <c r="M21" s="7">
-        <f>'[89]MD20000.18-DEC'!$O$1</f>
-        <v>2100</v>
+        <f>'[17]MD20000.18-DEC'!$O$1</f>
+        <v>4100</v>
       </c>
       <c r="N21" s="1">
         <v>700</v>
@@ -5566,16 +5657,16 @@
         <v>117</v>
       </c>
       <c r="E22" s="7">
-        <f>'[90]MD50000.15-DEC'!$C$1</f>
+        <f>'[18]MD50000.15-DEC'!$C$1</f>
         <v>200000</v>
       </c>
       <c r="F22" s="8">
-        <f>'[90]MD50000.15-DEC'!$K$1</f>
-        <v>253</v>
+        <f>'[18]MD50000.15-DEC'!$K$1</f>
+        <v>250</v>
       </c>
       <c r="G22" s="8">
-        <f>'[90]MD50000.15-DEC'!$K$2</f>
-        <v>14</v>
+        <f>'[18]MD50000.15-DEC'!$K$2</f>
+        <v>17</v>
       </c>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
@@ -5583,16 +5674,16 @@
         <v>12</v>
       </c>
       <c r="K22" s="10">
-        <f>'[90]MD50000.15-DEC'!$B$3</f>
+        <f>'[18]MD50000.15-DEC'!$B$3</f>
         <v>45648</v>
       </c>
       <c r="L22" s="7">
-        <f>'[90]MD50000.15-DEC'!$O$2</f>
-        <v>303600</v>
+        <f>'[18]MD50000.15-DEC'!$O$2</f>
+        <v>300000</v>
       </c>
       <c r="M22" s="7">
-        <f>'[90]MD50000.15-DEC'!$O$1</f>
-        <v>16800</v>
+        <f>'[18]MD50000.15-DEC'!$O$1</f>
+        <v>20400</v>
       </c>
       <c r="N22" s="1">
         <v>8400</v>
@@ -5609,32 +5700,32 @@
         <v>119</v>
       </c>
       <c r="E23" s="7">
-        <f>'[91]MD20000.15-DEc'!$C$1</f>
+        <f>'[19]MD20000.15-DEc'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
       <c r="H23" s="8">
-        <f>'[91]MD20000.15-DEc'!$K$1</f>
+        <f>'[19]MD20000.15-DEc'!$K$1</f>
         <v>14</v>
       </c>
       <c r="I23" s="8">
-        <f>'[91]MD20000.15-DEc'!$K$2</f>
+        <f>'[19]MD20000.15-DEc'!$K$2</f>
         <v>3</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>12</v>
       </c>
       <c r="K23" s="10">
-        <f>'[91]MD20000.15-DEc'!$B$3</f>
+        <f>'[19]MD20000.15-DEc'!$B$3</f>
         <v>45649</v>
       </c>
       <c r="L23" s="7">
-        <f>'[91]MD20000.15-DEc'!$O$2</f>
+        <f>'[19]MD20000.15-DEc'!$O$2</f>
         <v>9900</v>
       </c>
       <c r="M23" s="7">
-        <f>'[91]MD20000.15-DEc'!$O$1</f>
+        <f>'[19]MD20000.15-DEc'!$O$1</f>
         <v>2100</v>
       </c>
       <c r="N23" s="1">
@@ -5652,16 +5743,16 @@
         <v>96</v>
       </c>
       <c r="E24" s="7">
-        <f>'[92]MD50000.15-DEC'!$C$1</f>
+        <f>'[20]MD50000.15-DEC'!$C$1</f>
         <v>50000</v>
       </c>
       <c r="F24" s="8">
-        <f>'[92]MD50000.15-DEC'!$K$1</f>
-        <v>107</v>
+        <f>'[20]MD50000.15-DEC'!$K$1</f>
+        <v>104</v>
       </c>
       <c r="G24" s="8">
-        <f>'[92]MD50000.15-DEC'!$K$2</f>
-        <v>13</v>
+        <f>'[20]MD50000.15-DEC'!$K$2</f>
+        <v>16</v>
       </c>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
@@ -5669,16 +5760,16 @@
         <v>12</v>
       </c>
       <c r="K24" s="10">
-        <f>'[92]MD50000.15-DEC'!$B$3</f>
+        <f>'[20]MD50000.15-DEC'!$B$3</f>
         <v>45652</v>
       </c>
       <c r="L24" s="7">
-        <f>'[92]MD50000.15-DEC'!$O$2</f>
-        <v>53500</v>
+        <f>'[20]MD50000.15-DEC'!$O$2</f>
+        <v>52000</v>
       </c>
       <c r="M24" s="7">
-        <f>'[92]MD50000.15-DEC'!$O$1</f>
-        <v>6500</v>
+        <f>'[20]MD50000.15-DEC'!$O$1</f>
+        <v>8000</v>
       </c>
       <c r="N24" s="1">
         <v>3500</v>
@@ -5688,33 +5779,87 @@
       <c r="B25" s="6">
         <v>91</v>
       </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="7"/>
+      <c r="C25" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="E25" s="7">
+        <f>'[93]MD50000.15-DEC'!$C$1</f>
+        <v>20000</v>
+      </c>
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
+      <c r="H25" s="8">
+        <f>'[93]MD50000.15-DEC'!$K$1</f>
+        <v>17</v>
+      </c>
+      <c r="I25" s="8">
+        <f>'[93]MD50000.15-DEC'!$K$2</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K25" s="10">
+        <f>'[93]MD50000.15-DEC'!$B$3</f>
+        <v>0</v>
+      </c>
+      <c r="L25" s="7">
+        <f>'[93]MD50000.15-DEC'!$O$2</f>
+        <v>23800</v>
+      </c>
+      <c r="M25" s="7">
+        <f>'[93]MD50000.15-DEC'!$O$1</f>
+        <v>0</v>
+      </c>
+      <c r="N25" s="1">
+        <v>1400</v>
+      </c>
     </row>
     <row r="26" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="6">
         <v>92</v>
       </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="7"/>
+      <c r="C26" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E26" s="7">
+        <f>'[94]MD50000.15-DEC'!$C$1</f>
+        <v>20000</v>
+      </c>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
+      <c r="H26" s="8">
+        <f>'[94]MD50000.15-DEC'!$K$1</f>
+        <v>17</v>
+      </c>
+      <c r="I26" s="8">
+        <f>'[94]MD50000.15-DEC'!$K$2</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="K26" s="10">
+        <f>'[94]MD50000.15-DEC'!$B$3</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="7">
+        <f>'[94]MD50000.15-DEC'!$O$2</f>
+        <v>23800</v>
+      </c>
+      <c r="M26" s="7">
+        <f>'[94]MD50000.15-DEC'!$O$1</f>
+        <v>0</v>
+      </c>
+      <c r="N26" s="1">
+        <v>1400</v>
+      </c>
     </row>
     <row r="27" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="6">
@@ -5816,20 +5961,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="34"/>
+      <c r="C2" s="29"/>
       <c r="I2" s="30" t="s">
         <v>21</v>
       </c>
       <c r="J2" s="31"/>
       <c r="K2" s="32"/>
-      <c r="L2" s="28">
+      <c r="L2" s="33">
         <f>SUM(L5:L108)</f>
-        <v>854500</v>
-      </c>
-      <c r="M2" s="29"/>
+        <v>819450</v>
+      </c>
+      <c r="M2" s="34"/>
       <c r="N2" s="1">
         <f>SUM(N5:N117)</f>
         <v>36900</v>
@@ -5898,15 +6043,15 @@
         <v>18</v>
       </c>
       <c r="E5" s="19">
-        <f>'[1]SM5000.1-SEPT'!$C$1</f>
+        <f>'[21]SM5000.1-SEPT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F5" s="20">
-        <f>'[1]SM5000.1-SEPT'!$K$1</f>
+        <f>'[21]SM5000.1-SEPT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G5" s="20">
-        <f>'[1]SM5000.1-SEPT'!$K$2</f>
+        <f>'[21]SM5000.1-SEPT'!$K$2</f>
         <v>60</v>
       </c>
       <c r="H5" s="20"/>
@@ -5915,15 +6060,15 @@
         <v>22</v>
       </c>
       <c r="K5" s="22">
-        <f>'[1]SM5000.1-SEPT'!$B$3</f>
+        <f>'[21]SM5000.1-SEPT'!$B$3</f>
         <v>45180</v>
       </c>
       <c r="L5" s="19">
-        <f>'[1]SM5000.1-SEPT'!$O$2</f>
+        <f>'[21]SM5000.1-SEPT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M5" s="19">
-        <f>'[1]SM5000.1-SEPT'!$O$1</f>
+        <f>'[21]SM5000.1-SEPT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -5938,15 +6083,15 @@
         <v>18</v>
       </c>
       <c r="E6" s="19">
-        <f>'[1]SM5000.1-oct'!$C$1</f>
+        <f>'[21]SM5000.1-oct'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F6" s="20">
-        <f>'[1]SM5000.1-oct'!$K$1</f>
+        <f>'[21]SM5000.1-oct'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G6" s="20">
-        <f>'[1]SM5000.1-oct'!$K$2</f>
+        <f>'[21]SM5000.1-oct'!$K$2</f>
         <v>60</v>
       </c>
       <c r="H6" s="20"/>
@@ -5955,15 +6100,15 @@
         <v>22</v>
       </c>
       <c r="K6" s="22">
-        <f>'[1]SM5000.1-oct'!$B$3</f>
+        <f>'[21]SM5000.1-oct'!$B$3</f>
         <v>45201</v>
       </c>
       <c r="L6" s="19">
-        <f>'[1]SM5000.1-oct'!$O$2</f>
+        <f>'[21]SM5000.1-oct'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M6" s="19">
-        <f>'[1]SM5000.1-oct'!$O$1</f>
+        <f>'[21]SM5000.1-oct'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -5978,15 +6123,15 @@
         <v>19</v>
       </c>
       <c r="E7" s="19">
-        <f>'[2]MD10000.1-OCT'!$C$1</f>
+        <f>'[22]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F7" s="20">
-        <f>'[2]MD10000.1-OCT'!$K$1</f>
+        <f>'[22]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G7" s="20">
-        <f>'[2]MD10000.1-OCT'!$K$2</f>
+        <f>'[22]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H7" s="20"/>
@@ -5995,15 +6140,15 @@
         <v>22</v>
       </c>
       <c r="K7" s="22">
-        <f>'[2]MD10000.1-OCT'!$B$3</f>
+        <f>'[22]MD10000.1-OCT'!$B$3</f>
         <v>45212</v>
       </c>
       <c r="L7" s="19">
-        <f>'[2]MD10000.1-OCT'!$O$2</f>
+        <f>'[22]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M7" s="19">
-        <f>'[2]MD10000.1-OCT'!$O$1</f>
+        <f>'[22]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -6018,15 +6163,15 @@
         <v>19</v>
       </c>
       <c r="E8" s="19">
-        <f>'[3]MD10000.1-OCT'!$C$1</f>
+        <f>'[23]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F8" s="20">
-        <f>'[3]MD10000.1-OCT'!$K$1</f>
+        <f>'[23]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G8" s="20">
-        <f>'[3]MD10000.1-OCT'!$K$2</f>
+        <f>'[23]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H8" s="20"/>
@@ -6035,15 +6180,15 @@
         <v>22</v>
       </c>
       <c r="K8" s="22">
-        <f>'[3]MD10000.1-OCT'!$B$3</f>
+        <f>'[23]MD10000.1-OCT'!$B$3</f>
         <v>45213</v>
       </c>
       <c r="L8" s="19">
-        <f>'[3]MD10000.1-OCT'!$O$2</f>
+        <f>'[23]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M8" s="19">
-        <f>'[3]MD10000.1-OCT'!$O$1</f>
+        <f>'[23]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -6058,32 +6203,32 @@
         <v>20</v>
       </c>
       <c r="E9" s="19">
-        <f>'[4]MD10000.20-OCT'!$C$1</f>
+        <f>'[24]MD10000.20-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F9" s="20"/>
       <c r="G9" s="20"/>
       <c r="H9" s="20">
-        <f>'[4]MD10000.20-OCT'!$K$1</f>
+        <f>'[24]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I9" s="20">
-        <f>'[4]MD10000.20-OCT'!$K$2</f>
+        <f>'[24]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J9" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K9" s="22">
-        <f>'[4]MD10000.20-OCT'!$B$3</f>
+        <f>'[24]MD10000.20-OCT'!$B$3</f>
         <v>45226</v>
       </c>
       <c r="L9" s="19">
-        <f>'[4]MD10000.20-OCT'!$O$2</f>
+        <f>'[24]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M9" s="19">
-        <f>'[4]MD10000.20-OCT'!$O$1</f>
+        <f>'[24]MD10000.20-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -6098,15 +6243,15 @@
         <v>18</v>
       </c>
       <c r="E10" s="19">
-        <f>'[5]SM5000.1-SEPT (2)'!$C$1</f>
+        <f>'[25]SM5000.1-SEPT (2)'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F10" s="20">
-        <f>'[5]SM5000.1-SEPT (2)'!$K$1</f>
+        <f>'[25]SM5000.1-SEPT (2)'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G10" s="20">
-        <f>'[5]SM5000.1-SEPT (2)'!$K$2</f>
+        <f>'[25]SM5000.1-SEPT (2)'!$K$2</f>
         <v>60</v>
       </c>
       <c r="H10" s="20"/>
@@ -6115,15 +6260,15 @@
         <v>41</v>
       </c>
       <c r="K10" s="22">
-        <f>'[5]SM5000.1-SEPT (2)'!$B$3</f>
+        <f>'[25]SM5000.1-SEPT (2)'!$B$3</f>
         <v>45243</v>
       </c>
       <c r="L10" s="19">
-        <f>'[5]SM5000.1-SEPT (2)'!$O$2</f>
+        <f>'[25]SM5000.1-SEPT (2)'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M10" s="19">
-        <f>'[5]SM5000.1-SEPT (2)'!$O$1</f>
+        <f>'[25]SM5000.1-SEPT (2)'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -6138,32 +6283,32 @@
         <v>20</v>
       </c>
       <c r="E11" s="19">
-        <f>'[6]MD10000.20-OCT'!$C$1</f>
+        <f>'[26]MD10000.20-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F11" s="20"/>
       <c r="G11" s="20"/>
       <c r="H11" s="20">
-        <f>'[6]MD10000.20-OCT'!$K$1</f>
+        <f>'[26]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I11" s="20">
-        <f>'[6]MD10000.20-OCT'!$K$2</f>
+        <f>'[26]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J11" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K11" s="22">
-        <f>'[6]MD10000.20-OCT'!$B$3</f>
+        <f>'[26]MD10000.20-OCT'!$B$3</f>
         <v>45245</v>
       </c>
       <c r="L11" s="19">
-        <f>'[6]MD10000.20-OCT'!$O$2</f>
+        <f>'[26]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M11" s="19">
-        <f>'[6]MD10000.20-OCT'!$O$1</f>
+        <f>'[26]MD10000.20-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -6178,32 +6323,32 @@
         <v>25</v>
       </c>
       <c r="E12" s="19">
-        <f>'[7]MD15000.27-NOV'!$C$1</f>
+        <f>'[27]MD15000.27-NOV'!$C$1</f>
         <v>15000</v>
       </c>
       <c r="F12" s="20"/>
       <c r="G12" s="20"/>
       <c r="H12" s="20">
-        <f>'[7]MD15000.27-NOV'!$K$1</f>
+        <f>'[27]MD15000.27-NOV'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I12" s="20">
-        <f>'[7]MD15000.27-NOV'!$K$2</f>
+        <f>'[27]MD15000.27-NOV'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J12" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K12" s="22">
-        <f>'[7]MD15000.27-NOV'!$B$3</f>
+        <f>'[27]MD15000.27-NOV'!$B$3</f>
         <v>45266</v>
       </c>
       <c r="L12" s="19">
-        <f>'[7]MD15000.27-NOV'!$O$2</f>
+        <f>'[27]MD15000.27-NOV'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M12" s="19">
-        <f>'[7]MD15000.27-NOV'!$O$1</f>
+        <f>'[27]MD15000.27-NOV'!$O$1</f>
         <v>18000</v>
       </c>
     </row>
@@ -6218,32 +6363,32 @@
         <v>29</v>
       </c>
       <c r="E13" s="19">
-        <f>'[8]MD20000.15-DEC'!$C$1</f>
+        <f>'[28]MD20000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F13" s="20"/>
       <c r="G13" s="20"/>
       <c r="H13" s="20">
-        <f>'[8]MD20000.15-DEC'!$K$1</f>
+        <f>'[28]MD20000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I13" s="20">
-        <f>'[8]MD20000.15-DEC'!$K$2</f>
+        <f>'[28]MD20000.15-DEC'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J13" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K13" s="22">
-        <f>'[8]MD20000.15-DEC'!$B$3</f>
+        <f>'[28]MD20000.15-DEC'!$B$3</f>
         <v>45649</v>
       </c>
       <c r="L13" s="19">
-        <f>'[8]MD20000.15-DEC'!$O$2</f>
+        <f>'[28]MD20000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M13" s="19">
-        <f>'[8]MD20000.15-DEC'!$O$1</f>
+        <f>'[28]MD20000.15-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -6258,32 +6403,32 @@
         <v>28</v>
       </c>
       <c r="E14" s="19">
-        <f>'[9]MD20000.15-DEc'!$C$1</f>
+        <f>'[29]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F14" s="20"/>
       <c r="G14" s="20"/>
       <c r="H14" s="20">
-        <f>'[9]MD20000.15-DEc'!$K$1</f>
+        <f>'[29]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I14" s="20">
-        <f>'[9]MD20000.15-DEc'!$K$2</f>
+        <f>'[29]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J14" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K14" s="22">
-        <f>'[9]MD20000.15-DEc'!$B$3</f>
+        <f>'[29]MD20000.15-DEc'!$B$3</f>
         <v>45646</v>
       </c>
       <c r="L14" s="19">
-        <f>'[9]MD20000.15-DEc'!$O$2</f>
+        <f>'[29]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M14" s="19">
-        <f>'[9]MD20000.15-DEc'!$O$1</f>
+        <f>'[29]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -6298,32 +6443,32 @@
         <v>31</v>
       </c>
       <c r="E15" s="19">
-        <f>'[10]MD50000.15-DEC'!$C$1</f>
+        <f>'[30]MD50000.15-DEC'!$C$1</f>
         <v>50000</v>
       </c>
       <c r="F15" s="20"/>
       <c r="G15" s="20"/>
       <c r="H15" s="20">
-        <f>'[10]MD50000.15-DEC'!$K$1</f>
+        <f>'[30]MD50000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I15" s="20">
-        <f>'[10]MD50000.15-DEC'!$K$2</f>
+        <f>'[30]MD50000.15-DEC'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J15" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K15" s="22">
-        <f>'[10]MD50000.15-DEC'!$B$3</f>
+        <f>'[30]MD50000.15-DEC'!$B$3</f>
         <v>45648</v>
       </c>
       <c r="L15" s="19">
-        <f>'[10]MD50000.15-DEC'!$O$2</f>
+        <f>'[30]MD50000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M15" s="19">
-        <f>'[10]MD50000.15-DEC'!$O$1</f>
+        <f>'[30]MD50000.15-DEC'!$O$1</f>
         <v>84000</v>
       </c>
     </row>
@@ -6338,15 +6483,15 @@
         <v>33</v>
       </c>
       <c r="E16" s="19">
-        <f>'[11]MD20000.18-DEC'!$C$1</f>
+        <f>'[31]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F16" s="20">
-        <f>'[11]MD20000.18-DEC'!$K$1</f>
+        <f>'[31]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G16" s="20">
-        <f>'[11]MD20000.18-DEC'!$K$2</f>
+        <f>'[31]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H16" s="20"/>
@@ -6355,15 +6500,15 @@
         <v>53</v>
       </c>
       <c r="K16" s="22">
-        <f>'[11]MD20000.18-DEC'!$B$3</f>
+        <f>'[31]MD20000.18-DEC'!$B$3</f>
         <v>45279</v>
       </c>
       <c r="L16" s="19">
-        <f>'[11]MD20000.18-DEC'!$O$2</f>
+        <f>'[31]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M16" s="19">
-        <f>'[11]MD20000.18-DEC'!$O$1</f>
+        <f>'[31]MD20000.18-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -6378,15 +6523,15 @@
         <v>33</v>
       </c>
       <c r="E17" s="19">
-        <f>'[12]MD20000.22-DEC'!$C$1</f>
+        <f>'[32]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F17" s="20">
-        <f>'[12]MD20000.22-DEC'!$K$1</f>
+        <f>'[32]MD20000.22-DEC'!$K$1</f>
         <v>120</v>
       </c>
       <c r="G17" s="20">
-        <f>'[12]MD20000.22-DEC'!$K$2</f>
+        <f>'[32]MD20000.22-DEC'!$K$2</f>
         <v>0</v>
       </c>
       <c r="H17" s="20"/>
@@ -6395,12 +6540,12 @@
         <v>51</v>
       </c>
       <c r="K17" s="22">
-        <f>'[12]MD20000.22-DEC'!$B$3</f>
+        <f>'[32]MD20000.22-DEC'!$B$3</f>
         <v>0</v>
       </c>
       <c r="L17" s="19"/>
       <c r="M17" s="19">
-        <f>'[12]MD20000.22-DEC'!$O$1</f>
+        <f>'[32]MD20000.22-DEC'!$O$1</f>
         <v>0</v>
       </c>
     </row>
@@ -6415,32 +6560,32 @@
         <v>36</v>
       </c>
       <c r="E18" s="19">
-        <f>'[13]MD50000.15-DEC'!$C$1</f>
+        <f>'[33]MD50000.15-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F18" s="20"/>
       <c r="G18" s="20"/>
       <c r="H18" s="20">
-        <f>'[13]MD50000.15-DEC'!$K$1</f>
+        <f>'[33]MD50000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I18" s="20">
-        <f>'[13]MD50000.15-DEC'!$K$2</f>
+        <f>'[33]MD50000.15-DEC'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J18" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K18" s="22">
-        <f>'[13]MD50000.15-DEC'!$B$3</f>
+        <f>'[33]MD50000.15-DEC'!$B$3</f>
         <v>45310</v>
       </c>
       <c r="L18" s="19">
-        <f>'[13]MD50000.15-DEC'!$O$2</f>
+        <f>'[33]MD50000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M18" s="19">
-        <f>'[13]MD50000.15-DEC'!$O$1</f>
+        <f>'[33]MD50000.15-DEC'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -6455,15 +6600,15 @@
         <v>18</v>
       </c>
       <c r="E19" s="19">
-        <f>'[14]MD5000-Jan24'!$C$1</f>
+        <f>'[34]MD5000-Jan24'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F19" s="20">
-        <f>'[14]MD5000-Jan24'!$K$1</f>
+        <f>'[34]MD5000-Jan24'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G19" s="20">
-        <f>'[14]MD5000-Jan24'!$K$2</f>
+        <f>'[34]MD5000-Jan24'!$K$2</f>
         <v>60</v>
       </c>
       <c r="H19" s="20"/>
@@ -6472,15 +6617,15 @@
         <v>51</v>
       </c>
       <c r="K19" s="22">
-        <f>'[14]MD5000-Jan24'!$B$3</f>
+        <f>'[34]MD5000-Jan24'!$B$3</f>
         <v>45302</v>
       </c>
       <c r="L19" s="19">
-        <f>'[14]MD5000-Jan24'!$O$2</f>
+        <f>'[34]MD5000-Jan24'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M19" s="19">
-        <f>'[14]MD5000-Jan24'!$O$1</f>
+        <f>'[34]MD5000-Jan24'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -6495,32 +6640,32 @@
         <v>39</v>
       </c>
       <c r="E20" s="19">
-        <f>'[15]MD10000.10-JAN'!$C$1</f>
+        <f>'[35]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F20" s="20"/>
       <c r="G20" s="20"/>
       <c r="H20" s="20">
-        <f>'[15]MD10000.10-JAN'!$K$1</f>
+        <f>'[35]MD10000.10-JAN'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I20" s="20">
-        <f>'[15]MD10000.10-JAN'!$K$2</f>
+        <f>'[35]MD10000.10-JAN'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J20" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K20" s="22">
-        <f>'[15]MD10000.10-JAN'!$B$3</f>
+        <f>'[35]MD10000.10-JAN'!$B$3</f>
         <v>45308</v>
       </c>
       <c r="L20" s="19">
-        <f>'[15]MD10000.10-JAN'!$O$2</f>
+        <f>'[35]MD10000.10-JAN'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M20" s="19">
-        <f>'[15]MD10000.10-JAN'!$O$1</f>
+        <f>'[35]MD10000.10-JAN'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -6535,32 +6680,32 @@
         <v>39</v>
       </c>
       <c r="E21" s="19">
-        <f>'[16]MD10000.10-JAN'!$C$1</f>
+        <f>'[36]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F21" s="20"/>
       <c r="G21" s="20"/>
       <c r="H21" s="20">
-        <f>'[16]MD10000.10-JAN'!$K$1</f>
+        <f>'[36]MD10000.10-JAN'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I21" s="20">
-        <f>'[16]MD10000.10-JAN'!$K$2</f>
+        <f>'[36]MD10000.10-JAN'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J21" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K21" s="22">
-        <f>'[16]MD10000.10-JAN'!$B$3</f>
+        <f>'[36]MD10000.10-JAN'!$B$3</f>
         <v>45308</v>
       </c>
       <c r="L21" s="19">
-        <f>'[16]MD10000.10-JAN'!$O$2</f>
+        <f>'[36]MD10000.10-JAN'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M21" s="19">
-        <f>'[16]MD10000.10-JAN'!$O$1</f>
+        <f>'[36]MD10000.10-JAN'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -6575,32 +6720,32 @@
         <v>43</v>
       </c>
       <c r="E22" s="19">
-        <f>'[17]MD10000.20-OCT'!$C$1</f>
+        <f>'[37]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F22" s="20"/>
       <c r="G22" s="20"/>
       <c r="H22" s="20">
-        <f>'[17]MD10000.20-OCT'!$K$1</f>
+        <f>'[37]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I22" s="20">
-        <f>'[17]MD10000.20-OCT'!$K$2</f>
+        <f>'[37]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J22" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K22" s="22">
-        <f>'[17]MD10000.20-OCT'!$B$3</f>
+        <f>'[37]MD10000.20-OCT'!$B$3</f>
         <v>45316</v>
       </c>
       <c r="L22" s="19">
-        <f>'[17]MD10000.20-OCT'!$O$2</f>
+        <f>'[37]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M22" s="19">
-        <f>'[17]MD10000.20-OCT'!$O$1</f>
+        <f>'[37]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -6615,32 +6760,32 @@
         <v>36</v>
       </c>
       <c r="E23" s="19">
-        <f>'[18]MD10000.20-OCT'!$C$1</f>
+        <f>'[38]MD10000.20-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
       <c r="H23" s="20">
-        <f>'[18]MD10000.20-OCT'!$K$1</f>
+        <f>'[38]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I23" s="20">
-        <f>'[18]MD10000.20-OCT'!$K$2</f>
+        <f>'[38]MD10000.20-OCT'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J23" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K23" s="22">
-        <f>'[18]MD10000.20-OCT'!$B$3</f>
+        <f>'[38]MD10000.20-OCT'!$B$3</f>
         <v>45324</v>
       </c>
       <c r="L23" s="19">
-        <f>'[18]MD10000.20-OCT'!$O$2</f>
+        <f>'[38]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M23" s="19">
-        <f>'[18]MD10000.20-OCT'!$O$1</f>
+        <f>'[38]MD10000.20-OCT'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -6655,32 +6800,32 @@
         <v>46</v>
       </c>
       <c r="E24" s="19">
-        <f>'[19]MD10000.20-OCT'!$C$1</f>
+        <f>'[39]MD10000.20-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F24" s="20"/>
       <c r="G24" s="20"/>
       <c r="H24" s="20">
-        <f>'[19]MD10000.20-OCT'!$K$1</f>
+        <f>'[39]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I24" s="20">
-        <f>'[19]MD10000.20-OCT'!$K$2</f>
+        <f>'[39]MD10000.20-OCT'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J24" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K24" s="22">
-        <f>'[19]MD10000.20-OCT'!$B$3</f>
+        <f>'[39]MD10000.20-OCT'!$B$3</f>
         <v>45327</v>
       </c>
       <c r="L24" s="19">
-        <f>'[19]MD10000.20-OCT'!$O$2</f>
+        <f>'[39]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M24" s="19">
-        <f>'[19]MD10000.20-OCT'!$O$1</f>
+        <f>'[39]MD10000.20-OCT'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -6695,15 +6840,15 @@
         <v>18</v>
       </c>
       <c r="E25" s="19">
-        <f>'[20]SM5000.1-oct'!$C$1</f>
+        <f>'[40]SM5000.1-oct'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F25" s="20">
-        <f>'[20]SM5000.1-oct'!$K$1</f>
+        <f>'[40]SM5000.1-oct'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G25" s="20">
-        <f>'[20]SM5000.1-oct'!$K$2</f>
+        <f>'[40]SM5000.1-oct'!$K$2</f>
         <v>60</v>
       </c>
       <c r="H25" s="20"/>
@@ -6712,15 +6857,15 @@
         <v>12</v>
       </c>
       <c r="K25" s="22">
-        <f>'[20]SM5000.1-oct'!$B$3</f>
+        <f>'[40]SM5000.1-oct'!$B$3</f>
         <v>45323</v>
       </c>
       <c r="L25" s="19">
-        <f>'[20]SM5000.1-oct'!$O$2</f>
+        <f>'[40]SM5000.1-oct'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M25" s="19">
-        <f>'[20]SM5000.1-oct'!$O$1</f>
+        <f>'[40]SM5000.1-oct'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -6735,32 +6880,32 @@
         <v>48</v>
       </c>
       <c r="E26" s="19">
-        <f>'[21]MD10000.20-OCT'!$C$1</f>
+        <f>'[41]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F26" s="20"/>
       <c r="G26" s="20"/>
       <c r="H26" s="20">
-        <f>'[21]MD10000.20-OCT'!$K$1</f>
+        <f>'[41]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I26" s="20">
-        <f>'[21]MD10000.20-OCT'!$K$2</f>
+        <f>'[41]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J26" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K26" s="22">
-        <f>'[21]MD10000.20-OCT'!$B$3</f>
+        <f>'[41]MD10000.20-OCT'!$B$3</f>
         <v>45332</v>
       </c>
       <c r="L26" s="19">
-        <f>'[21]MD10000.20-OCT'!$O$2</f>
+        <f>'[41]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M26" s="19">
-        <f>'[21]MD10000.20-OCT'!$O$1</f>
+        <f>'[41]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -6775,15 +6920,15 @@
         <v>19</v>
       </c>
       <c r="E27" s="19">
-        <f>'[22]MD10000.1-OCT'!$C$1</f>
+        <f>'[42]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F27" s="20">
-        <f>'[22]MD10000.1-OCT'!$K$1</f>
+        <f>'[42]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G27" s="20">
-        <f>'[22]MD10000.1-OCT'!$K$2</f>
+        <f>'[42]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H27" s="20"/>
@@ -6792,15 +6937,15 @@
         <v>12</v>
       </c>
       <c r="K27" s="22">
-        <f>'[22]MD10000.1-OCT'!$B$3</f>
+        <f>'[42]MD10000.1-OCT'!$B$3</f>
         <v>45339</v>
       </c>
       <c r="L27" s="19">
-        <f>'[22]MD10000.1-OCT'!$O$2</f>
+        <f>'[42]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M27" s="19">
-        <f>'[22]MD10000.1-OCT'!$O$1</f>
+        <f>'[42]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -6815,15 +6960,15 @@
         <v>19</v>
       </c>
       <c r="E28" s="19">
-        <f>'[23]MD10000.1-OCT'!$C$1</f>
+        <f>'[43]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F28" s="20">
-        <f>'[23]MD10000.1-OCT'!$K$1</f>
+        <f>'[43]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G28" s="20">
-        <f>'[23]MD10000.1-OCT'!$K$2</f>
+        <f>'[43]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H28" s="20"/>
@@ -6832,15 +6977,15 @@
         <v>51</v>
       </c>
       <c r="K28" s="22">
-        <f>'[23]MD10000.1-OCT'!$B$3</f>
+        <f>'[43]MD10000.1-OCT'!$B$3</f>
         <v>45334</v>
       </c>
       <c r="L28" s="19">
-        <f>'[23]MD10000.1-OCT'!$O$2</f>
+        <f>'[43]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M28" s="19">
-        <f>'[23]MD10000.1-OCT'!$O$1</f>
+        <f>'[43]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -6855,32 +7000,32 @@
         <v>50</v>
       </c>
       <c r="E29" s="19">
-        <f>'[24]MD20000.15-DEC'!$C$1</f>
+        <f>'[44]MD20000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
       <c r="H29" s="20">
-        <f>'[24]MD20000.15-DEC'!$K$1</f>
+        <f>'[44]MD20000.15-DEC'!$K$1</f>
         <v>5</v>
       </c>
       <c r="I29" s="20">
-        <f>'[24]MD20000.15-DEC'!$K$2</f>
+        <f>'[44]MD20000.15-DEC'!$K$2</f>
         <v>12</v>
       </c>
       <c r="J29" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K29" s="22">
-        <f>'[24]MD20000.15-DEC'!$B$3</f>
+        <f>'[44]MD20000.15-DEC'!$B$3</f>
         <v>45337</v>
       </c>
       <c r="L29" s="19">
-        <f>'[25]MD20000.15-DEC'!$O$2</f>
+        <f>'[45]MD20000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M29" s="19">
-        <f>'[25]MD20000.15-DEC'!$O$1</f>
+        <f>'[45]MD20000.15-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -6895,32 +7040,32 @@
         <v>52</v>
       </c>
       <c r="E30" s="19">
-        <f>'[26]MD20000.15-DEC'!$C$1</f>
+        <f>'[46]MD20000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F30" s="20"/>
       <c r="G30" s="20"/>
       <c r="H30" s="20">
-        <f>'[26]MD20000.15-DEC'!$K$1</f>
+        <f>'[46]MD20000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I30" s="20">
-        <f>'[26]MD20000.15-DEC'!$K$2</f>
+        <f>'[46]MD20000.15-DEC'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J30" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K30" s="22">
-        <f>'[26]MD20000.15-DEC'!$B$3</f>
+        <f>'[46]MD20000.15-DEC'!$B$3</f>
         <v>45345</v>
       </c>
       <c r="L30" s="19">
-        <f>'[26]MD20000.15-DEC'!$O$2</f>
+        <f>'[46]MD20000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M30" s="19">
-        <f>'[26]MD20000.15-DEC'!$O$1</f>
+        <f>'[46]MD20000.15-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -6935,15 +7080,15 @@
         <v>33</v>
       </c>
       <c r="E31" s="19">
-        <f>'[27]MD20000.18-DEC'!$C$1</f>
+        <f>'[47]MD20000.18-DEC'!$C$1</f>
         <v>30000</v>
       </c>
       <c r="F31" s="20">
-        <f>'[27]MD20000.18-DEC'!$K$1</f>
+        <f>'[47]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G31" s="20">
-        <f>'[27]MD20000.18-DEC'!$K$2</f>
+        <f>'[47]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H31" s="20"/>
@@ -6952,15 +7097,15 @@
         <v>51</v>
       </c>
       <c r="K31" s="22">
-        <f>'[27]MD20000.18-DEC'!$B$3</f>
+        <f>'[47]MD20000.18-DEC'!$B$3</f>
         <v>45354</v>
       </c>
       <c r="L31" s="19">
-        <f>'[27]MD20000.18-DEC'!$O$2</f>
+        <f>'[47]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M31" s="19">
-        <f>'[27]MD20000.18-DEC'!$O$1</f>
+        <f>'[47]MD20000.18-DEC'!$O$1</f>
         <v>36000</v>
       </c>
     </row>
@@ -6975,32 +7120,32 @@
         <v>36</v>
       </c>
       <c r="E32" s="19">
-        <f>'[28]MD10000.10-JAN'!$C$1</f>
+        <f>'[48]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F32" s="20"/>
       <c r="G32" s="20"/>
       <c r="H32" s="20">
-        <f>'[28]MD10000.10-JAN'!$K$1</f>
+        <f>'[48]MD10000.10-JAN'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I32" s="20">
-        <f>'[28]MD10000.10-JAN'!$K$2</f>
+        <f>'[48]MD10000.10-JAN'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J32" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K32" s="22">
-        <f>'[28]MD10000.10-JAN'!$B$3</f>
+        <f>'[48]MD10000.10-JAN'!$B$3</f>
         <v>45366</v>
       </c>
       <c r="L32" s="19">
-        <f>'[28]MD10000.10-JAN'!$O$2</f>
+        <f>'[48]MD10000.10-JAN'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M32" s="19">
-        <f>'[28]MD10000.10-JAN'!$O$1</f>
+        <f>'[48]MD10000.10-JAN'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -7015,32 +7160,32 @@
         <v>52</v>
       </c>
       <c r="E33" s="19">
-        <f>'[29]MD20000.15-DEc'!$C$1</f>
+        <f>'[49]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F33" s="20"/>
       <c r="G33" s="20"/>
       <c r="H33" s="20">
-        <f>'[29]MD20000.15-DEc'!$K$1</f>
+        <f>'[49]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I33" s="20">
-        <f>'[29]MD20000.15-DEc'!$K$2</f>
+        <f>'[49]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J33" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K33" s="22">
-        <f>'[29]MD20000.15-DEc'!$B$3</f>
+        <f>'[49]MD20000.15-DEc'!$B$3</f>
         <v>45380</v>
       </c>
       <c r="L33" s="19">
-        <f>'[29]MD20000.15-DEc'!$O$2</f>
+        <f>'[49]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M33" s="19">
-        <f>'[29]MD20000.15-DEc'!$O$1</f>
+        <f>'[49]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7055,32 +7200,32 @@
         <v>36</v>
       </c>
       <c r="E34" s="19">
-        <f>'[30]MD10000.10-JAN'!$C$1</f>
+        <f>'[50]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F34" s="20"/>
       <c r="G34" s="20"/>
       <c r="H34" s="20">
-        <f>'[30]MD10000.10-JAN'!$K$1</f>
+        <f>'[50]MD10000.10-JAN'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I34" s="20">
-        <f>'[30]MD10000.10-JAN'!$K$2</f>
+        <f>'[50]MD10000.10-JAN'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J34" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K34" s="22">
-        <f>'[30]MD10000.10-JAN'!$B$3</f>
+        <f>'[50]MD10000.10-JAN'!$B$3</f>
         <v>45389</v>
       </c>
       <c r="L34" s="19">
-        <f>'[30]MD10000.10-JAN'!$O$2</f>
+        <f>'[50]MD10000.10-JAN'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M34" s="19">
-        <f>'[30]MD10000.10-JAN'!$O$1</f>
+        <f>'[50]MD10000.10-JAN'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -7095,32 +7240,32 @@
         <v>52</v>
       </c>
       <c r="E35" s="19">
-        <f>'[31]MD20000.15-DEc'!$C$1</f>
+        <f>'[51]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F35" s="20"/>
       <c r="G35" s="20"/>
       <c r="H35" s="20">
-        <f>'[31]MD20000.15-DEc'!$G$1</f>
+        <f>'[51]MD20000.15-DEc'!$G$1</f>
         <v>17</v>
       </c>
       <c r="I35" s="20">
-        <f>'[31]MD20000.15-DEc'!$K$2</f>
+        <f>'[51]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J35" s="21" t="s">
         <v>77</v>
       </c>
       <c r="K35" s="22">
-        <f>'[31]MD20000.15-DEc'!$B$3</f>
+        <f>'[51]MD20000.15-DEc'!$B$3</f>
         <v>45394</v>
       </c>
       <c r="L35" s="19">
-        <f>'[31]MD20000.15-DEc'!$O$2</f>
+        <f>'[51]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M35" s="19">
-        <f>'[31]MD20000.15-DEc'!$O$1</f>
+        <f>'[51]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7135,33 +7280,33 @@
         <v>39</v>
       </c>
       <c r="E36" s="15">
-        <f>'[32]MD10000.10-JAN'!$C$1</f>
+        <f>'[1]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F36" s="13"/>
       <c r="G36" s="13"/>
       <c r="H36" s="13">
-        <f>'[32]MD10000.10-JAN'!$G$1</f>
+        <f>'[1]MD10000.10-JAN'!$G$1</f>
         <v>48</v>
       </c>
       <c r="I36" s="13">
-        <f>'[32]MD10000.10-JAN'!$K$2</f>
-        <v>37</v>
+        <f>'[1]MD10000.10-JAN'!$K$2</f>
+        <v>40</v>
       </c>
       <c r="J36" s="16" t="s">
         <v>12</v>
       </c>
       <c r="K36" s="14">
-        <f>'[32]MD10000.10-JAN'!$B$3</f>
+        <f>'[1]MD10000.10-JAN'!$B$3</f>
         <v>45399</v>
       </c>
       <c r="L36" s="15">
-        <f>'[32]MD10000.10-JAN'!$O$2</f>
-        <v>3850</v>
+        <f>'[1]MD10000.10-JAN'!$O$2</f>
+        <v>2800</v>
       </c>
       <c r="M36" s="15">
-        <f>'[32]MD10000.10-JAN'!$O$1</f>
-        <v>12950</v>
+        <f>'[1]MD10000.10-JAN'!$O$1</f>
+        <v>14000</v>
       </c>
       <c r="N36" s="1">
         <v>350</v>
@@ -7178,32 +7323,32 @@
         <v>52</v>
       </c>
       <c r="E37" s="19">
-        <f>'[33]MD20000.15-DEc'!$C$1</f>
+        <f>'[52]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F37" s="20"/>
       <c r="G37" s="20"/>
       <c r="H37" s="20">
-        <f>'[33]MD20000.15-DEc'!$G$1</f>
+        <f>'[52]MD20000.15-DEc'!$G$1</f>
         <v>17</v>
       </c>
       <c r="I37" s="20">
-        <f>'[33]MD20000.15-DEc'!$K$2</f>
+        <f>'[52]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J37" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K37" s="22">
-        <f>'[33]MD20000.15-DEc'!$B$3</f>
+        <f>'[52]MD20000.15-DEc'!$B$3</f>
         <v>45406</v>
       </c>
       <c r="L37" s="19">
-        <f>'[33]MD20000.15-DEc'!$O$2</f>
+        <f>'[52]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M37" s="19">
-        <f>'[33]MD20000.15-DEc'!$O$1</f>
+        <f>'[52]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7218,32 +7363,32 @@
         <v>60</v>
       </c>
       <c r="E38" s="19">
-        <f>'[34]MD10000.20-OCT'!$C$1</f>
+        <f>'[53]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F38" s="20"/>
       <c r="G38" s="20"/>
       <c r="H38" s="20">
-        <f>'[34]MD10000.20-OCT'!$G$1</f>
+        <f>'[53]MD10000.20-OCT'!$G$1</f>
         <v>17</v>
       </c>
       <c r="I38" s="20">
-        <f>'[34]MD10000.20-OCT'!$K$2</f>
+        <f>'[53]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J38" s="21" t="s">
         <v>77</v>
       </c>
       <c r="K38" s="22">
-        <f>'[34]MD10000.20-OCT'!$B$3</f>
+        <f>'[53]MD10000.20-OCT'!$B$3</f>
         <v>45406</v>
       </c>
       <c r="L38" s="19">
-        <f>'[34]MD10000.20-OCT'!$O$2</f>
+        <f>'[53]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M38" s="19">
-        <f>'[34]MD10000.20-OCT'!$O$1</f>
+        <f>'[53]MD10000.20-OCT'!$O$1</f>
         <v>5950</v>
       </c>
     </row>
@@ -7258,32 +7403,32 @@
         <v>62</v>
       </c>
       <c r="E39" s="19">
-        <f>'[35]MD50000.15-DEC'!$C$1</f>
+        <f>'[54]MD50000.15-DEC'!$C$1</f>
         <v>40000</v>
       </c>
       <c r="F39" s="20"/>
       <c r="G39" s="20"/>
       <c r="H39" s="20">
-        <f>'[35]MD50000.15-DEC'!$K$1</f>
+        <f>'[54]MD50000.15-DEC'!$K$1</f>
         <v>47</v>
       </c>
       <c r="I39" s="20">
-        <f>'[35]MD50000.15-DEC'!$K$2</f>
+        <f>'[54]MD50000.15-DEC'!$K$2</f>
         <v>1</v>
       </c>
       <c r="J39" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K39" s="22">
-        <f>'[35]MD50000.15-DEC'!$B$3</f>
+        <f>'[54]MD50000.15-DEC'!$B$3</f>
         <v>45416</v>
       </c>
       <c r="L39" s="19">
-        <f>'[36]MD50000.15-DEC'!$O$2</f>
+        <f>'[55]MD50000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M39" s="19">
-        <f>'[35]MD50000.15-DEC'!$O$1</f>
+        <f>'[54]MD50000.15-DEC'!$O$1</f>
         <v>1400</v>
       </c>
     </row>
@@ -7298,32 +7443,32 @@
         <v>85</v>
       </c>
       <c r="E40" s="19">
-        <f>'[37]MD10000.20-OCT'!$C$1</f>
+        <f>'[56]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F40" s="20"/>
       <c r="G40" s="20"/>
       <c r="H40" s="20">
-        <f>'[37]MD10000.20-OCT'!$K$1</f>
+        <f>'[56]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I40" s="20">
-        <f>'[37]MD10000.20-OCT'!$K$2</f>
+        <f>'[56]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J40" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K40" s="22">
-        <f>'[37]MD10000.20-OCT'!$B$3</f>
+        <f>'[56]MD10000.20-OCT'!$B$3</f>
         <v>45427</v>
       </c>
       <c r="L40" s="19">
-        <f>'[37]MD10000.20-OCT'!$O$2</f>
+        <f>'[56]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M40" s="19">
-        <f>'[37]MD10000.20-OCT'!$O$1</f>
+        <f>'[56]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -7338,15 +7483,15 @@
         <v>33</v>
       </c>
       <c r="E41" s="19">
-        <f>'[38]MD20000.18-DEC'!$C$1</f>
+        <f>'[57]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F41" s="20">
-        <f>'[38]MD20000.18-DEC'!$K$1</f>
+        <f>'[57]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G41" s="20">
-        <f>'[38]MD20000.18-DEC'!$K$2</f>
+        <f>'[57]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H41" s="20"/>
@@ -7355,15 +7500,15 @@
         <v>77</v>
       </c>
       <c r="K41" s="22">
-        <f>'[38]MD20000.18-DEC'!$B$3</f>
+        <f>'[57]MD20000.18-DEC'!$B$3</f>
         <v>45425</v>
       </c>
       <c r="L41" s="19">
-        <f>'[38]MD20000.18-DEC'!$O$2</f>
+        <f>'[57]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M41" s="19">
-        <f>'[38]MD20000.18-DEC'!$O$1</f>
+        <f>'[57]MD20000.18-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7378,32 +7523,32 @@
         <v>66</v>
       </c>
       <c r="E42" s="19">
-        <f>'[39]MD10000.20-OCT'!$C$1</f>
+        <f>'[58]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F42" s="20"/>
       <c r="G42" s="20"/>
       <c r="H42" s="20">
-        <f>'[39]MD10000.20-OCT'!$K$1</f>
+        <f>'[58]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I42" s="20">
-        <f>'[39]MD10000.20-OCT'!$K$2</f>
+        <f>'[58]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J42" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K42" s="22">
-        <f>'[39]MD10000.20-OCT'!$B$3</f>
+        <f>'[58]MD10000.20-OCT'!$B$3</f>
         <v>45436</v>
       </c>
       <c r="L42" s="19">
-        <f>'[39]MD10000.20-OCT'!$O$2</f>
+        <f>'[58]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M42" s="19">
-        <f>'[39]MD10000.20-OCT'!$O$1</f>
+        <f>'[58]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -7418,15 +7563,15 @@
         <v>33</v>
       </c>
       <c r="E43" s="19">
-        <f>'[40]MD20000.22-DEC'!$C$1</f>
+        <f>'[59]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F43" s="20">
-        <f>'[40]MD20000.22-DEC'!$K$1</f>
+        <f>'[59]MD20000.22-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G43" s="20">
-        <f>'[40]MD20000.22-DEC'!$K$2</f>
+        <f>'[59]MD20000.22-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H43" s="20"/>
@@ -7435,15 +7580,15 @@
         <v>12</v>
       </c>
       <c r="K43" s="22">
-        <f>'[40]MD20000.22-DEC'!$B$3</f>
+        <f>'[59]MD20000.22-DEC'!$B$3</f>
         <v>45432</v>
       </c>
       <c r="L43" s="19">
-        <f>'[40]MD20000.22-DEC'!$O$2</f>
+        <f>'[59]MD20000.22-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M43" s="19">
-        <f>'[40]MD20000.22-DEC'!$O$1</f>
+        <f>'[59]MD20000.22-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7458,15 +7603,15 @@
         <v>68</v>
       </c>
       <c r="E44" s="19">
-        <f>'[41]MD10000.1-OCT'!$C$1</f>
+        <f>'[60]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F44" s="20">
-        <f>'[41]MD10000.1-OCT'!$G$1</f>
+        <f>'[60]MD10000.1-OCT'!$G$1</f>
         <v>120</v>
       </c>
       <c r="G44" s="20">
-        <f>'[41]MD10000.1-OCT'!$K$1</f>
+        <f>'[60]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="H44" s="20"/>
@@ -7475,15 +7620,15 @@
         <v>77</v>
       </c>
       <c r="K44" s="22">
-        <f>'[41]MD10000.1-OCT'!$B$3</f>
+        <f>'[60]MD10000.1-OCT'!$B$3</f>
         <v>45437</v>
       </c>
       <c r="L44" s="19">
-        <f>'[41]MD10000.1-OCT'!$O$2</f>
+        <f>'[60]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M44" s="19">
-        <f>'[41]MD10000.1-OCT'!$O$1</f>
+        <f>'[60]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -7498,29 +7643,29 @@
         <v>48</v>
       </c>
       <c r="E45" s="19">
-        <f>'[42]MD10000.20-OCT'!$C$1</f>
+        <f>'[61]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F45" s="20"/>
       <c r="G45" s="20"/>
       <c r="H45" s="20">
-        <f>'[42]MD10000.20-OCT'!$K$1</f>
+        <f>'[61]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I45" s="20">
-        <f>'[42]MD10000.20-OCT'!$K$2</f>
+        <f>'[61]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J45" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K45" s="22">
-        <f>'[42]MD10000.20-OCT'!$B$3</f>
+        <f>'[61]MD10000.20-OCT'!$B$3</f>
         <v>45444</v>
       </c>
       <c r="L45" s="19"/>
       <c r="M45" s="19">
-        <f>'[42]MD10000.20-OCT'!$O$1</f>
+        <f>'[61]MD10000.20-OCT'!$O$1</f>
         <v>5950</v>
       </c>
     </row>
@@ -7535,32 +7680,32 @@
         <v>71</v>
       </c>
       <c r="E46" s="19">
-        <f>'[43]MD10000.1-OCT'!$C$1</f>
+        <f>'[62]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F46" s="20"/>
       <c r="G46" s="20"/>
       <c r="H46" s="20">
-        <f>'[44]MD10000.1-OCT'!$K$1</f>
+        <f>'[63]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I46" s="20">
-        <f>'[44]MD10000.1-OCT'!$K$2</f>
+        <f>'[63]MD10000.1-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J46" s="21" t="s">
         <v>77</v>
       </c>
       <c r="K46" s="22">
-        <f>'[43]MD10000.1-OCT'!$B$3</f>
+        <f>'[62]MD10000.1-OCT'!$B$3</f>
         <v>45450</v>
       </c>
       <c r="L46" s="19">
-        <f>'[44]MD10000.1-OCT'!$O$2</f>
+        <f>'[63]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M46" s="19">
-        <f>'[44]MD10000.1-OCT'!$O$1</f>
+        <f>'[63]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -7575,15 +7720,15 @@
         <v>33</v>
       </c>
       <c r="E47" s="19">
-        <f>'[45]MD20000.22-DEC'!$C$1</f>
+        <f>'[64]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F47" s="20">
-        <f>'[45]MD20000.22-DEC'!$K$1</f>
+        <f>'[64]MD20000.22-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G47" s="20">
-        <f>'[45]MD20000.22-DEC'!$K$2</f>
+        <f>'[64]MD20000.22-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H47" s="20"/>
@@ -7592,15 +7737,15 @@
         <v>77</v>
       </c>
       <c r="K47" s="22">
-        <f>'[45]MD20000.22-DEC'!$B$3</f>
+        <f>'[64]MD20000.22-DEC'!$B$3</f>
         <v>45446</v>
       </c>
       <c r="L47" s="19">
-        <f>'[45]MD20000.22-DEC'!$O$2</f>
+        <f>'[64]MD20000.22-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M47" s="19">
-        <f>'[45]MD20000.22-DEC'!$O$1</f>
+        <f>'[64]MD20000.22-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7615,15 +7760,15 @@
         <v>68</v>
       </c>
       <c r="E48" s="19">
-        <f>'[46]MD20000.22-DEC'!$C$1</f>
+        <f>'[65]MD20000.22-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F48" s="20">
-        <f>'[46]MD20000.22-DEC'!$K$1</f>
+        <f>'[65]MD20000.22-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G48" s="20">
-        <f>'[46]MD20000.22-DEC'!$K$2</f>
+        <f>'[65]MD20000.22-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H48" s="20"/>
@@ -7632,15 +7777,15 @@
         <v>77</v>
       </c>
       <c r="K48" s="22">
-        <f>'[46]MD20000.22-DEC'!$B$3</f>
+        <f>'[65]MD20000.22-DEC'!$B$3</f>
         <v>45473</v>
       </c>
       <c r="L48" s="19">
-        <f>'[46]MD20000.22-DEC'!$O$2</f>
+        <f>'[65]MD20000.22-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M48" s="19">
-        <f>'[46]MD20000.22-DEC'!$O$1</f>
+        <f>'[65]MD20000.22-DEC'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -7655,32 +7800,32 @@
         <v>50</v>
       </c>
       <c r="E49" s="19">
-        <f>'[47]MD20000.15-DEc'!$C$1</f>
+        <f>'[66]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F49" s="20"/>
       <c r="G49" s="20"/>
       <c r="H49" s="20">
-        <f>'[47]MD20000.15-DEc'!$K$1</f>
+        <f>'[66]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I49" s="20">
-        <f>'[47]MD20000.15-DEc'!$K$2</f>
+        <f>'[66]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J49" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K49" s="22">
-        <f>'[47]MD20000.15-DEc'!$B$3</f>
+        <f>'[66]MD20000.15-DEc'!$B$3</f>
         <v>45495</v>
       </c>
       <c r="L49" s="19">
-        <f>'[47]MD20000.15-DEc'!$O$2</f>
+        <f>'[66]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M49" s="19">
-        <f>'[47]MD20000.15-DEc'!$O$1</f>
+        <f>'[66]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7695,32 +7840,32 @@
         <v>75</v>
       </c>
       <c r="E50" s="19">
-        <f>'[48]MD20000.15-DEc'!$C$1</f>
+        <f>'[67]MD20000.15-DEc'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F50" s="20"/>
       <c r="G50" s="20"/>
       <c r="H50" s="20">
-        <f>'[48]MD20000.15-DEc'!$K$1</f>
+        <f>'[67]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I50" s="20">
-        <f>'[48]MD20000.15-DEc'!$K$2</f>
+        <f>'[67]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J50" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K50" s="22">
-        <f>'[48]MD20000.15-DEc'!$B$3</f>
+        <f>'[67]MD20000.15-DEc'!$B$3</f>
         <v>45496</v>
       </c>
       <c r="L50" s="19">
-        <f>'[48]MD20000.15-DEc'!$O$2</f>
+        <f>'[67]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M50" s="19">
-        <f>'[48]MD20000.15-DEc'!$O$1</f>
+        <f>'[67]MD20000.15-DEc'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -7735,15 +7880,15 @@
         <v>33</v>
       </c>
       <c r="E51" s="19">
-        <f>'[49]MD20000.18-DEC'!$C$1</f>
+        <f>'[68]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F51" s="20">
-        <f>'[49]MD20000.18-DEC'!$K$1</f>
+        <f>'[68]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G51" s="20">
-        <f>'[49]MD20000.18-DEC'!$K$2</f>
+        <f>'[68]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H51" s="20"/>
@@ -7752,15 +7897,15 @@
         <v>12</v>
       </c>
       <c r="K51" s="22">
-        <f>'[49]MD20000.18-DEC'!$B$3</f>
+        <f>'[68]MD20000.18-DEC'!$B$3</f>
         <v>45493</v>
       </c>
       <c r="L51" s="19">
-        <f>'[49]MD20000.18-DEC'!$O$2</f>
+        <f>'[68]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M51" s="19">
-        <f>'[49]MD20000.18-DEC'!$O$1</f>
+        <f>'[68]MD20000.18-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7775,32 +7920,32 @@
         <v>76</v>
       </c>
       <c r="E52" s="19">
-        <f>'[50]MD20000.15-DEc'!$C$1</f>
+        <f>'[69]MD20000.15-DEc'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F52" s="20"/>
       <c r="G52" s="20"/>
       <c r="H52" s="20">
-        <f>'[50]MD20000.15-DEc'!$K$1</f>
+        <f>'[69]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I52" s="20">
-        <f>'[50]MD20000.15-DEc'!$K$2</f>
+        <f>'[69]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J52" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K52" s="22">
-        <f>'[50]MD20000.15-DEc'!$B$3</f>
+        <f>'[69]MD20000.15-DEc'!$B$3</f>
         <v>45502</v>
       </c>
       <c r="L52" s="19">
-        <f>'[50]MD20000.15-DEc'!$O$2</f>
+        <f>'[69]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M52" s="19">
-        <f>'[50]MD20000.15-DEc'!$O$1</f>
+        <f>'[69]MD20000.15-DEc'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -7815,32 +7960,32 @@
         <v>50</v>
       </c>
       <c r="E53" s="19">
-        <f>'[51]MD50000.15-DEC'!$C$1</f>
+        <f>'[70]MD50000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F53" s="20"/>
       <c r="G53" s="20"/>
       <c r="H53" s="20">
-        <f>'[51]MD50000.15-DEC'!$K$1</f>
+        <f>'[70]MD50000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I53" s="20">
-        <f>'[51]MD50000.15-DEC'!$K$2</f>
+        <f>'[70]MD50000.15-DEC'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J53" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K53" s="22">
-        <f>'[51]MD50000.15-DEC'!$B$3</f>
+        <f>'[70]MD50000.15-DEC'!$B$3</f>
         <v>45504</v>
       </c>
       <c r="L53" s="19">
-        <f>'[51]MD50000.15-DEC'!$O$2</f>
+        <f>'[70]MD50000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M53" s="19">
-        <f>'[51]MD50000.15-DEC'!$O$1</f>
+        <f>'[70]MD50000.15-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7855,32 +8000,32 @@
         <v>79</v>
       </c>
       <c r="E54" s="19">
-        <f>'[52]MD10000.20-OCT'!$C$1</f>
+        <f>'[71]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F54" s="20"/>
       <c r="G54" s="20"/>
       <c r="H54" s="20">
-        <f>'[52]MD10000.20-OCT'!$K$1</f>
+        <f>'[71]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I54" s="20">
-        <f>'[52]MD10000.20-OCT'!$K$2</f>
+        <f>'[71]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J54" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K54" s="22">
-        <f>'[52]MD10000.20-OCT'!$B$3</f>
+        <f>'[71]MD10000.20-OCT'!$B$3</f>
         <v>45511</v>
       </c>
       <c r="L54" s="19">
-        <f>'[52]MD10000.20-OCT'!$O$2</f>
+        <f>'[71]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M54" s="19">
-        <f>'[52]MD10000.20-OCT'!$O$1</f>
+        <f>'[71]MD10000.20-OCT'!$O$1</f>
         <v>5950</v>
       </c>
     </row>
@@ -7895,15 +8040,15 @@
         <v>80</v>
       </c>
       <c r="E55" s="19">
-        <f>'[53]MD20000.18-DEC'!$C$1</f>
+        <f>'[72]MD20000.18-DEC'!$C$1</f>
         <v>30000</v>
       </c>
       <c r="F55" s="20">
-        <f>'[53]MD20000.18-DEC'!$K$1</f>
+        <f>'[72]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G55" s="20">
-        <f>'[53]MD20000.18-DEC'!$K$2</f>
+        <f>'[72]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H55" s="20"/>
@@ -7912,15 +8057,15 @@
         <v>51</v>
       </c>
       <c r="K55" s="22">
-        <f>'[53]MD20000.18-DEC'!$B$3</f>
+        <f>'[72]MD20000.18-DEC'!$B$3</f>
         <v>45508</v>
       </c>
       <c r="L55" s="19">
-        <f>'[53]MD20000.18-DEC'!$O$2</f>
+        <f>'[72]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M55" s="19">
-        <f>'[53]MD20000.18-DEC'!$O$1</f>
+        <f>'[72]MD20000.18-DEC'!$O$1</f>
         <v>36000</v>
       </c>
     </row>
@@ -7935,15 +8080,15 @@
         <v>82</v>
       </c>
       <c r="E56" s="19">
-        <f>'[54]MD20000.18-DEC'!$C$1</f>
+        <f>'[73]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F56" s="20">
-        <f>'[54]MD20000.18-DEC'!$K$1</f>
+        <f>'[73]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G56" s="20">
-        <f>'[54]MD20000.18-DEC'!$K$2</f>
+        <f>'[73]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H56" s="20"/>
@@ -7952,15 +8097,15 @@
         <v>12</v>
       </c>
       <c r="K56" s="22">
-        <f>'[54]MD20000.18-DEC'!$B$3</f>
+        <f>'[73]MD20000.18-DEC'!$B$3</f>
         <v>45514</v>
       </c>
       <c r="L56" s="19">
-        <f>'[54]MD20000.18-DEC'!$O$2</f>
+        <f>'[73]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M56" s="19">
-        <f>'[54]MD20000.18-DEC'!$O$1</f>
+        <f>'[73]MD20000.18-DEC'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -7975,32 +8120,32 @@
         <v>52</v>
       </c>
       <c r="E57" s="19">
-        <f>'[55]MD20000.15-DEc'!$C$1</f>
+        <f>'[74]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F57" s="20"/>
       <c r="G57" s="20"/>
       <c r="H57" s="20">
-        <f>'[55]MD20000.15-DEc'!$K$1</f>
+        <f>'[74]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I57" s="20">
-        <f>'[55]MD20000.15-DEc'!$K$2</f>
+        <f>'[74]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J57" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K57" s="22">
-        <f>'[55]MD20000.15-DEc'!$B$3</f>
+        <f>'[74]MD20000.15-DEc'!$B$3</f>
         <v>45527</v>
       </c>
       <c r="L57" s="19">
-        <f>'[55]MD20000.15-DEc'!$O$2</f>
+        <f>'[74]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M57" s="19">
-        <f>'[55]MD20000.15-DEc'!$O$1</f>
+        <f>'[74]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -8015,32 +8160,32 @@
         <v>76</v>
       </c>
       <c r="E58" s="19">
-        <f>'[56]MD20000.15-DEc'!$C$1</f>
+        <f>'[75]MD20000.15-DEc'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F58" s="20"/>
       <c r="G58" s="20"/>
       <c r="H58" s="20">
-        <f>'[56]MD20000.15-DEc'!$K$1</f>
+        <f>'[75]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I58" s="20">
-        <f>'[56]MD20000.15-DEc'!$K$2</f>
+        <f>'[75]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J58" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K58" s="22">
-        <f>'[56]MD20000.15-DEc'!$B$3</f>
+        <f>'[75]MD20000.15-DEc'!$B$3</f>
         <v>45531</v>
       </c>
       <c r="L58" s="19">
-        <f>'[56]MD20000.15-DEc'!$O$2</f>
+        <f>'[75]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M58" s="19">
-        <f>'[56]MD20000.15-DEc'!$O$1</f>
+        <f>'[75]MD20000.15-DEc'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -8055,32 +8200,32 @@
         <v>85</v>
       </c>
       <c r="E59" s="19">
-        <f>'[57]MD10000.20-OCT'!$C$1</f>
+        <f>'[76]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F59" s="20"/>
       <c r="G59" s="20"/>
       <c r="H59" s="20">
-        <f>'[57]MD10000.20-OCT'!$K$1</f>
+        <f>'[76]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I59" s="20">
-        <f>'[57]MD10000.20-OCT'!$K$2</f>
+        <f>'[76]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J59" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K59" s="22">
-        <f>'[57]MD10000.20-OCT'!$B$3</f>
+        <f>'[76]MD10000.20-OCT'!$B$3</f>
         <v>45532</v>
       </c>
       <c r="L59" s="19">
-        <f>'[57]MD10000.20-OCT'!$O$2</f>
+        <f>'[76]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M59" s="19">
-        <f>'[57]MD10000.20-OCT'!$O$1</f>
+        <f>'[76]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -8095,32 +8240,32 @@
         <v>76</v>
       </c>
       <c r="E60" s="19">
-        <f>'[58]MD20000.15-DEc'!$C$1</f>
+        <f>'[77]MD20000.15-DEc'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F60" s="20"/>
       <c r="G60" s="20"/>
       <c r="H60" s="20">
-        <f>'[58]MD20000.15-DEc'!$K$1</f>
+        <f>'[77]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I60" s="20">
-        <f>'[58]MD20000.15-DEc'!$K$2</f>
+        <f>'[77]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J60" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K60" s="22">
-        <f>'[58]MD20000.15-DEc'!$B$3</f>
+        <f>'[77]MD20000.15-DEc'!$B$3</f>
         <v>45534</v>
       </c>
       <c r="L60" s="19">
-        <f>'[58]MD20000.15-DEc'!$O$2</f>
+        <f>'[77]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M60" s="19">
-        <f>'[58]MD20000.15-DEc'!$O$1</f>
+        <f>'[77]MD20000.15-DEc'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -8135,32 +8280,32 @@
         <v>87</v>
       </c>
       <c r="E61" s="19">
-        <f>'[59]MD10000.20-OCT'!$C$1</f>
+        <f>'[78]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F61" s="20"/>
       <c r="G61" s="20"/>
       <c r="H61" s="20">
-        <f>'[59]MD10000.20-OCT'!$K$1</f>
+        <f>'[78]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I61" s="20">
-        <f>'[59]MD10000.20-OCT'!$K$2</f>
+        <f>'[78]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J61" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K61" s="22">
-        <f>'[59]MD10000.20-OCT'!$B$3</f>
+        <f>'[78]MD10000.20-OCT'!$B$3</f>
         <v>45536</v>
       </c>
       <c r="L61" s="19">
-        <f>'[59]MD10000.20-OCT'!$O$2</f>
+        <f>'[78]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M61" s="19">
-        <f>'[59]MD10000.20-OCT'!$O$1</f>
+        <f>'[78]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -8175,15 +8320,15 @@
         <v>33</v>
       </c>
       <c r="E62" s="19">
-        <f>'[60]MD20000.22-DEC'!$C$1</f>
+        <f>'[79]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F62" s="20">
-        <f>'[60]MD20000.22-DEC'!$K$1</f>
+        <f>'[79]MD20000.22-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G62" s="20">
-        <f>'[60]MD20000.22-DEC'!$K$2</f>
+        <f>'[79]MD20000.22-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H62" s="20"/>
@@ -8192,15 +8337,15 @@
         <v>51</v>
       </c>
       <c r="K62" s="22">
-        <f>'[60]MD20000.22-DEC'!$B$3</f>
+        <f>'[79]MD20000.22-DEC'!$B$3</f>
         <v>45535</v>
       </c>
       <c r="L62" s="19">
-        <f>'[60]MD20000.22-DEC'!$O$2</f>
+        <f>'[79]MD20000.22-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M62" s="19">
-        <f>'[60]MD20000.22-DEC'!$O$1</f>
+        <f>'[79]MD20000.22-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -8215,32 +8360,32 @@
         <v>48</v>
       </c>
       <c r="E63" s="19">
-        <f>'[61]MD10000.20-OCT'!$C$1</f>
+        <f>'[80]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F63" s="20"/>
       <c r="G63" s="20"/>
       <c r="H63" s="20">
-        <f>'[61]MD10000.20-OCT'!$K$1</f>
+        <f>'[80]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I63" s="20">
-        <f>'[61]MD10000.20-OCT'!$K$2</f>
+        <f>'[80]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J63" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K63" s="22">
-        <f>'[61]MD10000.20-OCT'!$B$3</f>
+        <f>'[80]MD10000.20-OCT'!$B$3</f>
         <v>45549</v>
       </c>
       <c r="L63" s="19">
-        <f>'[61]MD10000.20-OCT'!$O$2</f>
+        <f>'[80]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M63" s="19">
-        <f>'[61]MD10000.20-OCT'!$O$1</f>
+        <f>'[80]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -8255,15 +8400,15 @@
         <v>90</v>
       </c>
       <c r="E64" s="19">
-        <f>'[62]MD20000.22-DEC'!$C$1</f>
+        <f>'[81]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F64" s="20">
-        <f>'[62]MD20000.22-DEC'!$K$1</f>
+        <f>'[81]MD20000.22-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G64" s="20">
-        <f>'[62]MD20000.22-DEC'!$K$2</f>
+        <f>'[81]MD20000.22-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H64" s="20"/>
@@ -8272,15 +8417,15 @@
         <v>12</v>
       </c>
       <c r="K64" s="22">
-        <f>'[62]MD20000.22-DEC'!$B$13</f>
+        <f>'[81]MD20000.22-DEC'!$B$13</f>
         <v>45562</v>
       </c>
       <c r="L64" s="19">
-        <f>'[62]MD20000.22-DEC'!$O$2</f>
+        <f>'[81]MD20000.22-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M64" s="19">
-        <f>'[62]MD20000.22-DEC'!$O$1</f>
+        <f>'[81]MD20000.22-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -8295,15 +8440,15 @@
         <v>68</v>
       </c>
       <c r="E65" s="19">
-        <f>'[63]MD10000.1-OCT'!$C$1</f>
+        <f>'[82]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F65" s="20">
-        <f>'[63]MD10000.1-OCT'!$K$1</f>
+        <f>'[82]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G65" s="20">
-        <f>'[63]MD10000.1-OCT'!$K$2</f>
+        <f>'[82]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H65" s="20"/>
@@ -8312,15 +8457,15 @@
         <v>12</v>
       </c>
       <c r="K65" s="22">
-        <f>'[63]MD10000.1-OCT'!$B$3</f>
+        <f>'[82]MD10000.1-OCT'!$B$3</f>
         <v>45557</v>
       </c>
       <c r="L65" s="19">
-        <f>'[63]MD10000.1-OCT'!$O$2</f>
+        <f>'[82]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M65" s="19">
-        <f>'[63]MD10000.1-OCT'!$O$1</f>
+        <f>'[82]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -8335,16 +8480,16 @@
         <v>68</v>
       </c>
       <c r="E66" s="7">
-        <f>'[64]MD10000.1-OCT'!$C$1</f>
+        <f>'[2]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F66" s="8">
-        <f>'[64]MD10000.1-OCT'!$K$1</f>
-        <v>28</v>
+        <f>'[2]MD10000.1-OCT'!$K$1</f>
+        <v>22</v>
       </c>
       <c r="G66" s="8">
-        <f>'[64]MD10000.1-OCT'!$K$2</f>
-        <v>92</v>
+        <f>'[2]MD10000.1-OCT'!$K$2</f>
+        <v>98</v>
       </c>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
@@ -8352,16 +8497,16 @@
         <v>12</v>
       </c>
       <c r="K66" s="10">
-        <f>'[64]MD10000.1-OCT'!$B$3</f>
+        <f>'[2]MD10000.1-OCT'!$B$3</f>
         <v>45557</v>
       </c>
       <c r="L66" s="7">
-        <f>'[64]MD10000.1-OCT'!$O$2</f>
-        <v>2800</v>
+        <f>'[2]MD10000.1-OCT'!$O$2</f>
+        <v>2200</v>
       </c>
       <c r="M66" s="7">
-        <f>'[64]MD10000.1-OCT'!$O$1</f>
-        <v>9200</v>
+        <f>'[2]MD10000.1-OCT'!$O$1</f>
+        <v>9800</v>
       </c>
       <c r="N66" s="1">
         <v>700</v>
@@ -8378,16 +8523,16 @@
         <v>68</v>
       </c>
       <c r="E67" s="7">
-        <f>'[65]MD10000.1-OCT'!$C$1</f>
+        <f>'[3]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F67" s="8">
-        <f>'[65]MD10000.1-OCT'!$K$1</f>
-        <v>16</v>
+        <f>'[3]MD10000.1-OCT'!$K$1</f>
+        <v>14</v>
       </c>
       <c r="G67" s="8">
-        <f>'[65]MD10000.1-OCT'!$K$2</f>
-        <v>104</v>
+        <f>'[3]MD10000.1-OCT'!$K$2</f>
+        <v>106</v>
       </c>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
@@ -8395,16 +8540,16 @@
         <v>12</v>
       </c>
       <c r="K67" s="10">
-        <f>'[65]MD10000.1-OCT'!$B$3</f>
+        <f>'[3]MD10000.1-OCT'!$B$3</f>
         <v>45561</v>
       </c>
       <c r="L67" s="7">
-        <f>'[65]MD10000.1-OCT'!$O$2</f>
-        <v>1600</v>
+        <f>'[3]MD10000.1-OCT'!$O$2</f>
+        <v>1400</v>
       </c>
       <c r="M67" s="7">
-        <f>'[65]MD10000.1-OCT'!$O$1</f>
-        <v>10400</v>
+        <f>'[3]MD10000.1-OCT'!$O$1</f>
+        <v>10600</v>
       </c>
       <c r="N67" s="1">
         <v>700</v>
@@ -8421,15 +8566,15 @@
         <v>33</v>
       </c>
       <c r="E68" s="19">
-        <f>'[66]MD20000.18-DEC'!$C$1</f>
+        <f>'[83]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F68" s="20">
-        <f>'[66]MD20000.18-DEC'!$K$1</f>
+        <f>'[83]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G68" s="20">
-        <f>'[66]MD20000.18-DEC'!$K$2</f>
+        <f>'[83]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H68" s="20"/>
@@ -8438,15 +8583,15 @@
         <v>12</v>
       </c>
       <c r="K68" s="22">
-        <f>'[66]MD20000.18-DEC'!$B$3</f>
+        <f>'[83]MD20000.18-DEC'!$B$3</f>
         <v>45562</v>
       </c>
       <c r="L68" s="19">
-        <f>'[66]MD20000.18-DEC'!$O$2</f>
+        <f>'[83]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M68" s="19">
-        <f>'[66]MD20000.18-DEC'!$O$1</f>
+        <f>'[83]MD20000.18-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -8461,16 +8606,16 @@
         <v>68</v>
       </c>
       <c r="E69" s="7">
-        <f>'[67]MD10000.1-OCT'!$C$1</f>
+        <f>'[4]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F69" s="8">
-        <f>'[67]MD10000.1-OCT'!$K$1</f>
-        <v>25</v>
+        <f>'[4]MD10000.1-OCT'!$K$1</f>
+        <v>18</v>
       </c>
       <c r="G69" s="8">
-        <f>'[67]MD10000.1-OCT'!$K$2</f>
-        <v>95</v>
+        <f>'[4]MD10000.1-OCT'!$K$2</f>
+        <v>102</v>
       </c>
       <c r="H69" s="8"/>
       <c r="I69" s="8"/>
@@ -8478,16 +8623,16 @@
         <v>12</v>
       </c>
       <c r="K69" s="10">
-        <f>'[67]MD10000.1-OCT'!$B$3</f>
+        <f>'[4]MD10000.1-OCT'!$B$3</f>
         <v>45563</v>
       </c>
       <c r="L69" s="7">
-        <f>'[67]MD10000.1-OCT'!$O$2</f>
-        <v>2500</v>
+        <f>'[4]MD10000.1-OCT'!$O$2</f>
+        <v>1800</v>
       </c>
       <c r="M69" s="7">
-        <f>'[67]MD10000.1-OCT'!$O$1</f>
-        <v>9500</v>
+        <f>'[4]MD10000.1-OCT'!$O$1</f>
+        <v>10200</v>
       </c>
       <c r="N69" s="1">
         <v>700</v>
@@ -8504,16 +8649,16 @@
         <v>94</v>
       </c>
       <c r="E70" s="7">
-        <f>'[68]MD10000.1-OCT'!$C$1</f>
+        <f>'[5]MD10000.1-OCT'!$C$1</f>
         <v>15000</v>
       </c>
       <c r="F70" s="8">
-        <f>'[68]MD10000.1-OCT'!$K$1</f>
-        <v>53</v>
+        <f>'[5]MD10000.1-OCT'!$K$1</f>
+        <v>47</v>
       </c>
       <c r="G70" s="8">
-        <f>'[68]MD10000.1-OCT'!$K$2</f>
-        <v>67</v>
+        <f>'[5]MD10000.1-OCT'!$K$2</f>
+        <v>73</v>
       </c>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
@@ -8521,16 +8666,16 @@
         <v>12</v>
       </c>
       <c r="K70" s="10">
-        <f>'[68]MD10000.1-OCT'!$B$3</f>
+        <f>'[5]MD10000.1-OCT'!$B$3</f>
         <v>45570</v>
       </c>
       <c r="L70" s="7">
-        <f>'[68]MD10000.1-OCT'!$O$2</f>
-        <v>7950</v>
+        <f>'[5]MD10000.1-OCT'!$O$2</f>
+        <v>7050</v>
       </c>
       <c r="M70" s="7">
-        <f>'[68]MD10000.1-OCT'!$O$1</f>
-        <v>10050</v>
+        <f>'[5]MD10000.1-OCT'!$O$1</f>
+        <v>10950</v>
       </c>
       <c r="N70" s="1">
         <v>1050</v>
@@ -8547,15 +8692,15 @@
         <v>96</v>
       </c>
       <c r="E71" s="26">
-        <f>'[69]MD20000.18-DEC'!$C$1</f>
+        <f>'[84]MD20000.18-DEC'!$C$1</f>
         <v>50000</v>
       </c>
       <c r="F71" s="24">
-        <f>'[69]MD20000.18-DEC'!$K$1</f>
+        <f>'[84]MD20000.18-DEC'!$K$1</f>
         <v>66</v>
       </c>
       <c r="G71" s="24">
-        <f>'[69]MD20000.18-DEC'!$K$2</f>
+        <f>'[84]MD20000.18-DEC'!$K$2</f>
         <v>54</v>
       </c>
       <c r="H71" s="24"/>
@@ -8564,15 +8709,15 @@
         <v>12</v>
       </c>
       <c r="K71" s="25">
-        <f>'[69]MD20000.18-DEC'!$B$3</f>
+        <f>'[84]MD20000.18-DEC'!$B$3</f>
         <v>45579</v>
       </c>
       <c r="L71" s="26">
-        <f>'[69]MD20000.18-DEC'!$O$2</f>
+        <f>'[84]MD20000.18-DEC'!$O$2</f>
         <v>33000</v>
       </c>
       <c r="M71" s="26">
-        <f>'[69]MD20000.18-DEC'!$O$1</f>
+        <f>'[84]MD20000.18-DEC'!$O$1</f>
         <v>27000</v>
       </c>
     </row>
@@ -8587,33 +8732,33 @@
         <v>98</v>
       </c>
       <c r="E72" s="7">
-        <f>'[70]MD20000.18-DEC'!$C$1</f>
+        <f>'[6]MD20000.18-DEC'!$C$1</f>
         <v>100000</v>
       </c>
       <c r="F72" s="8"/>
       <c r="G72" s="8"/>
       <c r="H72" s="8">
-        <f>'[70]MD20000.18-DEC'!$K$1</f>
-        <v>29</v>
+        <f>'[6]MD20000.18-DEC'!$K$1</f>
+        <v>27</v>
       </c>
       <c r="I72" s="8">
-        <f>'[70]MD20000.18-DEC'!$K$2</f>
-        <v>11</v>
+        <f>'[6]MD20000.18-DEC'!$K$2</f>
+        <v>13</v>
       </c>
       <c r="J72" s="9" t="s">
         <v>12</v>
       </c>
       <c r="K72" s="10">
-        <f>'[70]MD20000.18-DEC'!$B$3</f>
+        <f>'[6]MD20000.18-DEC'!$B$3</f>
         <v>45590</v>
       </c>
       <c r="L72" s="7">
-        <f>'[70]MD20000.18-DEC'!$O$2</f>
-        <v>116000</v>
+        <f>'[6]MD20000.18-DEC'!$O$2</f>
+        <v>108000</v>
       </c>
       <c r="M72" s="7">
-        <f>'[70]MD20000.18-DEC'!$O$1</f>
-        <v>44000</v>
+        <f>'[6]MD20000.18-DEC'!$O$1</f>
+        <v>52000</v>
       </c>
       <c r="N72" s="1">
         <v>4000</v>
@@ -8630,15 +8775,15 @@
         <v>96</v>
       </c>
       <c r="E73" s="19">
-        <f>'[71]MD20000.18-DEC'!$C$1</f>
+        <f>'[85]MD20000.18-DEC'!$C$1</f>
         <v>50000</v>
       </c>
       <c r="F73" s="20">
-        <f>'[71]MD20000.18-DEC'!$K$1</f>
+        <f>'[85]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G73" s="20">
-        <f>'[71]MD20000.18-DEC'!$K$2</f>
+        <f>'[85]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H73" s="20"/>
@@ -8647,15 +8792,15 @@
         <v>12</v>
       </c>
       <c r="K73" s="22">
-        <f>'[71]MD20000.18-DEC'!$B$3</f>
+        <f>'[85]MD20000.18-DEC'!$B$3</f>
         <v>45584</v>
       </c>
       <c r="L73" s="19">
-        <f>'[71]MD20000.18-DEC'!$O$2</f>
+        <f>'[85]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M73" s="19">
-        <f>'[71]MD20000.18-DEC'!$O$1</f>
+        <f>'[85]MD20000.18-DEC'!$O$1</f>
         <v>60000</v>
       </c>
     </row>
@@ -8670,15 +8815,15 @@
         <v>90</v>
       </c>
       <c r="E74" s="19">
-        <f>'[72]MD20000.18-DEC'!$C$1</f>
+        <f>'[86]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F74" s="20">
-        <f>'[72]MD20000.18-DEC'!$K$1</f>
+        <f>'[86]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G74" s="20">
-        <f>'[72]MD20000.18-DEC'!$K$2</f>
+        <f>'[86]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H74" s="20"/>
@@ -8687,15 +8832,15 @@
         <v>12</v>
       </c>
       <c r="K74" s="22">
-        <f>'[72]MD20000.18-DEC'!$B$3</f>
+        <f>'[86]MD20000.18-DEC'!$B$3</f>
         <v>45584</v>
       </c>
       <c r="L74" s="19">
-        <f>'[72]MD20000.18-DEC'!$O$2</f>
+        <f>'[86]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M74" s="19">
-        <f>'[72]MD20000.18-DEC'!$O$1</f>
+        <f>'[86]MD20000.18-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -8710,15 +8855,15 @@
         <v>90</v>
       </c>
       <c r="E75" s="7">
-        <f>'[73]MD20000.18-DEC'!$C$1</f>
+        <f>'[7]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F75" s="8">
-        <f>'[73]MD20000.18-DEC'!$K$1</f>
+        <f>'[7]MD20000.18-DEC'!$K$1</f>
         <v>82</v>
       </c>
       <c r="G75" s="8">
-        <f>'[73]MD20000.18-DEC'!$K$2</f>
+        <f>'[7]MD20000.18-DEC'!$K$2</f>
         <v>38</v>
       </c>
       <c r="H75" s="8"/>
@@ -8727,15 +8872,15 @@
         <v>12</v>
       </c>
       <c r="K75" s="10">
-        <f>'[73]MD20000.18-DEC'!$B$3</f>
+        <f>'[7]MD20000.18-DEC'!$B$3</f>
         <v>45584</v>
       </c>
       <c r="L75" s="7">
-        <f>'[73]MD20000.18-DEC'!$O$2</f>
+        <f>'[7]MD20000.18-DEC'!$O$2</f>
         <v>16400</v>
       </c>
       <c r="M75" s="7">
-        <f>'[73]MD20000.18-DEC'!$O$1</f>
+        <f>'[7]MD20000.18-DEC'!$O$1</f>
         <v>7600</v>
       </c>
       <c r="N75" s="1">
@@ -8753,15 +8898,15 @@
         <v>90</v>
       </c>
       <c r="E76" s="19">
-        <f>'[74]MD20000.18-DEC'!$C$1</f>
+        <f>'[87]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F76" s="20">
-        <f>'[74]MD20000.18-DEC'!$K$1</f>
+        <f>'[87]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G76" s="20">
-        <f>'[74]MD20000.18-DEC'!$K$2</f>
+        <f>'[87]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H76" s="20"/>
@@ -8770,15 +8915,15 @@
         <v>12</v>
       </c>
       <c r="K76" s="22">
-        <f>'[74]MD20000.18-DEC'!$B$3</f>
+        <f>'[87]MD20000.18-DEC'!$B$3</f>
         <v>45584</v>
       </c>
       <c r="L76" s="19">
-        <f>'[74]MD20000.18-DEC'!$O$2</f>
+        <f>'[87]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M76" s="19">
-        <f>'[74]MD20000.18-DEC'!$O$1</f>
+        <f>'[87]MD20000.18-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -8793,15 +8938,15 @@
         <v>90</v>
       </c>
       <c r="E77" s="7">
-        <f>'[75]MD20000.18-DEC'!$C$1</f>
+        <f>'[8]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F77" s="8">
-        <f>'[75]MD20000.18-DEC'!$K$1</f>
+        <f>'[8]MD20000.18-DEC'!$K$1</f>
         <v>36</v>
       </c>
       <c r="G77" s="8">
-        <f>'[75]MD20000.18-DEC'!$K$2</f>
+        <f>'[8]MD20000.18-DEC'!$K$2</f>
         <v>84</v>
       </c>
       <c r="H77" s="8"/>
@@ -8810,15 +8955,15 @@
         <v>12</v>
       </c>
       <c r="K77" s="10">
-        <f>'[75]MD20000.18-DEC'!$B$7</f>
+        <f>'[8]MD20000.18-DEC'!$B$7</f>
         <v>45587</v>
       </c>
       <c r="L77" s="7">
-        <f>'[75]MD20000.18-DEC'!$O$2</f>
+        <f>'[8]MD20000.18-DEC'!$O$2</f>
         <v>7200</v>
       </c>
       <c r="M77" s="7">
-        <f>'[75]MD20000.18-DEC'!$O$1</f>
+        <f>'[8]MD20000.18-DEC'!$O$1</f>
         <v>16800</v>
       </c>
       <c r="N77" s="1">
@@ -8836,16 +8981,16 @@
         <v>68</v>
       </c>
       <c r="E78" s="7">
-        <f>'[76]MD20000.18-DEC'!$C$1</f>
+        <f>'[9]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F78" s="8">
-        <f>'[76]MD20000.18-DEC'!$K$1</f>
-        <v>104</v>
+        <f>'[9]MD20000.18-DEC'!$K$1</f>
+        <v>94</v>
       </c>
       <c r="G78" s="8">
-        <f>'[76]MD20000.18-DEC'!$K$2</f>
-        <v>16</v>
+        <f>'[9]MD20000.18-DEC'!$K$2</f>
+        <v>26</v>
       </c>
       <c r="H78" s="8"/>
       <c r="I78" s="8"/>
@@ -8853,16 +8998,16 @@
         <v>12</v>
       </c>
       <c r="K78" s="10">
-        <f>'[76]MD20000.18-DEC'!$B$3</f>
+        <f>'[9]MD20000.18-DEC'!$B$3</f>
         <v>45584</v>
       </c>
       <c r="L78" s="7">
-        <f>'[76]MD20000.18-DEC'!$O$2</f>
-        <v>10400</v>
+        <f>'[9]MD20000.18-DEC'!$O$2</f>
+        <v>9400</v>
       </c>
       <c r="M78" s="7">
-        <f>'[76]MD20000.18-DEC'!$O$1</f>
-        <v>1600</v>
+        <f>'[9]MD20000.18-DEC'!$O$1</f>
+        <v>2600</v>
       </c>
       <c r="N78" s="1">
         <v>700</v>
@@ -8879,15 +9024,15 @@
         <v>68</v>
       </c>
       <c r="E79" s="7">
-        <f>'[77]MD20000.18-DEC'!$C$1</f>
+        <f>'[10]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F79" s="8">
-        <f>'[77]MD20000.18-DEC'!$K$1</f>
+        <f>'[10]MD20000.18-DEC'!$K$1</f>
         <v>75</v>
       </c>
       <c r="G79" s="8">
-        <f>'[77]MD20000.18-DEC'!$K$2</f>
+        <f>'[10]MD20000.18-DEC'!$K$2</f>
         <v>45</v>
       </c>
       <c r="H79" s="8"/>
@@ -8896,15 +9041,15 @@
         <v>12</v>
       </c>
       <c r="K79" s="10">
-        <f>'[77]MD20000.18-DEC'!$B$3</f>
+        <f>'[10]MD20000.18-DEC'!$B$3</f>
         <v>45584</v>
       </c>
       <c r="L79" s="7">
-        <f>'[77]MD20000.18-DEC'!$O$2</f>
+        <f>'[10]MD20000.18-DEC'!$O$2</f>
         <v>7500</v>
       </c>
       <c r="M79" s="7">
-        <f>'[77]MD20000.18-DEC'!$O$1</f>
+        <f>'[10]MD20000.18-DEC'!$O$1</f>
         <v>4500</v>
       </c>
       <c r="N79" s="1">
@@ -8922,15 +9067,15 @@
         <v>68</v>
       </c>
       <c r="E80" s="19">
-        <f>'[78]MD20000.18-DEC'!$C$1</f>
+        <f>'[88]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F80" s="20">
-        <f>'[78]MD20000.18-DEC'!$K$1</f>
+        <f>'[88]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G80" s="20">
-        <f>'[78]MD20000.18-DEC'!$K$2</f>
+        <f>'[88]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H80" s="20"/>
@@ -8939,15 +9084,15 @@
         <v>12</v>
       </c>
       <c r="K80" s="22">
-        <f>'[78]MD20000.18-DEC'!$B$3</f>
+        <f>'[88]MD20000.18-DEC'!$B$3</f>
         <v>45587</v>
       </c>
       <c r="L80" s="19">
-        <f>'[78]MD20000.18-DEC'!$O$2</f>
+        <f>'[88]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M80" s="19">
-        <f>'[78]MD20000.18-DEC'!$O$1</f>
+        <f>'[88]MD20000.18-DEC'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -8962,33 +9107,33 @@
         <v>52</v>
       </c>
       <c r="E81" s="7">
-        <f>'[79]MD20000.15-DEc'!$C$1</f>
+        <f>'[11]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F81" s="8"/>
       <c r="G81" s="8"/>
       <c r="H81" s="8">
-        <f>'[79]MD20000.15-DEc'!$K$1</f>
-        <v>7</v>
+        <f>'[11]MD20000.15-DEc'!$K$1</f>
+        <v>5</v>
       </c>
       <c r="I81" s="8">
-        <f>'[79]MD20000.15-DEc'!$K$2</f>
-        <v>10</v>
+        <f>'[11]MD20000.15-DEc'!$K$2</f>
+        <v>12</v>
       </c>
       <c r="J81" s="9" t="s">
         <v>12</v>
       </c>
       <c r="K81" s="10">
-        <f>'[79]MD20000.15-DEc'!$B$3</f>
+        <f>'[11]MD20000.15-DEc'!$B$3</f>
         <v>45595</v>
       </c>
       <c r="L81" s="7">
-        <f>'[79]MD20000.15-DEc'!$O$2</f>
-        <v>9800</v>
+        <f>'[11]MD20000.15-DEc'!$O$2</f>
+        <v>7000</v>
       </c>
       <c r="M81" s="7">
-        <f>'[79]MD20000.15-DEc'!$O$1</f>
-        <v>14200</v>
+        <f>'[11]MD20000.15-DEc'!$O$1</f>
+        <v>17000</v>
       </c>
       <c r="N81" s="1">
         <v>1400</v>
@@ -9005,33 +9150,33 @@
         <v>106</v>
       </c>
       <c r="E82" s="7">
-        <f>'[80]MD10000.10-JAN'!$C$1</f>
+        <f>'[12]MD10000.10-JAN'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F82" s="8"/>
       <c r="G82" s="8"/>
       <c r="H82" s="8">
-        <f>'[80]MD10000.10-JAN'!$K$1</f>
-        <v>8</v>
+        <f>'[12]MD10000.10-JAN'!$K$1</f>
+        <v>6</v>
       </c>
       <c r="I82" s="8">
-        <f>'[80]MD10000.10-JAN'!$K$2</f>
-        <v>9</v>
+        <f>'[12]MD10000.10-JAN'!$K$2</f>
+        <v>11</v>
       </c>
       <c r="J82" s="9" t="s">
         <v>12</v>
       </c>
       <c r="K82" s="10">
-        <f>'[80]MD10000.10-JAN'!$B$3</f>
+        <f>'[12]MD10000.10-JAN'!$B$3</f>
         <v>45602</v>
       </c>
       <c r="L82" s="7">
-        <f>'[80]MD10000.10-JAN'!$O$2</f>
-        <v>11200</v>
+        <f>'[12]MD10000.10-JAN'!$O$2</f>
+        <v>8400</v>
       </c>
       <c r="M82" s="7">
-        <f>'[80]MD10000.10-JAN'!$O$1</f>
-        <v>12800</v>
+        <f>'[12]MD10000.10-JAN'!$O$1</f>
+        <v>15600</v>
       </c>
       <c r="N82" s="1">
         <v>1400</v>
@@ -9048,15 +9193,15 @@
         <v>90</v>
       </c>
       <c r="E83" s="19">
-        <f>'[81]MD20000.22-DEC'!$C$1</f>
+        <f>'[89]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F83" s="20">
-        <f>'[81]MD20000.22-DEC'!$K$1</f>
+        <f>'[89]MD20000.22-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G83" s="20">
-        <f>'[81]MD20000.22-DEC'!$K$2</f>
+        <f>'[89]MD20000.22-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H83" s="20"/>
@@ -9065,15 +9210,15 @@
         <v>12</v>
       </c>
       <c r="K83" s="22">
-        <f>'[81]MD20000.22-DEC'!$B$3</f>
+        <f>'[89]MD20000.22-DEC'!$B$3</f>
         <v>45597</v>
       </c>
       <c r="L83" s="19">
-        <f>'[81]MD20000.22-DEC'!$O$2</f>
+        <f>'[89]MD20000.22-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M83" s="19">
-        <f>'[81]MD20000.22-DEC'!$O$1</f>
+        <f>'[89]MD20000.22-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -9088,15 +9233,15 @@
         <v>80</v>
       </c>
       <c r="E84" s="19">
-        <f>'[82]MD20000.18-DEC'!$C$1</f>
+        <f>'[90]MD20000.18-DEC'!$C$1</f>
         <v>30000</v>
       </c>
       <c r="F84" s="20">
-        <f>'[82]MD20000.18-DEC'!$K$1</f>
+        <f>'[90]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G84" s="20">
-        <f>'[82]MD20000.18-DEC'!$K$2</f>
+        <f>'[90]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H84" s="20"/>
@@ -9105,15 +9250,15 @@
         <v>12</v>
       </c>
       <c r="K84" s="22">
-        <f>'[82]MD20000.18-DEC'!$B$3</f>
+        <f>'[90]MD20000.18-DEC'!$B$3</f>
         <v>45602</v>
       </c>
       <c r="L84" s="19">
-        <f>'[82]MD20000.18-DEC'!$O$2</f>
+        <f>'[90]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M84" s="19">
-        <f>'[82]MD20000.18-DEC'!$O$1</f>
+        <f>'[90]MD20000.18-DEC'!$O$1</f>
         <v>36000</v>
       </c>
     </row>
@@ -9128,15 +9273,15 @@
         <v>109</v>
       </c>
       <c r="E85" s="26">
-        <f>'[83]MD20000.18-DEC'!$C$1</f>
+        <f>'[91]MD20000.18-DEC'!$C$1</f>
         <v>50000</v>
       </c>
       <c r="F85" s="24">
-        <f>'[83]MD20000.18-DEC'!$K$1</f>
+        <f>'[91]MD20000.18-DEC'!$K$1</f>
         <v>100</v>
       </c>
       <c r="G85" s="24">
-        <f>'[83]MD20000.18-DEC'!$K$2</f>
+        <f>'[91]MD20000.18-DEC'!$K$2</f>
         <v>20</v>
       </c>
       <c r="H85" s="24"/>
@@ -9145,15 +9290,15 @@
         <v>12</v>
       </c>
       <c r="K85" s="25">
-        <f>'[83]MD20000.18-DEC'!$B$3</f>
+        <f>'[91]MD20000.18-DEC'!$B$3</f>
         <v>45612</v>
       </c>
       <c r="L85" s="26">
-        <f>'[83]MD20000.18-DEC'!$O$2</f>
+        <f>'[91]MD20000.18-DEC'!$O$2</f>
         <v>50000</v>
       </c>
       <c r="M85" s="26">
-        <f>'[83]MD20000.18-DEC'!$O$1</f>
+        <f>'[91]MD20000.18-DEC'!$O$1</f>
         <v>10000</v>
       </c>
     </row>
@@ -9168,16 +9313,16 @@
         <v>68</v>
       </c>
       <c r="E86" s="7">
-        <f>'[84]MD20000.18-DEC'!$C$1</f>
+        <f>'[13]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F86" s="8">
-        <f>'[84]MD20000.18-DEC'!$K$1</f>
-        <v>77</v>
+        <f>'[13]MD20000.18-DEC'!$K$1</f>
+        <v>58</v>
       </c>
       <c r="G86" s="8">
-        <f>'[84]MD20000.18-DEC'!$K$2</f>
-        <v>43</v>
+        <f>'[13]MD20000.18-DEC'!$K$2</f>
+        <v>62</v>
       </c>
       <c r="H86" s="8"/>
       <c r="I86" s="8"/>
@@ -9185,16 +9330,16 @@
         <v>12</v>
       </c>
       <c r="K86" s="10">
-        <f>'[84]MD20000.18-DEC'!$B$3</f>
+        <f>'[13]MD20000.18-DEC'!$B$3</f>
         <v>45612</v>
       </c>
       <c r="L86" s="7">
-        <f>'[84]MD20000.18-DEC'!$O$2</f>
-        <v>7700</v>
+        <f>'[13]MD20000.18-DEC'!$O$2</f>
+        <v>5800</v>
       </c>
       <c r="M86" s="7">
-        <f>'[84]MD20000.18-DEC'!$O$1</f>
-        <v>4300</v>
+        <f>'[13]MD20000.18-DEC'!$O$1</f>
+        <v>6200</v>
       </c>
       <c r="N86" s="1">
         <v>700</v>
@@ -9211,16 +9356,16 @@
         <v>111</v>
       </c>
       <c r="E87" s="7">
-        <f>'[85]MD50000.15-DEC'!$C$1</f>
+        <f>'[14]MD50000.15-DEC'!$C$1</f>
         <v>100000</v>
       </c>
       <c r="F87" s="8">
-        <f>'[85]MD50000.15-DEC'!$K$1</f>
-        <v>233</v>
+        <f>'[14]MD50000.15-DEC'!$K$1</f>
+        <v>228</v>
       </c>
       <c r="G87" s="8">
-        <f>'[85]MD50000.15-DEC'!$K$2</f>
-        <v>34</v>
+        <f>'[14]MD50000.15-DEC'!$K$2</f>
+        <v>39</v>
       </c>
       <c r="H87" s="8"/>
       <c r="I87" s="8"/>
@@ -9228,16 +9373,16 @@
         <v>12</v>
       </c>
       <c r="K87" s="10">
-        <f>'[85]MD50000.15-DEC'!$B$3</f>
+        <f>'[14]MD50000.15-DEC'!$B$3</f>
         <v>45619</v>
       </c>
       <c r="L87" s="7">
-        <f>'[85]MD50000.15-DEC'!$O$2</f>
-        <v>139800</v>
+        <f>'[14]MD50000.15-DEC'!$O$2</f>
+        <v>136800</v>
       </c>
       <c r="M87" s="7">
-        <f>'[85]MD50000.15-DEC'!$O$1</f>
-        <v>20400</v>
+        <f>'[14]MD50000.15-DEC'!$O$1</f>
+        <v>23400</v>
       </c>
       <c r="N87" s="1">
         <v>4200</v>
@@ -9254,16 +9399,16 @@
         <v>96</v>
       </c>
       <c r="E88" s="7">
-        <f>'[86]MD20000.18-DEC'!$C$1</f>
+        <f>'[15]MD20000.18-DEC'!$C$1</f>
         <v>50000</v>
       </c>
       <c r="F88" s="8">
-        <f>'[86]MD20000.18-DEC'!$K$1</f>
-        <v>80</v>
+        <f>'[15]MD20000.18-DEC'!$K$1</f>
+        <v>74</v>
       </c>
       <c r="G88" s="8">
-        <f>'[86]MD20000.18-DEC'!$K$2</f>
-        <v>40</v>
+        <f>'[15]MD20000.18-DEC'!$K$2</f>
+        <v>46</v>
       </c>
       <c r="H88" s="8"/>
       <c r="I88" s="8"/>
@@ -9271,16 +9416,16 @@
         <v>12</v>
       </c>
       <c r="K88" s="10">
-        <f>'[86]MD20000.18-DEC'!$B$3</f>
+        <f>'[15]MD20000.18-DEC'!$B$3</f>
         <v>45628</v>
       </c>
       <c r="L88" s="7">
-        <f>'[86]MD20000.18-DEC'!$O$2</f>
-        <v>40000</v>
+        <f>'[15]MD20000.18-DEC'!$O$2</f>
+        <v>37000</v>
       </c>
       <c r="M88" s="7">
-        <f>'[86]MD20000.18-DEC'!$O$1</f>
-        <v>20000</v>
+        <f>'[15]MD20000.18-DEC'!$O$1</f>
+        <v>23000</v>
       </c>
       <c r="N88" s="1">
         <v>3500</v>
@@ -9297,15 +9442,15 @@
         <v>80</v>
       </c>
       <c r="E89" s="19">
-        <f>'[87]MD20000.18-DEC'!$C$1</f>
+        <f>'[92]MD20000.18-DEC'!$C$1</f>
         <v>30000</v>
       </c>
       <c r="F89" s="20">
-        <f>'[87]MD20000.18-DEC'!$K$1</f>
+        <f>'[92]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G89" s="20">
-        <f>'[87]MD20000.18-DEC'!$K$2</f>
+        <f>'[92]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H89" s="20"/>
@@ -9314,15 +9459,15 @@
         <v>12</v>
       </c>
       <c r="K89" s="22">
-        <f>'[87]MD20000.18-DEC'!$B$3</f>
+        <f>'[92]MD20000.18-DEC'!$B$3</f>
         <v>45647</v>
       </c>
       <c r="L89" s="19">
-        <f>'[87]MD20000.18-DEC'!$O$2</f>
+        <f>'[92]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M89" s="19">
-        <f>'[87]MD20000.18-DEC'!$O$1</f>
+        <f>'[92]MD20000.18-DEC'!$O$1</f>
         <v>36000</v>
       </c>
     </row>
@@ -9337,16 +9482,16 @@
         <v>68</v>
       </c>
       <c r="E90" s="7">
-        <f>'[88]MD20000.18-DEC'!$C$1</f>
+        <f>'[16]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F90" s="8">
-        <f>'[88]MD20000.18-DEC'!$K$1</f>
-        <v>99</v>
+        <f>'[16]MD20000.18-DEC'!$K$1</f>
+        <v>79</v>
       </c>
       <c r="G90" s="8">
-        <f>'[88]MD20000.18-DEC'!$K$2</f>
-        <v>21</v>
+        <f>'[16]MD20000.18-DEC'!$K$2</f>
+        <v>41</v>
       </c>
       <c r="H90" s="8"/>
       <c r="I90" s="8"/>
@@ -9354,16 +9499,16 @@
         <v>12</v>
       </c>
       <c r="K90" s="10">
-        <f>'[88]MD20000.18-DEC'!$B$3</f>
+        <f>'[16]MD20000.18-DEC'!$B$3</f>
         <v>45635</v>
       </c>
       <c r="L90" s="7">
-        <f>'[88]MD20000.18-DEC'!$O$2</f>
-        <v>9900</v>
+        <f>'[16]MD20000.18-DEC'!$O$2</f>
+        <v>7900</v>
       </c>
       <c r="M90" s="7">
-        <f>'[88]MD20000.18-DEC'!$O$1</f>
-        <v>2100</v>
+        <f>'[16]MD20000.18-DEC'!$O$1</f>
+        <v>4100</v>
       </c>
       <c r="N90" s="1">
         <v>700</v>
@@ -9380,16 +9525,16 @@
         <v>68</v>
       </c>
       <c r="E91" s="7">
-        <f>'[89]MD20000.18-DEC'!$C$1</f>
+        <f>'[17]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F91" s="8">
-        <f>'[89]MD20000.18-DEC'!$K$1</f>
-        <v>99</v>
+        <f>'[17]MD20000.18-DEC'!$K$1</f>
+        <v>79</v>
       </c>
       <c r="G91" s="8">
-        <f>'[89]MD20000.18-DEC'!$K$2</f>
-        <v>21</v>
+        <f>'[17]MD20000.18-DEC'!$K$2</f>
+        <v>41</v>
       </c>
       <c r="H91" s="8"/>
       <c r="I91" s="8"/>
@@ -9397,16 +9542,16 @@
         <v>12</v>
       </c>
       <c r="K91" s="10">
-        <f>'[89]MD20000.18-DEC'!$B$3</f>
+        <f>'[17]MD20000.18-DEC'!$B$3</f>
         <v>45635</v>
       </c>
       <c r="L91" s="7">
-        <f>'[89]MD20000.18-DEC'!$O$2</f>
-        <v>9900</v>
+        <f>'[17]MD20000.18-DEC'!$O$2</f>
+        <v>7900</v>
       </c>
       <c r="M91" s="7">
-        <f>'[89]MD20000.18-DEC'!$O$1</f>
-        <v>2100</v>
+        <f>'[17]MD20000.18-DEC'!$O$1</f>
+        <v>4100</v>
       </c>
       <c r="N91" s="1">
         <v>700</v>
@@ -9423,16 +9568,16 @@
         <v>117</v>
       </c>
       <c r="E92" s="7">
-        <f>'[90]MD50000.15-DEC'!$C$1</f>
+        <f>'[18]MD50000.15-DEC'!$C$1</f>
         <v>200000</v>
       </c>
       <c r="F92" s="8">
-        <f>'[90]MD50000.15-DEC'!$K$1</f>
-        <v>253</v>
+        <f>'[18]MD50000.15-DEC'!$K$1</f>
+        <v>250</v>
       </c>
       <c r="G92" s="8">
-        <f>'[90]MD50000.15-DEC'!$K$2</f>
-        <v>14</v>
+        <f>'[18]MD50000.15-DEC'!$K$2</f>
+        <v>17</v>
       </c>
       <c r="H92" s="8"/>
       <c r="I92" s="8"/>
@@ -9440,16 +9585,16 @@
         <v>12</v>
       </c>
       <c r="K92" s="10">
-        <f>'[90]MD50000.15-DEC'!$B$3</f>
+        <f>'[18]MD50000.15-DEC'!$B$3</f>
         <v>45648</v>
       </c>
       <c r="L92" s="7">
-        <f>'[90]MD50000.15-DEC'!$O$2</f>
-        <v>303600</v>
+        <f>'[18]MD50000.15-DEC'!$O$2</f>
+        <v>300000</v>
       </c>
       <c r="M92" s="7">
-        <f>'[90]MD50000.15-DEC'!$O$1</f>
-        <v>16800</v>
+        <f>'[18]MD50000.15-DEC'!$O$1</f>
+        <v>20400</v>
       </c>
       <c r="N92" s="1">
         <v>8400</v>
@@ -9466,32 +9611,32 @@
         <v>119</v>
       </c>
       <c r="E93" s="7">
-        <f>'[91]MD20000.15-DEc'!$C$1</f>
+        <f>'[19]MD20000.15-DEc'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F93" s="8"/>
       <c r="G93" s="8"/>
       <c r="H93" s="8">
-        <f>'[91]MD20000.15-DEc'!$K$1</f>
+        <f>'[19]MD20000.15-DEc'!$K$1</f>
         <v>14</v>
       </c>
       <c r="I93" s="8">
-        <f>'[91]MD20000.15-DEc'!$K$2</f>
+        <f>'[19]MD20000.15-DEc'!$K$2</f>
         <v>3</v>
       </c>
       <c r="J93" s="9" t="s">
         <v>12</v>
       </c>
       <c r="K93" s="10">
-        <f>'[91]MD20000.15-DEc'!$B$3</f>
+        <f>'[19]MD20000.15-DEc'!$B$3</f>
         <v>45649</v>
       </c>
       <c r="L93" s="7">
-        <f>'[91]MD20000.15-DEc'!$O$2</f>
+        <f>'[19]MD20000.15-DEc'!$O$2</f>
         <v>9900</v>
       </c>
       <c r="M93" s="7">
-        <f>'[91]MD20000.15-DEc'!$O$1</f>
+        <f>'[19]MD20000.15-DEc'!$O$1</f>
         <v>2100</v>
       </c>
       <c r="N93" s="1">
@@ -9509,16 +9654,16 @@
         <v>96</v>
       </c>
       <c r="E94" s="7">
-        <f>'[92]MD50000.15-DEC'!$C$1</f>
+        <f>'[20]MD50000.15-DEC'!$C$1</f>
         <v>50000</v>
       </c>
       <c r="F94" s="8">
-        <f>'[92]MD50000.15-DEC'!$K$1</f>
-        <v>107</v>
+        <f>'[20]MD50000.15-DEC'!$K$1</f>
+        <v>104</v>
       </c>
       <c r="G94" s="8">
-        <f>'[92]MD50000.15-DEC'!$K$2</f>
-        <v>13</v>
+        <f>'[20]MD50000.15-DEC'!$K$2</f>
+        <v>16</v>
       </c>
       <c r="H94" s="8"/>
       <c r="I94" s="8"/>
@@ -9526,16 +9671,16 @@
         <v>12</v>
       </c>
       <c r="K94" s="10">
-        <f>'[92]MD50000.15-DEC'!$B$3</f>
+        <f>'[20]MD50000.15-DEC'!$B$3</f>
         <v>45652</v>
       </c>
       <c r="L94" s="7">
-        <f>'[92]MD50000.15-DEC'!$O$2</f>
-        <v>53500</v>
+        <f>'[20]MD50000.15-DEC'!$O$2</f>
+        <v>52000</v>
       </c>
       <c r="M94" s="7">
-        <f>'[92]MD50000.15-DEC'!$O$1</f>
-        <v>6500</v>
+        <f>'[20]MD50000.15-DEC'!$O$1</f>
+        <v>8000</v>
       </c>
       <c r="N94" s="1">
         <v>3500</v>

--- a/LoanOfficer-A/LoanBook.xlsx
+++ b/LoanOfficer-A/LoanBook.xlsx
@@ -105,13 +105,17 @@
     <externalReference r:id="rId94"/>
     <externalReference r:id="rId95"/>
     <externalReference r:id="rId96"/>
+    <externalReference r:id="rId97"/>
+    <externalReference r:id="rId98"/>
+    <externalReference r:id="rId99"/>
+    <externalReference r:id="rId100"/>
   </externalReferences>
   <calcPr calcId="145621" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="129">
   <si>
     <t>Code</t>
   </si>
@@ -489,6 +493,15 @@
   </si>
   <si>
     <t>active</t>
+  </si>
+  <si>
+    <t>angom Joychandra</t>
+  </si>
+  <si>
+    <t>kh bidyakumar</t>
+  </si>
+  <si>
+    <t>L35000p120</t>
   </si>
 </sst>
 </file>
@@ -645,7 +658,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -747,6 +760,7 @@
     <xf numFmtId="165" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -794,15 +808,15 @@
             <v>48</v>
           </cell>
           <cell r="O1">
-            <v>14000</v>
+            <v>14700</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>40</v>
+            <v>42</v>
           </cell>
           <cell r="O2">
-            <v>2800</v>
+            <v>2100</v>
           </cell>
         </row>
         <row r="3">
@@ -825,25 +839,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>75</v>
+            <v>68</v>
           </cell>
           <cell r="O1">
-            <v>4500</v>
+            <v>5200</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>45</v>
+            <v>52</v>
           </cell>
           <cell r="O2">
-            <v>7500</v>
+            <v>6800</v>
           </cell>
         </row>
         <row r="3">
@@ -873,18 +887,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>5</v>
+            <v>2</v>
           </cell>
           <cell r="O1">
-            <v>17000</v>
+            <v>21200</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>12</v>
+            <v>15</v>
           </cell>
           <cell r="O2">
-            <v>7000</v>
+            <v>2800</v>
           </cell>
         </row>
         <row r="3">
@@ -915,18 +929,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>6</v>
+            <v>4</v>
           </cell>
           <cell r="O1">
-            <v>15600</v>
+            <v>18400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>11</v>
+            <v>13</v>
           </cell>
           <cell r="O2">
-            <v>8400</v>
+            <v>5600</v>
           </cell>
         </row>
         <row r="3">
@@ -956,18 +970,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>58</v>
+            <v>41</v>
           </cell>
           <cell r="O1">
-            <v>6200</v>
+            <v>7900</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>62</v>
+            <v>79</v>
           </cell>
           <cell r="O2">
-            <v>5800</v>
+            <v>4100</v>
           </cell>
         </row>
         <row r="3">
@@ -997,18 +1011,18 @@
             <v>100000</v>
           </cell>
           <cell r="K1">
-            <v>228</v>
+            <v>219</v>
           </cell>
           <cell r="O1">
-            <v>23400</v>
+            <v>28800</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>39</v>
+            <v>48</v>
           </cell>
           <cell r="O2">
-            <v>136800</v>
+            <v>131400</v>
           </cell>
         </row>
         <row r="3">
@@ -1038,18 +1052,18 @@
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>74</v>
+            <v>54</v>
           </cell>
           <cell r="O1">
-            <v>23000</v>
+            <v>33000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>46</v>
+            <v>66</v>
           </cell>
           <cell r="O2">
-            <v>37000</v>
+            <v>27000</v>
           </cell>
         </row>
         <row r="3">
@@ -1078,18 +1092,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>79</v>
+            <v>63</v>
           </cell>
           <cell r="O1">
-            <v>4100</v>
+            <v>5700</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>41</v>
+            <v>57</v>
           </cell>
           <cell r="O2">
-            <v>7900</v>
+            <v>6300</v>
           </cell>
         </row>
         <row r="3">
@@ -1118,18 +1132,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>79</v>
+            <v>63</v>
           </cell>
           <cell r="O1">
-            <v>4100</v>
+            <v>5700</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>41</v>
+            <v>57</v>
           </cell>
           <cell r="O2">
-            <v>7900</v>
+            <v>6300</v>
           </cell>
         </row>
         <row r="3">
@@ -1159,18 +1173,18 @@
             <v>200000</v>
           </cell>
           <cell r="K1">
-            <v>250</v>
+            <v>230</v>
           </cell>
           <cell r="O1">
-            <v>20400</v>
+            <v>44400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>17</v>
+            <v>37</v>
           </cell>
           <cell r="O2">
-            <v>300000</v>
+            <v>276000</v>
           </cell>
         </row>
         <row r="3">
@@ -1194,25 +1208,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>14</v>
+            <v>9</v>
           </cell>
           <cell r="O1">
-            <v>2100</v>
+            <v>5600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>3</v>
+            <v>8</v>
           </cell>
           <cell r="O2">
-            <v>9900</v>
+            <v>6400</v>
           </cell>
         </row>
         <row r="3">
@@ -1221,7 +1235,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1242,18 +1256,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>22</v>
+            <v>11</v>
           </cell>
           <cell r="O1">
-            <v>9800</v>
+            <v>10900</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>98</v>
+            <v>109</v>
           </cell>
           <cell r="O2">
-            <v>2200</v>
+            <v>1100</v>
           </cell>
         </row>
         <row r="3">
@@ -1283,18 +1297,18 @@
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>104</v>
+            <v>83</v>
           </cell>
           <cell r="O1">
-            <v>8000</v>
+            <v>18500</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>16</v>
+            <v>37</v>
           </cell>
           <cell r="O2">
-            <v>52000</v>
+            <v>41500</v>
           </cell>
         </row>
         <row r="3">
@@ -1310,6 +1324,90 @@
 </file>
 
 <file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD50000.15-DEC"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>17</v>
+          </cell>
+          <cell r="O1">
+            <v>2800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>2</v>
+          </cell>
+          <cell r="O2">
+            <v>21000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45678</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD50000.15-DEC"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>17</v>
+          </cell>
+          <cell r="O1">
+            <v>2800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>2</v>
+          </cell>
+          <cell r="O2">
+            <v>21000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45683</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1386,7 +1484,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1426,7 +1524,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1466,7 +1564,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1506,7 +1604,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1548,7 +1646,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1588,7 +1686,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1630,7 +1728,47 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>13</v>
+          </cell>
+          <cell r="O1">
+            <v>10700</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>107</v>
+          </cell>
+          <cell r="O2">
+            <v>1300</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45561</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1672,7 +1810,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1714,47 +1852,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.1-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>14</v>
-          </cell>
-          <cell r="O1">
-            <v>10600</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>106</v>
-          </cell>
-          <cell r="O2">
-            <v>1400</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45561</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1796,7 +1894,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1836,7 +1934,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1868,7 +1966,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1910,7 +2008,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1950,7 +2048,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1992,7 +2090,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2034,7 +2132,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2074,7 +2172,47 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45563</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2114,7 +2252,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2156,47 +2294,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.1-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>18</v>
-          </cell>
-          <cell r="O1">
-            <v>10200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>102</v>
-          </cell>
-          <cell r="O2">
-            <v>1800</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45563</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2238,7 +2336,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2278,7 +2376,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2318,7 +2416,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2358,7 +2456,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2394,7 +2492,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2422,7 +2520,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2464,7 +2562,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2499,90 +2597,6 @@
           </cell>
         </row>
       </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.10-JAN"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>16800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>48</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45366</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.15-DEc"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45380</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2603,18 +2617,18 @@
             <v>15000</v>
           </cell>
           <cell r="K1">
-            <v>47</v>
+            <v>35</v>
           </cell>
           <cell r="O1">
-            <v>10950</v>
+            <v>12750</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>73</v>
+            <v>85</v>
           </cell>
           <cell r="O2">
-            <v>7050</v>
+            <v>5250</v>
           </cell>
         </row>
         <row r="3">
@@ -2660,7 +2674,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45389</v>
+            <v>45366</v>
           </cell>
         </row>
       </sheetData>
@@ -2685,8 +2699,8 @@
           <cell r="C1">
             <v>20000</v>
           </cell>
-          <cell r="G1">
-            <v>17</v>
+          <cell r="K1">
+            <v>0</v>
           </cell>
           <cell r="O1">
             <v>24000</v>
@@ -2702,7 +2716,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45394</v>
+            <v>45380</v>
           </cell>
         </row>
       </sheetData>
@@ -2713,6 +2727,48 @@
 </file>
 
 <file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.10-JAN"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>16800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>48</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45389</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2744,7 +2800,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45406</v>
+            <v>45394</v>
           </cell>
         </row>
       </sheetData>
@@ -2754,7 +2810,49 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEc"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="G1">
+            <v>17</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45406</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2794,7 +2892,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2833,7 +2931,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2851,86 +2949,6 @@
         </row>
       </sheetData>
       <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.20-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1">
-        <row r="1">
-          <cell r="C1">
-            <v>5000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>6000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45427</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45425</v>
-          </cell>
-        </row>
-      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2967,7 +2985,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45436</v>
+            <v>45427</v>
           </cell>
         </row>
       </sheetData>
@@ -2981,7 +2999,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
-      <sheetName val="MD20000.22-DEC"/>
+      <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -3007,7 +3025,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45432</v>
+            <v>45425</v>
           </cell>
         </row>
       </sheetData>
@@ -3031,18 +3049,18 @@
             <v>100000</v>
           </cell>
           <cell r="K1">
-            <v>27</v>
+            <v>25</v>
           </cell>
           <cell r="O1">
-            <v>52000</v>
+            <v>60000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>13</v>
+            <v>15</v>
           </cell>
           <cell r="O2">
-            <v>108000</v>
+            <v>100000</v>
           </cell>
         </row>
         <row r="3">
@@ -3057,6 +3075,86 @@
 </file>
 
 <file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.20-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>5000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>6000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45436</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.22-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45432</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3096,7 +3194,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3133,7 +3231,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3159,7 +3257,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3167,7 +3265,7 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="K1">
@@ -3191,7 +3289,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3231,7 +3329,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3271,7 +3369,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3308,88 +3406,6 @@
         </row>
       </sheetData>
       <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.15-DEc"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>12000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45496</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45493</v>
-          </cell>
-        </row>
-      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3427,7 +3443,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45502</v>
+            <v>45496</v>
           </cell>
         </row>
       </sheetData>
@@ -3482,6 +3498,88 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45493</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink71.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEc"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45502</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink72.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
       <sheetName val="MD50000.15-DEC"/>
       <sheetName val="Sheet1"/>
     </sheetNames>
@@ -3519,7 +3617,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink71.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink73.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3559,7 +3657,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink72.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink74.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3599,7 +3697,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink73.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink75.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3639,7 +3737,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink74.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink76.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3676,88 +3774,6 @@
         </row>
       </sheetData>
       <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink75.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.15-DEc"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>12000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45531</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink76.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.20-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>5000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>6000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45532</v>
-          </cell>
-        </row>
-      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3795,7 +3811,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45534</v>
+            <v>45531</v>
           </cell>
         </row>
       </sheetData>
@@ -3836,7 +3852,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45536</v>
+            <v>45532</v>
           </cell>
         </row>
       </sheetData>
@@ -3850,25 +3866,26 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
-      <sheetName val="MD20000.22-DEC"/>
+      <sheetName val="MD20000.15-DEc"/>
+      <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
-            <v>20000</v>
+            <v>10000</v>
           </cell>
           <cell r="K1">
             <v>0</v>
           </cell>
           <cell r="O1">
-            <v>24000</v>
+            <v>12000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>120</v>
+            <v>17</v>
           </cell>
           <cell r="O2">
             <v>0</v>
@@ -3876,10 +3893,11 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45535</v>
+            <v>45534</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3893,25 +3911,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>36</v>
+            <v>10</v>
           </cell>
           <cell r="O1">
-            <v>16800</v>
+            <v>22000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>84</v>
+            <v>110</v>
           </cell>
           <cell r="O2">
-            <v>7200</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="7">
@@ -3933,7 +3951,7 @@
       <sheetName val="MD10000.20-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -3956,7 +3974,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45549</v>
+            <v>45536</v>
           </cell>
         </row>
       </sheetData>
@@ -3994,9 +4012,9 @@
             <v>0</v>
           </cell>
         </row>
-        <row r="13">
-          <cell r="B13">
-            <v>45562</v>
+        <row r="3">
+          <cell r="B3">
+            <v>45535</v>
           </cell>
         </row>
       </sheetData>
@@ -4006,6 +4024,86 @@
 </file>
 
 <file path=xl/externalLinks/externalLink82.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.20-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>5000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>6000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45549</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink83.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.22-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="B13">
+            <v>45562</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink84.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4045,7 +4143,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink83.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink85.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4085,7 +4183,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink84.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink86.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4125,7 +4223,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink85.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink87.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4165,7 +4263,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink86.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink88.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4205,7 +4303,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink87.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink89.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4237,84 +4335,6 @@
         <row r="3">
           <cell r="B3">
             <v>45584</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink88.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>12000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45587</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink89.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.22-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45597</v>
           </cell>
         </row>
       </sheetData>
@@ -4338,18 +4358,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>94</v>
+            <v>69</v>
           </cell>
           <cell r="O1">
-            <v>2600</v>
+            <v>5100</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>26</v>
+            <v>51</v>
           </cell>
           <cell r="O2">
-            <v>9400</v>
+            <v>6900</v>
           </cell>
         </row>
         <row r="3">
@@ -4367,21 +4387,59 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45587</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink91.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
       <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
+      <sheetName val="MD20000.22-DEC"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
-            <v>30000</v>
+            <v>20000</v>
           </cell>
           <cell r="K1">
             <v>0</v>
           </cell>
           <cell r="O1">
-            <v>36000</v>
+            <v>24000</v>
           </cell>
         </row>
         <row r="2">
@@ -4394,47 +4452,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45602</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink91.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>50000</v>
-          </cell>
-          <cell r="K1">
-            <v>100</v>
-          </cell>
-          <cell r="O1">
-            <v>10000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>20</v>
-          </cell>
-          <cell r="O2">
-            <v>50000</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45612</v>
+            <v>45597</v>
           </cell>
         </row>
       </sheetData>
@@ -4474,7 +4492,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45647</v>
+            <v>45602</v>
           </cell>
         </row>
       </sheetData>
@@ -4488,70 +4506,222 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
-      <sheetName val="MD50000.15-DEC"/>
-      <sheetName val="Sheet1"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>50000</v>
+          </cell>
+          <cell r="K1">
+            <v>100</v>
+          </cell>
+          <cell r="O1">
+            <v>10000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>20</v>
+          </cell>
+          <cell r="O2">
+            <v>50000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45612</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink94.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
-            <v>20000</v>
+            <v>30000</v>
           </cell>
           <cell r="K1">
-            <v>17</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
-            <v>0</v>
+            <v>36000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>0</v>
+            <v>120</v>
           </cell>
           <cell r="O2">
-            <v>23800</v>
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45647</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink94.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink95.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
-      <sheetName val="MD50000.15-DEC"/>
-      <sheetName val="Sheet1"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink96.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
-            <v>20000</v>
+            <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>17</v>
+            <v>109</v>
           </cell>
           <cell r="O1">
-            <v>0</v>
+            <v>5500</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>0</v>
+            <v>11</v>
           </cell>
           <cell r="O2">
-            <v>23800</v>
+            <v>54500</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45684</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink97.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>115</v>
+          </cell>
+          <cell r="O1">
+            <v>500</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>5</v>
+          </cell>
+          <cell r="O2">
+            <v>11500</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45690</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink98.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>35000</v>
+          </cell>
+          <cell r="K1">
+            <v>119</v>
+          </cell>
+          <cell r="O1">
+            <v>350</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>1</v>
+          </cell>
+          <cell r="O2">
+            <v>41650</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45696</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4812,7 +4982,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4820,7 +4990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:Q30"/>
+  <dimension ref="B2:Q44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="1" customWidth="1"/>
@@ -4838,8 +5008,7 @@
     <col min="13" max="13" width="15" style="1" customWidth="1"/>
     <col min="14" max="14" width="15.28515625" style="1" customWidth="1"/>
     <col min="15" max="15" width="11.85546875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -4854,13 +5023,13 @@
       <c r="J2" s="31"/>
       <c r="K2" s="32"/>
       <c r="L2" s="33">
-        <f>SUM(L5:L38)</f>
-        <v>784050</v>
+        <f>SUM(L5:L47)</f>
+        <v>782500</v>
       </c>
       <c r="M2" s="34"/>
       <c r="N2" s="1">
-        <f>SUM(N5:N47)</f>
-        <v>39700</v>
+        <f>SUM(N5:N56)</f>
+        <v>44950</v>
       </c>
       <c r="Q2" s="1">
         <f>14900+260750</f>
@@ -4937,7 +5106,7 @@
       </c>
       <c r="I5" s="13">
         <f>'[1]MD10000.10-JAN'!$K$2</f>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J5" s="16" t="s">
         <v>12</v>
@@ -4948,11 +5117,11 @@
       </c>
       <c r="L5" s="15">
         <f>'[1]MD10000.10-JAN'!$O$2</f>
-        <v>2800</v>
+        <v>2100</v>
       </c>
       <c r="M5" s="15">
         <f>'[1]MD10000.10-JAN'!$O$1</f>
-        <v>14000</v>
+        <v>14700</v>
       </c>
       <c r="N5" s="1">
         <v>350</v>
@@ -4974,11 +5143,11 @@
       </c>
       <c r="F6" s="8">
         <f>'[2]MD10000.1-OCT'!$K$1</f>
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G6" s="8">
         <f>'[2]MD10000.1-OCT'!$K$2</f>
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
@@ -4991,15 +5160,16 @@
       </c>
       <c r="L6" s="7">
         <f>'[2]MD10000.1-OCT'!$O$2</f>
-        <v>2200</v>
+        <v>1100</v>
       </c>
       <c r="M6" s="7">
         <f>'[2]MD10000.1-OCT'!$O$1</f>
-        <v>9800</v>
+        <v>10900</v>
       </c>
       <c r="N6" s="1">
         <v>700</v>
       </c>
+      <c r="P6" s="35"/>
     </row>
     <row r="7" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="6">
@@ -5017,11 +5187,11 @@
       </c>
       <c r="F7" s="8">
         <f>'[3]MD10000.1-OCT'!$K$1</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G7" s="8">
         <f>'[3]MD10000.1-OCT'!$K$2</f>
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
@@ -5034,15 +5204,16 @@
       </c>
       <c r="L7" s="7">
         <f>'[3]MD10000.1-OCT'!$O$2</f>
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="M7" s="7">
         <f>'[3]MD10000.1-OCT'!$O$1</f>
-        <v>10600</v>
+        <v>10700</v>
       </c>
       <c r="N7" s="1">
         <v>700</v>
       </c>
+      <c r="P7" s="35"/>
     </row>
     <row r="8" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="6">
@@ -5060,11 +5231,11 @@
       </c>
       <c r="F8" s="8">
         <f>'[4]MD10000.1-OCT'!$K$1</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G8" s="8">
         <f>'[4]MD10000.1-OCT'!$K$2</f>
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
@@ -5077,11 +5248,11 @@
       </c>
       <c r="L8" s="7">
         <f>'[4]MD10000.1-OCT'!$O$2</f>
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="M8" s="7">
         <f>'[4]MD10000.1-OCT'!$O$1</f>
-        <v>10200</v>
+        <v>12000</v>
       </c>
       <c r="N8" s="1">
         <v>700</v>
@@ -5103,11 +5274,11 @@
       </c>
       <c r="F9" s="8">
         <f>'[5]MD10000.1-OCT'!$K$1</f>
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G9" s="8">
         <f>'[5]MD10000.1-OCT'!$K$2</f>
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
@@ -5120,11 +5291,11 @@
       </c>
       <c r="L9" s="7">
         <f>'[5]MD10000.1-OCT'!$O$2</f>
-        <v>7050</v>
+        <v>5250</v>
       </c>
       <c r="M9" s="7">
         <f>'[5]MD10000.1-OCT'!$O$1</f>
-        <v>10950</v>
+        <v>12750</v>
       </c>
       <c r="N9" s="1">
         <v>1050</v>
@@ -5148,11 +5319,11 @@
       <c r="G10" s="8"/>
       <c r="H10" s="8">
         <f>'[6]MD20000.18-DEC'!$K$1</f>
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I10" s="8">
         <f>'[6]MD20000.18-DEC'!$K$2</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>12</v>
@@ -5163,57 +5334,54 @@
       </c>
       <c r="L10" s="7">
         <f>'[6]MD20000.18-DEC'!$O$2</f>
-        <v>108000</v>
+        <v>100000</v>
       </c>
       <c r="M10" s="7">
         <f>'[6]MD20000.18-DEC'!$O$1</f>
-        <v>52000</v>
+        <v>60000</v>
       </c>
       <c r="N10" s="1">
         <v>4000</v>
       </c>
     </row>
     <row r="11" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="6">
+      <c r="B11" s="17">
         <v>71</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="19">
         <f>'[7]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="20">
         <f>'[7]MD20000.18-DEC'!$K$1</f>
         <v>82</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="20">
         <f>'[7]MD20000.18-DEC'!$K$2</f>
         <v>38</v>
       </c>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="9" t="s">
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K11" s="22">
         <f>'[7]MD20000.18-DEC'!$B$3</f>
         <v>45584</v>
       </c>
-      <c r="L11" s="7">
-        <f>'[7]MD20000.18-DEC'!$O$2</f>
-        <v>16400</v>
-      </c>
-      <c r="M11" s="7">
-        <f>'[7]MD20000.18-DEC'!$O$1</f>
-        <v>7600</v>
-      </c>
-      <c r="N11" s="1">
-        <v>1400</v>
+      <c r="L11" s="19">
+        <f>'[95]MD20000.18-DEC'!$O$2</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="19">
+        <f>'[95]MD20000.18-DEC'!$O$1</f>
+        <v>24000</v>
       </c>
     </row>
     <row r="12" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5232,11 +5400,11 @@
       </c>
       <c r="F12" s="8">
         <f>'[8]MD20000.18-DEC'!$K$1</f>
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="G12" s="8">
         <f>'[8]MD20000.18-DEC'!$K$2</f>
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
@@ -5249,11 +5417,11 @@
       </c>
       <c r="L12" s="7">
         <f>'[8]MD20000.18-DEC'!$O$2</f>
-        <v>7200</v>
+        <v>2000</v>
       </c>
       <c r="M12" s="7">
         <f>'[8]MD20000.18-DEC'!$O$1</f>
-        <v>16800</v>
+        <v>22000</v>
       </c>
       <c r="N12" s="1">
         <v>1400</v>
@@ -5275,11 +5443,11 @@
       </c>
       <c r="F13" s="8">
         <f>'[9]MD20000.18-DEC'!$K$1</f>
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="G13" s="8">
         <f>'[9]MD20000.18-DEC'!$K$2</f>
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
@@ -5292,11 +5460,11 @@
       </c>
       <c r="L13" s="7">
         <f>'[9]MD20000.18-DEC'!$O$2</f>
-        <v>9400</v>
+        <v>6900</v>
       </c>
       <c r="M13" s="7">
         <f>'[9]MD20000.18-DEC'!$O$1</f>
-        <v>2600</v>
+        <v>5100</v>
       </c>
       <c r="N13" s="1">
         <v>700</v>
@@ -5318,11 +5486,11 @@
       </c>
       <c r="F14" s="8">
         <f>'[10]MD20000.18-DEC'!$K$1</f>
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="G14" s="8">
         <f>'[10]MD20000.18-DEC'!$K$2</f>
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="H14" s="8"/>
       <c r="I14" s="8"/>
@@ -5335,11 +5503,11 @@
       </c>
       <c r="L14" s="7">
         <f>'[10]MD20000.18-DEC'!$O$2</f>
-        <v>7500</v>
+        <v>6800</v>
       </c>
       <c r="M14" s="7">
         <f>'[10]MD20000.18-DEC'!$O$1</f>
-        <v>4500</v>
+        <v>5200</v>
       </c>
       <c r="N14" s="1">
         <v>700</v>
@@ -5363,11 +5531,11 @@
       <c r="G15" s="8"/>
       <c r="H15" s="8">
         <f>'[11]MD20000.15-DEc'!$K$1</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I15" s="8">
         <f>'[11]MD20000.15-DEc'!$K$2</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>12</v>
@@ -5378,11 +5546,11 @@
       </c>
       <c r="L15" s="7">
         <f>'[11]MD20000.15-DEc'!$O$2</f>
-        <v>7000</v>
+        <v>2800</v>
       </c>
       <c r="M15" s="7">
         <f>'[11]MD20000.15-DEc'!$O$1</f>
-        <v>17000</v>
+        <v>21200</v>
       </c>
       <c r="N15" s="1">
         <v>1400</v>
@@ -5406,11 +5574,11 @@
       <c r="G16" s="8"/>
       <c r="H16" s="8">
         <f>'[12]MD10000.10-JAN'!$K$1</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I16" s="8">
         <f>'[12]MD10000.10-JAN'!$K$2</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J16" s="9" t="s">
         <v>12</v>
@@ -5421,11 +5589,11 @@
       </c>
       <c r="L16" s="7">
         <f>'[12]MD10000.10-JAN'!$O$2</f>
-        <v>8400</v>
+        <v>5600</v>
       </c>
       <c r="M16" s="7">
         <f>'[12]MD10000.10-JAN'!$O$1</f>
-        <v>15600</v>
+        <v>18400</v>
       </c>
       <c r="N16" s="1">
         <v>1400</v>
@@ -5447,11 +5615,11 @@
       </c>
       <c r="F17" s="8">
         <f>'[13]MD20000.18-DEC'!$K$1</f>
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="G17" s="8">
         <f>'[13]MD20000.18-DEC'!$K$2</f>
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
@@ -5464,11 +5632,11 @@
       </c>
       <c r="L17" s="7">
         <f>'[13]MD20000.18-DEC'!$O$2</f>
-        <v>5800</v>
+        <v>4100</v>
       </c>
       <c r="M17" s="7">
         <f>'[13]MD20000.18-DEC'!$O$1</f>
-        <v>6200</v>
+        <v>7900</v>
       </c>
       <c r="N17" s="1">
         <v>700</v>
@@ -5490,11 +5658,11 @@
       </c>
       <c r="F18" s="8">
         <f>'[14]MD50000.15-DEC'!$K$1</f>
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="G18" s="8">
         <f>'[14]MD50000.15-DEC'!$K$2</f>
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
@@ -5507,11 +5675,11 @@
       </c>
       <c r="L18" s="7">
         <f>'[14]MD50000.15-DEC'!$O$2</f>
-        <v>136800</v>
+        <v>131400</v>
       </c>
       <c r="M18" s="7">
         <f>'[14]MD50000.15-DEC'!$O$1</f>
-        <v>23400</v>
+        <v>28800</v>
       </c>
       <c r="N18" s="1">
         <v>4200</v>
@@ -5533,11 +5701,11 @@
       </c>
       <c r="F19" s="8">
         <f>'[15]MD20000.18-DEC'!$K$1</f>
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="G19" s="8">
         <f>'[15]MD20000.18-DEC'!$K$2</f>
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -5550,11 +5718,11 @@
       </c>
       <c r="L19" s="7">
         <f>'[15]MD20000.18-DEC'!$O$2</f>
-        <v>37000</v>
+        <v>27000</v>
       </c>
       <c r="M19" s="7">
         <f>'[15]MD20000.18-DEC'!$O$1</f>
-        <v>23000</v>
+        <v>33000</v>
       </c>
       <c r="N19" s="1">
         <v>3500</v>
@@ -5576,11 +5744,11 @@
       </c>
       <c r="F20" s="8">
         <f>'[16]MD20000.18-DEC'!$K$1</f>
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="G20" s="8">
         <f>'[16]MD20000.18-DEC'!$K$2</f>
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
@@ -5593,11 +5761,11 @@
       </c>
       <c r="L20" s="7">
         <f>'[16]MD20000.18-DEC'!$O$2</f>
-        <v>7900</v>
+        <v>6300</v>
       </c>
       <c r="M20" s="7">
         <f>'[16]MD20000.18-DEC'!$O$1</f>
-        <v>4100</v>
+        <v>5700</v>
       </c>
       <c r="N20" s="1">
         <v>700</v>
@@ -5619,11 +5787,11 @@
       </c>
       <c r="F21" s="8">
         <f>'[17]MD20000.18-DEC'!$K$1</f>
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="G21" s="8">
         <f>'[17]MD20000.18-DEC'!$K$2</f>
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
@@ -5636,11 +5804,11 @@
       </c>
       <c r="L21" s="7">
         <f>'[17]MD20000.18-DEC'!$O$2</f>
-        <v>7900</v>
+        <v>6300</v>
       </c>
       <c r="M21" s="7">
         <f>'[17]MD20000.18-DEC'!$O$1</f>
-        <v>4100</v>
+        <v>5700</v>
       </c>
       <c r="N21" s="1">
         <v>700</v>
@@ -5662,11 +5830,11 @@
       </c>
       <c r="F22" s="8">
         <f>'[18]MD50000.15-DEC'!$K$1</f>
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="G22" s="8">
         <f>'[18]MD50000.15-DEC'!$K$2</f>
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
@@ -5679,11 +5847,11 @@
       </c>
       <c r="L22" s="7">
         <f>'[18]MD50000.15-DEC'!$O$2</f>
-        <v>300000</v>
+        <v>276000</v>
       </c>
       <c r="M22" s="7">
         <f>'[18]MD50000.15-DEC'!$O$1</f>
-        <v>20400</v>
+        <v>44400</v>
       </c>
       <c r="N22" s="1">
         <v>8400</v>
@@ -5707,11 +5875,11 @@
       <c r="G23" s="8"/>
       <c r="H23" s="8">
         <f>'[19]MD20000.15-DEc'!$K$1</f>
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I23" s="8">
         <f>'[19]MD20000.15-DEc'!$K$2</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>12</v>
@@ -5722,11 +5890,11 @@
       </c>
       <c r="L23" s="7">
         <f>'[19]MD20000.15-DEc'!$O$2</f>
-        <v>9900</v>
+        <v>6400</v>
       </c>
       <c r="M23" s="7">
         <f>'[19]MD20000.15-DEc'!$O$1</f>
-        <v>2100</v>
+        <v>5600</v>
       </c>
       <c r="N23" s="1">
         <v>700</v>
@@ -5748,11 +5916,11 @@
       </c>
       <c r="F24" s="8">
         <f>'[20]MD50000.15-DEC'!$K$1</f>
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="G24" s="8">
         <f>'[20]MD50000.15-DEC'!$K$2</f>
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
@@ -5765,11 +5933,11 @@
       </c>
       <c r="L24" s="7">
         <f>'[20]MD50000.15-DEC'!$O$2</f>
-        <v>52000</v>
+        <v>41500</v>
       </c>
       <c r="M24" s="7">
         <f>'[20]MD50000.15-DEC'!$O$1</f>
-        <v>8000</v>
+        <v>18500</v>
       </c>
       <c r="N24" s="1">
         <v>3500</v>
@@ -5786,33 +5954,33 @@
         <v>122</v>
       </c>
       <c r="E25" s="7">
-        <f>'[93]MD50000.15-DEC'!$C$1</f>
+        <f>'[21]MD50000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
       <c r="H25" s="8">
-        <f>'[93]MD50000.15-DEC'!$K$1</f>
+        <f>'[21]MD50000.15-DEC'!$K$1</f>
         <v>17</v>
       </c>
       <c r="I25" s="8">
-        <f>'[93]MD50000.15-DEC'!$K$2</f>
-        <v>0</v>
+        <f>'[21]MD50000.15-DEC'!$K$2</f>
+        <v>2</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>12</v>
       </c>
       <c r="K25" s="10">
-        <f>'[93]MD50000.15-DEC'!$B$3</f>
-        <v>0</v>
+        <f>'[21]MD50000.15-DEC'!$B$3</f>
+        <v>45678</v>
       </c>
       <c r="L25" s="7">
-        <f>'[93]MD50000.15-DEC'!$O$2</f>
-        <v>23800</v>
+        <f>'[21]MD50000.15-DEC'!$O$2</f>
+        <v>21000</v>
       </c>
       <c r="M25" s="7">
-        <f>'[93]MD50000.15-DEC'!$O$1</f>
-        <v>0</v>
+        <f>'[21]MD50000.15-DEC'!$O$1</f>
+        <v>2800</v>
       </c>
       <c r="N25" s="1">
         <v>1400</v>
@@ -5829,33 +5997,33 @@
         <v>124</v>
       </c>
       <c r="E26" s="7">
-        <f>'[94]MD50000.15-DEC'!$C$1</f>
+        <f>'[22]MD50000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
       <c r="H26" s="8">
-        <f>'[94]MD50000.15-DEC'!$K$1</f>
+        <f>'[22]MD50000.15-DEC'!$K$1</f>
         <v>17</v>
       </c>
       <c r="I26" s="8">
-        <f>'[94]MD50000.15-DEC'!$K$2</f>
-        <v>0</v>
+        <f>'[22]MD50000.15-DEC'!$K$2</f>
+        <v>2</v>
       </c>
       <c r="J26" s="9" t="s">
         <v>125</v>
       </c>
       <c r="K26" s="10">
-        <f>'[94]MD50000.15-DEC'!$B$3</f>
-        <v>0</v>
+        <f>'[22]MD50000.15-DEC'!$B$3</f>
+        <v>45683</v>
       </c>
       <c r="L26" s="7">
-        <f>'[94]MD50000.15-DEC'!$O$2</f>
-        <v>23800</v>
+        <f>'[22]MD50000.15-DEC'!$O$2</f>
+        <v>21000</v>
       </c>
       <c r="M26" s="7">
-        <f>'[94]MD50000.15-DEC'!$O$1</f>
-        <v>0</v>
+        <f>'[22]MD50000.15-DEC'!$O$1</f>
+        <v>2800</v>
       </c>
       <c r="N26" s="1">
         <v>1400</v>
@@ -5865,49 +6033,130 @@
       <c r="B27" s="6">
         <v>93</v>
       </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
+      <c r="C27" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27" s="7">
+        <f>'[96]MD20000.18-DEC'!$C$1</f>
+        <v>50000</v>
+      </c>
+      <c r="F27" s="8">
+        <f>'[96]MD20000.18-DEC'!$K$1</f>
+        <v>109</v>
+      </c>
+      <c r="G27" s="8">
+        <f>'[96]MD20000.18-DEC'!$K$2</f>
+        <v>11</v>
+      </c>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
+      <c r="J27" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K27" s="10">
+        <f>'[96]MD20000.18-DEC'!$B$3</f>
+        <v>45684</v>
+      </c>
+      <c r="L27" s="7">
+        <f>'[96]MD20000.18-DEC'!$O$2</f>
+        <v>54500</v>
+      </c>
+      <c r="M27" s="7">
+        <f>'[96]MD20000.18-DEC'!$O$1</f>
+        <v>5500</v>
+      </c>
+      <c r="N27" s="1">
+        <v>3500</v>
+      </c>
     </row>
     <row r="28" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="6">
         <v>94</v>
       </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
+      <c r="C28" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E28" s="7">
+        <f>'[97]MD20000.18-DEC'!$C$1</f>
+        <v>10000</v>
+      </c>
+      <c r="F28" s="8">
+        <f>'[97]MD20000.18-DEC'!$K$1</f>
+        <v>115</v>
+      </c>
+      <c r="G28" s="8">
+        <f>'[97]MD20000.18-DEC'!$K$2</f>
+        <v>5</v>
+      </c>
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
+      <c r="J28" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K28" s="10">
+        <f>'[97]MD20000.18-DEC'!$B$3</f>
+        <v>45690</v>
+      </c>
+      <c r="L28" s="7">
+        <f>'[97]MD20000.18-DEC'!$O$2</f>
+        <v>11500</v>
+      </c>
+      <c r="M28" s="7">
+        <f>'[97]MD20000.18-DEC'!$O$1</f>
+        <v>500</v>
+      </c>
+      <c r="N28" s="1">
+        <v>700</v>
+      </c>
     </row>
     <row r="29" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="6">
         <v>95</v>
       </c>
-      <c r="C29" s="8"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
+      <c r="C29" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="E29" s="7">
+        <f>'[98]MD20000.18-DEC'!$C$1</f>
+        <v>35000</v>
+      </c>
+      <c r="F29" s="8">
+        <f>'[98]MD20000.18-DEC'!$K$1</f>
+        <v>119</v>
+      </c>
+      <c r="G29" s="8">
+        <f>'[98]MD20000.18-DEC'!$K$2</f>
+        <v>1</v>
+      </c>
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
+      <c r="J29" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K29" s="10">
+        <f>'[98]MD20000.18-DEC'!$B$3</f>
+        <v>45696</v>
+      </c>
+      <c r="L29" s="7">
+        <f>'[98]MD20000.18-DEC'!$O$2</f>
+        <v>41650</v>
+      </c>
+      <c r="M29" s="7">
+        <f>'[98]MD20000.18-DEC'!$O$1</f>
+        <v>350</v>
+      </c>
+      <c r="N29" s="1">
+        <v>2450</v>
+      </c>
     </row>
     <row r="30" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="6">
@@ -5924,6 +6173,202 @@
       <c r="K30" s="10"/>
       <c r="L30" s="7"/>
       <c r="M30" s="7"/>
+    </row>
+    <row r="31" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="6"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+    </row>
+    <row r="32" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="6"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="7"/>
+      <c r="M32" s="7"/>
+    </row>
+    <row r="33" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="6"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
+    </row>
+    <row r="34" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="6"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="7"/>
+      <c r="M34" s="7"/>
+    </row>
+    <row r="35" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="6"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="7"/>
+      <c r="M35" s="7"/>
+    </row>
+    <row r="36" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="6"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="7"/>
+      <c r="M36" s="7"/>
+    </row>
+    <row r="37" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="6"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="7"/>
+      <c r="M37" s="7"/>
+    </row>
+    <row r="38" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="6"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
+    </row>
+    <row r="39" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="6"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="10"/>
+      <c r="L39" s="7"/>
+      <c r="M39" s="7"/>
+    </row>
+    <row r="40" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="6"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="7"/>
+      <c r="M40" s="7"/>
+    </row>
+    <row r="41" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="6"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="7"/>
+      <c r="M41" s="7"/>
+    </row>
+    <row r="42" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="6"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="9"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="7"/>
+      <c r="M42" s="7"/>
+    </row>
+    <row r="43" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="6"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="9"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="7"/>
+      <c r="M43" s="7"/>
+    </row>
+    <row r="44" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="6"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="9"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="7"/>
+      <c r="M44" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5972,7 +6417,7 @@
       <c r="K2" s="32"/>
       <c r="L2" s="33">
         <f>SUM(L5:L108)</f>
-        <v>819450</v>
+        <v>732250</v>
       </c>
       <c r="M2" s="34"/>
       <c r="N2" s="1">
@@ -6043,15 +6488,15 @@
         <v>18</v>
       </c>
       <c r="E5" s="19">
-        <f>'[21]SM5000.1-SEPT'!$C$1</f>
+        <f>'[23]SM5000.1-SEPT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F5" s="20">
-        <f>'[21]SM5000.1-SEPT'!$K$1</f>
+        <f>'[23]SM5000.1-SEPT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G5" s="20">
-        <f>'[21]SM5000.1-SEPT'!$K$2</f>
+        <f>'[23]SM5000.1-SEPT'!$K$2</f>
         <v>60</v>
       </c>
       <c r="H5" s="20"/>
@@ -6060,15 +6505,15 @@
         <v>22</v>
       </c>
       <c r="K5" s="22">
-        <f>'[21]SM5000.1-SEPT'!$B$3</f>
+        <f>'[23]SM5000.1-SEPT'!$B$3</f>
         <v>45180</v>
       </c>
       <c r="L5" s="19">
-        <f>'[21]SM5000.1-SEPT'!$O$2</f>
+        <f>'[23]SM5000.1-SEPT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M5" s="19">
-        <f>'[21]SM5000.1-SEPT'!$O$1</f>
+        <f>'[23]SM5000.1-SEPT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -6083,15 +6528,15 @@
         <v>18</v>
       </c>
       <c r="E6" s="19">
-        <f>'[21]SM5000.1-oct'!$C$1</f>
+        <f>'[23]SM5000.1-oct'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F6" s="20">
-        <f>'[21]SM5000.1-oct'!$K$1</f>
+        <f>'[23]SM5000.1-oct'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G6" s="20">
-        <f>'[21]SM5000.1-oct'!$K$2</f>
+        <f>'[23]SM5000.1-oct'!$K$2</f>
         <v>60</v>
       </c>
       <c r="H6" s="20"/>
@@ -6100,15 +6545,15 @@
         <v>22</v>
       </c>
       <c r="K6" s="22">
-        <f>'[21]SM5000.1-oct'!$B$3</f>
+        <f>'[23]SM5000.1-oct'!$B$3</f>
         <v>45201</v>
       </c>
       <c r="L6" s="19">
-        <f>'[21]SM5000.1-oct'!$O$2</f>
+        <f>'[23]SM5000.1-oct'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M6" s="19">
-        <f>'[21]SM5000.1-oct'!$O$1</f>
+        <f>'[23]SM5000.1-oct'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -6123,15 +6568,15 @@
         <v>19</v>
       </c>
       <c r="E7" s="19">
-        <f>'[22]MD10000.1-OCT'!$C$1</f>
+        <f>'[24]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F7" s="20">
-        <f>'[22]MD10000.1-OCT'!$K$1</f>
+        <f>'[24]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G7" s="20">
-        <f>'[22]MD10000.1-OCT'!$K$2</f>
+        <f>'[24]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H7" s="20"/>
@@ -6140,15 +6585,15 @@
         <v>22</v>
       </c>
       <c r="K7" s="22">
-        <f>'[22]MD10000.1-OCT'!$B$3</f>
+        <f>'[24]MD10000.1-OCT'!$B$3</f>
         <v>45212</v>
       </c>
       <c r="L7" s="19">
-        <f>'[22]MD10000.1-OCT'!$O$2</f>
+        <f>'[24]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M7" s="19">
-        <f>'[22]MD10000.1-OCT'!$O$1</f>
+        <f>'[24]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -6163,15 +6608,15 @@
         <v>19</v>
       </c>
       <c r="E8" s="19">
-        <f>'[23]MD10000.1-OCT'!$C$1</f>
+        <f>'[25]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F8" s="20">
-        <f>'[23]MD10000.1-OCT'!$K$1</f>
+        <f>'[25]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G8" s="20">
-        <f>'[23]MD10000.1-OCT'!$K$2</f>
+        <f>'[25]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H8" s="20"/>
@@ -6180,15 +6625,15 @@
         <v>22</v>
       </c>
       <c r="K8" s="22">
-        <f>'[23]MD10000.1-OCT'!$B$3</f>
+        <f>'[25]MD10000.1-OCT'!$B$3</f>
         <v>45213</v>
       </c>
       <c r="L8" s="19">
-        <f>'[23]MD10000.1-OCT'!$O$2</f>
+        <f>'[25]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M8" s="19">
-        <f>'[23]MD10000.1-OCT'!$O$1</f>
+        <f>'[25]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -6203,32 +6648,32 @@
         <v>20</v>
       </c>
       <c r="E9" s="19">
-        <f>'[24]MD10000.20-OCT'!$C$1</f>
+        <f>'[26]MD10000.20-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F9" s="20"/>
       <c r="G9" s="20"/>
       <c r="H9" s="20">
-        <f>'[24]MD10000.20-OCT'!$K$1</f>
+        <f>'[26]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I9" s="20">
-        <f>'[24]MD10000.20-OCT'!$K$2</f>
+        <f>'[26]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J9" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K9" s="22">
-        <f>'[24]MD10000.20-OCT'!$B$3</f>
+        <f>'[26]MD10000.20-OCT'!$B$3</f>
         <v>45226</v>
       </c>
       <c r="L9" s="19">
-        <f>'[24]MD10000.20-OCT'!$O$2</f>
+        <f>'[26]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M9" s="19">
-        <f>'[24]MD10000.20-OCT'!$O$1</f>
+        <f>'[26]MD10000.20-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -6243,15 +6688,15 @@
         <v>18</v>
       </c>
       <c r="E10" s="19">
-        <f>'[25]SM5000.1-SEPT (2)'!$C$1</f>
+        <f>'[27]SM5000.1-SEPT (2)'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F10" s="20">
-        <f>'[25]SM5000.1-SEPT (2)'!$K$1</f>
+        <f>'[27]SM5000.1-SEPT (2)'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G10" s="20">
-        <f>'[25]SM5000.1-SEPT (2)'!$K$2</f>
+        <f>'[27]SM5000.1-SEPT (2)'!$K$2</f>
         <v>60</v>
       </c>
       <c r="H10" s="20"/>
@@ -6260,15 +6705,15 @@
         <v>41</v>
       </c>
       <c r="K10" s="22">
-        <f>'[25]SM5000.1-SEPT (2)'!$B$3</f>
+        <f>'[27]SM5000.1-SEPT (2)'!$B$3</f>
         <v>45243</v>
       </c>
       <c r="L10" s="19">
-        <f>'[25]SM5000.1-SEPT (2)'!$O$2</f>
+        <f>'[27]SM5000.1-SEPT (2)'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M10" s="19">
-        <f>'[25]SM5000.1-SEPT (2)'!$O$1</f>
+        <f>'[27]SM5000.1-SEPT (2)'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -6283,32 +6728,32 @@
         <v>20</v>
       </c>
       <c r="E11" s="19">
-        <f>'[26]MD10000.20-OCT'!$C$1</f>
+        <f>'[28]MD10000.20-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F11" s="20"/>
       <c r="G11" s="20"/>
       <c r="H11" s="20">
-        <f>'[26]MD10000.20-OCT'!$K$1</f>
+        <f>'[28]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I11" s="20">
-        <f>'[26]MD10000.20-OCT'!$K$2</f>
+        <f>'[28]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J11" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K11" s="22">
-        <f>'[26]MD10000.20-OCT'!$B$3</f>
+        <f>'[28]MD10000.20-OCT'!$B$3</f>
         <v>45245</v>
       </c>
       <c r="L11" s="19">
-        <f>'[26]MD10000.20-OCT'!$O$2</f>
+        <f>'[28]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M11" s="19">
-        <f>'[26]MD10000.20-OCT'!$O$1</f>
+        <f>'[28]MD10000.20-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -6323,32 +6768,32 @@
         <v>25</v>
       </c>
       <c r="E12" s="19">
-        <f>'[27]MD15000.27-NOV'!$C$1</f>
+        <f>'[29]MD15000.27-NOV'!$C$1</f>
         <v>15000</v>
       </c>
       <c r="F12" s="20"/>
       <c r="G12" s="20"/>
       <c r="H12" s="20">
-        <f>'[27]MD15000.27-NOV'!$K$1</f>
+        <f>'[29]MD15000.27-NOV'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I12" s="20">
-        <f>'[27]MD15000.27-NOV'!$K$2</f>
+        <f>'[29]MD15000.27-NOV'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J12" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K12" s="22">
-        <f>'[27]MD15000.27-NOV'!$B$3</f>
+        <f>'[29]MD15000.27-NOV'!$B$3</f>
         <v>45266</v>
       </c>
       <c r="L12" s="19">
-        <f>'[27]MD15000.27-NOV'!$O$2</f>
+        <f>'[29]MD15000.27-NOV'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M12" s="19">
-        <f>'[27]MD15000.27-NOV'!$O$1</f>
+        <f>'[29]MD15000.27-NOV'!$O$1</f>
         <v>18000</v>
       </c>
     </row>
@@ -6363,32 +6808,32 @@
         <v>29</v>
       </c>
       <c r="E13" s="19">
-        <f>'[28]MD20000.15-DEC'!$C$1</f>
+        <f>'[30]MD20000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F13" s="20"/>
       <c r="G13" s="20"/>
       <c r="H13" s="20">
-        <f>'[28]MD20000.15-DEC'!$K$1</f>
+        <f>'[30]MD20000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I13" s="20">
-        <f>'[28]MD20000.15-DEC'!$K$2</f>
+        <f>'[30]MD20000.15-DEC'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J13" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K13" s="22">
-        <f>'[28]MD20000.15-DEC'!$B$3</f>
+        <f>'[30]MD20000.15-DEC'!$B$3</f>
         <v>45649</v>
       </c>
       <c r="L13" s="19">
-        <f>'[28]MD20000.15-DEC'!$O$2</f>
+        <f>'[30]MD20000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M13" s="19">
-        <f>'[28]MD20000.15-DEC'!$O$1</f>
+        <f>'[30]MD20000.15-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -6403,32 +6848,32 @@
         <v>28</v>
       </c>
       <c r="E14" s="19">
-        <f>'[29]MD20000.15-DEc'!$C$1</f>
+        <f>'[31]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F14" s="20"/>
       <c r="G14" s="20"/>
       <c r="H14" s="20">
-        <f>'[29]MD20000.15-DEc'!$K$1</f>
+        <f>'[31]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I14" s="20">
-        <f>'[29]MD20000.15-DEc'!$K$2</f>
+        <f>'[31]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J14" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K14" s="22">
-        <f>'[29]MD20000.15-DEc'!$B$3</f>
+        <f>'[31]MD20000.15-DEc'!$B$3</f>
         <v>45646</v>
       </c>
       <c r="L14" s="19">
-        <f>'[29]MD20000.15-DEc'!$O$2</f>
+        <f>'[31]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M14" s="19">
-        <f>'[29]MD20000.15-DEc'!$O$1</f>
+        <f>'[31]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -6443,32 +6888,32 @@
         <v>31</v>
       </c>
       <c r="E15" s="19">
-        <f>'[30]MD50000.15-DEC'!$C$1</f>
+        <f>'[32]MD50000.15-DEC'!$C$1</f>
         <v>50000</v>
       </c>
       <c r="F15" s="20"/>
       <c r="G15" s="20"/>
       <c r="H15" s="20">
-        <f>'[30]MD50000.15-DEC'!$K$1</f>
+        <f>'[32]MD50000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I15" s="20">
-        <f>'[30]MD50000.15-DEC'!$K$2</f>
+        <f>'[32]MD50000.15-DEC'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J15" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K15" s="22">
-        <f>'[30]MD50000.15-DEC'!$B$3</f>
+        <f>'[32]MD50000.15-DEC'!$B$3</f>
         <v>45648</v>
       </c>
       <c r="L15" s="19">
-        <f>'[30]MD50000.15-DEC'!$O$2</f>
+        <f>'[32]MD50000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M15" s="19">
-        <f>'[30]MD50000.15-DEC'!$O$1</f>
+        <f>'[32]MD50000.15-DEC'!$O$1</f>
         <v>84000</v>
       </c>
     </row>
@@ -6483,15 +6928,15 @@
         <v>33</v>
       </c>
       <c r="E16" s="19">
-        <f>'[31]MD20000.18-DEC'!$C$1</f>
+        <f>'[33]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F16" s="20">
-        <f>'[31]MD20000.18-DEC'!$K$1</f>
+        <f>'[33]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G16" s="20">
-        <f>'[31]MD20000.18-DEC'!$K$2</f>
+        <f>'[33]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H16" s="20"/>
@@ -6500,15 +6945,15 @@
         <v>53</v>
       </c>
       <c r="K16" s="22">
-        <f>'[31]MD20000.18-DEC'!$B$3</f>
+        <f>'[33]MD20000.18-DEC'!$B$3</f>
         <v>45279</v>
       </c>
       <c r="L16" s="19">
-        <f>'[31]MD20000.18-DEC'!$O$2</f>
+        <f>'[33]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M16" s="19">
-        <f>'[31]MD20000.18-DEC'!$O$1</f>
+        <f>'[33]MD20000.18-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -6523,15 +6968,15 @@
         <v>33</v>
       </c>
       <c r="E17" s="19">
-        <f>'[32]MD20000.22-DEC'!$C$1</f>
+        <f>'[34]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F17" s="20">
-        <f>'[32]MD20000.22-DEC'!$K$1</f>
+        <f>'[34]MD20000.22-DEC'!$K$1</f>
         <v>120</v>
       </c>
       <c r="G17" s="20">
-        <f>'[32]MD20000.22-DEC'!$K$2</f>
+        <f>'[34]MD20000.22-DEC'!$K$2</f>
         <v>0</v>
       </c>
       <c r="H17" s="20"/>
@@ -6540,12 +6985,12 @@
         <v>51</v>
       </c>
       <c r="K17" s="22">
-        <f>'[32]MD20000.22-DEC'!$B$3</f>
+        <f>'[34]MD20000.22-DEC'!$B$3</f>
         <v>0</v>
       </c>
       <c r="L17" s="19"/>
       <c r="M17" s="19">
-        <f>'[32]MD20000.22-DEC'!$O$1</f>
+        <f>'[34]MD20000.22-DEC'!$O$1</f>
         <v>0</v>
       </c>
     </row>
@@ -6560,32 +7005,32 @@
         <v>36</v>
       </c>
       <c r="E18" s="19">
-        <f>'[33]MD50000.15-DEC'!$C$1</f>
+        <f>'[35]MD50000.15-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F18" s="20"/>
       <c r="G18" s="20"/>
       <c r="H18" s="20">
-        <f>'[33]MD50000.15-DEC'!$K$1</f>
+        <f>'[35]MD50000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I18" s="20">
-        <f>'[33]MD50000.15-DEC'!$K$2</f>
+        <f>'[35]MD50000.15-DEC'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J18" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K18" s="22">
-        <f>'[33]MD50000.15-DEC'!$B$3</f>
+        <f>'[35]MD50000.15-DEC'!$B$3</f>
         <v>45310</v>
       </c>
       <c r="L18" s="19">
-        <f>'[33]MD50000.15-DEC'!$O$2</f>
+        <f>'[35]MD50000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M18" s="19">
-        <f>'[33]MD50000.15-DEC'!$O$1</f>
+        <f>'[35]MD50000.15-DEC'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -6600,15 +7045,15 @@
         <v>18</v>
       </c>
       <c r="E19" s="19">
-        <f>'[34]MD5000-Jan24'!$C$1</f>
+        <f>'[36]MD5000-Jan24'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F19" s="20">
-        <f>'[34]MD5000-Jan24'!$K$1</f>
+        <f>'[36]MD5000-Jan24'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G19" s="20">
-        <f>'[34]MD5000-Jan24'!$K$2</f>
+        <f>'[36]MD5000-Jan24'!$K$2</f>
         <v>60</v>
       </c>
       <c r="H19" s="20"/>
@@ -6617,15 +7062,15 @@
         <v>51</v>
       </c>
       <c r="K19" s="22">
-        <f>'[34]MD5000-Jan24'!$B$3</f>
+        <f>'[36]MD5000-Jan24'!$B$3</f>
         <v>45302</v>
       </c>
       <c r="L19" s="19">
-        <f>'[34]MD5000-Jan24'!$O$2</f>
+        <f>'[36]MD5000-Jan24'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M19" s="19">
-        <f>'[34]MD5000-Jan24'!$O$1</f>
+        <f>'[36]MD5000-Jan24'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -6640,32 +7085,32 @@
         <v>39</v>
       </c>
       <c r="E20" s="19">
-        <f>'[35]MD10000.10-JAN'!$C$1</f>
+        <f>'[37]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F20" s="20"/>
       <c r="G20" s="20"/>
       <c r="H20" s="20">
-        <f>'[35]MD10000.10-JAN'!$K$1</f>
+        <f>'[37]MD10000.10-JAN'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I20" s="20">
-        <f>'[35]MD10000.10-JAN'!$K$2</f>
+        <f>'[37]MD10000.10-JAN'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J20" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K20" s="22">
-        <f>'[35]MD10000.10-JAN'!$B$3</f>
+        <f>'[37]MD10000.10-JAN'!$B$3</f>
         <v>45308</v>
       </c>
       <c r="L20" s="19">
-        <f>'[35]MD10000.10-JAN'!$O$2</f>
+        <f>'[37]MD10000.10-JAN'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M20" s="19">
-        <f>'[35]MD10000.10-JAN'!$O$1</f>
+        <f>'[37]MD10000.10-JAN'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -6680,32 +7125,32 @@
         <v>39</v>
       </c>
       <c r="E21" s="19">
-        <f>'[36]MD10000.10-JAN'!$C$1</f>
+        <f>'[38]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F21" s="20"/>
       <c r="G21" s="20"/>
       <c r="H21" s="20">
-        <f>'[36]MD10000.10-JAN'!$K$1</f>
+        <f>'[38]MD10000.10-JAN'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I21" s="20">
-        <f>'[36]MD10000.10-JAN'!$K$2</f>
+        <f>'[38]MD10000.10-JAN'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J21" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K21" s="22">
-        <f>'[36]MD10000.10-JAN'!$B$3</f>
+        <f>'[38]MD10000.10-JAN'!$B$3</f>
         <v>45308</v>
       </c>
       <c r="L21" s="19">
-        <f>'[36]MD10000.10-JAN'!$O$2</f>
+        <f>'[38]MD10000.10-JAN'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M21" s="19">
-        <f>'[36]MD10000.10-JAN'!$O$1</f>
+        <f>'[38]MD10000.10-JAN'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -6720,32 +7165,32 @@
         <v>43</v>
       </c>
       <c r="E22" s="19">
-        <f>'[37]MD10000.20-OCT'!$C$1</f>
+        <f>'[39]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F22" s="20"/>
       <c r="G22" s="20"/>
       <c r="H22" s="20">
-        <f>'[37]MD10000.20-OCT'!$K$1</f>
+        <f>'[39]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I22" s="20">
-        <f>'[37]MD10000.20-OCT'!$K$2</f>
+        <f>'[39]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J22" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K22" s="22">
-        <f>'[37]MD10000.20-OCT'!$B$3</f>
+        <f>'[39]MD10000.20-OCT'!$B$3</f>
         <v>45316</v>
       </c>
       <c r="L22" s="19">
-        <f>'[37]MD10000.20-OCT'!$O$2</f>
+        <f>'[39]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M22" s="19">
-        <f>'[37]MD10000.20-OCT'!$O$1</f>
+        <f>'[39]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -6760,32 +7205,32 @@
         <v>36</v>
       </c>
       <c r="E23" s="19">
-        <f>'[38]MD10000.20-OCT'!$C$1</f>
+        <f>'[40]MD10000.20-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
       <c r="H23" s="20">
-        <f>'[38]MD10000.20-OCT'!$K$1</f>
+        <f>'[40]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I23" s="20">
-        <f>'[38]MD10000.20-OCT'!$K$2</f>
+        <f>'[40]MD10000.20-OCT'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J23" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K23" s="22">
-        <f>'[38]MD10000.20-OCT'!$B$3</f>
+        <f>'[40]MD10000.20-OCT'!$B$3</f>
         <v>45324</v>
       </c>
       <c r="L23" s="19">
-        <f>'[38]MD10000.20-OCT'!$O$2</f>
+        <f>'[40]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M23" s="19">
-        <f>'[38]MD10000.20-OCT'!$O$1</f>
+        <f>'[40]MD10000.20-OCT'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -6800,32 +7245,32 @@
         <v>46</v>
       </c>
       <c r="E24" s="19">
-        <f>'[39]MD10000.20-OCT'!$C$1</f>
+        <f>'[41]MD10000.20-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F24" s="20"/>
       <c r="G24" s="20"/>
       <c r="H24" s="20">
-        <f>'[39]MD10000.20-OCT'!$K$1</f>
+        <f>'[41]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I24" s="20">
-        <f>'[39]MD10000.20-OCT'!$K$2</f>
+        <f>'[41]MD10000.20-OCT'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J24" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K24" s="22">
-        <f>'[39]MD10000.20-OCT'!$B$3</f>
+        <f>'[41]MD10000.20-OCT'!$B$3</f>
         <v>45327</v>
       </c>
       <c r="L24" s="19">
-        <f>'[39]MD10000.20-OCT'!$O$2</f>
+        <f>'[41]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M24" s="19">
-        <f>'[39]MD10000.20-OCT'!$O$1</f>
+        <f>'[41]MD10000.20-OCT'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -6840,15 +7285,15 @@
         <v>18</v>
       </c>
       <c r="E25" s="19">
-        <f>'[40]SM5000.1-oct'!$C$1</f>
+        <f>'[42]SM5000.1-oct'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F25" s="20">
-        <f>'[40]SM5000.1-oct'!$K$1</f>
+        <f>'[42]SM5000.1-oct'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G25" s="20">
-        <f>'[40]SM5000.1-oct'!$K$2</f>
+        <f>'[42]SM5000.1-oct'!$K$2</f>
         <v>60</v>
       </c>
       <c r="H25" s="20"/>
@@ -6857,15 +7302,15 @@
         <v>12</v>
       </c>
       <c r="K25" s="22">
-        <f>'[40]SM5000.1-oct'!$B$3</f>
+        <f>'[42]SM5000.1-oct'!$B$3</f>
         <v>45323</v>
       </c>
       <c r="L25" s="19">
-        <f>'[40]SM5000.1-oct'!$O$2</f>
+        <f>'[42]SM5000.1-oct'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M25" s="19">
-        <f>'[40]SM5000.1-oct'!$O$1</f>
+        <f>'[42]SM5000.1-oct'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -6880,32 +7325,32 @@
         <v>48</v>
       </c>
       <c r="E26" s="19">
-        <f>'[41]MD10000.20-OCT'!$C$1</f>
+        <f>'[43]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F26" s="20"/>
       <c r="G26" s="20"/>
       <c r="H26" s="20">
-        <f>'[41]MD10000.20-OCT'!$K$1</f>
+        <f>'[43]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I26" s="20">
-        <f>'[41]MD10000.20-OCT'!$K$2</f>
+        <f>'[43]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J26" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K26" s="22">
-        <f>'[41]MD10000.20-OCT'!$B$3</f>
+        <f>'[43]MD10000.20-OCT'!$B$3</f>
         <v>45332</v>
       </c>
       <c r="L26" s="19">
-        <f>'[41]MD10000.20-OCT'!$O$2</f>
+        <f>'[43]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M26" s="19">
-        <f>'[41]MD10000.20-OCT'!$O$1</f>
+        <f>'[43]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -6920,15 +7365,15 @@
         <v>19</v>
       </c>
       <c r="E27" s="19">
-        <f>'[42]MD10000.1-OCT'!$C$1</f>
+        <f>'[44]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F27" s="20">
-        <f>'[42]MD10000.1-OCT'!$K$1</f>
+        <f>'[44]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G27" s="20">
-        <f>'[42]MD10000.1-OCT'!$K$2</f>
+        <f>'[44]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H27" s="20"/>
@@ -6937,15 +7382,15 @@
         <v>12</v>
       </c>
       <c r="K27" s="22">
-        <f>'[42]MD10000.1-OCT'!$B$3</f>
+        <f>'[44]MD10000.1-OCT'!$B$3</f>
         <v>45339</v>
       </c>
       <c r="L27" s="19">
-        <f>'[42]MD10000.1-OCT'!$O$2</f>
+        <f>'[44]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M27" s="19">
-        <f>'[42]MD10000.1-OCT'!$O$1</f>
+        <f>'[44]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -6960,15 +7405,15 @@
         <v>19</v>
       </c>
       <c r="E28" s="19">
-        <f>'[43]MD10000.1-OCT'!$C$1</f>
+        <f>'[45]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F28" s="20">
-        <f>'[43]MD10000.1-OCT'!$K$1</f>
+        <f>'[45]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G28" s="20">
-        <f>'[43]MD10000.1-OCT'!$K$2</f>
+        <f>'[45]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H28" s="20"/>
@@ -6977,15 +7422,15 @@
         <v>51</v>
       </c>
       <c r="K28" s="22">
-        <f>'[43]MD10000.1-OCT'!$B$3</f>
+        <f>'[45]MD10000.1-OCT'!$B$3</f>
         <v>45334</v>
       </c>
       <c r="L28" s="19">
-        <f>'[43]MD10000.1-OCT'!$O$2</f>
+        <f>'[45]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M28" s="19">
-        <f>'[43]MD10000.1-OCT'!$O$1</f>
+        <f>'[45]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -7000,32 +7445,32 @@
         <v>50</v>
       </c>
       <c r="E29" s="19">
-        <f>'[44]MD20000.15-DEC'!$C$1</f>
+        <f>'[46]MD20000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
       <c r="H29" s="20">
-        <f>'[44]MD20000.15-DEC'!$K$1</f>
+        <f>'[46]MD20000.15-DEC'!$K$1</f>
         <v>5</v>
       </c>
       <c r="I29" s="20">
-        <f>'[44]MD20000.15-DEC'!$K$2</f>
+        <f>'[46]MD20000.15-DEC'!$K$2</f>
         <v>12</v>
       </c>
       <c r="J29" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K29" s="22">
-        <f>'[44]MD20000.15-DEC'!$B$3</f>
+        <f>'[46]MD20000.15-DEC'!$B$3</f>
         <v>45337</v>
       </c>
       <c r="L29" s="19">
-        <f>'[45]MD20000.15-DEC'!$O$2</f>
+        <f>'[47]MD20000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M29" s="19">
-        <f>'[45]MD20000.15-DEC'!$O$1</f>
+        <f>'[47]MD20000.15-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7040,32 +7485,32 @@
         <v>52</v>
       </c>
       <c r="E30" s="19">
-        <f>'[46]MD20000.15-DEC'!$C$1</f>
+        <f>'[48]MD20000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F30" s="20"/>
       <c r="G30" s="20"/>
       <c r="H30" s="20">
-        <f>'[46]MD20000.15-DEC'!$K$1</f>
+        <f>'[48]MD20000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I30" s="20">
-        <f>'[46]MD20000.15-DEC'!$K$2</f>
+        <f>'[48]MD20000.15-DEC'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J30" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K30" s="22">
-        <f>'[46]MD20000.15-DEC'!$B$3</f>
+        <f>'[48]MD20000.15-DEC'!$B$3</f>
         <v>45345</v>
       </c>
       <c r="L30" s="19">
-        <f>'[46]MD20000.15-DEC'!$O$2</f>
+        <f>'[48]MD20000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M30" s="19">
-        <f>'[46]MD20000.15-DEC'!$O$1</f>
+        <f>'[48]MD20000.15-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7080,15 +7525,15 @@
         <v>33</v>
       </c>
       <c r="E31" s="19">
-        <f>'[47]MD20000.18-DEC'!$C$1</f>
+        <f>'[49]MD20000.18-DEC'!$C$1</f>
         <v>30000</v>
       </c>
       <c r="F31" s="20">
-        <f>'[47]MD20000.18-DEC'!$K$1</f>
+        <f>'[49]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G31" s="20">
-        <f>'[47]MD20000.18-DEC'!$K$2</f>
+        <f>'[49]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H31" s="20"/>
@@ -7097,15 +7542,15 @@
         <v>51</v>
       </c>
       <c r="K31" s="22">
-        <f>'[47]MD20000.18-DEC'!$B$3</f>
+        <f>'[49]MD20000.18-DEC'!$B$3</f>
         <v>45354</v>
       </c>
       <c r="L31" s="19">
-        <f>'[47]MD20000.18-DEC'!$O$2</f>
+        <f>'[49]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M31" s="19">
-        <f>'[47]MD20000.18-DEC'!$O$1</f>
+        <f>'[49]MD20000.18-DEC'!$O$1</f>
         <v>36000</v>
       </c>
     </row>
@@ -7120,32 +7565,32 @@
         <v>36</v>
       </c>
       <c r="E32" s="19">
-        <f>'[48]MD10000.10-JAN'!$C$1</f>
+        <f>'[50]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F32" s="20"/>
       <c r="G32" s="20"/>
       <c r="H32" s="20">
-        <f>'[48]MD10000.10-JAN'!$K$1</f>
+        <f>'[50]MD10000.10-JAN'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I32" s="20">
-        <f>'[48]MD10000.10-JAN'!$K$2</f>
+        <f>'[50]MD10000.10-JAN'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J32" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K32" s="22">
-        <f>'[48]MD10000.10-JAN'!$B$3</f>
+        <f>'[50]MD10000.10-JAN'!$B$3</f>
         <v>45366</v>
       </c>
       <c r="L32" s="19">
-        <f>'[48]MD10000.10-JAN'!$O$2</f>
+        <f>'[50]MD10000.10-JAN'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M32" s="19">
-        <f>'[48]MD10000.10-JAN'!$O$1</f>
+        <f>'[50]MD10000.10-JAN'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -7160,32 +7605,32 @@
         <v>52</v>
       </c>
       <c r="E33" s="19">
-        <f>'[49]MD20000.15-DEc'!$C$1</f>
+        <f>'[51]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F33" s="20"/>
       <c r="G33" s="20"/>
       <c r="H33" s="20">
-        <f>'[49]MD20000.15-DEc'!$K$1</f>
+        <f>'[51]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I33" s="20">
-        <f>'[49]MD20000.15-DEc'!$K$2</f>
+        <f>'[51]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J33" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K33" s="22">
-        <f>'[49]MD20000.15-DEc'!$B$3</f>
+        <f>'[51]MD20000.15-DEc'!$B$3</f>
         <v>45380</v>
       </c>
       <c r="L33" s="19">
-        <f>'[49]MD20000.15-DEc'!$O$2</f>
+        <f>'[51]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M33" s="19">
-        <f>'[49]MD20000.15-DEc'!$O$1</f>
+        <f>'[51]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7200,32 +7645,32 @@
         <v>36</v>
       </c>
       <c r="E34" s="19">
-        <f>'[50]MD10000.10-JAN'!$C$1</f>
+        <f>'[52]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F34" s="20"/>
       <c r="G34" s="20"/>
       <c r="H34" s="20">
-        <f>'[50]MD10000.10-JAN'!$K$1</f>
+        <f>'[52]MD10000.10-JAN'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I34" s="20">
-        <f>'[50]MD10000.10-JAN'!$K$2</f>
+        <f>'[52]MD10000.10-JAN'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J34" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K34" s="22">
-        <f>'[50]MD10000.10-JAN'!$B$3</f>
+        <f>'[52]MD10000.10-JAN'!$B$3</f>
         <v>45389</v>
       </c>
       <c r="L34" s="19">
-        <f>'[50]MD10000.10-JAN'!$O$2</f>
+        <f>'[52]MD10000.10-JAN'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M34" s="19">
-        <f>'[50]MD10000.10-JAN'!$O$1</f>
+        <f>'[52]MD10000.10-JAN'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -7240,32 +7685,32 @@
         <v>52</v>
       </c>
       <c r="E35" s="19">
-        <f>'[51]MD20000.15-DEc'!$C$1</f>
+        <f>'[53]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F35" s="20"/>
       <c r="G35" s="20"/>
       <c r="H35" s="20">
-        <f>'[51]MD20000.15-DEc'!$G$1</f>
+        <f>'[53]MD20000.15-DEc'!$G$1</f>
         <v>17</v>
       </c>
       <c r="I35" s="20">
-        <f>'[51]MD20000.15-DEc'!$K$2</f>
+        <f>'[53]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J35" s="21" t="s">
         <v>77</v>
       </c>
       <c r="K35" s="22">
-        <f>'[51]MD20000.15-DEc'!$B$3</f>
+        <f>'[53]MD20000.15-DEc'!$B$3</f>
         <v>45394</v>
       </c>
       <c r="L35" s="19">
-        <f>'[51]MD20000.15-DEc'!$O$2</f>
+        <f>'[53]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M35" s="19">
-        <f>'[51]MD20000.15-DEc'!$O$1</f>
+        <f>'[53]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7291,7 +7736,7 @@
       </c>
       <c r="I36" s="13">
         <f>'[1]MD10000.10-JAN'!$K$2</f>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J36" s="16" t="s">
         <v>12</v>
@@ -7302,11 +7747,11 @@
       </c>
       <c r="L36" s="15">
         <f>'[1]MD10000.10-JAN'!$O$2</f>
-        <v>2800</v>
+        <v>2100</v>
       </c>
       <c r="M36" s="15">
         <f>'[1]MD10000.10-JAN'!$O$1</f>
-        <v>14000</v>
+        <v>14700</v>
       </c>
       <c r="N36" s="1">
         <v>350</v>
@@ -7323,32 +7768,32 @@
         <v>52</v>
       </c>
       <c r="E37" s="19">
-        <f>'[52]MD20000.15-DEc'!$C$1</f>
+        <f>'[54]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F37" s="20"/>
       <c r="G37" s="20"/>
       <c r="H37" s="20">
-        <f>'[52]MD20000.15-DEc'!$G$1</f>
+        <f>'[54]MD20000.15-DEc'!$G$1</f>
         <v>17</v>
       </c>
       <c r="I37" s="20">
-        <f>'[52]MD20000.15-DEc'!$K$2</f>
+        <f>'[54]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J37" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K37" s="22">
-        <f>'[52]MD20000.15-DEc'!$B$3</f>
+        <f>'[54]MD20000.15-DEc'!$B$3</f>
         <v>45406</v>
       </c>
       <c r="L37" s="19">
-        <f>'[52]MD20000.15-DEc'!$O$2</f>
+        <f>'[54]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M37" s="19">
-        <f>'[52]MD20000.15-DEc'!$O$1</f>
+        <f>'[54]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7363,32 +7808,32 @@
         <v>60</v>
       </c>
       <c r="E38" s="19">
-        <f>'[53]MD10000.20-OCT'!$C$1</f>
+        <f>'[55]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F38" s="20"/>
       <c r="G38" s="20"/>
       <c r="H38" s="20">
-        <f>'[53]MD10000.20-OCT'!$G$1</f>
+        <f>'[55]MD10000.20-OCT'!$G$1</f>
         <v>17</v>
       </c>
       <c r="I38" s="20">
-        <f>'[53]MD10000.20-OCT'!$K$2</f>
+        <f>'[55]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J38" s="21" t="s">
         <v>77</v>
       </c>
       <c r="K38" s="22">
-        <f>'[53]MD10000.20-OCT'!$B$3</f>
+        <f>'[55]MD10000.20-OCT'!$B$3</f>
         <v>45406</v>
       </c>
       <c r="L38" s="19">
-        <f>'[53]MD10000.20-OCT'!$O$2</f>
+        <f>'[55]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M38" s="19">
-        <f>'[53]MD10000.20-OCT'!$O$1</f>
+        <f>'[55]MD10000.20-OCT'!$O$1</f>
         <v>5950</v>
       </c>
     </row>
@@ -7403,32 +7848,32 @@
         <v>62</v>
       </c>
       <c r="E39" s="19">
-        <f>'[54]MD50000.15-DEC'!$C$1</f>
+        <f>'[56]MD50000.15-DEC'!$C$1</f>
         <v>40000</v>
       </c>
       <c r="F39" s="20"/>
       <c r="G39" s="20"/>
       <c r="H39" s="20">
-        <f>'[54]MD50000.15-DEC'!$K$1</f>
+        <f>'[56]MD50000.15-DEC'!$K$1</f>
         <v>47</v>
       </c>
       <c r="I39" s="20">
-        <f>'[54]MD50000.15-DEC'!$K$2</f>
+        <f>'[56]MD50000.15-DEC'!$K$2</f>
         <v>1</v>
       </c>
       <c r="J39" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K39" s="22">
-        <f>'[54]MD50000.15-DEC'!$B$3</f>
+        <f>'[56]MD50000.15-DEC'!$B$3</f>
         <v>45416</v>
       </c>
       <c r="L39" s="19">
-        <f>'[55]MD50000.15-DEC'!$O$2</f>
+        <f>'[57]MD50000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M39" s="19">
-        <f>'[54]MD50000.15-DEC'!$O$1</f>
+        <f>'[56]MD50000.15-DEC'!$O$1</f>
         <v>1400</v>
       </c>
     </row>
@@ -7443,32 +7888,32 @@
         <v>85</v>
       </c>
       <c r="E40" s="19">
-        <f>'[56]MD10000.20-OCT'!$C$1</f>
+        <f>'[58]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F40" s="20"/>
       <c r="G40" s="20"/>
       <c r="H40" s="20">
-        <f>'[56]MD10000.20-OCT'!$K$1</f>
+        <f>'[58]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I40" s="20">
-        <f>'[56]MD10000.20-OCT'!$K$2</f>
+        <f>'[58]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J40" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K40" s="22">
-        <f>'[56]MD10000.20-OCT'!$B$3</f>
+        <f>'[58]MD10000.20-OCT'!$B$3</f>
         <v>45427</v>
       </c>
       <c r="L40" s="19">
-        <f>'[56]MD10000.20-OCT'!$O$2</f>
+        <f>'[58]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M40" s="19">
-        <f>'[56]MD10000.20-OCT'!$O$1</f>
+        <f>'[58]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -7483,15 +7928,15 @@
         <v>33</v>
       </c>
       <c r="E41" s="19">
-        <f>'[57]MD20000.18-DEC'!$C$1</f>
+        <f>'[59]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F41" s="20">
-        <f>'[57]MD20000.18-DEC'!$K$1</f>
+        <f>'[59]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G41" s="20">
-        <f>'[57]MD20000.18-DEC'!$K$2</f>
+        <f>'[59]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H41" s="20"/>
@@ -7500,15 +7945,15 @@
         <v>77</v>
       </c>
       <c r="K41" s="22">
-        <f>'[57]MD20000.18-DEC'!$B$3</f>
+        <f>'[59]MD20000.18-DEC'!$B$3</f>
         <v>45425</v>
       </c>
       <c r="L41" s="19">
-        <f>'[57]MD20000.18-DEC'!$O$2</f>
+        <f>'[59]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M41" s="19">
-        <f>'[57]MD20000.18-DEC'!$O$1</f>
+        <f>'[59]MD20000.18-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7523,32 +7968,32 @@
         <v>66</v>
       </c>
       <c r="E42" s="19">
-        <f>'[58]MD10000.20-OCT'!$C$1</f>
+        <f>'[60]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F42" s="20"/>
       <c r="G42" s="20"/>
       <c r="H42" s="20">
-        <f>'[58]MD10000.20-OCT'!$K$1</f>
+        <f>'[60]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I42" s="20">
-        <f>'[58]MD10000.20-OCT'!$K$2</f>
+        <f>'[60]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J42" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K42" s="22">
-        <f>'[58]MD10000.20-OCT'!$B$3</f>
+        <f>'[60]MD10000.20-OCT'!$B$3</f>
         <v>45436</v>
       </c>
       <c r="L42" s="19">
-        <f>'[58]MD10000.20-OCT'!$O$2</f>
+        <f>'[60]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M42" s="19">
-        <f>'[58]MD10000.20-OCT'!$O$1</f>
+        <f>'[60]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -7563,15 +8008,15 @@
         <v>33</v>
       </c>
       <c r="E43" s="19">
-        <f>'[59]MD20000.22-DEC'!$C$1</f>
+        <f>'[61]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F43" s="20">
-        <f>'[59]MD20000.22-DEC'!$K$1</f>
+        <f>'[61]MD20000.22-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G43" s="20">
-        <f>'[59]MD20000.22-DEC'!$K$2</f>
+        <f>'[61]MD20000.22-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H43" s="20"/>
@@ -7580,15 +8025,15 @@
         <v>12</v>
       </c>
       <c r="K43" s="22">
-        <f>'[59]MD20000.22-DEC'!$B$3</f>
+        <f>'[61]MD20000.22-DEC'!$B$3</f>
         <v>45432</v>
       </c>
       <c r="L43" s="19">
-        <f>'[59]MD20000.22-DEC'!$O$2</f>
+        <f>'[61]MD20000.22-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M43" s="19">
-        <f>'[59]MD20000.22-DEC'!$O$1</f>
+        <f>'[61]MD20000.22-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7603,15 +8048,15 @@
         <v>68</v>
       </c>
       <c r="E44" s="19">
-        <f>'[60]MD10000.1-OCT'!$C$1</f>
+        <f>'[62]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F44" s="20">
-        <f>'[60]MD10000.1-OCT'!$G$1</f>
+        <f>'[62]MD10000.1-OCT'!$G$1</f>
         <v>120</v>
       </c>
       <c r="G44" s="20">
-        <f>'[60]MD10000.1-OCT'!$K$1</f>
+        <f>'[62]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="H44" s="20"/>
@@ -7620,15 +8065,15 @@
         <v>77</v>
       </c>
       <c r="K44" s="22">
-        <f>'[60]MD10000.1-OCT'!$B$3</f>
+        <f>'[62]MD10000.1-OCT'!$B$3</f>
         <v>45437</v>
       </c>
       <c r="L44" s="19">
-        <f>'[60]MD10000.1-OCT'!$O$2</f>
+        <f>'[62]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M44" s="19">
-        <f>'[60]MD10000.1-OCT'!$O$1</f>
+        <f>'[62]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -7643,29 +8088,29 @@
         <v>48</v>
       </c>
       <c r="E45" s="19">
-        <f>'[61]MD10000.20-OCT'!$C$1</f>
+        <f>'[63]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F45" s="20"/>
       <c r="G45" s="20"/>
       <c r="H45" s="20">
-        <f>'[61]MD10000.20-OCT'!$K$1</f>
+        <f>'[63]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I45" s="20">
-        <f>'[61]MD10000.20-OCT'!$K$2</f>
+        <f>'[63]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J45" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K45" s="22">
-        <f>'[61]MD10000.20-OCT'!$B$3</f>
+        <f>'[63]MD10000.20-OCT'!$B$3</f>
         <v>45444</v>
       </c>
       <c r="L45" s="19"/>
       <c r="M45" s="19">
-        <f>'[61]MD10000.20-OCT'!$O$1</f>
+        <f>'[63]MD10000.20-OCT'!$O$1</f>
         <v>5950</v>
       </c>
     </row>
@@ -7680,32 +8125,32 @@
         <v>71</v>
       </c>
       <c r="E46" s="19">
-        <f>'[62]MD10000.1-OCT'!$C$1</f>
+        <f>'[64]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F46" s="20"/>
       <c r="G46" s="20"/>
       <c r="H46" s="20">
-        <f>'[63]MD10000.1-OCT'!$K$1</f>
+        <f>'[65]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I46" s="20">
-        <f>'[63]MD10000.1-OCT'!$K$2</f>
+        <f>'[65]MD10000.1-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J46" s="21" t="s">
         <v>77</v>
       </c>
       <c r="K46" s="22">
-        <f>'[62]MD10000.1-OCT'!$B$3</f>
+        <f>'[64]MD10000.1-OCT'!$B$3</f>
         <v>45450</v>
       </c>
       <c r="L46" s="19">
-        <f>'[63]MD10000.1-OCT'!$O$2</f>
+        <f>'[65]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M46" s="19">
-        <f>'[63]MD10000.1-OCT'!$O$1</f>
+        <f>'[65]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -7720,15 +8165,15 @@
         <v>33</v>
       </c>
       <c r="E47" s="19">
-        <f>'[64]MD20000.22-DEC'!$C$1</f>
+        <f>'[66]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F47" s="20">
-        <f>'[64]MD20000.22-DEC'!$K$1</f>
+        <f>'[66]MD20000.22-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G47" s="20">
-        <f>'[64]MD20000.22-DEC'!$K$2</f>
+        <f>'[66]MD20000.22-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H47" s="20"/>
@@ -7737,15 +8182,15 @@
         <v>77</v>
       </c>
       <c r="K47" s="22">
-        <f>'[64]MD20000.22-DEC'!$B$3</f>
+        <f>'[66]MD20000.22-DEC'!$B$3</f>
         <v>45446</v>
       </c>
       <c r="L47" s="19">
-        <f>'[64]MD20000.22-DEC'!$O$2</f>
+        <f>'[66]MD20000.22-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M47" s="19">
-        <f>'[64]MD20000.22-DEC'!$O$1</f>
+        <f>'[66]MD20000.22-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7760,15 +8205,15 @@
         <v>68</v>
       </c>
       <c r="E48" s="19">
-        <f>'[65]MD20000.22-DEC'!$C$1</f>
+        <f>'[67]MD20000.22-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F48" s="20">
-        <f>'[65]MD20000.22-DEC'!$K$1</f>
+        <f>'[67]MD20000.22-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G48" s="20">
-        <f>'[65]MD20000.22-DEC'!$K$2</f>
+        <f>'[67]MD20000.22-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H48" s="20"/>
@@ -7777,15 +8222,15 @@
         <v>77</v>
       </c>
       <c r="K48" s="22">
-        <f>'[65]MD20000.22-DEC'!$B$3</f>
+        <f>'[67]MD20000.22-DEC'!$B$3</f>
         <v>45473</v>
       </c>
       <c r="L48" s="19">
-        <f>'[65]MD20000.22-DEC'!$O$2</f>
+        <f>'[67]MD20000.22-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M48" s="19">
-        <f>'[65]MD20000.22-DEC'!$O$1</f>
+        <f>'[67]MD20000.22-DEC'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -7800,32 +8245,32 @@
         <v>50</v>
       </c>
       <c r="E49" s="19">
-        <f>'[66]MD20000.15-DEc'!$C$1</f>
+        <f>'[68]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F49" s="20"/>
       <c r="G49" s="20"/>
       <c r="H49" s="20">
-        <f>'[66]MD20000.15-DEc'!$K$1</f>
+        <f>'[68]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I49" s="20">
-        <f>'[66]MD20000.15-DEc'!$K$2</f>
+        <f>'[68]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J49" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K49" s="22">
-        <f>'[66]MD20000.15-DEc'!$B$3</f>
+        <f>'[68]MD20000.15-DEc'!$B$3</f>
         <v>45495</v>
       </c>
       <c r="L49" s="19">
-        <f>'[66]MD20000.15-DEc'!$O$2</f>
+        <f>'[68]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M49" s="19">
-        <f>'[66]MD20000.15-DEc'!$O$1</f>
+        <f>'[68]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7840,32 +8285,32 @@
         <v>75</v>
       </c>
       <c r="E50" s="19">
-        <f>'[67]MD20000.15-DEc'!$C$1</f>
+        <f>'[69]MD20000.15-DEc'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F50" s="20"/>
       <c r="G50" s="20"/>
       <c r="H50" s="20">
-        <f>'[67]MD20000.15-DEc'!$K$1</f>
+        <f>'[69]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I50" s="20">
-        <f>'[67]MD20000.15-DEc'!$K$2</f>
+        <f>'[69]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J50" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K50" s="22">
-        <f>'[67]MD20000.15-DEc'!$B$3</f>
+        <f>'[69]MD20000.15-DEc'!$B$3</f>
         <v>45496</v>
       </c>
       <c r="L50" s="19">
-        <f>'[67]MD20000.15-DEc'!$O$2</f>
+        <f>'[69]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M50" s="19">
-        <f>'[67]MD20000.15-DEc'!$O$1</f>
+        <f>'[69]MD20000.15-DEc'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -7880,15 +8325,15 @@
         <v>33</v>
       </c>
       <c r="E51" s="19">
-        <f>'[68]MD20000.18-DEC'!$C$1</f>
+        <f>'[70]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F51" s="20">
-        <f>'[68]MD20000.18-DEC'!$K$1</f>
+        <f>'[70]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G51" s="20">
-        <f>'[68]MD20000.18-DEC'!$K$2</f>
+        <f>'[70]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H51" s="20"/>
@@ -7897,15 +8342,15 @@
         <v>12</v>
       </c>
       <c r="K51" s="22">
-        <f>'[68]MD20000.18-DEC'!$B$3</f>
+        <f>'[70]MD20000.18-DEC'!$B$3</f>
         <v>45493</v>
       </c>
       <c r="L51" s="19">
-        <f>'[68]MD20000.18-DEC'!$O$2</f>
+        <f>'[70]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M51" s="19">
-        <f>'[68]MD20000.18-DEC'!$O$1</f>
+        <f>'[70]MD20000.18-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7920,32 +8365,32 @@
         <v>76</v>
       </c>
       <c r="E52" s="19">
-        <f>'[69]MD20000.15-DEc'!$C$1</f>
+        <f>'[71]MD20000.15-DEc'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F52" s="20"/>
       <c r="G52" s="20"/>
       <c r="H52" s="20">
-        <f>'[69]MD20000.15-DEc'!$K$1</f>
+        <f>'[71]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I52" s="20">
-        <f>'[69]MD20000.15-DEc'!$K$2</f>
+        <f>'[71]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J52" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K52" s="22">
-        <f>'[69]MD20000.15-DEc'!$B$3</f>
+        <f>'[71]MD20000.15-DEc'!$B$3</f>
         <v>45502</v>
       </c>
       <c r="L52" s="19">
-        <f>'[69]MD20000.15-DEc'!$O$2</f>
+        <f>'[71]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M52" s="19">
-        <f>'[69]MD20000.15-DEc'!$O$1</f>
+        <f>'[71]MD20000.15-DEc'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -7960,32 +8405,32 @@
         <v>50</v>
       </c>
       <c r="E53" s="19">
-        <f>'[70]MD50000.15-DEC'!$C$1</f>
+        <f>'[72]MD50000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F53" s="20"/>
       <c r="G53" s="20"/>
       <c r="H53" s="20">
-        <f>'[70]MD50000.15-DEC'!$K$1</f>
+        <f>'[72]MD50000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I53" s="20">
-        <f>'[70]MD50000.15-DEC'!$K$2</f>
+        <f>'[72]MD50000.15-DEC'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J53" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K53" s="22">
-        <f>'[70]MD50000.15-DEC'!$B$3</f>
+        <f>'[72]MD50000.15-DEC'!$B$3</f>
         <v>45504</v>
       </c>
       <c r="L53" s="19">
-        <f>'[70]MD50000.15-DEC'!$O$2</f>
+        <f>'[72]MD50000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M53" s="19">
-        <f>'[70]MD50000.15-DEC'!$O$1</f>
+        <f>'[72]MD50000.15-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -8000,32 +8445,32 @@
         <v>79</v>
       </c>
       <c r="E54" s="19">
-        <f>'[71]MD10000.20-OCT'!$C$1</f>
+        <f>'[73]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F54" s="20"/>
       <c r="G54" s="20"/>
       <c r="H54" s="20">
-        <f>'[71]MD10000.20-OCT'!$K$1</f>
+        <f>'[73]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I54" s="20">
-        <f>'[71]MD10000.20-OCT'!$K$2</f>
+        <f>'[73]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J54" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K54" s="22">
-        <f>'[71]MD10000.20-OCT'!$B$3</f>
+        <f>'[73]MD10000.20-OCT'!$B$3</f>
         <v>45511</v>
       </c>
       <c r="L54" s="19">
-        <f>'[71]MD10000.20-OCT'!$O$2</f>
+        <f>'[73]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M54" s="19">
-        <f>'[71]MD10000.20-OCT'!$O$1</f>
+        <f>'[73]MD10000.20-OCT'!$O$1</f>
         <v>5950</v>
       </c>
     </row>
@@ -8040,15 +8485,15 @@
         <v>80</v>
       </c>
       <c r="E55" s="19">
-        <f>'[72]MD20000.18-DEC'!$C$1</f>
+        <f>'[74]MD20000.18-DEC'!$C$1</f>
         <v>30000</v>
       </c>
       <c r="F55" s="20">
-        <f>'[72]MD20000.18-DEC'!$K$1</f>
+        <f>'[74]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G55" s="20">
-        <f>'[72]MD20000.18-DEC'!$K$2</f>
+        <f>'[74]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H55" s="20"/>
@@ -8057,15 +8502,15 @@
         <v>51</v>
       </c>
       <c r="K55" s="22">
-        <f>'[72]MD20000.18-DEC'!$B$3</f>
+        <f>'[74]MD20000.18-DEC'!$B$3</f>
         <v>45508</v>
       </c>
       <c r="L55" s="19">
-        <f>'[72]MD20000.18-DEC'!$O$2</f>
+        <f>'[74]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M55" s="19">
-        <f>'[72]MD20000.18-DEC'!$O$1</f>
+        <f>'[74]MD20000.18-DEC'!$O$1</f>
         <v>36000</v>
       </c>
     </row>
@@ -8080,15 +8525,15 @@
         <v>82</v>
       </c>
       <c r="E56" s="19">
-        <f>'[73]MD20000.18-DEC'!$C$1</f>
+        <f>'[75]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F56" s="20">
-        <f>'[73]MD20000.18-DEC'!$K$1</f>
+        <f>'[75]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G56" s="20">
-        <f>'[73]MD20000.18-DEC'!$K$2</f>
+        <f>'[75]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H56" s="20"/>
@@ -8097,15 +8542,15 @@
         <v>12</v>
       </c>
       <c r="K56" s="22">
-        <f>'[73]MD20000.18-DEC'!$B$3</f>
+        <f>'[75]MD20000.18-DEC'!$B$3</f>
         <v>45514</v>
       </c>
       <c r="L56" s="19">
-        <f>'[73]MD20000.18-DEC'!$O$2</f>
+        <f>'[75]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M56" s="19">
-        <f>'[73]MD20000.18-DEC'!$O$1</f>
+        <f>'[75]MD20000.18-DEC'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -8120,32 +8565,32 @@
         <v>52</v>
       </c>
       <c r="E57" s="19">
-        <f>'[74]MD20000.15-DEc'!$C$1</f>
+        <f>'[76]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F57" s="20"/>
       <c r="G57" s="20"/>
       <c r="H57" s="20">
-        <f>'[74]MD20000.15-DEc'!$K$1</f>
+        <f>'[76]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I57" s="20">
-        <f>'[74]MD20000.15-DEc'!$K$2</f>
+        <f>'[76]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J57" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K57" s="22">
-        <f>'[74]MD20000.15-DEc'!$B$3</f>
+        <f>'[76]MD20000.15-DEc'!$B$3</f>
         <v>45527</v>
       </c>
       <c r="L57" s="19">
-        <f>'[74]MD20000.15-DEc'!$O$2</f>
+        <f>'[76]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M57" s="19">
-        <f>'[74]MD20000.15-DEc'!$O$1</f>
+        <f>'[76]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -8160,32 +8605,32 @@
         <v>76</v>
       </c>
       <c r="E58" s="19">
-        <f>'[75]MD20000.15-DEc'!$C$1</f>
+        <f>'[77]MD20000.15-DEc'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F58" s="20"/>
       <c r="G58" s="20"/>
       <c r="H58" s="20">
-        <f>'[75]MD20000.15-DEc'!$K$1</f>
+        <f>'[77]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I58" s="20">
-        <f>'[75]MD20000.15-DEc'!$K$2</f>
+        <f>'[77]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J58" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K58" s="22">
-        <f>'[75]MD20000.15-DEc'!$B$3</f>
+        <f>'[77]MD20000.15-DEc'!$B$3</f>
         <v>45531</v>
       </c>
       <c r="L58" s="19">
-        <f>'[75]MD20000.15-DEc'!$O$2</f>
+        <f>'[77]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M58" s="19">
-        <f>'[75]MD20000.15-DEc'!$O$1</f>
+        <f>'[77]MD20000.15-DEc'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -8200,32 +8645,32 @@
         <v>85</v>
       </c>
       <c r="E59" s="19">
-        <f>'[76]MD10000.20-OCT'!$C$1</f>
+        <f>'[78]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F59" s="20"/>
       <c r="G59" s="20"/>
       <c r="H59" s="20">
-        <f>'[76]MD10000.20-OCT'!$K$1</f>
+        <f>'[78]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I59" s="20">
-        <f>'[76]MD10000.20-OCT'!$K$2</f>
+        <f>'[78]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J59" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K59" s="22">
-        <f>'[76]MD10000.20-OCT'!$B$3</f>
+        <f>'[78]MD10000.20-OCT'!$B$3</f>
         <v>45532</v>
       </c>
       <c r="L59" s="19">
-        <f>'[76]MD10000.20-OCT'!$O$2</f>
+        <f>'[78]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M59" s="19">
-        <f>'[76]MD10000.20-OCT'!$O$1</f>
+        <f>'[78]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -8240,32 +8685,32 @@
         <v>76</v>
       </c>
       <c r="E60" s="19">
-        <f>'[77]MD20000.15-DEc'!$C$1</f>
+        <f>'[79]MD20000.15-DEc'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F60" s="20"/>
       <c r="G60" s="20"/>
       <c r="H60" s="20">
-        <f>'[77]MD20000.15-DEc'!$K$1</f>
+        <f>'[79]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I60" s="20">
-        <f>'[77]MD20000.15-DEc'!$K$2</f>
+        <f>'[79]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J60" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K60" s="22">
-        <f>'[77]MD20000.15-DEc'!$B$3</f>
+        <f>'[79]MD20000.15-DEc'!$B$3</f>
         <v>45534</v>
       </c>
       <c r="L60" s="19">
-        <f>'[77]MD20000.15-DEc'!$O$2</f>
+        <f>'[79]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M60" s="19">
-        <f>'[77]MD20000.15-DEc'!$O$1</f>
+        <f>'[79]MD20000.15-DEc'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -8280,32 +8725,32 @@
         <v>87</v>
       </c>
       <c r="E61" s="19">
-        <f>'[78]MD10000.20-OCT'!$C$1</f>
+        <f>'[80]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F61" s="20"/>
       <c r="G61" s="20"/>
       <c r="H61" s="20">
-        <f>'[78]MD10000.20-OCT'!$K$1</f>
+        <f>'[80]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I61" s="20">
-        <f>'[78]MD10000.20-OCT'!$K$2</f>
+        <f>'[80]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J61" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K61" s="22">
-        <f>'[78]MD10000.20-OCT'!$B$3</f>
+        <f>'[80]MD10000.20-OCT'!$B$3</f>
         <v>45536</v>
       </c>
       <c r="L61" s="19">
-        <f>'[78]MD10000.20-OCT'!$O$2</f>
+        <f>'[80]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M61" s="19">
-        <f>'[78]MD10000.20-OCT'!$O$1</f>
+        <f>'[80]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -8320,15 +8765,15 @@
         <v>33</v>
       </c>
       <c r="E62" s="19">
-        <f>'[79]MD20000.22-DEC'!$C$1</f>
+        <f>'[81]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F62" s="20">
-        <f>'[79]MD20000.22-DEC'!$K$1</f>
+        <f>'[81]MD20000.22-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G62" s="20">
-        <f>'[79]MD20000.22-DEC'!$K$2</f>
+        <f>'[81]MD20000.22-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H62" s="20"/>
@@ -8337,15 +8782,15 @@
         <v>51</v>
       </c>
       <c r="K62" s="22">
-        <f>'[79]MD20000.22-DEC'!$B$3</f>
+        <f>'[81]MD20000.22-DEC'!$B$3</f>
         <v>45535</v>
       </c>
       <c r="L62" s="19">
-        <f>'[79]MD20000.22-DEC'!$O$2</f>
+        <f>'[81]MD20000.22-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M62" s="19">
-        <f>'[79]MD20000.22-DEC'!$O$1</f>
+        <f>'[81]MD20000.22-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -8360,32 +8805,32 @@
         <v>48</v>
       </c>
       <c r="E63" s="19">
-        <f>'[80]MD10000.20-OCT'!$C$1</f>
+        <f>'[82]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F63" s="20"/>
       <c r="G63" s="20"/>
       <c r="H63" s="20">
-        <f>'[80]MD10000.20-OCT'!$K$1</f>
+        <f>'[82]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I63" s="20">
-        <f>'[80]MD10000.20-OCT'!$K$2</f>
+        <f>'[82]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J63" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K63" s="22">
-        <f>'[80]MD10000.20-OCT'!$B$3</f>
+        <f>'[82]MD10000.20-OCT'!$B$3</f>
         <v>45549</v>
       </c>
       <c r="L63" s="19">
-        <f>'[80]MD10000.20-OCT'!$O$2</f>
+        <f>'[82]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M63" s="19">
-        <f>'[80]MD10000.20-OCT'!$O$1</f>
+        <f>'[82]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -8400,15 +8845,15 @@
         <v>90</v>
       </c>
       <c r="E64" s="19">
-        <f>'[81]MD20000.22-DEC'!$C$1</f>
+        <f>'[83]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F64" s="20">
-        <f>'[81]MD20000.22-DEC'!$K$1</f>
+        <f>'[83]MD20000.22-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G64" s="20">
-        <f>'[81]MD20000.22-DEC'!$K$2</f>
+        <f>'[83]MD20000.22-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H64" s="20"/>
@@ -8417,15 +8862,15 @@
         <v>12</v>
       </c>
       <c r="K64" s="22">
-        <f>'[81]MD20000.22-DEC'!$B$13</f>
+        <f>'[83]MD20000.22-DEC'!$B$13</f>
         <v>45562</v>
       </c>
       <c r="L64" s="19">
-        <f>'[81]MD20000.22-DEC'!$O$2</f>
+        <f>'[83]MD20000.22-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M64" s="19">
-        <f>'[81]MD20000.22-DEC'!$O$1</f>
+        <f>'[83]MD20000.22-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -8440,15 +8885,15 @@
         <v>68</v>
       </c>
       <c r="E65" s="19">
-        <f>'[82]MD10000.1-OCT'!$C$1</f>
+        <f>'[84]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F65" s="20">
-        <f>'[82]MD10000.1-OCT'!$K$1</f>
+        <f>'[84]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G65" s="20">
-        <f>'[82]MD10000.1-OCT'!$K$2</f>
+        <f>'[84]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H65" s="20"/>
@@ -8457,15 +8902,15 @@
         <v>12</v>
       </c>
       <c r="K65" s="22">
-        <f>'[82]MD10000.1-OCT'!$B$3</f>
+        <f>'[84]MD10000.1-OCT'!$B$3</f>
         <v>45557</v>
       </c>
       <c r="L65" s="19">
-        <f>'[82]MD10000.1-OCT'!$O$2</f>
+        <f>'[84]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M65" s="19">
-        <f>'[82]MD10000.1-OCT'!$O$1</f>
+        <f>'[84]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -8485,11 +8930,11 @@
       </c>
       <c r="F66" s="8">
         <f>'[2]MD10000.1-OCT'!$K$1</f>
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G66" s="8">
         <f>'[2]MD10000.1-OCT'!$K$2</f>
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
@@ -8502,11 +8947,11 @@
       </c>
       <c r="L66" s="7">
         <f>'[2]MD10000.1-OCT'!$O$2</f>
-        <v>2200</v>
+        <v>1100</v>
       </c>
       <c r="M66" s="7">
         <f>'[2]MD10000.1-OCT'!$O$1</f>
-        <v>9800</v>
+        <v>10900</v>
       </c>
       <c r="N66" s="1">
         <v>700</v>
@@ -8528,11 +8973,11 @@
       </c>
       <c r="F67" s="8">
         <f>'[3]MD10000.1-OCT'!$K$1</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G67" s="8">
         <f>'[3]MD10000.1-OCT'!$K$2</f>
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
@@ -8545,11 +8990,11 @@
       </c>
       <c r="L67" s="7">
         <f>'[3]MD10000.1-OCT'!$O$2</f>
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="M67" s="7">
         <f>'[3]MD10000.1-OCT'!$O$1</f>
-        <v>10600</v>
+        <v>10700</v>
       </c>
       <c r="N67" s="1">
         <v>700</v>
@@ -8566,15 +9011,15 @@
         <v>33</v>
       </c>
       <c r="E68" s="19">
-        <f>'[83]MD20000.18-DEC'!$C$1</f>
+        <f>'[85]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F68" s="20">
-        <f>'[83]MD20000.18-DEC'!$K$1</f>
+        <f>'[85]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G68" s="20">
-        <f>'[83]MD20000.18-DEC'!$K$2</f>
+        <f>'[85]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H68" s="20"/>
@@ -8583,15 +9028,15 @@
         <v>12</v>
       </c>
       <c r="K68" s="22">
-        <f>'[83]MD20000.18-DEC'!$B$3</f>
+        <f>'[85]MD20000.18-DEC'!$B$3</f>
         <v>45562</v>
       </c>
       <c r="L68" s="19">
-        <f>'[83]MD20000.18-DEC'!$O$2</f>
+        <f>'[85]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M68" s="19">
-        <f>'[83]MD20000.18-DEC'!$O$1</f>
+        <f>'[85]MD20000.18-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -8611,11 +9056,11 @@
       </c>
       <c r="F69" s="8">
         <f>'[4]MD10000.1-OCT'!$K$1</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G69" s="8">
         <f>'[4]MD10000.1-OCT'!$K$2</f>
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="H69" s="8"/>
       <c r="I69" s="8"/>
@@ -8628,11 +9073,11 @@
       </c>
       <c r="L69" s="7">
         <f>'[4]MD10000.1-OCT'!$O$2</f>
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="M69" s="7">
         <f>'[4]MD10000.1-OCT'!$O$1</f>
-        <v>10200</v>
+        <v>12000</v>
       </c>
       <c r="N69" s="1">
         <v>700</v>
@@ -8654,11 +9099,11 @@
       </c>
       <c r="F70" s="8">
         <f>'[5]MD10000.1-OCT'!$K$1</f>
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G70" s="8">
         <f>'[5]MD10000.1-OCT'!$K$2</f>
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
@@ -8671,11 +9116,11 @@
       </c>
       <c r="L70" s="7">
         <f>'[5]MD10000.1-OCT'!$O$2</f>
-        <v>7050</v>
+        <v>5250</v>
       </c>
       <c r="M70" s="7">
         <f>'[5]MD10000.1-OCT'!$O$1</f>
-        <v>10950</v>
+        <v>12750</v>
       </c>
       <c r="N70" s="1">
         <v>1050</v>
@@ -8692,15 +9137,15 @@
         <v>96</v>
       </c>
       <c r="E71" s="26">
-        <f>'[84]MD20000.18-DEC'!$C$1</f>
+        <f>'[86]MD20000.18-DEC'!$C$1</f>
         <v>50000</v>
       </c>
       <c r="F71" s="24">
-        <f>'[84]MD20000.18-DEC'!$K$1</f>
+        <f>'[86]MD20000.18-DEC'!$K$1</f>
         <v>66</v>
       </c>
       <c r="G71" s="24">
-        <f>'[84]MD20000.18-DEC'!$K$2</f>
+        <f>'[86]MD20000.18-DEC'!$K$2</f>
         <v>54</v>
       </c>
       <c r="H71" s="24"/>
@@ -8709,15 +9154,15 @@
         <v>12</v>
       </c>
       <c r="K71" s="25">
-        <f>'[84]MD20000.18-DEC'!$B$3</f>
+        <f>'[86]MD20000.18-DEC'!$B$3</f>
         <v>45579</v>
       </c>
       <c r="L71" s="26">
-        <f>'[84]MD20000.18-DEC'!$O$2</f>
+        <f>'[86]MD20000.18-DEC'!$O$2</f>
         <v>33000</v>
       </c>
       <c r="M71" s="26">
-        <f>'[84]MD20000.18-DEC'!$O$1</f>
+        <f>'[86]MD20000.18-DEC'!$O$1</f>
         <v>27000</v>
       </c>
     </row>
@@ -8739,11 +9184,11 @@
       <c r="G72" s="8"/>
       <c r="H72" s="8">
         <f>'[6]MD20000.18-DEC'!$K$1</f>
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I72" s="8">
         <f>'[6]MD20000.18-DEC'!$K$2</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J72" s="9" t="s">
         <v>12</v>
@@ -8754,11 +9199,11 @@
       </c>
       <c r="L72" s="7">
         <f>'[6]MD20000.18-DEC'!$O$2</f>
-        <v>108000</v>
+        <v>100000</v>
       </c>
       <c r="M72" s="7">
         <f>'[6]MD20000.18-DEC'!$O$1</f>
-        <v>52000</v>
+        <v>60000</v>
       </c>
       <c r="N72" s="1">
         <v>4000</v>
@@ -8775,15 +9220,15 @@
         <v>96</v>
       </c>
       <c r="E73" s="19">
-        <f>'[85]MD20000.18-DEC'!$C$1</f>
+        <f>'[87]MD20000.18-DEC'!$C$1</f>
         <v>50000</v>
       </c>
       <c r="F73" s="20">
-        <f>'[85]MD20000.18-DEC'!$K$1</f>
+        <f>'[87]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G73" s="20">
-        <f>'[85]MD20000.18-DEC'!$K$2</f>
+        <f>'[87]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H73" s="20"/>
@@ -8792,15 +9237,15 @@
         <v>12</v>
       </c>
       <c r="K73" s="22">
-        <f>'[85]MD20000.18-DEC'!$B$3</f>
+        <f>'[87]MD20000.18-DEC'!$B$3</f>
         <v>45584</v>
       </c>
       <c r="L73" s="19">
-        <f>'[85]MD20000.18-DEC'!$O$2</f>
+        <f>'[87]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M73" s="19">
-        <f>'[85]MD20000.18-DEC'!$O$1</f>
+        <f>'[87]MD20000.18-DEC'!$O$1</f>
         <v>60000</v>
       </c>
     </row>
@@ -8815,15 +9260,15 @@
         <v>90</v>
       </c>
       <c r="E74" s="19">
-        <f>'[86]MD20000.18-DEC'!$C$1</f>
+        <f>'[88]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F74" s="20">
-        <f>'[86]MD20000.18-DEC'!$K$1</f>
+        <f>'[88]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G74" s="20">
-        <f>'[86]MD20000.18-DEC'!$K$2</f>
+        <f>'[88]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H74" s="20"/>
@@ -8832,15 +9277,15 @@
         <v>12</v>
       </c>
       <c r="K74" s="22">
-        <f>'[86]MD20000.18-DEC'!$B$3</f>
+        <f>'[88]MD20000.18-DEC'!$B$3</f>
         <v>45584</v>
       </c>
       <c r="L74" s="19">
-        <f>'[86]MD20000.18-DEC'!$O$2</f>
+        <f>'[88]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M74" s="19">
-        <f>'[86]MD20000.18-DEC'!$O$1</f>
+        <f>'[88]MD20000.18-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -8898,15 +9343,15 @@
         <v>90</v>
       </c>
       <c r="E76" s="19">
-        <f>'[87]MD20000.18-DEC'!$C$1</f>
+        <f>'[89]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F76" s="20">
-        <f>'[87]MD20000.18-DEC'!$K$1</f>
+        <f>'[89]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G76" s="20">
-        <f>'[87]MD20000.18-DEC'!$K$2</f>
+        <f>'[89]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H76" s="20"/>
@@ -8915,15 +9360,15 @@
         <v>12</v>
       </c>
       <c r="K76" s="22">
-        <f>'[87]MD20000.18-DEC'!$B$3</f>
+        <f>'[89]MD20000.18-DEC'!$B$3</f>
         <v>45584</v>
       </c>
       <c r="L76" s="19">
-        <f>'[87]MD20000.18-DEC'!$O$2</f>
+        <f>'[89]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M76" s="19">
-        <f>'[87]MD20000.18-DEC'!$O$1</f>
+        <f>'[89]MD20000.18-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -8943,11 +9388,11 @@
       </c>
       <c r="F77" s="8">
         <f>'[8]MD20000.18-DEC'!$K$1</f>
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="G77" s="8">
         <f>'[8]MD20000.18-DEC'!$K$2</f>
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="H77" s="8"/>
       <c r="I77" s="8"/>
@@ -8960,11 +9405,11 @@
       </c>
       <c r="L77" s="7">
         <f>'[8]MD20000.18-DEC'!$O$2</f>
-        <v>7200</v>
+        <v>2000</v>
       </c>
       <c r="M77" s="7">
         <f>'[8]MD20000.18-DEC'!$O$1</f>
-        <v>16800</v>
+        <v>22000</v>
       </c>
       <c r="N77" s="1">
         <v>1400</v>
@@ -8986,11 +9431,11 @@
       </c>
       <c r="F78" s="8">
         <f>'[9]MD20000.18-DEC'!$K$1</f>
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="G78" s="8">
         <f>'[9]MD20000.18-DEC'!$K$2</f>
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="H78" s="8"/>
       <c r="I78" s="8"/>
@@ -9003,11 +9448,11 @@
       </c>
       <c r="L78" s="7">
         <f>'[9]MD20000.18-DEC'!$O$2</f>
-        <v>9400</v>
+        <v>6900</v>
       </c>
       <c r="M78" s="7">
         <f>'[9]MD20000.18-DEC'!$O$1</f>
-        <v>2600</v>
+        <v>5100</v>
       </c>
       <c r="N78" s="1">
         <v>700</v>
@@ -9029,11 +9474,11 @@
       </c>
       <c r="F79" s="8">
         <f>'[10]MD20000.18-DEC'!$K$1</f>
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="G79" s="8">
         <f>'[10]MD20000.18-DEC'!$K$2</f>
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="H79" s="8"/>
       <c r="I79" s="8"/>
@@ -9046,11 +9491,11 @@
       </c>
       <c r="L79" s="7">
         <f>'[10]MD20000.18-DEC'!$O$2</f>
-        <v>7500</v>
+        <v>6800</v>
       </c>
       <c r="M79" s="7">
         <f>'[10]MD20000.18-DEC'!$O$1</f>
-        <v>4500</v>
+        <v>5200</v>
       </c>
       <c r="N79" s="1">
         <v>700</v>
@@ -9067,15 +9512,15 @@
         <v>68</v>
       </c>
       <c r="E80" s="19">
-        <f>'[88]MD20000.18-DEC'!$C$1</f>
+        <f>'[90]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F80" s="20">
-        <f>'[88]MD20000.18-DEC'!$K$1</f>
+        <f>'[90]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G80" s="20">
-        <f>'[88]MD20000.18-DEC'!$K$2</f>
+        <f>'[90]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H80" s="20"/>
@@ -9084,15 +9529,15 @@
         <v>12</v>
       </c>
       <c r="K80" s="22">
-        <f>'[88]MD20000.18-DEC'!$B$3</f>
+        <f>'[90]MD20000.18-DEC'!$B$3</f>
         <v>45587</v>
       </c>
       <c r="L80" s="19">
-        <f>'[88]MD20000.18-DEC'!$O$2</f>
+        <f>'[90]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M80" s="19">
-        <f>'[88]MD20000.18-DEC'!$O$1</f>
+        <f>'[90]MD20000.18-DEC'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -9114,11 +9559,11 @@
       <c r="G81" s="8"/>
       <c r="H81" s="8">
         <f>'[11]MD20000.15-DEc'!$K$1</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I81" s="8">
         <f>'[11]MD20000.15-DEc'!$K$2</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J81" s="9" t="s">
         <v>12</v>
@@ -9129,11 +9574,11 @@
       </c>
       <c r="L81" s="7">
         <f>'[11]MD20000.15-DEc'!$O$2</f>
-        <v>7000</v>
+        <v>2800</v>
       </c>
       <c r="M81" s="7">
         <f>'[11]MD20000.15-DEc'!$O$1</f>
-        <v>17000</v>
+        <v>21200</v>
       </c>
       <c r="N81" s="1">
         <v>1400</v>
@@ -9157,11 +9602,11 @@
       <c r="G82" s="8"/>
       <c r="H82" s="8">
         <f>'[12]MD10000.10-JAN'!$K$1</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I82" s="8">
         <f>'[12]MD10000.10-JAN'!$K$2</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J82" s="9" t="s">
         <v>12</v>
@@ -9172,11 +9617,11 @@
       </c>
       <c r="L82" s="7">
         <f>'[12]MD10000.10-JAN'!$O$2</f>
-        <v>8400</v>
+        <v>5600</v>
       </c>
       <c r="M82" s="7">
         <f>'[12]MD10000.10-JAN'!$O$1</f>
-        <v>15600</v>
+        <v>18400</v>
       </c>
       <c r="N82" s="1">
         <v>1400</v>
@@ -9193,15 +9638,15 @@
         <v>90</v>
       </c>
       <c r="E83" s="19">
-        <f>'[89]MD20000.22-DEC'!$C$1</f>
+        <f>'[91]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F83" s="20">
-        <f>'[89]MD20000.22-DEC'!$K$1</f>
+        <f>'[91]MD20000.22-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G83" s="20">
-        <f>'[89]MD20000.22-DEC'!$K$2</f>
+        <f>'[91]MD20000.22-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H83" s="20"/>
@@ -9210,15 +9655,15 @@
         <v>12</v>
       </c>
       <c r="K83" s="22">
-        <f>'[89]MD20000.22-DEC'!$B$3</f>
+        <f>'[91]MD20000.22-DEC'!$B$3</f>
         <v>45597</v>
       </c>
       <c r="L83" s="19">
-        <f>'[89]MD20000.22-DEC'!$O$2</f>
+        <f>'[91]MD20000.22-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M83" s="19">
-        <f>'[89]MD20000.22-DEC'!$O$1</f>
+        <f>'[91]MD20000.22-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -9233,15 +9678,15 @@
         <v>80</v>
       </c>
       <c r="E84" s="19">
-        <f>'[90]MD20000.18-DEC'!$C$1</f>
+        <f>'[92]MD20000.18-DEC'!$C$1</f>
         <v>30000</v>
       </c>
       <c r="F84" s="20">
-        <f>'[90]MD20000.18-DEC'!$K$1</f>
+        <f>'[92]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G84" s="20">
-        <f>'[90]MD20000.18-DEC'!$K$2</f>
+        <f>'[92]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H84" s="20"/>
@@ -9250,15 +9695,15 @@
         <v>12</v>
       </c>
       <c r="K84" s="22">
-        <f>'[90]MD20000.18-DEC'!$B$3</f>
+        <f>'[92]MD20000.18-DEC'!$B$3</f>
         <v>45602</v>
       </c>
       <c r="L84" s="19">
-        <f>'[90]MD20000.18-DEC'!$O$2</f>
+        <f>'[92]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M84" s="19">
-        <f>'[90]MD20000.18-DEC'!$O$1</f>
+        <f>'[92]MD20000.18-DEC'!$O$1</f>
         <v>36000</v>
       </c>
     </row>
@@ -9273,15 +9718,15 @@
         <v>109</v>
       </c>
       <c r="E85" s="26">
-        <f>'[91]MD20000.18-DEC'!$C$1</f>
+        <f>'[93]MD20000.18-DEC'!$C$1</f>
         <v>50000</v>
       </c>
       <c r="F85" s="24">
-        <f>'[91]MD20000.18-DEC'!$K$1</f>
+        <f>'[93]MD20000.18-DEC'!$K$1</f>
         <v>100</v>
       </c>
       <c r="G85" s="24">
-        <f>'[91]MD20000.18-DEC'!$K$2</f>
+        <f>'[93]MD20000.18-DEC'!$K$2</f>
         <v>20</v>
       </c>
       <c r="H85" s="24"/>
@@ -9290,15 +9735,15 @@
         <v>12</v>
       </c>
       <c r="K85" s="25">
-        <f>'[91]MD20000.18-DEC'!$B$3</f>
+        <f>'[93]MD20000.18-DEC'!$B$3</f>
         <v>45612</v>
       </c>
       <c r="L85" s="26">
-        <f>'[91]MD20000.18-DEC'!$O$2</f>
+        <f>'[93]MD20000.18-DEC'!$O$2</f>
         <v>50000</v>
       </c>
       <c r="M85" s="26">
-        <f>'[91]MD20000.18-DEC'!$O$1</f>
+        <f>'[93]MD20000.18-DEC'!$O$1</f>
         <v>10000</v>
       </c>
     </row>
@@ -9318,11 +9763,11 @@
       </c>
       <c r="F86" s="8">
         <f>'[13]MD20000.18-DEC'!$K$1</f>
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="G86" s="8">
         <f>'[13]MD20000.18-DEC'!$K$2</f>
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="H86" s="8"/>
       <c r="I86" s="8"/>
@@ -9335,11 +9780,11 @@
       </c>
       <c r="L86" s="7">
         <f>'[13]MD20000.18-DEC'!$O$2</f>
-        <v>5800</v>
+        <v>4100</v>
       </c>
       <c r="M86" s="7">
         <f>'[13]MD20000.18-DEC'!$O$1</f>
-        <v>6200</v>
+        <v>7900</v>
       </c>
       <c r="N86" s="1">
         <v>700</v>
@@ -9361,11 +9806,11 @@
       </c>
       <c r="F87" s="8">
         <f>'[14]MD50000.15-DEC'!$K$1</f>
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="G87" s="8">
         <f>'[14]MD50000.15-DEC'!$K$2</f>
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H87" s="8"/>
       <c r="I87" s="8"/>
@@ -9378,11 +9823,11 @@
       </c>
       <c r="L87" s="7">
         <f>'[14]MD50000.15-DEC'!$O$2</f>
-        <v>136800</v>
+        <v>131400</v>
       </c>
       <c r="M87" s="7">
         <f>'[14]MD50000.15-DEC'!$O$1</f>
-        <v>23400</v>
+        <v>28800</v>
       </c>
       <c r="N87" s="1">
         <v>4200</v>
@@ -9404,11 +9849,11 @@
       </c>
       <c r="F88" s="8">
         <f>'[15]MD20000.18-DEC'!$K$1</f>
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="G88" s="8">
         <f>'[15]MD20000.18-DEC'!$K$2</f>
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="H88" s="8"/>
       <c r="I88" s="8"/>
@@ -9421,11 +9866,11 @@
       </c>
       <c r="L88" s="7">
         <f>'[15]MD20000.18-DEC'!$O$2</f>
-        <v>37000</v>
+        <v>27000</v>
       </c>
       <c r="M88" s="7">
         <f>'[15]MD20000.18-DEC'!$O$1</f>
-        <v>23000</v>
+        <v>33000</v>
       </c>
       <c r="N88" s="1">
         <v>3500</v>
@@ -9442,15 +9887,15 @@
         <v>80</v>
       </c>
       <c r="E89" s="19">
-        <f>'[92]MD20000.18-DEC'!$C$1</f>
+        <f>'[94]MD20000.18-DEC'!$C$1</f>
         <v>30000</v>
       </c>
       <c r="F89" s="20">
-        <f>'[92]MD20000.18-DEC'!$K$1</f>
+        <f>'[94]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G89" s="20">
-        <f>'[92]MD20000.18-DEC'!$K$2</f>
+        <f>'[94]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H89" s="20"/>
@@ -9459,15 +9904,15 @@
         <v>12</v>
       </c>
       <c r="K89" s="22">
-        <f>'[92]MD20000.18-DEC'!$B$3</f>
+        <f>'[94]MD20000.18-DEC'!$B$3</f>
         <v>45647</v>
       </c>
       <c r="L89" s="19">
-        <f>'[92]MD20000.18-DEC'!$O$2</f>
+        <f>'[94]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M89" s="19">
-        <f>'[92]MD20000.18-DEC'!$O$1</f>
+        <f>'[94]MD20000.18-DEC'!$O$1</f>
         <v>36000</v>
       </c>
     </row>
@@ -9487,11 +9932,11 @@
       </c>
       <c r="F90" s="8">
         <f>'[16]MD20000.18-DEC'!$K$1</f>
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="G90" s="8">
         <f>'[16]MD20000.18-DEC'!$K$2</f>
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="H90" s="8"/>
       <c r="I90" s="8"/>
@@ -9504,11 +9949,11 @@
       </c>
       <c r="L90" s="7">
         <f>'[16]MD20000.18-DEC'!$O$2</f>
-        <v>7900</v>
+        <v>6300</v>
       </c>
       <c r="M90" s="7">
         <f>'[16]MD20000.18-DEC'!$O$1</f>
-        <v>4100</v>
+        <v>5700</v>
       </c>
       <c r="N90" s="1">
         <v>700</v>
@@ -9530,11 +9975,11 @@
       </c>
       <c r="F91" s="8">
         <f>'[17]MD20000.18-DEC'!$K$1</f>
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="G91" s="8">
         <f>'[17]MD20000.18-DEC'!$K$2</f>
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="H91" s="8"/>
       <c r="I91" s="8"/>
@@ -9547,11 +9992,11 @@
       </c>
       <c r="L91" s="7">
         <f>'[17]MD20000.18-DEC'!$O$2</f>
-        <v>7900</v>
+        <v>6300</v>
       </c>
       <c r="M91" s="7">
         <f>'[17]MD20000.18-DEC'!$O$1</f>
-        <v>4100</v>
+        <v>5700</v>
       </c>
       <c r="N91" s="1">
         <v>700</v>
@@ -9573,11 +10018,11 @@
       </c>
       <c r="F92" s="8">
         <f>'[18]MD50000.15-DEC'!$K$1</f>
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="G92" s="8">
         <f>'[18]MD50000.15-DEC'!$K$2</f>
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="H92" s="8"/>
       <c r="I92" s="8"/>
@@ -9590,11 +10035,11 @@
       </c>
       <c r="L92" s="7">
         <f>'[18]MD50000.15-DEC'!$O$2</f>
-        <v>300000</v>
+        <v>276000</v>
       </c>
       <c r="M92" s="7">
         <f>'[18]MD50000.15-DEC'!$O$1</f>
-        <v>20400</v>
+        <v>44400</v>
       </c>
       <c r="N92" s="1">
         <v>8400</v>
@@ -9618,11 +10063,11 @@
       <c r="G93" s="8"/>
       <c r="H93" s="8">
         <f>'[19]MD20000.15-DEc'!$K$1</f>
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I93" s="8">
         <f>'[19]MD20000.15-DEc'!$K$2</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J93" s="9" t="s">
         <v>12</v>
@@ -9633,11 +10078,11 @@
       </c>
       <c r="L93" s="7">
         <f>'[19]MD20000.15-DEc'!$O$2</f>
-        <v>9900</v>
+        <v>6400</v>
       </c>
       <c r="M93" s="7">
         <f>'[19]MD20000.15-DEc'!$O$1</f>
-        <v>2100</v>
+        <v>5600</v>
       </c>
       <c r="N93" s="1">
         <v>700</v>
@@ -9659,11 +10104,11 @@
       </c>
       <c r="F94" s="8">
         <f>'[20]MD50000.15-DEC'!$K$1</f>
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="G94" s="8">
         <f>'[20]MD50000.15-DEC'!$K$2</f>
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="H94" s="8"/>
       <c r="I94" s="8"/>
@@ -9676,11 +10121,11 @@
       </c>
       <c r="L94" s="7">
         <f>'[20]MD50000.15-DEC'!$O$2</f>
-        <v>52000</v>
+        <v>41500</v>
       </c>
       <c r="M94" s="7">
         <f>'[20]MD50000.15-DEC'!$O$1</f>
-        <v>8000</v>
+        <v>18500</v>
       </c>
       <c r="N94" s="1">
         <v>3500</v>

--- a/LoanOfficer-A/LoanBook.xlsx
+++ b/LoanOfficer-A/LoanBook.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3600" windowWidth="20520" windowHeight="4425"/>
+    <workbookView xWindow="0" yWindow="3600" windowWidth="15360" windowHeight="4410"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="7" r:id="rId1"/>
@@ -109,13 +109,14 @@
     <externalReference r:id="rId98"/>
     <externalReference r:id="rId99"/>
     <externalReference r:id="rId100"/>
+    <externalReference r:id="rId101"/>
   </externalReferences>
   <calcPr calcId="145621" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="130">
   <si>
     <t>Code</t>
   </si>
@@ -502,6 +503,9 @@
   </si>
   <si>
     <t>L35000p120</t>
+  </si>
+  <si>
+    <t>Athokpam manao</t>
   </si>
 </sst>
 </file>
@@ -739,6 +743,7 @@
     <xf numFmtId="164" fontId="3" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -760,7 +765,6 @@
     <xf numFmtId="165" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -808,15 +812,15 @@
             <v>48</v>
           </cell>
           <cell r="O1">
-            <v>14700</v>
+            <v>15400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>42</v>
+            <v>44</v>
           </cell>
           <cell r="O2">
-            <v>2100</v>
+            <v>1400</v>
           </cell>
         </row>
         <row r="3">
@@ -839,25 +843,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>68</v>
+            <v>60</v>
           </cell>
           <cell r="O1">
-            <v>5200</v>
+            <v>6000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>52</v>
+            <v>60</v>
           </cell>
           <cell r="O2">
-            <v>6800</v>
+            <v>6000</v>
           </cell>
         </row>
         <row r="3">
@@ -872,6 +876,46 @@
 </file>
 
 <file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>68</v>
+          </cell>
+          <cell r="O1">
+            <v>5200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>52</v>
+          </cell>
+          <cell r="O2">
+            <v>6800</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45584</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -880,25 +924,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>2</v>
+            <v>1</v>
           </cell>
           <cell r="O1">
-            <v>21200</v>
+            <v>22600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>15</v>
+            <v>16</v>
           </cell>
           <cell r="O2">
-            <v>2800</v>
+            <v>1400</v>
           </cell>
         </row>
         <row r="3">
@@ -907,13 +951,13 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -929,18 +973,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>4</v>
+            <v>2</v>
           </cell>
           <cell r="O1">
-            <v>18400</v>
+            <v>21200</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>13</v>
+            <v>15</v>
           </cell>
           <cell r="O2">
-            <v>5600</v>
+            <v>2800</v>
           </cell>
         </row>
         <row r="3">
@@ -955,7 +999,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -963,25 +1007,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>41</v>
+            <v>34</v>
           </cell>
           <cell r="O1">
-            <v>7900</v>
+            <v>8600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>79</v>
+            <v>86</v>
           </cell>
           <cell r="O2">
-            <v>4100</v>
+            <v>3400</v>
           </cell>
         </row>
         <row r="3">
@@ -995,7 +1039,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1004,25 +1048,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>100000</v>
           </cell>
           <cell r="K1">
-            <v>219</v>
+            <v>216</v>
           </cell>
           <cell r="O1">
-            <v>28800</v>
+            <v>30600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>48</v>
+            <v>51</v>
           </cell>
           <cell r="O2">
-            <v>131400</v>
+            <v>129600</v>
           </cell>
         </row>
         <row r="3">
@@ -1031,47 +1075,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>50000</v>
-          </cell>
-          <cell r="K1">
-            <v>54</v>
-          </cell>
-          <cell r="O1">
-            <v>33000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>66</v>
-          </cell>
-          <cell r="O2">
-            <v>27000</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45628</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1085,30 +1089,30 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
-            <v>10000</v>
+            <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>63</v>
+            <v>46</v>
           </cell>
           <cell r="O1">
-            <v>5700</v>
+            <v>37000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>57</v>
+            <v>74</v>
           </cell>
           <cell r="O2">
-            <v>6300</v>
+            <v>23000</v>
           </cell>
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45635</v>
+            <v>45628</v>
           </cell>
         </row>
       </sheetData>
@@ -1125,25 +1129,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>63</v>
+            <v>57</v>
           </cell>
           <cell r="O1">
-            <v>5700</v>
+            <v>6300</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>57</v>
+            <v>63</v>
           </cell>
           <cell r="O2">
-            <v>6300</v>
+            <v>5700</v>
           </cell>
         </row>
         <row r="3">
@@ -1158,6 +1162,46 @@
 </file>
 
 <file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>57</v>
+          </cell>
+          <cell r="O1">
+            <v>6300</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>63</v>
+          </cell>
+          <cell r="O2">
+            <v>5700</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45635</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1173,18 +1217,18 @@
             <v>200000</v>
           </cell>
           <cell r="K1">
-            <v>230</v>
+            <v>226</v>
           </cell>
           <cell r="O1">
-            <v>44400</v>
+            <v>49200</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>37</v>
+            <v>41</v>
           </cell>
           <cell r="O2">
-            <v>276000</v>
+            <v>271200</v>
           </cell>
         </row>
         <row r="3">
@@ -1199,7 +1243,47 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>11</v>
+          </cell>
+          <cell r="O1">
+            <v>10900</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>109</v>
+          </cell>
+          <cell r="O2">
+            <v>1100</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45557</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1208,7 +1292,7 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -1235,89 +1319,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.1-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>11</v>
-          </cell>
-          <cell r="O1">
-            <v>10900</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>109</v>
-          </cell>
-          <cell r="O2">
-            <v>1100</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45557</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD50000.15-DEC"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>50000</v>
-          </cell>
-          <cell r="K1">
-            <v>83</v>
-          </cell>
-          <cell r="O1">
-            <v>18500</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>37</v>
-          </cell>
-          <cell r="O2">
-            <v>41500</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45652</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1332,34 +1334,34 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
+            <v>50000</v>
+          </cell>
+          <cell r="K1">
+            <v>80</v>
+          </cell>
+          <cell r="O1">
             <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>17</v>
-          </cell>
-          <cell r="O1">
-            <v>2800</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>2</v>
+            <v>40</v>
           </cell>
           <cell r="O2">
-            <v>21000</v>
+            <v>40000</v>
           </cell>
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45678</v>
+            <v>45652</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1374,7 +1376,7 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -1384,30 +1386,232 @@
             <v>17</v>
           </cell>
           <cell r="O1">
-            <v>2800</v>
+            <v>5600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>2</v>
+            <v>4</v>
           </cell>
           <cell r="O2">
-            <v>21000</v>
+            <v>18200</v>
           </cell>
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45683</v>
+            <v>45678</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
 <file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD50000.15-DEC"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>17</v>
+          </cell>
+          <cell r="O1">
+            <v>4200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>3</v>
+          </cell>
+          <cell r="O2">
+            <v>19600</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45683</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>50000</v>
+          </cell>
+          <cell r="K1">
+            <v>105</v>
+          </cell>
+          <cell r="O1">
+            <v>7500</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>15</v>
+          </cell>
+          <cell r="O2">
+            <v>52500</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45684</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>110</v>
+          </cell>
+          <cell r="O1">
+            <v>1000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>10</v>
+          </cell>
+          <cell r="O2">
+            <v>11000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45690</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>35000</v>
+          </cell>
+          <cell r="K1">
+            <v>114</v>
+          </cell>
+          <cell r="O1">
+            <v>2100</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>6</v>
+          </cell>
+          <cell r="O2">
+            <v>39900</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45696</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>116</v>
+          </cell>
+          <cell r="O1">
+            <v>800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>4</v>
+          </cell>
+          <cell r="O2">
+            <v>23200</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45699</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1484,7 +1688,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1524,7 +1728,47 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>9</v>
+          </cell>
+          <cell r="O1">
+            <v>11100</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>111</v>
+          </cell>
+          <cell r="O2">
+            <v>900</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45561</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1564,7 +1808,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1604,7 +1848,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1646,7 +1890,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1686,7 +1930,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1728,47 +1972,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.1-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>13</v>
-          </cell>
-          <cell r="O1">
-            <v>10700</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>107</v>
-          </cell>
-          <cell r="O2">
-            <v>1300</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45561</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1810,7 +2014,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1852,7 +2056,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1894,7 +2098,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1934,7 +2138,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1966,7 +2170,47 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45563</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2008,7 +2252,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2048,7 +2292,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2090,7 +2334,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2132,7 +2376,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2172,47 +2416,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.1-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>12000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45563</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2252,7 +2456,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2294,7 +2498,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2336,7 +2540,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2376,7 +2580,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2416,7 +2620,47 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>15000</v>
+          </cell>
+          <cell r="K1">
+            <v>35</v>
+          </cell>
+          <cell r="O1">
+            <v>12750</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>85</v>
+          </cell>
+          <cell r="O2">
+            <v>5250</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45570</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2456,7 +2700,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2492,7 +2736,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2520,7 +2764,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2562,7 +2806,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2602,47 +2846,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.1-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>15000</v>
-          </cell>
-          <cell r="K1">
-            <v>35</v>
-          </cell>
-          <cell r="O1">
-            <v>12750</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>85</v>
-          </cell>
-          <cell r="O2">
-            <v>5250</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45570</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2684,7 +2888,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2726,7 +2930,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2768,7 +2972,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2810,7 +3014,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2852,7 +3056,47 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>100000</v>
+          </cell>
+          <cell r="K1">
+            <v>24</v>
+          </cell>
+          <cell r="O1">
+            <v>64000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>16</v>
+          </cell>
+          <cell r="O2">
+            <v>96000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45590</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2892,7 +3136,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2931,7 +3175,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2954,7 +3198,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2994,7 +3238,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3034,47 +3278,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>100000</v>
-          </cell>
-          <cell r="K1">
-            <v>25</v>
-          </cell>
-          <cell r="O1">
-            <v>60000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>15</v>
-          </cell>
-          <cell r="O2">
-            <v>100000</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45590</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3106,181 +3310,6 @@
         <row r="3">
           <cell r="B3">
             <v>45436</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.22-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45432</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.1-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="G1">
-            <v>120</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>12000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45437</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.20-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>5000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>5950</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45444</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.1-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45450</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.1-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>12000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
           </cell>
         </row>
       </sheetData>
@@ -3320,7 +3349,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45446</v>
+            <v>45432</v>
           </cell>
         </row>
       </sheetData>
@@ -3330,6 +3359,221 @@
 </file>
 
 <file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="G1">
+            <v>120</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45437</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.20-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>5000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>5950</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45444</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45450</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>82</v>
+          </cell>
+          <cell r="O1">
+            <v>7600</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>38</v>
+          </cell>
+          <cell r="O2">
+            <v>16400</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45584</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink71.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.22-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45446</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink72.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3369,7 +3613,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink73.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3411,7 +3655,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink74.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3453,7 +3697,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink75.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3468,23 +3712,23 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>82</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
-            <v>7600</v>
+            <v>24000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>38</v>
+            <v>120</v>
           </cell>
           <cell r="O2">
-            <v>16400</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45584</v>
+            <v>45493</v>
           </cell>
         </row>
       </sheetData>
@@ -3493,47 +3737,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45493</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink71.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink76.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3575,7 +3779,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink72.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink77.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3617,7 +3821,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink73.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink78.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3657,7 +3861,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink74.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink79.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3697,7 +3901,33 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink75.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink80.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3737,7 +3967,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink76.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink81.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3779,7 +4009,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink77.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink82.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3821,7 +4051,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink78.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink83.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3861,7 +4091,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink79.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink84.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3903,7 +4133,247 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink85.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.20-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>5000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>6000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45536</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink86.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.22-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45535</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink87.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.20-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>5000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>6000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45549</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink88.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.22-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="B13">
+            <v>45562</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink89.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45557</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>5</v>
+          </cell>
+          <cell r="O1">
+            <v>23000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>115</v>
+          </cell>
+          <cell r="O2">
+            <v>1000</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7">
+            <v>45587</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink90.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3918,23 +4388,23 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>10</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
-            <v>22000</v>
+            <v>24000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>110</v>
+            <v>120</v>
           </cell>
           <cell r="O2">
-            <v>2000</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7">
-            <v>45587</v>
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45562</v>
           </cell>
         </row>
       </sheetData>
@@ -3943,30 +4413,70 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink80.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink91.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
-      <sheetName val="MD10000.20-OCT"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>50000</v>
+          </cell>
+          <cell r="K1">
+            <v>66</v>
+          </cell>
+          <cell r="O1">
+            <v>27000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>54</v>
+          </cell>
+          <cell r="O2">
+            <v>33000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45579</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink92.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
-            <v>5000</v>
+            <v>50000</v>
           </cell>
           <cell r="K1">
             <v>0</v>
           </cell>
           <cell r="O1">
-            <v>6000</v>
+            <v>60000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>17</v>
+            <v>120</v>
           </cell>
           <cell r="O2">
             <v>0</v>
@@ -3974,7 +4484,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45536</v>
+            <v>45584</v>
           </cell>
         </row>
       </sheetData>
@@ -3983,7 +4493,125 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink81.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink93.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45584</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink94.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45584</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink95.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45587</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink96.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4014,7 +4642,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45535</v>
+            <v>45597</v>
           </cell>
         </row>
       </sheetData>
@@ -4023,127 +4651,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink82.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.20-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>5000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>6000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45549</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink83.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.22-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13">
-            <v>45562</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink84.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.1-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>12000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45557</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink85.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink97.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4155,13 +4663,13 @@
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
-            <v>20000</v>
+            <v>30000</v>
           </cell>
           <cell r="K1">
             <v>0</v>
           </cell>
           <cell r="O1">
-            <v>24000</v>
+            <v>36000</v>
           </cell>
         </row>
         <row r="2">
@@ -4174,7 +4682,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45562</v>
+            <v>45602</v>
           </cell>
         </row>
       </sheetData>
@@ -4183,7 +4691,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink86.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink98.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4198,23 +4706,23 @@
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>66</v>
+            <v>100</v>
           </cell>
           <cell r="O1">
-            <v>27000</v>
+            <v>10000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>54</v>
+            <v>20</v>
           </cell>
           <cell r="O2">
-            <v>33000</v>
+            <v>50000</v>
           </cell>
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45579</v>
+            <v>45612</v>
           </cell>
         </row>
       </sheetData>
@@ -4223,245 +4731,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink87.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>50000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>60000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45584</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink88.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45584</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink89.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45584</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>69</v>
-          </cell>
-          <cell r="O1">
-            <v>5100</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>51</v>
-          </cell>
-          <cell r="O2">
-            <v>6900</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45584</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink90.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>12000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45587</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink91.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.22-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45597</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink92.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink99.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4492,233 +4762,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45602</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink93.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>50000</v>
-          </cell>
-          <cell r="K1">
-            <v>100</v>
-          </cell>
-          <cell r="O1">
-            <v>10000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>20</v>
-          </cell>
-          <cell r="O2">
-            <v>50000</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45612</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink94.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>30000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>36000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
             <v>45647</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink95.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink96.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>50000</v>
-          </cell>
-          <cell r="K1">
-            <v>109</v>
-          </cell>
-          <cell r="O1">
-            <v>5500</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>11</v>
-          </cell>
-          <cell r="O2">
-            <v>54500</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45684</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink97.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>115</v>
-          </cell>
-          <cell r="O1">
-            <v>500</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>5</v>
-          </cell>
-          <cell r="O2">
-            <v>11500</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45690</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink98.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>35000</v>
-          </cell>
-          <cell r="K1">
-            <v>119</v>
-          </cell>
-          <cell r="O1">
-            <v>350</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>1</v>
-          </cell>
-          <cell r="O2">
-            <v>41650</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45696</v>
           </cell>
         </row>
       </sheetData>
@@ -5013,23 +5057,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="I2" s="30" t="s">
+      <c r="C2" s="30"/>
+      <c r="I2" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="31"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="33">
+      <c r="J2" s="32"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="34">
         <f>SUM(L5:L47)</f>
-        <v>782500</v>
-      </c>
-      <c r="M2" s="34"/>
+        <v>772050</v>
+      </c>
+      <c r="M2" s="35"/>
       <c r="N2" s="1">
         <f>SUM(N5:N56)</f>
-        <v>44950</v>
+        <v>45650</v>
       </c>
       <c r="Q2" s="1">
         <f>14900+260750</f>
@@ -5106,7 +5150,7 @@
       </c>
       <c r="I5" s="13">
         <f>'[1]MD10000.10-JAN'!$K$2</f>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J5" s="16" t="s">
         <v>12</v>
@@ -5117,11 +5161,11 @@
       </c>
       <c r="L5" s="15">
         <f>'[1]MD10000.10-JAN'!$O$2</f>
-        <v>2100</v>
+        <v>1400</v>
       </c>
       <c r="M5" s="15">
         <f>'[1]MD10000.10-JAN'!$O$1</f>
-        <v>14700</v>
+        <v>15400</v>
       </c>
       <c r="N5" s="1">
         <v>350</v>
@@ -5169,7 +5213,7 @@
       <c r="N6" s="1">
         <v>700</v>
       </c>
-      <c r="P6" s="35"/>
+      <c r="P6" s="28"/>
     </row>
     <row r="7" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="6">
@@ -5187,11 +5231,11 @@
       </c>
       <c r="F7" s="8">
         <f>'[3]MD10000.1-OCT'!$K$1</f>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G7" s="8">
         <f>'[3]MD10000.1-OCT'!$K$2</f>
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
@@ -5204,58 +5248,55 @@
       </c>
       <c r="L7" s="7">
         <f>'[3]MD10000.1-OCT'!$O$2</f>
-        <v>1300</v>
+        <v>900</v>
       </c>
       <c r="M7" s="7">
         <f>'[3]MD10000.1-OCT'!$O$1</f>
-        <v>10700</v>
+        <v>11100</v>
       </c>
       <c r="N7" s="1">
         <v>700</v>
       </c>
-      <c r="P7" s="35"/>
+      <c r="P7" s="28"/>
     </row>
     <row r="8" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="6">
+      <c r="B8" s="17">
         <v>65</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="19">
         <f>'[4]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="20">
         <f>'[4]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="20">
         <f>'[4]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="9" t="s">
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K8" s="10">
+      <c r="K8" s="22">
         <f>'[4]MD10000.1-OCT'!$B$3</f>
         <v>45563</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="19">
         <f>'[4]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="19">
         <f>'[4]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
-      </c>
-      <c r="N8" s="1">
-        <v>700</v>
       </c>
     </row>
     <row r="9" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5319,11 +5360,11 @@
       <c r="G10" s="8"/>
       <c r="H10" s="8">
         <f>'[6]MD20000.18-DEC'!$K$1</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I10" s="8">
         <f>'[6]MD20000.18-DEC'!$K$2</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>12</v>
@@ -5334,11 +5375,11 @@
       </c>
       <c r="L10" s="7">
         <f>'[6]MD20000.18-DEC'!$O$2</f>
-        <v>100000</v>
+        <v>96000</v>
       </c>
       <c r="M10" s="7">
         <f>'[6]MD20000.18-DEC'!$O$1</f>
-        <v>60000</v>
+        <v>64000</v>
       </c>
       <c r="N10" s="1">
         <v>4000</v>
@@ -5376,11 +5417,11 @@
         <v>45584</v>
       </c>
       <c r="L11" s="19">
-        <f>'[95]MD20000.18-DEC'!$O$2</f>
+        <f>'[8]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M11" s="19">
-        <f>'[95]MD20000.18-DEC'!$O$1</f>
+        <f>'[8]MD20000.18-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -5395,16 +5436,16 @@
         <v>90</v>
       </c>
       <c r="E12" s="7">
-        <f>'[8]MD20000.18-DEC'!$C$1</f>
+        <f>'[9]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F12" s="8">
-        <f>'[8]MD20000.18-DEC'!$K$1</f>
-        <v>10</v>
+        <f>'[9]MD20000.18-DEC'!$K$1</f>
+        <v>5</v>
       </c>
       <c r="G12" s="8">
-        <f>'[8]MD20000.18-DEC'!$K$2</f>
-        <v>110</v>
+        <f>'[9]MD20000.18-DEC'!$K$2</f>
+        <v>115</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
@@ -5412,16 +5453,16 @@
         <v>12</v>
       </c>
       <c r="K12" s="10">
-        <f>'[8]MD20000.18-DEC'!$B$7</f>
+        <f>'[9]MD20000.18-DEC'!$B$7</f>
         <v>45587</v>
       </c>
       <c r="L12" s="7">
-        <f>'[8]MD20000.18-DEC'!$O$2</f>
-        <v>2000</v>
+        <f>'[9]MD20000.18-DEC'!$O$2</f>
+        <v>1000</v>
       </c>
       <c r="M12" s="7">
-        <f>'[8]MD20000.18-DEC'!$O$1</f>
-        <v>22000</v>
+        <f>'[9]MD20000.18-DEC'!$O$1</f>
+        <v>23000</v>
       </c>
       <c r="N12" s="1">
         <v>1400</v>
@@ -5438,16 +5479,16 @@
         <v>68</v>
       </c>
       <c r="E13" s="7">
-        <f>'[9]MD20000.18-DEC'!$C$1</f>
+        <f>'[10]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F13" s="8">
-        <f>'[9]MD20000.18-DEC'!$K$1</f>
-        <v>69</v>
+        <f>'[10]MD20000.18-DEC'!$K$1</f>
+        <v>60</v>
       </c>
       <c r="G13" s="8">
-        <f>'[9]MD20000.18-DEC'!$K$2</f>
-        <v>51</v>
+        <f>'[10]MD20000.18-DEC'!$K$2</f>
+        <v>60</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
@@ -5455,16 +5496,16 @@
         <v>12</v>
       </c>
       <c r="K13" s="10">
-        <f>'[9]MD20000.18-DEC'!$B$3</f>
+        <f>'[10]MD20000.18-DEC'!$B$3</f>
         <v>45584</v>
       </c>
       <c r="L13" s="7">
-        <f>'[9]MD20000.18-DEC'!$O$2</f>
-        <v>6900</v>
+        <f>'[10]MD20000.18-DEC'!$O$2</f>
+        <v>6000</v>
       </c>
       <c r="M13" s="7">
-        <f>'[9]MD20000.18-DEC'!$O$1</f>
-        <v>5100</v>
+        <f>'[10]MD20000.18-DEC'!$O$1</f>
+        <v>6000</v>
       </c>
       <c r="N13" s="1">
         <v>700</v>
@@ -5481,15 +5522,15 @@
         <v>68</v>
       </c>
       <c r="E14" s="7">
-        <f>'[10]MD20000.18-DEC'!$C$1</f>
+        <f>'[11]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F14" s="8">
-        <f>'[10]MD20000.18-DEC'!$K$1</f>
+        <f>'[11]MD20000.18-DEC'!$K$1</f>
         <v>68</v>
       </c>
       <c r="G14" s="8">
-        <f>'[10]MD20000.18-DEC'!$K$2</f>
+        <f>'[11]MD20000.18-DEC'!$K$2</f>
         <v>52</v>
       </c>
       <c r="H14" s="8"/>
@@ -5498,15 +5539,15 @@
         <v>12</v>
       </c>
       <c r="K14" s="10">
-        <f>'[10]MD20000.18-DEC'!$B$3</f>
+        <f>'[11]MD20000.18-DEC'!$B$3</f>
         <v>45584</v>
       </c>
       <c r="L14" s="7">
-        <f>'[10]MD20000.18-DEC'!$O$2</f>
+        <f>'[11]MD20000.18-DEC'!$O$2</f>
         <v>6800</v>
       </c>
       <c r="M14" s="7">
-        <f>'[10]MD20000.18-DEC'!$O$1</f>
+        <f>'[11]MD20000.18-DEC'!$O$1</f>
         <v>5200</v>
       </c>
       <c r="N14" s="1">
@@ -5524,33 +5565,33 @@
         <v>52</v>
       </c>
       <c r="E15" s="7">
-        <f>'[11]MD20000.15-DEc'!$C$1</f>
+        <f>'[12]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F15" s="8"/>
       <c r="G15" s="8"/>
       <c r="H15" s="8">
-        <f>'[11]MD20000.15-DEc'!$K$1</f>
-        <v>2</v>
+        <f>'[12]MD20000.15-DEc'!$K$1</f>
+        <v>1</v>
       </c>
       <c r="I15" s="8">
-        <f>'[11]MD20000.15-DEc'!$K$2</f>
-        <v>15</v>
+        <f>'[12]MD20000.15-DEc'!$K$2</f>
+        <v>16</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>12</v>
       </c>
       <c r="K15" s="10">
-        <f>'[11]MD20000.15-DEc'!$B$3</f>
+        <f>'[12]MD20000.15-DEc'!$B$3</f>
         <v>45595</v>
       </c>
       <c r="L15" s="7">
-        <f>'[11]MD20000.15-DEc'!$O$2</f>
-        <v>2800</v>
+        <f>'[12]MD20000.15-DEc'!$O$2</f>
+        <v>1400</v>
       </c>
       <c r="M15" s="7">
-        <f>'[11]MD20000.15-DEc'!$O$1</f>
-        <v>21200</v>
+        <f>'[12]MD20000.15-DEc'!$O$1</f>
+        <v>22600</v>
       </c>
       <c r="N15" s="1">
         <v>1400</v>
@@ -5567,33 +5608,33 @@
         <v>106</v>
       </c>
       <c r="E16" s="7">
-        <f>'[12]MD10000.10-JAN'!$C$1</f>
+        <f>'[13]MD10000.10-JAN'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
       <c r="H16" s="8">
-        <f>'[12]MD10000.10-JAN'!$K$1</f>
-        <v>4</v>
+        <f>'[13]MD10000.10-JAN'!$K$1</f>
+        <v>2</v>
       </c>
       <c r="I16" s="8">
-        <f>'[12]MD10000.10-JAN'!$K$2</f>
-        <v>13</v>
+        <f>'[13]MD10000.10-JAN'!$K$2</f>
+        <v>15</v>
       </c>
       <c r="J16" s="9" t="s">
         <v>12</v>
       </c>
       <c r="K16" s="10">
-        <f>'[12]MD10000.10-JAN'!$B$3</f>
+        <f>'[13]MD10000.10-JAN'!$B$3</f>
         <v>45602</v>
       </c>
       <c r="L16" s="7">
-        <f>'[12]MD10000.10-JAN'!$O$2</f>
-        <v>5600</v>
+        <f>'[13]MD10000.10-JAN'!$O$2</f>
+        <v>2800</v>
       </c>
       <c r="M16" s="7">
-        <f>'[12]MD10000.10-JAN'!$O$1</f>
-        <v>18400</v>
+        <f>'[13]MD10000.10-JAN'!$O$1</f>
+        <v>21200</v>
       </c>
       <c r="N16" s="1">
         <v>1400</v>
@@ -5610,16 +5651,16 @@
         <v>68</v>
       </c>
       <c r="E17" s="7">
-        <f>'[13]MD20000.18-DEC'!$C$1</f>
+        <f>'[14]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F17" s="8">
-        <f>'[13]MD20000.18-DEC'!$K$1</f>
-        <v>41</v>
+        <f>'[14]MD20000.18-DEC'!$K$1</f>
+        <v>34</v>
       </c>
       <c r="G17" s="8">
-        <f>'[13]MD20000.18-DEC'!$K$2</f>
-        <v>79</v>
+        <f>'[14]MD20000.18-DEC'!$K$2</f>
+        <v>86</v>
       </c>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
@@ -5627,16 +5668,16 @@
         <v>12</v>
       </c>
       <c r="K17" s="10">
-        <f>'[13]MD20000.18-DEC'!$B$3</f>
+        <f>'[14]MD20000.18-DEC'!$B$3</f>
         <v>45612</v>
       </c>
       <c r="L17" s="7">
-        <f>'[13]MD20000.18-DEC'!$O$2</f>
-        <v>4100</v>
+        <f>'[14]MD20000.18-DEC'!$O$2</f>
+        <v>3400</v>
       </c>
       <c r="M17" s="7">
-        <f>'[13]MD20000.18-DEC'!$O$1</f>
-        <v>7900</v>
+        <f>'[14]MD20000.18-DEC'!$O$1</f>
+        <v>8600</v>
       </c>
       <c r="N17" s="1">
         <v>700</v>
@@ -5653,16 +5694,16 @@
         <v>111</v>
       </c>
       <c r="E18" s="7">
-        <f>'[14]MD50000.15-DEC'!$C$1</f>
+        <f>'[15]MD50000.15-DEC'!$C$1</f>
         <v>100000</v>
       </c>
       <c r="F18" s="8">
-        <f>'[14]MD50000.15-DEC'!$K$1</f>
-        <v>219</v>
+        <f>'[15]MD50000.15-DEC'!$K$1</f>
+        <v>216</v>
       </c>
       <c r="G18" s="8">
-        <f>'[14]MD50000.15-DEC'!$K$2</f>
-        <v>48</v>
+        <f>'[15]MD50000.15-DEC'!$K$2</f>
+        <v>51</v>
       </c>
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
@@ -5670,16 +5711,16 @@
         <v>12</v>
       </c>
       <c r="K18" s="10">
-        <f>'[14]MD50000.15-DEC'!$B$3</f>
+        <f>'[15]MD50000.15-DEC'!$B$3</f>
         <v>45619</v>
       </c>
       <c r="L18" s="7">
-        <f>'[14]MD50000.15-DEC'!$O$2</f>
-        <v>131400</v>
+        <f>'[15]MD50000.15-DEC'!$O$2</f>
+        <v>129600</v>
       </c>
       <c r="M18" s="7">
-        <f>'[14]MD50000.15-DEC'!$O$1</f>
-        <v>28800</v>
+        <f>'[15]MD50000.15-DEC'!$O$1</f>
+        <v>30600</v>
       </c>
       <c r="N18" s="1">
         <v>4200</v>
@@ -5696,16 +5737,16 @@
         <v>96</v>
       </c>
       <c r="E19" s="7">
-        <f>'[15]MD20000.18-DEC'!$C$1</f>
+        <f>'[16]MD20000.18-DEC'!$C$1</f>
         <v>50000</v>
       </c>
       <c r="F19" s="8">
-        <f>'[15]MD20000.18-DEC'!$K$1</f>
-        <v>54</v>
+        <f>'[16]MD20000.18-DEC'!$K$1</f>
+        <v>46</v>
       </c>
       <c r="G19" s="8">
-        <f>'[15]MD20000.18-DEC'!$K$2</f>
-        <v>66</v>
+        <f>'[16]MD20000.18-DEC'!$K$2</f>
+        <v>74</v>
       </c>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -5713,16 +5754,16 @@
         <v>12</v>
       </c>
       <c r="K19" s="10">
-        <f>'[15]MD20000.18-DEC'!$B$3</f>
+        <f>'[16]MD20000.18-DEC'!$B$3</f>
         <v>45628</v>
       </c>
       <c r="L19" s="7">
-        <f>'[15]MD20000.18-DEC'!$O$2</f>
-        <v>27000</v>
+        <f>'[16]MD20000.18-DEC'!$O$2</f>
+        <v>23000</v>
       </c>
       <c r="M19" s="7">
-        <f>'[15]MD20000.18-DEC'!$O$1</f>
-        <v>33000</v>
+        <f>'[16]MD20000.18-DEC'!$O$1</f>
+        <v>37000</v>
       </c>
       <c r="N19" s="1">
         <v>3500</v>
@@ -5739,16 +5780,16 @@
         <v>68</v>
       </c>
       <c r="E20" s="7">
-        <f>'[16]MD20000.18-DEC'!$C$1</f>
+        <f>'[17]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F20" s="8">
-        <f>'[16]MD20000.18-DEC'!$K$1</f>
+        <f>'[17]MD20000.18-DEC'!$K$1</f>
+        <v>57</v>
+      </c>
+      <c r="G20" s="8">
+        <f>'[17]MD20000.18-DEC'!$K$2</f>
         <v>63</v>
-      </c>
-      <c r="G20" s="8">
-        <f>'[16]MD20000.18-DEC'!$K$2</f>
-        <v>57</v>
       </c>
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
@@ -5756,16 +5797,16 @@
         <v>12</v>
       </c>
       <c r="K20" s="10">
-        <f>'[16]MD20000.18-DEC'!$B$3</f>
+        <f>'[17]MD20000.18-DEC'!$B$3</f>
         <v>45635</v>
       </c>
       <c r="L20" s="7">
-        <f>'[16]MD20000.18-DEC'!$O$2</f>
+        <f>'[17]MD20000.18-DEC'!$O$2</f>
+        <v>5700</v>
+      </c>
+      <c r="M20" s="7">
+        <f>'[17]MD20000.18-DEC'!$O$1</f>
         <v>6300</v>
-      </c>
-      <c r="M20" s="7">
-        <f>'[16]MD20000.18-DEC'!$O$1</f>
-        <v>5700</v>
       </c>
       <c r="N20" s="1">
         <v>700</v>
@@ -5782,16 +5823,16 @@
         <v>68</v>
       </c>
       <c r="E21" s="7">
-        <f>'[17]MD20000.18-DEC'!$C$1</f>
+        <f>'[18]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F21" s="8">
-        <f>'[17]MD20000.18-DEC'!$K$1</f>
+        <f>'[18]MD20000.18-DEC'!$K$1</f>
+        <v>57</v>
+      </c>
+      <c r="G21" s="8">
+        <f>'[18]MD20000.18-DEC'!$K$2</f>
         <v>63</v>
-      </c>
-      <c r="G21" s="8">
-        <f>'[17]MD20000.18-DEC'!$K$2</f>
-        <v>57</v>
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
@@ -5799,16 +5840,16 @@
         <v>12</v>
       </c>
       <c r="K21" s="10">
-        <f>'[17]MD20000.18-DEC'!$B$3</f>
+        <f>'[18]MD20000.18-DEC'!$B$3</f>
         <v>45635</v>
       </c>
       <c r="L21" s="7">
-        <f>'[17]MD20000.18-DEC'!$O$2</f>
+        <f>'[18]MD20000.18-DEC'!$O$2</f>
+        <v>5700</v>
+      </c>
+      <c r="M21" s="7">
+        <f>'[18]MD20000.18-DEC'!$O$1</f>
         <v>6300</v>
-      </c>
-      <c r="M21" s="7">
-        <f>'[17]MD20000.18-DEC'!$O$1</f>
-        <v>5700</v>
       </c>
       <c r="N21" s="1">
         <v>700</v>
@@ -5825,16 +5866,16 @@
         <v>117</v>
       </c>
       <c r="E22" s="7">
-        <f>'[18]MD50000.15-DEC'!$C$1</f>
+        <f>'[19]MD50000.15-DEC'!$C$1</f>
         <v>200000</v>
       </c>
       <c r="F22" s="8">
-        <f>'[18]MD50000.15-DEC'!$K$1</f>
-        <v>230</v>
+        <f>'[19]MD50000.15-DEC'!$K$1</f>
+        <v>226</v>
       </c>
       <c r="G22" s="8">
-        <f>'[18]MD50000.15-DEC'!$K$2</f>
-        <v>37</v>
+        <f>'[19]MD50000.15-DEC'!$K$2</f>
+        <v>41</v>
       </c>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
@@ -5842,16 +5883,16 @@
         <v>12</v>
       </c>
       <c r="K22" s="10">
-        <f>'[18]MD50000.15-DEC'!$B$3</f>
+        <f>'[19]MD50000.15-DEC'!$B$3</f>
         <v>45648</v>
       </c>
       <c r="L22" s="7">
-        <f>'[18]MD50000.15-DEC'!$O$2</f>
-        <v>276000</v>
+        <f>'[19]MD50000.15-DEC'!$O$2</f>
+        <v>271200</v>
       </c>
       <c r="M22" s="7">
-        <f>'[18]MD50000.15-DEC'!$O$1</f>
-        <v>44400</v>
+        <f>'[19]MD50000.15-DEC'!$O$1</f>
+        <v>49200</v>
       </c>
       <c r="N22" s="1">
         <v>8400</v>
@@ -5868,32 +5909,32 @@
         <v>119</v>
       </c>
       <c r="E23" s="7">
-        <f>'[19]MD20000.15-DEc'!$C$1</f>
+        <f>'[20]MD20000.15-DEc'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
       <c r="H23" s="8">
-        <f>'[19]MD20000.15-DEc'!$K$1</f>
+        <f>'[20]MD20000.15-DEc'!$K$1</f>
         <v>9</v>
       </c>
       <c r="I23" s="8">
-        <f>'[19]MD20000.15-DEc'!$K$2</f>
+        <f>'[20]MD20000.15-DEc'!$K$2</f>
         <v>8</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>12</v>
       </c>
       <c r="K23" s="10">
-        <f>'[19]MD20000.15-DEc'!$B$3</f>
+        <f>'[20]MD20000.15-DEc'!$B$3</f>
         <v>45649</v>
       </c>
       <c r="L23" s="7">
-        <f>'[19]MD20000.15-DEc'!$O$2</f>
+        <f>'[20]MD20000.15-DEc'!$O$2</f>
         <v>6400</v>
       </c>
       <c r="M23" s="7">
-        <f>'[19]MD20000.15-DEc'!$O$1</f>
+        <f>'[20]MD20000.15-DEc'!$O$1</f>
         <v>5600</v>
       </c>
       <c r="N23" s="1">
@@ -5911,16 +5952,16 @@
         <v>96</v>
       </c>
       <c r="E24" s="7">
-        <f>'[20]MD50000.15-DEC'!$C$1</f>
+        <f>'[21]MD50000.15-DEC'!$C$1</f>
         <v>50000</v>
       </c>
       <c r="F24" s="8">
-        <f>'[20]MD50000.15-DEC'!$K$1</f>
-        <v>83</v>
+        <f>'[21]MD50000.15-DEC'!$K$1</f>
+        <v>80</v>
       </c>
       <c r="G24" s="8">
-        <f>'[20]MD50000.15-DEC'!$K$2</f>
-        <v>37</v>
+        <f>'[21]MD50000.15-DEC'!$K$2</f>
+        <v>40</v>
       </c>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
@@ -5928,16 +5969,16 @@
         <v>12</v>
       </c>
       <c r="K24" s="10">
-        <f>'[20]MD50000.15-DEC'!$B$3</f>
+        <f>'[21]MD50000.15-DEC'!$B$3</f>
         <v>45652</v>
       </c>
       <c r="L24" s="7">
-        <f>'[20]MD50000.15-DEC'!$O$2</f>
-        <v>41500</v>
+        <f>'[21]MD50000.15-DEC'!$O$2</f>
+        <v>40000</v>
       </c>
       <c r="M24" s="7">
-        <f>'[20]MD50000.15-DEC'!$O$1</f>
-        <v>18500</v>
+        <f>'[21]MD50000.15-DEC'!$O$1</f>
+        <v>20000</v>
       </c>
       <c r="N24" s="1">
         <v>3500</v>
@@ -5954,33 +5995,33 @@
         <v>122</v>
       </c>
       <c r="E25" s="7">
-        <f>'[21]MD50000.15-DEC'!$C$1</f>
+        <f>'[22]MD50000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
       <c r="H25" s="8">
-        <f>'[21]MD50000.15-DEC'!$K$1</f>
+        <f>'[22]MD50000.15-DEC'!$K$1</f>
         <v>17</v>
       </c>
       <c r="I25" s="8">
-        <f>'[21]MD50000.15-DEC'!$K$2</f>
-        <v>2</v>
+        <f>'[22]MD50000.15-DEC'!$K$2</f>
+        <v>4</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>12</v>
       </c>
       <c r="K25" s="10">
-        <f>'[21]MD50000.15-DEC'!$B$3</f>
+        <f>'[22]MD50000.15-DEC'!$B$3</f>
         <v>45678</v>
       </c>
       <c r="L25" s="7">
-        <f>'[21]MD50000.15-DEC'!$O$2</f>
-        <v>21000</v>
+        <f>'[22]MD50000.15-DEC'!$O$2</f>
+        <v>18200</v>
       </c>
       <c r="M25" s="7">
-        <f>'[21]MD50000.15-DEC'!$O$1</f>
-        <v>2800</v>
+        <f>'[22]MD50000.15-DEC'!$O$1</f>
+        <v>5600</v>
       </c>
       <c r="N25" s="1">
         <v>1400</v>
@@ -5997,33 +6038,33 @@
         <v>124</v>
       </c>
       <c r="E26" s="7">
-        <f>'[22]MD50000.15-DEC'!$C$1</f>
+        <f>'[23]MD50000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
       <c r="H26" s="8">
-        <f>'[22]MD50000.15-DEC'!$K$1</f>
+        <f>'[23]MD50000.15-DEC'!$K$1</f>
         <v>17</v>
       </c>
       <c r="I26" s="8">
-        <f>'[22]MD50000.15-DEC'!$K$2</f>
-        <v>2</v>
+        <f>'[23]MD50000.15-DEC'!$K$2</f>
+        <v>3</v>
       </c>
       <c r="J26" s="9" t="s">
         <v>125</v>
       </c>
       <c r="K26" s="10">
-        <f>'[22]MD50000.15-DEC'!$B$3</f>
+        <f>'[23]MD50000.15-DEC'!$B$3</f>
         <v>45683</v>
       </c>
       <c r="L26" s="7">
-        <f>'[22]MD50000.15-DEC'!$O$2</f>
-        <v>21000</v>
+        <f>'[23]MD50000.15-DEC'!$O$2</f>
+        <v>19600</v>
       </c>
       <c r="M26" s="7">
-        <f>'[22]MD50000.15-DEC'!$O$1</f>
-        <v>2800</v>
+        <f>'[23]MD50000.15-DEC'!$O$1</f>
+        <v>4200</v>
       </c>
       <c r="N26" s="1">
         <v>1400</v>
@@ -6040,16 +6081,16 @@
         <v>96</v>
       </c>
       <c r="E27" s="7">
-        <f>'[96]MD20000.18-DEC'!$C$1</f>
+        <f>'[24]MD20000.18-DEC'!$C$1</f>
         <v>50000</v>
       </c>
       <c r="F27" s="8">
-        <f>'[96]MD20000.18-DEC'!$K$1</f>
-        <v>109</v>
+        <f>'[24]MD20000.18-DEC'!$K$1</f>
+        <v>105</v>
       </c>
       <c r="G27" s="8">
-        <f>'[96]MD20000.18-DEC'!$K$2</f>
-        <v>11</v>
+        <f>'[24]MD20000.18-DEC'!$K$2</f>
+        <v>15</v>
       </c>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
@@ -6057,16 +6098,16 @@
         <v>12</v>
       </c>
       <c r="K27" s="10">
-        <f>'[96]MD20000.18-DEC'!$B$3</f>
+        <f>'[24]MD20000.18-DEC'!$B$3</f>
         <v>45684</v>
       </c>
       <c r="L27" s="7">
-        <f>'[96]MD20000.18-DEC'!$O$2</f>
-        <v>54500</v>
+        <f>'[24]MD20000.18-DEC'!$O$2</f>
+        <v>52500</v>
       </c>
       <c r="M27" s="7">
-        <f>'[96]MD20000.18-DEC'!$O$1</f>
-        <v>5500</v>
+        <f>'[24]MD20000.18-DEC'!$O$1</f>
+        <v>7500</v>
       </c>
       <c r="N27" s="1">
         <v>3500</v>
@@ -6083,16 +6124,16 @@
         <v>68</v>
       </c>
       <c r="E28" s="7">
-        <f>'[97]MD20000.18-DEC'!$C$1</f>
+        <f>'[25]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F28" s="8">
-        <f>'[97]MD20000.18-DEC'!$K$1</f>
-        <v>115</v>
+        <f>'[25]MD20000.18-DEC'!$K$1</f>
+        <v>110</v>
       </c>
       <c r="G28" s="8">
-        <f>'[97]MD20000.18-DEC'!$K$2</f>
-        <v>5</v>
+        <f>'[25]MD20000.18-DEC'!$K$2</f>
+        <v>10</v>
       </c>
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
@@ -6100,16 +6141,16 @@
         <v>12</v>
       </c>
       <c r="K28" s="10">
-        <f>'[97]MD20000.18-DEC'!$B$3</f>
+        <f>'[25]MD20000.18-DEC'!$B$3</f>
         <v>45690</v>
       </c>
       <c r="L28" s="7">
-        <f>'[97]MD20000.18-DEC'!$O$2</f>
-        <v>11500</v>
+        <f>'[25]MD20000.18-DEC'!$O$2</f>
+        <v>11000</v>
       </c>
       <c r="M28" s="7">
-        <f>'[97]MD20000.18-DEC'!$O$1</f>
-        <v>500</v>
+        <f>'[25]MD20000.18-DEC'!$O$1</f>
+        <v>1000</v>
       </c>
       <c r="N28" s="1">
         <v>700</v>
@@ -6126,16 +6167,16 @@
         <v>128</v>
       </c>
       <c r="E29" s="7">
-        <f>'[98]MD20000.18-DEC'!$C$1</f>
+        <f>'[26]MD20000.18-DEC'!$C$1</f>
         <v>35000</v>
       </c>
       <c r="F29" s="8">
-        <f>'[98]MD20000.18-DEC'!$K$1</f>
-        <v>119</v>
+        <f>'[26]MD20000.18-DEC'!$K$1</f>
+        <v>114</v>
       </c>
       <c r="G29" s="8">
-        <f>'[98]MD20000.18-DEC'!$K$2</f>
-        <v>1</v>
+        <f>'[26]MD20000.18-DEC'!$K$2</f>
+        <v>6</v>
       </c>
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
@@ -6143,16 +6184,16 @@
         <v>12</v>
       </c>
       <c r="K29" s="10">
-        <f>'[98]MD20000.18-DEC'!$B$3</f>
+        <f>'[26]MD20000.18-DEC'!$B$3</f>
         <v>45696</v>
       </c>
       <c r="L29" s="7">
-        <f>'[98]MD20000.18-DEC'!$O$2</f>
-        <v>41650</v>
+        <f>'[26]MD20000.18-DEC'!$O$2</f>
+        <v>39900</v>
       </c>
       <c r="M29" s="7">
-        <f>'[98]MD20000.18-DEC'!$O$1</f>
-        <v>350</v>
+        <f>'[26]MD20000.18-DEC'!$O$1</f>
+        <v>2100</v>
       </c>
       <c r="N29" s="1">
         <v>2450</v>
@@ -6162,17 +6203,44 @@
       <c r="B30" s="6">
         <v>96</v>
       </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
+      <c r="C30" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E30" s="7">
+        <f>'[27]MD20000.18-DEC'!$C$1</f>
+        <v>20000</v>
+      </c>
+      <c r="F30" s="8">
+        <f>'[27]MD20000.18-DEC'!$K$1</f>
+        <v>116</v>
+      </c>
+      <c r="G30" s="8">
+        <f>'[27]MD20000.18-DEC'!$K$2</f>
+        <v>4</v>
+      </c>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
+      <c r="J30" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="K30" s="10">
+        <f>'[27]MD20000.18-DEC'!$B$3</f>
+        <v>45699</v>
+      </c>
+      <c r="L30" s="7">
+        <f>'[27]MD20000.18-DEC'!$O$2</f>
+        <v>23200</v>
+      </c>
+      <c r="M30" s="7">
+        <f>'[27]MD20000.18-DEC'!$O$1</f>
+        <v>800</v>
+      </c>
+      <c r="N30" s="1">
+        <v>1400</v>
+      </c>
     </row>
     <row r="31" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="6"/>
@@ -6406,20 +6474,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="I2" s="30" t="s">
+      <c r="C2" s="30"/>
+      <c r="I2" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="31"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="33">
+      <c r="J2" s="32"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="34">
         <f>SUM(L5:L108)</f>
-        <v>732250</v>
-      </c>
-      <c r="M2" s="34"/>
+        <v>707050</v>
+      </c>
+      <c r="M2" s="35"/>
       <c r="N2" s="1">
         <f>SUM(N5:N117)</f>
         <v>36900</v>
@@ -6488,15 +6556,15 @@
         <v>18</v>
       </c>
       <c r="E5" s="19">
-        <f>'[23]SM5000.1-SEPT'!$C$1</f>
+        <f>'[28]SM5000.1-SEPT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F5" s="20">
-        <f>'[23]SM5000.1-SEPT'!$K$1</f>
+        <f>'[28]SM5000.1-SEPT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G5" s="20">
-        <f>'[23]SM5000.1-SEPT'!$K$2</f>
+        <f>'[28]SM5000.1-SEPT'!$K$2</f>
         <v>60</v>
       </c>
       <c r="H5" s="20"/>
@@ -6505,15 +6573,15 @@
         <v>22</v>
       </c>
       <c r="K5" s="22">
-        <f>'[23]SM5000.1-SEPT'!$B$3</f>
+        <f>'[28]SM5000.1-SEPT'!$B$3</f>
         <v>45180</v>
       </c>
       <c r="L5" s="19">
-        <f>'[23]SM5000.1-SEPT'!$O$2</f>
+        <f>'[28]SM5000.1-SEPT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M5" s="19">
-        <f>'[23]SM5000.1-SEPT'!$O$1</f>
+        <f>'[28]SM5000.1-SEPT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -6528,15 +6596,15 @@
         <v>18</v>
       </c>
       <c r="E6" s="19">
-        <f>'[23]SM5000.1-oct'!$C$1</f>
+        <f>'[28]SM5000.1-oct'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F6" s="20">
-        <f>'[23]SM5000.1-oct'!$K$1</f>
+        <f>'[28]SM5000.1-oct'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G6" s="20">
-        <f>'[23]SM5000.1-oct'!$K$2</f>
+        <f>'[28]SM5000.1-oct'!$K$2</f>
         <v>60</v>
       </c>
       <c r="H6" s="20"/>
@@ -6545,15 +6613,15 @@
         <v>22</v>
       </c>
       <c r="K6" s="22">
-        <f>'[23]SM5000.1-oct'!$B$3</f>
+        <f>'[28]SM5000.1-oct'!$B$3</f>
         <v>45201</v>
       </c>
       <c r="L6" s="19">
-        <f>'[23]SM5000.1-oct'!$O$2</f>
+        <f>'[28]SM5000.1-oct'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M6" s="19">
-        <f>'[23]SM5000.1-oct'!$O$1</f>
+        <f>'[28]SM5000.1-oct'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -6568,15 +6636,15 @@
         <v>19</v>
       </c>
       <c r="E7" s="19">
-        <f>'[24]MD10000.1-OCT'!$C$1</f>
+        <f>'[29]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F7" s="20">
-        <f>'[24]MD10000.1-OCT'!$K$1</f>
+        <f>'[29]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G7" s="20">
-        <f>'[24]MD10000.1-OCT'!$K$2</f>
+        <f>'[29]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H7" s="20"/>
@@ -6585,15 +6653,15 @@
         <v>22</v>
       </c>
       <c r="K7" s="22">
-        <f>'[24]MD10000.1-OCT'!$B$3</f>
+        <f>'[29]MD10000.1-OCT'!$B$3</f>
         <v>45212</v>
       </c>
       <c r="L7" s="19">
-        <f>'[24]MD10000.1-OCT'!$O$2</f>
+        <f>'[29]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M7" s="19">
-        <f>'[24]MD10000.1-OCT'!$O$1</f>
+        <f>'[29]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -6608,15 +6676,15 @@
         <v>19</v>
       </c>
       <c r="E8" s="19">
-        <f>'[25]MD10000.1-OCT'!$C$1</f>
+        <f>'[30]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F8" s="20">
-        <f>'[25]MD10000.1-OCT'!$K$1</f>
+        <f>'[30]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G8" s="20">
-        <f>'[25]MD10000.1-OCT'!$K$2</f>
+        <f>'[30]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H8" s="20"/>
@@ -6625,15 +6693,15 @@
         <v>22</v>
       </c>
       <c r="K8" s="22">
-        <f>'[25]MD10000.1-OCT'!$B$3</f>
+        <f>'[30]MD10000.1-OCT'!$B$3</f>
         <v>45213</v>
       </c>
       <c r="L8" s="19">
-        <f>'[25]MD10000.1-OCT'!$O$2</f>
+        <f>'[30]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M8" s="19">
-        <f>'[25]MD10000.1-OCT'!$O$1</f>
+        <f>'[30]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -6648,32 +6716,32 @@
         <v>20</v>
       </c>
       <c r="E9" s="19">
-        <f>'[26]MD10000.20-OCT'!$C$1</f>
+        <f>'[31]MD10000.20-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F9" s="20"/>
       <c r="G9" s="20"/>
       <c r="H9" s="20">
-        <f>'[26]MD10000.20-OCT'!$K$1</f>
+        <f>'[31]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I9" s="20">
-        <f>'[26]MD10000.20-OCT'!$K$2</f>
+        <f>'[31]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J9" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K9" s="22">
-        <f>'[26]MD10000.20-OCT'!$B$3</f>
+        <f>'[31]MD10000.20-OCT'!$B$3</f>
         <v>45226</v>
       </c>
       <c r="L9" s="19">
-        <f>'[26]MD10000.20-OCT'!$O$2</f>
+        <f>'[31]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M9" s="19">
-        <f>'[26]MD10000.20-OCT'!$O$1</f>
+        <f>'[31]MD10000.20-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -6688,15 +6756,15 @@
         <v>18</v>
       </c>
       <c r="E10" s="19">
-        <f>'[27]SM5000.1-SEPT (2)'!$C$1</f>
+        <f>'[32]SM5000.1-SEPT (2)'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F10" s="20">
-        <f>'[27]SM5000.1-SEPT (2)'!$K$1</f>
+        <f>'[32]SM5000.1-SEPT (2)'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G10" s="20">
-        <f>'[27]SM5000.1-SEPT (2)'!$K$2</f>
+        <f>'[32]SM5000.1-SEPT (2)'!$K$2</f>
         <v>60</v>
       </c>
       <c r="H10" s="20"/>
@@ -6705,15 +6773,15 @@
         <v>41</v>
       </c>
       <c r="K10" s="22">
-        <f>'[27]SM5000.1-SEPT (2)'!$B$3</f>
+        <f>'[32]SM5000.1-SEPT (2)'!$B$3</f>
         <v>45243</v>
       </c>
       <c r="L10" s="19">
-        <f>'[27]SM5000.1-SEPT (2)'!$O$2</f>
+        <f>'[32]SM5000.1-SEPT (2)'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M10" s="19">
-        <f>'[27]SM5000.1-SEPT (2)'!$O$1</f>
+        <f>'[32]SM5000.1-SEPT (2)'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -6728,32 +6796,32 @@
         <v>20</v>
       </c>
       <c r="E11" s="19">
-        <f>'[28]MD10000.20-OCT'!$C$1</f>
+        <f>'[33]MD10000.20-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F11" s="20"/>
       <c r="G11" s="20"/>
       <c r="H11" s="20">
-        <f>'[28]MD10000.20-OCT'!$K$1</f>
+        <f>'[33]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I11" s="20">
-        <f>'[28]MD10000.20-OCT'!$K$2</f>
+        <f>'[33]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J11" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K11" s="22">
-        <f>'[28]MD10000.20-OCT'!$B$3</f>
+        <f>'[33]MD10000.20-OCT'!$B$3</f>
         <v>45245</v>
       </c>
       <c r="L11" s="19">
-        <f>'[28]MD10000.20-OCT'!$O$2</f>
+        <f>'[33]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M11" s="19">
-        <f>'[28]MD10000.20-OCT'!$O$1</f>
+        <f>'[33]MD10000.20-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -6768,32 +6836,32 @@
         <v>25</v>
       </c>
       <c r="E12" s="19">
-        <f>'[29]MD15000.27-NOV'!$C$1</f>
+        <f>'[34]MD15000.27-NOV'!$C$1</f>
         <v>15000</v>
       </c>
       <c r="F12" s="20"/>
       <c r="G12" s="20"/>
       <c r="H12" s="20">
-        <f>'[29]MD15000.27-NOV'!$K$1</f>
+        <f>'[34]MD15000.27-NOV'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I12" s="20">
-        <f>'[29]MD15000.27-NOV'!$K$2</f>
+        <f>'[34]MD15000.27-NOV'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J12" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K12" s="22">
-        <f>'[29]MD15000.27-NOV'!$B$3</f>
+        <f>'[34]MD15000.27-NOV'!$B$3</f>
         <v>45266</v>
       </c>
       <c r="L12" s="19">
-        <f>'[29]MD15000.27-NOV'!$O$2</f>
+        <f>'[34]MD15000.27-NOV'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M12" s="19">
-        <f>'[29]MD15000.27-NOV'!$O$1</f>
+        <f>'[34]MD15000.27-NOV'!$O$1</f>
         <v>18000</v>
       </c>
     </row>
@@ -6808,32 +6876,32 @@
         <v>29</v>
       </c>
       <c r="E13" s="19">
-        <f>'[30]MD20000.15-DEC'!$C$1</f>
+        <f>'[35]MD20000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F13" s="20"/>
       <c r="G13" s="20"/>
       <c r="H13" s="20">
-        <f>'[30]MD20000.15-DEC'!$K$1</f>
+        <f>'[35]MD20000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I13" s="20">
-        <f>'[30]MD20000.15-DEC'!$K$2</f>
+        <f>'[35]MD20000.15-DEC'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J13" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K13" s="22">
-        <f>'[30]MD20000.15-DEC'!$B$3</f>
+        <f>'[35]MD20000.15-DEC'!$B$3</f>
         <v>45649</v>
       </c>
       <c r="L13" s="19">
-        <f>'[30]MD20000.15-DEC'!$O$2</f>
+        <f>'[35]MD20000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M13" s="19">
-        <f>'[30]MD20000.15-DEC'!$O$1</f>
+        <f>'[35]MD20000.15-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -6848,32 +6916,32 @@
         <v>28</v>
       </c>
       <c r="E14" s="19">
-        <f>'[31]MD20000.15-DEc'!$C$1</f>
+        <f>'[36]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F14" s="20"/>
       <c r="G14" s="20"/>
       <c r="H14" s="20">
-        <f>'[31]MD20000.15-DEc'!$K$1</f>
+        <f>'[36]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I14" s="20">
-        <f>'[31]MD20000.15-DEc'!$K$2</f>
+        <f>'[36]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J14" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K14" s="22">
-        <f>'[31]MD20000.15-DEc'!$B$3</f>
+        <f>'[36]MD20000.15-DEc'!$B$3</f>
         <v>45646</v>
       </c>
       <c r="L14" s="19">
-        <f>'[31]MD20000.15-DEc'!$O$2</f>
+        <f>'[36]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M14" s="19">
-        <f>'[31]MD20000.15-DEc'!$O$1</f>
+        <f>'[36]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -6888,32 +6956,32 @@
         <v>31</v>
       </c>
       <c r="E15" s="19">
-        <f>'[32]MD50000.15-DEC'!$C$1</f>
+        <f>'[37]MD50000.15-DEC'!$C$1</f>
         <v>50000</v>
       </c>
       <c r="F15" s="20"/>
       <c r="G15" s="20"/>
       <c r="H15" s="20">
-        <f>'[32]MD50000.15-DEC'!$K$1</f>
+        <f>'[37]MD50000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I15" s="20">
-        <f>'[32]MD50000.15-DEC'!$K$2</f>
+        <f>'[37]MD50000.15-DEC'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J15" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K15" s="22">
-        <f>'[32]MD50000.15-DEC'!$B$3</f>
+        <f>'[37]MD50000.15-DEC'!$B$3</f>
         <v>45648</v>
       </c>
       <c r="L15" s="19">
-        <f>'[32]MD50000.15-DEC'!$O$2</f>
+        <f>'[37]MD50000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M15" s="19">
-        <f>'[32]MD50000.15-DEC'!$O$1</f>
+        <f>'[37]MD50000.15-DEC'!$O$1</f>
         <v>84000</v>
       </c>
     </row>
@@ -6928,15 +6996,15 @@
         <v>33</v>
       </c>
       <c r="E16" s="19">
-        <f>'[33]MD20000.18-DEC'!$C$1</f>
+        <f>'[38]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F16" s="20">
-        <f>'[33]MD20000.18-DEC'!$K$1</f>
+        <f>'[38]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G16" s="20">
-        <f>'[33]MD20000.18-DEC'!$K$2</f>
+        <f>'[38]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H16" s="20"/>
@@ -6945,15 +7013,15 @@
         <v>53</v>
       </c>
       <c r="K16" s="22">
-        <f>'[33]MD20000.18-DEC'!$B$3</f>
+        <f>'[38]MD20000.18-DEC'!$B$3</f>
         <v>45279</v>
       </c>
       <c r="L16" s="19">
-        <f>'[33]MD20000.18-DEC'!$O$2</f>
+        <f>'[38]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M16" s="19">
-        <f>'[33]MD20000.18-DEC'!$O$1</f>
+        <f>'[38]MD20000.18-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -6968,15 +7036,15 @@
         <v>33</v>
       </c>
       <c r="E17" s="19">
-        <f>'[34]MD20000.22-DEC'!$C$1</f>
+        <f>'[39]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F17" s="20">
-        <f>'[34]MD20000.22-DEC'!$K$1</f>
+        <f>'[39]MD20000.22-DEC'!$K$1</f>
         <v>120</v>
       </c>
       <c r="G17" s="20">
-        <f>'[34]MD20000.22-DEC'!$K$2</f>
+        <f>'[39]MD20000.22-DEC'!$K$2</f>
         <v>0</v>
       </c>
       <c r="H17" s="20"/>
@@ -6985,12 +7053,12 @@
         <v>51</v>
       </c>
       <c r="K17" s="22">
-        <f>'[34]MD20000.22-DEC'!$B$3</f>
+        <f>'[39]MD20000.22-DEC'!$B$3</f>
         <v>0</v>
       </c>
       <c r="L17" s="19"/>
       <c r="M17" s="19">
-        <f>'[34]MD20000.22-DEC'!$O$1</f>
+        <f>'[39]MD20000.22-DEC'!$O$1</f>
         <v>0</v>
       </c>
     </row>
@@ -7005,32 +7073,32 @@
         <v>36</v>
       </c>
       <c r="E18" s="19">
-        <f>'[35]MD50000.15-DEC'!$C$1</f>
+        <f>'[40]MD50000.15-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F18" s="20"/>
       <c r="G18" s="20"/>
       <c r="H18" s="20">
-        <f>'[35]MD50000.15-DEC'!$K$1</f>
+        <f>'[40]MD50000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I18" s="20">
-        <f>'[35]MD50000.15-DEC'!$K$2</f>
+        <f>'[40]MD50000.15-DEC'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J18" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K18" s="22">
-        <f>'[35]MD50000.15-DEC'!$B$3</f>
+        <f>'[40]MD50000.15-DEC'!$B$3</f>
         <v>45310</v>
       </c>
       <c r="L18" s="19">
-        <f>'[35]MD50000.15-DEC'!$O$2</f>
+        <f>'[40]MD50000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M18" s="19">
-        <f>'[35]MD50000.15-DEC'!$O$1</f>
+        <f>'[40]MD50000.15-DEC'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -7045,15 +7113,15 @@
         <v>18</v>
       </c>
       <c r="E19" s="19">
-        <f>'[36]MD5000-Jan24'!$C$1</f>
+        <f>'[41]MD5000-Jan24'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F19" s="20">
-        <f>'[36]MD5000-Jan24'!$K$1</f>
+        <f>'[41]MD5000-Jan24'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G19" s="20">
-        <f>'[36]MD5000-Jan24'!$K$2</f>
+        <f>'[41]MD5000-Jan24'!$K$2</f>
         <v>60</v>
       </c>
       <c r="H19" s="20"/>
@@ -7062,15 +7130,15 @@
         <v>51</v>
       </c>
       <c r="K19" s="22">
-        <f>'[36]MD5000-Jan24'!$B$3</f>
+        <f>'[41]MD5000-Jan24'!$B$3</f>
         <v>45302</v>
       </c>
       <c r="L19" s="19">
-        <f>'[36]MD5000-Jan24'!$O$2</f>
+        <f>'[41]MD5000-Jan24'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M19" s="19">
-        <f>'[36]MD5000-Jan24'!$O$1</f>
+        <f>'[41]MD5000-Jan24'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -7085,32 +7153,32 @@
         <v>39</v>
       </c>
       <c r="E20" s="19">
-        <f>'[37]MD10000.10-JAN'!$C$1</f>
+        <f>'[42]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F20" s="20"/>
       <c r="G20" s="20"/>
       <c r="H20" s="20">
-        <f>'[37]MD10000.10-JAN'!$K$1</f>
+        <f>'[42]MD10000.10-JAN'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I20" s="20">
-        <f>'[37]MD10000.10-JAN'!$K$2</f>
+        <f>'[42]MD10000.10-JAN'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J20" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K20" s="22">
-        <f>'[37]MD10000.10-JAN'!$B$3</f>
+        <f>'[42]MD10000.10-JAN'!$B$3</f>
         <v>45308</v>
       </c>
       <c r="L20" s="19">
-        <f>'[37]MD10000.10-JAN'!$O$2</f>
+        <f>'[42]MD10000.10-JAN'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M20" s="19">
-        <f>'[37]MD10000.10-JAN'!$O$1</f>
+        <f>'[42]MD10000.10-JAN'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -7125,32 +7193,32 @@
         <v>39</v>
       </c>
       <c r="E21" s="19">
-        <f>'[38]MD10000.10-JAN'!$C$1</f>
+        <f>'[43]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F21" s="20"/>
       <c r="G21" s="20"/>
       <c r="H21" s="20">
-        <f>'[38]MD10000.10-JAN'!$K$1</f>
+        <f>'[43]MD10000.10-JAN'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I21" s="20">
-        <f>'[38]MD10000.10-JAN'!$K$2</f>
+        <f>'[43]MD10000.10-JAN'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J21" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K21" s="22">
-        <f>'[38]MD10000.10-JAN'!$B$3</f>
+        <f>'[43]MD10000.10-JAN'!$B$3</f>
         <v>45308</v>
       </c>
       <c r="L21" s="19">
-        <f>'[38]MD10000.10-JAN'!$O$2</f>
+        <f>'[43]MD10000.10-JAN'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M21" s="19">
-        <f>'[38]MD10000.10-JAN'!$O$1</f>
+        <f>'[43]MD10000.10-JAN'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -7165,32 +7233,32 @@
         <v>43</v>
       </c>
       <c r="E22" s="19">
-        <f>'[39]MD10000.20-OCT'!$C$1</f>
+        <f>'[44]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F22" s="20"/>
       <c r="G22" s="20"/>
       <c r="H22" s="20">
-        <f>'[39]MD10000.20-OCT'!$K$1</f>
+        <f>'[44]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I22" s="20">
-        <f>'[39]MD10000.20-OCT'!$K$2</f>
+        <f>'[44]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J22" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K22" s="22">
-        <f>'[39]MD10000.20-OCT'!$B$3</f>
+        <f>'[44]MD10000.20-OCT'!$B$3</f>
         <v>45316</v>
       </c>
       <c r="L22" s="19">
-        <f>'[39]MD10000.20-OCT'!$O$2</f>
+        <f>'[44]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M22" s="19">
-        <f>'[39]MD10000.20-OCT'!$O$1</f>
+        <f>'[44]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -7205,32 +7273,32 @@
         <v>36</v>
       </c>
       <c r="E23" s="19">
-        <f>'[40]MD10000.20-OCT'!$C$1</f>
+        <f>'[45]MD10000.20-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
       <c r="H23" s="20">
-        <f>'[40]MD10000.20-OCT'!$K$1</f>
+        <f>'[45]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I23" s="20">
-        <f>'[40]MD10000.20-OCT'!$K$2</f>
+        <f>'[45]MD10000.20-OCT'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J23" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K23" s="22">
-        <f>'[40]MD10000.20-OCT'!$B$3</f>
+        <f>'[45]MD10000.20-OCT'!$B$3</f>
         <v>45324</v>
       </c>
       <c r="L23" s="19">
-        <f>'[40]MD10000.20-OCT'!$O$2</f>
+        <f>'[45]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M23" s="19">
-        <f>'[40]MD10000.20-OCT'!$O$1</f>
+        <f>'[45]MD10000.20-OCT'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -7245,32 +7313,32 @@
         <v>46</v>
       </c>
       <c r="E24" s="19">
-        <f>'[41]MD10000.20-OCT'!$C$1</f>
+        <f>'[46]MD10000.20-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F24" s="20"/>
       <c r="G24" s="20"/>
       <c r="H24" s="20">
-        <f>'[41]MD10000.20-OCT'!$K$1</f>
+        <f>'[46]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I24" s="20">
-        <f>'[41]MD10000.20-OCT'!$K$2</f>
+        <f>'[46]MD10000.20-OCT'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J24" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K24" s="22">
-        <f>'[41]MD10000.20-OCT'!$B$3</f>
+        <f>'[46]MD10000.20-OCT'!$B$3</f>
         <v>45327</v>
       </c>
       <c r="L24" s="19">
-        <f>'[41]MD10000.20-OCT'!$O$2</f>
+        <f>'[46]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M24" s="19">
-        <f>'[41]MD10000.20-OCT'!$O$1</f>
+        <f>'[46]MD10000.20-OCT'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -7285,15 +7353,15 @@
         <v>18</v>
       </c>
       <c r="E25" s="19">
-        <f>'[42]SM5000.1-oct'!$C$1</f>
+        <f>'[47]SM5000.1-oct'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F25" s="20">
-        <f>'[42]SM5000.1-oct'!$K$1</f>
+        <f>'[47]SM5000.1-oct'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G25" s="20">
-        <f>'[42]SM5000.1-oct'!$K$2</f>
+        <f>'[47]SM5000.1-oct'!$K$2</f>
         <v>60</v>
       </c>
       <c r="H25" s="20"/>
@@ -7302,15 +7370,15 @@
         <v>12</v>
       </c>
       <c r="K25" s="22">
-        <f>'[42]SM5000.1-oct'!$B$3</f>
+        <f>'[47]SM5000.1-oct'!$B$3</f>
         <v>45323</v>
       </c>
       <c r="L25" s="19">
-        <f>'[42]SM5000.1-oct'!$O$2</f>
+        <f>'[47]SM5000.1-oct'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M25" s="19">
-        <f>'[42]SM5000.1-oct'!$O$1</f>
+        <f>'[47]SM5000.1-oct'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -7325,32 +7393,32 @@
         <v>48</v>
       </c>
       <c r="E26" s="19">
-        <f>'[43]MD10000.20-OCT'!$C$1</f>
+        <f>'[48]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F26" s="20"/>
       <c r="G26" s="20"/>
       <c r="H26" s="20">
-        <f>'[43]MD10000.20-OCT'!$K$1</f>
+        <f>'[48]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I26" s="20">
-        <f>'[43]MD10000.20-OCT'!$K$2</f>
+        <f>'[48]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J26" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K26" s="22">
-        <f>'[43]MD10000.20-OCT'!$B$3</f>
+        <f>'[48]MD10000.20-OCT'!$B$3</f>
         <v>45332</v>
       </c>
       <c r="L26" s="19">
-        <f>'[43]MD10000.20-OCT'!$O$2</f>
+        <f>'[48]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M26" s="19">
-        <f>'[43]MD10000.20-OCT'!$O$1</f>
+        <f>'[48]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -7365,15 +7433,15 @@
         <v>19</v>
       </c>
       <c r="E27" s="19">
-        <f>'[44]MD10000.1-OCT'!$C$1</f>
+        <f>'[49]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F27" s="20">
-        <f>'[44]MD10000.1-OCT'!$K$1</f>
+        <f>'[49]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G27" s="20">
-        <f>'[44]MD10000.1-OCT'!$K$2</f>
+        <f>'[49]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H27" s="20"/>
@@ -7382,15 +7450,15 @@
         <v>12</v>
       </c>
       <c r="K27" s="22">
-        <f>'[44]MD10000.1-OCT'!$B$3</f>
+        <f>'[49]MD10000.1-OCT'!$B$3</f>
         <v>45339</v>
       </c>
       <c r="L27" s="19">
-        <f>'[44]MD10000.1-OCT'!$O$2</f>
+        <f>'[49]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M27" s="19">
-        <f>'[44]MD10000.1-OCT'!$O$1</f>
+        <f>'[49]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -7405,15 +7473,15 @@
         <v>19</v>
       </c>
       <c r="E28" s="19">
-        <f>'[45]MD10000.1-OCT'!$C$1</f>
+        <f>'[50]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F28" s="20">
-        <f>'[45]MD10000.1-OCT'!$K$1</f>
+        <f>'[50]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G28" s="20">
-        <f>'[45]MD10000.1-OCT'!$K$2</f>
+        <f>'[50]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H28" s="20"/>
@@ -7422,15 +7490,15 @@
         <v>51</v>
       </c>
       <c r="K28" s="22">
-        <f>'[45]MD10000.1-OCT'!$B$3</f>
+        <f>'[50]MD10000.1-OCT'!$B$3</f>
         <v>45334</v>
       </c>
       <c r="L28" s="19">
-        <f>'[45]MD10000.1-OCT'!$O$2</f>
+        <f>'[50]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M28" s="19">
-        <f>'[45]MD10000.1-OCT'!$O$1</f>
+        <f>'[50]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -7445,32 +7513,32 @@
         <v>50</v>
       </c>
       <c r="E29" s="19">
-        <f>'[46]MD20000.15-DEC'!$C$1</f>
+        <f>'[51]MD20000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
       <c r="H29" s="20">
-        <f>'[46]MD20000.15-DEC'!$K$1</f>
+        <f>'[51]MD20000.15-DEC'!$K$1</f>
         <v>5</v>
       </c>
       <c r="I29" s="20">
-        <f>'[46]MD20000.15-DEC'!$K$2</f>
+        <f>'[51]MD20000.15-DEC'!$K$2</f>
         <v>12</v>
       </c>
       <c r="J29" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K29" s="22">
-        <f>'[46]MD20000.15-DEC'!$B$3</f>
+        <f>'[51]MD20000.15-DEC'!$B$3</f>
         <v>45337</v>
       </c>
       <c r="L29" s="19">
-        <f>'[47]MD20000.15-DEC'!$O$2</f>
+        <f>'[52]MD20000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M29" s="19">
-        <f>'[47]MD20000.15-DEC'!$O$1</f>
+        <f>'[52]MD20000.15-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7485,32 +7553,32 @@
         <v>52</v>
       </c>
       <c r="E30" s="19">
-        <f>'[48]MD20000.15-DEC'!$C$1</f>
+        <f>'[53]MD20000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F30" s="20"/>
       <c r="G30" s="20"/>
       <c r="H30" s="20">
-        <f>'[48]MD20000.15-DEC'!$K$1</f>
+        <f>'[53]MD20000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I30" s="20">
-        <f>'[48]MD20000.15-DEC'!$K$2</f>
+        <f>'[53]MD20000.15-DEC'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J30" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K30" s="22">
-        <f>'[48]MD20000.15-DEC'!$B$3</f>
+        <f>'[53]MD20000.15-DEC'!$B$3</f>
         <v>45345</v>
       </c>
       <c r="L30" s="19">
-        <f>'[48]MD20000.15-DEC'!$O$2</f>
+        <f>'[53]MD20000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M30" s="19">
-        <f>'[48]MD20000.15-DEC'!$O$1</f>
+        <f>'[53]MD20000.15-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7525,15 +7593,15 @@
         <v>33</v>
       </c>
       <c r="E31" s="19">
-        <f>'[49]MD20000.18-DEC'!$C$1</f>
+        <f>'[54]MD20000.18-DEC'!$C$1</f>
         <v>30000</v>
       </c>
       <c r="F31" s="20">
-        <f>'[49]MD20000.18-DEC'!$K$1</f>
+        <f>'[54]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G31" s="20">
-        <f>'[49]MD20000.18-DEC'!$K$2</f>
+        <f>'[54]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H31" s="20"/>
@@ -7542,15 +7610,15 @@
         <v>51</v>
       </c>
       <c r="K31" s="22">
-        <f>'[49]MD20000.18-DEC'!$B$3</f>
+        <f>'[54]MD20000.18-DEC'!$B$3</f>
         <v>45354</v>
       </c>
       <c r="L31" s="19">
-        <f>'[49]MD20000.18-DEC'!$O$2</f>
+        <f>'[54]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M31" s="19">
-        <f>'[49]MD20000.18-DEC'!$O$1</f>
+        <f>'[54]MD20000.18-DEC'!$O$1</f>
         <v>36000</v>
       </c>
     </row>
@@ -7565,32 +7633,32 @@
         <v>36</v>
       </c>
       <c r="E32" s="19">
-        <f>'[50]MD10000.10-JAN'!$C$1</f>
+        <f>'[55]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F32" s="20"/>
       <c r="G32" s="20"/>
       <c r="H32" s="20">
-        <f>'[50]MD10000.10-JAN'!$K$1</f>
+        <f>'[55]MD10000.10-JAN'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I32" s="20">
-        <f>'[50]MD10000.10-JAN'!$K$2</f>
+        <f>'[55]MD10000.10-JAN'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J32" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K32" s="22">
-        <f>'[50]MD10000.10-JAN'!$B$3</f>
+        <f>'[55]MD10000.10-JAN'!$B$3</f>
         <v>45366</v>
       </c>
       <c r="L32" s="19">
-        <f>'[50]MD10000.10-JAN'!$O$2</f>
+        <f>'[55]MD10000.10-JAN'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M32" s="19">
-        <f>'[50]MD10000.10-JAN'!$O$1</f>
+        <f>'[55]MD10000.10-JAN'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -7605,32 +7673,32 @@
         <v>52</v>
       </c>
       <c r="E33" s="19">
-        <f>'[51]MD20000.15-DEc'!$C$1</f>
+        <f>'[56]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F33" s="20"/>
       <c r="G33" s="20"/>
       <c r="H33" s="20">
-        <f>'[51]MD20000.15-DEc'!$K$1</f>
+        <f>'[56]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I33" s="20">
-        <f>'[51]MD20000.15-DEc'!$K$2</f>
+        <f>'[56]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J33" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K33" s="22">
-        <f>'[51]MD20000.15-DEc'!$B$3</f>
+        <f>'[56]MD20000.15-DEc'!$B$3</f>
         <v>45380</v>
       </c>
       <c r="L33" s="19">
-        <f>'[51]MD20000.15-DEc'!$O$2</f>
+        <f>'[56]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M33" s="19">
-        <f>'[51]MD20000.15-DEc'!$O$1</f>
+        <f>'[56]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7645,32 +7713,32 @@
         <v>36</v>
       </c>
       <c r="E34" s="19">
-        <f>'[52]MD10000.10-JAN'!$C$1</f>
+        <f>'[57]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F34" s="20"/>
       <c r="G34" s="20"/>
       <c r="H34" s="20">
-        <f>'[52]MD10000.10-JAN'!$K$1</f>
+        <f>'[57]MD10000.10-JAN'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I34" s="20">
-        <f>'[52]MD10000.10-JAN'!$K$2</f>
+        <f>'[57]MD10000.10-JAN'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J34" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K34" s="22">
-        <f>'[52]MD10000.10-JAN'!$B$3</f>
+        <f>'[57]MD10000.10-JAN'!$B$3</f>
         <v>45389</v>
       </c>
       <c r="L34" s="19">
-        <f>'[52]MD10000.10-JAN'!$O$2</f>
+        <f>'[57]MD10000.10-JAN'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M34" s="19">
-        <f>'[52]MD10000.10-JAN'!$O$1</f>
+        <f>'[57]MD10000.10-JAN'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -7685,32 +7753,32 @@
         <v>52</v>
       </c>
       <c r="E35" s="19">
-        <f>'[53]MD20000.15-DEc'!$C$1</f>
+        <f>'[58]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F35" s="20"/>
       <c r="G35" s="20"/>
       <c r="H35" s="20">
-        <f>'[53]MD20000.15-DEc'!$G$1</f>
+        <f>'[58]MD20000.15-DEc'!$G$1</f>
         <v>17</v>
       </c>
       <c r="I35" s="20">
-        <f>'[53]MD20000.15-DEc'!$K$2</f>
+        <f>'[58]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J35" s="21" t="s">
         <v>77</v>
       </c>
       <c r="K35" s="22">
-        <f>'[53]MD20000.15-DEc'!$B$3</f>
+        <f>'[58]MD20000.15-DEc'!$B$3</f>
         <v>45394</v>
       </c>
       <c r="L35" s="19">
-        <f>'[53]MD20000.15-DEc'!$O$2</f>
+        <f>'[58]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M35" s="19">
-        <f>'[53]MD20000.15-DEc'!$O$1</f>
+        <f>'[58]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7736,7 +7804,7 @@
       </c>
       <c r="I36" s="13">
         <f>'[1]MD10000.10-JAN'!$K$2</f>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J36" s="16" t="s">
         <v>12</v>
@@ -7747,11 +7815,11 @@
       </c>
       <c r="L36" s="15">
         <f>'[1]MD10000.10-JAN'!$O$2</f>
-        <v>2100</v>
+        <v>1400</v>
       </c>
       <c r="M36" s="15">
         <f>'[1]MD10000.10-JAN'!$O$1</f>
-        <v>14700</v>
+        <v>15400</v>
       </c>
       <c r="N36" s="1">
         <v>350</v>
@@ -7768,32 +7836,32 @@
         <v>52</v>
       </c>
       <c r="E37" s="19">
-        <f>'[54]MD20000.15-DEc'!$C$1</f>
+        <f>'[59]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F37" s="20"/>
       <c r="G37" s="20"/>
       <c r="H37" s="20">
-        <f>'[54]MD20000.15-DEc'!$G$1</f>
+        <f>'[59]MD20000.15-DEc'!$G$1</f>
         <v>17</v>
       </c>
       <c r="I37" s="20">
-        <f>'[54]MD20000.15-DEc'!$K$2</f>
+        <f>'[59]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J37" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K37" s="22">
-        <f>'[54]MD20000.15-DEc'!$B$3</f>
+        <f>'[59]MD20000.15-DEc'!$B$3</f>
         <v>45406</v>
       </c>
       <c r="L37" s="19">
-        <f>'[54]MD20000.15-DEc'!$O$2</f>
+        <f>'[59]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M37" s="19">
-        <f>'[54]MD20000.15-DEc'!$O$1</f>
+        <f>'[59]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7808,32 +7876,32 @@
         <v>60</v>
       </c>
       <c r="E38" s="19">
-        <f>'[55]MD10000.20-OCT'!$C$1</f>
+        <f>'[60]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F38" s="20"/>
       <c r="G38" s="20"/>
       <c r="H38" s="20">
-        <f>'[55]MD10000.20-OCT'!$G$1</f>
+        <f>'[60]MD10000.20-OCT'!$G$1</f>
         <v>17</v>
       </c>
       <c r="I38" s="20">
-        <f>'[55]MD10000.20-OCT'!$K$2</f>
+        <f>'[60]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J38" s="21" t="s">
         <v>77</v>
       </c>
       <c r="K38" s="22">
-        <f>'[55]MD10000.20-OCT'!$B$3</f>
+        <f>'[60]MD10000.20-OCT'!$B$3</f>
         <v>45406</v>
       </c>
       <c r="L38" s="19">
-        <f>'[55]MD10000.20-OCT'!$O$2</f>
+        <f>'[60]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M38" s="19">
-        <f>'[55]MD10000.20-OCT'!$O$1</f>
+        <f>'[60]MD10000.20-OCT'!$O$1</f>
         <v>5950</v>
       </c>
     </row>
@@ -7848,32 +7916,32 @@
         <v>62</v>
       </c>
       <c r="E39" s="19">
-        <f>'[56]MD50000.15-DEC'!$C$1</f>
+        <f>'[61]MD50000.15-DEC'!$C$1</f>
         <v>40000</v>
       </c>
       <c r="F39" s="20"/>
       <c r="G39" s="20"/>
       <c r="H39" s="20">
-        <f>'[56]MD50000.15-DEC'!$K$1</f>
+        <f>'[61]MD50000.15-DEC'!$K$1</f>
         <v>47</v>
       </c>
       <c r="I39" s="20">
-        <f>'[56]MD50000.15-DEC'!$K$2</f>
+        <f>'[61]MD50000.15-DEC'!$K$2</f>
         <v>1</v>
       </c>
       <c r="J39" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K39" s="22">
-        <f>'[56]MD50000.15-DEC'!$B$3</f>
+        <f>'[61]MD50000.15-DEC'!$B$3</f>
         <v>45416</v>
       </c>
       <c r="L39" s="19">
-        <f>'[57]MD50000.15-DEC'!$O$2</f>
+        <f>'[62]MD50000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M39" s="19">
-        <f>'[56]MD50000.15-DEC'!$O$1</f>
+        <f>'[61]MD50000.15-DEC'!$O$1</f>
         <v>1400</v>
       </c>
     </row>
@@ -7888,32 +7956,32 @@
         <v>85</v>
       </c>
       <c r="E40" s="19">
-        <f>'[58]MD10000.20-OCT'!$C$1</f>
+        <f>'[63]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F40" s="20"/>
       <c r="G40" s="20"/>
       <c r="H40" s="20">
-        <f>'[58]MD10000.20-OCT'!$K$1</f>
+        <f>'[63]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I40" s="20">
-        <f>'[58]MD10000.20-OCT'!$K$2</f>
+        <f>'[63]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J40" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K40" s="22">
-        <f>'[58]MD10000.20-OCT'!$B$3</f>
+        <f>'[63]MD10000.20-OCT'!$B$3</f>
         <v>45427</v>
       </c>
       <c r="L40" s="19">
-        <f>'[58]MD10000.20-OCT'!$O$2</f>
+        <f>'[63]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M40" s="19">
-        <f>'[58]MD10000.20-OCT'!$O$1</f>
+        <f>'[63]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -7928,15 +7996,15 @@
         <v>33</v>
       </c>
       <c r="E41" s="19">
-        <f>'[59]MD20000.18-DEC'!$C$1</f>
+        <f>'[64]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F41" s="20">
-        <f>'[59]MD20000.18-DEC'!$K$1</f>
+        <f>'[64]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G41" s="20">
-        <f>'[59]MD20000.18-DEC'!$K$2</f>
+        <f>'[64]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H41" s="20"/>
@@ -7945,15 +8013,15 @@
         <v>77</v>
       </c>
       <c r="K41" s="22">
-        <f>'[59]MD20000.18-DEC'!$B$3</f>
+        <f>'[64]MD20000.18-DEC'!$B$3</f>
         <v>45425</v>
       </c>
       <c r="L41" s="19">
-        <f>'[59]MD20000.18-DEC'!$O$2</f>
+        <f>'[64]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M41" s="19">
-        <f>'[59]MD20000.18-DEC'!$O$1</f>
+        <f>'[64]MD20000.18-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7968,32 +8036,32 @@
         <v>66</v>
       </c>
       <c r="E42" s="19">
-        <f>'[60]MD10000.20-OCT'!$C$1</f>
+        <f>'[65]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F42" s="20"/>
       <c r="G42" s="20"/>
       <c r="H42" s="20">
-        <f>'[60]MD10000.20-OCT'!$K$1</f>
+        <f>'[65]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I42" s="20">
-        <f>'[60]MD10000.20-OCT'!$K$2</f>
+        <f>'[65]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J42" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K42" s="22">
-        <f>'[60]MD10000.20-OCT'!$B$3</f>
+        <f>'[65]MD10000.20-OCT'!$B$3</f>
         <v>45436</v>
       </c>
       <c r="L42" s="19">
-        <f>'[60]MD10000.20-OCT'!$O$2</f>
+        <f>'[65]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M42" s="19">
-        <f>'[60]MD10000.20-OCT'!$O$1</f>
+        <f>'[65]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -8008,15 +8076,15 @@
         <v>33</v>
       </c>
       <c r="E43" s="19">
-        <f>'[61]MD20000.22-DEC'!$C$1</f>
+        <f>'[66]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F43" s="20">
-        <f>'[61]MD20000.22-DEC'!$K$1</f>
+        <f>'[66]MD20000.22-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G43" s="20">
-        <f>'[61]MD20000.22-DEC'!$K$2</f>
+        <f>'[66]MD20000.22-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H43" s="20"/>
@@ -8025,15 +8093,15 @@
         <v>12</v>
       </c>
       <c r="K43" s="22">
-        <f>'[61]MD20000.22-DEC'!$B$3</f>
+        <f>'[66]MD20000.22-DEC'!$B$3</f>
         <v>45432</v>
       </c>
       <c r="L43" s="19">
-        <f>'[61]MD20000.22-DEC'!$O$2</f>
+        <f>'[66]MD20000.22-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M43" s="19">
-        <f>'[61]MD20000.22-DEC'!$O$1</f>
+        <f>'[66]MD20000.22-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -8048,15 +8116,15 @@
         <v>68</v>
       </c>
       <c r="E44" s="19">
-        <f>'[62]MD10000.1-OCT'!$C$1</f>
+        <f>'[67]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F44" s="20">
-        <f>'[62]MD10000.1-OCT'!$G$1</f>
+        <f>'[67]MD10000.1-OCT'!$G$1</f>
         <v>120</v>
       </c>
       <c r="G44" s="20">
-        <f>'[62]MD10000.1-OCT'!$K$1</f>
+        <f>'[67]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="H44" s="20"/>
@@ -8065,15 +8133,15 @@
         <v>77</v>
       </c>
       <c r="K44" s="22">
-        <f>'[62]MD10000.1-OCT'!$B$3</f>
+        <f>'[67]MD10000.1-OCT'!$B$3</f>
         <v>45437</v>
       </c>
       <c r="L44" s="19">
-        <f>'[62]MD10000.1-OCT'!$O$2</f>
+        <f>'[67]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M44" s="19">
-        <f>'[62]MD10000.1-OCT'!$O$1</f>
+        <f>'[67]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -8088,29 +8156,29 @@
         <v>48</v>
       </c>
       <c r="E45" s="19">
-        <f>'[63]MD10000.20-OCT'!$C$1</f>
+        <f>'[68]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F45" s="20"/>
       <c r="G45" s="20"/>
       <c r="H45" s="20">
-        <f>'[63]MD10000.20-OCT'!$K$1</f>
+        <f>'[68]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I45" s="20">
-        <f>'[63]MD10000.20-OCT'!$K$2</f>
+        <f>'[68]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J45" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K45" s="22">
-        <f>'[63]MD10000.20-OCT'!$B$3</f>
+        <f>'[68]MD10000.20-OCT'!$B$3</f>
         <v>45444</v>
       </c>
       <c r="L45" s="19"/>
       <c r="M45" s="19">
-        <f>'[63]MD10000.20-OCT'!$O$1</f>
+        <f>'[68]MD10000.20-OCT'!$O$1</f>
         <v>5950</v>
       </c>
     </row>
@@ -8125,32 +8193,32 @@
         <v>71</v>
       </c>
       <c r="E46" s="19">
-        <f>'[64]MD10000.1-OCT'!$C$1</f>
+        <f>'[69]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F46" s="20"/>
       <c r="G46" s="20"/>
       <c r="H46" s="20">
-        <f>'[65]MD10000.1-OCT'!$K$1</f>
+        <f>'[70]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I46" s="20">
-        <f>'[65]MD10000.1-OCT'!$K$2</f>
+        <f>'[70]MD10000.1-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J46" s="21" t="s">
         <v>77</v>
       </c>
       <c r="K46" s="22">
-        <f>'[64]MD10000.1-OCT'!$B$3</f>
+        <f>'[69]MD10000.1-OCT'!$B$3</f>
         <v>45450</v>
       </c>
       <c r="L46" s="19">
-        <f>'[65]MD10000.1-OCT'!$O$2</f>
+        <f>'[70]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M46" s="19">
-        <f>'[65]MD10000.1-OCT'!$O$1</f>
+        <f>'[70]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -8165,15 +8233,15 @@
         <v>33</v>
       </c>
       <c r="E47" s="19">
-        <f>'[66]MD20000.22-DEC'!$C$1</f>
+        <f>'[71]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F47" s="20">
-        <f>'[66]MD20000.22-DEC'!$K$1</f>
+        <f>'[71]MD20000.22-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G47" s="20">
-        <f>'[66]MD20000.22-DEC'!$K$2</f>
+        <f>'[71]MD20000.22-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H47" s="20"/>
@@ -8182,15 +8250,15 @@
         <v>77</v>
       </c>
       <c r="K47" s="22">
-        <f>'[66]MD20000.22-DEC'!$B$3</f>
+        <f>'[71]MD20000.22-DEC'!$B$3</f>
         <v>45446</v>
       </c>
       <c r="L47" s="19">
-        <f>'[66]MD20000.22-DEC'!$O$2</f>
+        <f>'[71]MD20000.22-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M47" s="19">
-        <f>'[66]MD20000.22-DEC'!$O$1</f>
+        <f>'[71]MD20000.22-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -8205,15 +8273,15 @@
         <v>68</v>
       </c>
       <c r="E48" s="19">
-        <f>'[67]MD20000.22-DEC'!$C$1</f>
+        <f>'[72]MD20000.22-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F48" s="20">
-        <f>'[67]MD20000.22-DEC'!$K$1</f>
+        <f>'[72]MD20000.22-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G48" s="20">
-        <f>'[67]MD20000.22-DEC'!$K$2</f>
+        <f>'[72]MD20000.22-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H48" s="20"/>
@@ -8222,15 +8290,15 @@
         <v>77</v>
       </c>
       <c r="K48" s="22">
-        <f>'[67]MD20000.22-DEC'!$B$3</f>
+        <f>'[72]MD20000.22-DEC'!$B$3</f>
         <v>45473</v>
       </c>
       <c r="L48" s="19">
-        <f>'[67]MD20000.22-DEC'!$O$2</f>
+        <f>'[72]MD20000.22-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M48" s="19">
-        <f>'[67]MD20000.22-DEC'!$O$1</f>
+        <f>'[72]MD20000.22-DEC'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -8245,32 +8313,32 @@
         <v>50</v>
       </c>
       <c r="E49" s="19">
-        <f>'[68]MD20000.15-DEc'!$C$1</f>
+        <f>'[73]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F49" s="20"/>
       <c r="G49" s="20"/>
       <c r="H49" s="20">
-        <f>'[68]MD20000.15-DEc'!$K$1</f>
+        <f>'[73]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I49" s="20">
-        <f>'[68]MD20000.15-DEc'!$K$2</f>
+        <f>'[73]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J49" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K49" s="22">
-        <f>'[68]MD20000.15-DEc'!$B$3</f>
+        <f>'[73]MD20000.15-DEc'!$B$3</f>
         <v>45495</v>
       </c>
       <c r="L49" s="19">
-        <f>'[68]MD20000.15-DEc'!$O$2</f>
+        <f>'[73]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M49" s="19">
-        <f>'[68]MD20000.15-DEc'!$O$1</f>
+        <f>'[73]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -8285,32 +8353,32 @@
         <v>75</v>
       </c>
       <c r="E50" s="19">
-        <f>'[69]MD20000.15-DEc'!$C$1</f>
+        <f>'[74]MD20000.15-DEc'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F50" s="20"/>
       <c r="G50" s="20"/>
       <c r="H50" s="20">
-        <f>'[69]MD20000.15-DEc'!$K$1</f>
+        <f>'[74]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I50" s="20">
-        <f>'[69]MD20000.15-DEc'!$K$2</f>
+        <f>'[74]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J50" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K50" s="22">
-        <f>'[69]MD20000.15-DEc'!$B$3</f>
+        <f>'[74]MD20000.15-DEc'!$B$3</f>
         <v>45496</v>
       </c>
       <c r="L50" s="19">
-        <f>'[69]MD20000.15-DEc'!$O$2</f>
+        <f>'[74]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M50" s="19">
-        <f>'[69]MD20000.15-DEc'!$O$1</f>
+        <f>'[74]MD20000.15-DEc'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -8325,15 +8393,15 @@
         <v>33</v>
       </c>
       <c r="E51" s="19">
-        <f>'[70]MD20000.18-DEC'!$C$1</f>
+        <f>'[75]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F51" s="20">
-        <f>'[70]MD20000.18-DEC'!$K$1</f>
+        <f>'[75]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G51" s="20">
-        <f>'[70]MD20000.18-DEC'!$K$2</f>
+        <f>'[75]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H51" s="20"/>
@@ -8342,15 +8410,15 @@
         <v>12</v>
       </c>
       <c r="K51" s="22">
-        <f>'[70]MD20000.18-DEC'!$B$3</f>
+        <f>'[75]MD20000.18-DEC'!$B$3</f>
         <v>45493</v>
       </c>
       <c r="L51" s="19">
-        <f>'[70]MD20000.18-DEC'!$O$2</f>
+        <f>'[75]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M51" s="19">
-        <f>'[70]MD20000.18-DEC'!$O$1</f>
+        <f>'[75]MD20000.18-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -8365,32 +8433,32 @@
         <v>76</v>
       </c>
       <c r="E52" s="19">
-        <f>'[71]MD20000.15-DEc'!$C$1</f>
+        <f>'[76]MD20000.15-DEc'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F52" s="20"/>
       <c r="G52" s="20"/>
       <c r="H52" s="20">
-        <f>'[71]MD20000.15-DEc'!$K$1</f>
+        <f>'[76]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I52" s="20">
-        <f>'[71]MD20000.15-DEc'!$K$2</f>
+        <f>'[76]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J52" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K52" s="22">
-        <f>'[71]MD20000.15-DEc'!$B$3</f>
+        <f>'[76]MD20000.15-DEc'!$B$3</f>
         <v>45502</v>
       </c>
       <c r="L52" s="19">
-        <f>'[71]MD20000.15-DEc'!$O$2</f>
+        <f>'[76]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M52" s="19">
-        <f>'[71]MD20000.15-DEc'!$O$1</f>
+        <f>'[76]MD20000.15-DEc'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -8405,32 +8473,32 @@
         <v>50</v>
       </c>
       <c r="E53" s="19">
-        <f>'[72]MD50000.15-DEC'!$C$1</f>
+        <f>'[77]MD50000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F53" s="20"/>
       <c r="G53" s="20"/>
       <c r="H53" s="20">
-        <f>'[72]MD50000.15-DEC'!$K$1</f>
+        <f>'[77]MD50000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I53" s="20">
-        <f>'[72]MD50000.15-DEC'!$K$2</f>
+        <f>'[77]MD50000.15-DEC'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J53" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K53" s="22">
-        <f>'[72]MD50000.15-DEC'!$B$3</f>
+        <f>'[77]MD50000.15-DEC'!$B$3</f>
         <v>45504</v>
       </c>
       <c r="L53" s="19">
-        <f>'[72]MD50000.15-DEC'!$O$2</f>
+        <f>'[77]MD50000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M53" s="19">
-        <f>'[72]MD50000.15-DEC'!$O$1</f>
+        <f>'[77]MD50000.15-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -8445,32 +8513,32 @@
         <v>79</v>
       </c>
       <c r="E54" s="19">
-        <f>'[73]MD10000.20-OCT'!$C$1</f>
+        <f>'[78]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F54" s="20"/>
       <c r="G54" s="20"/>
       <c r="H54" s="20">
-        <f>'[73]MD10000.20-OCT'!$K$1</f>
+        <f>'[78]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I54" s="20">
-        <f>'[73]MD10000.20-OCT'!$K$2</f>
+        <f>'[78]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J54" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K54" s="22">
-        <f>'[73]MD10000.20-OCT'!$B$3</f>
+        <f>'[78]MD10000.20-OCT'!$B$3</f>
         <v>45511</v>
       </c>
       <c r="L54" s="19">
-        <f>'[73]MD10000.20-OCT'!$O$2</f>
+        <f>'[78]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M54" s="19">
-        <f>'[73]MD10000.20-OCT'!$O$1</f>
+        <f>'[78]MD10000.20-OCT'!$O$1</f>
         <v>5950</v>
       </c>
     </row>
@@ -8485,15 +8553,15 @@
         <v>80</v>
       </c>
       <c r="E55" s="19">
-        <f>'[74]MD20000.18-DEC'!$C$1</f>
+        <f>'[79]MD20000.18-DEC'!$C$1</f>
         <v>30000</v>
       </c>
       <c r="F55" s="20">
-        <f>'[74]MD20000.18-DEC'!$K$1</f>
+        <f>'[79]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G55" s="20">
-        <f>'[74]MD20000.18-DEC'!$K$2</f>
+        <f>'[79]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H55" s="20"/>
@@ -8502,15 +8570,15 @@
         <v>51</v>
       </c>
       <c r="K55" s="22">
-        <f>'[74]MD20000.18-DEC'!$B$3</f>
+        <f>'[79]MD20000.18-DEC'!$B$3</f>
         <v>45508</v>
       </c>
       <c r="L55" s="19">
-        <f>'[74]MD20000.18-DEC'!$O$2</f>
+        <f>'[79]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M55" s="19">
-        <f>'[74]MD20000.18-DEC'!$O$1</f>
+        <f>'[79]MD20000.18-DEC'!$O$1</f>
         <v>36000</v>
       </c>
     </row>
@@ -8525,15 +8593,15 @@
         <v>82</v>
       </c>
       <c r="E56" s="19">
-        <f>'[75]MD20000.18-DEC'!$C$1</f>
+        <f>'[80]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F56" s="20">
-        <f>'[75]MD20000.18-DEC'!$K$1</f>
+        <f>'[80]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G56" s="20">
-        <f>'[75]MD20000.18-DEC'!$K$2</f>
+        <f>'[80]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H56" s="20"/>
@@ -8542,15 +8610,15 @@
         <v>12</v>
       </c>
       <c r="K56" s="22">
-        <f>'[75]MD20000.18-DEC'!$B$3</f>
+        <f>'[80]MD20000.18-DEC'!$B$3</f>
         <v>45514</v>
       </c>
       <c r="L56" s="19">
-        <f>'[75]MD20000.18-DEC'!$O$2</f>
+        <f>'[80]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M56" s="19">
-        <f>'[75]MD20000.18-DEC'!$O$1</f>
+        <f>'[80]MD20000.18-DEC'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -8565,32 +8633,32 @@
         <v>52</v>
       </c>
       <c r="E57" s="19">
-        <f>'[76]MD20000.15-DEc'!$C$1</f>
+        <f>'[81]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F57" s="20"/>
       <c r="G57" s="20"/>
       <c r="H57" s="20">
-        <f>'[76]MD20000.15-DEc'!$K$1</f>
+        <f>'[81]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I57" s="20">
-        <f>'[76]MD20000.15-DEc'!$K$2</f>
+        <f>'[81]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J57" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K57" s="22">
-        <f>'[76]MD20000.15-DEc'!$B$3</f>
+        <f>'[81]MD20000.15-DEc'!$B$3</f>
         <v>45527</v>
       </c>
       <c r="L57" s="19">
-        <f>'[76]MD20000.15-DEc'!$O$2</f>
+        <f>'[81]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M57" s="19">
-        <f>'[76]MD20000.15-DEc'!$O$1</f>
+        <f>'[81]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -8605,32 +8673,32 @@
         <v>76</v>
       </c>
       <c r="E58" s="19">
-        <f>'[77]MD20000.15-DEc'!$C$1</f>
+        <f>'[82]MD20000.15-DEc'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F58" s="20"/>
       <c r="G58" s="20"/>
       <c r="H58" s="20">
-        <f>'[77]MD20000.15-DEc'!$K$1</f>
+        <f>'[82]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I58" s="20">
-        <f>'[77]MD20000.15-DEc'!$K$2</f>
+        <f>'[82]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J58" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K58" s="22">
-        <f>'[77]MD20000.15-DEc'!$B$3</f>
+        <f>'[82]MD20000.15-DEc'!$B$3</f>
         <v>45531</v>
       </c>
       <c r="L58" s="19">
-        <f>'[77]MD20000.15-DEc'!$O$2</f>
+        <f>'[82]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M58" s="19">
-        <f>'[77]MD20000.15-DEc'!$O$1</f>
+        <f>'[82]MD20000.15-DEc'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -8645,32 +8713,32 @@
         <v>85</v>
       </c>
       <c r="E59" s="19">
-        <f>'[78]MD10000.20-OCT'!$C$1</f>
+        <f>'[83]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F59" s="20"/>
       <c r="G59" s="20"/>
       <c r="H59" s="20">
-        <f>'[78]MD10000.20-OCT'!$K$1</f>
+        <f>'[83]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I59" s="20">
-        <f>'[78]MD10000.20-OCT'!$K$2</f>
+        <f>'[83]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J59" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K59" s="22">
-        <f>'[78]MD10000.20-OCT'!$B$3</f>
+        <f>'[83]MD10000.20-OCT'!$B$3</f>
         <v>45532</v>
       </c>
       <c r="L59" s="19">
-        <f>'[78]MD10000.20-OCT'!$O$2</f>
+        <f>'[83]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M59" s="19">
-        <f>'[78]MD10000.20-OCT'!$O$1</f>
+        <f>'[83]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -8685,32 +8753,32 @@
         <v>76</v>
       </c>
       <c r="E60" s="19">
-        <f>'[79]MD20000.15-DEc'!$C$1</f>
+        <f>'[84]MD20000.15-DEc'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F60" s="20"/>
       <c r="G60" s="20"/>
       <c r="H60" s="20">
-        <f>'[79]MD20000.15-DEc'!$K$1</f>
+        <f>'[84]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I60" s="20">
-        <f>'[79]MD20000.15-DEc'!$K$2</f>
+        <f>'[84]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J60" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K60" s="22">
-        <f>'[79]MD20000.15-DEc'!$B$3</f>
+        <f>'[84]MD20000.15-DEc'!$B$3</f>
         <v>45534</v>
       </c>
       <c r="L60" s="19">
-        <f>'[79]MD20000.15-DEc'!$O$2</f>
+        <f>'[84]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M60" s="19">
-        <f>'[79]MD20000.15-DEc'!$O$1</f>
+        <f>'[84]MD20000.15-DEc'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -8725,32 +8793,32 @@
         <v>87</v>
       </c>
       <c r="E61" s="19">
-        <f>'[80]MD10000.20-OCT'!$C$1</f>
+        <f>'[85]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F61" s="20"/>
       <c r="G61" s="20"/>
       <c r="H61" s="20">
-        <f>'[80]MD10000.20-OCT'!$K$1</f>
+        <f>'[85]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I61" s="20">
-        <f>'[80]MD10000.20-OCT'!$K$2</f>
+        <f>'[85]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J61" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K61" s="22">
-        <f>'[80]MD10000.20-OCT'!$B$3</f>
+        <f>'[85]MD10000.20-OCT'!$B$3</f>
         <v>45536</v>
       </c>
       <c r="L61" s="19">
-        <f>'[80]MD10000.20-OCT'!$O$2</f>
+        <f>'[85]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M61" s="19">
-        <f>'[80]MD10000.20-OCT'!$O$1</f>
+        <f>'[85]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -8765,15 +8833,15 @@
         <v>33</v>
       </c>
       <c r="E62" s="19">
-        <f>'[81]MD20000.22-DEC'!$C$1</f>
+        <f>'[86]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F62" s="20">
-        <f>'[81]MD20000.22-DEC'!$K$1</f>
+        <f>'[86]MD20000.22-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G62" s="20">
-        <f>'[81]MD20000.22-DEC'!$K$2</f>
+        <f>'[86]MD20000.22-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H62" s="20"/>
@@ -8782,15 +8850,15 @@
         <v>51</v>
       </c>
       <c r="K62" s="22">
-        <f>'[81]MD20000.22-DEC'!$B$3</f>
+        <f>'[86]MD20000.22-DEC'!$B$3</f>
         <v>45535</v>
       </c>
       <c r="L62" s="19">
-        <f>'[81]MD20000.22-DEC'!$O$2</f>
+        <f>'[86]MD20000.22-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M62" s="19">
-        <f>'[81]MD20000.22-DEC'!$O$1</f>
+        <f>'[86]MD20000.22-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -8805,32 +8873,32 @@
         <v>48</v>
       </c>
       <c r="E63" s="19">
-        <f>'[82]MD10000.20-OCT'!$C$1</f>
+        <f>'[87]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F63" s="20"/>
       <c r="G63" s="20"/>
       <c r="H63" s="20">
-        <f>'[82]MD10000.20-OCT'!$K$1</f>
+        <f>'[87]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I63" s="20">
-        <f>'[82]MD10000.20-OCT'!$K$2</f>
+        <f>'[87]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J63" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K63" s="22">
-        <f>'[82]MD10000.20-OCT'!$B$3</f>
+        <f>'[87]MD10000.20-OCT'!$B$3</f>
         <v>45549</v>
       </c>
       <c r="L63" s="19">
-        <f>'[82]MD10000.20-OCT'!$O$2</f>
+        <f>'[87]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M63" s="19">
-        <f>'[82]MD10000.20-OCT'!$O$1</f>
+        <f>'[87]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -8845,15 +8913,15 @@
         <v>90</v>
       </c>
       <c r="E64" s="19">
-        <f>'[83]MD20000.22-DEC'!$C$1</f>
+        <f>'[88]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F64" s="20">
-        <f>'[83]MD20000.22-DEC'!$K$1</f>
+        <f>'[88]MD20000.22-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G64" s="20">
-        <f>'[83]MD20000.22-DEC'!$K$2</f>
+        <f>'[88]MD20000.22-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H64" s="20"/>
@@ -8862,15 +8930,15 @@
         <v>12</v>
       </c>
       <c r="K64" s="22">
-        <f>'[83]MD20000.22-DEC'!$B$13</f>
+        <f>'[88]MD20000.22-DEC'!$B$13</f>
         <v>45562</v>
       </c>
       <c r="L64" s="19">
-        <f>'[83]MD20000.22-DEC'!$O$2</f>
+        <f>'[88]MD20000.22-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M64" s="19">
-        <f>'[83]MD20000.22-DEC'!$O$1</f>
+        <f>'[88]MD20000.22-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -8885,15 +8953,15 @@
         <v>68</v>
       </c>
       <c r="E65" s="19">
-        <f>'[84]MD10000.1-OCT'!$C$1</f>
+        <f>'[89]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F65" s="20">
-        <f>'[84]MD10000.1-OCT'!$K$1</f>
+        <f>'[89]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G65" s="20">
-        <f>'[84]MD10000.1-OCT'!$K$2</f>
+        <f>'[89]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H65" s="20"/>
@@ -8902,15 +8970,15 @@
         <v>12</v>
       </c>
       <c r="K65" s="22">
-        <f>'[84]MD10000.1-OCT'!$B$3</f>
+        <f>'[89]MD10000.1-OCT'!$B$3</f>
         <v>45557</v>
       </c>
       <c r="L65" s="19">
-        <f>'[84]MD10000.1-OCT'!$O$2</f>
+        <f>'[89]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M65" s="19">
-        <f>'[84]MD10000.1-OCT'!$O$1</f>
+        <f>'[89]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -8973,11 +9041,11 @@
       </c>
       <c r="F67" s="8">
         <f>'[3]MD10000.1-OCT'!$K$1</f>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G67" s="8">
         <f>'[3]MD10000.1-OCT'!$K$2</f>
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
@@ -8990,11 +9058,11 @@
       </c>
       <c r="L67" s="7">
         <f>'[3]MD10000.1-OCT'!$O$2</f>
-        <v>1300</v>
+        <v>900</v>
       </c>
       <c r="M67" s="7">
         <f>'[3]MD10000.1-OCT'!$O$1</f>
-        <v>10700</v>
+        <v>11100</v>
       </c>
       <c r="N67" s="1">
         <v>700</v>
@@ -9011,15 +9079,15 @@
         <v>33</v>
       </c>
       <c r="E68" s="19">
-        <f>'[85]MD20000.18-DEC'!$C$1</f>
+        <f>'[90]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F68" s="20">
-        <f>'[85]MD20000.18-DEC'!$K$1</f>
+        <f>'[90]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G68" s="20">
-        <f>'[85]MD20000.18-DEC'!$K$2</f>
+        <f>'[90]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H68" s="20"/>
@@ -9028,15 +9096,15 @@
         <v>12</v>
       </c>
       <c r="K68" s="22">
-        <f>'[85]MD20000.18-DEC'!$B$3</f>
+        <f>'[90]MD20000.18-DEC'!$B$3</f>
         <v>45562</v>
       </c>
       <c r="L68" s="19">
-        <f>'[85]MD20000.18-DEC'!$O$2</f>
+        <f>'[90]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M68" s="19">
-        <f>'[85]MD20000.18-DEC'!$O$1</f>
+        <f>'[90]MD20000.18-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -9137,15 +9205,15 @@
         <v>96</v>
       </c>
       <c r="E71" s="26">
-        <f>'[86]MD20000.18-DEC'!$C$1</f>
+        <f>'[91]MD20000.18-DEC'!$C$1</f>
         <v>50000</v>
       </c>
       <c r="F71" s="24">
-        <f>'[86]MD20000.18-DEC'!$K$1</f>
+        <f>'[91]MD20000.18-DEC'!$K$1</f>
         <v>66</v>
       </c>
       <c r="G71" s="24">
-        <f>'[86]MD20000.18-DEC'!$K$2</f>
+        <f>'[91]MD20000.18-DEC'!$K$2</f>
         <v>54</v>
       </c>
       <c r="H71" s="24"/>
@@ -9154,15 +9222,15 @@
         <v>12</v>
       </c>
       <c r="K71" s="25">
-        <f>'[86]MD20000.18-DEC'!$B$3</f>
+        <f>'[91]MD20000.18-DEC'!$B$3</f>
         <v>45579</v>
       </c>
       <c r="L71" s="26">
-        <f>'[86]MD20000.18-DEC'!$O$2</f>
+        <f>'[91]MD20000.18-DEC'!$O$2</f>
         <v>33000</v>
       </c>
       <c r="M71" s="26">
-        <f>'[86]MD20000.18-DEC'!$O$1</f>
+        <f>'[91]MD20000.18-DEC'!$O$1</f>
         <v>27000</v>
       </c>
     </row>
@@ -9184,11 +9252,11 @@
       <c r="G72" s="8"/>
       <c r="H72" s="8">
         <f>'[6]MD20000.18-DEC'!$K$1</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I72" s="8">
         <f>'[6]MD20000.18-DEC'!$K$2</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J72" s="9" t="s">
         <v>12</v>
@@ -9199,11 +9267,11 @@
       </c>
       <c r="L72" s="7">
         <f>'[6]MD20000.18-DEC'!$O$2</f>
-        <v>100000</v>
+        <v>96000</v>
       </c>
       <c r="M72" s="7">
         <f>'[6]MD20000.18-DEC'!$O$1</f>
-        <v>60000</v>
+        <v>64000</v>
       </c>
       <c r="N72" s="1">
         <v>4000</v>
@@ -9220,15 +9288,15 @@
         <v>96</v>
       </c>
       <c r="E73" s="19">
-        <f>'[87]MD20000.18-DEC'!$C$1</f>
+        <f>'[92]MD20000.18-DEC'!$C$1</f>
         <v>50000</v>
       </c>
       <c r="F73" s="20">
-        <f>'[87]MD20000.18-DEC'!$K$1</f>
+        <f>'[92]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G73" s="20">
-        <f>'[87]MD20000.18-DEC'!$K$2</f>
+        <f>'[92]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H73" s="20"/>
@@ -9237,15 +9305,15 @@
         <v>12</v>
       </c>
       <c r="K73" s="22">
-        <f>'[87]MD20000.18-DEC'!$B$3</f>
+        <f>'[92]MD20000.18-DEC'!$B$3</f>
         <v>45584</v>
       </c>
       <c r="L73" s="19">
-        <f>'[87]MD20000.18-DEC'!$O$2</f>
+        <f>'[92]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M73" s="19">
-        <f>'[87]MD20000.18-DEC'!$O$1</f>
+        <f>'[92]MD20000.18-DEC'!$O$1</f>
         <v>60000</v>
       </c>
     </row>
@@ -9260,15 +9328,15 @@
         <v>90</v>
       </c>
       <c r="E74" s="19">
-        <f>'[88]MD20000.18-DEC'!$C$1</f>
+        <f>'[93]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F74" s="20">
-        <f>'[88]MD20000.18-DEC'!$K$1</f>
+        <f>'[93]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G74" s="20">
-        <f>'[88]MD20000.18-DEC'!$K$2</f>
+        <f>'[93]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H74" s="20"/>
@@ -9277,15 +9345,15 @@
         <v>12</v>
       </c>
       <c r="K74" s="22">
-        <f>'[88]MD20000.18-DEC'!$B$3</f>
+        <f>'[93]MD20000.18-DEC'!$B$3</f>
         <v>45584</v>
       </c>
       <c r="L74" s="19">
-        <f>'[88]MD20000.18-DEC'!$O$2</f>
+        <f>'[93]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M74" s="19">
-        <f>'[88]MD20000.18-DEC'!$O$1</f>
+        <f>'[93]MD20000.18-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -9343,15 +9411,15 @@
         <v>90</v>
       </c>
       <c r="E76" s="19">
-        <f>'[89]MD20000.18-DEC'!$C$1</f>
+        <f>'[94]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F76" s="20">
-        <f>'[89]MD20000.18-DEC'!$K$1</f>
+        <f>'[94]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G76" s="20">
-        <f>'[89]MD20000.18-DEC'!$K$2</f>
+        <f>'[94]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H76" s="20"/>
@@ -9360,15 +9428,15 @@
         <v>12</v>
       </c>
       <c r="K76" s="22">
-        <f>'[89]MD20000.18-DEC'!$B$3</f>
+        <f>'[94]MD20000.18-DEC'!$B$3</f>
         <v>45584</v>
       </c>
       <c r="L76" s="19">
-        <f>'[89]MD20000.18-DEC'!$O$2</f>
+        <f>'[94]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M76" s="19">
-        <f>'[89]MD20000.18-DEC'!$O$1</f>
+        <f>'[94]MD20000.18-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -9383,16 +9451,16 @@
         <v>90</v>
       </c>
       <c r="E77" s="7">
-        <f>'[8]MD20000.18-DEC'!$C$1</f>
+        <f>'[9]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F77" s="8">
-        <f>'[8]MD20000.18-DEC'!$K$1</f>
-        <v>10</v>
+        <f>'[9]MD20000.18-DEC'!$K$1</f>
+        <v>5</v>
       </c>
       <c r="G77" s="8">
-        <f>'[8]MD20000.18-DEC'!$K$2</f>
-        <v>110</v>
+        <f>'[9]MD20000.18-DEC'!$K$2</f>
+        <v>115</v>
       </c>
       <c r="H77" s="8"/>
       <c r="I77" s="8"/>
@@ -9400,16 +9468,16 @@
         <v>12</v>
       </c>
       <c r="K77" s="10">
-        <f>'[8]MD20000.18-DEC'!$B$7</f>
+        <f>'[9]MD20000.18-DEC'!$B$7</f>
         <v>45587</v>
       </c>
       <c r="L77" s="7">
-        <f>'[8]MD20000.18-DEC'!$O$2</f>
-        <v>2000</v>
+        <f>'[9]MD20000.18-DEC'!$O$2</f>
+        <v>1000</v>
       </c>
       <c r="M77" s="7">
-        <f>'[8]MD20000.18-DEC'!$O$1</f>
-        <v>22000</v>
+        <f>'[9]MD20000.18-DEC'!$O$1</f>
+        <v>23000</v>
       </c>
       <c r="N77" s="1">
         <v>1400</v>
@@ -9426,16 +9494,16 @@
         <v>68</v>
       </c>
       <c r="E78" s="7">
-        <f>'[9]MD20000.18-DEC'!$C$1</f>
+        <f>'[10]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F78" s="8">
-        <f>'[9]MD20000.18-DEC'!$K$1</f>
-        <v>69</v>
+        <f>'[10]MD20000.18-DEC'!$K$1</f>
+        <v>60</v>
       </c>
       <c r="G78" s="8">
-        <f>'[9]MD20000.18-DEC'!$K$2</f>
-        <v>51</v>
+        <f>'[10]MD20000.18-DEC'!$K$2</f>
+        <v>60</v>
       </c>
       <c r="H78" s="8"/>
       <c r="I78" s="8"/>
@@ -9443,16 +9511,16 @@
         <v>12</v>
       </c>
       <c r="K78" s="10">
-        <f>'[9]MD20000.18-DEC'!$B$3</f>
+        <f>'[10]MD20000.18-DEC'!$B$3</f>
         <v>45584</v>
       </c>
       <c r="L78" s="7">
-        <f>'[9]MD20000.18-DEC'!$O$2</f>
-        <v>6900</v>
+        <f>'[10]MD20000.18-DEC'!$O$2</f>
+        <v>6000</v>
       </c>
       <c r="M78" s="7">
-        <f>'[9]MD20000.18-DEC'!$O$1</f>
-        <v>5100</v>
+        <f>'[10]MD20000.18-DEC'!$O$1</f>
+        <v>6000</v>
       </c>
       <c r="N78" s="1">
         <v>700</v>
@@ -9469,15 +9537,15 @@
         <v>68</v>
       </c>
       <c r="E79" s="7">
-        <f>'[10]MD20000.18-DEC'!$C$1</f>
+        <f>'[11]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F79" s="8">
-        <f>'[10]MD20000.18-DEC'!$K$1</f>
+        <f>'[11]MD20000.18-DEC'!$K$1</f>
         <v>68</v>
       </c>
       <c r="G79" s="8">
-        <f>'[10]MD20000.18-DEC'!$K$2</f>
+        <f>'[11]MD20000.18-DEC'!$K$2</f>
         <v>52</v>
       </c>
       <c r="H79" s="8"/>
@@ -9486,15 +9554,15 @@
         <v>12</v>
       </c>
       <c r="K79" s="10">
-        <f>'[10]MD20000.18-DEC'!$B$3</f>
+        <f>'[11]MD20000.18-DEC'!$B$3</f>
         <v>45584</v>
       </c>
       <c r="L79" s="7">
-        <f>'[10]MD20000.18-DEC'!$O$2</f>
+        <f>'[11]MD20000.18-DEC'!$O$2</f>
         <v>6800</v>
       </c>
       <c r="M79" s="7">
-        <f>'[10]MD20000.18-DEC'!$O$1</f>
+        <f>'[11]MD20000.18-DEC'!$O$1</f>
         <v>5200</v>
       </c>
       <c r="N79" s="1">
@@ -9512,15 +9580,15 @@
         <v>68</v>
       </c>
       <c r="E80" s="19">
-        <f>'[90]MD20000.18-DEC'!$C$1</f>
+        <f>'[95]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F80" s="20">
-        <f>'[90]MD20000.18-DEC'!$K$1</f>
+        <f>'[95]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G80" s="20">
-        <f>'[90]MD20000.18-DEC'!$K$2</f>
+        <f>'[95]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H80" s="20"/>
@@ -9529,15 +9597,15 @@
         <v>12</v>
       </c>
       <c r="K80" s="22">
-        <f>'[90]MD20000.18-DEC'!$B$3</f>
+        <f>'[95]MD20000.18-DEC'!$B$3</f>
         <v>45587</v>
       </c>
       <c r="L80" s="19">
-        <f>'[90]MD20000.18-DEC'!$O$2</f>
+        <f>'[95]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M80" s="19">
-        <f>'[90]MD20000.18-DEC'!$O$1</f>
+        <f>'[95]MD20000.18-DEC'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -9552,33 +9620,33 @@
         <v>52</v>
       </c>
       <c r="E81" s="7">
-        <f>'[11]MD20000.15-DEc'!$C$1</f>
+        <f>'[12]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F81" s="8"/>
       <c r="G81" s="8"/>
       <c r="H81" s="8">
-        <f>'[11]MD20000.15-DEc'!$K$1</f>
-        <v>2</v>
+        <f>'[12]MD20000.15-DEc'!$K$1</f>
+        <v>1</v>
       </c>
       <c r="I81" s="8">
-        <f>'[11]MD20000.15-DEc'!$K$2</f>
-        <v>15</v>
+        <f>'[12]MD20000.15-DEc'!$K$2</f>
+        <v>16</v>
       </c>
       <c r="J81" s="9" t="s">
         <v>12</v>
       </c>
       <c r="K81" s="10">
-        <f>'[11]MD20000.15-DEc'!$B$3</f>
+        <f>'[12]MD20000.15-DEc'!$B$3</f>
         <v>45595</v>
       </c>
       <c r="L81" s="7">
-        <f>'[11]MD20000.15-DEc'!$O$2</f>
-        <v>2800</v>
+        <f>'[12]MD20000.15-DEc'!$O$2</f>
+        <v>1400</v>
       </c>
       <c r="M81" s="7">
-        <f>'[11]MD20000.15-DEc'!$O$1</f>
-        <v>21200</v>
+        <f>'[12]MD20000.15-DEc'!$O$1</f>
+        <v>22600</v>
       </c>
       <c r="N81" s="1">
         <v>1400</v>
@@ -9595,33 +9663,33 @@
         <v>106</v>
       </c>
       <c r="E82" s="7">
-        <f>'[12]MD10000.10-JAN'!$C$1</f>
+        <f>'[13]MD10000.10-JAN'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F82" s="8"/>
       <c r="G82" s="8"/>
       <c r="H82" s="8">
-        <f>'[12]MD10000.10-JAN'!$K$1</f>
-        <v>4</v>
+        <f>'[13]MD10000.10-JAN'!$K$1</f>
+        <v>2</v>
       </c>
       <c r="I82" s="8">
-        <f>'[12]MD10000.10-JAN'!$K$2</f>
-        <v>13</v>
+        <f>'[13]MD10000.10-JAN'!$K$2</f>
+        <v>15</v>
       </c>
       <c r="J82" s="9" t="s">
         <v>12</v>
       </c>
       <c r="K82" s="10">
-        <f>'[12]MD10000.10-JAN'!$B$3</f>
+        <f>'[13]MD10000.10-JAN'!$B$3</f>
         <v>45602</v>
       </c>
       <c r="L82" s="7">
-        <f>'[12]MD10000.10-JAN'!$O$2</f>
-        <v>5600</v>
+        <f>'[13]MD10000.10-JAN'!$O$2</f>
+        <v>2800</v>
       </c>
       <c r="M82" s="7">
-        <f>'[12]MD10000.10-JAN'!$O$1</f>
-        <v>18400</v>
+        <f>'[13]MD10000.10-JAN'!$O$1</f>
+        <v>21200</v>
       </c>
       <c r="N82" s="1">
         <v>1400</v>
@@ -9638,15 +9706,15 @@
         <v>90</v>
       </c>
       <c r="E83" s="19">
-        <f>'[91]MD20000.22-DEC'!$C$1</f>
+        <f>'[96]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F83" s="20">
-        <f>'[91]MD20000.22-DEC'!$K$1</f>
+        <f>'[96]MD20000.22-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G83" s="20">
-        <f>'[91]MD20000.22-DEC'!$K$2</f>
+        <f>'[96]MD20000.22-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H83" s="20"/>
@@ -9655,15 +9723,15 @@
         <v>12</v>
       </c>
       <c r="K83" s="22">
-        <f>'[91]MD20000.22-DEC'!$B$3</f>
+        <f>'[96]MD20000.22-DEC'!$B$3</f>
         <v>45597</v>
       </c>
       <c r="L83" s="19">
-        <f>'[91]MD20000.22-DEC'!$O$2</f>
+        <f>'[96]MD20000.22-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M83" s="19">
-        <f>'[91]MD20000.22-DEC'!$O$1</f>
+        <f>'[96]MD20000.22-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -9678,15 +9746,15 @@
         <v>80</v>
       </c>
       <c r="E84" s="19">
-        <f>'[92]MD20000.18-DEC'!$C$1</f>
+        <f>'[97]MD20000.18-DEC'!$C$1</f>
         <v>30000</v>
       </c>
       <c r="F84" s="20">
-        <f>'[92]MD20000.18-DEC'!$K$1</f>
+        <f>'[97]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G84" s="20">
-        <f>'[92]MD20000.18-DEC'!$K$2</f>
+        <f>'[97]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H84" s="20"/>
@@ -9695,15 +9763,15 @@
         <v>12</v>
       </c>
       <c r="K84" s="22">
-        <f>'[92]MD20000.18-DEC'!$B$3</f>
+        <f>'[97]MD20000.18-DEC'!$B$3</f>
         <v>45602</v>
       </c>
       <c r="L84" s="19">
-        <f>'[92]MD20000.18-DEC'!$O$2</f>
+        <f>'[97]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M84" s="19">
-        <f>'[92]MD20000.18-DEC'!$O$1</f>
+        <f>'[97]MD20000.18-DEC'!$O$1</f>
         <v>36000</v>
       </c>
     </row>
@@ -9718,15 +9786,15 @@
         <v>109</v>
       </c>
       <c r="E85" s="26">
-        <f>'[93]MD20000.18-DEC'!$C$1</f>
+        <f>'[98]MD20000.18-DEC'!$C$1</f>
         <v>50000</v>
       </c>
       <c r="F85" s="24">
-        <f>'[93]MD20000.18-DEC'!$K$1</f>
+        <f>'[98]MD20000.18-DEC'!$K$1</f>
         <v>100</v>
       </c>
       <c r="G85" s="24">
-        <f>'[93]MD20000.18-DEC'!$K$2</f>
+        <f>'[98]MD20000.18-DEC'!$K$2</f>
         <v>20</v>
       </c>
       <c r="H85" s="24"/>
@@ -9735,15 +9803,15 @@
         <v>12</v>
       </c>
       <c r="K85" s="25">
-        <f>'[93]MD20000.18-DEC'!$B$3</f>
+        <f>'[98]MD20000.18-DEC'!$B$3</f>
         <v>45612</v>
       </c>
       <c r="L85" s="26">
-        <f>'[93]MD20000.18-DEC'!$O$2</f>
+        <f>'[98]MD20000.18-DEC'!$O$2</f>
         <v>50000</v>
       </c>
       <c r="M85" s="26">
-        <f>'[93]MD20000.18-DEC'!$O$1</f>
+        <f>'[98]MD20000.18-DEC'!$O$1</f>
         <v>10000</v>
       </c>
     </row>
@@ -9758,16 +9826,16 @@
         <v>68</v>
       </c>
       <c r="E86" s="7">
-        <f>'[13]MD20000.18-DEC'!$C$1</f>
+        <f>'[14]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F86" s="8">
-        <f>'[13]MD20000.18-DEC'!$K$1</f>
-        <v>41</v>
+        <f>'[14]MD20000.18-DEC'!$K$1</f>
+        <v>34</v>
       </c>
       <c r="G86" s="8">
-        <f>'[13]MD20000.18-DEC'!$K$2</f>
-        <v>79</v>
+        <f>'[14]MD20000.18-DEC'!$K$2</f>
+        <v>86</v>
       </c>
       <c r="H86" s="8"/>
       <c r="I86" s="8"/>
@@ -9775,16 +9843,16 @@
         <v>12</v>
       </c>
       <c r="K86" s="10">
-        <f>'[13]MD20000.18-DEC'!$B$3</f>
+        <f>'[14]MD20000.18-DEC'!$B$3</f>
         <v>45612</v>
       </c>
       <c r="L86" s="7">
-        <f>'[13]MD20000.18-DEC'!$O$2</f>
-        <v>4100</v>
+        <f>'[14]MD20000.18-DEC'!$O$2</f>
+        <v>3400</v>
       </c>
       <c r="M86" s="7">
-        <f>'[13]MD20000.18-DEC'!$O$1</f>
-        <v>7900</v>
+        <f>'[14]MD20000.18-DEC'!$O$1</f>
+        <v>8600</v>
       </c>
       <c r="N86" s="1">
         <v>700</v>
@@ -9801,16 +9869,16 @@
         <v>111</v>
       </c>
       <c r="E87" s="7">
-        <f>'[14]MD50000.15-DEC'!$C$1</f>
+        <f>'[15]MD50000.15-DEC'!$C$1</f>
         <v>100000</v>
       </c>
       <c r="F87" s="8">
-        <f>'[14]MD50000.15-DEC'!$K$1</f>
-        <v>219</v>
+        <f>'[15]MD50000.15-DEC'!$K$1</f>
+        <v>216</v>
       </c>
       <c r="G87" s="8">
-        <f>'[14]MD50000.15-DEC'!$K$2</f>
-        <v>48</v>
+        <f>'[15]MD50000.15-DEC'!$K$2</f>
+        <v>51</v>
       </c>
       <c r="H87" s="8"/>
       <c r="I87" s="8"/>
@@ -9818,16 +9886,16 @@
         <v>12</v>
       </c>
       <c r="K87" s="10">
-        <f>'[14]MD50000.15-DEC'!$B$3</f>
+        <f>'[15]MD50000.15-DEC'!$B$3</f>
         <v>45619</v>
       </c>
       <c r="L87" s="7">
-        <f>'[14]MD50000.15-DEC'!$O$2</f>
-        <v>131400</v>
+        <f>'[15]MD50000.15-DEC'!$O$2</f>
+        <v>129600</v>
       </c>
       <c r="M87" s="7">
-        <f>'[14]MD50000.15-DEC'!$O$1</f>
-        <v>28800</v>
+        <f>'[15]MD50000.15-DEC'!$O$1</f>
+        <v>30600</v>
       </c>
       <c r="N87" s="1">
         <v>4200</v>
@@ -9844,16 +9912,16 @@
         <v>96</v>
       </c>
       <c r="E88" s="7">
-        <f>'[15]MD20000.18-DEC'!$C$1</f>
+        <f>'[16]MD20000.18-DEC'!$C$1</f>
         <v>50000</v>
       </c>
       <c r="F88" s="8">
-        <f>'[15]MD20000.18-DEC'!$K$1</f>
-        <v>54</v>
+        <f>'[16]MD20000.18-DEC'!$K$1</f>
+        <v>46</v>
       </c>
       <c r="G88" s="8">
-        <f>'[15]MD20000.18-DEC'!$K$2</f>
-        <v>66</v>
+        <f>'[16]MD20000.18-DEC'!$K$2</f>
+        <v>74</v>
       </c>
       <c r="H88" s="8"/>
       <c r="I88" s="8"/>
@@ -9861,16 +9929,16 @@
         <v>12</v>
       </c>
       <c r="K88" s="10">
-        <f>'[15]MD20000.18-DEC'!$B$3</f>
+        <f>'[16]MD20000.18-DEC'!$B$3</f>
         <v>45628</v>
       </c>
       <c r="L88" s="7">
-        <f>'[15]MD20000.18-DEC'!$O$2</f>
-        <v>27000</v>
+        <f>'[16]MD20000.18-DEC'!$O$2</f>
+        <v>23000</v>
       </c>
       <c r="M88" s="7">
-        <f>'[15]MD20000.18-DEC'!$O$1</f>
-        <v>33000</v>
+        <f>'[16]MD20000.18-DEC'!$O$1</f>
+        <v>37000</v>
       </c>
       <c r="N88" s="1">
         <v>3500</v>
@@ -9887,15 +9955,15 @@
         <v>80</v>
       </c>
       <c r="E89" s="19">
-        <f>'[94]MD20000.18-DEC'!$C$1</f>
+        <f>'[99]MD20000.18-DEC'!$C$1</f>
         <v>30000</v>
       </c>
       <c r="F89" s="20">
-        <f>'[94]MD20000.18-DEC'!$K$1</f>
+        <f>'[99]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G89" s="20">
-        <f>'[94]MD20000.18-DEC'!$K$2</f>
+        <f>'[99]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H89" s="20"/>
@@ -9904,15 +9972,15 @@
         <v>12</v>
       </c>
       <c r="K89" s="22">
-        <f>'[94]MD20000.18-DEC'!$B$3</f>
+        <f>'[99]MD20000.18-DEC'!$B$3</f>
         <v>45647</v>
       </c>
       <c r="L89" s="19">
-        <f>'[94]MD20000.18-DEC'!$O$2</f>
+        <f>'[99]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M89" s="19">
-        <f>'[94]MD20000.18-DEC'!$O$1</f>
+        <f>'[99]MD20000.18-DEC'!$O$1</f>
         <v>36000</v>
       </c>
     </row>
@@ -9927,16 +9995,16 @@
         <v>68</v>
       </c>
       <c r="E90" s="7">
-        <f>'[16]MD20000.18-DEC'!$C$1</f>
+        <f>'[17]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F90" s="8">
-        <f>'[16]MD20000.18-DEC'!$K$1</f>
+        <f>'[17]MD20000.18-DEC'!$K$1</f>
+        <v>57</v>
+      </c>
+      <c r="G90" s="8">
+        <f>'[17]MD20000.18-DEC'!$K$2</f>
         <v>63</v>
-      </c>
-      <c r="G90" s="8">
-        <f>'[16]MD20000.18-DEC'!$K$2</f>
-        <v>57</v>
       </c>
       <c r="H90" s="8"/>
       <c r="I90" s="8"/>
@@ -9944,16 +10012,16 @@
         <v>12</v>
       </c>
       <c r="K90" s="10">
-        <f>'[16]MD20000.18-DEC'!$B$3</f>
+        <f>'[17]MD20000.18-DEC'!$B$3</f>
         <v>45635</v>
       </c>
       <c r="L90" s="7">
-        <f>'[16]MD20000.18-DEC'!$O$2</f>
+        <f>'[17]MD20000.18-DEC'!$O$2</f>
+        <v>5700</v>
+      </c>
+      <c r="M90" s="7">
+        <f>'[17]MD20000.18-DEC'!$O$1</f>
         <v>6300</v>
-      </c>
-      <c r="M90" s="7">
-        <f>'[16]MD20000.18-DEC'!$O$1</f>
-        <v>5700</v>
       </c>
       <c r="N90" s="1">
         <v>700</v>
@@ -9970,16 +10038,16 @@
         <v>68</v>
       </c>
       <c r="E91" s="7">
-        <f>'[17]MD20000.18-DEC'!$C$1</f>
+        <f>'[18]MD20000.18-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F91" s="8">
-        <f>'[17]MD20000.18-DEC'!$K$1</f>
+        <f>'[18]MD20000.18-DEC'!$K$1</f>
+        <v>57</v>
+      </c>
+      <c r="G91" s="8">
+        <f>'[18]MD20000.18-DEC'!$K$2</f>
         <v>63</v>
-      </c>
-      <c r="G91" s="8">
-        <f>'[17]MD20000.18-DEC'!$K$2</f>
-        <v>57</v>
       </c>
       <c r="H91" s="8"/>
       <c r="I91" s="8"/>
@@ -9987,16 +10055,16 @@
         <v>12</v>
       </c>
       <c r="K91" s="10">
-        <f>'[17]MD20000.18-DEC'!$B$3</f>
+        <f>'[18]MD20000.18-DEC'!$B$3</f>
         <v>45635</v>
       </c>
       <c r="L91" s="7">
-        <f>'[17]MD20000.18-DEC'!$O$2</f>
+        <f>'[18]MD20000.18-DEC'!$O$2</f>
+        <v>5700</v>
+      </c>
+      <c r="M91" s="7">
+        <f>'[18]MD20000.18-DEC'!$O$1</f>
         <v>6300</v>
-      </c>
-      <c r="M91" s="7">
-        <f>'[17]MD20000.18-DEC'!$O$1</f>
-        <v>5700</v>
       </c>
       <c r="N91" s="1">
         <v>700</v>
@@ -10013,16 +10081,16 @@
         <v>117</v>
       </c>
       <c r="E92" s="7">
-        <f>'[18]MD50000.15-DEC'!$C$1</f>
+        <f>'[19]MD50000.15-DEC'!$C$1</f>
         <v>200000</v>
       </c>
       <c r="F92" s="8">
-        <f>'[18]MD50000.15-DEC'!$K$1</f>
-        <v>230</v>
+        <f>'[19]MD50000.15-DEC'!$K$1</f>
+        <v>226</v>
       </c>
       <c r="G92" s="8">
-        <f>'[18]MD50000.15-DEC'!$K$2</f>
-        <v>37</v>
+        <f>'[19]MD50000.15-DEC'!$K$2</f>
+        <v>41</v>
       </c>
       <c r="H92" s="8"/>
       <c r="I92" s="8"/>
@@ -10030,16 +10098,16 @@
         <v>12</v>
       </c>
       <c r="K92" s="10">
-        <f>'[18]MD50000.15-DEC'!$B$3</f>
+        <f>'[19]MD50000.15-DEC'!$B$3</f>
         <v>45648</v>
       </c>
       <c r="L92" s="7">
-        <f>'[18]MD50000.15-DEC'!$O$2</f>
-        <v>276000</v>
+        <f>'[19]MD50000.15-DEC'!$O$2</f>
+        <v>271200</v>
       </c>
       <c r="M92" s="7">
-        <f>'[18]MD50000.15-DEC'!$O$1</f>
-        <v>44400</v>
+        <f>'[19]MD50000.15-DEC'!$O$1</f>
+        <v>49200</v>
       </c>
       <c r="N92" s="1">
         <v>8400</v>
@@ -10056,32 +10124,32 @@
         <v>119</v>
       </c>
       <c r="E93" s="7">
-        <f>'[19]MD20000.15-DEc'!$C$1</f>
+        <f>'[20]MD20000.15-DEc'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F93" s="8"/>
       <c r="G93" s="8"/>
       <c r="H93" s="8">
-        <f>'[19]MD20000.15-DEc'!$K$1</f>
+        <f>'[20]MD20000.15-DEc'!$K$1</f>
         <v>9</v>
       </c>
       <c r="I93" s="8">
-        <f>'[19]MD20000.15-DEc'!$K$2</f>
+        <f>'[20]MD20000.15-DEc'!$K$2</f>
         <v>8</v>
       </c>
       <c r="J93" s="9" t="s">
         <v>12</v>
       </c>
       <c r="K93" s="10">
-        <f>'[19]MD20000.15-DEc'!$B$3</f>
+        <f>'[20]MD20000.15-DEc'!$B$3</f>
         <v>45649</v>
       </c>
       <c r="L93" s="7">
-        <f>'[19]MD20000.15-DEc'!$O$2</f>
+        <f>'[20]MD20000.15-DEc'!$O$2</f>
         <v>6400</v>
       </c>
       <c r="M93" s="7">
-        <f>'[19]MD20000.15-DEc'!$O$1</f>
+        <f>'[20]MD20000.15-DEc'!$O$1</f>
         <v>5600</v>
       </c>
       <c r="N93" s="1">
@@ -10099,16 +10167,16 @@
         <v>96</v>
       </c>
       <c r="E94" s="7">
-        <f>'[20]MD50000.15-DEC'!$C$1</f>
+        <f>'[21]MD50000.15-DEC'!$C$1</f>
         <v>50000</v>
       </c>
       <c r="F94" s="8">
-        <f>'[20]MD50000.15-DEC'!$K$1</f>
-        <v>83</v>
+        <f>'[21]MD50000.15-DEC'!$K$1</f>
+        <v>80</v>
       </c>
       <c r="G94" s="8">
-        <f>'[20]MD50000.15-DEC'!$K$2</f>
-        <v>37</v>
+        <f>'[21]MD50000.15-DEC'!$K$2</f>
+        <v>40</v>
       </c>
       <c r="H94" s="8"/>
       <c r="I94" s="8"/>
@@ -10116,16 +10184,16 @@
         <v>12</v>
       </c>
       <c r="K94" s="10">
-        <f>'[20]MD50000.15-DEC'!$B$3</f>
+        <f>'[21]MD50000.15-DEC'!$B$3</f>
         <v>45652</v>
       </c>
       <c r="L94" s="7">
-        <f>'[20]MD50000.15-DEC'!$O$2</f>
-        <v>41500</v>
+        <f>'[21]MD50000.15-DEC'!$O$2</f>
+        <v>40000</v>
       </c>
       <c r="M94" s="7">
-        <f>'[20]MD50000.15-DEC'!$O$1</f>
-        <v>18500</v>
+        <f>'[21]MD50000.15-DEC'!$O$1</f>
+        <v>20000</v>
       </c>
       <c r="N94" s="1">
         <v>3500</v>

--- a/LoanOfficer-A/LoanBook.xlsx
+++ b/LoanOfficer-A/LoanBook.xlsx
@@ -110,13 +110,15 @@
     <externalReference r:id="rId99"/>
     <externalReference r:id="rId100"/>
     <externalReference r:id="rId101"/>
+    <externalReference r:id="rId102"/>
+    <externalReference r:id="rId103"/>
   </externalReferences>
   <calcPr calcId="145621" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="132">
   <si>
     <t>Code</t>
   </si>
@@ -506,6 +508,12 @@
   </si>
   <si>
     <t>Athokpam manao</t>
+  </si>
+  <si>
+    <t>L10000W17P1400-sat</t>
+  </si>
+  <si>
+    <t>sonia</t>
   </si>
 </sst>
 </file>
@@ -812,15 +820,15 @@
             <v>48</v>
           </cell>
           <cell r="O1">
-            <v>15400</v>
+            <v>16450</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>44</v>
+            <v>47</v>
           </cell>
           <cell r="O2">
-            <v>1400</v>
+            <v>350</v>
           </cell>
         </row>
         <row r="3">
@@ -875,6 +883,78 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink100.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD50000.15-DEC"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>17</v>
+          </cell>
+          <cell r="O1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>0</v>
+          </cell>
+          <cell r="O2">
+            <v>11900</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink101.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>120</v>
+          </cell>
+          <cell r="O1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>0</v>
+          </cell>
+          <cell r="O2">
+            <v>24000</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -924,25 +1004,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
-            <v>22600</v>
+            <v>24000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>16</v>
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>1400</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -951,7 +1031,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -973,18 +1053,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
-            <v>21200</v>
+            <v>24000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>15</v>
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>2800</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -1007,25 +1087,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>34</v>
+            <v>21</v>
           </cell>
           <cell r="O1">
-            <v>8600</v>
+            <v>9900</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>86</v>
+            <v>99</v>
           </cell>
           <cell r="O2">
-            <v>3400</v>
+            <v>2100</v>
           </cell>
         </row>
         <row r="3">
@@ -1048,25 +1128,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>100000</v>
           </cell>
           <cell r="K1">
-            <v>216</v>
+            <v>213</v>
           </cell>
           <cell r="O1">
-            <v>30600</v>
+            <v>32400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>51</v>
+            <v>54</v>
           </cell>
           <cell r="O2">
-            <v>129600</v>
+            <v>127800</v>
           </cell>
         </row>
         <row r="3">
@@ -1075,7 +1155,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1089,25 +1169,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>46</v>
+            <v>37</v>
           </cell>
           <cell r="O1">
-            <v>37000</v>
+            <v>41500</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>74</v>
+            <v>83</v>
           </cell>
           <cell r="O2">
-            <v>23000</v>
+            <v>18500</v>
           </cell>
         </row>
         <row r="3">
@@ -1129,25 +1209,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>57</v>
+            <v>44</v>
           </cell>
           <cell r="O1">
-            <v>6300</v>
+            <v>7600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>63</v>
+            <v>76</v>
           </cell>
           <cell r="O2">
-            <v>5700</v>
+            <v>4400</v>
           </cell>
         </row>
         <row r="3">
@@ -1169,25 +1249,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>57</v>
+            <v>44</v>
           </cell>
           <cell r="O1">
-            <v>6300</v>
+            <v>7600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>63</v>
+            <v>76</v>
           </cell>
           <cell r="O2">
-            <v>5700</v>
+            <v>4400</v>
           </cell>
         </row>
         <row r="3">
@@ -1217,18 +1297,18 @@
             <v>200000</v>
           </cell>
           <cell r="K1">
-            <v>226</v>
+            <v>225</v>
           </cell>
           <cell r="O1">
-            <v>49200</v>
+            <v>50400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>41</v>
+            <v>42</v>
           </cell>
           <cell r="O2">
-            <v>271200</v>
+            <v>270000</v>
           </cell>
         </row>
         <row r="3">
@@ -1292,25 +1372,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>9</v>
+            <v>7</v>
           </cell>
           <cell r="O1">
-            <v>5600</v>
+            <v>7000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>8</v>
+            <v>10</v>
           </cell>
           <cell r="O2">
-            <v>6400</v>
+            <v>5000</v>
           </cell>
         </row>
         <row r="3">
@@ -1319,7 +1399,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1334,25 +1414,25 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>80</v>
+            <v>76</v>
           </cell>
           <cell r="O1">
-            <v>20000</v>
+            <v>22000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>40</v>
+            <v>44</v>
           </cell>
           <cell r="O2">
-            <v>40000</v>
+            <v>38000</v>
           </cell>
         </row>
         <row r="3">
@@ -1361,7 +1441,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1376,7 +1456,7 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -1386,15 +1466,15 @@
             <v>17</v>
           </cell>
           <cell r="O1">
-            <v>5600</v>
+            <v>8400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>4</v>
+            <v>6</v>
           </cell>
           <cell r="O2">
-            <v>18200</v>
+            <v>15400</v>
           </cell>
         </row>
         <row r="3">
@@ -1403,7 +1483,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1418,7 +1498,7 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -1428,15 +1508,15 @@
             <v>17</v>
           </cell>
           <cell r="O1">
-            <v>4200</v>
+            <v>7000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>3</v>
+            <v>5</v>
           </cell>
           <cell r="O2">
-            <v>19600</v>
+            <v>16800</v>
           </cell>
         </row>
         <row r="3">
@@ -1445,7 +1525,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1459,25 +1539,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>105</v>
+            <v>101</v>
           </cell>
           <cell r="O1">
-            <v>7500</v>
+            <v>9500</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>15</v>
+            <v>19</v>
           </cell>
           <cell r="O2">
-            <v>52500</v>
+            <v>50500</v>
           </cell>
         </row>
         <row r="3">
@@ -1499,25 +1579,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>110</v>
+            <v>103</v>
           </cell>
           <cell r="O1">
-            <v>1000</v>
+            <v>1700</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>10</v>
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>11000</v>
+            <v>10300</v>
           </cell>
         </row>
         <row r="3">
@@ -1539,25 +1619,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>35000</v>
           </cell>
           <cell r="K1">
-            <v>114</v>
+            <v>112</v>
           </cell>
           <cell r="O1">
-            <v>2100</v>
+            <v>2800</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>6</v>
+            <v>8</v>
           </cell>
           <cell r="O2">
-            <v>39900</v>
+            <v>39200</v>
           </cell>
         </row>
         <row r="3">
@@ -1579,25 +1659,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>116</v>
+            <v>108</v>
           </cell>
           <cell r="O1">
-            <v>800</v>
+            <v>2400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>4</v>
+            <v>12</v>
           </cell>
           <cell r="O2">
-            <v>23200</v>
+            <v>21600</v>
           </cell>
         </row>
         <row r="3">
@@ -1736,25 +1816,25 @@
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>9</v>
+            <v>8</v>
           </cell>
           <cell r="O1">
-            <v>11100</v>
+            <v>11200</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>111</v>
+            <v>112</v>
           </cell>
           <cell r="O2">
-            <v>900</v>
+            <v>800</v>
           </cell>
         </row>
         <row r="3">
@@ -3064,25 +3144,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>100000</v>
           </cell>
           <cell r="K1">
-            <v>24</v>
+            <v>22</v>
           </cell>
           <cell r="O1">
-            <v>64000</v>
+            <v>72000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>16</v>
+            <v>18</v>
           </cell>
           <cell r="O2">
-            <v>96000</v>
+            <v>88000</v>
           </cell>
         </row>
         <row r="3">
@@ -4341,25 +4421,25 @@
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>5</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
-            <v>23000</v>
+            <v>24000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>115</v>
+            <v>120</v>
           </cell>
           <cell r="O2">
-            <v>1000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="7">
@@ -5026,7 +5106,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5068,12 +5148,12 @@
       <c r="K2" s="33"/>
       <c r="L2" s="34">
         <f>SUM(L5:L47)</f>
-        <v>772050</v>
+        <v>768200</v>
       </c>
       <c r="M2" s="35"/>
       <c r="N2" s="1">
         <f>SUM(N5:N56)</f>
-        <v>45650</v>
+        <v>43550</v>
       </c>
       <c r="Q2" s="1">
         <f>14900+260750</f>
@@ -5150,7 +5230,7 @@
       </c>
       <c r="I5" s="13">
         <f>'[1]MD10000.10-JAN'!$K$2</f>
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J5" s="16" t="s">
         <v>12</v>
@@ -5161,11 +5241,11 @@
       </c>
       <c r="L5" s="15">
         <f>'[1]MD10000.10-JAN'!$O$2</f>
-        <v>1400</v>
+        <v>350</v>
       </c>
       <c r="M5" s="15">
         <f>'[1]MD10000.10-JAN'!$O$1</f>
-        <v>15400</v>
+        <v>16450</v>
       </c>
       <c r="N5" s="1">
         <v>350</v>
@@ -5231,11 +5311,11 @@
       </c>
       <c r="F7" s="8">
         <f>'[3]MD10000.1-OCT'!$K$1</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G7" s="8">
         <f>'[3]MD10000.1-OCT'!$K$2</f>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
@@ -5248,11 +5328,11 @@
       </c>
       <c r="L7" s="7">
         <f>'[3]MD10000.1-OCT'!$O$2</f>
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="M7" s="7">
         <f>'[3]MD10000.1-OCT'!$O$1</f>
-        <v>11100</v>
+        <v>11200</v>
       </c>
       <c r="N7" s="1">
         <v>700</v>
@@ -5360,11 +5440,11 @@
       <c r="G10" s="8"/>
       <c r="H10" s="8">
         <f>'[6]MD20000.18-DEC'!$K$1</f>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I10" s="8">
         <f>'[6]MD20000.18-DEC'!$K$2</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>12</v>
@@ -5375,11 +5455,11 @@
       </c>
       <c r="L10" s="7">
         <f>'[6]MD20000.18-DEC'!$O$2</f>
-        <v>96000</v>
+        <v>88000</v>
       </c>
       <c r="M10" s="7">
         <f>'[6]MD20000.18-DEC'!$O$1</f>
-        <v>64000</v>
+        <v>72000</v>
       </c>
       <c r="N10" s="1">
         <v>4000</v>
@@ -5426,46 +5506,43 @@
       </c>
     </row>
     <row r="12" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="6">
+      <c r="B12" s="17">
         <v>73</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="19">
         <f>'[9]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="20">
         <f>'[9]MD20000.18-DEC'!$K$1</f>
-        <v>5</v>
-      </c>
-      <c r="G12" s="8">
+        <v>0</v>
+      </c>
+      <c r="G12" s="20">
         <f>'[9]MD20000.18-DEC'!$K$2</f>
-        <v>115</v>
-      </c>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K12" s="10">
+      <c r="K12" s="22">
         <f>'[9]MD20000.18-DEC'!$B$7</f>
         <v>45587</v>
       </c>
-      <c r="L12" s="7">
+      <c r="L12" s="19">
         <f>'[9]MD20000.18-DEC'!$O$2</f>
-        <v>1000</v>
-      </c>
-      <c r="M12" s="7">
+        <v>0</v>
+      </c>
+      <c r="M12" s="19">
         <f>'[9]MD20000.18-DEC'!$O$1</f>
-        <v>23000</v>
-      </c>
-      <c r="N12" s="1">
-        <v>1400</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="13" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5555,89 +5632,83 @@
       </c>
     </row>
     <row r="15" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="6">
+      <c r="B15" s="17">
         <v>77</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="19">
         <f>'[12]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8">
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20">
         <f>'[12]MD20000.15-DEc'!$K$1</f>
-        <v>1</v>
-      </c>
-      <c r="I15" s="8">
+        <v>0</v>
+      </c>
+      <c r="I15" s="20">
         <f>'[12]MD20000.15-DEc'!$K$2</f>
-        <v>16</v>
-      </c>
-      <c r="J15" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K15" s="10">
+      <c r="K15" s="22">
         <f>'[12]MD20000.15-DEc'!$B$3</f>
         <v>45595</v>
       </c>
-      <c r="L15" s="7">
+      <c r="L15" s="19">
         <f>'[12]MD20000.15-DEc'!$O$2</f>
-        <v>1400</v>
-      </c>
-      <c r="M15" s="7">
+        <v>0</v>
+      </c>
+      <c r="M15" s="19">
         <f>'[12]MD20000.15-DEc'!$O$1</f>
-        <v>22600</v>
-      </c>
-      <c r="N15" s="1">
-        <v>1400</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="16" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="6">
+      <c r="B16" s="17">
         <v>78</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="19">
         <f>'[13]MD10000.10-JAN'!$C$1</f>
         <v>20000</v>
       </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8">
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20">
         <f>'[13]MD10000.10-JAN'!$K$1</f>
-        <v>2</v>
-      </c>
-      <c r="I16" s="8">
+        <v>0</v>
+      </c>
+      <c r="I16" s="20">
         <f>'[13]MD10000.10-JAN'!$K$2</f>
-        <v>15</v>
-      </c>
-      <c r="J16" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K16" s="10">
+      <c r="K16" s="22">
         <f>'[13]MD10000.10-JAN'!$B$3</f>
         <v>45602</v>
       </c>
-      <c r="L16" s="7">
+      <c r="L16" s="19">
         <f>'[13]MD10000.10-JAN'!$O$2</f>
-        <v>2800</v>
-      </c>
-      <c r="M16" s="7">
+        <v>0</v>
+      </c>
+      <c r="M16" s="19">
         <f>'[13]MD10000.10-JAN'!$O$1</f>
-        <v>21200</v>
-      </c>
-      <c r="N16" s="1">
-        <v>1400</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="17" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5656,11 +5727,11 @@
       </c>
       <c r="F17" s="8">
         <f>'[14]MD20000.18-DEC'!$K$1</f>
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G17" s="8">
         <f>'[14]MD20000.18-DEC'!$K$2</f>
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
@@ -5673,11 +5744,11 @@
       </c>
       <c r="L17" s="7">
         <f>'[14]MD20000.18-DEC'!$O$2</f>
-        <v>3400</v>
+        <v>2100</v>
       </c>
       <c r="M17" s="7">
         <f>'[14]MD20000.18-DEC'!$O$1</f>
-        <v>8600</v>
+        <v>9900</v>
       </c>
       <c r="N17" s="1">
         <v>700</v>
@@ -5699,11 +5770,11 @@
       </c>
       <c r="F18" s="8">
         <f>'[15]MD50000.15-DEC'!$K$1</f>
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G18" s="8">
         <f>'[15]MD50000.15-DEC'!$K$2</f>
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
@@ -5716,11 +5787,11 @@
       </c>
       <c r="L18" s="7">
         <f>'[15]MD50000.15-DEC'!$O$2</f>
-        <v>129600</v>
+        <v>127800</v>
       </c>
       <c r="M18" s="7">
         <f>'[15]MD50000.15-DEC'!$O$1</f>
-        <v>30600</v>
+        <v>32400</v>
       </c>
       <c r="N18" s="1">
         <v>4200</v>
@@ -5742,11 +5813,11 @@
       </c>
       <c r="F19" s="8">
         <f>'[16]MD20000.18-DEC'!$K$1</f>
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="G19" s="8">
         <f>'[16]MD20000.18-DEC'!$K$2</f>
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -5759,11 +5830,11 @@
       </c>
       <c r="L19" s="7">
         <f>'[16]MD20000.18-DEC'!$O$2</f>
-        <v>23000</v>
+        <v>18500</v>
       </c>
       <c r="M19" s="7">
         <f>'[16]MD20000.18-DEC'!$O$1</f>
-        <v>37000</v>
+        <v>41500</v>
       </c>
       <c r="N19" s="1">
         <v>3500</v>
@@ -5785,11 +5856,11 @@
       </c>
       <c r="F20" s="8">
         <f>'[17]MD20000.18-DEC'!$K$1</f>
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G20" s="8">
         <f>'[17]MD20000.18-DEC'!$K$2</f>
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
@@ -5802,11 +5873,11 @@
       </c>
       <c r="L20" s="7">
         <f>'[17]MD20000.18-DEC'!$O$2</f>
-        <v>5700</v>
+        <v>4400</v>
       </c>
       <c r="M20" s="7">
         <f>'[17]MD20000.18-DEC'!$O$1</f>
-        <v>6300</v>
+        <v>7600</v>
       </c>
       <c r="N20" s="1">
         <v>700</v>
@@ -5828,11 +5899,11 @@
       </c>
       <c r="F21" s="8">
         <f>'[18]MD20000.18-DEC'!$K$1</f>
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G21" s="8">
         <f>'[18]MD20000.18-DEC'!$K$2</f>
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
@@ -5845,11 +5916,11 @@
       </c>
       <c r="L21" s="7">
         <f>'[18]MD20000.18-DEC'!$O$2</f>
-        <v>5700</v>
+        <v>4400</v>
       </c>
       <c r="M21" s="7">
         <f>'[18]MD20000.18-DEC'!$O$1</f>
-        <v>6300</v>
+        <v>7600</v>
       </c>
       <c r="N21" s="1">
         <v>700</v>
@@ -5871,11 +5942,11 @@
       </c>
       <c r="F22" s="8">
         <f>'[19]MD50000.15-DEC'!$K$1</f>
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G22" s="8">
         <f>'[19]MD50000.15-DEC'!$K$2</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
@@ -5888,11 +5959,11 @@
       </c>
       <c r="L22" s="7">
         <f>'[19]MD50000.15-DEC'!$O$2</f>
-        <v>271200</v>
+        <v>270000</v>
       </c>
       <c r="M22" s="7">
         <f>'[19]MD50000.15-DEC'!$O$1</f>
-        <v>49200</v>
+        <v>50400</v>
       </c>
       <c r="N22" s="1">
         <v>8400</v>
@@ -5916,11 +5987,11 @@
       <c r="G23" s="8"/>
       <c r="H23" s="8">
         <f>'[20]MD20000.15-DEc'!$K$1</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I23" s="8">
         <f>'[20]MD20000.15-DEc'!$K$2</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>12</v>
@@ -5931,11 +6002,11 @@
       </c>
       <c r="L23" s="7">
         <f>'[20]MD20000.15-DEc'!$O$2</f>
-        <v>6400</v>
+        <v>5000</v>
       </c>
       <c r="M23" s="7">
         <f>'[20]MD20000.15-DEc'!$O$1</f>
-        <v>5600</v>
+        <v>7000</v>
       </c>
       <c r="N23" s="1">
         <v>700</v>
@@ -5957,11 +6028,11 @@
       </c>
       <c r="F24" s="8">
         <f>'[21]MD50000.15-DEC'!$K$1</f>
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G24" s="8">
         <f>'[21]MD50000.15-DEC'!$K$2</f>
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
@@ -5974,11 +6045,11 @@
       </c>
       <c r="L24" s="7">
         <f>'[21]MD50000.15-DEC'!$O$2</f>
-        <v>40000</v>
+        <v>38000</v>
       </c>
       <c r="M24" s="7">
         <f>'[21]MD50000.15-DEC'!$O$1</f>
-        <v>20000</v>
+        <v>22000</v>
       </c>
       <c r="N24" s="1">
         <v>3500</v>
@@ -6006,7 +6077,7 @@
       </c>
       <c r="I25" s="8">
         <f>'[22]MD50000.15-DEC'!$K$2</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>12</v>
@@ -6017,11 +6088,11 @@
       </c>
       <c r="L25" s="7">
         <f>'[22]MD50000.15-DEC'!$O$2</f>
-        <v>18200</v>
+        <v>15400</v>
       </c>
       <c r="M25" s="7">
         <f>'[22]MD50000.15-DEC'!$O$1</f>
-        <v>5600</v>
+        <v>8400</v>
       </c>
       <c r="N25" s="1">
         <v>1400</v>
@@ -6049,7 +6120,7 @@
       </c>
       <c r="I26" s="8">
         <f>'[23]MD50000.15-DEC'!$K$2</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J26" s="9" t="s">
         <v>125</v>
@@ -6060,11 +6131,11 @@
       </c>
       <c r="L26" s="7">
         <f>'[23]MD50000.15-DEC'!$O$2</f>
-        <v>19600</v>
+        <v>16800</v>
       </c>
       <c r="M26" s="7">
         <f>'[23]MD50000.15-DEC'!$O$1</f>
-        <v>4200</v>
+        <v>7000</v>
       </c>
       <c r="N26" s="1">
         <v>1400</v>
@@ -6086,11 +6157,11 @@
       </c>
       <c r="F27" s="8">
         <f>'[24]MD20000.18-DEC'!$K$1</f>
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G27" s="8">
         <f>'[24]MD20000.18-DEC'!$K$2</f>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
@@ -6103,11 +6174,11 @@
       </c>
       <c r="L27" s="7">
         <f>'[24]MD20000.18-DEC'!$O$2</f>
-        <v>52500</v>
+        <v>50500</v>
       </c>
       <c r="M27" s="7">
         <f>'[24]MD20000.18-DEC'!$O$1</f>
-        <v>7500</v>
+        <v>9500</v>
       </c>
       <c r="N27" s="1">
         <v>3500</v>
@@ -6129,11 +6200,11 @@
       </c>
       <c r="F28" s="8">
         <f>'[25]MD20000.18-DEC'!$K$1</f>
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G28" s="8">
         <f>'[25]MD20000.18-DEC'!$K$2</f>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
@@ -6146,11 +6217,11 @@
       </c>
       <c r="L28" s="7">
         <f>'[25]MD20000.18-DEC'!$O$2</f>
-        <v>11000</v>
+        <v>10300</v>
       </c>
       <c r="M28" s="7">
         <f>'[25]MD20000.18-DEC'!$O$1</f>
-        <v>1000</v>
+        <v>1700</v>
       </c>
       <c r="N28" s="1">
         <v>700</v>
@@ -6172,11 +6243,11 @@
       </c>
       <c r="F29" s="8">
         <f>'[26]MD20000.18-DEC'!$K$1</f>
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G29" s="8">
         <f>'[26]MD20000.18-DEC'!$K$2</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
@@ -6189,11 +6260,11 @@
       </c>
       <c r="L29" s="7">
         <f>'[26]MD20000.18-DEC'!$O$2</f>
-        <v>39900</v>
+        <v>39200</v>
       </c>
       <c r="M29" s="7">
         <f>'[26]MD20000.18-DEC'!$O$1</f>
-        <v>2100</v>
+        <v>2800</v>
       </c>
       <c r="N29" s="1">
         <v>2450</v>
@@ -6215,11 +6286,11 @@
       </c>
       <c r="F30" s="8">
         <f>'[27]MD20000.18-DEC'!$K$1</f>
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="G30" s="8">
         <f>'[27]MD20000.18-DEC'!$K$2</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
@@ -6232,43 +6303,101 @@
       </c>
       <c r="L30" s="7">
         <f>'[27]MD20000.18-DEC'!$O$2</f>
-        <v>23200</v>
+        <v>21600</v>
       </c>
       <c r="M30" s="7">
         <f>'[27]MD20000.18-DEC'!$O$1</f>
-        <v>800</v>
+        <v>2400</v>
       </c>
       <c r="N30" s="1">
         <v>1400</v>
       </c>
     </row>
     <row r="31" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="6"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="7"/>
+      <c r="B31" s="6">
+        <v>97</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="E31" s="7">
+        <f>'[100]MD50000.15-DEC'!$C$1</f>
+        <v>10000</v>
+      </c>
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
+      <c r="H31" s="8">
+        <f>'[100]MD50000.15-DEC'!$K$1</f>
+        <v>17</v>
+      </c>
+      <c r="I31" s="8">
+        <f>'[100]MD50000.15-DEC'!$K$2</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K31" s="10">
+        <f>'[100]MD50000.15-DEC'!$B$3</f>
+        <v>0</v>
+      </c>
+      <c r="L31" s="7">
+        <f>'[100]MD50000.15-DEC'!$O$2</f>
+        <v>11900</v>
+      </c>
+      <c r="M31" s="7">
+        <f>'[100]MD50000.15-DEC'!$O$1</f>
+        <v>0</v>
+      </c>
+      <c r="N31" s="1">
+        <v>700</v>
+      </c>
     </row>
     <row r="32" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="6"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
+      <c r="B32" s="6">
+        <v>98</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E32" s="7">
+        <f>'[101]MD20000.18-DEC'!$C$1</f>
+        <v>20000</v>
+      </c>
+      <c r="F32" s="8">
+        <f>'[101]MD20000.18-DEC'!$K$1</f>
+        <v>120</v>
+      </c>
+      <c r="G32" s="8">
+        <f>'[101]MD20000.18-DEC'!$K$2</f>
+        <v>0</v>
+      </c>
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
+      <c r="J32" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K32" s="10">
+        <f>'[101]MD20000.18-DEC'!$B$3</f>
+        <v>0</v>
+      </c>
+      <c r="L32" s="7">
+        <f>'[101]MD20000.18-DEC'!$O$2</f>
+        <v>24000</v>
+      </c>
+      <c r="M32" s="7">
+        <f>'[101]MD20000.18-DEC'!$O$1</f>
+        <v>0</v>
+      </c>
+      <c r="N32" s="1">
+        <v>1400</v>
+      </c>
     </row>
     <row r="33" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="6"/>
@@ -6485,7 +6614,7 @@
       <c r="K2" s="33"/>
       <c r="L2" s="34">
         <f>SUM(L5:L108)</f>
-        <v>707050</v>
+        <v>677900</v>
       </c>
       <c r="M2" s="35"/>
       <c r="N2" s="1">
@@ -7804,7 +7933,7 @@
       </c>
       <c r="I36" s="13">
         <f>'[1]MD10000.10-JAN'!$K$2</f>
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J36" s="16" t="s">
         <v>12</v>
@@ -7815,11 +7944,11 @@
       </c>
       <c r="L36" s="15">
         <f>'[1]MD10000.10-JAN'!$O$2</f>
-        <v>1400</v>
+        <v>350</v>
       </c>
       <c r="M36" s="15">
         <f>'[1]MD10000.10-JAN'!$O$1</f>
-        <v>15400</v>
+        <v>16450</v>
       </c>
       <c r="N36" s="1">
         <v>350</v>
@@ -9041,11 +9170,11 @@
       </c>
       <c r="F67" s="8">
         <f>'[3]MD10000.1-OCT'!$K$1</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G67" s="8">
         <f>'[3]MD10000.1-OCT'!$K$2</f>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
@@ -9058,11 +9187,11 @@
       </c>
       <c r="L67" s="7">
         <f>'[3]MD10000.1-OCT'!$O$2</f>
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="M67" s="7">
         <f>'[3]MD10000.1-OCT'!$O$1</f>
-        <v>11100</v>
+        <v>11200</v>
       </c>
       <c r="N67" s="1">
         <v>700</v>
@@ -9252,11 +9381,11 @@
       <c r="G72" s="8"/>
       <c r="H72" s="8">
         <f>'[6]MD20000.18-DEC'!$K$1</f>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I72" s="8">
         <f>'[6]MD20000.18-DEC'!$K$2</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J72" s="9" t="s">
         <v>12</v>
@@ -9267,11 +9396,11 @@
       </c>
       <c r="L72" s="7">
         <f>'[6]MD20000.18-DEC'!$O$2</f>
-        <v>96000</v>
+        <v>88000</v>
       </c>
       <c r="M72" s="7">
         <f>'[6]MD20000.18-DEC'!$O$1</f>
-        <v>64000</v>
+        <v>72000</v>
       </c>
       <c r="N72" s="1">
         <v>4000</v>
@@ -9456,11 +9585,11 @@
       </c>
       <c r="F77" s="8">
         <f>'[9]MD20000.18-DEC'!$K$1</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G77" s="8">
         <f>'[9]MD20000.18-DEC'!$K$2</f>
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="H77" s="8"/>
       <c r="I77" s="8"/>
@@ -9473,11 +9602,11 @@
       </c>
       <c r="L77" s="7">
         <f>'[9]MD20000.18-DEC'!$O$2</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="M77" s="7">
         <f>'[9]MD20000.18-DEC'!$O$1</f>
-        <v>23000</v>
+        <v>24000</v>
       </c>
       <c r="N77" s="1">
         <v>1400</v>
@@ -9627,11 +9756,11 @@
       <c r="G81" s="8"/>
       <c r="H81" s="8">
         <f>'[12]MD20000.15-DEc'!$K$1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I81" s="8">
         <f>'[12]MD20000.15-DEc'!$K$2</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J81" s="9" t="s">
         <v>12</v>
@@ -9642,11 +9771,11 @@
       </c>
       <c r="L81" s="7">
         <f>'[12]MD20000.15-DEc'!$O$2</f>
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="M81" s="7">
         <f>'[12]MD20000.15-DEc'!$O$1</f>
-        <v>22600</v>
+        <v>24000</v>
       </c>
       <c r="N81" s="1">
         <v>1400</v>
@@ -9670,11 +9799,11 @@
       <c r="G82" s="8"/>
       <c r="H82" s="8">
         <f>'[13]MD10000.10-JAN'!$K$1</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I82" s="8">
         <f>'[13]MD10000.10-JAN'!$K$2</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J82" s="9" t="s">
         <v>12</v>
@@ -9685,11 +9814,11 @@
       </c>
       <c r="L82" s="7">
         <f>'[13]MD10000.10-JAN'!$O$2</f>
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="M82" s="7">
         <f>'[13]MD10000.10-JAN'!$O$1</f>
-        <v>21200</v>
+        <v>24000</v>
       </c>
       <c r="N82" s="1">
         <v>1400</v>
@@ -9831,11 +9960,11 @@
       </c>
       <c r="F86" s="8">
         <f>'[14]MD20000.18-DEC'!$K$1</f>
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G86" s="8">
         <f>'[14]MD20000.18-DEC'!$K$2</f>
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="H86" s="8"/>
       <c r="I86" s="8"/>
@@ -9848,11 +9977,11 @@
       </c>
       <c r="L86" s="7">
         <f>'[14]MD20000.18-DEC'!$O$2</f>
-        <v>3400</v>
+        <v>2100</v>
       </c>
       <c r="M86" s="7">
         <f>'[14]MD20000.18-DEC'!$O$1</f>
-        <v>8600</v>
+        <v>9900</v>
       </c>
       <c r="N86" s="1">
         <v>700</v>
@@ -9874,11 +10003,11 @@
       </c>
       <c r="F87" s="8">
         <f>'[15]MD50000.15-DEC'!$K$1</f>
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G87" s="8">
         <f>'[15]MD50000.15-DEC'!$K$2</f>
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H87" s="8"/>
       <c r="I87" s="8"/>
@@ -9891,11 +10020,11 @@
       </c>
       <c r="L87" s="7">
         <f>'[15]MD50000.15-DEC'!$O$2</f>
-        <v>129600</v>
+        <v>127800</v>
       </c>
       <c r="M87" s="7">
         <f>'[15]MD50000.15-DEC'!$O$1</f>
-        <v>30600</v>
+        <v>32400</v>
       </c>
       <c r="N87" s="1">
         <v>4200</v>
@@ -9917,11 +10046,11 @@
       </c>
       <c r="F88" s="8">
         <f>'[16]MD20000.18-DEC'!$K$1</f>
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="G88" s="8">
         <f>'[16]MD20000.18-DEC'!$K$2</f>
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H88" s="8"/>
       <c r="I88" s="8"/>
@@ -9934,11 +10063,11 @@
       </c>
       <c r="L88" s="7">
         <f>'[16]MD20000.18-DEC'!$O$2</f>
-        <v>23000</v>
+        <v>18500</v>
       </c>
       <c r="M88" s="7">
         <f>'[16]MD20000.18-DEC'!$O$1</f>
-        <v>37000</v>
+        <v>41500</v>
       </c>
       <c r="N88" s="1">
         <v>3500</v>
@@ -10000,11 +10129,11 @@
       </c>
       <c r="F90" s="8">
         <f>'[17]MD20000.18-DEC'!$K$1</f>
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G90" s="8">
         <f>'[17]MD20000.18-DEC'!$K$2</f>
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="H90" s="8"/>
       <c r="I90" s="8"/>
@@ -10017,11 +10146,11 @@
       </c>
       <c r="L90" s="7">
         <f>'[17]MD20000.18-DEC'!$O$2</f>
-        <v>5700</v>
+        <v>4400</v>
       </c>
       <c r="M90" s="7">
         <f>'[17]MD20000.18-DEC'!$O$1</f>
-        <v>6300</v>
+        <v>7600</v>
       </c>
       <c r="N90" s="1">
         <v>700</v>
@@ -10043,11 +10172,11 @@
       </c>
       <c r="F91" s="8">
         <f>'[18]MD20000.18-DEC'!$K$1</f>
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G91" s="8">
         <f>'[18]MD20000.18-DEC'!$K$2</f>
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="H91" s="8"/>
       <c r="I91" s="8"/>
@@ -10060,11 +10189,11 @@
       </c>
       <c r="L91" s="7">
         <f>'[18]MD20000.18-DEC'!$O$2</f>
-        <v>5700</v>
+        <v>4400</v>
       </c>
       <c r="M91" s="7">
         <f>'[18]MD20000.18-DEC'!$O$1</f>
-        <v>6300</v>
+        <v>7600</v>
       </c>
       <c r="N91" s="1">
         <v>700</v>
@@ -10086,11 +10215,11 @@
       </c>
       <c r="F92" s="8">
         <f>'[19]MD50000.15-DEC'!$K$1</f>
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G92" s="8">
         <f>'[19]MD50000.15-DEC'!$K$2</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H92" s="8"/>
       <c r="I92" s="8"/>
@@ -10103,11 +10232,11 @@
       </c>
       <c r="L92" s="7">
         <f>'[19]MD50000.15-DEC'!$O$2</f>
-        <v>271200</v>
+        <v>270000</v>
       </c>
       <c r="M92" s="7">
         <f>'[19]MD50000.15-DEC'!$O$1</f>
-        <v>49200</v>
+        <v>50400</v>
       </c>
       <c r="N92" s="1">
         <v>8400</v>
@@ -10131,11 +10260,11 @@
       <c r="G93" s="8"/>
       <c r="H93" s="8">
         <f>'[20]MD20000.15-DEc'!$K$1</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I93" s="8">
         <f>'[20]MD20000.15-DEc'!$K$2</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J93" s="9" t="s">
         <v>12</v>
@@ -10146,11 +10275,11 @@
       </c>
       <c r="L93" s="7">
         <f>'[20]MD20000.15-DEc'!$O$2</f>
-        <v>6400</v>
+        <v>5000</v>
       </c>
       <c r="M93" s="7">
         <f>'[20]MD20000.15-DEc'!$O$1</f>
-        <v>5600</v>
+        <v>7000</v>
       </c>
       <c r="N93" s="1">
         <v>700</v>
@@ -10172,11 +10301,11 @@
       </c>
       <c r="F94" s="8">
         <f>'[21]MD50000.15-DEC'!$K$1</f>
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G94" s="8">
         <f>'[21]MD50000.15-DEC'!$K$2</f>
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H94" s="8"/>
       <c r="I94" s="8"/>
@@ -10189,11 +10318,11 @@
       </c>
       <c r="L94" s="7">
         <f>'[21]MD50000.15-DEC'!$O$2</f>
-        <v>40000</v>
+        <v>38000</v>
       </c>
       <c r="M94" s="7">
         <f>'[21]MD50000.15-DEC'!$O$1</f>
-        <v>20000</v>
+        <v>22000</v>
       </c>
       <c r="N94" s="1">
         <v>3500</v>

--- a/LoanOfficer-A/LoanBook.xlsx
+++ b/LoanOfficer-A/LoanBook.xlsx
@@ -112,13 +112,14 @@
     <externalReference r:id="rId101"/>
     <externalReference r:id="rId102"/>
     <externalReference r:id="rId103"/>
+    <externalReference r:id="rId104"/>
   </externalReferences>
   <calcPr calcId="145621" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="133">
   <si>
     <t>Code</t>
   </si>
@@ -514,6 +515,9 @@
   </si>
   <si>
     <t>sonia</t>
+  </si>
+  <si>
+    <t>bijenty</t>
   </si>
 </sst>
 </file>
@@ -820,15 +824,15 @@
             <v>48</v>
           </cell>
           <cell r="O1">
-            <v>16450</v>
+            <v>16800</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>47</v>
+            <v>48</v>
           </cell>
           <cell r="O2">
-            <v>350</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -844,6 +848,46 @@
 </file>
 
 <file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>30</v>
+          </cell>
+          <cell r="O1">
+            <v>9000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>90</v>
+          </cell>
+          <cell r="O2">
+            <v>3000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45584</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink100.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -855,26 +899,26 @@
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
+            <v>50000</v>
+          </cell>
+          <cell r="K1">
+            <v>100</v>
+          </cell>
+          <cell r="O1">
             <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>60</v>
-          </cell>
-          <cell r="O1">
-            <v>6000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>60</v>
+            <v>20</v>
           </cell>
           <cell r="O2">
-            <v>6000</v>
+            <v>50000</v>
           </cell>
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45584</v>
+            <v>45612</v>
           </cell>
         </row>
       </sheetData>
@@ -883,7 +927,47 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink100.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink101.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>30000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>36000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45647</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink102.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -896,7 +980,7 @@
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
-            <v>10000</v>
+            <v>20000</v>
           </cell>
           <cell r="K1">
             <v>17</v>
@@ -910,46 +994,11 @@
             <v>0</v>
           </cell>
           <cell r="O2">
-            <v>11900</v>
+            <v>23800</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink101.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>120</v>
-          </cell>
-          <cell r="O1">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>0</v>
-          </cell>
-          <cell r="O2">
-            <v>24000</v>
-          </cell>
-        </row>
-      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1094,18 +1143,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>21</v>
+            <v>14</v>
           </cell>
           <cell r="O1">
-            <v>9900</v>
+            <v>10600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>99</v>
+            <v>106</v>
           </cell>
           <cell r="O2">
-            <v>2100</v>
+            <v>1400</v>
           </cell>
         </row>
         <row r="3">
@@ -1135,18 +1184,18 @@
             <v>100000</v>
           </cell>
           <cell r="K1">
-            <v>213</v>
+            <v>211</v>
           </cell>
           <cell r="O1">
-            <v>32400</v>
+            <v>33600</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>54</v>
+            <v>56</v>
           </cell>
           <cell r="O2">
-            <v>127800</v>
+            <v>126600</v>
           </cell>
         </row>
         <row r="3">
@@ -1176,18 +1225,18 @@
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>37</v>
+            <v>27</v>
           </cell>
           <cell r="O1">
-            <v>41500</v>
+            <v>46500</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>83</v>
+            <v>93</v>
           </cell>
           <cell r="O2">
-            <v>18500</v>
+            <v>13500</v>
           </cell>
         </row>
         <row r="3">
@@ -1216,18 +1265,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>44</v>
+            <v>37</v>
           </cell>
           <cell r="O1">
-            <v>7600</v>
+            <v>8300</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>76</v>
+            <v>83</v>
           </cell>
           <cell r="O2">
-            <v>4400</v>
+            <v>3700</v>
           </cell>
         </row>
         <row r="3">
@@ -1256,18 +1305,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>44</v>
+            <v>37</v>
           </cell>
           <cell r="O1">
-            <v>7600</v>
+            <v>8300</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>76</v>
+            <v>83</v>
           </cell>
           <cell r="O2">
-            <v>4400</v>
+            <v>3700</v>
           </cell>
         </row>
         <row r="3">
@@ -1290,7 +1339,7 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -1317,7 +1366,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1372,7 +1421,7 @@
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -1399,7 +1448,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1421,18 +1470,18 @@
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>76</v>
+            <v>68</v>
           </cell>
           <cell r="O1">
-            <v>22000</v>
+            <v>26000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>44</v>
+            <v>52</v>
           </cell>
           <cell r="O2">
-            <v>38000</v>
+            <v>34000</v>
           </cell>
         </row>
         <row r="3">
@@ -1466,15 +1515,15 @@
             <v>17</v>
           </cell>
           <cell r="O1">
-            <v>8400</v>
+            <v>9800</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>6</v>
+            <v>7</v>
           </cell>
           <cell r="O2">
-            <v>15400</v>
+            <v>14000</v>
           </cell>
         </row>
         <row r="3">
@@ -1508,15 +1557,15 @@
             <v>17</v>
           </cell>
           <cell r="O1">
-            <v>7000</v>
+            <v>8400</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>5</v>
+            <v>6</v>
           </cell>
           <cell r="O2">
-            <v>16800</v>
+            <v>15400</v>
           </cell>
         </row>
         <row r="3">
@@ -1546,18 +1595,18 @@
             <v>50000</v>
           </cell>
           <cell r="K1">
-            <v>101</v>
+            <v>94</v>
           </cell>
           <cell r="O1">
-            <v>9500</v>
+            <v>13000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>19</v>
+            <v>26</v>
           </cell>
           <cell r="O2">
-            <v>50500</v>
+            <v>47000</v>
           </cell>
         </row>
         <row r="3">
@@ -1586,18 +1635,18 @@
             <v>10000</v>
           </cell>
           <cell r="K1">
-            <v>103</v>
+            <v>91</v>
           </cell>
           <cell r="O1">
-            <v>1700</v>
+            <v>2900</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>17</v>
+            <v>29</v>
           </cell>
           <cell r="O2">
-            <v>10300</v>
+            <v>9100</v>
           </cell>
         </row>
         <row r="3">
@@ -1626,18 +1675,18 @@
             <v>35000</v>
           </cell>
           <cell r="K1">
-            <v>112</v>
+            <v>105</v>
           </cell>
           <cell r="O1">
-            <v>2800</v>
+            <v>5250</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>8</v>
+            <v>15</v>
           </cell>
           <cell r="O2">
-            <v>39200</v>
+            <v>36750</v>
           </cell>
         </row>
         <row r="3">
@@ -1666,18 +1715,18 @@
             <v>20000</v>
           </cell>
           <cell r="K1">
-            <v>108</v>
+            <v>95</v>
           </cell>
           <cell r="O1">
-            <v>2400</v>
+            <v>5000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>12</v>
+            <v>25</v>
           </cell>
           <cell r="O2">
-            <v>21600</v>
+            <v>19000</v>
           </cell>
         </row>
         <row r="3">
@@ -1692,6 +1741,123 @@
 </file>
 
 <file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD50000.15-DEC"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>17</v>
+          </cell>
+          <cell r="O1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>0</v>
+          </cell>
+          <cell r="O2">
+            <v>23800</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>110</v>
+          </cell>
+          <cell r="O1">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>10</v>
+          </cell>
+          <cell r="O2">
+            <v>22000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45716</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>8</v>
+          </cell>
+          <cell r="O1">
+            <v>11200</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>112</v>
+          </cell>
+          <cell r="O2">
+            <v>800</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45561</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1768,7 +1934,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1808,47 +1974,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.1-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>8</v>
-          </cell>
-          <cell r="O1">
-            <v>11200</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>112</v>
-          </cell>
-          <cell r="O2">
-            <v>800</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45561</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1888,7 +2014,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1928,7 +2054,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1970,7 +2096,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2010,7 +2136,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2052,7 +2178,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2094,7 +2220,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2136,7 +2262,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2178,78 +2304,6 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45279</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.22-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>120</v>
-          </cell>
-          <cell r="O1">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -2295,6 +2349,78 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45279</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.22-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>120</v>
+          </cell>
+          <cell r="O1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
       <sheetName val="MD50000.15-DEC"/>
       <sheetName val="Sheet1"/>
     </sheetNames>
@@ -2332,7 +2458,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2372,7 +2498,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2414,7 +2540,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2456,7 +2582,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2496,7 +2622,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2536,7 +2662,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2578,7 +2704,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2620,86 +2746,6 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.20-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1">
-        <row r="1">
-          <cell r="C1">
-            <v>5000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>6000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45332</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.1-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>12000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45339</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -2745,6 +2791,46 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
+      <sheetName val="MD10000.20-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>5000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>6000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45332</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
@@ -2771,7 +2857,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45334</v>
+            <v>45339</v>
           </cell>
         </row>
       </sheetData>
@@ -2780,7 +2866,47 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45334</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2816,7 +2942,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2844,7 +2970,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2886,7 +3012,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2921,90 +3047,6 @@
           </cell>
         </row>
       </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.10-JAN"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>16800</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>48</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45366</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.15-DEc"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45380</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3042,7 +3084,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45389</v>
+            <v>45366</v>
           </cell>
         </row>
       </sheetData>
@@ -3067,8 +3109,8 @@
           <cell r="C1">
             <v>20000</v>
           </cell>
-          <cell r="G1">
-            <v>17</v>
+          <cell r="K1">
+            <v>0</v>
           </cell>
           <cell r="O1">
             <v>24000</v>
@@ -3084,7 +3126,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45394</v>
+            <v>45380</v>
           </cell>
         </row>
       </sheetData>
@@ -3095,6 +3137,88 @@
 </file>
 
 <file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.10-JAN"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>16800</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>48</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45389</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>100000</v>
+          </cell>
+          <cell r="K1">
+            <v>21</v>
+          </cell>
+          <cell r="O1">
+            <v>76000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>19</v>
+          </cell>
+          <cell r="O2">
+            <v>84000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45590</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3126,7 +3250,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45406</v>
+            <v>45394</v>
           </cell>
         </row>
       </sheetData>
@@ -3136,47 +3260,49 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
+      <sheetName val="MD20000.15-DEc"/>
+      <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
+      <sheetData sheetId="1" refreshError="1">
         <row r="1">
           <cell r="C1">
-            <v>100000</v>
-          </cell>
-          <cell r="K1">
-            <v>22</v>
+            <v>20000</v>
+          </cell>
+          <cell r="G1">
+            <v>17</v>
           </cell>
           <cell r="O1">
-            <v>72000</v>
+            <v>24000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>18</v>
+            <v>17</v>
           </cell>
           <cell r="O2">
-            <v>88000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45590</v>
+            <v>45406</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3216,7 +3342,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3255,7 +3381,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3273,86 +3399,6 @@
         </row>
       </sheetData>
       <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.20-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1">
-        <row r="1">
-          <cell r="C1">
-            <v>5000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>6000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45427</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45425</v>
-          </cell>
-        </row>
-      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3389,7 +3435,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45436</v>
+            <v>45427</v>
           </cell>
         </row>
       </sheetData>
@@ -3399,6 +3445,86 @@
 </file>
 
 <file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45425</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.20-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>5000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>6000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45436</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3438,7 +3564,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3470,69 +3596,6 @@
         <row r="3">
           <cell r="B3">
             <v>45437</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.20-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>5000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>5950</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45444</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.1-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45450</v>
           </cell>
         </row>
       </sheetData>
@@ -3586,6 +3649,69 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
+      <sheetName val="MD10000.20-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>5000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>5950</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45444</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink71.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45450</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink72.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
       <sheetName val="MD10000.1-OCT"/>
     </sheetNames>
     <sheetDataSet>
@@ -3613,7 +3739,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink71.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink73.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3653,7 +3779,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink72.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink74.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3693,7 +3819,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink73.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink75.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3730,88 +3856,6 @@
         </row>
       </sheetData>
       <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink74.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.15-DEc"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>12000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45496</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink75.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>20000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45493</v>
-          </cell>
-        </row>
-      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3849,7 +3893,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45502</v>
+            <v>45496</v>
           </cell>
         </row>
       </sheetData>
@@ -3860,6 +3904,88 @@
 </file>
 
 <file path=xl/externalLinks/externalLink77.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45493</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink78.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.15-DEc"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45502</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink79.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3901,86 +4027,6 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink78.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.20-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1">
-        <row r="1">
-          <cell r="C1">
-            <v>5000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>5950</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45511</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink79.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>30000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>36000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45508</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -4012,6 +4058,86 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
+      <sheetName val="MD10000.20-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="1">
+          <cell r="C1">
+            <v>5000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>5950</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>17</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45511</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink81.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD20000.18-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>30000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>36000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45508</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink82.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
@@ -4047,7 +4173,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink81.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink83.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4084,88 +4210,6 @@
         </row>
       </sheetData>
       <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink82.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.15-DEc"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>10000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>12000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45531</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink83.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD10000.20-OCT"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>5000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>6000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>17</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45532</v>
-          </cell>
-        </row>
-      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4203,7 +4247,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45534</v>
+            <v>45531</v>
           </cell>
         </row>
       </sheetData>
@@ -4244,7 +4288,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45536</v>
+            <v>45532</v>
           </cell>
         </row>
       </sheetData>
@@ -4258,25 +4302,26 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
-      <sheetName val="MD20000.22-DEC"/>
+      <sheetName val="MD20000.15-DEc"/>
+      <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
-            <v>20000</v>
+            <v>10000</v>
           </cell>
           <cell r="K1">
             <v>0</v>
           </cell>
           <cell r="O1">
-            <v>24000</v>
+            <v>12000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>120</v>
+            <v>17</v>
           </cell>
           <cell r="O2">
             <v>0</v>
@@ -4284,10 +4329,11 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45535</v>
+            <v>45534</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4301,7 +4347,7 @@
       <sheetName val="MD10000.20-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
@@ -4324,7 +4370,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45549</v>
+            <v>45536</v>
           </cell>
         </row>
       </sheetData>
@@ -4362,9 +4408,9 @@
             <v>0</v>
           </cell>
         </row>
-        <row r="13">
-          <cell r="B13">
-            <v>45562</v>
+        <row r="3">
+          <cell r="B3">
+            <v>45535</v>
           </cell>
         </row>
       </sheetData>
@@ -4378,25 +4424,25 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
-      <sheetName val="MD10000.1-OCT"/>
+      <sheetName val="MD10000.20-OCT"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="C1">
-            <v>10000</v>
+            <v>5000</v>
           </cell>
           <cell r="K1">
             <v>0</v>
           </cell>
           <cell r="O1">
-            <v>12000</v>
+            <v>6000</v>
           </cell>
         </row>
         <row r="2">
           <cell r="K2">
-            <v>120</v>
+            <v>17</v>
           </cell>
           <cell r="O2">
             <v>0</v>
@@ -4404,7 +4450,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45557</v>
+            <v>45549</v>
           </cell>
         </row>
       </sheetData>
@@ -4458,6 +4504,86 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="loanForm"/>
+      <sheetName val="MD20000.22-DEC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>20000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>24000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="B13">
+            <v>45562</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink91.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
+      <sheetName val="MD10000.1-OCT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>10000</v>
+          </cell>
+          <cell r="K1">
+            <v>0</v>
+          </cell>
+          <cell r="O1">
+            <v>12000</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="K2">
+            <v>120</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>45557</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink92.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="loanForm"/>
       <sheetName val="MD20000.18-DEC"/>
     </sheetNames>
     <sheetDataSet>
@@ -4493,7 +4619,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink91.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink93.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4533,7 +4659,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink92.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink94.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4573,7 +4699,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink93.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink95.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4613,7 +4739,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink94.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink96.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4653,7 +4779,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink95.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink97.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4691,7 +4817,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink96.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink98.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4723,86 +4849,6 @@
         <row r="3">
           <cell r="B3">
             <v>45597</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink97.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>30000</v>
-          </cell>
-          <cell r="K1">
-            <v>0</v>
-          </cell>
-          <cell r="O1">
-            <v>36000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>120</v>
-          </cell>
-          <cell r="O2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45602</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink98.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="loanForm"/>
-      <sheetName val="MD20000.18-DEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="C1">
-            <v>50000</v>
-          </cell>
-          <cell r="K1">
-            <v>100</v>
-          </cell>
-          <cell r="O1">
-            <v>10000</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="K2">
-            <v>20</v>
-          </cell>
-          <cell r="O2">
-            <v>50000</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>45612</v>
           </cell>
         </row>
       </sheetData>
@@ -4842,7 +4888,7 @@
         </row>
         <row r="3">
           <cell r="B3">
-            <v>45647</v>
+            <v>45602</v>
           </cell>
         </row>
       </sheetData>
@@ -5106,7 +5152,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5148,12 +5194,12 @@
       <c r="K2" s="33"/>
       <c r="L2" s="34">
         <f>SUM(L5:L47)</f>
-        <v>768200</v>
+        <v>769700</v>
       </c>
       <c r="M2" s="35"/>
       <c r="N2" s="1">
         <f>SUM(N5:N56)</f>
-        <v>43550</v>
+        <v>45300</v>
       </c>
       <c r="Q2" s="1">
         <f>14900+260750</f>
@@ -5209,46 +5255,43 @@
       </c>
     </row>
     <row r="5" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="12">
+      <c r="B5" s="17">
         <v>32</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="19">
         <f>'[1]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13">
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20">
         <f>'[1]MD10000.10-JAN'!$G$1</f>
         <v>48</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="20">
         <f>'[1]MD10000.10-JAN'!$K$2</f>
-        <v>47</v>
-      </c>
-      <c r="J5" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="22">
         <f>'[1]MD10000.10-JAN'!$B$3</f>
         <v>45399</v>
       </c>
-      <c r="L5" s="15">
+      <c r="L5" s="19">
         <f>'[1]MD10000.10-JAN'!$O$2</f>
-        <v>350</v>
-      </c>
-      <c r="M5" s="15">
+        <v>0</v>
+      </c>
+      <c r="M5" s="19">
         <f>'[1]MD10000.10-JAN'!$O$1</f>
-        <v>16450</v>
-      </c>
-      <c r="N5" s="1">
-        <v>350</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="6" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5440,11 +5483,11 @@
       <c r="G10" s="8"/>
       <c r="H10" s="8">
         <f>'[6]MD20000.18-DEC'!$K$1</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I10" s="8">
         <f>'[6]MD20000.18-DEC'!$K$2</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>12</v>
@@ -5455,11 +5498,11 @@
       </c>
       <c r="L10" s="7">
         <f>'[6]MD20000.18-DEC'!$O$2</f>
-        <v>88000</v>
+        <v>84000</v>
       </c>
       <c r="M10" s="7">
         <f>'[6]MD20000.18-DEC'!$O$1</f>
-        <v>72000</v>
+        <v>76000</v>
       </c>
       <c r="N10" s="1">
         <v>4000</v>
@@ -5561,11 +5604,11 @@
       </c>
       <c r="F13" s="8">
         <f>'[10]MD20000.18-DEC'!$K$1</f>
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G13" s="8">
         <f>'[10]MD20000.18-DEC'!$K$2</f>
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
@@ -5578,11 +5621,11 @@
       </c>
       <c r="L13" s="7">
         <f>'[10]MD20000.18-DEC'!$O$2</f>
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="M13" s="7">
         <f>'[10]MD20000.18-DEC'!$O$1</f>
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="N13" s="1">
         <v>700</v>
@@ -5727,11 +5770,11 @@
       </c>
       <c r="F17" s="8">
         <f>'[14]MD20000.18-DEC'!$K$1</f>
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G17" s="8">
         <f>'[14]MD20000.18-DEC'!$K$2</f>
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
@@ -5744,11 +5787,11 @@
       </c>
       <c r="L17" s="7">
         <f>'[14]MD20000.18-DEC'!$O$2</f>
-        <v>2100</v>
+        <v>1400</v>
       </c>
       <c r="M17" s="7">
         <f>'[14]MD20000.18-DEC'!$O$1</f>
-        <v>9900</v>
+        <v>10600</v>
       </c>
       <c r="N17" s="1">
         <v>700</v>
@@ -5770,11 +5813,11 @@
       </c>
       <c r="F18" s="8">
         <f>'[15]MD50000.15-DEC'!$K$1</f>
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G18" s="8">
         <f>'[15]MD50000.15-DEC'!$K$2</f>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
@@ -5787,11 +5830,11 @@
       </c>
       <c r="L18" s="7">
         <f>'[15]MD50000.15-DEC'!$O$2</f>
-        <v>127800</v>
+        <v>126600</v>
       </c>
       <c r="M18" s="7">
         <f>'[15]MD50000.15-DEC'!$O$1</f>
-        <v>32400</v>
+        <v>33600</v>
       </c>
       <c r="N18" s="1">
         <v>4200</v>
@@ -5813,11 +5856,11 @@
       </c>
       <c r="F19" s="8">
         <f>'[16]MD20000.18-DEC'!$K$1</f>
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G19" s="8">
         <f>'[16]MD20000.18-DEC'!$K$2</f>
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -5830,11 +5873,11 @@
       </c>
       <c r="L19" s="7">
         <f>'[16]MD20000.18-DEC'!$O$2</f>
-        <v>18500</v>
+        <v>13500</v>
       </c>
       <c r="M19" s="7">
         <f>'[16]MD20000.18-DEC'!$O$1</f>
-        <v>41500</v>
+        <v>46500</v>
       </c>
       <c r="N19" s="1">
         <v>3500</v>
@@ -5856,11 +5899,11 @@
       </c>
       <c r="F20" s="8">
         <f>'[17]MD20000.18-DEC'!$K$1</f>
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G20" s="8">
         <f>'[17]MD20000.18-DEC'!$K$2</f>
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
@@ -5873,11 +5916,11 @@
       </c>
       <c r="L20" s="7">
         <f>'[17]MD20000.18-DEC'!$O$2</f>
-        <v>4400</v>
+        <v>3700</v>
       </c>
       <c r="M20" s="7">
         <f>'[17]MD20000.18-DEC'!$O$1</f>
-        <v>7600</v>
+        <v>8300</v>
       </c>
       <c r="N20" s="1">
         <v>700</v>
@@ -5899,11 +5942,11 @@
       </c>
       <c r="F21" s="8">
         <f>'[18]MD20000.18-DEC'!$K$1</f>
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G21" s="8">
         <f>'[18]MD20000.18-DEC'!$K$2</f>
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
@@ -5916,11 +5959,11 @@
       </c>
       <c r="L21" s="7">
         <f>'[18]MD20000.18-DEC'!$O$2</f>
-        <v>4400</v>
+        <v>3700</v>
       </c>
       <c r="M21" s="7">
         <f>'[18]MD20000.18-DEC'!$O$1</f>
-        <v>7600</v>
+        <v>8300</v>
       </c>
       <c r="N21" s="1">
         <v>700</v>
@@ -6028,11 +6071,11 @@
       </c>
       <c r="F24" s="8">
         <f>'[21]MD50000.15-DEC'!$K$1</f>
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G24" s="8">
         <f>'[21]MD50000.15-DEC'!$K$2</f>
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
@@ -6045,11 +6088,11 @@
       </c>
       <c r="L24" s="7">
         <f>'[21]MD50000.15-DEC'!$O$2</f>
-        <v>38000</v>
+        <v>34000</v>
       </c>
       <c r="M24" s="7">
         <f>'[21]MD50000.15-DEC'!$O$1</f>
-        <v>22000</v>
+        <v>26000</v>
       </c>
       <c r="N24" s="1">
         <v>3500</v>
@@ -6077,7 +6120,7 @@
       </c>
       <c r="I25" s="8">
         <f>'[22]MD50000.15-DEC'!$K$2</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>12</v>
@@ -6088,11 +6131,11 @@
       </c>
       <c r="L25" s="7">
         <f>'[22]MD50000.15-DEC'!$O$2</f>
-        <v>15400</v>
+        <v>14000</v>
       </c>
       <c r="M25" s="7">
         <f>'[22]MD50000.15-DEC'!$O$1</f>
-        <v>8400</v>
+        <v>9800</v>
       </c>
       <c r="N25" s="1">
         <v>1400</v>
@@ -6120,7 +6163,7 @@
       </c>
       <c r="I26" s="8">
         <f>'[23]MD50000.15-DEC'!$K$2</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J26" s="9" t="s">
         <v>125</v>
@@ -6131,11 +6174,11 @@
       </c>
       <c r="L26" s="7">
         <f>'[23]MD50000.15-DEC'!$O$2</f>
-        <v>16800</v>
+        <v>15400</v>
       </c>
       <c r="M26" s="7">
         <f>'[23]MD50000.15-DEC'!$O$1</f>
-        <v>7000</v>
+        <v>8400</v>
       </c>
       <c r="N26" s="1">
         <v>1400</v>
@@ -6157,11 +6200,11 @@
       </c>
       <c r="F27" s="8">
         <f>'[24]MD20000.18-DEC'!$K$1</f>
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="G27" s="8">
         <f>'[24]MD20000.18-DEC'!$K$2</f>
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
@@ -6174,11 +6217,11 @@
       </c>
       <c r="L27" s="7">
         <f>'[24]MD20000.18-DEC'!$O$2</f>
-        <v>50500</v>
+        <v>47000</v>
       </c>
       <c r="M27" s="7">
         <f>'[24]MD20000.18-DEC'!$O$1</f>
-        <v>9500</v>
+        <v>13000</v>
       </c>
       <c r="N27" s="1">
         <v>3500</v>
@@ -6200,11 +6243,11 @@
       </c>
       <c r="F28" s="8">
         <f>'[25]MD20000.18-DEC'!$K$1</f>
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G28" s="8">
         <f>'[25]MD20000.18-DEC'!$K$2</f>
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
@@ -6217,11 +6260,11 @@
       </c>
       <c r="L28" s="7">
         <f>'[25]MD20000.18-DEC'!$O$2</f>
-        <v>10300</v>
+        <v>9100</v>
       </c>
       <c r="M28" s="7">
         <f>'[25]MD20000.18-DEC'!$O$1</f>
-        <v>1700</v>
+        <v>2900</v>
       </c>
       <c r="N28" s="1">
         <v>700</v>
@@ -6243,11 +6286,11 @@
       </c>
       <c r="F29" s="8">
         <f>'[26]MD20000.18-DEC'!$K$1</f>
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G29" s="8">
         <f>'[26]MD20000.18-DEC'!$K$2</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
@@ -6260,11 +6303,11 @@
       </c>
       <c r="L29" s="7">
         <f>'[26]MD20000.18-DEC'!$O$2</f>
-        <v>39200</v>
+        <v>36750</v>
       </c>
       <c r="M29" s="7">
         <f>'[26]MD20000.18-DEC'!$O$1</f>
-        <v>2800</v>
+        <v>5250</v>
       </c>
       <c r="N29" s="1">
         <v>2450</v>
@@ -6286,11 +6329,11 @@
       </c>
       <c r="F30" s="8">
         <f>'[27]MD20000.18-DEC'!$K$1</f>
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="G30" s="8">
         <f>'[27]MD20000.18-DEC'!$K$2</f>
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
@@ -6303,11 +6346,11 @@
       </c>
       <c r="L30" s="7">
         <f>'[27]MD20000.18-DEC'!$O$2</f>
-        <v>21600</v>
+        <v>19000</v>
       </c>
       <c r="M30" s="7">
         <f>'[27]MD20000.18-DEC'!$O$1</f>
-        <v>2400</v>
+        <v>5000</v>
       </c>
       <c r="N30" s="1">
         <v>1400</v>
@@ -6324,36 +6367,36 @@
         <v>130</v>
       </c>
       <c r="E31" s="7">
-        <f>'[100]MD50000.15-DEC'!$C$1</f>
-        <v>10000</v>
+        <f>'[28]MD50000.15-DEC'!$C$1</f>
+        <v>20000</v>
       </c>
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
       <c r="H31" s="8">
-        <f>'[100]MD50000.15-DEC'!$K$1</f>
+        <f>'[28]MD50000.15-DEC'!$K$1</f>
         <v>17</v>
       </c>
       <c r="I31" s="8">
-        <f>'[100]MD50000.15-DEC'!$K$2</f>
+        <f>'[28]MD50000.15-DEC'!$K$2</f>
         <v>0</v>
       </c>
       <c r="J31" s="9" t="s">
         <v>12</v>
       </c>
       <c r="K31" s="10">
-        <f>'[100]MD50000.15-DEC'!$B$3</f>
+        <f>'[28]MD50000.15-DEC'!$B$3</f>
         <v>0</v>
       </c>
       <c r="L31" s="7">
-        <f>'[100]MD50000.15-DEC'!$O$2</f>
-        <v>11900</v>
+        <f>'[28]MD50000.15-DEC'!$O$2</f>
+        <v>23800</v>
       </c>
       <c r="M31" s="7">
-        <f>'[100]MD50000.15-DEC'!$O$1</f>
+        <f>'[28]MD50000.15-DEC'!$O$1</f>
         <v>0</v>
       </c>
       <c r="N31" s="1">
-        <v>700</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="32" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6367,16 +6410,16 @@
         <v>90</v>
       </c>
       <c r="E32" s="7">
-        <f>'[101]MD20000.18-DEC'!$C$1</f>
+        <f>'[29]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F32" s="8">
-        <f>'[101]MD20000.18-DEC'!$K$1</f>
-        <v>120</v>
+        <f>'[29]MD20000.18-DEC'!$K$1</f>
+        <v>110</v>
       </c>
       <c r="G32" s="8">
-        <f>'[101]MD20000.18-DEC'!$K$2</f>
-        <v>0</v>
+        <f>'[29]MD20000.18-DEC'!$K$2</f>
+        <v>10</v>
       </c>
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
@@ -6384,36 +6427,65 @@
         <v>12</v>
       </c>
       <c r="K32" s="10">
-        <f>'[101]MD20000.18-DEC'!$B$3</f>
-        <v>0</v>
+        <f>'[29]MD20000.18-DEC'!$B$3</f>
+        <v>45716</v>
       </c>
       <c r="L32" s="7">
-        <f>'[101]MD20000.18-DEC'!$O$2</f>
-        <v>24000</v>
+        <f>'[29]MD20000.18-DEC'!$O$2</f>
+        <v>22000</v>
       </c>
       <c r="M32" s="7">
-        <f>'[101]MD20000.18-DEC'!$O$1</f>
-        <v>0</v>
+        <f>'[29]MD20000.18-DEC'!$O$1</f>
+        <v>2000</v>
       </c>
       <c r="N32" s="1">
         <v>1400</v>
       </c>
     </row>
-    <row r="33" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="6"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="7"/>
+    <row r="33" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="6">
+        <v>99</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="E33" s="7">
+        <f>'[102]MD50000.15-DEC'!$C$1</f>
+        <v>20000</v>
+      </c>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="10"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-    </row>
-    <row r="34" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H33" s="8">
+        <f>'[102]MD50000.15-DEC'!$K$1</f>
+        <v>17</v>
+      </c>
+      <c r="I33" s="8">
+        <f>'[102]MD50000.15-DEC'!$K$2</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K33" s="10">
+        <f>'[102]MD50000.15-DEC'!$B$3</f>
+        <v>0</v>
+      </c>
+      <c r="L33" s="7">
+        <f>'[102]MD50000.15-DEC'!$O$2</f>
+        <v>23800</v>
+      </c>
+      <c r="M33" s="7">
+        <f>'[102]MD50000.15-DEC'!$O$1</f>
+        <v>0</v>
+      </c>
+      <c r="N33" s="1">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="6"/>
       <c r="C34" s="8"/>
       <c r="D34" s="14"/>
@@ -6427,7 +6499,7 @@
       <c r="L34" s="7"/>
       <c r="M34" s="7"/>
     </row>
-    <row r="35" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" s="6"/>
       <c r="C35" s="8"/>
       <c r="D35" s="14"/>
@@ -6441,7 +6513,7 @@
       <c r="L35" s="7"/>
       <c r="M35" s="7"/>
     </row>
-    <row r="36" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="6"/>
       <c r="C36" s="8"/>
       <c r="D36" s="14"/>
@@ -6455,7 +6527,7 @@
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
     </row>
-    <row r="37" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B37" s="6"/>
       <c r="C37" s="8"/>
       <c r="D37" s="14"/>
@@ -6469,7 +6541,7 @@
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
     </row>
-    <row r="38" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B38" s="6"/>
       <c r="C38" s="8"/>
       <c r="D38" s="14"/>
@@ -6483,7 +6555,7 @@
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
     </row>
-    <row r="39" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B39" s="6"/>
       <c r="C39" s="8"/>
       <c r="D39" s="14"/>
@@ -6497,7 +6569,7 @@
       <c r="L39" s="7"/>
       <c r="M39" s="7"/>
     </row>
-    <row r="40" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40" s="6"/>
       <c r="C40" s="8"/>
       <c r="D40" s="14"/>
@@ -6511,7 +6583,7 @@
       <c r="L40" s="7"/>
       <c r="M40" s="7"/>
     </row>
-    <row r="41" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B41" s="6"/>
       <c r="C41" s="8"/>
       <c r="D41" s="14"/>
@@ -6525,7 +6597,7 @@
       <c r="L41" s="7"/>
       <c r="M41" s="7"/>
     </row>
-    <row r="42" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="6"/>
       <c r="C42" s="8"/>
       <c r="D42" s="14"/>
@@ -6539,7 +6611,7 @@
       <c r="L42" s="7"/>
       <c r="M42" s="7"/>
     </row>
-    <row r="43" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B43" s="6"/>
       <c r="C43" s="8"/>
       <c r="D43" s="14"/>
@@ -6553,7 +6625,7 @@
       <c r="L43" s="7"/>
       <c r="M43" s="7"/>
     </row>
-    <row r="44" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B44" s="6"/>
       <c r="C44" s="8"/>
       <c r="D44" s="14"/>
@@ -6614,7 +6686,7 @@
       <c r="K2" s="33"/>
       <c r="L2" s="34">
         <f>SUM(L5:L108)</f>
-        <v>677900</v>
+        <v>658250</v>
       </c>
       <c r="M2" s="35"/>
       <c r="N2" s="1">
@@ -6685,15 +6757,15 @@
         <v>18</v>
       </c>
       <c r="E5" s="19">
-        <f>'[28]SM5000.1-SEPT'!$C$1</f>
+        <f>'[30]SM5000.1-SEPT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F5" s="20">
-        <f>'[28]SM5000.1-SEPT'!$K$1</f>
+        <f>'[30]SM5000.1-SEPT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G5" s="20">
-        <f>'[28]SM5000.1-SEPT'!$K$2</f>
+        <f>'[30]SM5000.1-SEPT'!$K$2</f>
         <v>60</v>
       </c>
       <c r="H5" s="20"/>
@@ -6702,15 +6774,15 @@
         <v>22</v>
       </c>
       <c r="K5" s="22">
-        <f>'[28]SM5000.1-SEPT'!$B$3</f>
+        <f>'[30]SM5000.1-SEPT'!$B$3</f>
         <v>45180</v>
       </c>
       <c r="L5" s="19">
-        <f>'[28]SM5000.1-SEPT'!$O$2</f>
+        <f>'[30]SM5000.1-SEPT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M5" s="19">
-        <f>'[28]SM5000.1-SEPT'!$O$1</f>
+        <f>'[30]SM5000.1-SEPT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -6725,15 +6797,15 @@
         <v>18</v>
       </c>
       <c r="E6" s="19">
-        <f>'[28]SM5000.1-oct'!$C$1</f>
+        <f>'[30]SM5000.1-oct'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F6" s="20">
-        <f>'[28]SM5000.1-oct'!$K$1</f>
+        <f>'[30]SM5000.1-oct'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G6" s="20">
-        <f>'[28]SM5000.1-oct'!$K$2</f>
+        <f>'[30]SM5000.1-oct'!$K$2</f>
         <v>60</v>
       </c>
       <c r="H6" s="20"/>
@@ -6742,15 +6814,15 @@
         <v>22</v>
       </c>
       <c r="K6" s="22">
-        <f>'[28]SM5000.1-oct'!$B$3</f>
+        <f>'[30]SM5000.1-oct'!$B$3</f>
         <v>45201</v>
       </c>
       <c r="L6" s="19">
-        <f>'[28]SM5000.1-oct'!$O$2</f>
+        <f>'[30]SM5000.1-oct'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M6" s="19">
-        <f>'[28]SM5000.1-oct'!$O$1</f>
+        <f>'[30]SM5000.1-oct'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -6765,15 +6837,15 @@
         <v>19</v>
       </c>
       <c r="E7" s="19">
-        <f>'[29]MD10000.1-OCT'!$C$1</f>
+        <f>'[31]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F7" s="20">
-        <f>'[29]MD10000.1-OCT'!$K$1</f>
+        <f>'[31]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G7" s="20">
-        <f>'[29]MD10000.1-OCT'!$K$2</f>
+        <f>'[31]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H7" s="20"/>
@@ -6782,15 +6854,15 @@
         <v>22</v>
       </c>
       <c r="K7" s="22">
-        <f>'[29]MD10000.1-OCT'!$B$3</f>
+        <f>'[31]MD10000.1-OCT'!$B$3</f>
         <v>45212</v>
       </c>
       <c r="L7" s="19">
-        <f>'[29]MD10000.1-OCT'!$O$2</f>
+        <f>'[31]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M7" s="19">
-        <f>'[29]MD10000.1-OCT'!$O$1</f>
+        <f>'[31]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -6805,15 +6877,15 @@
         <v>19</v>
       </c>
       <c r="E8" s="19">
-        <f>'[30]MD10000.1-OCT'!$C$1</f>
+        <f>'[32]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F8" s="20">
-        <f>'[30]MD10000.1-OCT'!$K$1</f>
+        <f>'[32]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G8" s="20">
-        <f>'[30]MD10000.1-OCT'!$K$2</f>
+        <f>'[32]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H8" s="20"/>
@@ -6822,15 +6894,15 @@
         <v>22</v>
       </c>
       <c r="K8" s="22">
-        <f>'[30]MD10000.1-OCT'!$B$3</f>
+        <f>'[32]MD10000.1-OCT'!$B$3</f>
         <v>45213</v>
       </c>
       <c r="L8" s="19">
-        <f>'[30]MD10000.1-OCT'!$O$2</f>
+        <f>'[32]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M8" s="19">
-        <f>'[30]MD10000.1-OCT'!$O$1</f>
+        <f>'[32]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -6845,32 +6917,32 @@
         <v>20</v>
       </c>
       <c r="E9" s="19">
-        <f>'[31]MD10000.20-OCT'!$C$1</f>
+        <f>'[33]MD10000.20-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F9" s="20"/>
       <c r="G9" s="20"/>
       <c r="H9" s="20">
-        <f>'[31]MD10000.20-OCT'!$K$1</f>
+        <f>'[33]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I9" s="20">
-        <f>'[31]MD10000.20-OCT'!$K$2</f>
+        <f>'[33]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J9" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K9" s="22">
-        <f>'[31]MD10000.20-OCT'!$B$3</f>
+        <f>'[33]MD10000.20-OCT'!$B$3</f>
         <v>45226</v>
       </c>
       <c r="L9" s="19">
-        <f>'[31]MD10000.20-OCT'!$O$2</f>
+        <f>'[33]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M9" s="19">
-        <f>'[31]MD10000.20-OCT'!$O$1</f>
+        <f>'[33]MD10000.20-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -6885,15 +6957,15 @@
         <v>18</v>
       </c>
       <c r="E10" s="19">
-        <f>'[32]SM5000.1-SEPT (2)'!$C$1</f>
+        <f>'[34]SM5000.1-SEPT (2)'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F10" s="20">
-        <f>'[32]SM5000.1-SEPT (2)'!$K$1</f>
+        <f>'[34]SM5000.1-SEPT (2)'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G10" s="20">
-        <f>'[32]SM5000.1-SEPT (2)'!$K$2</f>
+        <f>'[34]SM5000.1-SEPT (2)'!$K$2</f>
         <v>60</v>
       </c>
       <c r="H10" s="20"/>
@@ -6902,15 +6974,15 @@
         <v>41</v>
       </c>
       <c r="K10" s="22">
-        <f>'[32]SM5000.1-SEPT (2)'!$B$3</f>
+        <f>'[34]SM5000.1-SEPT (2)'!$B$3</f>
         <v>45243</v>
       </c>
       <c r="L10" s="19">
-        <f>'[32]SM5000.1-SEPT (2)'!$O$2</f>
+        <f>'[34]SM5000.1-SEPT (2)'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M10" s="19">
-        <f>'[32]SM5000.1-SEPT (2)'!$O$1</f>
+        <f>'[34]SM5000.1-SEPT (2)'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -6925,32 +6997,32 @@
         <v>20</v>
       </c>
       <c r="E11" s="19">
-        <f>'[33]MD10000.20-OCT'!$C$1</f>
+        <f>'[35]MD10000.20-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F11" s="20"/>
       <c r="G11" s="20"/>
       <c r="H11" s="20">
-        <f>'[33]MD10000.20-OCT'!$K$1</f>
+        <f>'[35]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I11" s="20">
-        <f>'[33]MD10000.20-OCT'!$K$2</f>
+        <f>'[35]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J11" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K11" s="22">
-        <f>'[33]MD10000.20-OCT'!$B$3</f>
+        <f>'[35]MD10000.20-OCT'!$B$3</f>
         <v>45245</v>
       </c>
       <c r="L11" s="19">
-        <f>'[33]MD10000.20-OCT'!$O$2</f>
+        <f>'[35]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M11" s="19">
-        <f>'[33]MD10000.20-OCT'!$O$1</f>
+        <f>'[35]MD10000.20-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -6965,32 +7037,32 @@
         <v>25</v>
       </c>
       <c r="E12" s="19">
-        <f>'[34]MD15000.27-NOV'!$C$1</f>
+        <f>'[36]MD15000.27-NOV'!$C$1</f>
         <v>15000</v>
       </c>
       <c r="F12" s="20"/>
       <c r="G12" s="20"/>
       <c r="H12" s="20">
-        <f>'[34]MD15000.27-NOV'!$K$1</f>
+        <f>'[36]MD15000.27-NOV'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I12" s="20">
-        <f>'[34]MD15000.27-NOV'!$K$2</f>
+        <f>'[36]MD15000.27-NOV'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J12" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K12" s="22">
-        <f>'[34]MD15000.27-NOV'!$B$3</f>
+        <f>'[36]MD15000.27-NOV'!$B$3</f>
         <v>45266</v>
       </c>
       <c r="L12" s="19">
-        <f>'[34]MD15000.27-NOV'!$O$2</f>
+        <f>'[36]MD15000.27-NOV'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M12" s="19">
-        <f>'[34]MD15000.27-NOV'!$O$1</f>
+        <f>'[36]MD15000.27-NOV'!$O$1</f>
         <v>18000</v>
       </c>
     </row>
@@ -7005,32 +7077,32 @@
         <v>29</v>
       </c>
       <c r="E13" s="19">
-        <f>'[35]MD20000.15-DEC'!$C$1</f>
+        <f>'[37]MD20000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F13" s="20"/>
       <c r="G13" s="20"/>
       <c r="H13" s="20">
-        <f>'[35]MD20000.15-DEC'!$K$1</f>
+        <f>'[37]MD20000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I13" s="20">
-        <f>'[35]MD20000.15-DEC'!$K$2</f>
+        <f>'[37]MD20000.15-DEC'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J13" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K13" s="22">
-        <f>'[35]MD20000.15-DEC'!$B$3</f>
+        <f>'[37]MD20000.15-DEC'!$B$3</f>
         <v>45649</v>
       </c>
       <c r="L13" s="19">
-        <f>'[35]MD20000.15-DEC'!$O$2</f>
+        <f>'[37]MD20000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M13" s="19">
-        <f>'[35]MD20000.15-DEC'!$O$1</f>
+        <f>'[37]MD20000.15-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7045,32 +7117,32 @@
         <v>28</v>
       </c>
       <c r="E14" s="19">
-        <f>'[36]MD20000.15-DEc'!$C$1</f>
+        <f>'[38]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F14" s="20"/>
       <c r="G14" s="20"/>
       <c r="H14" s="20">
-        <f>'[36]MD20000.15-DEc'!$K$1</f>
+        <f>'[38]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I14" s="20">
-        <f>'[36]MD20000.15-DEc'!$K$2</f>
+        <f>'[38]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J14" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K14" s="22">
-        <f>'[36]MD20000.15-DEc'!$B$3</f>
+        <f>'[38]MD20000.15-DEc'!$B$3</f>
         <v>45646</v>
       </c>
       <c r="L14" s="19">
-        <f>'[36]MD20000.15-DEc'!$O$2</f>
+        <f>'[38]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M14" s="19">
-        <f>'[36]MD20000.15-DEc'!$O$1</f>
+        <f>'[38]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7085,32 +7157,32 @@
         <v>31</v>
       </c>
       <c r="E15" s="19">
-        <f>'[37]MD50000.15-DEC'!$C$1</f>
+        <f>'[39]MD50000.15-DEC'!$C$1</f>
         <v>50000</v>
       </c>
       <c r="F15" s="20"/>
       <c r="G15" s="20"/>
       <c r="H15" s="20">
-        <f>'[37]MD50000.15-DEC'!$K$1</f>
+        <f>'[39]MD50000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I15" s="20">
-        <f>'[37]MD50000.15-DEC'!$K$2</f>
+        <f>'[39]MD50000.15-DEC'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J15" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K15" s="22">
-        <f>'[37]MD50000.15-DEC'!$B$3</f>
+        <f>'[39]MD50000.15-DEC'!$B$3</f>
         <v>45648</v>
       </c>
       <c r="L15" s="19">
-        <f>'[37]MD50000.15-DEC'!$O$2</f>
+        <f>'[39]MD50000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M15" s="19">
-        <f>'[37]MD50000.15-DEC'!$O$1</f>
+        <f>'[39]MD50000.15-DEC'!$O$1</f>
         <v>84000</v>
       </c>
     </row>
@@ -7125,15 +7197,15 @@
         <v>33</v>
       </c>
       <c r="E16" s="19">
-        <f>'[38]MD20000.18-DEC'!$C$1</f>
+        <f>'[40]MD20000.18-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F16" s="20">
-        <f>'[38]MD20000.18-DEC'!$K$1</f>
+        <f>'[40]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G16" s="20">
-        <f>'[38]MD20000.18-DEC'!$K$2</f>
+        <f>'[40]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H16" s="20"/>
@@ -7142,15 +7214,15 @@
         <v>53</v>
       </c>
       <c r="K16" s="22">
-        <f>'[38]MD20000.18-DEC'!$B$3</f>
+        <f>'[40]MD20000.18-DEC'!$B$3</f>
         <v>45279</v>
       </c>
       <c r="L16" s="19">
-        <f>'[38]MD20000.18-DEC'!$O$2</f>
+        <f>'[40]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M16" s="19">
-        <f>'[38]MD20000.18-DEC'!$O$1</f>
+        <f>'[40]MD20000.18-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7165,15 +7237,15 @@
         <v>33</v>
       </c>
       <c r="E17" s="19">
-        <f>'[39]MD20000.22-DEC'!$C$1</f>
+        <f>'[41]MD20000.22-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F17" s="20">
-        <f>'[39]MD20000.22-DEC'!$K$1</f>
+        <f>'[41]MD20000.22-DEC'!$K$1</f>
         <v>120</v>
       </c>
       <c r="G17" s="20">
-        <f>'[39]MD20000.22-DEC'!$K$2</f>
+        <f>'[41]MD20000.22-DEC'!$K$2</f>
         <v>0</v>
       </c>
       <c r="H17" s="20"/>
@@ -7182,12 +7254,12 @@
         <v>51</v>
       </c>
       <c r="K17" s="22">
-        <f>'[39]MD20000.22-DEC'!$B$3</f>
+        <f>'[41]MD20000.22-DEC'!$B$3</f>
         <v>0</v>
       </c>
       <c r="L17" s="19"/>
       <c r="M17" s="19">
-        <f>'[39]MD20000.22-DEC'!$O$1</f>
+        <f>'[41]MD20000.22-DEC'!$O$1</f>
         <v>0</v>
       </c>
     </row>
@@ -7202,32 +7274,32 @@
         <v>36</v>
       </c>
       <c r="E18" s="19">
-        <f>'[40]MD50000.15-DEC'!$C$1</f>
+        <f>'[42]MD50000.15-DEC'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F18" s="20"/>
       <c r="G18" s="20"/>
       <c r="H18" s="20">
-        <f>'[40]MD50000.15-DEC'!$K$1</f>
+        <f>'[42]MD50000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I18" s="20">
-        <f>'[40]MD50000.15-DEC'!$K$2</f>
+        <f>'[42]MD50000.15-DEC'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J18" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K18" s="22">
-        <f>'[40]MD50000.15-DEC'!$B$3</f>
+        <f>'[42]MD50000.15-DEC'!$B$3</f>
         <v>45310</v>
       </c>
       <c r="L18" s="19">
-        <f>'[40]MD50000.15-DEC'!$O$2</f>
+        <f>'[42]MD50000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M18" s="19">
-        <f>'[40]MD50000.15-DEC'!$O$1</f>
+        <f>'[42]MD50000.15-DEC'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -7242,15 +7314,15 @@
         <v>18</v>
       </c>
       <c r="E19" s="19">
-        <f>'[41]MD5000-Jan24'!$C$1</f>
+        <f>'[43]MD5000-Jan24'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F19" s="20">
-        <f>'[41]MD5000-Jan24'!$K$1</f>
+        <f>'[43]MD5000-Jan24'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G19" s="20">
-        <f>'[41]MD5000-Jan24'!$K$2</f>
+        <f>'[43]MD5000-Jan24'!$K$2</f>
         <v>60</v>
       </c>
       <c r="H19" s="20"/>
@@ -7259,15 +7331,15 @@
         <v>51</v>
       </c>
       <c r="K19" s="22">
-        <f>'[41]MD5000-Jan24'!$B$3</f>
+        <f>'[43]MD5000-Jan24'!$B$3</f>
         <v>45302</v>
       </c>
       <c r="L19" s="19">
-        <f>'[41]MD5000-Jan24'!$O$2</f>
+        <f>'[43]MD5000-Jan24'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M19" s="19">
-        <f>'[41]MD5000-Jan24'!$O$1</f>
+        <f>'[43]MD5000-Jan24'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -7282,32 +7354,32 @@
         <v>39</v>
       </c>
       <c r="E20" s="19">
-        <f>'[42]MD10000.10-JAN'!$C$1</f>
+        <f>'[44]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F20" s="20"/>
       <c r="G20" s="20"/>
       <c r="H20" s="20">
-        <f>'[42]MD10000.10-JAN'!$K$1</f>
+        <f>'[44]MD10000.10-JAN'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I20" s="20">
-        <f>'[42]MD10000.10-JAN'!$K$2</f>
+        <f>'[44]MD10000.10-JAN'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J20" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K20" s="22">
-        <f>'[42]MD10000.10-JAN'!$B$3</f>
+        <f>'[44]MD10000.10-JAN'!$B$3</f>
         <v>45308</v>
       </c>
       <c r="L20" s="19">
-        <f>'[42]MD10000.10-JAN'!$O$2</f>
+        <f>'[44]MD10000.10-JAN'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M20" s="19">
-        <f>'[42]MD10000.10-JAN'!$O$1</f>
+        <f>'[44]MD10000.10-JAN'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -7322,32 +7394,32 @@
         <v>39</v>
       </c>
       <c r="E21" s="19">
-        <f>'[43]MD10000.10-JAN'!$C$1</f>
+        <f>'[45]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F21" s="20"/>
       <c r="G21" s="20"/>
       <c r="H21" s="20">
-        <f>'[43]MD10000.10-JAN'!$K$1</f>
+        <f>'[45]MD10000.10-JAN'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I21" s="20">
-        <f>'[43]MD10000.10-JAN'!$K$2</f>
+        <f>'[45]MD10000.10-JAN'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J21" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K21" s="22">
-        <f>'[43]MD10000.10-JAN'!$B$3</f>
+        <f>'[45]MD10000.10-JAN'!$B$3</f>
         <v>45308</v>
       </c>
       <c r="L21" s="19">
-        <f>'[43]MD10000.10-JAN'!$O$2</f>
+        <f>'[45]MD10000.10-JAN'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M21" s="19">
-        <f>'[43]MD10000.10-JAN'!$O$1</f>
+        <f>'[45]MD10000.10-JAN'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -7362,32 +7434,32 @@
         <v>43</v>
       </c>
       <c r="E22" s="19">
-        <f>'[44]MD10000.20-OCT'!$C$1</f>
+        <f>'[46]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F22" s="20"/>
       <c r="G22" s="20"/>
       <c r="H22" s="20">
-        <f>'[44]MD10000.20-OCT'!$K$1</f>
+        <f>'[46]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I22" s="20">
-        <f>'[44]MD10000.20-OCT'!$K$2</f>
+        <f>'[46]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J22" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K22" s="22">
-        <f>'[44]MD10000.20-OCT'!$B$3</f>
+        <f>'[46]MD10000.20-OCT'!$B$3</f>
         <v>45316</v>
       </c>
       <c r="L22" s="19">
-        <f>'[44]MD10000.20-OCT'!$O$2</f>
+        <f>'[46]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M22" s="19">
-        <f>'[44]MD10000.20-OCT'!$O$1</f>
+        <f>'[46]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -7402,32 +7474,32 @@
         <v>36</v>
       </c>
       <c r="E23" s="19">
-        <f>'[45]MD10000.20-OCT'!$C$1</f>
+        <f>'[47]MD10000.20-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
       <c r="H23" s="20">
-        <f>'[45]MD10000.20-OCT'!$K$1</f>
+        <f>'[47]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I23" s="20">
-        <f>'[45]MD10000.20-OCT'!$K$2</f>
+        <f>'[47]MD10000.20-OCT'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J23" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K23" s="22">
-        <f>'[45]MD10000.20-OCT'!$B$3</f>
+        <f>'[47]MD10000.20-OCT'!$B$3</f>
         <v>45324</v>
       </c>
       <c r="L23" s="19">
-        <f>'[45]MD10000.20-OCT'!$O$2</f>
+        <f>'[47]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M23" s="19">
-        <f>'[45]MD10000.20-OCT'!$O$1</f>
+        <f>'[47]MD10000.20-OCT'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -7442,32 +7514,32 @@
         <v>46</v>
       </c>
       <c r="E24" s="19">
-        <f>'[46]MD10000.20-OCT'!$C$1</f>
+        <f>'[48]MD10000.20-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F24" s="20"/>
       <c r="G24" s="20"/>
       <c r="H24" s="20">
-        <f>'[46]MD10000.20-OCT'!$K$1</f>
+        <f>'[48]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I24" s="20">
-        <f>'[46]MD10000.20-OCT'!$K$2</f>
+        <f>'[48]MD10000.20-OCT'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J24" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K24" s="22">
-        <f>'[46]MD10000.20-OCT'!$B$3</f>
+        <f>'[48]MD10000.20-OCT'!$B$3</f>
         <v>45327</v>
       </c>
       <c r="L24" s="19">
-        <f>'[46]MD10000.20-OCT'!$O$2</f>
+        <f>'[48]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M24" s="19">
-        <f>'[46]MD10000.20-OCT'!$O$1</f>
+        <f>'[48]MD10000.20-OCT'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -7482,15 +7554,15 @@
         <v>18</v>
       </c>
       <c r="E25" s="19">
-        <f>'[47]SM5000.1-oct'!$C$1</f>
+        <f>'[49]SM5000.1-oct'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F25" s="20">
-        <f>'[47]SM5000.1-oct'!$K$1</f>
+        <f>'[49]SM5000.1-oct'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G25" s="20">
-        <f>'[47]SM5000.1-oct'!$K$2</f>
+        <f>'[49]SM5000.1-oct'!$K$2</f>
         <v>60</v>
       </c>
       <c r="H25" s="20"/>
@@ -7499,15 +7571,15 @@
         <v>12</v>
       </c>
       <c r="K25" s="22">
-        <f>'[47]SM5000.1-oct'!$B$3</f>
+        <f>'[49]SM5000.1-oct'!$B$3</f>
         <v>45323</v>
       </c>
       <c r="L25" s="19">
-        <f>'[47]SM5000.1-oct'!$O$2</f>
+        <f>'[49]SM5000.1-oct'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M25" s="19">
-        <f>'[47]SM5000.1-oct'!$O$1</f>
+        <f>'[49]SM5000.1-oct'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -7522,32 +7594,32 @@
         <v>48</v>
       </c>
       <c r="E26" s="19">
-        <f>'[48]MD10000.20-OCT'!$C$1</f>
+        <f>'[50]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F26" s="20"/>
       <c r="G26" s="20"/>
       <c r="H26" s="20">
-        <f>'[48]MD10000.20-OCT'!$K$1</f>
+        <f>'[50]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I26" s="20">
-        <f>'[48]MD10000.20-OCT'!$K$2</f>
+        <f>'[50]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J26" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K26" s="22">
-        <f>'[48]MD10000.20-OCT'!$B$3</f>
+        <f>'[50]MD10000.20-OCT'!$B$3</f>
         <v>45332</v>
       </c>
       <c r="L26" s="19">
-        <f>'[48]MD10000.20-OCT'!$O$2</f>
+        <f>'[50]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M26" s="19">
-        <f>'[48]MD10000.20-OCT'!$O$1</f>
+        <f>'[50]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -7562,15 +7634,15 @@
         <v>19</v>
       </c>
       <c r="E27" s="19">
-        <f>'[49]MD10000.1-OCT'!$C$1</f>
+        <f>'[51]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F27" s="20">
-        <f>'[49]MD10000.1-OCT'!$K$1</f>
+        <f>'[51]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G27" s="20">
-        <f>'[49]MD10000.1-OCT'!$K$2</f>
+        <f>'[51]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H27" s="20"/>
@@ -7579,15 +7651,15 @@
         <v>12</v>
       </c>
       <c r="K27" s="22">
-        <f>'[49]MD10000.1-OCT'!$B$3</f>
+        <f>'[51]MD10000.1-OCT'!$B$3</f>
         <v>45339</v>
       </c>
       <c r="L27" s="19">
-        <f>'[49]MD10000.1-OCT'!$O$2</f>
+        <f>'[51]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M27" s="19">
-        <f>'[49]MD10000.1-OCT'!$O$1</f>
+        <f>'[51]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -7602,15 +7674,15 @@
         <v>19</v>
       </c>
       <c r="E28" s="19">
-        <f>'[50]MD10000.1-OCT'!$C$1</f>
+        <f>'[52]MD10000.1-OCT'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F28" s="20">
-        <f>'[50]MD10000.1-OCT'!$K$1</f>
+        <f>'[52]MD10000.1-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G28" s="20">
-        <f>'[50]MD10000.1-OCT'!$K$2</f>
+        <f>'[52]MD10000.1-OCT'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H28" s="20"/>
@@ -7619,15 +7691,15 @@
         <v>51</v>
       </c>
       <c r="K28" s="22">
-        <f>'[50]MD10000.1-OCT'!$B$3</f>
+        <f>'[52]MD10000.1-OCT'!$B$3</f>
         <v>45334</v>
       </c>
       <c r="L28" s="19">
-        <f>'[50]MD10000.1-OCT'!$O$2</f>
+        <f>'[52]MD10000.1-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M28" s="19">
-        <f>'[50]MD10000.1-OCT'!$O$1</f>
+        <f>'[52]MD10000.1-OCT'!$O$1</f>
         <v>12000</v>
       </c>
     </row>
@@ -7642,32 +7714,32 @@
         <v>50</v>
       </c>
       <c r="E29" s="19">
-        <f>'[51]MD20000.15-DEC'!$C$1</f>
+        <f>'[53]MD20000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
       <c r="H29" s="20">
-        <f>'[51]MD20000.15-DEC'!$K$1</f>
+        <f>'[53]MD20000.15-DEC'!$K$1</f>
         <v>5</v>
       </c>
       <c r="I29" s="20">
-        <f>'[51]MD20000.15-DEC'!$K$2</f>
+        <f>'[53]MD20000.15-DEC'!$K$2</f>
         <v>12</v>
       </c>
       <c r="J29" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K29" s="22">
-        <f>'[51]MD20000.15-DEC'!$B$3</f>
+        <f>'[53]MD20000.15-DEC'!$B$3</f>
         <v>45337</v>
       </c>
       <c r="L29" s="19">
-        <f>'[52]MD20000.15-DEC'!$O$2</f>
+        <f>'[54]MD20000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M29" s="19">
-        <f>'[52]MD20000.15-DEC'!$O$1</f>
+        <f>'[54]MD20000.15-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7682,32 +7754,32 @@
         <v>52</v>
       </c>
       <c r="E30" s="19">
-        <f>'[53]MD20000.15-DEC'!$C$1</f>
+        <f>'[55]MD20000.15-DEC'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F30" s="20"/>
       <c r="G30" s="20"/>
       <c r="H30" s="20">
-        <f>'[53]MD20000.15-DEC'!$K$1</f>
+        <f>'[55]MD20000.15-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I30" s="20">
-        <f>'[53]MD20000.15-DEC'!$K$2</f>
+        <f>'[55]MD20000.15-DEC'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J30" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K30" s="22">
-        <f>'[53]MD20000.15-DEC'!$B$3</f>
+        <f>'[55]MD20000.15-DEC'!$B$3</f>
         <v>45345</v>
       </c>
       <c r="L30" s="19">
-        <f>'[53]MD20000.15-DEC'!$O$2</f>
+        <f>'[55]MD20000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M30" s="19">
-        <f>'[53]MD20000.15-DEC'!$O$1</f>
+        <f>'[55]MD20000.15-DEC'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7722,15 +7794,15 @@
         <v>33</v>
       </c>
       <c r="E31" s="19">
-        <f>'[54]MD20000.18-DEC'!$C$1</f>
+        <f>'[56]MD20000.18-DEC'!$C$1</f>
         <v>30000</v>
       </c>
       <c r="F31" s="20">
-        <f>'[54]MD20000.18-DEC'!$K$1</f>
+        <f>'[56]MD20000.18-DEC'!$K$1</f>
         <v>0</v>
       </c>
       <c r="G31" s="20">
-        <f>'[54]MD20000.18-DEC'!$K$2</f>
+        <f>'[56]MD20000.18-DEC'!$K$2</f>
         <v>120</v>
       </c>
       <c r="H31" s="20"/>
@@ -7739,15 +7811,15 @@
         <v>51</v>
       </c>
       <c r="K31" s="22">
-        <f>'[54]MD20000.18-DEC'!$B$3</f>
+        <f>'[56]MD20000.18-DEC'!$B$3</f>
         <v>45354</v>
       </c>
       <c r="L31" s="19">
-        <f>'[54]MD20000.18-DEC'!$O$2</f>
+        <f>'[56]MD20000.18-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M31" s="19">
-        <f>'[54]MD20000.18-DEC'!$O$1</f>
+        <f>'[56]MD20000.18-DEC'!$O$1</f>
         <v>36000</v>
       </c>
     </row>
@@ -7762,32 +7834,32 @@
         <v>36</v>
       </c>
       <c r="E32" s="19">
-        <f>'[55]MD10000.10-JAN'!$C$1</f>
+        <f>'[57]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F32" s="20"/>
       <c r="G32" s="20"/>
       <c r="H32" s="20">
-        <f>'[55]MD10000.10-JAN'!$K$1</f>
+        <f>'[57]MD10000.10-JAN'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I32" s="20">
-        <f>'[55]MD10000.10-JAN'!$K$2</f>
+        <f>'[57]MD10000.10-JAN'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J32" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K32" s="22">
-        <f>'[55]MD10000.10-JAN'!$B$3</f>
+        <f>'[57]MD10000.10-JAN'!$B$3</f>
         <v>45366</v>
       </c>
       <c r="L32" s="19">
-        <f>'[55]MD10000.10-JAN'!$O$2</f>
+        <f>'[57]MD10000.10-JAN'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M32" s="19">
-        <f>'[55]MD10000.10-JAN'!$O$1</f>
+        <f>'[57]MD10000.10-JAN'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -7802,32 +7874,32 @@
         <v>52</v>
       </c>
       <c r="E33" s="19">
-        <f>'[56]MD20000.15-DEc'!$C$1</f>
+        <f>'[58]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F33" s="20"/>
       <c r="G33" s="20"/>
       <c r="H33" s="20">
-        <f>'[56]MD20000.15-DEc'!$K$1</f>
+        <f>'[58]MD20000.15-DEc'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I33" s="20">
-        <f>'[56]MD20000.15-DEc'!$K$2</f>
+        <f>'[58]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J33" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K33" s="22">
-        <f>'[56]MD20000.15-DEc'!$B$3</f>
+        <f>'[58]MD20000.15-DEc'!$B$3</f>
         <v>45380</v>
       </c>
       <c r="L33" s="19">
-        <f>'[56]MD20000.15-DEc'!$O$2</f>
+        <f>'[58]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M33" s="19">
-        <f>'[56]MD20000.15-DEc'!$O$1</f>
+        <f>'[58]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7842,32 +7914,32 @@
         <v>36</v>
       </c>
       <c r="E34" s="19">
-        <f>'[57]MD10000.10-JAN'!$C$1</f>
+        <f>'[59]MD10000.10-JAN'!$C$1</f>
         <v>10000</v>
       </c>
       <c r="F34" s="20"/>
       <c r="G34" s="20"/>
       <c r="H34" s="20">
-        <f>'[57]MD10000.10-JAN'!$K$1</f>
+        <f>'[59]MD10000.10-JAN'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I34" s="20">
-        <f>'[57]MD10000.10-JAN'!$K$2</f>
+        <f>'[59]MD10000.10-JAN'!$K$2</f>
         <v>48</v>
       </c>
       <c r="J34" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K34" s="22">
-        <f>'[57]MD10000.10-JAN'!$B$3</f>
+        <f>'[59]MD10000.10-JAN'!$B$3</f>
         <v>45389</v>
       </c>
       <c r="L34" s="19">
-        <f>'[57]MD10000.10-JAN'!$O$2</f>
+        <f>'[59]MD10000.10-JAN'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M34" s="19">
-        <f>'[57]MD10000.10-JAN'!$O$1</f>
+        <f>'[59]MD10000.10-JAN'!$O$1</f>
         <v>16800</v>
       </c>
     </row>
@@ -7882,32 +7954,32 @@
         <v>52</v>
       </c>
       <c r="E35" s="19">
-        <f>'[58]MD20000.15-DEc'!$C$1</f>
+        <f>'[60]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F35" s="20"/>
       <c r="G35" s="20"/>
       <c r="H35" s="20">
-        <f>'[58]MD20000.15-DEc'!$G$1</f>
+        <f>'[60]MD20000.15-DEc'!$G$1</f>
         <v>17</v>
       </c>
       <c r="I35" s="20">
-        <f>'[58]MD20000.15-DEc'!$K$2</f>
+        <f>'[60]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J35" s="21" t="s">
         <v>77</v>
       </c>
       <c r="K35" s="22">
-        <f>'[58]MD20000.15-DEc'!$B$3</f>
+        <f>'[60]MD20000.15-DEc'!$B$3</f>
         <v>45394</v>
       </c>
       <c r="L35" s="19">
-        <f>'[58]MD20000.15-DEc'!$O$2</f>
+        <f>'[60]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M35" s="19">
-        <f>'[58]MD20000.15-DEc'!$O$1</f>
+        <f>'[60]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -7933,7 +8005,7 @@
       </c>
       <c r="I36" s="13">
         <f>'[1]MD10000.10-JAN'!$K$2</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J36" s="16" t="s">
         <v>12</v>
@@ -7944,11 +8016,11 @@
       </c>
       <c r="L36" s="15">
         <f>'[1]MD10000.10-JAN'!$O$2</f>
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="M36" s="15">
         <f>'[1]MD10000.10-JAN'!$O$1</f>
-        <v>16450</v>
+        <v>16800</v>
       </c>
       <c r="N36" s="1">
         <v>350</v>
@@ -7965,32 +8037,32 @@
         <v>52</v>
       </c>
       <c r="E37" s="19">
-        <f>'[59]MD20000.15-DEc'!$C$1</f>
+        <f>'[61]MD20000.15-DEc'!$C$1</f>
         <v>20000</v>
       </c>
       <c r="F37" s="20"/>
       <c r="G37" s="20"/>
       <c r="H37" s="20">
-        <f>'[59]MD20000.15-DEc'!$G$1</f>
+        <f>'[61]MD20000.15-DEc'!$G$1</f>
         <v>17</v>
       </c>
       <c r="I37" s="20">
-        <f>'[59]MD20000.15-DEc'!$K$2</f>
+        <f>'[61]MD20000.15-DEc'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J37" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K37" s="22">
-        <f>'[59]MD20000.15-DEc'!$B$3</f>
+        <f>'[61]MD20000.15-DEc'!$B$3</f>
         <v>45406</v>
       </c>
       <c r="L37" s="19">
-        <f>'[59]MD20000.15-DEc'!$O$2</f>
+        <f>'[61]MD20000.15-DEc'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M37" s="19">
-        <f>'[59]MD20000.15-DEc'!$O$1</f>
+        <f>'[61]MD20000.15-DEc'!$O$1</f>
         <v>24000</v>
       </c>
     </row>
@@ -8005,32 +8077,32 @@
         <v>60</v>
       </c>
       <c r="E38" s="19">
-        <f>'[60]MD10000.20-OCT'!$C$1</f>
+        <f>'[62]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F38" s="20"/>
       <c r="G38" s="20"/>
       <c r="H38" s="20">
-        <f>'[60]MD10000.20-OCT'!$G$1</f>
+        <f>'[62]MD10000.20-OCT'!$G$1</f>
         <v>17</v>
       </c>
       <c r="I38" s="20">
-        <f>'[60]MD10000.20-OCT'!$K$2</f>
+        <f>'[62]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J38" s="21" t="s">
         <v>77</v>
       </c>
       <c r="K38" s="22">
-        <f>'[60]MD10000.20-OCT'!$B$3</f>
+        <f>'[62]MD10000.20-OCT'!$B$3</f>
         <v>45406</v>
       </c>
       <c r="L38" s="19">
-        <f>'[60]MD10000.20-OCT'!$O$2</f>
+        <f>'[62]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M38" s="19">
-        <f>'[60]MD10000.20-OCT'!$O$1</f>
+        <f>'[62]MD10000.20-OCT'!$O$1</f>
         <v>5950</v>
       </c>
     </row>
@@ -8045,32 +8117,32 @@
         <v>62</v>
       </c>
       <c r="E39" s="19">
-        <f>'[61]MD50000.15-DEC'!$C$1</f>
+        <f>'[63]MD50000.15-DEC'!$C$1</f>
         <v>40000</v>
       </c>
       <c r="F39" s="20"/>
       <c r="G39" s="20"/>
       <c r="H39" s="20">
-        <f>'[61]MD50000.15-DEC'!$K$1</f>
+        <f>'[63]MD50000.15-DEC'!$K$1</f>
         <v>47</v>
       </c>
       <c r="I39" s="20">
-        <f>'[61]MD50000.15-DEC'!$K$2</f>
+        <f>'[63]MD50000.15-DEC'!$K$2</f>
         <v>1</v>
       </c>
       <c r="J39" s="21" t="s">
         <v>12</v>
       </c>
       <c r="K39" s="22">
-        <f>'[61]MD50000.15-DEC'!$B$3</f>
+        <f>'[63]MD50000.15-DEC'!$B$3</f>
         <v>45416</v>
       </c>
       <c r="L39" s="19">
-        <f>'[62]MD50000.15-DEC'!$O$2</f>
+        <f>'[64]MD50000.15-DEC'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M39" s="19">
-        <f>'[61]MD50000.15-DEC'!$O$1</f>
+        <f>'[63]MD50000.15-DEC'!$O$1</f>
         <v>1400</v>
       </c>
     </row>
@@ -8085,32 +8157,32 @@
         <v>85</v>
       </c>
       <c r="E40" s="19">
-        <f>'[63]MD10000.20-OCT'!$C$1</f>
+        <f>'[65]MD10000.20-OCT'!$C$1</f>
         <v>5000</v>
       </c>
       <c r="F40" s="20"/>
       <c r="G40" s="20"/>
       <c r="H40" s="20">
-        <f>'[63]MD10000.20-OCT'!$K$1</f>
+        <f>'[65]MD10000.20-OCT'!$K$1</f>
         <v>0</v>
       </c>
       <c r="I40" s="20">
-        <f>'[63]MD10000.20-OCT'!$K$2</f>
+        <f>'[65]MD10000.20-OCT'!$K$2</f>
         <v>17</v>
       </c>
       <c r="J40" s="21" t="s">
         <v>51</v>
       </c>
       <c r="K40" s="22">
-        <f>'[63]MD10000.20-OCT'!$B$3</f>
+        <f>'[65]MD10000.20-OCT'!$B$3</f>
         <v>45427</v>
       </c>
       <c r="L40" s="19">
-        <f>'[63]MD10000.20-OCT'!$O$2</f>
+        <f>'[65]MD10000.20-OCT'!$O$2</f>
         <v>0</v>
       </c>
       <c r="M40" s="19">
-        <f>'[63]MD10000.20-OCT'!$O$1</f>
+        <f>'[65]MD10000.20-OCT'!$O$1</f>
         <v>6000</v>
       </c>
     </row>
@@ -8125,15 +8197,15 @@
         <v>33</v>
       </c>
       <c r="E41" s="19">
-        <f>'[64]MD20000.18-DEC'!$C$1</f>
+        <f>'[66]MD20000.18-DEC'!$C$1</f>
  